--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2CEE52-452D-41AC-BD45-7B2950F76299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E029CB-B23D-4E4A-86BF-86C4B1044A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -838,15 +838,6 @@
     <xf numFmtId="2" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -855,6 +846,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5716,22 +5716,22 @@
             <v>16178.560000000001</v>
           </cell>
           <cell r="AA13">
-            <v>10178.75</v>
+            <v>12132.5</v>
           </cell>
           <cell r="AB13">
-            <v>11.687093208891072</v>
+            <v>9.8050690294663099</v>
           </cell>
           <cell r="AC13">
-            <v>1.1687093208891073</v>
+            <v>0.9805069029466309</v>
           </cell>
           <cell r="AD13">
-            <v>1717.25</v>
+            <v>-236.5</v>
           </cell>
           <cell r="AE13">
-            <v>5089.375</v>
+            <v>6066.25</v>
           </cell>
           <cell r="AF13">
-            <v>3372.125</v>
+            <v>6302.75</v>
           </cell>
           <cell r="AG13">
             <v>148.69999999999999</v>
@@ -5808,22 +5808,22 @@
             <v>1163.8800000000001</v>
           </cell>
           <cell r="AA14">
-            <v>703.75</v>
+            <v>786.25</v>
           </cell>
           <cell r="AB14">
-            <v>10.401420959147424</v>
+            <v>9.3100158982511925</v>
           </cell>
           <cell r="AC14">
-            <v>1.0401420959147425</v>
+            <v>0.93100158982511927</v>
           </cell>
           <cell r="AD14">
-            <v>28.25</v>
+            <v>-54.25</v>
           </cell>
           <cell r="AE14">
-            <v>351.875</v>
+            <v>393.125</v>
           </cell>
           <cell r="AF14">
-            <v>323.625</v>
+            <v>447.375</v>
           </cell>
           <cell r="AG14">
             <v>9.15</v>
@@ -5900,22 +5900,22 @@
             <v>8566.5999999999985</v>
           </cell>
           <cell r="AA15">
-            <v>3878.75</v>
+            <v>4708.75</v>
           </cell>
           <cell r="AB15">
-            <v>10.87979374798582</v>
+            <v>8.9620387576320688</v>
           </cell>
           <cell r="AC15">
-            <v>1.087979374798582</v>
+            <v>0.89620387576320681</v>
           </cell>
           <cell r="AD15">
-            <v>341.25</v>
+            <v>-488.75</v>
           </cell>
           <cell r="AE15">
-            <v>1939.375</v>
+            <v>2354.375</v>
           </cell>
           <cell r="AF15">
-            <v>1598.125</v>
+            <v>2843.125</v>
           </cell>
           <cell r="AG15">
             <v>70.333333333333329</v>
@@ -5992,22 +5992,22 @@
             <v>1342.9199999999998</v>
           </cell>
           <cell r="AA16">
-            <v>903.75</v>
+            <v>1082.5</v>
           </cell>
           <cell r="AB16">
-            <v>4.1161825726141075</v>
+            <v>3.4364896073903002</v>
           </cell>
           <cell r="AC16">
-            <v>0.41161825726141077</v>
+            <v>0.34364896073903001</v>
           </cell>
           <cell r="AD16">
-            <v>-531.75</v>
+            <v>-710.5</v>
           </cell>
           <cell r="AE16">
-            <v>451.875</v>
+            <v>541.25</v>
           </cell>
           <cell r="AF16">
-            <v>983.625</v>
+            <v>1251.75</v>
           </cell>
           <cell r="AG16">
             <v>13.285714285714286</v>
@@ -6084,22 +6084,22 @@
             <v>2010.62</v>
           </cell>
           <cell r="AA17">
-            <v>80</v>
+            <v>93.75</v>
           </cell>
           <cell r="AB17">
-            <v>28.625</v>
+            <v>24.426666666666666</v>
           </cell>
           <cell r="AC17">
-            <v>2.8624999999999998</v>
+            <v>2.4426666666666668</v>
           </cell>
           <cell r="AD17">
-            <v>149</v>
+            <v>135.25</v>
           </cell>
           <cell r="AE17">
-            <v>40</v>
+            <v>46.875</v>
           </cell>
           <cell r="AF17">
-            <v>-109</v>
+            <v>-88.375</v>
           </cell>
           <cell r="AG17">
             <v>19.083333333333332</v>
@@ -6176,22 +6176,22 @@
             <v>4077.36</v>
           </cell>
           <cell r="AA18">
-            <v>12571.25</v>
+            <v>14558.75</v>
           </cell>
           <cell r="AB18">
-            <v>5.1482549468032213</v>
+            <v>4.4454365931141062</v>
           </cell>
           <cell r="AC18">
-            <v>0.51482549468032213</v>
+            <v>0.44454365931141065</v>
           </cell>
           <cell r="AD18">
-            <v>-6099.25</v>
+            <v>-8086.75</v>
           </cell>
           <cell r="AE18">
-            <v>6285.625</v>
+            <v>7279.375</v>
           </cell>
           <cell r="AF18">
-            <v>12384.875</v>
+            <v>15366.125</v>
           </cell>
           <cell r="AG18">
             <v>107.86666666666666</v>
@@ -6268,22 +6268,22 @@
             <v>1168.02</v>
           </cell>
           <cell r="AA19">
-            <v>1205</v>
+            <v>1447.5</v>
           </cell>
           <cell r="AB19">
-            <v>15.385892116182573</v>
+            <v>12.808290155440414</v>
           </cell>
           <cell r="AC19">
-            <v>1.5385892116182573</v>
+            <v>1.2808290155440414</v>
           </cell>
           <cell r="AD19">
-            <v>649</v>
+            <v>406.5</v>
           </cell>
           <cell r="AE19">
-            <v>602.5</v>
+            <v>723.75</v>
           </cell>
           <cell r="AF19">
-            <v>-46.5</v>
+            <v>317.25</v>
           </cell>
           <cell r="AG19">
             <v>30.9</v>
@@ -6360,22 +6360,22 @@
             <v>2730.42</v>
           </cell>
           <cell r="AA20">
-            <v>3137.5</v>
+            <v>3460</v>
           </cell>
           <cell r="AB20">
-            <v>13.813545816733068</v>
+            <v>12.526011560693641</v>
           </cell>
           <cell r="AC20">
-            <v>1.3813545816733068</v>
+            <v>1.2526011560693642</v>
           </cell>
           <cell r="AD20">
-            <v>1196.5</v>
+            <v>874</v>
           </cell>
           <cell r="AE20">
-            <v>1568.75</v>
+            <v>1730</v>
           </cell>
           <cell r="AF20">
-            <v>372.25</v>
+            <v>856</v>
           </cell>
           <cell r="AG20">
             <v>72.233333333333334</v>
@@ -6452,22 +6452,22 @@
             <v>10090.130000000001</v>
           </cell>
           <cell r="AA21">
-            <v>5957.5</v>
+            <v>7250</v>
           </cell>
           <cell r="AB21">
-            <v>15.538396978598405</v>
+            <v>12.768275862068965</v>
           </cell>
           <cell r="AC21">
-            <v>1.5538396978598406</v>
+            <v>1.2768275862068965</v>
           </cell>
           <cell r="AD21">
-            <v>3299.5</v>
+            <v>2007</v>
           </cell>
           <cell r="AE21">
-            <v>2978.75</v>
+            <v>3625</v>
           </cell>
           <cell r="AF21">
-            <v>-320.75</v>
+            <v>1618</v>
           </cell>
           <cell r="AG21">
             <v>171.42592592592592</v>
@@ -6544,22 +6544,22 @@
             <v>4768.75</v>
           </cell>
           <cell r="AA22">
-            <v>3410</v>
+            <v>3872.5</v>
           </cell>
           <cell r="AB22">
-            <v>12.829912023460411</v>
+            <v>11.297611362169141</v>
           </cell>
           <cell r="AC22">
-            <v>1.282991202346041</v>
+            <v>1.1297611362169142</v>
           </cell>
           <cell r="AD22">
-            <v>965</v>
+            <v>502.5</v>
           </cell>
           <cell r="AE22">
-            <v>1705</v>
+            <v>1936.25</v>
           </cell>
           <cell r="AF22">
-            <v>740</v>
+            <v>1433.75</v>
           </cell>
           <cell r="AG22">
             <v>81.018518518518519</v>
@@ -6636,22 +6636,22 @@
             <v>42715.839999999997</v>
           </cell>
           <cell r="AA23">
-            <v>30086.25</v>
+            <v>35335</v>
           </cell>
           <cell r="AB23">
-            <v>12.239478166936724</v>
+            <v>10.421395217206735</v>
           </cell>
           <cell r="AC23">
-            <v>1.2239478166936724</v>
+            <v>1.0421395217206735</v>
           </cell>
           <cell r="AD23">
-            <v>6737.75</v>
+            <v>1489</v>
           </cell>
           <cell r="AE23">
-            <v>15043.125</v>
+            <v>17667.5</v>
           </cell>
           <cell r="AF23">
-            <v>8305.375</v>
+            <v>16178.5</v>
           </cell>
           <cell r="AG23">
             <v>681.92592592592598</v>
@@ -6728,22 +6728,22 @@
             <v>27060.48</v>
           </cell>
           <cell r="AA24">
-            <v>19360</v>
+            <v>22485</v>
           </cell>
           <cell r="AB24">
-            <v>12.049586776859504</v>
+            <v>10.374916611074049</v>
           </cell>
           <cell r="AC24">
-            <v>1.2049586776859504</v>
+            <v>1.037491661107405</v>
           </cell>
           <cell r="AD24">
-            <v>3968</v>
+            <v>843</v>
           </cell>
           <cell r="AE24">
-            <v>9680</v>
+            <v>11242.5</v>
           </cell>
           <cell r="AF24">
-            <v>5712</v>
+            <v>10399.5</v>
           </cell>
           <cell r="AG24">
             <v>432</v>
@@ -6820,22 +6820,22 @@
             <v>31054.359999999997</v>
           </cell>
           <cell r="AA25">
-            <v>19323.75</v>
+            <v>22183.75</v>
           </cell>
           <cell r="AB25">
-            <v>13.853936218384113</v>
+            <v>12.067842452245451</v>
           </cell>
           <cell r="AC25">
-            <v>1.3853936218384113</v>
+            <v>1.206784245224545</v>
           </cell>
           <cell r="AD25">
-            <v>7447.25</v>
+            <v>4587.25</v>
           </cell>
           <cell r="AE25">
-            <v>9661.875</v>
+            <v>11091.875</v>
           </cell>
           <cell r="AF25">
-            <v>2214.625</v>
+            <v>6504.625</v>
           </cell>
           <cell r="AG25">
             <v>495.75925925925924</v>
@@ -6912,22 +6912,22 @@
             <v>43143.88</v>
           </cell>
           <cell r="AA26">
-            <v>22578.75</v>
+            <v>26742.5</v>
           </cell>
           <cell r="AB26">
-            <v>16.472568233405305</v>
+            <v>13.907824623726279</v>
           </cell>
           <cell r="AC26">
-            <v>1.6472568233405305</v>
+            <v>1.3907824623726279</v>
           </cell>
           <cell r="AD26">
-            <v>14614.25</v>
+            <v>10450.5</v>
           </cell>
           <cell r="AE26">
-            <v>11289.375</v>
+            <v>13371.25</v>
           </cell>
           <cell r="AF26">
-            <v>-3324.875</v>
+            <v>2920.75</v>
           </cell>
           <cell r="AG26">
             <v>688.75925925925924</v>
@@ -7004,22 +7004,22 @@
             <v>3529.8799999999997</v>
           </cell>
           <cell r="AA27">
-            <v>398.75</v>
+            <v>435</v>
           </cell>
           <cell r="AB27">
-            <v>76.313479623824449</v>
+            <v>69.954022988505741</v>
           </cell>
           <cell r="AC27">
-            <v>7.6313479623824447</v>
+            <v>6.9954022988505749</v>
           </cell>
           <cell r="AD27">
-            <v>2644.25</v>
+            <v>2608</v>
           </cell>
           <cell r="AE27">
-            <v>199.375</v>
+            <v>217.5</v>
           </cell>
           <cell r="AF27">
-            <v>-2444.875</v>
+            <v>-2390.5</v>
           </cell>
           <cell r="AG27">
             <v>56.351851851851855</v>
@@ -7345,22 +7345,22 @@
             <v>7161.2800000000007</v>
           </cell>
           <cell r="AA31">
-            <v>1768.75</v>
+            <v>2222.5</v>
           </cell>
           <cell r="AB31">
-            <v>11.002120141342756</v>
+            <v>8.7559055118110241</v>
           </cell>
           <cell r="AC31">
-            <v>1.1002120141342757</v>
+            <v>0.87559055118110241</v>
           </cell>
           <cell r="AD31">
-            <v>177.25</v>
+            <v>-276.5</v>
           </cell>
           <cell r="AE31">
-            <v>884.375</v>
+            <v>1111.25</v>
           </cell>
           <cell r="AF31">
-            <v>707.125</v>
+            <v>1387.75</v>
           </cell>
           <cell r="AG31">
             <v>121.625</v>
@@ -7437,22 +7437,22 @@
             <v>4791.3600000000006</v>
           </cell>
           <cell r="AA32">
-            <v>1055</v>
+            <v>1297.5</v>
           </cell>
           <cell r="AB32">
-            <v>12.341232227488153</v>
+            <v>10.034682080924856</v>
           </cell>
           <cell r="AC32">
-            <v>1.2341232227488153</v>
+            <v>1.0034682080924855</v>
           </cell>
           <cell r="AD32">
-            <v>247</v>
+            <v>4.5</v>
           </cell>
           <cell r="AE32">
-            <v>527.5</v>
+            <v>648.75</v>
           </cell>
           <cell r="AF32">
-            <v>280.5</v>
+            <v>644.25</v>
           </cell>
           <cell r="AG32">
             <v>81.375</v>
@@ -7529,22 +7529,22 @@
             <v>12284.000000000002</v>
           </cell>
           <cell r="AA33">
-            <v>4278.75</v>
+            <v>5282.5</v>
           </cell>
           <cell r="AB33">
-            <v>6.9179082676015193</v>
+            <v>5.6034074775201139</v>
           </cell>
           <cell r="AC33">
-            <v>0.69179082676015191</v>
+            <v>0.56034074775201137</v>
           </cell>
           <cell r="AD33">
-            <v>-1318.75</v>
+            <v>-2322.5</v>
           </cell>
           <cell r="AE33">
-            <v>2139.375</v>
+            <v>2641.25</v>
           </cell>
           <cell r="AF33">
-            <v>3458.125</v>
+            <v>4963.75</v>
           </cell>
           <cell r="AG33">
             <v>185</v>
@@ -7621,22 +7621,22 @@
             <v>30697.550000000003</v>
           </cell>
           <cell r="AA34">
-            <v>6318.75</v>
+            <v>7961.25</v>
           </cell>
           <cell r="AB34">
-            <v>11.706429277942631</v>
+            <v>9.2912545140524418</v>
           </cell>
           <cell r="AC34">
-            <v>1.1706429277942632</v>
+            <v>0.92912545140524416</v>
           </cell>
           <cell r="AD34">
-            <v>1078.25</v>
+            <v>-564.25</v>
           </cell>
           <cell r="AE34">
-            <v>3159.375</v>
+            <v>3980.625</v>
           </cell>
           <cell r="AF34">
-            <v>2081.125</v>
+            <v>4544.875</v>
           </cell>
           <cell r="AG34">
             <v>462.3125</v>
@@ -7870,22 +7870,22 @@
             <v>16727.059999999998</v>
           </cell>
           <cell r="AA37">
-            <v>5358.75</v>
+            <v>6561.25</v>
           </cell>
           <cell r="AB37">
-            <v>19.149988336832283</v>
+            <v>15.64031244046485</v>
           </cell>
           <cell r="AC37">
-            <v>1.9149988336832284</v>
+            <v>1.564031244046485</v>
           </cell>
           <cell r="AD37">
-            <v>4903.25</v>
+            <v>3700.75</v>
           </cell>
           <cell r="AE37">
-            <v>2679.375</v>
+            <v>3280.625</v>
           </cell>
           <cell r="AF37">
-            <v>-2223.875</v>
+            <v>-420.125</v>
           </cell>
           <cell r="AG37">
             <v>190.03703703703704</v>
@@ -7962,22 +7962,22 @@
             <v>13189.96</v>
           </cell>
           <cell r="AA38">
-            <v>10077.5</v>
+            <v>11485</v>
           </cell>
           <cell r="AB38">
-            <v>8.0297692880178619</v>
+            <v>7.045711797997388</v>
           </cell>
           <cell r="AC38">
-            <v>0.80297692880178617</v>
+            <v>0.70457117979973882</v>
           </cell>
           <cell r="AD38">
-            <v>-1985.5</v>
+            <v>-3393</v>
           </cell>
           <cell r="AE38">
-            <v>5038.75</v>
+            <v>5742.5</v>
           </cell>
           <cell r="AF38">
-            <v>7024.25</v>
+            <v>9135.5</v>
           </cell>
           <cell r="AG38">
             <v>149.85185185185185</v>
@@ -8054,22 +8054,22 @@
             <v>4886.74</v>
           </cell>
           <cell r="AA39">
-            <v>4235</v>
+            <v>5206.25</v>
           </cell>
           <cell r="AB39">
-            <v>7.0791027154663517</v>
+            <v>5.7584633853541414</v>
           </cell>
           <cell r="AC39">
-            <v>0.70791027154663522</v>
+            <v>0.57584633853541412</v>
           </cell>
           <cell r="AD39">
-            <v>-1237</v>
+            <v>-2208.25</v>
           </cell>
           <cell r="AE39">
-            <v>2117.5</v>
+            <v>2603.125</v>
           </cell>
           <cell r="AF39">
-            <v>3354.5</v>
+            <v>4811.375</v>
           </cell>
           <cell r="AG39">
             <v>55.518518518518519</v>
@@ -8146,22 +8146,22 @@
             <v>2934</v>
           </cell>
           <cell r="AA40">
-            <v>3182.5</v>
+            <v>3810</v>
           </cell>
           <cell r="AB40">
-            <v>5.6559308719560093</v>
+            <v>4.7244094488188972</v>
           </cell>
           <cell r="AC40">
-            <v>0.56559308719560097</v>
+            <v>0.47244094488188976</v>
           </cell>
           <cell r="AD40">
-            <v>-1382.5</v>
+            <v>-2010</v>
           </cell>
           <cell r="AE40">
-            <v>1591.25</v>
+            <v>1905</v>
           </cell>
           <cell r="AF40">
-            <v>2973.75</v>
+            <v>3915</v>
           </cell>
           <cell r="AG40">
             <v>33.333333333333336</v>
@@ -8238,22 +8238,22 @@
             <v>6863.4000000000005</v>
           </cell>
           <cell r="AA41">
-            <v>1142.5</v>
+            <v>1361.25</v>
           </cell>
           <cell r="AB41">
-            <v>9.7680525164113785</v>
+            <v>8.1983471074380159</v>
           </cell>
           <cell r="AC41">
-            <v>0.97680525164113785</v>
+            <v>0.81983471074380165</v>
           </cell>
           <cell r="AD41">
-            <v>-26.5</v>
+            <v>-245.25</v>
           </cell>
           <cell r="AE41">
-            <v>571.25</v>
+            <v>680.625</v>
           </cell>
           <cell r="AF41">
-            <v>597.75</v>
+            <v>925.875</v>
           </cell>
           <cell r="AG41">
             <v>20.666666666666668</v>
@@ -8330,22 +8330,22 @@
             <v>9255.75</v>
           </cell>
           <cell r="AA42">
-            <v>936.25</v>
+            <v>1106.25</v>
           </cell>
           <cell r="AB42">
-            <v>16.074766355140188</v>
+            <v>13.604519774011299</v>
           </cell>
           <cell r="AC42">
-            <v>1.6074766355140186</v>
+            <v>1.3604519774011299</v>
           </cell>
           <cell r="AD42">
-            <v>568.75</v>
+            <v>398.75</v>
           </cell>
           <cell r="AE42">
-            <v>468.125</v>
+            <v>553.125</v>
           </cell>
           <cell r="AF42">
-            <v>-100.625</v>
+            <v>154.375</v>
           </cell>
           <cell r="AG42">
             <v>27.87037037037037</v>
@@ -8422,22 +8422,22 @@
             <v>6508.7599999999993</v>
           </cell>
           <cell r="AA43">
-            <v>4292.5</v>
+            <v>6173.75</v>
           </cell>
           <cell r="AB43">
-            <v>13.071636575422248</v>
+            <v>9.0884794492812304</v>
           </cell>
           <cell r="AC43">
-            <v>1.3071636575422247</v>
+            <v>0.90884794492812315</v>
           </cell>
           <cell r="AD43">
-            <v>1318.5</v>
+            <v>-562.75</v>
           </cell>
           <cell r="AE43">
-            <v>2146.25</v>
+            <v>3086.875</v>
           </cell>
           <cell r="AF43">
-            <v>827.75</v>
+            <v>3649.625</v>
           </cell>
           <cell r="AG43">
             <v>103.9074074074074</v>
@@ -8514,22 +8514,22 @@
             <v>11774</v>
           </cell>
           <cell r="AA44">
-            <v>5648.75</v>
+            <v>6892.5</v>
           </cell>
           <cell r="AB44">
-            <v>17.9685771188316</v>
+            <v>14.726151614073268</v>
           </cell>
           <cell r="AC44">
-            <v>1.7968577118831599</v>
+            <v>1.4726151614073268</v>
           </cell>
           <cell r="AD44">
-            <v>4501.25</v>
+            <v>3257.5</v>
           </cell>
           <cell r="AE44">
-            <v>2824.375</v>
+            <v>3446.25</v>
           </cell>
           <cell r="AF44">
-            <v>-1676.875</v>
+            <v>188.75</v>
           </cell>
           <cell r="AG44">
             <v>187.96296296296296</v>
@@ -8606,22 +8606,22 @@
             <v>9532.8799999999992</v>
           </cell>
           <cell r="AA45">
-            <v>7397.5</v>
+            <v>9117.5</v>
           </cell>
           <cell r="AB45">
-            <v>11.109158499493072</v>
+            <v>9.0134357005758154</v>
           </cell>
           <cell r="AC45">
-            <v>1.1109158499493073</v>
+            <v>0.90134357005758159</v>
           </cell>
           <cell r="AD45">
-            <v>820.5</v>
+            <v>-899.5</v>
           </cell>
           <cell r="AE45">
-            <v>3698.75</v>
+            <v>4558.75</v>
           </cell>
           <cell r="AF45">
-            <v>2878.25</v>
+            <v>5458.25</v>
           </cell>
           <cell r="AG45">
             <v>152.18518518518519</v>
@@ -8698,22 +8698,22 @@
             <v>7790.5599999999995</v>
           </cell>
           <cell r="AA46">
-            <v>4765</v>
+            <v>5860</v>
           </cell>
           <cell r="AB46">
-            <v>14.094438614900314</v>
+            <v>11.46075085324232</v>
           </cell>
           <cell r="AC46">
-            <v>1.4094438614900315</v>
+            <v>1.1460750853242321</v>
           </cell>
           <cell r="AD46">
-            <v>1951</v>
+            <v>856</v>
           </cell>
           <cell r="AE46">
-            <v>2382.5</v>
+            <v>2930</v>
           </cell>
           <cell r="AF46">
-            <v>431.5</v>
+            <v>2074</v>
           </cell>
           <cell r="AG46">
             <v>124.37037037037037</v>
@@ -8769,22 +8769,22 @@
             <v>288</v>
           </cell>
           <cell r="AA47">
-            <v>13.75</v>
+            <v>16.25</v>
           </cell>
           <cell r="AB47">
-            <v>11.636363636363637</v>
+            <v>9.8461538461538467</v>
           </cell>
           <cell r="AC47">
-            <v>1.1636363636363636</v>
+            <v>0.98461538461538467</v>
           </cell>
           <cell r="AD47">
-            <v>2.25</v>
+            <v>-0.25</v>
           </cell>
           <cell r="AE47">
-            <v>6.875</v>
+            <v>8.125</v>
           </cell>
           <cell r="AF47">
-            <v>4.625</v>
+            <v>8.375</v>
           </cell>
           <cell r="AG47">
             <v>8</v>
@@ -9190,22 +9190,22 @@
             <v>6486.4800000000005</v>
           </cell>
           <cell r="AA52">
-            <v>2726.25</v>
+            <v>3163.75</v>
           </cell>
           <cell r="AB52">
-            <v>29.373681797340669</v>
+            <v>25.311734492295535</v>
           </cell>
           <cell r="AC52">
-            <v>2.9373681797340669</v>
+            <v>2.5311734492295535</v>
           </cell>
           <cell r="AD52">
-            <v>5281.75</v>
+            <v>4844.25</v>
           </cell>
           <cell r="AE52">
-            <v>1363.125</v>
+            <v>1581.875</v>
           </cell>
           <cell r="AF52">
-            <v>-3918.625</v>
+            <v>-3262.375</v>
           </cell>
           <cell r="AG52">
             <v>667.33333333333337</v>
@@ -9279,22 +9279,22 @@
             <v>5956.7400000000007</v>
           </cell>
           <cell r="AA53">
-            <v>4877.5</v>
+            <v>5653.75</v>
           </cell>
           <cell r="AB53">
-            <v>15.077396207073296</v>
+            <v>13.007296042449701</v>
           </cell>
           <cell r="AC53">
-            <v>1.5077396207073295</v>
+            <v>1.3007296042449701</v>
           </cell>
           <cell r="AD53">
-            <v>2476.5</v>
+            <v>1700.25</v>
           </cell>
           <cell r="AE53">
-            <v>2438.75</v>
+            <v>2826.875</v>
           </cell>
           <cell r="AF53">
-            <v>-37.75</v>
+            <v>1126.625</v>
           </cell>
           <cell r="AG53">
             <v>612.83333333333337</v>
@@ -9368,22 +9368,22 @@
             <v>5804.46</v>
           </cell>
           <cell r="AA54">
-            <v>2813.75</v>
+            <v>3317.5</v>
           </cell>
           <cell r="AB54">
-            <v>25.467792092403375</v>
+            <v>21.600602863602109</v>
           </cell>
           <cell r="AC54">
-            <v>2.5467792092403378</v>
+            <v>2.1600602863602112</v>
           </cell>
           <cell r="AD54">
-            <v>4352.25</v>
+            <v>3848.5</v>
           </cell>
           <cell r="AE54">
-            <v>1406.875</v>
+            <v>1658.75</v>
           </cell>
           <cell r="AF54">
-            <v>-2945.375</v>
+            <v>-2189.75</v>
           </cell>
           <cell r="AG54">
             <v>597.16666666666663</v>
@@ -9457,22 +9457,22 @@
             <v>7047.81</v>
           </cell>
           <cell r="AA55">
-            <v>2270</v>
+            <v>2681.25</v>
           </cell>
           <cell r="AB55">
-            <v>38.330396475770925</v>
+            <v>32.45128205128205</v>
           </cell>
           <cell r="AC55">
-            <v>3.8330396475770927</v>
+            <v>3.2451282051282053</v>
           </cell>
           <cell r="AD55">
-            <v>6431</v>
+            <v>6019.75</v>
           </cell>
           <cell r="AE55">
-            <v>1135</v>
+            <v>1340.625</v>
           </cell>
           <cell r="AF55">
-            <v>-5296</v>
+            <v>-4679.125</v>
           </cell>
           <cell r="AG55">
             <v>725.08333333333337</v>
@@ -9546,22 +9546,22 @@
             <v>1433.14</v>
           </cell>
           <cell r="AA56">
-            <v>431.25</v>
+            <v>522.5</v>
           </cell>
           <cell r="AB56">
-            <v>12.684057971014493</v>
+            <v>10.4688995215311</v>
           </cell>
           <cell r="AC56">
-            <v>1.2684057971014493</v>
+            <v>1.0468899521531101</v>
           </cell>
           <cell r="AD56">
-            <v>115.75</v>
+            <v>24.5</v>
           </cell>
           <cell r="AE56">
-            <v>215.625</v>
+            <v>261.25</v>
           </cell>
           <cell r="AF56">
-            <v>99.875</v>
+            <v>236.75</v>
           </cell>
           <cell r="AG56">
             <v>91.166666666666671</v>
@@ -9635,22 +9635,22 @@
             <v>896.04000000000008</v>
           </cell>
           <cell r="AA57">
-            <v>893.75</v>
+            <v>1036.25</v>
           </cell>
           <cell r="AB57">
-            <v>3.8265734265734266</v>
+            <v>3.3003618817852836</v>
           </cell>
           <cell r="AC57">
-            <v>0.38265734265734264</v>
+            <v>0.33003618817852837</v>
           </cell>
           <cell r="AD57">
-            <v>-551.75</v>
+            <v>-694.25</v>
           </cell>
           <cell r="AE57">
-            <v>446.875</v>
+            <v>518.125</v>
           </cell>
           <cell r="AF57">
-            <v>998.625</v>
+            <v>1212.375</v>
           </cell>
           <cell r="AG57">
             <v>57</v>
@@ -9724,22 +9724,22 @@
             <v>592.12</v>
           </cell>
           <cell r="AA58">
-            <v>603.75</v>
+            <v>673.75</v>
           </cell>
           <cell r="AB58">
-            <v>3.7432712215320909</v>
+            <v>3.3543599257884971</v>
           </cell>
           <cell r="AC58">
-            <v>0.37432712215320912</v>
+            <v>0.33543599257884971</v>
           </cell>
           <cell r="AD58">
-            <v>-377.75</v>
+            <v>-447.75</v>
           </cell>
           <cell r="AE58">
-            <v>301.875</v>
+            <v>336.875</v>
           </cell>
           <cell r="AF58">
-            <v>679.625</v>
+            <v>784.625</v>
           </cell>
           <cell r="AG58">
             <v>37.666666666666664</v>
@@ -9813,22 +9813,22 @@
             <v>503.04</v>
           </cell>
           <cell r="AA59">
-            <v>483.75</v>
+            <v>550</v>
           </cell>
           <cell r="AB59">
-            <v>3.9689922480620154</v>
+            <v>3.4909090909090907</v>
           </cell>
           <cell r="AC59">
-            <v>0.39689922480620154</v>
+            <v>0.34909090909090912</v>
           </cell>
           <cell r="AD59">
-            <v>-291.75</v>
+            <v>-358</v>
           </cell>
           <cell r="AE59">
-            <v>241.875</v>
+            <v>275</v>
           </cell>
           <cell r="AF59">
-            <v>533.625</v>
+            <v>633</v>
           </cell>
           <cell r="AG59">
             <v>32</v>
@@ -10202,212 +10202,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="66" t="s">
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="66"/>
-      <c r="AC1" s="66"/>
-      <c r="AD1" s="66"/>
-      <c r="AE1" s="66"/>
-      <c r="AF1" s="66"/>
-      <c r="AG1" s="66"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="66"/>
-      <c r="AB2" s="66"/>
-      <c r="AC2" s="66"/>
-      <c r="AD2" s="66"/>
-      <c r="AE2" s="66"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
+      <c r="AD2" s="63"/>
+      <c r="AE2" s="63"/>
+      <c r="AF2" s="63"/>
+      <c r="AG2" s="63"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="66"/>
-      <c r="AB3" s="66"/>
-      <c r="AC3" s="66"/>
-      <c r="AD3" s="66"/>
-      <c r="AE3" s="66"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="62"/>
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="63"/>
+      <c r="AD3" s="63"/>
+      <c r="AE3" s="63"/>
+      <c r="AF3" s="63"/>
+      <c r="AG3" s="63"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="66"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="62"/>
+      <c r="Y4" s="62"/>
+      <c r="Z4" s="62"/>
+      <c r="AA4" s="63"/>
+      <c r="AB4" s="63"/>
+      <c r="AC4" s="63"/>
+      <c r="AD4" s="63"/>
+      <c r="AE4" s="63"/>
+      <c r="AF4" s="63"/>
+      <c r="AG4" s="63"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="66"/>
-      <c r="AB5" s="66"/>
-      <c r="AC5" s="66"/>
-      <c r="AD5" s="66"/>
-      <c r="AE5" s="66"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="62"/>
+      <c r="Z5" s="62"/>
+      <c r="AA5" s="63"/>
+      <c r="AB5" s="63"/>
+      <c r="AC5" s="63"/>
+      <c r="AD5" s="63"/>
+      <c r="AE5" s="63"/>
+      <c r="AF5" s="63"/>
+      <c r="AG5" s="63"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="66"/>
-      <c r="AB6" s="66"/>
-      <c r="AC6" s="66"/>
-      <c r="AD6" s="66"/>
-      <c r="AE6" s="66"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="62"/>
+      <c r="X6" s="62"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="63"/>
+      <c r="AB6" s="63"/>
+      <c r="AC6" s="63"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="63"/>
+      <c r="AG6" s="63"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
@@ -10778,27 +10778,27 @@
       </c>
       <c r="AA13" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA13</f>
-        <v>10178.75</v>
+        <v>12132.5</v>
       </c>
       <c r="AB13" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB13</f>
-        <v>11.687093208891072</v>
+        <v>9.8050690294663099</v>
       </c>
       <c r="AC13" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC13</f>
-        <v>1.1687093208891073</v>
+        <v>0.9805069029466309</v>
       </c>
       <c r="AD13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD13</f>
-        <v>1717.25</v>
+        <v>-236.5</v>
       </c>
       <c r="AE13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE13</f>
-        <v>5089.375</v>
+        <v>6066.25</v>
       </c>
       <c r="AF13" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF13</f>
-        <v>3372.125</v>
+        <v>6302.75</v>
       </c>
       <c r="AG13" s="27">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG13</f>
@@ -10906,27 +10906,27 @@
       </c>
       <c r="AA14" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA14</f>
-        <v>703.75</v>
+        <v>786.25</v>
       </c>
       <c r="AB14" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB14</f>
-        <v>10.401420959147424</v>
+        <v>9.3100158982511925</v>
       </c>
       <c r="AC14" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC14</f>
-        <v>1.0401420959147425</v>
+        <v>0.93100158982511927</v>
       </c>
       <c r="AD14" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD14</f>
-        <v>28.25</v>
+        <v>-54.25</v>
       </c>
       <c r="AE14" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE14</f>
-        <v>351.875</v>
+        <v>393.125</v>
       </c>
       <c r="AF14" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF14</f>
-        <v>323.625</v>
+        <v>447.375</v>
       </c>
       <c r="AG14" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG14</f>
@@ -11034,27 +11034,27 @@
       </c>
       <c r="AA15" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA15</f>
-        <v>3878.75</v>
+        <v>4708.75</v>
       </c>
       <c r="AB15" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB15</f>
-        <v>10.87979374798582</v>
+        <v>8.9620387576320688</v>
       </c>
       <c r="AC15" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC15</f>
-        <v>1.087979374798582</v>
+        <v>0.89620387576320681</v>
       </c>
       <c r="AD15" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD15</f>
-        <v>341.25</v>
+        <v>-488.75</v>
       </c>
       <c r="AE15" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE15</f>
-        <v>1939.375</v>
+        <v>2354.375</v>
       </c>
       <c r="AF15" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF15</f>
-        <v>1598.125</v>
+        <v>2843.125</v>
       </c>
       <c r="AG15" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG15</f>
@@ -11162,27 +11162,27 @@
       </c>
       <c r="AA16" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA16</f>
-        <v>903.75</v>
+        <v>1082.5</v>
       </c>
       <c r="AB16" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB16</f>
-        <v>4.1161825726141075</v>
+        <v>3.4364896073903002</v>
       </c>
       <c r="AC16" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC16</f>
-        <v>0.41161825726141077</v>
+        <v>0.34364896073903001</v>
       </c>
       <c r="AD16" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD16</f>
-        <v>-531.75</v>
+        <v>-710.5</v>
       </c>
       <c r="AE16" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE16</f>
-        <v>451.875</v>
+        <v>541.25</v>
       </c>
       <c r="AF16" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF16</f>
-        <v>983.625</v>
+        <v>1251.75</v>
       </c>
       <c r="AG16" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG16</f>
@@ -11290,27 +11290,27 @@
       </c>
       <c r="AA17" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA17</f>
-        <v>80</v>
+        <v>93.75</v>
       </c>
       <c r="AB17" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB17</f>
-        <v>28.625</v>
+        <v>24.426666666666666</v>
       </c>
       <c r="AC17" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC17</f>
-        <v>2.8624999999999998</v>
+        <v>2.4426666666666668</v>
       </c>
       <c r="AD17" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD17</f>
-        <v>149</v>
+        <v>135.25</v>
       </c>
       <c r="AE17" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE17</f>
-        <v>40</v>
+        <v>46.875</v>
       </c>
       <c r="AF17" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF17</f>
-        <v>-109</v>
+        <v>-88.375</v>
       </c>
       <c r="AG17" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG17</f>
@@ -11418,27 +11418,27 @@
       </c>
       <c r="AA18" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA18</f>
-        <v>12571.25</v>
+        <v>14558.75</v>
       </c>
       <c r="AB18" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB18</f>
-        <v>5.1482549468032213</v>
+        <v>4.4454365931141062</v>
       </c>
       <c r="AC18" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC18</f>
-        <v>0.51482549468032213</v>
+        <v>0.44454365931141065</v>
       </c>
       <c r="AD18" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD18</f>
-        <v>-6099.25</v>
+        <v>-8086.75</v>
       </c>
       <c r="AE18" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE18</f>
-        <v>6285.625</v>
+        <v>7279.375</v>
       </c>
       <c r="AF18" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF18</f>
-        <v>12384.875</v>
+        <v>15366.125</v>
       </c>
       <c r="AG18" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG18</f>
@@ -11546,27 +11546,27 @@
       </c>
       <c r="AA19" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA19</f>
-        <v>1205</v>
+        <v>1447.5</v>
       </c>
       <c r="AB19" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB19</f>
-        <v>15.385892116182573</v>
+        <v>12.808290155440414</v>
       </c>
       <c r="AC19" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC19</f>
-        <v>1.5385892116182573</v>
+        <v>1.2808290155440414</v>
       </c>
       <c r="AD19" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD19</f>
-        <v>649</v>
+        <v>406.5</v>
       </c>
       <c r="AE19" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE19</f>
-        <v>602.5</v>
+        <v>723.75</v>
       </c>
       <c r="AF19" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF19</f>
-        <v>-46.5</v>
+        <v>317.25</v>
       </c>
       <c r="AG19" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG19</f>
@@ -11674,27 +11674,27 @@
       </c>
       <c r="AA20" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA20</f>
-        <v>3137.5</v>
+        <v>3460</v>
       </c>
       <c r="AB20" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB20</f>
-        <v>13.813545816733068</v>
+        <v>12.526011560693641</v>
       </c>
       <c r="AC20" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC20</f>
-        <v>1.3813545816733068</v>
+        <v>1.2526011560693642</v>
       </c>
       <c r="AD20" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD20</f>
-        <v>1196.5</v>
+        <v>874</v>
       </c>
       <c r="AE20" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE20</f>
-        <v>1568.75</v>
+        <v>1730</v>
       </c>
       <c r="AF20" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF20</f>
-        <v>372.25</v>
+        <v>856</v>
       </c>
       <c r="AG20" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG20</f>
@@ -11802,27 +11802,27 @@
       </c>
       <c r="AA21" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA21</f>
-        <v>5957.5</v>
+        <v>7250</v>
       </c>
       <c r="AB21" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB21</f>
-        <v>15.538396978598405</v>
+        <v>12.768275862068965</v>
       </c>
       <c r="AC21" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC21</f>
-        <v>1.5538396978598406</v>
+        <v>1.2768275862068965</v>
       </c>
       <c r="AD21" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD21</f>
-        <v>3299.5</v>
+        <v>2007</v>
       </c>
       <c r="AE21" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE21</f>
-        <v>2978.75</v>
+        <v>3625</v>
       </c>
       <c r="AF21" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF21</f>
-        <v>-320.75</v>
+        <v>1618</v>
       </c>
       <c r="AG21" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG21</f>
@@ -11930,27 +11930,27 @@
       </c>
       <c r="AA22" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA22</f>
-        <v>3410</v>
+        <v>3872.5</v>
       </c>
       <c r="AB22" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB22</f>
-        <v>12.829912023460411</v>
+        <v>11.297611362169141</v>
       </c>
       <c r="AC22" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC22</f>
-        <v>1.282991202346041</v>
+        <v>1.1297611362169142</v>
       </c>
       <c r="AD22" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD22</f>
-        <v>965</v>
+        <v>502.5</v>
       </c>
       <c r="AE22" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE22</f>
-        <v>1705</v>
+        <v>1936.25</v>
       </c>
       <c r="AF22" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF22</f>
-        <v>740</v>
+        <v>1433.75</v>
       </c>
       <c r="AG22" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG22</f>
@@ -12058,27 +12058,27 @@
       </c>
       <c r="AA23" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA23</f>
-        <v>30086.25</v>
+        <v>35335</v>
       </c>
       <c r="AB23" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB23</f>
-        <v>12.239478166936724</v>
+        <v>10.421395217206735</v>
       </c>
       <c r="AC23" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC23</f>
-        <v>1.2239478166936724</v>
+        <v>1.0421395217206735</v>
       </c>
       <c r="AD23" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD23</f>
-        <v>6737.75</v>
+        <v>1489</v>
       </c>
       <c r="AE23" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE23</f>
-        <v>15043.125</v>
+        <v>17667.5</v>
       </c>
       <c r="AF23" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF23</f>
-        <v>8305.375</v>
+        <v>16178.5</v>
       </c>
       <c r="AG23" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG23</f>
@@ -12186,27 +12186,27 @@
       </c>
       <c r="AA24" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA24</f>
-        <v>19360</v>
+        <v>22485</v>
       </c>
       <c r="AB24" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB24</f>
-        <v>12.049586776859504</v>
+        <v>10.374916611074049</v>
       </c>
       <c r="AC24" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC24</f>
-        <v>1.2049586776859504</v>
+        <v>1.037491661107405</v>
       </c>
       <c r="AD24" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD24</f>
-        <v>3968</v>
+        <v>843</v>
       </c>
       <c r="AE24" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE24</f>
-        <v>9680</v>
+        <v>11242.5</v>
       </c>
       <c r="AF24" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF24</f>
-        <v>5712</v>
+        <v>10399.5</v>
       </c>
       <c r="AG24" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG24</f>
@@ -12314,27 +12314,27 @@
       </c>
       <c r="AA25" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA25</f>
-        <v>19323.75</v>
+        <v>22183.75</v>
       </c>
       <c r="AB25" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB25</f>
-        <v>13.853936218384113</v>
+        <v>12.067842452245451</v>
       </c>
       <c r="AC25" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC25</f>
-        <v>1.3853936218384113</v>
+        <v>1.206784245224545</v>
       </c>
       <c r="AD25" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD25</f>
-        <v>7447.25</v>
+        <v>4587.25</v>
       </c>
       <c r="AE25" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE25</f>
-        <v>9661.875</v>
+        <v>11091.875</v>
       </c>
       <c r="AF25" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF25</f>
-        <v>2214.625</v>
+        <v>6504.625</v>
       </c>
       <c r="AG25" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG25</f>
@@ -12442,27 +12442,27 @@
       </c>
       <c r="AA26" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA26</f>
-        <v>22578.75</v>
+        <v>26742.5</v>
       </c>
       <c r="AB26" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB26</f>
-        <v>16.472568233405305</v>
+        <v>13.907824623726279</v>
       </c>
       <c r="AC26" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC26</f>
-        <v>1.6472568233405305</v>
+        <v>1.3907824623726279</v>
       </c>
       <c r="AD26" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD26</f>
-        <v>14614.25</v>
+        <v>10450.5</v>
       </c>
       <c r="AE26" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE26</f>
-        <v>11289.375</v>
+        <v>13371.25</v>
       </c>
       <c r="AF26" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF26</f>
-        <v>-3324.875</v>
+        <v>2920.75</v>
       </c>
       <c r="AG26" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG26</f>
@@ -12570,27 +12570,27 @@
       </c>
       <c r="AA27" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA27</f>
-        <v>398.75</v>
+        <v>435</v>
       </c>
       <c r="AB27" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB27</f>
-        <v>76.313479623824449</v>
+        <v>69.954022988505741</v>
       </c>
       <c r="AC27" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC27</f>
-        <v>7.6313479623824447</v>
+        <v>6.9954022988505749</v>
       </c>
       <c r="AD27" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD27</f>
-        <v>2644.25</v>
+        <v>2608</v>
       </c>
       <c r="AE27" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE27</f>
-        <v>199.375</v>
+        <v>217.5</v>
       </c>
       <c r="AF27" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF27</f>
-        <v>-2444.875</v>
+        <v>-2390.5</v>
       </c>
       <c r="AG27" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG27</f>
@@ -13073,27 +13073,27 @@
       </c>
       <c r="AA31" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA31</f>
-        <v>1768.75</v>
+        <v>2222.5</v>
       </c>
       <c r="AB31" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB31</f>
-        <v>11.002120141342756</v>
+        <v>8.7559055118110241</v>
       </c>
       <c r="AC31" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC31</f>
-        <v>1.1002120141342757</v>
+        <v>0.87559055118110241</v>
       </c>
       <c r="AD31" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD31</f>
-        <v>177.25</v>
+        <v>-276.5</v>
       </c>
       <c r="AE31" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE31</f>
-        <v>884.375</v>
+        <v>1111.25</v>
       </c>
       <c r="AF31" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF31</f>
-        <v>707.125</v>
+        <v>1387.75</v>
       </c>
       <c r="AG31" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG31</f>
@@ -13201,27 +13201,27 @@
       </c>
       <c r="AA32" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA32</f>
-        <v>1055</v>
+        <v>1297.5</v>
       </c>
       <c r="AB32" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB32</f>
-        <v>12.341232227488153</v>
+        <v>10.034682080924856</v>
       </c>
       <c r="AC32" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC32</f>
-        <v>1.2341232227488153</v>
+        <v>1.0034682080924855</v>
       </c>
       <c r="AD32" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD32</f>
-        <v>247</v>
+        <v>4.5</v>
       </c>
       <c r="AE32" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE32</f>
-        <v>527.5</v>
+        <v>648.75</v>
       </c>
       <c r="AF32" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF32</f>
-        <v>280.5</v>
+        <v>644.25</v>
       </c>
       <c r="AG32" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG32</f>
@@ -13329,27 +13329,27 @@
       </c>
       <c r="AA33" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA33</f>
-        <v>4278.75</v>
+        <v>5282.5</v>
       </c>
       <c r="AB33" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB33</f>
-        <v>6.9179082676015193</v>
+        <v>5.6034074775201139</v>
       </c>
       <c r="AC33" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC33</f>
-        <v>0.69179082676015191</v>
+        <v>0.56034074775201137</v>
       </c>
       <c r="AD33" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD33</f>
-        <v>-1318.75</v>
+        <v>-2322.5</v>
       </c>
       <c r="AE33" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE33</f>
-        <v>2139.375</v>
+        <v>2641.25</v>
       </c>
       <c r="AF33" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF33</f>
-        <v>3458.125</v>
+        <v>4963.75</v>
       </c>
       <c r="AG33" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG33</f>
@@ -13457,27 +13457,27 @@
       </c>
       <c r="AA34" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA34</f>
-        <v>6318.75</v>
+        <v>7961.25</v>
       </c>
       <c r="AB34" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB34</f>
-        <v>11.706429277942631</v>
+        <v>9.2912545140524418</v>
       </c>
       <c r="AC34" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC34</f>
-        <v>1.1706429277942632</v>
+        <v>0.92912545140524416</v>
       </c>
       <c r="AD34" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD34</f>
-        <v>1078.25</v>
+        <v>-564.25</v>
       </c>
       <c r="AE34" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE34</f>
-        <v>3159.375</v>
+        <v>3980.625</v>
       </c>
       <c r="AF34" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF34</f>
-        <v>2081.125</v>
+        <v>4544.875</v>
       </c>
       <c r="AG34" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG34</f>
@@ -13832,27 +13832,27 @@
       </c>
       <c r="AA37" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA37</f>
-        <v>5358.75</v>
+        <v>6561.25</v>
       </c>
       <c r="AB37" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB37</f>
-        <v>19.149988336832283</v>
+        <v>15.64031244046485</v>
       </c>
       <c r="AC37" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC37</f>
-        <v>1.9149988336832284</v>
+        <v>1.564031244046485</v>
       </c>
       <c r="AD37" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD37</f>
-        <v>4903.25</v>
+        <v>3700.75</v>
       </c>
       <c r="AE37" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE37</f>
-        <v>2679.375</v>
+        <v>3280.625</v>
       </c>
       <c r="AF37" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF37</f>
-        <v>-2223.875</v>
+        <v>-420.125</v>
       </c>
       <c r="AG37" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG37</f>
@@ -13960,27 +13960,27 @@
       </c>
       <c r="AA38" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA38</f>
-        <v>10077.5</v>
+        <v>11485</v>
       </c>
       <c r="AB38" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB38</f>
-        <v>8.0297692880178619</v>
+        <v>7.045711797997388</v>
       </c>
       <c r="AC38" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC38</f>
-        <v>0.80297692880178617</v>
+        <v>0.70457117979973882</v>
       </c>
       <c r="AD38" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD38</f>
-        <v>-1985.5</v>
+        <v>-3393</v>
       </c>
       <c r="AE38" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE38</f>
-        <v>5038.75</v>
+        <v>5742.5</v>
       </c>
       <c r="AF38" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF38</f>
-        <v>7024.25</v>
+        <v>9135.5</v>
       </c>
       <c r="AG38" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG38</f>
@@ -14088,27 +14088,27 @@
       </c>
       <c r="AA39" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA39</f>
-        <v>4235</v>
+        <v>5206.25</v>
       </c>
       <c r="AB39" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB39</f>
-        <v>7.0791027154663517</v>
+        <v>5.7584633853541414</v>
       </c>
       <c r="AC39" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC39</f>
-        <v>0.70791027154663522</v>
+        <v>0.57584633853541412</v>
       </c>
       <c r="AD39" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD39</f>
-        <v>-1237</v>
+        <v>-2208.25</v>
       </c>
       <c r="AE39" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE39</f>
-        <v>2117.5</v>
+        <v>2603.125</v>
       </c>
       <c r="AF39" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF39</f>
-        <v>3354.5</v>
+        <v>4811.375</v>
       </c>
       <c r="AG39" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG39</f>
@@ -14216,27 +14216,27 @@
       </c>
       <c r="AA40" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA40</f>
-        <v>3182.5</v>
+        <v>3810</v>
       </c>
       <c r="AB40" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB40</f>
-        <v>5.6559308719560093</v>
+        <v>4.7244094488188972</v>
       </c>
       <c r="AC40" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC40</f>
-        <v>0.56559308719560097</v>
+        <v>0.47244094488188976</v>
       </c>
       <c r="AD40" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD40</f>
-        <v>-1382.5</v>
+        <v>-2010</v>
       </c>
       <c r="AE40" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE40</f>
-        <v>1591.25</v>
+        <v>1905</v>
       </c>
       <c r="AF40" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF40</f>
-        <v>2973.75</v>
+        <v>3915</v>
       </c>
       <c r="AG40" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG40</f>
@@ -14344,27 +14344,27 @@
       </c>
       <c r="AA41" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA41</f>
-        <v>1142.5</v>
+        <v>1361.25</v>
       </c>
       <c r="AB41" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB41</f>
-        <v>9.7680525164113785</v>
+        <v>8.1983471074380159</v>
       </c>
       <c r="AC41" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC41</f>
-        <v>0.97680525164113785</v>
+        <v>0.81983471074380165</v>
       </c>
       <c r="AD41" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD41</f>
-        <v>-26.5</v>
+        <v>-245.25</v>
       </c>
       <c r="AE41" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE41</f>
-        <v>571.25</v>
+        <v>680.625</v>
       </c>
       <c r="AF41" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF41</f>
-        <v>597.75</v>
+        <v>925.875</v>
       </c>
       <c r="AG41" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG41</f>
@@ -14472,27 +14472,27 @@
       </c>
       <c r="AA42" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA42</f>
-        <v>936.25</v>
+        <v>1106.25</v>
       </c>
       <c r="AB42" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB42</f>
-        <v>16.074766355140188</v>
+        <v>13.604519774011299</v>
       </c>
       <c r="AC42" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC42</f>
-        <v>1.6074766355140186</v>
+        <v>1.3604519774011299</v>
       </c>
       <c r="AD42" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD42</f>
-        <v>568.75</v>
+        <v>398.75</v>
       </c>
       <c r="AE42" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE42</f>
-        <v>468.125</v>
+        <v>553.125</v>
       </c>
       <c r="AF42" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF42</f>
-        <v>-100.625</v>
+        <v>154.375</v>
       </c>
       <c r="AG42" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG42</f>
@@ -14600,27 +14600,27 @@
       </c>
       <c r="AA43" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA43</f>
-        <v>4292.5</v>
+        <v>6173.75</v>
       </c>
       <c r="AB43" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB43</f>
-        <v>13.071636575422248</v>
+        <v>9.0884794492812304</v>
       </c>
       <c r="AC43" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC43</f>
-        <v>1.3071636575422247</v>
+        <v>0.90884794492812315</v>
       </c>
       <c r="AD43" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD43</f>
-        <v>1318.5</v>
+        <v>-562.75</v>
       </c>
       <c r="AE43" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE43</f>
-        <v>2146.25</v>
+        <v>3086.875</v>
       </c>
       <c r="AF43" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF43</f>
-        <v>827.75</v>
+        <v>3649.625</v>
       </c>
       <c r="AG43" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG43</f>
@@ -14728,27 +14728,27 @@
       </c>
       <c r="AA44" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA44</f>
-        <v>5648.75</v>
+        <v>6892.5</v>
       </c>
       <c r="AB44" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB44</f>
-        <v>17.9685771188316</v>
+        <v>14.726151614073268</v>
       </c>
       <c r="AC44" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC44</f>
-        <v>1.7968577118831599</v>
+        <v>1.4726151614073268</v>
       </c>
       <c r="AD44" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD44</f>
-        <v>4501.25</v>
+        <v>3257.5</v>
       </c>
       <c r="AE44" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE44</f>
-        <v>2824.375</v>
+        <v>3446.25</v>
       </c>
       <c r="AF44" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF44</f>
-        <v>-1676.875</v>
+        <v>188.75</v>
       </c>
       <c r="AG44" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG44</f>
@@ -14856,27 +14856,27 @@
       </c>
       <c r="AA45" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA45</f>
-        <v>7397.5</v>
+        <v>9117.5</v>
       </c>
       <c r="AB45" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB45</f>
-        <v>11.109158499493072</v>
+        <v>9.0134357005758154</v>
       </c>
       <c r="AC45" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC45</f>
-        <v>1.1109158499493073</v>
+        <v>0.90134357005758159</v>
       </c>
       <c r="AD45" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD45</f>
-        <v>820.5</v>
+        <v>-899.5</v>
       </c>
       <c r="AE45" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE45</f>
-        <v>3698.75</v>
+        <v>4558.75</v>
       </c>
       <c r="AF45" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF45</f>
-        <v>2878.25</v>
+        <v>5458.25</v>
       </c>
       <c r="AG45" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG45</f>
@@ -14984,27 +14984,27 @@
       </c>
       <c r="AA46" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA46</f>
-        <v>4765</v>
+        <v>5860</v>
       </c>
       <c r="AB46" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB46</f>
-        <v>14.094438614900314</v>
+        <v>11.46075085324232</v>
       </c>
       <c r="AC46" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC46</f>
-        <v>1.4094438614900315</v>
+        <v>1.1460750853242321</v>
       </c>
       <c r="AD46" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD46</f>
-        <v>1951</v>
+        <v>856</v>
       </c>
       <c r="AE46" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE46</f>
-        <v>2382.5</v>
+        <v>2930</v>
       </c>
       <c r="AF46" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF46</f>
-        <v>431.5</v>
+        <v>2074</v>
       </c>
       <c r="AG46" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG46</f>
@@ -15105,27 +15105,27 @@
       </c>
       <c r="AA47" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA47</f>
-        <v>13.75</v>
+        <v>16.25</v>
       </c>
       <c r="AB47" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB47</f>
-        <v>11.636363636363637</v>
+        <v>9.8461538461538467</v>
       </c>
       <c r="AC47" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC47</f>
-        <v>1.1636363636363636</v>
+        <v>0.98461538461538467</v>
       </c>
       <c r="AD47" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD47</f>
-        <v>2.25</v>
+        <v>-0.25</v>
       </c>
       <c r="AE47" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE47</f>
-        <v>6.875</v>
+        <v>8.125</v>
       </c>
       <c r="AF47" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF47</f>
-        <v>4.625</v>
+        <v>8.375</v>
       </c>
       <c r="AG47" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG47</f>
@@ -15733,27 +15733,27 @@
       </c>
       <c r="AA52" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA52</f>
-        <v>2726.25</v>
+        <v>3163.75</v>
       </c>
       <c r="AB52" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB52</f>
-        <v>29.373681797340669</v>
+        <v>25.311734492295535</v>
       </c>
       <c r="AC52" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC52</f>
-        <v>2.9373681797340669</v>
+        <v>2.5311734492295535</v>
       </c>
       <c r="AD52" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD52</f>
-        <v>5281.75</v>
+        <v>4844.25</v>
       </c>
       <c r="AE52" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE52</f>
-        <v>1363.125</v>
+        <v>1581.875</v>
       </c>
       <c r="AF52" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF52</f>
-        <v>-3918.625</v>
+        <v>-3262.375</v>
       </c>
       <c r="AG52" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG52</f>
@@ -15861,27 +15861,27 @@
       </c>
       <c r="AA53" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA53</f>
-        <v>4877.5</v>
+        <v>5653.75</v>
       </c>
       <c r="AB53" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB53</f>
-        <v>15.077396207073296</v>
+        <v>13.007296042449701</v>
       </c>
       <c r="AC53" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC53</f>
-        <v>1.5077396207073295</v>
+        <v>1.3007296042449701</v>
       </c>
       <c r="AD53" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD53</f>
-        <v>2476.5</v>
+        <v>1700.25</v>
       </c>
       <c r="AE53" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE53</f>
-        <v>2438.75</v>
+        <v>2826.875</v>
       </c>
       <c r="AF53" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF53</f>
-        <v>-37.75</v>
+        <v>1126.625</v>
       </c>
       <c r="AG53" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG53</f>
@@ -15989,27 +15989,27 @@
       </c>
       <c r="AA54" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA54</f>
-        <v>2813.75</v>
+        <v>3317.5</v>
       </c>
       <c r="AB54" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB54</f>
-        <v>25.467792092403375</v>
+        <v>21.600602863602109</v>
       </c>
       <c r="AC54" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC54</f>
-        <v>2.5467792092403378</v>
+        <v>2.1600602863602112</v>
       </c>
       <c r="AD54" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD54</f>
-        <v>4352.25</v>
+        <v>3848.5</v>
       </c>
       <c r="AE54" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE54</f>
-        <v>1406.875</v>
+        <v>1658.75</v>
       </c>
       <c r="AF54" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF54</f>
-        <v>-2945.375</v>
+        <v>-2189.75</v>
       </c>
       <c r="AG54" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG54</f>
@@ -16117,27 +16117,27 @@
       </c>
       <c r="AA55" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA55</f>
-        <v>2270</v>
+        <v>2681.25</v>
       </c>
       <c r="AB55" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB55</f>
-        <v>38.330396475770925</v>
+        <v>32.45128205128205</v>
       </c>
       <c r="AC55" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC55</f>
-        <v>3.8330396475770927</v>
+        <v>3.2451282051282053</v>
       </c>
       <c r="AD55" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD55</f>
-        <v>6431</v>
+        <v>6019.75</v>
       </c>
       <c r="AE55" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE55</f>
-        <v>1135</v>
+        <v>1340.625</v>
       </c>
       <c r="AF55" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF55</f>
-        <v>-5296</v>
+        <v>-4679.125</v>
       </c>
       <c r="AG55" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG55</f>
@@ -16245,27 +16245,27 @@
       </c>
       <c r="AA56" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA56</f>
-        <v>431.25</v>
+        <v>522.5</v>
       </c>
       <c r="AB56" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB56</f>
-        <v>12.684057971014493</v>
+        <v>10.4688995215311</v>
       </c>
       <c r="AC56" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC56</f>
-        <v>1.2684057971014493</v>
+        <v>1.0468899521531101</v>
       </c>
       <c r="AD56" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD56</f>
-        <v>115.75</v>
+        <v>24.5</v>
       </c>
       <c r="AE56" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE56</f>
-        <v>215.625</v>
+        <v>261.25</v>
       </c>
       <c r="AF56" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF56</f>
-        <v>99.875</v>
+        <v>236.75</v>
       </c>
       <c r="AG56" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG56</f>
@@ -16373,27 +16373,27 @@
       </c>
       <c r="AA57" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA57</f>
-        <v>893.75</v>
+        <v>1036.25</v>
       </c>
       <c r="AB57" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB57</f>
-        <v>3.8265734265734266</v>
+        <v>3.3003618817852836</v>
       </c>
       <c r="AC57" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC57</f>
-        <v>0.38265734265734264</v>
+        <v>0.33003618817852837</v>
       </c>
       <c r="AD57" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD57</f>
-        <v>-551.75</v>
+        <v>-694.25</v>
       </c>
       <c r="AE57" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE57</f>
-        <v>446.875</v>
+        <v>518.125</v>
       </c>
       <c r="AF57" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF57</f>
-        <v>998.625</v>
+        <v>1212.375</v>
       </c>
       <c r="AG57" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG57</f>
@@ -16501,27 +16501,27 @@
       </c>
       <c r="AA58" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA58</f>
-        <v>603.75</v>
+        <v>673.75</v>
       </c>
       <c r="AB58" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB58</f>
-        <v>3.7432712215320909</v>
+        <v>3.3543599257884971</v>
       </c>
       <c r="AC58" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC58</f>
-        <v>0.37432712215320912</v>
+        <v>0.33543599257884971</v>
       </c>
       <c r="AD58" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD58</f>
-        <v>-377.75</v>
+        <v>-447.75</v>
       </c>
       <c r="AE58" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE58</f>
-        <v>301.875</v>
+        <v>336.875</v>
       </c>
       <c r="AF58" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF58</f>
-        <v>679.625</v>
+        <v>784.625</v>
       </c>
       <c r="AG58" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG58</f>
@@ -16629,27 +16629,27 @@
       </c>
       <c r="AA59" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA59</f>
-        <v>483.75</v>
+        <v>550</v>
       </c>
       <c r="AB59" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB59</f>
-        <v>3.9689922480620154</v>
+        <v>3.4909090909090907</v>
       </c>
       <c r="AC59" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC59</f>
-        <v>0.39689922480620154</v>
+        <v>0.34909090909090912</v>
       </c>
       <c r="AD59" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD59</f>
-        <v>-291.75</v>
+        <v>-358</v>
       </c>
       <c r="AE59" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE59</f>
-        <v>241.875</v>
+        <v>275</v>
       </c>
       <c r="AF59" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF59</f>
-        <v>533.625</v>
+        <v>633</v>
       </c>
       <c r="AG59" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG59</f>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AF60" s="44">
         <f ca="1">SUMIF(AF13:AF59,"&gt;0")</f>
-        <v>69418.375</v>
+        <v>118775.375</v>
       </c>
     </row>
     <row r="61" spans="2:33" x14ac:dyDescent="0.25">
@@ -16697,10 +16697,10 @@
       </c>
       <c r="C61" s="46"/>
       <c r="D61" s="46"/>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="F61" s="67"/>
+      <c r="F61" s="64"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -16725,10 +16725,10 @@
       <c r="AB61" s="42"/>
     </row>
     <row r="62" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B62" s="63" t="s">
+      <c r="B62" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="C62" s="63"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="48">
         <f>SUM(F13:F59)</f>
         <v>169370.28999999998</v>
@@ -16873,19 +16873,19 @@
       <c r="AB65" s="42"/>
     </row>
     <row r="66" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B66" s="63" t="s">
+      <c r="B66" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="C66" s="63"/>
+      <c r="C66" s="65"/>
       <c r="D66" s="50">
         <f>SUM(Z13:Z59)</f>
         <v>396824.73999999993</v>
       </c>
-      <c r="E66" s="64">
+      <c r="E66" s="66">
         <f>D66*100/D66</f>
         <v>100</v>
       </c>
-      <c r="F66" s="64"/>
+      <c r="F66" s="66"/>
       <c r="G66" s="51"/>
       <c r="H66" s="51"/>
       <c r="I66" s="51"/>
@@ -16970,10 +16970,10 @@
       <c r="AB68" s="42"/>
     </row>
     <row r="69" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B69" s="63" t="s">
+      <c r="B69" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="C69" s="63"/>
+      <c r="C69" s="65"/>
       <c r="D69" s="3">
         <f>SUM(E13:E59)</f>
         <v>125925</v>
@@ -17088,11 +17088,11 @@
         <f>SUM(T13:T59)</f>
         <v>46674</v>
       </c>
-      <c r="E72" s="62">
+      <c r="E72" s="67">
         <f>D72*100/D73</f>
         <v>15.919695481335953</v>
       </c>
-      <c r="F72" s="62"/>
+      <c r="F72" s="67"/>
       <c r="G72" s="56"/>
       <c r="H72" s="56"/>
       <c r="I72" s="56"/>
@@ -17117,19 +17117,19 @@
       <c r="AB72" s="42"/>
     </row>
     <row r="73" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B73" s="63" t="s">
+      <c r="B73" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="63"/>
+      <c r="C73" s="65"/>
       <c r="D73" s="55">
         <f>SUM(Y13:Y59)</f>
         <v>293184</v>
       </c>
-      <c r="E73" s="62">
+      <c r="E73" s="67">
         <f>D73*100/D73</f>
         <v>100</v>
       </c>
-      <c r="F73" s="62"/>
+      <c r="F73" s="67"/>
       <c r="G73" s="56"/>
       <c r="H73" s="56"/>
       <c r="I73" s="56"/>
@@ -17890,23 +17890,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="E69:F69"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="B1:Z6"/>
     <mergeCell ref="AA1:AG6"/>
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="E73:F73"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="5">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E029CB-B23D-4E4A-86BF-86C4B1044A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AD9A4E-A97A-494F-88A6-0E22C0CB77D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -838,6 +838,15 @@
     <xf numFmtId="2" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -846,15 +855,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5632,6 +5632,8 @@
       <sheetName val="INVENTARIO NACIONAL 11-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -5716,22 +5718,22 @@
             <v>16178.560000000001</v>
           </cell>
           <cell r="AA13">
-            <v>12132.5</v>
+            <v>11756</v>
           </cell>
           <cell r="AB13">
-            <v>9.8050690294663099</v>
+            <v>10.119088125212658</v>
           </cell>
           <cell r="AC13">
-            <v>0.9805069029466309</v>
+            <v>1.0119088125212656</v>
           </cell>
           <cell r="AD13">
-            <v>-236.5</v>
+            <v>140</v>
           </cell>
           <cell r="AE13">
-            <v>6066.25</v>
+            <v>5878</v>
           </cell>
           <cell r="AF13">
-            <v>6302.75</v>
+            <v>5738</v>
           </cell>
           <cell r="AG13">
             <v>148.69999999999999</v>
@@ -5808,22 +5810,22 @@
             <v>1163.8800000000001</v>
           </cell>
           <cell r="AA14">
-            <v>786.25</v>
+            <v>823</v>
           </cell>
           <cell r="AB14">
-            <v>9.3100158982511925</v>
+            <v>8.8942891859052242</v>
           </cell>
           <cell r="AC14">
-            <v>0.93100158982511927</v>
+            <v>0.88942891859052253</v>
           </cell>
           <cell r="AD14">
-            <v>-54.25</v>
+            <v>-91</v>
           </cell>
           <cell r="AE14">
-            <v>393.125</v>
+            <v>411.5</v>
           </cell>
           <cell r="AF14">
-            <v>447.375</v>
+            <v>502.5</v>
           </cell>
           <cell r="AG14">
             <v>9.15</v>
@@ -5900,22 +5902,22 @@
             <v>8566.5999999999985</v>
           </cell>
           <cell r="AA15">
-            <v>4708.75</v>
+            <v>4634</v>
           </cell>
           <cell r="AB15">
-            <v>8.9620387576320688</v>
+            <v>9.1066033664220978</v>
           </cell>
           <cell r="AC15">
-            <v>0.89620387576320681</v>
+            <v>0.9106603366422098</v>
           </cell>
           <cell r="AD15">
-            <v>-488.75</v>
+            <v>-414</v>
           </cell>
           <cell r="AE15">
-            <v>2354.375</v>
+            <v>2317</v>
           </cell>
           <cell r="AF15">
-            <v>2843.125</v>
+            <v>2731</v>
           </cell>
           <cell r="AG15">
             <v>70.333333333333329</v>
@@ -5992,22 +5994,22 @@
             <v>1342.9199999999998</v>
           </cell>
           <cell r="AA16">
-            <v>1082.5</v>
+            <v>1004</v>
           </cell>
           <cell r="AB16">
-            <v>3.4364896073903002</v>
+            <v>3.7051792828685257</v>
           </cell>
           <cell r="AC16">
-            <v>0.34364896073903001</v>
+            <v>0.37051792828685259</v>
           </cell>
           <cell r="AD16">
-            <v>-710.5</v>
+            <v>-632</v>
           </cell>
           <cell r="AE16">
-            <v>541.25</v>
+            <v>502</v>
           </cell>
           <cell r="AF16">
-            <v>1251.75</v>
+            <v>1134</v>
           </cell>
           <cell r="AG16">
             <v>13.285714285714286</v>
@@ -6084,22 +6086,22 @@
             <v>2010.62</v>
           </cell>
           <cell r="AA17">
-            <v>93.75</v>
+            <v>90</v>
           </cell>
           <cell r="AB17">
-            <v>24.426666666666666</v>
+            <v>25.444444444444443</v>
           </cell>
           <cell r="AC17">
-            <v>2.4426666666666668</v>
+            <v>2.5444444444444443</v>
           </cell>
           <cell r="AD17">
-            <v>135.25</v>
+            <v>139</v>
           </cell>
           <cell r="AE17">
-            <v>46.875</v>
+            <v>45</v>
           </cell>
           <cell r="AF17">
-            <v>-88.375</v>
+            <v>-94</v>
           </cell>
           <cell r="AG17">
             <v>19.083333333333332</v>
@@ -6176,22 +6178,22 @@
             <v>4077.36</v>
           </cell>
           <cell r="AA18">
-            <v>14558.75</v>
+            <v>14437</v>
           </cell>
           <cell r="AB18">
-            <v>4.4454365931141062</v>
+            <v>4.4829258156126617</v>
           </cell>
           <cell r="AC18">
-            <v>0.44454365931141065</v>
+            <v>0.44829258156126617</v>
           </cell>
           <cell r="AD18">
-            <v>-8086.75</v>
+            <v>-7965</v>
           </cell>
           <cell r="AE18">
-            <v>7279.375</v>
+            <v>7218.5</v>
           </cell>
           <cell r="AF18">
-            <v>15366.125</v>
+            <v>15183.5</v>
           </cell>
           <cell r="AG18">
             <v>107.86666666666666</v>
@@ -6268,22 +6270,22 @@
             <v>1168.02</v>
           </cell>
           <cell r="AA19">
-            <v>1447.5</v>
+            <v>1441</v>
           </cell>
           <cell r="AB19">
-            <v>12.808290155440414</v>
+            <v>12.866065232477446</v>
           </cell>
           <cell r="AC19">
-            <v>1.2808290155440414</v>
+            <v>1.2866065232477446</v>
           </cell>
           <cell r="AD19">
-            <v>406.5</v>
+            <v>413</v>
           </cell>
           <cell r="AE19">
-            <v>723.75</v>
+            <v>720.5</v>
           </cell>
           <cell r="AF19">
-            <v>317.25</v>
+            <v>307.5</v>
           </cell>
           <cell r="AG19">
             <v>30.9</v>
@@ -6360,22 +6362,22 @@
             <v>2730.42</v>
           </cell>
           <cell r="AA20">
-            <v>3460</v>
+            <v>3157</v>
           </cell>
           <cell r="AB20">
-            <v>12.526011560693641</v>
+            <v>13.728222996515679</v>
           </cell>
           <cell r="AC20">
-            <v>1.2526011560693642</v>
+            <v>1.372822299651568</v>
           </cell>
           <cell r="AD20">
-            <v>874</v>
+            <v>1177</v>
           </cell>
           <cell r="AE20">
-            <v>1730</v>
+            <v>1578.5</v>
           </cell>
           <cell r="AF20">
-            <v>856</v>
+            <v>401.5</v>
           </cell>
           <cell r="AG20">
             <v>72.233333333333334</v>
@@ -6452,22 +6454,22 @@
             <v>10090.130000000001</v>
           </cell>
           <cell r="AA21">
-            <v>7250</v>
+            <v>7180</v>
           </cell>
           <cell r="AB21">
-            <v>12.768275862068965</v>
+            <v>12.892757660167131</v>
           </cell>
           <cell r="AC21">
-            <v>1.2768275862068965</v>
+            <v>1.2892757660167131</v>
           </cell>
           <cell r="AD21">
-            <v>2007</v>
+            <v>2077</v>
           </cell>
           <cell r="AE21">
-            <v>3625</v>
+            <v>3590</v>
           </cell>
           <cell r="AF21">
-            <v>1618</v>
+            <v>1513</v>
           </cell>
           <cell r="AG21">
             <v>171.42592592592592</v>
@@ -6544,22 +6546,22 @@
             <v>4768.75</v>
           </cell>
           <cell r="AA22">
-            <v>3872.5</v>
+            <v>3422</v>
           </cell>
           <cell r="AB22">
-            <v>11.297611362169141</v>
+            <v>12.784921098772648</v>
           </cell>
           <cell r="AC22">
-            <v>1.1297611362169142</v>
+            <v>1.2784921098772648</v>
           </cell>
           <cell r="AD22">
-            <v>502.5</v>
+            <v>953</v>
           </cell>
           <cell r="AE22">
-            <v>1936.25</v>
+            <v>1711</v>
           </cell>
           <cell r="AF22">
-            <v>1433.75</v>
+            <v>758</v>
           </cell>
           <cell r="AG22">
             <v>81.018518518518519</v>
@@ -6636,22 +6638,22 @@
             <v>42715.839999999997</v>
           </cell>
           <cell r="AA23">
-            <v>35335</v>
+            <v>36510</v>
           </cell>
           <cell r="AB23">
-            <v>10.421395217206735</v>
+            <v>10.086003834565872</v>
           </cell>
           <cell r="AC23">
-            <v>1.0421395217206735</v>
+            <v>1.0086003834565873</v>
           </cell>
           <cell r="AD23">
-            <v>1489</v>
+            <v>314</v>
           </cell>
           <cell r="AE23">
-            <v>17667.5</v>
+            <v>18255</v>
           </cell>
           <cell r="AF23">
-            <v>16178.5</v>
+            <v>17941</v>
           </cell>
           <cell r="AG23">
             <v>681.92592592592598</v>
@@ -6728,22 +6730,22 @@
             <v>27060.48</v>
           </cell>
           <cell r="AA24">
-            <v>22485</v>
+            <v>24080</v>
           </cell>
           <cell r="AB24">
-            <v>10.374916611074049</v>
+            <v>9.6877076411960132</v>
           </cell>
           <cell r="AC24">
-            <v>1.037491661107405</v>
+            <v>0.96877076411960128</v>
           </cell>
           <cell r="AD24">
-            <v>843</v>
+            <v>-752</v>
           </cell>
           <cell r="AE24">
-            <v>11242.5</v>
+            <v>12040</v>
           </cell>
           <cell r="AF24">
-            <v>10399.5</v>
+            <v>12792</v>
           </cell>
           <cell r="AG24">
             <v>432</v>
@@ -6820,22 +6822,22 @@
             <v>31054.359999999997</v>
           </cell>
           <cell r="AA25">
-            <v>22183.75</v>
+            <v>23292</v>
           </cell>
           <cell r="AB25">
-            <v>12.067842452245451</v>
+            <v>11.493645886999829</v>
           </cell>
           <cell r="AC25">
-            <v>1.206784245224545</v>
+            <v>1.1493645886999828</v>
           </cell>
           <cell r="AD25">
-            <v>4587.25</v>
+            <v>3479</v>
           </cell>
           <cell r="AE25">
-            <v>11091.875</v>
+            <v>11646</v>
           </cell>
           <cell r="AF25">
-            <v>6504.625</v>
+            <v>8167</v>
           </cell>
           <cell r="AG25">
             <v>495.75925925925924</v>
@@ -6912,22 +6914,22 @@
             <v>43143.88</v>
           </cell>
           <cell r="AA26">
-            <v>26742.5</v>
+            <v>27946</v>
           </cell>
           <cell r="AB26">
-            <v>13.907824623726279</v>
+            <v>13.308881414155872</v>
           </cell>
           <cell r="AC26">
-            <v>1.3907824623726279</v>
+            <v>1.3308881414155873</v>
           </cell>
           <cell r="AD26">
-            <v>10450.5</v>
+            <v>9247</v>
           </cell>
           <cell r="AE26">
-            <v>13371.25</v>
+            <v>13973</v>
           </cell>
           <cell r="AF26">
-            <v>2920.75</v>
+            <v>4726</v>
           </cell>
           <cell r="AG26">
             <v>688.75925925925924</v>
@@ -7004,22 +7006,22 @@
             <v>3529.8799999999997</v>
           </cell>
           <cell r="AA27">
-            <v>435</v>
+            <v>355</v>
           </cell>
           <cell r="AB27">
-            <v>69.954022988505741</v>
+            <v>85.718309859154928</v>
           </cell>
           <cell r="AC27">
-            <v>6.9954022988505749</v>
+            <v>8.5718309859154935</v>
           </cell>
           <cell r="AD27">
-            <v>2608</v>
+            <v>2688</v>
           </cell>
           <cell r="AE27">
-            <v>217.5</v>
+            <v>177.5</v>
           </cell>
           <cell r="AF27">
-            <v>-2390.5</v>
+            <v>-2510.5</v>
           </cell>
           <cell r="AG27">
             <v>56.351851851851855</v>
@@ -7048,13 +7050,13 @@
             <v>3695.7599999999998</v>
           </cell>
           <cell r="L28">
-            <v>66.548302872062663</v>
+            <v>29.971777986829728</v>
           </cell>
           <cell r="M28">
-            <v>1053.25</v>
+            <v>2338.6</v>
           </cell>
           <cell r="N28">
-            <v>2707.25</v>
+            <v>2123</v>
           </cell>
           <cell r="O28">
             <v>324</v>
@@ -7087,22 +7089,22 @@
             <v>6389.28</v>
           </cell>
           <cell r="AA28">
-            <v>478.75</v>
+            <v>1063</v>
           </cell>
           <cell r="AB28">
-            <v>115.04960835509138</v>
+            <v>51.815616180620886</v>
           </cell>
           <cell r="AC28">
-            <v>11.504960835509138</v>
+            <v>5.181561618062088</v>
           </cell>
           <cell r="AD28">
-            <v>5029.25</v>
+            <v>4445</v>
           </cell>
           <cell r="AE28">
-            <v>239.375</v>
+            <v>531.5</v>
           </cell>
           <cell r="AF28">
-            <v>-4789.875</v>
+            <v>-3913.5</v>
           </cell>
           <cell r="AG28">
             <v>102</v>
@@ -7131,13 +7133,13 @@
             <v>3658.64</v>
           </cell>
           <cell r="L29">
-            <v>45.13774597495528</v>
+            <v>21.872399445214981</v>
           </cell>
           <cell r="M29">
-            <v>1537.25</v>
+            <v>3172.3999999999996</v>
           </cell>
           <cell r="N29">
-            <v>2455.25</v>
+            <v>1712</v>
           </cell>
           <cell r="O29">
             <v>324</v>
@@ -7170,22 +7172,22 @@
             <v>6352.16</v>
           </cell>
           <cell r="AA29">
-            <v>698.75</v>
+            <v>1442</v>
           </cell>
           <cell r="AB29">
-            <v>78.368515205724506</v>
+            <v>37.975034674063807</v>
           </cell>
           <cell r="AC29">
-            <v>7.8368515205724512</v>
+            <v>3.7975034674063801</v>
           </cell>
           <cell r="AD29">
-            <v>4777.25</v>
+            <v>4034</v>
           </cell>
           <cell r="AE29">
-            <v>349.375</v>
+            <v>721</v>
           </cell>
           <cell r="AF29">
-            <v>-4427.875</v>
+            <v>-3313</v>
           </cell>
           <cell r="AG29">
             <v>101.4074074074074</v>
@@ -7214,13 +7216,13 @@
             <v>3539.16</v>
           </cell>
           <cell r="L30">
-            <v>53.880794701986758</v>
+            <v>23.272311212814646</v>
           </cell>
           <cell r="M30">
-            <v>1245.75</v>
+            <v>2884.2</v>
           </cell>
           <cell r="N30">
-            <v>2484.75</v>
+            <v>1740</v>
           </cell>
           <cell r="O30">
             <v>324</v>
@@ -7253,22 +7255,22 @@
             <v>6232.6799999999994</v>
           </cell>
           <cell r="AA30">
-            <v>566.25</v>
+            <v>1311</v>
           </cell>
           <cell r="AB30">
-            <v>94.88741721854305</v>
+            <v>40.983981693363845</v>
           </cell>
           <cell r="AC30">
-            <v>9.4887417218543053</v>
+            <v>4.0983981693363845</v>
           </cell>
           <cell r="AD30">
-            <v>4806.75</v>
+            <v>4062</v>
           </cell>
           <cell r="AE30">
-            <v>283.125</v>
+            <v>655.5</v>
           </cell>
           <cell r="AF30">
-            <v>-4523.625</v>
+            <v>-3406.5</v>
           </cell>
           <cell r="AG30">
             <v>99.5</v>
@@ -7345,22 +7347,22 @@
             <v>7161.2800000000007</v>
           </cell>
           <cell r="AA31">
-            <v>2222.5</v>
+            <v>2384</v>
           </cell>
           <cell r="AB31">
-            <v>8.7559055118110241</v>
+            <v>8.1627516778523486</v>
           </cell>
           <cell r="AC31">
-            <v>0.87559055118110241</v>
+            <v>0.8162751677852349</v>
           </cell>
           <cell r="AD31">
-            <v>-276.5</v>
+            <v>-438</v>
           </cell>
           <cell r="AE31">
-            <v>1111.25</v>
+            <v>1192</v>
           </cell>
           <cell r="AF31">
-            <v>1387.75</v>
+            <v>1630</v>
           </cell>
           <cell r="AG31">
             <v>121.625</v>
@@ -7437,22 +7439,22 @@
             <v>4791.3600000000006</v>
           </cell>
           <cell r="AA32">
-            <v>1297.5</v>
+            <v>1298</v>
           </cell>
           <cell r="AB32">
-            <v>10.034682080924856</v>
+            <v>10.030816640986131</v>
           </cell>
           <cell r="AC32">
-            <v>1.0034682080924855</v>
+            <v>1.0030816640986133</v>
           </cell>
           <cell r="AD32">
-            <v>4.5</v>
+            <v>4</v>
           </cell>
           <cell r="AE32">
-            <v>648.75</v>
+            <v>649</v>
           </cell>
           <cell r="AF32">
-            <v>644.25</v>
+            <v>645</v>
           </cell>
           <cell r="AG32">
             <v>81.375</v>
@@ -7529,22 +7531,22 @@
             <v>12284.000000000002</v>
           </cell>
           <cell r="AA33">
-            <v>5282.5</v>
+            <v>5003</v>
           </cell>
           <cell r="AB33">
-            <v>5.6034074775201139</v>
+            <v>5.9164501299220467</v>
           </cell>
           <cell r="AC33">
-            <v>0.56034074775201137</v>
+            <v>0.59164501299220462</v>
           </cell>
           <cell r="AD33">
-            <v>-2322.5</v>
+            <v>-2043</v>
           </cell>
           <cell r="AE33">
-            <v>2641.25</v>
+            <v>2501.5</v>
           </cell>
           <cell r="AF33">
-            <v>4963.75</v>
+            <v>4544.5</v>
           </cell>
           <cell r="AG33">
             <v>185</v>
@@ -7621,22 +7623,22 @@
             <v>30697.550000000003</v>
           </cell>
           <cell r="AA34">
-            <v>7961.25</v>
+            <v>7763</v>
           </cell>
           <cell r="AB34">
-            <v>9.2912545140524418</v>
+            <v>9.528532783717635</v>
           </cell>
           <cell r="AC34">
-            <v>0.92912545140524416</v>
+            <v>0.95285327837176348</v>
           </cell>
           <cell r="AD34">
-            <v>-564.25</v>
+            <v>-366</v>
           </cell>
           <cell r="AE34">
-            <v>3980.625</v>
+            <v>3881.5</v>
           </cell>
           <cell r="AF34">
-            <v>4544.875</v>
+            <v>4247.5</v>
           </cell>
           <cell r="AG34">
             <v>462.3125</v>
@@ -7713,16 +7715,16 @@
             <v>0</v>
           </cell>
           <cell r="AA35">
-            <v>0</v>
+            <v>100</v>
           </cell>
           <cell r="AD35">
-            <v>0</v>
+            <v>-100</v>
           </cell>
           <cell r="AE35">
-            <v>0</v>
+            <v>50</v>
           </cell>
           <cell r="AF35">
-            <v>0</v>
+            <v>150</v>
           </cell>
           <cell r="AG35">
             <v>0</v>
@@ -7778,22 +7780,22 @@
             <v>1149.5500000000002</v>
           </cell>
           <cell r="AA36">
-            <v>727.5</v>
+            <v>1500</v>
           </cell>
           <cell r="AB36">
-            <v>3.8075601374570445</v>
+            <v>1.8466666666666667</v>
           </cell>
           <cell r="AC36">
-            <v>0.38075601374570445</v>
+            <v>0.18466666666666667</v>
           </cell>
           <cell r="AD36">
-            <v>-450.5</v>
+            <v>-1223</v>
           </cell>
           <cell r="AE36">
-            <v>363.75</v>
+            <v>750</v>
           </cell>
           <cell r="AF36">
-            <v>814.25</v>
+            <v>1973</v>
           </cell>
           <cell r="AG36">
             <v>17.3125</v>
@@ -7870,22 +7872,22 @@
             <v>16727.059999999998</v>
           </cell>
           <cell r="AA37">
-            <v>6561.25</v>
+            <v>6782</v>
           </cell>
           <cell r="AB37">
-            <v>15.64031244046485</v>
+            <v>15.131229725744618</v>
           </cell>
           <cell r="AC37">
-            <v>1.564031244046485</v>
+            <v>1.5131229725744617</v>
           </cell>
           <cell r="AD37">
-            <v>3700.75</v>
+            <v>3480</v>
           </cell>
           <cell r="AE37">
-            <v>3280.625</v>
+            <v>3391</v>
           </cell>
           <cell r="AF37">
-            <v>-420.125</v>
+            <v>-89</v>
           </cell>
           <cell r="AG37">
             <v>190.03703703703704</v>
@@ -7962,22 +7964,22 @@
             <v>13189.96</v>
           </cell>
           <cell r="AA38">
-            <v>11485</v>
+            <v>11052</v>
           </cell>
           <cell r="AB38">
-            <v>7.045711797997388</v>
+            <v>7.3217517191458557</v>
           </cell>
           <cell r="AC38">
-            <v>0.70457117979973882</v>
+            <v>0.73217517191458559</v>
           </cell>
           <cell r="AD38">
-            <v>-3393</v>
+            <v>-2960</v>
           </cell>
           <cell r="AE38">
-            <v>5742.5</v>
+            <v>5526</v>
           </cell>
           <cell r="AF38">
-            <v>9135.5</v>
+            <v>8486</v>
           </cell>
           <cell r="AG38">
             <v>149.85185185185185</v>
@@ -8054,22 +8056,22 @@
             <v>4886.74</v>
           </cell>
           <cell r="AA39">
-            <v>5206.25</v>
+            <v>4932</v>
           </cell>
           <cell r="AB39">
-            <v>5.7584633853541414</v>
+            <v>6.078669910786699</v>
           </cell>
           <cell r="AC39">
-            <v>0.57584633853541412</v>
+            <v>0.60786699107866993</v>
           </cell>
           <cell r="AD39">
-            <v>-2208.25</v>
+            <v>-1934</v>
           </cell>
           <cell r="AE39">
-            <v>2603.125</v>
+            <v>2466</v>
           </cell>
           <cell r="AF39">
-            <v>4811.375</v>
+            <v>4400</v>
           </cell>
           <cell r="AG39">
             <v>55.518518518518519</v>
@@ -8146,22 +8148,22 @@
             <v>2934</v>
           </cell>
           <cell r="AA40">
-            <v>3810</v>
+            <v>3391</v>
           </cell>
           <cell r="AB40">
-            <v>4.7244094488188972</v>
+            <v>5.3081686818047773</v>
           </cell>
           <cell r="AC40">
-            <v>0.47244094488188976</v>
+            <v>0.53081686818047769</v>
           </cell>
           <cell r="AD40">
-            <v>-2010</v>
+            <v>-1591</v>
           </cell>
           <cell r="AE40">
-            <v>1905</v>
+            <v>1695.5</v>
           </cell>
           <cell r="AF40">
-            <v>3915</v>
+            <v>3286.5</v>
           </cell>
           <cell r="AG40">
             <v>33.333333333333336</v>
@@ -8238,22 +8240,22 @@
             <v>6863.4000000000005</v>
           </cell>
           <cell r="AA41">
-            <v>1361.25</v>
+            <v>1326</v>
           </cell>
           <cell r="AB41">
-            <v>8.1983471074380159</v>
+            <v>8.4162895927601813</v>
           </cell>
           <cell r="AC41">
-            <v>0.81983471074380165</v>
+            <v>0.84162895927601811</v>
           </cell>
           <cell r="AD41">
-            <v>-245.25</v>
+            <v>-210</v>
           </cell>
           <cell r="AE41">
-            <v>680.625</v>
+            <v>663</v>
           </cell>
           <cell r="AF41">
-            <v>925.875</v>
+            <v>873</v>
           </cell>
           <cell r="AG41">
             <v>20.666666666666668</v>
@@ -8330,22 +8332,22 @@
             <v>9255.75</v>
           </cell>
           <cell r="AA42">
-            <v>1106.25</v>
+            <v>1192</v>
           </cell>
           <cell r="AB42">
-            <v>13.604519774011299</v>
+            <v>12.625838926174497</v>
           </cell>
           <cell r="AC42">
-            <v>1.3604519774011299</v>
+            <v>1.2625838926174497</v>
           </cell>
           <cell r="AD42">
-            <v>398.75</v>
+            <v>313</v>
           </cell>
           <cell r="AE42">
-            <v>553.125</v>
+            <v>596</v>
           </cell>
           <cell r="AF42">
-            <v>154.375</v>
+            <v>283</v>
           </cell>
           <cell r="AG42">
             <v>27.87037037037037</v>
@@ -8422,22 +8424,22 @@
             <v>6508.7599999999993</v>
           </cell>
           <cell r="AA43">
-            <v>6173.75</v>
+            <v>6145</v>
           </cell>
           <cell r="AB43">
-            <v>9.0884794492812304</v>
+            <v>9.131000813669651</v>
           </cell>
           <cell r="AC43">
-            <v>0.90884794492812315</v>
+            <v>0.91310008136696497</v>
           </cell>
           <cell r="AD43">
-            <v>-562.75</v>
+            <v>-534</v>
           </cell>
           <cell r="AE43">
-            <v>3086.875</v>
+            <v>3072.5</v>
           </cell>
           <cell r="AF43">
-            <v>3649.625</v>
+            <v>3606.5</v>
           </cell>
           <cell r="AG43">
             <v>103.9074074074074</v>
@@ -8514,22 +8516,22 @@
             <v>11774</v>
           </cell>
           <cell r="AA44">
-            <v>6892.5</v>
+            <v>6715</v>
           </cell>
           <cell r="AB44">
-            <v>14.726151614073268</v>
+            <v>15.115413253909159</v>
           </cell>
           <cell r="AC44">
-            <v>1.4726151614073268</v>
+            <v>1.5115413253909158</v>
           </cell>
           <cell r="AD44">
-            <v>3257.5</v>
+            <v>3435</v>
           </cell>
           <cell r="AE44">
-            <v>3446.25</v>
+            <v>3357.5</v>
           </cell>
           <cell r="AF44">
-            <v>188.75</v>
+            <v>-77.5</v>
           </cell>
           <cell r="AG44">
             <v>187.96296296296296</v>
@@ -8606,22 +8608,22 @@
             <v>9532.8799999999992</v>
           </cell>
           <cell r="AA45">
-            <v>9117.5</v>
+            <v>8316</v>
           </cell>
           <cell r="AB45">
-            <v>9.0134357005758154</v>
+            <v>9.8821548821548824</v>
           </cell>
           <cell r="AC45">
-            <v>0.90134357005758159</v>
+            <v>0.98821548821548821</v>
           </cell>
           <cell r="AD45">
-            <v>-899.5</v>
+            <v>-98</v>
           </cell>
           <cell r="AE45">
-            <v>4558.75</v>
+            <v>4158</v>
           </cell>
           <cell r="AF45">
-            <v>5458.25</v>
+            <v>4256</v>
           </cell>
           <cell r="AG45">
             <v>152.18518518518519</v>
@@ -8698,22 +8700,22 @@
             <v>7790.5599999999995</v>
           </cell>
           <cell r="AA46">
-            <v>5860</v>
+            <v>5818</v>
           </cell>
           <cell r="AB46">
-            <v>11.46075085324232</v>
+            <v>11.543485733929186</v>
           </cell>
           <cell r="AC46">
-            <v>1.1460750853242321</v>
+            <v>1.1543485733929186</v>
           </cell>
           <cell r="AD46">
-            <v>856</v>
+            <v>898</v>
           </cell>
           <cell r="AE46">
-            <v>2930</v>
+            <v>2909</v>
           </cell>
           <cell r="AF46">
-            <v>2074</v>
+            <v>2011</v>
           </cell>
           <cell r="AG46">
             <v>124.37037037037037</v>
@@ -8769,22 +8771,22 @@
             <v>288</v>
           </cell>
           <cell r="AA47">
-            <v>16.25</v>
+            <v>24</v>
           </cell>
           <cell r="AB47">
-            <v>9.8461538461538467</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="AC47">
-            <v>0.98461538461538467</v>
+            <v>0.66666666666666663</v>
           </cell>
           <cell r="AD47">
-            <v>-0.25</v>
+            <v>-8</v>
           </cell>
           <cell r="AE47">
-            <v>8.125</v>
+            <v>12</v>
           </cell>
           <cell r="AF47">
-            <v>8.375</v>
+            <v>20</v>
           </cell>
           <cell r="AG47">
             <v>8</v>
@@ -8917,22 +8919,22 @@
             <v>126.44</v>
           </cell>
           <cell r="AA49">
-            <v>218.75</v>
+            <v>175</v>
           </cell>
           <cell r="AB49">
-            <v>4.9828571428571431</v>
+            <v>6.2285714285714286</v>
           </cell>
           <cell r="AC49">
-            <v>0.49828571428571428</v>
+            <v>0.62285714285714289</v>
           </cell>
           <cell r="AD49">
-            <v>-109.75</v>
+            <v>-66</v>
           </cell>
           <cell r="AE49">
-            <v>109.375</v>
+            <v>87.5</v>
           </cell>
           <cell r="AF49">
-            <v>219.125</v>
+            <v>153.5</v>
           </cell>
           <cell r="AG49">
             <v>2.7250000000000001</v>
@@ -9101,22 +9103,22 @@
             <v>19.72</v>
           </cell>
           <cell r="AA51">
-            <v>886.25</v>
+            <v>709</v>
           </cell>
           <cell r="AB51">
-            <v>0.1918194640338505</v>
+            <v>0.23977433004231311</v>
           </cell>
           <cell r="AC51">
-            <v>1.9181946403385049E-2</v>
+            <v>2.3977433004231313E-2</v>
           </cell>
           <cell r="AD51">
-            <v>-869.25</v>
+            <v>-692</v>
           </cell>
           <cell r="AE51">
-            <v>443.125</v>
+            <v>354.5</v>
           </cell>
           <cell r="AF51">
-            <v>1312.375</v>
+            <v>1046.5</v>
           </cell>
           <cell r="AG51">
             <v>0.42499999999999999</v>
@@ -9190,22 +9192,22 @@
             <v>6486.4800000000005</v>
           </cell>
           <cell r="AA52">
-            <v>3163.75</v>
+            <v>3036</v>
           </cell>
           <cell r="AB52">
-            <v>25.311734492295535</v>
+            <v>26.376811594202895</v>
           </cell>
           <cell r="AC52">
-            <v>2.5311734492295535</v>
+            <v>2.63768115942029</v>
           </cell>
           <cell r="AD52">
-            <v>4844.25</v>
+            <v>4972</v>
           </cell>
           <cell r="AE52">
-            <v>1581.875</v>
+            <v>1518</v>
           </cell>
           <cell r="AF52">
-            <v>-3262.375</v>
+            <v>-3454</v>
           </cell>
           <cell r="AG52">
             <v>667.33333333333337</v>
@@ -9279,22 +9281,22 @@
             <v>5956.7400000000007</v>
           </cell>
           <cell r="AA53">
-            <v>5653.75</v>
+            <v>5285</v>
           </cell>
           <cell r="AB53">
-            <v>13.007296042449701</v>
+            <v>13.914853358561968</v>
           </cell>
           <cell r="AC53">
-            <v>1.3007296042449701</v>
+            <v>1.3914853358561967</v>
           </cell>
           <cell r="AD53">
-            <v>1700.25</v>
+            <v>2069</v>
           </cell>
           <cell r="AE53">
-            <v>2826.875</v>
+            <v>2642.5</v>
           </cell>
           <cell r="AF53">
-            <v>1126.625</v>
+            <v>573.5</v>
           </cell>
           <cell r="AG53">
             <v>612.83333333333337</v>
@@ -9368,22 +9370,22 @@
             <v>5804.46</v>
           </cell>
           <cell r="AA54">
-            <v>3317.5</v>
+            <v>3223</v>
           </cell>
           <cell r="AB54">
-            <v>21.600602863602109</v>
+            <v>22.233943530871858</v>
           </cell>
           <cell r="AC54">
-            <v>2.1600602863602112</v>
+            <v>2.223394353087186</v>
           </cell>
           <cell r="AD54">
-            <v>3848.5</v>
+            <v>3943</v>
           </cell>
           <cell r="AE54">
-            <v>1658.75</v>
+            <v>1611.5</v>
           </cell>
           <cell r="AF54">
-            <v>-2189.75</v>
+            <v>-2331.5</v>
           </cell>
           <cell r="AG54">
             <v>597.16666666666663</v>
@@ -9457,22 +9459,22 @@
             <v>7047.81</v>
           </cell>
           <cell r="AA55">
-            <v>2681.25</v>
+            <v>2734</v>
           </cell>
           <cell r="AB55">
-            <v>32.45128205128205</v>
+            <v>31.825164594001464</v>
           </cell>
           <cell r="AC55">
-            <v>3.2451282051282053</v>
+            <v>3.1825164594001465</v>
           </cell>
           <cell r="AD55">
-            <v>6019.75</v>
+            <v>5967</v>
           </cell>
           <cell r="AE55">
-            <v>1340.625</v>
+            <v>1367</v>
           </cell>
           <cell r="AF55">
-            <v>-4679.125</v>
+            <v>-4600</v>
           </cell>
           <cell r="AG55">
             <v>725.08333333333337</v>
@@ -9546,22 +9548,22 @@
             <v>1433.14</v>
           </cell>
           <cell r="AA56">
-            <v>522.5</v>
+            <v>446</v>
           </cell>
           <cell r="AB56">
-            <v>10.4688995215311</v>
+            <v>12.264573991031389</v>
           </cell>
           <cell r="AC56">
-            <v>1.0468899521531101</v>
+            <v>1.2264573991031391</v>
           </cell>
           <cell r="AD56">
-            <v>24.5</v>
+            <v>101</v>
           </cell>
           <cell r="AE56">
-            <v>261.25</v>
+            <v>223</v>
           </cell>
           <cell r="AF56">
-            <v>236.75</v>
+            <v>122</v>
           </cell>
           <cell r="AG56">
             <v>91.166666666666671</v>
@@ -9635,22 +9637,22 @@
             <v>896.04000000000008</v>
           </cell>
           <cell r="AA57">
-            <v>1036.25</v>
+            <v>933</v>
           </cell>
           <cell r="AB57">
-            <v>3.3003618817852836</v>
+            <v>3.6655948553054665</v>
           </cell>
           <cell r="AC57">
-            <v>0.33003618817852837</v>
+            <v>0.36655948553054662</v>
           </cell>
           <cell r="AD57">
-            <v>-694.25</v>
+            <v>-591</v>
           </cell>
           <cell r="AE57">
-            <v>518.125</v>
+            <v>466.5</v>
           </cell>
           <cell r="AF57">
-            <v>1212.375</v>
+            <v>1057.5</v>
           </cell>
           <cell r="AG57">
             <v>57</v>
@@ -9724,22 +9726,22 @@
             <v>592.12</v>
           </cell>
           <cell r="AA58">
-            <v>673.75</v>
+            <v>546</v>
           </cell>
           <cell r="AB58">
-            <v>3.3543599257884971</v>
+            <v>4.1391941391941387</v>
           </cell>
           <cell r="AC58">
-            <v>0.33543599257884971</v>
+            <v>0.41391941391941389</v>
           </cell>
           <cell r="AD58">
-            <v>-447.75</v>
+            <v>-320</v>
           </cell>
           <cell r="AE58">
-            <v>336.875</v>
+            <v>273</v>
           </cell>
           <cell r="AF58">
-            <v>784.625</v>
+            <v>593</v>
           </cell>
           <cell r="AG58">
             <v>37.666666666666664</v>
@@ -9813,22 +9815,22 @@
             <v>503.04</v>
           </cell>
           <cell r="AA59">
-            <v>550</v>
+            <v>467</v>
           </cell>
           <cell r="AB59">
-            <v>3.4909090909090907</v>
+            <v>4.1113490364025695</v>
           </cell>
           <cell r="AC59">
-            <v>0.34909090909090912</v>
+            <v>0.41113490364025695</v>
           </cell>
           <cell r="AD59">
-            <v>-358</v>
+            <v>-275</v>
           </cell>
           <cell r="AE59">
-            <v>275</v>
+            <v>233.5</v>
           </cell>
           <cell r="AF59">
-            <v>633</v>
+            <v>508.5</v>
           </cell>
           <cell r="AG59">
             <v>32</v>
@@ -9878,6 +9880,8 @@
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10202,212 +10206,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="63" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="63"/>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="63"/>
+      <c r="AB1" s="66"/>
+      <c r="AC1" s="66"/>
+      <c r="AD1" s="66"/>
+      <c r="AE1" s="66"/>
+      <c r="AF1" s="66"/>
+      <c r="AG1" s="66"/>
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
-      <c r="AA2" s="63"/>
-      <c r="AB2" s="63"/>
-      <c r="AC2" s="63"/>
-      <c r="AD2" s="63"/>
-      <c r="AE2" s="63"/>
-      <c r="AF2" s="63"/>
-      <c r="AG2" s="63"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="66"/>
+      <c r="AC2" s="66"/>
+      <c r="AD2" s="66"/>
+      <c r="AE2" s="66"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="62"/>
-      <c r="U3" s="62"/>
-      <c r="V3" s="62"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="62"/>
-      <c r="AA3" s="63"/>
-      <c r="AB3" s="63"/>
-      <c r="AC3" s="63"/>
-      <c r="AD3" s="63"/>
-      <c r="AE3" s="63"/>
-      <c r="AF3" s="63"/>
-      <c r="AG3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="66"/>
+      <c r="AB3" s="66"/>
+      <c r="AC3" s="66"/>
+      <c r="AD3" s="66"/>
+      <c r="AE3" s="66"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="62"/>
-      <c r="W4" s="62"/>
-      <c r="X4" s="62"/>
-      <c r="Y4" s="62"/>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="63"/>
-      <c r="AB4" s="63"/>
-      <c r="AC4" s="63"/>
-      <c r="AD4" s="63"/>
-      <c r="AE4" s="63"/>
-      <c r="AF4" s="63"/>
-      <c r="AG4" s="63"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="62"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="62"/>
-      <c r="Y5" s="62"/>
-      <c r="Z5" s="62"/>
-      <c r="AA5" s="63"/>
-      <c r="AB5" s="63"/>
-      <c r="AC5" s="63"/>
-      <c r="AD5" s="63"/>
-      <c r="AE5" s="63"/>
-      <c r="AF5" s="63"/>
-      <c r="AG5" s="63"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="66"/>
+      <c r="AB5" s="66"/>
+      <c r="AC5" s="66"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="63"/>
-      <c r="AB6" s="63"/>
-      <c r="AC6" s="63"/>
-      <c r="AD6" s="63"/>
-      <c r="AE6" s="63"/>
-      <c r="AF6" s="63"/>
-      <c r="AG6" s="63"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="66"/>
+      <c r="AB6" s="66"/>
+      <c r="AC6" s="66"/>
+      <c r="AD6" s="66"/>
+      <c r="AE6" s="66"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
@@ -10778,27 +10782,27 @@
       </c>
       <c r="AA13" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA13</f>
-        <v>12132.5</v>
+        <v>11756</v>
       </c>
       <c r="AB13" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB13</f>
-        <v>9.8050690294663099</v>
+        <v>10.119088125212658</v>
       </c>
       <c r="AC13" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC13</f>
-        <v>0.9805069029466309</v>
+        <v>1.0119088125212656</v>
       </c>
       <c r="AD13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD13</f>
-        <v>-236.5</v>
+        <v>140</v>
       </c>
       <c r="AE13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE13</f>
-        <v>6066.25</v>
+        <v>5878</v>
       </c>
       <c r="AF13" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF13</f>
-        <v>6302.75</v>
+        <v>5738</v>
       </c>
       <c r="AG13" s="27">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG13</f>
@@ -10906,27 +10910,27 @@
       </c>
       <c r="AA14" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA14</f>
-        <v>786.25</v>
+        <v>823</v>
       </c>
       <c r="AB14" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB14</f>
-        <v>9.3100158982511925</v>
+        <v>8.8942891859052242</v>
       </c>
       <c r="AC14" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC14</f>
-        <v>0.93100158982511927</v>
+        <v>0.88942891859052253</v>
       </c>
       <c r="AD14" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD14</f>
-        <v>-54.25</v>
+        <v>-91</v>
       </c>
       <c r="AE14" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE14</f>
-        <v>393.125</v>
+        <v>411.5</v>
       </c>
       <c r="AF14" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF14</f>
-        <v>447.375</v>
+        <v>502.5</v>
       </c>
       <c r="AG14" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG14</f>
@@ -11034,27 +11038,27 @@
       </c>
       <c r="AA15" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA15</f>
-        <v>4708.75</v>
+        <v>4634</v>
       </c>
       <c r="AB15" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB15</f>
-        <v>8.9620387576320688</v>
+        <v>9.1066033664220978</v>
       </c>
       <c r="AC15" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC15</f>
-        <v>0.89620387576320681</v>
+        <v>0.9106603366422098</v>
       </c>
       <c r="AD15" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD15</f>
-        <v>-488.75</v>
+        <v>-414</v>
       </c>
       <c r="AE15" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE15</f>
-        <v>2354.375</v>
+        <v>2317</v>
       </c>
       <c r="AF15" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF15</f>
-        <v>2843.125</v>
+        <v>2731</v>
       </c>
       <c r="AG15" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG15</f>
@@ -11162,27 +11166,27 @@
       </c>
       <c r="AA16" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA16</f>
-        <v>1082.5</v>
+        <v>1004</v>
       </c>
       <c r="AB16" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB16</f>
-        <v>3.4364896073903002</v>
+        <v>3.7051792828685257</v>
       </c>
       <c r="AC16" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC16</f>
-        <v>0.34364896073903001</v>
+        <v>0.37051792828685259</v>
       </c>
       <c r="AD16" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD16</f>
-        <v>-710.5</v>
+        <v>-632</v>
       </c>
       <c r="AE16" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE16</f>
-        <v>541.25</v>
+        <v>502</v>
       </c>
       <c r="AF16" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF16</f>
-        <v>1251.75</v>
+        <v>1134</v>
       </c>
       <c r="AG16" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG16</f>
@@ -11290,27 +11294,27 @@
       </c>
       <c r="AA17" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA17</f>
-        <v>93.75</v>
+        <v>90</v>
       </c>
       <c r="AB17" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB17</f>
-        <v>24.426666666666666</v>
+        <v>25.444444444444443</v>
       </c>
       <c r="AC17" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC17</f>
-        <v>2.4426666666666668</v>
+        <v>2.5444444444444443</v>
       </c>
       <c r="AD17" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD17</f>
-        <v>135.25</v>
+        <v>139</v>
       </c>
       <c r="AE17" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE17</f>
-        <v>46.875</v>
+        <v>45</v>
       </c>
       <c r="AF17" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF17</f>
-        <v>-88.375</v>
+        <v>-94</v>
       </c>
       <c r="AG17" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG17</f>
@@ -11418,27 +11422,27 @@
       </c>
       <c r="AA18" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA18</f>
-        <v>14558.75</v>
+        <v>14437</v>
       </c>
       <c r="AB18" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB18</f>
-        <v>4.4454365931141062</v>
+        <v>4.4829258156126617</v>
       </c>
       <c r="AC18" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC18</f>
-        <v>0.44454365931141065</v>
+        <v>0.44829258156126617</v>
       </c>
       <c r="AD18" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD18</f>
-        <v>-8086.75</v>
+        <v>-7965</v>
       </c>
       <c r="AE18" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE18</f>
-        <v>7279.375</v>
+        <v>7218.5</v>
       </c>
       <c r="AF18" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF18</f>
-        <v>15366.125</v>
+        <v>15183.5</v>
       </c>
       <c r="AG18" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG18</f>
@@ -11546,27 +11550,27 @@
       </c>
       <c r="AA19" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA19</f>
-        <v>1447.5</v>
+        <v>1441</v>
       </c>
       <c r="AB19" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB19</f>
-        <v>12.808290155440414</v>
+        <v>12.866065232477446</v>
       </c>
       <c r="AC19" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC19</f>
-        <v>1.2808290155440414</v>
+        <v>1.2866065232477446</v>
       </c>
       <c r="AD19" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD19</f>
-        <v>406.5</v>
+        <v>413</v>
       </c>
       <c r="AE19" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE19</f>
-        <v>723.75</v>
+        <v>720.5</v>
       </c>
       <c r="AF19" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF19</f>
-        <v>317.25</v>
+        <v>307.5</v>
       </c>
       <c r="AG19" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG19</f>
@@ -11674,27 +11678,27 @@
       </c>
       <c r="AA20" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA20</f>
-        <v>3460</v>
+        <v>3157</v>
       </c>
       <c r="AB20" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB20</f>
-        <v>12.526011560693641</v>
+        <v>13.728222996515679</v>
       </c>
       <c r="AC20" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC20</f>
-        <v>1.2526011560693642</v>
+        <v>1.372822299651568</v>
       </c>
       <c r="AD20" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD20</f>
-        <v>874</v>
+        <v>1177</v>
       </c>
       <c r="AE20" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE20</f>
-        <v>1730</v>
+        <v>1578.5</v>
       </c>
       <c r="AF20" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF20</f>
-        <v>856</v>
+        <v>401.5</v>
       </c>
       <c r="AG20" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG20</f>
@@ -11802,27 +11806,27 @@
       </c>
       <c r="AA21" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA21</f>
-        <v>7250</v>
+        <v>7180</v>
       </c>
       <c r="AB21" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB21</f>
-        <v>12.768275862068965</v>
+        <v>12.892757660167131</v>
       </c>
       <c r="AC21" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC21</f>
-        <v>1.2768275862068965</v>
+        <v>1.2892757660167131</v>
       </c>
       <c r="AD21" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD21</f>
-        <v>2007</v>
+        <v>2077</v>
       </c>
       <c r="AE21" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE21</f>
-        <v>3625</v>
+        <v>3590</v>
       </c>
       <c r="AF21" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF21</f>
-        <v>1618</v>
+        <v>1513</v>
       </c>
       <c r="AG21" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG21</f>
@@ -11930,27 +11934,27 @@
       </c>
       <c r="AA22" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA22</f>
-        <v>3872.5</v>
+        <v>3422</v>
       </c>
       <c r="AB22" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB22</f>
-        <v>11.297611362169141</v>
+        <v>12.784921098772648</v>
       </c>
       <c r="AC22" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC22</f>
-        <v>1.1297611362169142</v>
+        <v>1.2784921098772648</v>
       </c>
       <c r="AD22" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD22</f>
-        <v>502.5</v>
+        <v>953</v>
       </c>
       <c r="AE22" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE22</f>
-        <v>1936.25</v>
+        <v>1711</v>
       </c>
       <c r="AF22" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF22</f>
-        <v>1433.75</v>
+        <v>758</v>
       </c>
       <c r="AG22" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG22</f>
@@ -12058,27 +12062,27 @@
       </c>
       <c r="AA23" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA23</f>
-        <v>35335</v>
+        <v>36510</v>
       </c>
       <c r="AB23" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB23</f>
-        <v>10.421395217206735</v>
+        <v>10.086003834565872</v>
       </c>
       <c r="AC23" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC23</f>
-        <v>1.0421395217206735</v>
+        <v>1.0086003834565873</v>
       </c>
       <c r="AD23" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD23</f>
-        <v>1489</v>
+        <v>314</v>
       </c>
       <c r="AE23" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE23</f>
-        <v>17667.5</v>
+        <v>18255</v>
       </c>
       <c r="AF23" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF23</f>
-        <v>16178.5</v>
+        <v>17941</v>
       </c>
       <c r="AG23" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG23</f>
@@ -12186,27 +12190,27 @@
       </c>
       <c r="AA24" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA24</f>
-        <v>22485</v>
+        <v>24080</v>
       </c>
       <c r="AB24" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB24</f>
-        <v>10.374916611074049</v>
+        <v>9.6877076411960132</v>
       </c>
       <c r="AC24" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC24</f>
-        <v>1.037491661107405</v>
+        <v>0.96877076411960128</v>
       </c>
       <c r="AD24" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD24</f>
-        <v>843</v>
+        <v>-752</v>
       </c>
       <c r="AE24" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE24</f>
-        <v>11242.5</v>
+        <v>12040</v>
       </c>
       <c r="AF24" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF24</f>
-        <v>10399.5</v>
+        <v>12792</v>
       </c>
       <c r="AG24" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG24</f>
@@ -12314,27 +12318,27 @@
       </c>
       <c r="AA25" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA25</f>
-        <v>22183.75</v>
+        <v>23292</v>
       </c>
       <c r="AB25" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB25</f>
-        <v>12.067842452245451</v>
+        <v>11.493645886999829</v>
       </c>
       <c r="AC25" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC25</f>
-        <v>1.206784245224545</v>
+        <v>1.1493645886999828</v>
       </c>
       <c r="AD25" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD25</f>
-        <v>4587.25</v>
+        <v>3479</v>
       </c>
       <c r="AE25" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE25</f>
-        <v>11091.875</v>
+        <v>11646</v>
       </c>
       <c r="AF25" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF25</f>
-        <v>6504.625</v>
+        <v>8167</v>
       </c>
       <c r="AG25" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG25</f>
@@ -12442,27 +12446,27 @@
       </c>
       <c r="AA26" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA26</f>
-        <v>26742.5</v>
+        <v>27946</v>
       </c>
       <c r="AB26" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB26</f>
-        <v>13.907824623726279</v>
+        <v>13.308881414155872</v>
       </c>
       <c r="AC26" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC26</f>
-        <v>1.3907824623726279</v>
+        <v>1.3308881414155873</v>
       </c>
       <c r="AD26" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD26</f>
-        <v>10450.5</v>
+        <v>9247</v>
       </c>
       <c r="AE26" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE26</f>
-        <v>13371.25</v>
+        <v>13973</v>
       </c>
       <c r="AF26" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF26</f>
-        <v>2920.75</v>
+        <v>4726</v>
       </c>
       <c r="AG26" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG26</f>
@@ -12570,27 +12574,27 @@
       </c>
       <c r="AA27" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA27</f>
-        <v>435</v>
+        <v>355</v>
       </c>
       <c r="AB27" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB27</f>
-        <v>69.954022988505741</v>
+        <v>85.718309859154928</v>
       </c>
       <c r="AC27" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC27</f>
-        <v>6.9954022988505749</v>
+        <v>8.5718309859154935</v>
       </c>
       <c r="AD27" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD27</f>
-        <v>2608</v>
+        <v>2688</v>
       </c>
       <c r="AE27" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE27</f>
-        <v>217.5</v>
+        <v>177.5</v>
       </c>
       <c r="AF27" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF27</f>
-        <v>-2390.5</v>
+        <v>-2510.5</v>
       </c>
       <c r="AG27" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG27</f>
@@ -12637,15 +12641,15 @@
       </c>
       <c r="L28" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!L28</f>
-        <v>66.548302872062663</v>
+        <v>29.971777986829728</v>
       </c>
       <c r="M28" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!M28</f>
-        <v>1053.25</v>
+        <v>2338.6</v>
       </c>
       <c r="N28" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!N28</f>
-        <v>2707.25</v>
+        <v>2123</v>
       </c>
       <c r="O28" s="19">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!O28</f>
@@ -12695,27 +12699,27 @@
       </c>
       <c r="AA28" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA28</f>
-        <v>478.75</v>
+        <v>1063</v>
       </c>
       <c r="AB28" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB28</f>
-        <v>115.04960835509138</v>
+        <v>51.815616180620886</v>
       </c>
       <c r="AC28" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC28</f>
-        <v>11.504960835509138</v>
+        <v>5.181561618062088</v>
       </c>
       <c r="AD28" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD28</f>
-        <v>5029.25</v>
+        <v>4445</v>
       </c>
       <c r="AE28" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE28</f>
-        <v>239.375</v>
+        <v>531.5</v>
       </c>
       <c r="AF28" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF28</f>
-        <v>-4789.875</v>
+        <v>-3913.5</v>
       </c>
       <c r="AG28" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG28</f>
@@ -12762,15 +12766,15 @@
       </c>
       <c r="L29" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!L29</f>
-        <v>45.13774597495528</v>
+        <v>21.872399445214981</v>
       </c>
       <c r="M29" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!M29</f>
-        <v>1537.25</v>
+        <v>3172.3999999999996</v>
       </c>
       <c r="N29" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!N29</f>
-        <v>2455.25</v>
+        <v>1712</v>
       </c>
       <c r="O29" s="19">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!O29</f>
@@ -12820,27 +12824,27 @@
       </c>
       <c r="AA29" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA29</f>
-        <v>698.75</v>
+        <v>1442</v>
       </c>
       <c r="AB29" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB29</f>
-        <v>78.368515205724506</v>
+        <v>37.975034674063807</v>
       </c>
       <c r="AC29" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC29</f>
-        <v>7.8368515205724512</v>
+        <v>3.7975034674063801</v>
       </c>
       <c r="AD29" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD29</f>
-        <v>4777.25</v>
+        <v>4034</v>
       </c>
       <c r="AE29" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE29</f>
-        <v>349.375</v>
+        <v>721</v>
       </c>
       <c r="AF29" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF29</f>
-        <v>-4427.875</v>
+        <v>-3313</v>
       </c>
       <c r="AG29" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG29</f>
@@ -12887,15 +12891,15 @@
       </c>
       <c r="L30" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!L30</f>
-        <v>53.880794701986758</v>
+        <v>23.272311212814646</v>
       </c>
       <c r="M30" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!M30</f>
-        <v>1245.75</v>
+        <v>2884.2</v>
       </c>
       <c r="N30" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!N30</f>
-        <v>2484.75</v>
+        <v>1740</v>
       </c>
       <c r="O30" s="19">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!O30</f>
@@ -12945,27 +12949,27 @@
       </c>
       <c r="AA30" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA30</f>
-        <v>566.25</v>
+        <v>1311</v>
       </c>
       <c r="AB30" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB30</f>
-        <v>94.88741721854305</v>
+        <v>40.983981693363845</v>
       </c>
       <c r="AC30" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC30</f>
-        <v>9.4887417218543053</v>
+        <v>4.0983981693363845</v>
       </c>
       <c r="AD30" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD30</f>
-        <v>4806.75</v>
+        <v>4062</v>
       </c>
       <c r="AE30" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE30</f>
-        <v>283.125</v>
+        <v>655.5</v>
       </c>
       <c r="AF30" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF30</f>
-        <v>-4523.625</v>
+        <v>-3406.5</v>
       </c>
       <c r="AG30" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG30</f>
@@ -13073,27 +13077,27 @@
       </c>
       <c r="AA31" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA31</f>
-        <v>2222.5</v>
+        <v>2384</v>
       </c>
       <c r="AB31" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB31</f>
-        <v>8.7559055118110241</v>
+        <v>8.1627516778523486</v>
       </c>
       <c r="AC31" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC31</f>
-        <v>0.87559055118110241</v>
+        <v>0.8162751677852349</v>
       </c>
       <c r="AD31" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD31</f>
-        <v>-276.5</v>
+        <v>-438</v>
       </c>
       <c r="AE31" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE31</f>
-        <v>1111.25</v>
+        <v>1192</v>
       </c>
       <c r="AF31" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF31</f>
-        <v>1387.75</v>
+        <v>1630</v>
       </c>
       <c r="AG31" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG31</f>
@@ -13201,27 +13205,27 @@
       </c>
       <c r="AA32" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA32</f>
-        <v>1297.5</v>
+        <v>1298</v>
       </c>
       <c r="AB32" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB32</f>
-        <v>10.034682080924856</v>
+        <v>10.030816640986131</v>
       </c>
       <c r="AC32" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC32</f>
-        <v>1.0034682080924855</v>
+        <v>1.0030816640986133</v>
       </c>
       <c r="AD32" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD32</f>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AE32" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE32</f>
-        <v>648.75</v>
+        <v>649</v>
       </c>
       <c r="AF32" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF32</f>
-        <v>644.25</v>
+        <v>645</v>
       </c>
       <c r="AG32" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG32</f>
@@ -13329,27 +13333,27 @@
       </c>
       <c r="AA33" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA33</f>
-        <v>5282.5</v>
+        <v>5003</v>
       </c>
       <c r="AB33" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB33</f>
-        <v>5.6034074775201139</v>
+        <v>5.9164501299220467</v>
       </c>
       <c r="AC33" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC33</f>
-        <v>0.56034074775201137</v>
+        <v>0.59164501299220462</v>
       </c>
       <c r="AD33" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD33</f>
-        <v>-2322.5</v>
+        <v>-2043</v>
       </c>
       <c r="AE33" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE33</f>
-        <v>2641.25</v>
+        <v>2501.5</v>
       </c>
       <c r="AF33" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF33</f>
-        <v>4963.75</v>
+        <v>4544.5</v>
       </c>
       <c r="AG33" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG33</f>
@@ -13457,27 +13461,27 @@
       </c>
       <c r="AA34" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA34</f>
-        <v>7961.25</v>
+        <v>7763</v>
       </c>
       <c r="AB34" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB34</f>
-        <v>9.2912545140524418</v>
+        <v>9.528532783717635</v>
       </c>
       <c r="AC34" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC34</f>
-        <v>0.92912545140524416</v>
+        <v>0.95285327837176348</v>
       </c>
       <c r="AD34" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD34</f>
-        <v>-564.25</v>
+        <v>-366</v>
       </c>
       <c r="AE34" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE34</f>
-        <v>3980.625</v>
+        <v>3881.5</v>
       </c>
       <c r="AF34" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF34</f>
-        <v>4544.875</v>
+        <v>4247.5</v>
       </c>
       <c r="AG34" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG34</f>
@@ -13585,7 +13589,7 @@
       </c>
       <c r="AA35" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA35</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB35" s="34">
         <v>0</v>
@@ -13595,15 +13599,15 @@
       </c>
       <c r="AD35" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD35</f>
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE35" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE35</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF35" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF35</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AG35" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG35</f>
@@ -13704,27 +13708,27 @@
       </c>
       <c r="AA36" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA36</f>
-        <v>727.5</v>
+        <v>1500</v>
       </c>
       <c r="AB36" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB36</f>
-        <v>3.8075601374570445</v>
+        <v>1.8466666666666667</v>
       </c>
       <c r="AC36" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC36</f>
-        <v>0.38075601374570445</v>
+        <v>0.18466666666666667</v>
       </c>
       <c r="AD36" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD36</f>
-        <v>-450.5</v>
+        <v>-1223</v>
       </c>
       <c r="AE36" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE36</f>
-        <v>363.75</v>
+        <v>750</v>
       </c>
       <c r="AF36" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF36</f>
-        <v>814.25</v>
+        <v>1973</v>
       </c>
       <c r="AG36" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG36</f>
@@ -13832,27 +13836,27 @@
       </c>
       <c r="AA37" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA37</f>
-        <v>6561.25</v>
+        <v>6782</v>
       </c>
       <c r="AB37" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB37</f>
-        <v>15.64031244046485</v>
+        <v>15.131229725744618</v>
       </c>
       <c r="AC37" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC37</f>
-        <v>1.564031244046485</v>
+        <v>1.5131229725744617</v>
       </c>
       <c r="AD37" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD37</f>
-        <v>3700.75</v>
+        <v>3480</v>
       </c>
       <c r="AE37" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE37</f>
-        <v>3280.625</v>
+        <v>3391</v>
       </c>
       <c r="AF37" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF37</f>
-        <v>-420.125</v>
+        <v>-89</v>
       </c>
       <c r="AG37" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG37</f>
@@ -13960,27 +13964,27 @@
       </c>
       <c r="AA38" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA38</f>
-        <v>11485</v>
+        <v>11052</v>
       </c>
       <c r="AB38" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB38</f>
-        <v>7.045711797997388</v>
+        <v>7.3217517191458557</v>
       </c>
       <c r="AC38" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC38</f>
-        <v>0.70457117979973882</v>
+        <v>0.73217517191458559</v>
       </c>
       <c r="AD38" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD38</f>
-        <v>-3393</v>
+        <v>-2960</v>
       </c>
       <c r="AE38" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE38</f>
-        <v>5742.5</v>
+        <v>5526</v>
       </c>
       <c r="AF38" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF38</f>
-        <v>9135.5</v>
+        <v>8486</v>
       </c>
       <c r="AG38" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG38</f>
@@ -14088,27 +14092,27 @@
       </c>
       <c r="AA39" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA39</f>
-        <v>5206.25</v>
+        <v>4932</v>
       </c>
       <c r="AB39" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB39</f>
-        <v>5.7584633853541414</v>
+        <v>6.078669910786699</v>
       </c>
       <c r="AC39" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC39</f>
-        <v>0.57584633853541412</v>
+        <v>0.60786699107866993</v>
       </c>
       <c r="AD39" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD39</f>
-        <v>-2208.25</v>
+        <v>-1934</v>
       </c>
       <c r="AE39" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE39</f>
-        <v>2603.125</v>
+        <v>2466</v>
       </c>
       <c r="AF39" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF39</f>
-        <v>4811.375</v>
+        <v>4400</v>
       </c>
       <c r="AG39" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG39</f>
@@ -14216,27 +14220,27 @@
       </c>
       <c r="AA40" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA40</f>
-        <v>3810</v>
+        <v>3391</v>
       </c>
       <c r="AB40" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB40</f>
-        <v>4.7244094488188972</v>
+        <v>5.3081686818047773</v>
       </c>
       <c r="AC40" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC40</f>
-        <v>0.47244094488188976</v>
+        <v>0.53081686818047769</v>
       </c>
       <c r="AD40" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD40</f>
-        <v>-2010</v>
+        <v>-1591</v>
       </c>
       <c r="AE40" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE40</f>
-        <v>1905</v>
+        <v>1695.5</v>
       </c>
       <c r="AF40" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF40</f>
-        <v>3915</v>
+        <v>3286.5</v>
       </c>
       <c r="AG40" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG40</f>
@@ -14344,27 +14348,27 @@
       </c>
       <c r="AA41" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA41</f>
-        <v>1361.25</v>
+        <v>1326</v>
       </c>
       <c r="AB41" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB41</f>
-        <v>8.1983471074380159</v>
+        <v>8.4162895927601813</v>
       </c>
       <c r="AC41" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC41</f>
-        <v>0.81983471074380165</v>
+        <v>0.84162895927601811</v>
       </c>
       <c r="AD41" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD41</f>
-        <v>-245.25</v>
+        <v>-210</v>
       </c>
       <c r="AE41" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE41</f>
-        <v>680.625</v>
+        <v>663</v>
       </c>
       <c r="AF41" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF41</f>
-        <v>925.875</v>
+        <v>873</v>
       </c>
       <c r="AG41" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG41</f>
@@ -14472,27 +14476,27 @@
       </c>
       <c r="AA42" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA42</f>
-        <v>1106.25</v>
+        <v>1192</v>
       </c>
       <c r="AB42" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB42</f>
-        <v>13.604519774011299</v>
+        <v>12.625838926174497</v>
       </c>
       <c r="AC42" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC42</f>
-        <v>1.3604519774011299</v>
+        <v>1.2625838926174497</v>
       </c>
       <c r="AD42" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD42</f>
-        <v>398.75</v>
+        <v>313</v>
       </c>
       <c r="AE42" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE42</f>
-        <v>553.125</v>
+        <v>596</v>
       </c>
       <c r="AF42" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF42</f>
-        <v>154.375</v>
+        <v>283</v>
       </c>
       <c r="AG42" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG42</f>
@@ -14600,27 +14604,27 @@
       </c>
       <c r="AA43" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA43</f>
-        <v>6173.75</v>
+        <v>6145</v>
       </c>
       <c r="AB43" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB43</f>
-        <v>9.0884794492812304</v>
+        <v>9.131000813669651</v>
       </c>
       <c r="AC43" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC43</f>
-        <v>0.90884794492812315</v>
+        <v>0.91310008136696497</v>
       </c>
       <c r="AD43" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD43</f>
-        <v>-562.75</v>
+        <v>-534</v>
       </c>
       <c r="AE43" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE43</f>
-        <v>3086.875</v>
+        <v>3072.5</v>
       </c>
       <c r="AF43" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF43</f>
-        <v>3649.625</v>
+        <v>3606.5</v>
       </c>
       <c r="AG43" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG43</f>
@@ -14728,27 +14732,27 @@
       </c>
       <c r="AA44" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA44</f>
-        <v>6892.5</v>
+        <v>6715</v>
       </c>
       <c r="AB44" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB44</f>
-        <v>14.726151614073268</v>
+        <v>15.115413253909159</v>
       </c>
       <c r="AC44" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC44</f>
-        <v>1.4726151614073268</v>
+        <v>1.5115413253909158</v>
       </c>
       <c r="AD44" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD44</f>
-        <v>3257.5</v>
+        <v>3435</v>
       </c>
       <c r="AE44" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE44</f>
-        <v>3446.25</v>
+        <v>3357.5</v>
       </c>
       <c r="AF44" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF44</f>
-        <v>188.75</v>
+        <v>-77.5</v>
       </c>
       <c r="AG44" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG44</f>
@@ -14856,27 +14860,27 @@
       </c>
       <c r="AA45" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA45</f>
-        <v>9117.5</v>
+        <v>8316</v>
       </c>
       <c r="AB45" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB45</f>
-        <v>9.0134357005758154</v>
+        <v>9.8821548821548824</v>
       </c>
       <c r="AC45" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC45</f>
-        <v>0.90134357005758159</v>
+        <v>0.98821548821548821</v>
       </c>
       <c r="AD45" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD45</f>
-        <v>-899.5</v>
+        <v>-98</v>
       </c>
       <c r="AE45" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE45</f>
-        <v>4558.75</v>
+        <v>4158</v>
       </c>
       <c r="AF45" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF45</f>
-        <v>5458.25</v>
+        <v>4256</v>
       </c>
       <c r="AG45" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG45</f>
@@ -14984,27 +14988,27 @@
       </c>
       <c r="AA46" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA46</f>
-        <v>5860</v>
+        <v>5818</v>
       </c>
       <c r="AB46" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB46</f>
-        <v>11.46075085324232</v>
+        <v>11.543485733929186</v>
       </c>
       <c r="AC46" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC46</f>
-        <v>1.1460750853242321</v>
+        <v>1.1543485733929186</v>
       </c>
       <c r="AD46" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD46</f>
-        <v>856</v>
+        <v>898</v>
       </c>
       <c r="AE46" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE46</f>
-        <v>2930</v>
+        <v>2909</v>
       </c>
       <c r="AF46" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF46</f>
-        <v>2074</v>
+        <v>2011</v>
       </c>
       <c r="AG46" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG46</f>
@@ -15105,27 +15109,27 @@
       </c>
       <c r="AA47" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA47</f>
-        <v>16.25</v>
+        <v>24</v>
       </c>
       <c r="AB47" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB47</f>
-        <v>9.8461538461538467</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="AC47" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC47</f>
-        <v>0.98461538461538467</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AD47" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD47</f>
-        <v>-0.25</v>
+        <v>-8</v>
       </c>
       <c r="AE47" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE47</f>
-        <v>8.125</v>
+        <v>12</v>
       </c>
       <c r="AF47" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF47</f>
-        <v>8.375</v>
+        <v>20</v>
       </c>
       <c r="AG47" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG47</f>
@@ -15349,27 +15353,27 @@
       </c>
       <c r="AA49" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA49</f>
-        <v>218.75</v>
+        <v>175</v>
       </c>
       <c r="AB49" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB49</f>
-        <v>4.9828571428571431</v>
+        <v>6.2285714285714286</v>
       </c>
       <c r="AC49" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC49</f>
-        <v>0.49828571428571428</v>
+        <v>0.62285714285714289</v>
       </c>
       <c r="AD49" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD49</f>
-        <v>-109.75</v>
+        <v>-66</v>
       </c>
       <c r="AE49" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE49</f>
-        <v>109.375</v>
+        <v>87.5</v>
       </c>
       <c r="AF49" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF49</f>
-        <v>219.125</v>
+        <v>153.5</v>
       </c>
       <c r="AG49" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG49</f>
@@ -15605,27 +15609,27 @@
       </c>
       <c r="AA51" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA51</f>
-        <v>886.25</v>
+        <v>709</v>
       </c>
       <c r="AB51" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB51</f>
-        <v>0.1918194640338505</v>
+        <v>0.23977433004231311</v>
       </c>
       <c r="AC51" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC51</f>
-        <v>1.9181946403385049E-2</v>
+        <v>2.3977433004231313E-2</v>
       </c>
       <c r="AD51" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD51</f>
-        <v>-869.25</v>
+        <v>-692</v>
       </c>
       <c r="AE51" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE51</f>
-        <v>443.125</v>
+        <v>354.5</v>
       </c>
       <c r="AF51" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF51</f>
-        <v>1312.375</v>
+        <v>1046.5</v>
       </c>
       <c r="AG51" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG51</f>
@@ -15733,27 +15737,27 @@
       </c>
       <c r="AA52" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA52</f>
-        <v>3163.75</v>
+        <v>3036</v>
       </c>
       <c r="AB52" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB52</f>
-        <v>25.311734492295535</v>
+        <v>26.376811594202895</v>
       </c>
       <c r="AC52" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC52</f>
-        <v>2.5311734492295535</v>
+        <v>2.63768115942029</v>
       </c>
       <c r="AD52" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD52</f>
-        <v>4844.25</v>
+        <v>4972</v>
       </c>
       <c r="AE52" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE52</f>
-        <v>1581.875</v>
+        <v>1518</v>
       </c>
       <c r="AF52" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF52</f>
-        <v>-3262.375</v>
+        <v>-3454</v>
       </c>
       <c r="AG52" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG52</f>
@@ -15861,27 +15865,27 @@
       </c>
       <c r="AA53" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA53</f>
-        <v>5653.75</v>
+        <v>5285</v>
       </c>
       <c r="AB53" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB53</f>
-        <v>13.007296042449701</v>
+        <v>13.914853358561968</v>
       </c>
       <c r="AC53" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC53</f>
-        <v>1.3007296042449701</v>
+        <v>1.3914853358561967</v>
       </c>
       <c r="AD53" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD53</f>
-        <v>1700.25</v>
+        <v>2069</v>
       </c>
       <c r="AE53" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE53</f>
-        <v>2826.875</v>
+        <v>2642.5</v>
       </c>
       <c r="AF53" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF53</f>
-        <v>1126.625</v>
+        <v>573.5</v>
       </c>
       <c r="AG53" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG53</f>
@@ -15989,27 +15993,27 @@
       </c>
       <c r="AA54" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA54</f>
-        <v>3317.5</v>
+        <v>3223</v>
       </c>
       <c r="AB54" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB54</f>
-        <v>21.600602863602109</v>
+        <v>22.233943530871858</v>
       </c>
       <c r="AC54" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC54</f>
-        <v>2.1600602863602112</v>
+        <v>2.223394353087186</v>
       </c>
       <c r="AD54" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD54</f>
-        <v>3848.5</v>
+        <v>3943</v>
       </c>
       <c r="AE54" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE54</f>
-        <v>1658.75</v>
+        <v>1611.5</v>
       </c>
       <c r="AF54" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF54</f>
-        <v>-2189.75</v>
+        <v>-2331.5</v>
       </c>
       <c r="AG54" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG54</f>
@@ -16117,27 +16121,27 @@
       </c>
       <c r="AA55" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA55</f>
-        <v>2681.25</v>
+        <v>2734</v>
       </c>
       <c r="AB55" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB55</f>
-        <v>32.45128205128205</v>
+        <v>31.825164594001464</v>
       </c>
       <c r="AC55" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC55</f>
-        <v>3.2451282051282053</v>
+        <v>3.1825164594001465</v>
       </c>
       <c r="AD55" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD55</f>
-        <v>6019.75</v>
+        <v>5967</v>
       </c>
       <c r="AE55" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE55</f>
-        <v>1340.625</v>
+        <v>1367</v>
       </c>
       <c r="AF55" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF55</f>
-        <v>-4679.125</v>
+        <v>-4600</v>
       </c>
       <c r="AG55" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG55</f>
@@ -16245,27 +16249,27 @@
       </c>
       <c r="AA56" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA56</f>
-        <v>522.5</v>
+        <v>446</v>
       </c>
       <c r="AB56" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB56</f>
-        <v>10.4688995215311</v>
+        <v>12.264573991031389</v>
       </c>
       <c r="AC56" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC56</f>
-        <v>1.0468899521531101</v>
+        <v>1.2264573991031391</v>
       </c>
       <c r="AD56" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD56</f>
-        <v>24.5</v>
+        <v>101</v>
       </c>
       <c r="AE56" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE56</f>
-        <v>261.25</v>
+        <v>223</v>
       </c>
       <c r="AF56" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF56</f>
-        <v>236.75</v>
+        <v>122</v>
       </c>
       <c r="AG56" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG56</f>
@@ -16373,27 +16377,27 @@
       </c>
       <c r="AA57" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA57</f>
-        <v>1036.25</v>
+        <v>933</v>
       </c>
       <c r="AB57" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB57</f>
-        <v>3.3003618817852836</v>
+        <v>3.6655948553054665</v>
       </c>
       <c r="AC57" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC57</f>
-        <v>0.33003618817852837</v>
+        <v>0.36655948553054662</v>
       </c>
       <c r="AD57" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD57</f>
-        <v>-694.25</v>
+        <v>-591</v>
       </c>
       <c r="AE57" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE57</f>
-        <v>518.125</v>
+        <v>466.5</v>
       </c>
       <c r="AF57" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF57</f>
-        <v>1212.375</v>
+        <v>1057.5</v>
       </c>
       <c r="AG57" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG57</f>
@@ -16501,27 +16505,27 @@
       </c>
       <c r="AA58" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA58</f>
-        <v>673.75</v>
+        <v>546</v>
       </c>
       <c r="AB58" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB58</f>
-        <v>3.3543599257884971</v>
+        <v>4.1391941391941387</v>
       </c>
       <c r="AC58" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC58</f>
-        <v>0.33543599257884971</v>
+        <v>0.41391941391941389</v>
       </c>
       <c r="AD58" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD58</f>
-        <v>-447.75</v>
+        <v>-320</v>
       </c>
       <c r="AE58" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE58</f>
-        <v>336.875</v>
+        <v>273</v>
       </c>
       <c r="AF58" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF58</f>
-        <v>784.625</v>
+        <v>593</v>
       </c>
       <c r="AG58" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG58</f>
@@ -16629,27 +16633,27 @@
       </c>
       <c r="AA59" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AA59</f>
-        <v>550</v>
+        <v>467</v>
       </c>
       <c r="AB59" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AB59</f>
-        <v>3.4909090909090907</v>
+        <v>4.1113490364025695</v>
       </c>
       <c r="AC59" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AC59</f>
-        <v>0.34909090909090912</v>
+        <v>0.41113490364025695</v>
       </c>
       <c r="AD59" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AD59</f>
-        <v>-358</v>
+        <v>-275</v>
       </c>
       <c r="AE59" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AE59</f>
-        <v>275</v>
+        <v>233.5</v>
       </c>
       <c r="AF59" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 13-08-26'!AF59</f>
-        <v>633</v>
+        <v>508.5</v>
       </c>
       <c r="AG59" s="31">
         <f>'[1]INVENTARIO NACIONAL 13-08-26'!AG59</f>
@@ -16688,7 +16692,7 @@
       </c>
       <c r="AF60" s="44">
         <f ca="1">SUMIF(AF13:AF59,"&gt;0")</f>
-        <v>118775.375</v>
+        <v>120496.5</v>
       </c>
     </row>
     <row r="61" spans="2:33" x14ac:dyDescent="0.25">
@@ -16697,10 +16701,10 @@
       </c>
       <c r="C61" s="46"/>
       <c r="D61" s="46"/>
-      <c r="E61" s="64" t="s">
+      <c r="E61" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="F61" s="64"/>
+      <c r="F61" s="67"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -16725,10 +16729,10 @@
       <c r="AB61" s="42"/>
     </row>
     <row r="62" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="C62" s="65"/>
+      <c r="C62" s="63"/>
       <c r="D62" s="48">
         <f>SUM(F13:F59)</f>
         <v>169370.28999999998</v>
@@ -16873,19 +16877,19 @@
       <c r="AB65" s="42"/>
     </row>
     <row r="66" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B66" s="65" t="s">
+      <c r="B66" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="C66" s="65"/>
+      <c r="C66" s="63"/>
       <c r="D66" s="50">
         <f>SUM(Z13:Z59)</f>
         <v>396824.73999999993</v>
       </c>
-      <c r="E66" s="66">
+      <c r="E66" s="64">
         <f>D66*100/D66</f>
         <v>100</v>
       </c>
-      <c r="F66" s="66"/>
+      <c r="F66" s="64"/>
       <c r="G66" s="51"/>
       <c r="H66" s="51"/>
       <c r="I66" s="51"/>
@@ -16970,10 +16974,10 @@
       <c r="AB68" s="42"/>
     </row>
     <row r="69" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B69" s="65" t="s">
+      <c r="B69" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="C69" s="65"/>
+      <c r="C69" s="63"/>
       <c r="D69" s="3">
         <f>SUM(E13:E59)</f>
         <v>125925</v>
@@ -17088,11 +17092,11 @@
         <f>SUM(T13:T59)</f>
         <v>46674</v>
       </c>
-      <c r="E72" s="67">
+      <c r="E72" s="62">
         <f>D72*100/D73</f>
         <v>15.919695481335953</v>
       </c>
-      <c r="F72" s="67"/>
+      <c r="F72" s="62"/>
       <c r="G72" s="56"/>
       <c r="H72" s="56"/>
       <c r="I72" s="56"/>
@@ -17117,19 +17121,19 @@
       <c r="AB72" s="42"/>
     </row>
     <row r="73" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B73" s="65" t="s">
+      <c r="B73" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="65"/>
+      <c r="C73" s="63"/>
       <c r="D73" s="55">
         <f>SUM(Y13:Y59)</f>
         <v>293184</v>
       </c>
-      <c r="E73" s="67">
+      <c r="E73" s="62">
         <f>D73*100/D73</f>
         <v>100</v>
       </c>
-      <c r="F73" s="67"/>
+      <c r="F73" s="62"/>
       <c r="G73" s="56"/>
       <c r="H73" s="56"/>
       <c r="I73" s="56"/>
@@ -17890,23 +17894,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B1:Z6"/>
+    <mergeCell ref="AA1:AG6"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
     <mergeCell ref="E64:F64"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="B66:C66"/>
     <mergeCell ref="E66:F66"/>
     <mergeCell ref="B69:C69"/>
     <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="B1:Z6"/>
-    <mergeCell ref="AA1:AG6"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="E73:F73"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="5">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6A0ABD-52FC-4E8D-9265-1B3B569BDB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01A8870-B5F7-4FC8-A364-3BBA159AB4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -841,6 +841,15 @@
     <xf numFmtId="2" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -849,15 +858,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5637,6 +5637,7 @@
       <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -5764,22 +5765,22 @@
             <v>13606.800000000001</v>
           </cell>
           <cell r="AA13">
-            <v>11756</v>
+            <v>12944</v>
           </cell>
           <cell r="AB13">
-            <v>8.5105478053759782</v>
+            <v>7.7294499381953026</v>
           </cell>
           <cell r="AC13">
-            <v>0.85105478053759787</v>
+            <v>0.7729449938195303</v>
           </cell>
           <cell r="AD13">
-            <v>-1751</v>
+            <v>-2939</v>
           </cell>
           <cell r="AE13">
-            <v>5878</v>
+            <v>6472</v>
           </cell>
           <cell r="AF13">
-            <v>7629</v>
+            <v>9411</v>
           </cell>
           <cell r="AG13">
             <v>125.0625</v>
@@ -5856,22 +5857,22 @@
             <v>888.81000000000006</v>
           </cell>
           <cell r="AA14">
-            <v>823</v>
+            <v>903</v>
           </cell>
           <cell r="AB14">
-            <v>6.7922235722964768</v>
+            <v>6.1904761904761907</v>
           </cell>
           <cell r="AC14">
-            <v>0.67922235722964763</v>
+            <v>0.61904761904761907</v>
           </cell>
           <cell r="AD14">
-            <v>-264</v>
+            <v>-344</v>
           </cell>
           <cell r="AE14">
-            <v>411.5</v>
+            <v>451.5</v>
           </cell>
           <cell r="AF14">
-            <v>675.5</v>
+            <v>795.5</v>
           </cell>
           <cell r="AG14">
             <v>6.9874999999999998</v>
@@ -5948,22 +5949,22 @@
             <v>6966.9599999999991</v>
           </cell>
           <cell r="AA15">
-            <v>4634</v>
+            <v>5279</v>
           </cell>
           <cell r="AB15">
-            <v>7.4061286145878293</v>
+            <v>6.5012312938056454</v>
           </cell>
           <cell r="AC15">
-            <v>0.74061286145878291</v>
+            <v>0.65012312938056449</v>
           </cell>
           <cell r="AD15">
-            <v>-1202</v>
+            <v>-1847</v>
           </cell>
           <cell r="AE15">
-            <v>2317</v>
+            <v>2639.5</v>
           </cell>
           <cell r="AF15">
-            <v>3519</v>
+            <v>4486.5</v>
           </cell>
           <cell r="AG15">
             <v>57.2</v>
@@ -6040,22 +6041,22 @@
             <v>743.66</v>
           </cell>
           <cell r="AA16">
-            <v>1004</v>
+            <v>1061</v>
           </cell>
           <cell r="AB16">
-            <v>2.0517928286852589</v>
+            <v>1.9415645617342132</v>
           </cell>
           <cell r="AC16">
-            <v>0.20517928286852591</v>
+            <v>0.19415645617342131</v>
           </cell>
           <cell r="AD16">
-            <v>-798</v>
+            <v>-855</v>
           </cell>
           <cell r="AE16">
-            <v>502</v>
+            <v>530.5</v>
           </cell>
           <cell r="AF16">
-            <v>1300</v>
+            <v>1385.5</v>
           </cell>
           <cell r="AG16">
             <v>7.3571428571428568</v>
@@ -6132,22 +6133,22 @@
             <v>1861.36</v>
           </cell>
           <cell r="AA17">
-            <v>90</v>
+            <v>105</v>
           </cell>
           <cell r="AB17">
-            <v>23.555555555555557</v>
+            <v>20.19047619047619</v>
           </cell>
           <cell r="AC17">
-            <v>2.3555555555555556</v>
+            <v>2.019047619047619</v>
           </cell>
           <cell r="AD17">
-            <v>122</v>
+            <v>107</v>
           </cell>
           <cell r="AE17">
-            <v>45</v>
+            <v>52.5</v>
           </cell>
           <cell r="AF17">
-            <v>-77</v>
+            <v>-54.5</v>
           </cell>
           <cell r="AG17">
             <v>17.666666666666668</v>
@@ -6224,22 +6225,22 @@
             <v>5277.51</v>
           </cell>
           <cell r="AA18">
-            <v>14437</v>
+            <v>15948</v>
           </cell>
           <cell r="AB18">
-            <v>5.8024520329708382</v>
+            <v>5.2526962628542764</v>
           </cell>
           <cell r="AC18">
-            <v>0.58024520329708384</v>
+            <v>0.52526962628542762</v>
           </cell>
           <cell r="AD18">
-            <v>-6060</v>
+            <v>-7571</v>
           </cell>
           <cell r="AE18">
-            <v>7218.5</v>
+            <v>7974</v>
           </cell>
           <cell r="AF18">
-            <v>13278.5</v>
+            <v>15545</v>
           </cell>
           <cell r="AG18">
             <v>139.61666666666667</v>
@@ -6316,22 +6317,22 @@
             <v>949.41</v>
           </cell>
           <cell r="AA19">
-            <v>1441</v>
+            <v>1537</v>
           </cell>
           <cell r="AB19">
-            <v>10.458015267175574</v>
+            <v>9.8048145738451531</v>
           </cell>
           <cell r="AC19">
-            <v>1.0458015267175573</v>
+            <v>0.98048145738451531</v>
           </cell>
           <cell r="AD19">
-            <v>66</v>
+            <v>-30</v>
           </cell>
           <cell r="AE19">
-            <v>720.5</v>
+            <v>768.5</v>
           </cell>
           <cell r="AF19">
-            <v>654.5</v>
+            <v>798.5</v>
           </cell>
           <cell r="AG19">
             <v>25.116666666666667</v>
@@ -6408,22 +6409,22 @@
             <v>2498.58</v>
           </cell>
           <cell r="AA20">
-            <v>3157</v>
+            <v>3403</v>
           </cell>
           <cell r="AB20">
-            <v>12.562559391827685</v>
+            <v>11.654422568322069</v>
           </cell>
           <cell r="AC20">
-            <v>1.2562559391827683</v>
+            <v>1.1654422568322069</v>
           </cell>
           <cell r="AD20">
-            <v>809</v>
+            <v>563</v>
           </cell>
           <cell r="AE20">
-            <v>1578.5</v>
+            <v>1701.5</v>
           </cell>
           <cell r="AF20">
-            <v>769.5</v>
+            <v>1138.5</v>
           </cell>
           <cell r="AG20">
             <v>66.099999999999994</v>
@@ -6500,22 +6501,22 @@
             <v>8325.42</v>
           </cell>
           <cell r="AA21">
-            <v>7180</v>
+            <v>7625</v>
           </cell>
           <cell r="AB21">
-            <v>10.637883008356546</v>
+            <v>10.017049180327868</v>
           </cell>
           <cell r="AC21">
-            <v>1.0637883008356546</v>
+            <v>1.0017049180327868</v>
           </cell>
           <cell r="AD21">
-            <v>458</v>
+            <v>13</v>
           </cell>
           <cell r="AE21">
-            <v>3590</v>
+            <v>3812.5</v>
           </cell>
           <cell r="AF21">
-            <v>3132</v>
+            <v>3799.5</v>
           </cell>
           <cell r="AG21">
             <v>141.44444444444446</v>
@@ -6592,22 +6593,22 @@
             <v>4099.4900000000007</v>
           </cell>
           <cell r="AA22">
-            <v>3422</v>
+            <v>3542</v>
           </cell>
           <cell r="AB22">
-            <v>10.990648743424899</v>
+            <v>10.618294748729532</v>
           </cell>
           <cell r="AC22">
-            <v>1.0990648743424898</v>
+            <v>1.0618294748729531</v>
           </cell>
           <cell r="AD22">
-            <v>339</v>
+            <v>219</v>
           </cell>
           <cell r="AE22">
-            <v>1711</v>
+            <v>1771</v>
           </cell>
           <cell r="AF22">
-            <v>1372</v>
+            <v>1552</v>
           </cell>
           <cell r="AG22">
             <v>69.648148148148152</v>
@@ -6684,22 +6685,22 @@
             <v>38473.719999999994</v>
           </cell>
           <cell r="AA23">
-            <v>36510</v>
+            <v>39911</v>
           </cell>
           <cell r="AB23">
-            <v>9.0843604491920029</v>
+            <v>8.3102402846333092</v>
           </cell>
           <cell r="AC23">
-            <v>0.90843604491920027</v>
+            <v>0.8310240284633309</v>
           </cell>
           <cell r="AD23">
-            <v>-3343</v>
+            <v>-6744</v>
           </cell>
           <cell r="AE23">
-            <v>18255</v>
+            <v>19955.5</v>
           </cell>
           <cell r="AF23">
-            <v>21598</v>
+            <v>26699.5</v>
           </cell>
           <cell r="AG23">
             <v>614.2037037037037</v>
@@ -6776,22 +6777,22 @@
             <v>29054.519999999997</v>
           </cell>
           <cell r="AA24">
-            <v>24080</v>
+            <v>26342</v>
           </cell>
           <cell r="AB24">
-            <v>10.4015780730897</v>
+            <v>9.5083896439146613</v>
           </cell>
           <cell r="AC24">
-            <v>1.0401578073089701</v>
+            <v>0.95083896439146609</v>
           </cell>
           <cell r="AD24">
-            <v>967</v>
+            <v>-1295</v>
           </cell>
           <cell r="AE24">
-            <v>12040</v>
+            <v>13171</v>
           </cell>
           <cell r="AF24">
-            <v>11073</v>
+            <v>14466</v>
           </cell>
           <cell r="AG24">
             <v>463.83333333333331</v>
@@ -6868,22 +6869,22 @@
             <v>30040.519999999997</v>
           </cell>
           <cell r="AA25">
-            <v>23292</v>
+            <v>25420</v>
           </cell>
           <cell r="AB25">
-            <v>11.118409754422119</v>
+            <v>10.187647521636507</v>
           </cell>
           <cell r="AC25">
-            <v>1.1118409754422118</v>
+            <v>1.0187647521636507</v>
           </cell>
           <cell r="AD25">
-            <v>2605</v>
+            <v>477</v>
           </cell>
           <cell r="AE25">
-            <v>11646</v>
+            <v>12710</v>
           </cell>
           <cell r="AF25">
-            <v>9041</v>
+            <v>12233</v>
           </cell>
           <cell r="AG25">
             <v>479.57407407407408</v>
@@ -6960,22 +6961,22 @@
             <v>34369.64</v>
           </cell>
           <cell r="AA26">
-            <v>27946</v>
+            <v>30373</v>
           </cell>
           <cell r="AB26">
-            <v>10.602232877692693</v>
+            <v>9.7550455997102681</v>
           </cell>
           <cell r="AC26">
-            <v>1.0602232877692692</v>
+            <v>0.97550455997102692</v>
           </cell>
           <cell r="AD26">
-            <v>1683</v>
+            <v>-744</v>
           </cell>
           <cell r="AE26">
-            <v>13973</v>
+            <v>15186.5</v>
           </cell>
           <cell r="AF26">
-            <v>12290</v>
+            <v>15930.5</v>
           </cell>
           <cell r="AG26">
             <v>548.68518518518522</v>
@@ -7052,22 +7053,22 @@
             <v>1758.56</v>
           </cell>
           <cell r="AA27">
-            <v>355</v>
+            <v>365</v>
           </cell>
           <cell r="AB27">
-            <v>42.70422535211268</v>
+            <v>41.534246575342465</v>
           </cell>
           <cell r="AC27">
-            <v>4.2704225352112672</v>
+            <v>4.1534246575342468</v>
           </cell>
           <cell r="AD27">
-            <v>1161</v>
+            <v>1151</v>
           </cell>
           <cell r="AE27">
-            <v>177.5</v>
+            <v>182.5</v>
           </cell>
           <cell r="AF27">
-            <v>-983.5</v>
+            <v>-968.5</v>
           </cell>
           <cell r="AG27">
             <v>28.074074074074073</v>
@@ -7099,13 +7100,13 @@
             <v>3519.4399999999996</v>
           </cell>
           <cell r="L28">
-            <v>28.541862652869238</v>
+            <v>17.847058823529412</v>
           </cell>
           <cell r="M28">
-            <v>2338.6</v>
+            <v>3740</v>
           </cell>
           <cell r="N28">
-            <v>1439.5</v>
+            <v>484</v>
           </cell>
           <cell r="O28">
             <v>251</v>
@@ -7144,22 +7145,22 @@
             <v>5583.08</v>
           </cell>
           <cell r="AA28">
-            <v>1063</v>
+            <v>1700</v>
           </cell>
           <cell r="AB28">
-            <v>45.277516462841014</v>
+            <v>28.311764705882354</v>
           </cell>
           <cell r="AC28">
-            <v>4.5277516462841012</v>
+            <v>2.8311764705882352</v>
           </cell>
           <cell r="AD28">
-            <v>3750</v>
+            <v>3113</v>
           </cell>
           <cell r="AE28">
-            <v>531.5</v>
+            <v>850</v>
           </cell>
           <cell r="AF28">
-            <v>-3218.5</v>
+            <v>-2263</v>
           </cell>
           <cell r="AG28">
             <v>89.129629629629633</v>
@@ -7191,13 +7192,13 @@
             <v>3309.4799999999996</v>
           </cell>
           <cell r="L29">
-            <v>19.785020804438282</v>
+            <v>13.245125348189415</v>
           </cell>
           <cell r="M29">
-            <v>3172.3999999999996</v>
+            <v>4738.8</v>
           </cell>
           <cell r="N29">
-            <v>690</v>
+            <v>-378</v>
           </cell>
           <cell r="O29">
             <v>236</v>
@@ -7236,22 +7237,22 @@
             <v>5281.48</v>
           </cell>
           <cell r="AA29">
-            <v>1442</v>
+            <v>2154</v>
           </cell>
           <cell r="AB29">
-            <v>31.574202496532596</v>
+            <v>21.137418755803157</v>
           </cell>
           <cell r="AC29">
-            <v>3.1574202496532595</v>
+            <v>2.1137418755803159</v>
           </cell>
           <cell r="AD29">
-            <v>3111</v>
+            <v>2399</v>
           </cell>
           <cell r="AE29">
-            <v>721</v>
+            <v>1077</v>
           </cell>
           <cell r="AF29">
-            <v>-2390</v>
+            <v>-1322</v>
           </cell>
           <cell r="AG29">
             <v>84.31481481481481</v>
@@ -7283,13 +7284,13 @@
             <v>3259.6</v>
           </cell>
           <cell r="L30">
-            <v>21.434019832189168</v>
+            <v>13.876543209876543</v>
           </cell>
           <cell r="M30">
-            <v>2884.2</v>
+            <v>4455</v>
           </cell>
           <cell r="N30">
-            <v>843.5</v>
+            <v>-227.5</v>
           </cell>
           <cell r="O30">
             <v>236</v>
@@ -7328,22 +7329,22 @@
             <v>6992.48</v>
           </cell>
           <cell r="AA30">
-            <v>1311</v>
+            <v>2025</v>
           </cell>
           <cell r="AB30">
-            <v>45.980167810831425</v>
+            <v>29.767901234567901</v>
           </cell>
           <cell r="AC30">
-            <v>4.5980167810831425</v>
+            <v>2.9767901234567899</v>
           </cell>
           <cell r="AD30">
-            <v>4717</v>
+            <v>4003</v>
           </cell>
           <cell r="AE30">
-            <v>655.5</v>
+            <v>1012.5</v>
           </cell>
           <cell r="AF30">
-            <v>-4061.5</v>
+            <v>-2990.5</v>
           </cell>
           <cell r="AG30">
             <v>111.62962962962963</v>
@@ -7420,22 +7421,22 @@
             <v>5045.2800000000007</v>
           </cell>
           <cell r="AA31">
-            <v>2384</v>
+            <v>2523</v>
           </cell>
           <cell r="AB31">
-            <v>5.7508389261744961</v>
+            <v>5.4340071343638527</v>
           </cell>
           <cell r="AC31">
-            <v>0.57508389261744963</v>
+            <v>0.5434007134363853</v>
           </cell>
           <cell r="AD31">
-            <v>-1013</v>
+            <v>-1152</v>
           </cell>
           <cell r="AE31">
-            <v>1192</v>
+            <v>1261.5</v>
           </cell>
           <cell r="AF31">
-            <v>2205</v>
+            <v>2413.5</v>
           </cell>
           <cell r="AG31">
             <v>85.6875</v>
@@ -7512,22 +7513,22 @@
             <v>3606.4</v>
           </cell>
           <cell r="AA32">
-            <v>1298</v>
+            <v>1391</v>
           </cell>
           <cell r="AB32">
-            <v>7.5500770416024645</v>
+            <v>7.0452911574406905</v>
           </cell>
           <cell r="AC32">
-            <v>0.75500770416024654</v>
+            <v>0.70452911574406907</v>
           </cell>
           <cell r="AD32">
-            <v>-318</v>
+            <v>-411</v>
           </cell>
           <cell r="AE32">
-            <v>649</v>
+            <v>695.5</v>
           </cell>
           <cell r="AF32">
-            <v>967</v>
+            <v>1106.5</v>
           </cell>
           <cell r="AG32">
             <v>61.25</v>
@@ -7604,22 +7605,22 @@
             <v>13703.300000000001</v>
           </cell>
           <cell r="AA33">
-            <v>5003</v>
+            <v>5336</v>
           </cell>
           <cell r="AB33">
-            <v>6.6000399760143909</v>
+            <v>6.1881559220389803</v>
           </cell>
           <cell r="AC33">
-            <v>0.66000399760143913</v>
+            <v>0.61881559220389803</v>
           </cell>
           <cell r="AD33">
-            <v>-1701</v>
+            <v>-2034</v>
           </cell>
           <cell r="AE33">
-            <v>2501.5</v>
+            <v>2668</v>
           </cell>
           <cell r="AF33">
-            <v>4202.5</v>
+            <v>4702</v>
           </cell>
           <cell r="AG33">
             <v>206.375</v>
@@ -7696,22 +7697,22 @@
             <v>26174.050000000003</v>
           </cell>
           <cell r="AA34">
-            <v>7763</v>
+            <v>8373</v>
           </cell>
           <cell r="AB34">
-            <v>8.1244364292155105</v>
+            <v>7.5325450853935276</v>
           </cell>
           <cell r="AC34">
-            <v>0.81244364292155091</v>
+            <v>0.75325450853935272</v>
           </cell>
           <cell r="AD34">
-            <v>-1456</v>
+            <v>-2066</v>
           </cell>
           <cell r="AE34">
-            <v>3881.5</v>
+            <v>4186.5</v>
           </cell>
           <cell r="AF34">
-            <v>5337.5</v>
+            <v>6252.5</v>
           </cell>
           <cell r="AG34">
             <v>394.1875</v>
@@ -7880,22 +7881,22 @@
             <v>2253.4500000000003</v>
           </cell>
           <cell r="AA36">
-            <v>1500</v>
+            <v>1682</v>
           </cell>
           <cell r="AB36">
-            <v>3.62</v>
+            <v>3.2282996432818076</v>
           </cell>
           <cell r="AC36">
-            <v>0.36199999999999999</v>
+            <v>0.32282996432818073</v>
           </cell>
           <cell r="AD36">
-            <v>-957</v>
+            <v>-1139</v>
           </cell>
           <cell r="AE36">
-            <v>750</v>
+            <v>841</v>
           </cell>
           <cell r="AF36">
-            <v>1707</v>
+            <v>1980</v>
           </cell>
           <cell r="AG36">
             <v>33.9375</v>
@@ -7972,22 +7973,22 @@
             <v>16573.84</v>
           </cell>
           <cell r="AA37">
-            <v>6782</v>
+            <v>7434</v>
           </cell>
           <cell r="AB37">
-            <v>14.992627543497493</v>
+            <v>13.677697067527577</v>
           </cell>
           <cell r="AC37">
-            <v>1.4992627543497494</v>
+            <v>1.3677697067527577</v>
           </cell>
           <cell r="AD37">
-            <v>3386</v>
+            <v>2734</v>
           </cell>
           <cell r="AE37">
-            <v>3391</v>
+            <v>3717</v>
           </cell>
           <cell r="AF37">
-            <v>5</v>
+            <v>983</v>
           </cell>
           <cell r="AG37">
             <v>188.2962962962963</v>
@@ -8064,22 +8065,22 @@
             <v>16068.539999999999</v>
           </cell>
           <cell r="AA38">
-            <v>11052</v>
+            <v>12107</v>
           </cell>
           <cell r="AB38">
-            <v>8.9196525515743748</v>
+            <v>8.1423969604361108</v>
           </cell>
           <cell r="AC38">
-            <v>0.89196525515743752</v>
+            <v>0.81423969604361113</v>
           </cell>
           <cell r="AD38">
-            <v>-1194</v>
+            <v>-2249</v>
           </cell>
           <cell r="AE38">
-            <v>5526</v>
+            <v>6053.5</v>
           </cell>
           <cell r="AF38">
-            <v>6720</v>
+            <v>8302.5</v>
           </cell>
           <cell r="AG38">
             <v>182.55555555555554</v>
@@ -8156,22 +8157,22 @@
             <v>3204.58</v>
           </cell>
           <cell r="AA39">
-            <v>4932</v>
+            <v>5311</v>
           </cell>
           <cell r="AB39">
-            <v>3.9862124898621252</v>
+            <v>3.7017510826586331</v>
           </cell>
           <cell r="AC39">
-            <v>0.39862124898621248</v>
+            <v>0.37017510826586331</v>
           </cell>
           <cell r="AD39">
-            <v>-2966</v>
+            <v>-3345</v>
           </cell>
           <cell r="AE39">
-            <v>2466</v>
+            <v>2655.5</v>
           </cell>
           <cell r="AF39">
-            <v>5432</v>
+            <v>6000.5</v>
           </cell>
           <cell r="AG39">
             <v>36.407407407407405</v>
@@ -8248,22 +8249,22 @@
             <v>7409.98</v>
           </cell>
           <cell r="AA40">
-            <v>3391</v>
+            <v>3730</v>
           </cell>
           <cell r="AB40">
-            <v>13.406074904158064</v>
+            <v>12.187667560321715</v>
           </cell>
           <cell r="AC40">
-            <v>1.3406074904158065</v>
+            <v>1.2187667560321715</v>
           </cell>
           <cell r="AD40">
-            <v>1155</v>
+            <v>816</v>
           </cell>
           <cell r="AE40">
-            <v>1695.5</v>
+            <v>1865</v>
           </cell>
           <cell r="AF40">
-            <v>540.5</v>
+            <v>1049</v>
           </cell>
           <cell r="AG40">
             <v>84.18518518518519</v>
@@ -8524,22 +8525,22 @@
             <v>4065.15</v>
           </cell>
           <cell r="AA43">
-            <v>1326</v>
+            <v>47</v>
           </cell>
           <cell r="AB43">
-            <v>4.9849170437405732</v>
+            <v>140.63829787234042</v>
           </cell>
           <cell r="AC43">
-            <v>0.49849170437405732</v>
+            <v>14.063829787234043</v>
           </cell>
           <cell r="AD43">
-            <v>-665</v>
+            <v>614</v>
           </cell>
           <cell r="AE43">
-            <v>663</v>
+            <v>23.5</v>
           </cell>
           <cell r="AF43">
-            <v>1328</v>
+            <v>-590.5</v>
           </cell>
           <cell r="AG43">
             <v>12.24074074074074</v>
@@ -8616,22 +8617,22 @@
             <v>6980.25</v>
           </cell>
           <cell r="AA44">
-            <v>1192</v>
+            <v>46</v>
           </cell>
           <cell r="AB44">
-            <v>9.5218120805369129</v>
+            <v>246.73913043478262</v>
           </cell>
           <cell r="AC44">
-            <v>0.95218120805369133</v>
+            <v>24.673913043478262</v>
           </cell>
           <cell r="AD44">
-            <v>-57</v>
+            <v>1089</v>
           </cell>
           <cell r="AE44">
-            <v>596</v>
+            <v>23</v>
           </cell>
           <cell r="AF44">
-            <v>653</v>
+            <v>-1066</v>
           </cell>
           <cell r="AG44">
             <v>21.018518518518519</v>
@@ -8708,22 +8709,22 @@
             <v>4816.32</v>
           </cell>
           <cell r="AA45">
-            <v>6145</v>
+            <v>1424</v>
           </cell>
           <cell r="AB45">
-            <v>6.7567127746135069</v>
+            <v>29.157303370786515</v>
           </cell>
           <cell r="AC45">
-            <v>0.67567127746135069</v>
+            <v>2.9157303370786516</v>
           </cell>
           <cell r="AD45">
-            <v>-1993</v>
+            <v>2728</v>
           </cell>
           <cell r="AE45">
-            <v>3072.5</v>
+            <v>712</v>
           </cell>
           <cell r="AF45">
-            <v>5065.5</v>
+            <v>-2016</v>
           </cell>
           <cell r="AG45">
             <v>76.888888888888886</v>
@@ -8800,22 +8801,22 @@
             <v>9920.32</v>
           </cell>
           <cell r="AA46">
-            <v>6715</v>
+            <v>1357</v>
           </cell>
           <cell r="AB46">
-            <v>12.735666418466121</v>
+            <v>63.021370670596909</v>
           </cell>
           <cell r="AC46">
-            <v>1.2735666418466121</v>
+            <v>6.3021370670596903</v>
           </cell>
           <cell r="AD46">
-            <v>1837</v>
+            <v>7195</v>
           </cell>
           <cell r="AE46">
-            <v>3357.5</v>
+            <v>678.5</v>
           </cell>
           <cell r="AF46">
-            <v>1520.5</v>
+            <v>-6516.5</v>
           </cell>
           <cell r="AG46">
             <v>158.37037037037038</v>
@@ -8892,22 +8893,22 @@
             <v>7810.28</v>
           </cell>
           <cell r="AA47">
-            <v>8316</v>
+            <v>6422</v>
           </cell>
           <cell r="AB47">
-            <v>8.0964405964405959</v>
+            <v>10.484272812208035</v>
           </cell>
           <cell r="AC47">
-            <v>0.80964405964405961</v>
+            <v>1.0484272812208035</v>
           </cell>
           <cell r="AD47">
-            <v>-1583</v>
+            <v>311</v>
           </cell>
           <cell r="AE47">
-            <v>4158</v>
+            <v>3211</v>
           </cell>
           <cell r="AF47">
-            <v>5741</v>
+            <v>2900</v>
           </cell>
           <cell r="AG47">
             <v>124.68518518518519</v>
@@ -8984,22 +8985,22 @@
             <v>6063.32</v>
           </cell>
           <cell r="AA48">
-            <v>5818</v>
+            <v>7168</v>
           </cell>
           <cell r="AB48">
-            <v>8.9841870058439337</v>
+            <v>7.2921316964285721</v>
           </cell>
           <cell r="AC48">
-            <v>0.89841870058439322</v>
+            <v>0.7292131696428571</v>
           </cell>
           <cell r="AD48">
-            <v>-591</v>
+            <v>-1941</v>
           </cell>
           <cell r="AE48">
-            <v>2909</v>
+            <v>3584</v>
           </cell>
           <cell r="AF48">
-            <v>3500</v>
+            <v>5525</v>
           </cell>
           <cell r="AG48">
             <v>96.796296296296291</v>
@@ -9076,22 +9077,22 @@
             <v>216</v>
           </cell>
           <cell r="AA49">
-            <v>24</v>
+            <v>476</v>
           </cell>
           <cell r="AB49">
-            <v>5</v>
+            <v>0.25210084033613445</v>
           </cell>
           <cell r="AC49">
-            <v>0.5</v>
+            <v>2.5210084033613446E-2</v>
           </cell>
           <cell r="AD49">
-            <v>-12</v>
+            <v>-464</v>
           </cell>
           <cell r="AE49">
-            <v>12</v>
+            <v>238</v>
           </cell>
           <cell r="AF49">
-            <v>24</v>
+            <v>702</v>
           </cell>
           <cell r="AG49">
             <v>6</v>
@@ -9168,7 +9169,7 @@
             <v>198</v>
           </cell>
           <cell r="AA50">
-            <v>0</v>
+            <v>612</v>
           </cell>
           <cell r="AB50">
             <v>0</v>
@@ -9177,13 +9178,13 @@
             <v>0</v>
           </cell>
           <cell r="AD50">
-            <v>11</v>
+            <v>-601</v>
           </cell>
           <cell r="AE50">
-            <v>0</v>
+            <v>306</v>
           </cell>
           <cell r="AF50">
-            <v>-11</v>
+            <v>907</v>
           </cell>
           <cell r="AG50">
             <v>5.5</v>
@@ -9260,22 +9261,22 @@
             <v>49.879999999999995</v>
           </cell>
           <cell r="AA51">
-            <v>175</v>
+            <v>8941</v>
           </cell>
           <cell r="AB51">
-            <v>2.4571428571428573</v>
+            <v>4.8093054468180289E-2</v>
           </cell>
           <cell r="AC51">
-            <v>0.24571428571428572</v>
+            <v>4.8093054468180295E-3</v>
           </cell>
           <cell r="AD51">
-            <v>-132</v>
+            <v>-8898</v>
           </cell>
           <cell r="AE51">
-            <v>87.5</v>
+            <v>4470.5</v>
           </cell>
           <cell r="AF51">
-            <v>219.5</v>
+            <v>13368.5</v>
           </cell>
           <cell r="AG51">
             <v>1.075</v>
@@ -9444,22 +9445,22 @@
             <v>4.6399999999999997</v>
           </cell>
           <cell r="AA53">
-            <v>709</v>
+            <v>191</v>
           </cell>
           <cell r="AB53">
-            <v>5.6417489421720729E-2</v>
+            <v>0.20942408376963348</v>
           </cell>
           <cell r="AC53">
-            <v>5.6417489421720732E-3</v>
+            <v>2.0942408376963352E-2</v>
           </cell>
           <cell r="AD53">
-            <v>-705</v>
+            <v>-187</v>
           </cell>
           <cell r="AE53">
-            <v>354.5</v>
+            <v>95.5</v>
           </cell>
           <cell r="AF53">
-            <v>1059.5</v>
+            <v>282.5</v>
           </cell>
           <cell r="AG53">
             <v>0.1</v>
@@ -9536,22 +9537,22 @@
             <v>18284.13</v>
           </cell>
           <cell r="AA54">
-            <v>3036</v>
+            <v>6086</v>
           </cell>
           <cell r="AB54">
-            <v>74.351119894598156</v>
+            <v>37.090042720999016</v>
           </cell>
           <cell r="AC54">
-            <v>7.4351119894598154</v>
+            <v>3.7090042720999015</v>
           </cell>
           <cell r="AD54">
-            <v>19537</v>
+            <v>16487</v>
           </cell>
           <cell r="AE54">
-            <v>1518</v>
+            <v>3043</v>
           </cell>
           <cell r="AF54">
-            <v>-18019</v>
+            <v>-13444</v>
           </cell>
           <cell r="AG54">
             <v>1881.0833333333333</v>
@@ -9628,22 +9629,22 @@
             <v>23675.49</v>
           </cell>
           <cell r="AA55">
-            <v>5285</v>
+            <v>712</v>
           </cell>
           <cell r="AB55">
-            <v>55.305581835383158</v>
+            <v>410.5196629213483</v>
           </cell>
           <cell r="AC55">
-            <v>5.5305581835383162</v>
+            <v>41.051966292134829</v>
           </cell>
           <cell r="AD55">
-            <v>23944</v>
+            <v>28517</v>
           </cell>
           <cell r="AE55">
-            <v>2642.5</v>
+            <v>356</v>
           </cell>
           <cell r="AF55">
-            <v>-21301.5</v>
+            <v>-28161</v>
           </cell>
           <cell r="AG55">
             <v>2435.75</v>
@@ -9720,22 +9721,22 @@
             <v>13081.5</v>
           </cell>
           <cell r="AA56">
-            <v>3223</v>
+            <v>3447</v>
           </cell>
           <cell r="AB56">
-            <v>50.108594477195155</v>
+            <v>46.852335364084716</v>
           </cell>
           <cell r="AC56">
-            <v>5.0108594477195156</v>
+            <v>4.6852335364084707</v>
           </cell>
           <cell r="AD56">
-            <v>12927</v>
+            <v>12703</v>
           </cell>
           <cell r="AE56">
-            <v>1611.5</v>
+            <v>1723.5</v>
           </cell>
           <cell r="AF56">
-            <v>-11315.5</v>
+            <v>-10979.5</v>
           </cell>
           <cell r="AG56">
             <v>1345.8333333333333</v>
@@ -9812,22 +9813,22 @@
             <v>15625.710000000001</v>
           </cell>
           <cell r="AA57">
-            <v>2734</v>
+            <v>5851</v>
           </cell>
           <cell r="AB57">
-            <v>70.559619604974401</v>
+            <v>32.970432404717144</v>
           </cell>
           <cell r="AC57">
-            <v>7.0559619604974397</v>
+            <v>3.297043240471714</v>
           </cell>
           <cell r="AD57">
-            <v>16557</v>
+            <v>13440</v>
           </cell>
           <cell r="AE57">
-            <v>1367</v>
+            <v>2925.5</v>
           </cell>
           <cell r="AF57">
-            <v>-15190</v>
+            <v>-10514.5</v>
           </cell>
           <cell r="AG57">
             <v>1607.5833333333333</v>
@@ -9904,22 +9905,22 @@
             <v>1873.3000000000002</v>
           </cell>
           <cell r="AA58">
-            <v>446</v>
+            <v>3575</v>
           </cell>
           <cell r="AB58">
-            <v>16.031390134529147</v>
+            <v>2</v>
           </cell>
           <cell r="AC58">
-            <v>1.6031390134529149</v>
+            <v>0.2</v>
           </cell>
           <cell r="AD58">
-            <v>269</v>
+            <v>-2860</v>
           </cell>
           <cell r="AE58">
-            <v>223</v>
+            <v>1787.5</v>
           </cell>
           <cell r="AF58">
-            <v>-46</v>
+            <v>4647.5</v>
           </cell>
           <cell r="AG58">
             <v>119.16666666666667</v>
@@ -9996,22 +9997,22 @@
             <v>1011.32</v>
           </cell>
           <cell r="AA59">
-            <v>933</v>
+            <v>3107</v>
           </cell>
           <cell r="AB59">
-            <v>4.137191854233655</v>
+            <v>1.2423559703894433</v>
           </cell>
           <cell r="AC59">
-            <v>0.4137191854233655</v>
+            <v>0.12423559703894432</v>
           </cell>
           <cell r="AD59">
-            <v>-547</v>
+            <v>-2721</v>
           </cell>
           <cell r="AE59">
-            <v>466.5</v>
+            <v>1553.5</v>
           </cell>
           <cell r="AF59">
-            <v>1013.5</v>
+            <v>4274.5</v>
           </cell>
           <cell r="AG59">
             <v>64.333333333333329</v>
@@ -10088,22 +10089,22 @@
             <v>780.76</v>
           </cell>
           <cell r="AA60">
-            <v>546</v>
+            <v>506</v>
           </cell>
           <cell r="AB60">
-            <v>5.457875457875458</v>
+            <v>5.8893280632411065</v>
           </cell>
           <cell r="AC60">
-            <v>0.54578754578754574</v>
+            <v>0.58893280632411071</v>
           </cell>
           <cell r="AD60">
-            <v>-248</v>
+            <v>-208</v>
           </cell>
           <cell r="AE60">
-            <v>273</v>
+            <v>253</v>
           </cell>
           <cell r="AF60">
-            <v>521</v>
+            <v>461</v>
           </cell>
           <cell r="AG60">
             <v>49.666666666666664</v>
@@ -10180,22 +10181,22 @@
             <v>382.52000000000004</v>
           </cell>
           <cell r="AA61">
-            <v>467</v>
+            <v>1021</v>
           </cell>
           <cell r="AB61">
-            <v>3.1263383297644536</v>
+            <v>1.4299706170421156</v>
           </cell>
           <cell r="AC61">
-            <v>0.31263383297644537</v>
+            <v>0.14299706170421156</v>
           </cell>
           <cell r="AD61">
-            <v>-321</v>
+            <v>-875</v>
           </cell>
           <cell r="AE61">
-            <v>233.5</v>
+            <v>510.5</v>
           </cell>
           <cell r="AF61">
-            <v>554.5</v>
+            <v>1385.5</v>
           </cell>
           <cell r="AG61">
             <v>24.333333333333332</v>
@@ -10206,13 +10207,14 @@
             <v>Units Produce</v>
           </cell>
           <cell r="AF62">
-            <v>139758.5</v>
+            <v>180594</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10537,212 +10539,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="63" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="63"/>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="63"/>
+      <c r="AB1" s="66"/>
+      <c r="AC1" s="66"/>
+      <c r="AD1" s="66"/>
+      <c r="AE1" s="66"/>
+      <c r="AF1" s="66"/>
+      <c r="AG1" s="66"/>
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
-      <c r="AA2" s="63"/>
-      <c r="AB2" s="63"/>
-      <c r="AC2" s="63"/>
-      <c r="AD2" s="63"/>
-      <c r="AE2" s="63"/>
-      <c r="AF2" s="63"/>
-      <c r="AG2" s="63"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="66"/>
+      <c r="AC2" s="66"/>
+      <c r="AD2" s="66"/>
+      <c r="AE2" s="66"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="62"/>
-      <c r="U3" s="62"/>
-      <c r="V3" s="62"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="62"/>
-      <c r="AA3" s="63"/>
-      <c r="AB3" s="63"/>
-      <c r="AC3" s="63"/>
-      <c r="AD3" s="63"/>
-      <c r="AE3" s="63"/>
-      <c r="AF3" s="63"/>
-      <c r="AG3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="66"/>
+      <c r="AB3" s="66"/>
+      <c r="AC3" s="66"/>
+      <c r="AD3" s="66"/>
+      <c r="AE3" s="66"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="62"/>
-      <c r="W4" s="62"/>
-      <c r="X4" s="62"/>
-      <c r="Y4" s="62"/>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="63"/>
-      <c r="AB4" s="63"/>
-      <c r="AC4" s="63"/>
-      <c r="AD4" s="63"/>
-      <c r="AE4" s="63"/>
-      <c r="AF4" s="63"/>
-      <c r="AG4" s="63"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="62"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="62"/>
-      <c r="Y5" s="62"/>
-      <c r="Z5" s="62"/>
-      <c r="AA5" s="63"/>
-      <c r="AB5" s="63"/>
-      <c r="AC5" s="63"/>
-      <c r="AD5" s="63"/>
-      <c r="AE5" s="63"/>
-      <c r="AF5" s="63"/>
-      <c r="AG5" s="63"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="66"/>
+      <c r="AB5" s="66"/>
+      <c r="AC5" s="66"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="63"/>
-      <c r="AB6" s="63"/>
-      <c r="AC6" s="63"/>
-      <c r="AD6" s="63"/>
-      <c r="AE6" s="63"/>
-      <c r="AF6" s="63"/>
-      <c r="AG6" s="63"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="66"/>
+      <c r="AB6" s="66"/>
+      <c r="AC6" s="66"/>
+      <c r="AD6" s="66"/>
+      <c r="AE6" s="66"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
@@ -11113,27 +11115,27 @@
       </c>
       <c r="AA13" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA13</f>
-        <v>11756</v>
+        <v>12944</v>
       </c>
       <c r="AB13" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB13</f>
-        <v>8.5105478053759782</v>
+        <v>7.7294499381953026</v>
       </c>
       <c r="AC13" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC13</f>
-        <v>0.85105478053759787</v>
+        <v>0.7729449938195303</v>
       </c>
       <c r="AD13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD13</f>
-        <v>-1751</v>
+        <v>-2939</v>
       </c>
       <c r="AE13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE13</f>
-        <v>5878</v>
+        <v>6472</v>
       </c>
       <c r="AF13" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF13</f>
-        <v>7629</v>
+        <v>9411</v>
       </c>
       <c r="AG13" s="27">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG13</f>
@@ -11241,27 +11243,27 @@
       </c>
       <c r="AA14" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA14</f>
-        <v>823</v>
+        <v>903</v>
       </c>
       <c r="AB14" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB14</f>
-        <v>6.7922235722964768</v>
+        <v>6.1904761904761907</v>
       </c>
       <c r="AC14" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC14</f>
-        <v>0.67922235722964763</v>
+        <v>0.61904761904761907</v>
       </c>
       <c r="AD14" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD14</f>
-        <v>-264</v>
+        <v>-344</v>
       </c>
       <c r="AE14" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE14</f>
-        <v>411.5</v>
+        <v>451.5</v>
       </c>
       <c r="AF14" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF14</f>
-        <v>675.5</v>
+        <v>795.5</v>
       </c>
       <c r="AG14" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG14</f>
@@ -11369,27 +11371,27 @@
       </c>
       <c r="AA15" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA15</f>
-        <v>4634</v>
+        <v>5279</v>
       </c>
       <c r="AB15" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB15</f>
-        <v>7.4061286145878293</v>
+        <v>6.5012312938056454</v>
       </c>
       <c r="AC15" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC15</f>
-        <v>0.74061286145878291</v>
+        <v>0.65012312938056449</v>
       </c>
       <c r="AD15" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD15</f>
-        <v>-1202</v>
+        <v>-1847</v>
       </c>
       <c r="AE15" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE15</f>
-        <v>2317</v>
+        <v>2639.5</v>
       </c>
       <c r="AF15" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF15</f>
-        <v>3519</v>
+        <v>4486.5</v>
       </c>
       <c r="AG15" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG15</f>
@@ -11497,27 +11499,27 @@
       </c>
       <c r="AA16" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA16</f>
-        <v>1004</v>
+        <v>1061</v>
       </c>
       <c r="AB16" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB16</f>
-        <v>2.0517928286852589</v>
+        <v>1.9415645617342132</v>
       </c>
       <c r="AC16" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC16</f>
-        <v>0.20517928286852591</v>
+        <v>0.19415645617342131</v>
       </c>
       <c r="AD16" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD16</f>
-        <v>-798</v>
+        <v>-855</v>
       </c>
       <c r="AE16" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE16</f>
-        <v>502</v>
+        <v>530.5</v>
       </c>
       <c r="AF16" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF16</f>
-        <v>1300</v>
+        <v>1385.5</v>
       </c>
       <c r="AG16" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG16</f>
@@ -11625,27 +11627,27 @@
       </c>
       <c r="AA17" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA17</f>
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AB17" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB17</f>
-        <v>23.555555555555557</v>
+        <v>20.19047619047619</v>
       </c>
       <c r="AC17" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC17</f>
-        <v>2.3555555555555556</v>
+        <v>2.019047619047619</v>
       </c>
       <c r="AD17" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD17</f>
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="AE17" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE17</f>
-        <v>45</v>
+        <v>52.5</v>
       </c>
       <c r="AF17" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF17</f>
-        <v>-77</v>
+        <v>-54.5</v>
       </c>
       <c r="AG17" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG17</f>
@@ -11753,27 +11755,27 @@
       </c>
       <c r="AA18" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA18</f>
-        <v>14437</v>
+        <v>15948</v>
       </c>
       <c r="AB18" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB18</f>
-        <v>5.8024520329708382</v>
+        <v>5.2526962628542764</v>
       </c>
       <c r="AC18" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC18</f>
-        <v>0.58024520329708384</v>
+        <v>0.52526962628542762</v>
       </c>
       <c r="AD18" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD18</f>
-        <v>-6060</v>
+        <v>-7571</v>
       </c>
       <c r="AE18" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE18</f>
-        <v>7218.5</v>
+        <v>7974</v>
       </c>
       <c r="AF18" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF18</f>
-        <v>13278.5</v>
+        <v>15545</v>
       </c>
       <c r="AG18" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG18</f>
@@ -11881,27 +11883,27 @@
       </c>
       <c r="AA19" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA19</f>
-        <v>1441</v>
+        <v>1537</v>
       </c>
       <c r="AB19" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB19</f>
-        <v>10.458015267175574</v>
+        <v>9.8048145738451531</v>
       </c>
       <c r="AC19" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC19</f>
-        <v>1.0458015267175573</v>
+        <v>0.98048145738451531</v>
       </c>
       <c r="AD19" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD19</f>
-        <v>66</v>
+        <v>-30</v>
       </c>
       <c r="AE19" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE19</f>
-        <v>720.5</v>
+        <v>768.5</v>
       </c>
       <c r="AF19" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF19</f>
-        <v>654.5</v>
+        <v>798.5</v>
       </c>
       <c r="AG19" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG19</f>
@@ -12009,27 +12011,27 @@
       </c>
       <c r="AA20" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA20</f>
-        <v>3157</v>
+        <v>3403</v>
       </c>
       <c r="AB20" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB20</f>
-        <v>12.562559391827685</v>
+        <v>11.654422568322069</v>
       </c>
       <c r="AC20" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC20</f>
-        <v>1.2562559391827683</v>
+        <v>1.1654422568322069</v>
       </c>
       <c r="AD20" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD20</f>
-        <v>809</v>
+        <v>563</v>
       </c>
       <c r="AE20" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE20</f>
-        <v>1578.5</v>
+        <v>1701.5</v>
       </c>
       <c r="AF20" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF20</f>
-        <v>769.5</v>
+        <v>1138.5</v>
       </c>
       <c r="AG20" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG20</f>
@@ -12137,27 +12139,27 @@
       </c>
       <c r="AA21" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA21</f>
-        <v>7180</v>
+        <v>7625</v>
       </c>
       <c r="AB21" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB21</f>
-        <v>10.637883008356546</v>
+        <v>10.017049180327868</v>
       </c>
       <c r="AC21" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC21</f>
-        <v>1.0637883008356546</v>
+        <v>1.0017049180327868</v>
       </c>
       <c r="AD21" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD21</f>
-        <v>458</v>
+        <v>13</v>
       </c>
       <c r="AE21" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE21</f>
-        <v>3590</v>
+        <v>3812.5</v>
       </c>
       <c r="AF21" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF21</f>
-        <v>3132</v>
+        <v>3799.5</v>
       </c>
       <c r="AG21" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG21</f>
@@ -12265,27 +12267,27 @@
       </c>
       <c r="AA22" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA22</f>
-        <v>3422</v>
+        <v>3542</v>
       </c>
       <c r="AB22" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB22</f>
-        <v>10.990648743424899</v>
+        <v>10.618294748729532</v>
       </c>
       <c r="AC22" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC22</f>
-        <v>1.0990648743424898</v>
+        <v>1.0618294748729531</v>
       </c>
       <c r="AD22" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD22</f>
-        <v>339</v>
+        <v>219</v>
       </c>
       <c r="AE22" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE22</f>
-        <v>1711</v>
+        <v>1771</v>
       </c>
       <c r="AF22" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF22</f>
-        <v>1372</v>
+        <v>1552</v>
       </c>
       <c r="AG22" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG22</f>
@@ -12393,27 +12395,27 @@
       </c>
       <c r="AA23" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA23</f>
-        <v>36510</v>
+        <v>39911</v>
       </c>
       <c r="AB23" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB23</f>
-        <v>9.0843604491920029</v>
+        <v>8.3102402846333092</v>
       </c>
       <c r="AC23" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC23</f>
-        <v>0.90843604491920027</v>
+        <v>0.8310240284633309</v>
       </c>
       <c r="AD23" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD23</f>
-        <v>-3343</v>
+        <v>-6744</v>
       </c>
       <c r="AE23" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE23</f>
-        <v>18255</v>
+        <v>19955.5</v>
       </c>
       <c r="AF23" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF23</f>
-        <v>21598</v>
+        <v>26699.5</v>
       </c>
       <c r="AG23" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG23</f>
@@ -12521,27 +12523,27 @@
       </c>
       <c r="AA24" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA24</f>
-        <v>24080</v>
+        <v>26342</v>
       </c>
       <c r="AB24" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB24</f>
-        <v>10.4015780730897</v>
+        <v>9.5083896439146613</v>
       </c>
       <c r="AC24" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC24</f>
-        <v>1.0401578073089701</v>
+        <v>0.95083896439146609</v>
       </c>
       <c r="AD24" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD24</f>
-        <v>967</v>
+        <v>-1295</v>
       </c>
       <c r="AE24" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE24</f>
-        <v>12040</v>
+        <v>13171</v>
       </c>
       <c r="AF24" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF24</f>
-        <v>11073</v>
+        <v>14466</v>
       </c>
       <c r="AG24" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG24</f>
@@ -12649,27 +12651,27 @@
       </c>
       <c r="AA25" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA25</f>
-        <v>23292</v>
+        <v>25420</v>
       </c>
       <c r="AB25" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB25</f>
-        <v>11.118409754422119</v>
+        <v>10.187647521636507</v>
       </c>
       <c r="AC25" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC25</f>
-        <v>1.1118409754422118</v>
+        <v>1.0187647521636507</v>
       </c>
       <c r="AD25" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD25</f>
-        <v>2605</v>
+        <v>477</v>
       </c>
       <c r="AE25" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE25</f>
-        <v>11646</v>
+        <v>12710</v>
       </c>
       <c r="AF25" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF25</f>
-        <v>9041</v>
+        <v>12233</v>
       </c>
       <c r="AG25" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG25</f>
@@ -12777,27 +12779,27 @@
       </c>
       <c r="AA26" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA26</f>
-        <v>27946</v>
+        <v>30373</v>
       </c>
       <c r="AB26" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB26</f>
-        <v>10.602232877692693</v>
+        <v>9.7550455997102681</v>
       </c>
       <c r="AC26" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC26</f>
-        <v>1.0602232877692692</v>
+        <v>0.97550455997102692</v>
       </c>
       <c r="AD26" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD26</f>
-        <v>1683</v>
+        <v>-744</v>
       </c>
       <c r="AE26" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE26</f>
-        <v>13973</v>
+        <v>15186.5</v>
       </c>
       <c r="AF26" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF26</f>
-        <v>12290</v>
+        <v>15930.5</v>
       </c>
       <c r="AG26" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG26</f>
@@ -12905,27 +12907,27 @@
       </c>
       <c r="AA27" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA27</f>
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="AB27" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB27</f>
-        <v>42.70422535211268</v>
+        <v>41.534246575342465</v>
       </c>
       <c r="AC27" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC27</f>
-        <v>4.2704225352112672</v>
+        <v>4.1534246575342468</v>
       </c>
       <c r="AD27" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD27</f>
-        <v>1161</v>
+        <v>1151</v>
       </c>
       <c r="AE27" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE27</f>
-        <v>177.5</v>
+        <v>182.5</v>
       </c>
       <c r="AF27" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF27</f>
-        <v>-983.5</v>
+        <v>-968.5</v>
       </c>
       <c r="AG27" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG27</f>
@@ -12973,15 +12975,15 @@
       </c>
       <c r="L28" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L28</f>
-        <v>28.541862652869238</v>
+        <v>17.847058823529412</v>
       </c>
       <c r="M28" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M28</f>
-        <v>2338.6</v>
+        <v>3740</v>
       </c>
       <c r="N28" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N28</f>
-        <v>1439.5</v>
+        <v>484</v>
       </c>
       <c r="O28" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O28</f>
@@ -13033,27 +13035,27 @@
       </c>
       <c r="AA28" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA28</f>
-        <v>1063</v>
+        <v>1700</v>
       </c>
       <c r="AB28" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB28</f>
-        <v>45.277516462841014</v>
+        <v>28.311764705882354</v>
       </c>
       <c r="AC28" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC28</f>
-        <v>4.5277516462841012</v>
+        <v>2.8311764705882352</v>
       </c>
       <c r="AD28" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD28</f>
-        <v>3750</v>
+        <v>3113</v>
       </c>
       <c r="AE28" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE28</f>
-        <v>531.5</v>
+        <v>850</v>
       </c>
       <c r="AF28" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF28</f>
-        <v>-3218.5</v>
+        <v>-2263</v>
       </c>
       <c r="AG28" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG28</f>
@@ -13101,15 +13103,15 @@
       </c>
       <c r="L29" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L29</f>
-        <v>19.785020804438282</v>
+        <v>13.245125348189415</v>
       </c>
       <c r="M29" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M29</f>
-        <v>3172.3999999999996</v>
+        <v>4738.8</v>
       </c>
       <c r="N29" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N29</f>
-        <v>690</v>
+        <v>-378</v>
       </c>
       <c r="O29" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O29</f>
@@ -13161,27 +13163,27 @@
       </c>
       <c r="AA29" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA29</f>
-        <v>1442</v>
+        <v>2154</v>
       </c>
       <c r="AB29" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB29</f>
-        <v>31.574202496532596</v>
+        <v>21.137418755803157</v>
       </c>
       <c r="AC29" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC29</f>
-        <v>3.1574202496532595</v>
+        <v>2.1137418755803159</v>
       </c>
       <c r="AD29" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD29</f>
-        <v>3111</v>
+        <v>2399</v>
       </c>
       <c r="AE29" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE29</f>
-        <v>721</v>
+        <v>1077</v>
       </c>
       <c r="AF29" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF29</f>
-        <v>-2390</v>
+        <v>-1322</v>
       </c>
       <c r="AG29" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG29</f>
@@ -13229,15 +13231,15 @@
       </c>
       <c r="L30" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L30</f>
-        <v>21.434019832189168</v>
+        <v>13.876543209876543</v>
       </c>
       <c r="M30" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M30</f>
-        <v>2884.2</v>
+        <v>4455</v>
       </c>
       <c r="N30" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N30</f>
-        <v>843.5</v>
+        <v>-227.5</v>
       </c>
       <c r="O30" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O30</f>
@@ -13289,27 +13291,27 @@
       </c>
       <c r="AA30" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA30</f>
-        <v>1311</v>
+        <v>2025</v>
       </c>
       <c r="AB30" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB30</f>
-        <v>45.980167810831425</v>
+        <v>29.767901234567901</v>
       </c>
       <c r="AC30" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC30</f>
-        <v>4.5980167810831425</v>
+        <v>2.9767901234567899</v>
       </c>
       <c r="AD30" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD30</f>
-        <v>4717</v>
+        <v>4003</v>
       </c>
       <c r="AE30" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE30</f>
-        <v>655.5</v>
+        <v>1012.5</v>
       </c>
       <c r="AF30" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF30</f>
-        <v>-4061.5</v>
+        <v>-2990.5</v>
       </c>
       <c r="AG30" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG30</f>
@@ -13417,27 +13419,27 @@
       </c>
       <c r="AA31" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA31</f>
-        <v>2384</v>
+        <v>2523</v>
       </c>
       <c r="AB31" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB31</f>
-        <v>5.7508389261744961</v>
+        <v>5.4340071343638527</v>
       </c>
       <c r="AC31" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC31</f>
-        <v>0.57508389261744963</v>
+        <v>0.5434007134363853</v>
       </c>
       <c r="AD31" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD31</f>
-        <v>-1013</v>
+        <v>-1152</v>
       </c>
       <c r="AE31" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE31</f>
-        <v>1192</v>
+        <v>1261.5</v>
       </c>
       <c r="AF31" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF31</f>
-        <v>2205</v>
+        <v>2413.5</v>
       </c>
       <c r="AG31" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG31</f>
@@ -13545,27 +13547,27 @@
       </c>
       <c r="AA32" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA32</f>
-        <v>1298</v>
+        <v>1391</v>
       </c>
       <c r="AB32" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB32</f>
-        <v>7.5500770416024645</v>
+        <v>7.0452911574406905</v>
       </c>
       <c r="AC32" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC32</f>
-        <v>0.75500770416024654</v>
+        <v>0.70452911574406907</v>
       </c>
       <c r="AD32" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD32</f>
-        <v>-318</v>
+        <v>-411</v>
       </c>
       <c r="AE32" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE32</f>
-        <v>649</v>
+        <v>695.5</v>
       </c>
       <c r="AF32" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF32</f>
-        <v>967</v>
+        <v>1106.5</v>
       </c>
       <c r="AG32" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG32</f>
@@ -13673,27 +13675,27 @@
       </c>
       <c r="AA33" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA33</f>
-        <v>5003</v>
+        <v>5336</v>
       </c>
       <c r="AB33" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB33</f>
-        <v>6.6000399760143909</v>
+        <v>6.1881559220389803</v>
       </c>
       <c r="AC33" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC33</f>
-        <v>0.66000399760143913</v>
+        <v>0.61881559220389803</v>
       </c>
       <c r="AD33" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD33</f>
-        <v>-1701</v>
+        <v>-2034</v>
       </c>
       <c r="AE33" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE33</f>
-        <v>2501.5</v>
+        <v>2668</v>
       </c>
       <c r="AF33" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF33</f>
-        <v>4202.5</v>
+        <v>4702</v>
       </c>
       <c r="AG33" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG33</f>
@@ -13801,27 +13803,27 @@
       </c>
       <c r="AA34" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA34</f>
-        <v>7763</v>
+        <v>8373</v>
       </c>
       <c r="AB34" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB34</f>
-        <v>8.1244364292155105</v>
+        <v>7.5325450853935276</v>
       </c>
       <c r="AC34" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC34</f>
-        <v>0.81244364292155091</v>
+        <v>0.75325450853935272</v>
       </c>
       <c r="AD34" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD34</f>
-        <v>-1456</v>
+        <v>-2066</v>
       </c>
       <c r="AE34" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE34</f>
-        <v>3881.5</v>
+        <v>4186.5</v>
       </c>
       <c r="AF34" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF34</f>
-        <v>5337.5</v>
+        <v>6252.5</v>
       </c>
       <c r="AG34" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG34</f>
@@ -14057,27 +14059,27 @@
       </c>
       <c r="AA36" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA36</f>
-        <v>1500</v>
+        <v>1682</v>
       </c>
       <c r="AB36" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB36</f>
-        <v>3.62</v>
+        <v>3.2282996432818076</v>
       </c>
       <c r="AC36" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC36</f>
-        <v>0.36199999999999999</v>
+        <v>0.32282996432818073</v>
       </c>
       <c r="AD36" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD36</f>
-        <v>-957</v>
+        <v>-1139</v>
       </c>
       <c r="AE36" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE36</f>
-        <v>750</v>
+        <v>841</v>
       </c>
       <c r="AF36" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF36</f>
-        <v>1707</v>
+        <v>1980</v>
       </c>
       <c r="AG36" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG36</f>
@@ -14185,27 +14187,27 @@
       </c>
       <c r="AA37" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA37</f>
-        <v>6782</v>
+        <v>7434</v>
       </c>
       <c r="AB37" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB37</f>
-        <v>14.992627543497493</v>
+        <v>13.677697067527577</v>
       </c>
       <c r="AC37" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC37</f>
-        <v>1.4992627543497494</v>
+        <v>1.3677697067527577</v>
       </c>
       <c r="AD37" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD37</f>
-        <v>3386</v>
+        <v>2734</v>
       </c>
       <c r="AE37" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE37</f>
-        <v>3391</v>
+        <v>3717</v>
       </c>
       <c r="AF37" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF37</f>
-        <v>5</v>
+        <v>983</v>
       </c>
       <c r="AG37" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG37</f>
@@ -14313,27 +14315,27 @@
       </c>
       <c r="AA38" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA38</f>
-        <v>11052</v>
+        <v>12107</v>
       </c>
       <c r="AB38" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB38</f>
-        <v>8.9196525515743748</v>
+        <v>8.1423969604361108</v>
       </c>
       <c r="AC38" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC38</f>
-        <v>0.89196525515743752</v>
+        <v>0.81423969604361113</v>
       </c>
       <c r="AD38" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD38</f>
-        <v>-1194</v>
+        <v>-2249</v>
       </c>
       <c r="AE38" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE38</f>
-        <v>5526</v>
+        <v>6053.5</v>
       </c>
       <c r="AF38" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF38</f>
-        <v>6720</v>
+        <v>8302.5</v>
       </c>
       <c r="AG38" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG38</f>
@@ -14441,27 +14443,27 @@
       </c>
       <c r="AA39" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA39</f>
-        <v>4932</v>
+        <v>5311</v>
       </c>
       <c r="AB39" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB39</f>
-        <v>3.9862124898621252</v>
+        <v>3.7017510826586331</v>
       </c>
       <c r="AC39" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC39</f>
-        <v>0.39862124898621248</v>
+        <v>0.37017510826586331</v>
       </c>
       <c r="AD39" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD39</f>
-        <v>-2966</v>
+        <v>-3345</v>
       </c>
       <c r="AE39" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE39</f>
-        <v>2466</v>
+        <v>2655.5</v>
       </c>
       <c r="AF39" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF39</f>
-        <v>5432</v>
+        <v>6000.5</v>
       </c>
       <c r="AG39" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG39</f>
@@ -14569,27 +14571,27 @@
       </c>
       <c r="AA40" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA40</f>
-        <v>3391</v>
+        <v>3730</v>
       </c>
       <c r="AB40" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB40</f>
-        <v>13.406074904158064</v>
+        <v>12.187667560321715</v>
       </c>
       <c r="AC40" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC40</f>
-        <v>1.3406074904158065</v>
+        <v>1.2187667560321715</v>
       </c>
       <c r="AD40" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD40</f>
-        <v>1155</v>
+        <v>816</v>
       </c>
       <c r="AE40" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE40</f>
-        <v>1695.5</v>
+        <v>1865</v>
       </c>
       <c r="AF40" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF40</f>
-        <v>540.5</v>
+        <v>1049</v>
       </c>
       <c r="AG40" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG40</f>
@@ -14953,27 +14955,27 @@
       </c>
       <c r="AA43" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA43</f>
-        <v>1326</v>
+        <v>47</v>
       </c>
       <c r="AB43" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB43</f>
-        <v>4.9849170437405732</v>
+        <v>140.63829787234042</v>
       </c>
       <c r="AC43" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC43</f>
-        <v>0.49849170437405732</v>
+        <v>14.063829787234043</v>
       </c>
       <c r="AD43" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD43</f>
-        <v>-665</v>
+        <v>614</v>
       </c>
       <c r="AE43" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE43</f>
-        <v>663</v>
+        <v>23.5</v>
       </c>
       <c r="AF43" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF43</f>
-        <v>1328</v>
+        <v>-590.5</v>
       </c>
       <c r="AG43" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG43</f>
@@ -15081,27 +15083,27 @@
       </c>
       <c r="AA44" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA44</f>
-        <v>1192</v>
+        <v>46</v>
       </c>
       <c r="AB44" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB44</f>
-        <v>9.5218120805369129</v>
+        <v>246.73913043478262</v>
       </c>
       <c r="AC44" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC44</f>
-        <v>0.95218120805369133</v>
+        <v>24.673913043478262</v>
       </c>
       <c r="AD44" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD44</f>
-        <v>-57</v>
+        <v>1089</v>
       </c>
       <c r="AE44" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE44</f>
-        <v>596</v>
+        <v>23</v>
       </c>
       <c r="AF44" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF44</f>
-        <v>653</v>
+        <v>-1066</v>
       </c>
       <c r="AG44" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG44</f>
@@ -15209,27 +15211,27 @@
       </c>
       <c r="AA45" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA45</f>
-        <v>6145</v>
+        <v>1424</v>
       </c>
       <c r="AB45" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB45</f>
-        <v>6.7567127746135069</v>
+        <v>29.157303370786515</v>
       </c>
       <c r="AC45" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC45</f>
-        <v>0.67567127746135069</v>
+        <v>2.9157303370786516</v>
       </c>
       <c r="AD45" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD45</f>
-        <v>-1993</v>
+        <v>2728</v>
       </c>
       <c r="AE45" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE45</f>
-        <v>3072.5</v>
+        <v>712</v>
       </c>
       <c r="AF45" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF45</f>
-        <v>5065.5</v>
+        <v>-2016</v>
       </c>
       <c r="AG45" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG45</f>
@@ -15337,27 +15339,27 @@
       </c>
       <c r="AA46" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA46</f>
-        <v>6715</v>
+        <v>1357</v>
       </c>
       <c r="AB46" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB46</f>
-        <v>12.735666418466121</v>
+        <v>63.021370670596909</v>
       </c>
       <c r="AC46" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC46</f>
-        <v>1.2735666418466121</v>
+        <v>6.3021370670596903</v>
       </c>
       <c r="AD46" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD46</f>
-        <v>1837</v>
+        <v>7195</v>
       </c>
       <c r="AE46" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE46</f>
-        <v>3357.5</v>
+        <v>678.5</v>
       </c>
       <c r="AF46" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF46</f>
-        <v>1520.5</v>
+        <v>-6516.5</v>
       </c>
       <c r="AG46" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG46</f>
@@ -15465,27 +15467,27 @@
       </c>
       <c r="AA47" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA47</f>
-        <v>8316</v>
+        <v>6422</v>
       </c>
       <c r="AB47" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB47</f>
-        <v>8.0964405964405959</v>
+        <v>10.484272812208035</v>
       </c>
       <c r="AC47" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC47</f>
-        <v>0.80964405964405961</v>
+        <v>1.0484272812208035</v>
       </c>
       <c r="AD47" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD47</f>
-        <v>-1583</v>
+        <v>311</v>
       </c>
       <c r="AE47" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE47</f>
-        <v>4158</v>
+        <v>3211</v>
       </c>
       <c r="AF47" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF47</f>
-        <v>5741</v>
+        <v>2900</v>
       </c>
       <c r="AG47" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG47</f>
@@ -15593,27 +15595,27 @@
       </c>
       <c r="AA48" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA48</f>
-        <v>5818</v>
+        <v>7168</v>
       </c>
       <c r="AB48" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB48</f>
-        <v>8.9841870058439337</v>
+        <v>7.2921316964285721</v>
       </c>
       <c r="AC48" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC48</f>
-        <v>0.89841870058439322</v>
+        <v>0.7292131696428571</v>
       </c>
       <c r="AD48" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD48</f>
-        <v>-591</v>
+        <v>-1941</v>
       </c>
       <c r="AE48" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE48</f>
-        <v>2909</v>
+        <v>3584</v>
       </c>
       <c r="AF48" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF48</f>
-        <v>3500</v>
+        <v>5525</v>
       </c>
       <c r="AG48" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG48</f>
@@ -15721,27 +15723,27 @@
       </c>
       <c r="AA49" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA49</f>
-        <v>24</v>
+        <v>476</v>
       </c>
       <c r="AB49" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB49</f>
-        <v>5</v>
+        <v>0.25210084033613445</v>
       </c>
       <c r="AC49" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC49</f>
-        <v>0.5</v>
+        <v>2.5210084033613446E-2</v>
       </c>
       <c r="AD49" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD49</f>
-        <v>-12</v>
+        <v>-464</v>
       </c>
       <c r="AE49" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE49</f>
-        <v>12</v>
+        <v>238</v>
       </c>
       <c r="AF49" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF49</f>
-        <v>24</v>
+        <v>702</v>
       </c>
       <c r="AG49" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG49</f>
@@ -15849,7 +15851,7 @@
       </c>
       <c r="AA50" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA50</f>
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="AB50" s="25">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB50</f>
@@ -15861,15 +15863,15 @@
       </c>
       <c r="AD50" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD50</f>
-        <v>11</v>
+        <v>-601</v>
       </c>
       <c r="AE50" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE50</f>
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="AF50" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF50</f>
-        <v>-11</v>
+        <v>907</v>
       </c>
       <c r="AG50" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG50</f>
@@ -15977,27 +15979,27 @@
       </c>
       <c r="AA51" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA51</f>
-        <v>175</v>
+        <v>8941</v>
       </c>
       <c r="AB51" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB51</f>
-        <v>2.4571428571428573</v>
+        <v>4.8093054468180289E-2</v>
       </c>
       <c r="AC51" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC51</f>
-        <v>0.24571428571428572</v>
+        <v>4.8093054468180295E-3</v>
       </c>
       <c r="AD51" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD51</f>
-        <v>-132</v>
+        <v>-8898</v>
       </c>
       <c r="AE51" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE51</f>
-        <v>87.5</v>
+        <v>4470.5</v>
       </c>
       <c r="AF51" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF51</f>
-        <v>219.5</v>
+        <v>13368.5</v>
       </c>
       <c r="AG51" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG51</f>
@@ -16233,27 +16235,27 @@
       </c>
       <c r="AA53" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA53</f>
-        <v>709</v>
+        <v>191</v>
       </c>
       <c r="AB53" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB53</f>
-        <v>5.6417489421720729E-2</v>
+        <v>0.20942408376963348</v>
       </c>
       <c r="AC53" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC53</f>
-        <v>5.6417489421720732E-3</v>
+        <v>2.0942408376963352E-2</v>
       </c>
       <c r="AD53" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD53</f>
-        <v>-705</v>
+        <v>-187</v>
       </c>
       <c r="AE53" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE53</f>
-        <v>354.5</v>
+        <v>95.5</v>
       </c>
       <c r="AF53" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF53</f>
-        <v>1059.5</v>
+        <v>282.5</v>
       </c>
       <c r="AG53" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG53</f>
@@ -16361,27 +16363,27 @@
       </c>
       <c r="AA54" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA54</f>
-        <v>3036</v>
+        <v>6086</v>
       </c>
       <c r="AB54" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB54</f>
-        <v>74.351119894598156</v>
+        <v>37.090042720999016</v>
       </c>
       <c r="AC54" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC54</f>
-        <v>7.4351119894598154</v>
+        <v>3.7090042720999015</v>
       </c>
       <c r="AD54" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD54</f>
-        <v>19537</v>
+        <v>16487</v>
       </c>
       <c r="AE54" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE54</f>
-        <v>1518</v>
+        <v>3043</v>
       </c>
       <c r="AF54" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF54</f>
-        <v>-18019</v>
+        <v>-13444</v>
       </c>
       <c r="AG54" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG54</f>
@@ -16489,27 +16491,27 @@
       </c>
       <c r="AA55" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA55</f>
-        <v>5285</v>
+        <v>712</v>
       </c>
       <c r="AB55" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB55</f>
-        <v>55.305581835383158</v>
+        <v>410.5196629213483</v>
       </c>
       <c r="AC55" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC55</f>
-        <v>5.5305581835383162</v>
+        <v>41.051966292134829</v>
       </c>
       <c r="AD55" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD55</f>
-        <v>23944</v>
+        <v>28517</v>
       </c>
       <c r="AE55" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE55</f>
-        <v>2642.5</v>
+        <v>356</v>
       </c>
       <c r="AF55" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF55</f>
-        <v>-21301.5</v>
+        <v>-28161</v>
       </c>
       <c r="AG55" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG55</f>
@@ -16617,27 +16619,27 @@
       </c>
       <c r="AA56" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA56</f>
-        <v>3223</v>
+        <v>3447</v>
       </c>
       <c r="AB56" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB56</f>
-        <v>50.108594477195155</v>
+        <v>46.852335364084716</v>
       </c>
       <c r="AC56" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC56</f>
-        <v>5.0108594477195156</v>
+        <v>4.6852335364084707</v>
       </c>
       <c r="AD56" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD56</f>
-        <v>12927</v>
+        <v>12703</v>
       </c>
       <c r="AE56" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE56</f>
-        <v>1611.5</v>
+        <v>1723.5</v>
       </c>
       <c r="AF56" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF56</f>
-        <v>-11315.5</v>
+        <v>-10979.5</v>
       </c>
       <c r="AG56" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG56</f>
@@ -16745,27 +16747,27 @@
       </c>
       <c r="AA57" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA57</f>
-        <v>2734</v>
+        <v>5851</v>
       </c>
       <c r="AB57" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB57</f>
-        <v>70.559619604974401</v>
+        <v>32.970432404717144</v>
       </c>
       <c r="AC57" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC57</f>
-        <v>7.0559619604974397</v>
+        <v>3.297043240471714</v>
       </c>
       <c r="AD57" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD57</f>
-        <v>16557</v>
+        <v>13440</v>
       </c>
       <c r="AE57" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE57</f>
-        <v>1367</v>
+        <v>2925.5</v>
       </c>
       <c r="AF57" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF57</f>
-        <v>-15190</v>
+        <v>-10514.5</v>
       </c>
       <c r="AG57" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG57</f>
@@ -16873,27 +16875,27 @@
       </c>
       <c r="AA58" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA58</f>
-        <v>446</v>
+        <v>3575</v>
       </c>
       <c r="AB58" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB58</f>
-        <v>16.031390134529147</v>
+        <v>2</v>
       </c>
       <c r="AC58" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC58</f>
-        <v>1.6031390134529149</v>
+        <v>0.2</v>
       </c>
       <c r="AD58" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD58</f>
-        <v>269</v>
+        <v>-2860</v>
       </c>
       <c r="AE58" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE58</f>
-        <v>223</v>
+        <v>1787.5</v>
       </c>
       <c r="AF58" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF58</f>
-        <v>-46</v>
+        <v>4647.5</v>
       </c>
       <c r="AG58" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG58</f>
@@ -17001,27 +17003,27 @@
       </c>
       <c r="AA59" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA59</f>
-        <v>933</v>
+        <v>3107</v>
       </c>
       <c r="AB59" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB59</f>
-        <v>4.137191854233655</v>
+        <v>1.2423559703894433</v>
       </c>
       <c r="AC59" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC59</f>
-        <v>0.4137191854233655</v>
+        <v>0.12423559703894432</v>
       </c>
       <c r="AD59" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD59</f>
-        <v>-547</v>
+        <v>-2721</v>
       </c>
       <c r="AE59" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE59</f>
-        <v>466.5</v>
+        <v>1553.5</v>
       </c>
       <c r="AF59" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF59</f>
-        <v>1013.5</v>
+        <v>4274.5</v>
       </c>
       <c r="AG59" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG59</f>
@@ -17129,27 +17131,27 @@
       </c>
       <c r="AA60" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA60</f>
-        <v>546</v>
+        <v>506</v>
       </c>
       <c r="AB60" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB60</f>
-        <v>5.457875457875458</v>
+        <v>5.8893280632411065</v>
       </c>
       <c r="AC60" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC60</f>
-        <v>0.54578754578754574</v>
+        <v>0.58893280632411071</v>
       </c>
       <c r="AD60" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD60</f>
-        <v>-248</v>
+        <v>-208</v>
       </c>
       <c r="AE60" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE60</f>
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="AF60" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF60</f>
-        <v>521</v>
+        <v>461</v>
       </c>
       <c r="AG60" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG60</f>
@@ -17257,27 +17259,27 @@
       </c>
       <c r="AA61" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA61</f>
-        <v>467</v>
+        <v>1021</v>
       </c>
       <c r="AB61" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB61</f>
-        <v>3.1263383297644536</v>
+        <v>1.4299706170421156</v>
       </c>
       <c r="AC61" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC61</f>
-        <v>0.31263383297644537</v>
+        <v>0.14299706170421156</v>
       </c>
       <c r="AD61" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD61</f>
-        <v>-321</v>
+        <v>-875</v>
       </c>
       <c r="AE61" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE61</f>
-        <v>233.5</v>
+        <v>510.5</v>
       </c>
       <c r="AF61" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF61</f>
-        <v>554.5</v>
+        <v>1385.5</v>
       </c>
       <c r="AG61" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG61</f>
@@ -17317,7 +17319,7 @@
       </c>
       <c r="AF62" s="44">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF62</f>
-        <v>139758.5</v>
+        <v>180594</v>
       </c>
     </row>
     <row r="63" spans="2:33" x14ac:dyDescent="0.25">
@@ -17326,10 +17328,10 @@
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
-      <c r="E63" s="64" t="s">
+      <c r="E63" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="F63" s="64"/>
+      <c r="F63" s="67"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -17354,10 +17356,10 @@
       <c r="AB63" s="42"/>
     </row>
     <row r="64" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B64" s="65" t="s">
+      <c r="B64" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="65"/>
+      <c r="C64" s="63"/>
       <c r="D64" s="48">
         <f>SUM(F13:F61)</f>
         <v>144936.54999999999</v>
@@ -17502,19 +17504,19 @@
       <c r="AB67" s="42"/>
     </row>
     <row r="68" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B68" s="65" t="s">
+      <c r="B68" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="C68" s="65"/>
+      <c r="C68" s="63"/>
       <c r="D68" s="50">
         <f>SUM(Z13:Z61)</f>
         <v>421177.93000000017</v>
       </c>
-      <c r="E68" s="66">
+      <c r="E68" s="64">
         <f>D68*100/D68</f>
         <v>100</v>
       </c>
-      <c r="F68" s="66"/>
+      <c r="F68" s="64"/>
       <c r="G68" s="51"/>
       <c r="H68" s="51"/>
       <c r="I68" s="51"/>
@@ -17599,10 +17601,10 @@
       <c r="AB70" s="42"/>
     </row>
     <row r="71" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="65"/>
+      <c r="C71" s="63"/>
       <c r="D71" s="3">
         <f>SUM(E13:E61)</f>
         <v>112990</v>
@@ -17717,11 +17719,11 @@
         <f>SUM(T13:T61)</f>
         <v>36961</v>
       </c>
-      <c r="E74" s="67">
+      <c r="E74" s="62">
         <f>D74*100/D75</f>
         <v>11.039956032533535</v>
       </c>
-      <c r="F74" s="67"/>
+      <c r="F74" s="62"/>
       <c r="G74" s="56"/>
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
@@ -17746,19 +17748,19 @@
       <c r="AB74" s="42"/>
     </row>
     <row r="75" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="63"/>
       <c r="D75" s="55">
         <f>SUM(Y13:Y61)</f>
         <v>334793</v>
       </c>
-      <c r="E75" s="67">
+      <c r="E75" s="62">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="67"/>
+      <c r="F75" s="62"/>
       <c r="G75" s="56"/>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
@@ -18519,23 +18521,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="B1:Z6"/>
+    <mergeCell ref="AA1:AG6"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="E64:F64"/>
     <mergeCell ref="E66:F66"/>
     <mergeCell ref="E67:F67"/>
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="E68:F68"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="B1:Z6"/>
-    <mergeCell ref="AA1:AG6"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G61">
     <cfRule type="colorScale" priority="5">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01A8870-B5F7-4FC8-A364-3BBA159AB4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED352C4B-DD2C-4B50-A022-F18BAA4EC641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -841,15 +841,6 @@
     <xf numFmtId="2" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -858,6 +849,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5638,6 +5638,7 @@
       <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -5765,22 +5766,22 @@
             <v>13606.800000000001</v>
           </cell>
           <cell r="AA13">
-            <v>12944</v>
+            <v>11620.833333333332</v>
           </cell>
           <cell r="AB13">
-            <v>7.7294499381953026</v>
+            <v>8.6095374686267476</v>
           </cell>
           <cell r="AC13">
-            <v>0.7729449938195303</v>
+            <v>0.8609537468626749</v>
           </cell>
           <cell r="AD13">
-            <v>-2939</v>
+            <v>-1615.8333333333321</v>
           </cell>
           <cell r="AE13">
-            <v>6472</v>
+            <v>5810.4166666666661</v>
           </cell>
           <cell r="AF13">
-            <v>9411</v>
+            <v>7426.2499999999982</v>
           </cell>
           <cell r="AG13">
             <v>125.0625</v>
@@ -5857,22 +5858,22 @@
             <v>888.81000000000006</v>
           </cell>
           <cell r="AA14">
-            <v>903</v>
+            <v>830.83333333333326</v>
           </cell>
           <cell r="AB14">
-            <v>6.1904761904761907</v>
+            <v>6.7281845536609834</v>
           </cell>
           <cell r="AC14">
-            <v>0.61904761904761907</v>
+            <v>0.67281845536609841</v>
           </cell>
           <cell r="AD14">
-            <v>-344</v>
+            <v>-271.83333333333326</v>
           </cell>
           <cell r="AE14">
-            <v>451.5</v>
+            <v>415.41666666666663</v>
           </cell>
           <cell r="AF14">
-            <v>795.5</v>
+            <v>687.24999999999989</v>
           </cell>
           <cell r="AG14">
             <v>6.9874999999999998</v>
@@ -5949,22 +5950,22 @@
             <v>6966.9599999999991</v>
           </cell>
           <cell r="AA15">
-            <v>5279</v>
+            <v>4660.833333333333</v>
           </cell>
           <cell r="AB15">
-            <v>6.5012312938056454</v>
+            <v>7.363490076881817</v>
           </cell>
           <cell r="AC15">
-            <v>0.65012312938056449</v>
+            <v>0.73634900768818168</v>
           </cell>
           <cell r="AD15">
-            <v>-1847</v>
+            <v>-1228.833333333333</v>
           </cell>
           <cell r="AE15">
-            <v>2639.5</v>
+            <v>2330.4166666666665</v>
           </cell>
           <cell r="AF15">
-            <v>4486.5</v>
+            <v>3559.2499999999995</v>
           </cell>
           <cell r="AG15">
             <v>57.2</v>
@@ -6041,22 +6042,22 @@
             <v>743.66</v>
           </cell>
           <cell r="AA16">
-            <v>1061</v>
+            <v>908.33333333333326</v>
           </cell>
           <cell r="AB16">
-            <v>1.9415645617342132</v>
+            <v>2.2678899082568806</v>
           </cell>
           <cell r="AC16">
-            <v>0.19415645617342131</v>
+            <v>0.2267889908256881</v>
           </cell>
           <cell r="AD16">
-            <v>-855</v>
+            <v>-702.33333333333326</v>
           </cell>
           <cell r="AE16">
-            <v>530.5</v>
+            <v>454.16666666666663</v>
           </cell>
           <cell r="AF16">
-            <v>1385.5</v>
+            <v>1156.5</v>
           </cell>
           <cell r="AG16">
             <v>7.3571428571428568</v>
@@ -6133,22 +6134,22 @@
             <v>1861.36</v>
           </cell>
           <cell r="AA17">
-            <v>105</v>
+            <v>94.166666666666657</v>
           </cell>
           <cell r="AB17">
-            <v>20.19047619047619</v>
+            <v>22.513274336283189</v>
           </cell>
           <cell r="AC17">
-            <v>2.019047619047619</v>
+            <v>2.2513274336283189</v>
           </cell>
           <cell r="AD17">
-            <v>107</v>
+            <v>117.83333333333334</v>
           </cell>
           <cell r="AE17">
-            <v>52.5</v>
+            <v>47.083333333333329</v>
           </cell>
           <cell r="AF17">
-            <v>-54.5</v>
+            <v>-70.750000000000014</v>
           </cell>
           <cell r="AG17">
             <v>17.666666666666668</v>
@@ -6225,22 +6226,22 @@
             <v>5277.51</v>
           </cell>
           <cell r="AA18">
-            <v>15948</v>
+            <v>13972.5</v>
           </cell>
           <cell r="AB18">
-            <v>5.2526962628542764</v>
+            <v>5.9953480050098404</v>
           </cell>
           <cell r="AC18">
-            <v>0.52526962628542762</v>
+            <v>0.59953480050098407</v>
           </cell>
           <cell r="AD18">
-            <v>-7571</v>
+            <v>-5595.5</v>
           </cell>
           <cell r="AE18">
-            <v>7974</v>
+            <v>6986.25</v>
           </cell>
           <cell r="AF18">
-            <v>15545</v>
+            <v>12581.75</v>
           </cell>
           <cell r="AG18">
             <v>139.61666666666667</v>
@@ -6317,22 +6318,22 @@
             <v>949.41</v>
           </cell>
           <cell r="AA19">
-            <v>1537</v>
+            <v>1384.1666666666665</v>
           </cell>
           <cell r="AB19">
-            <v>9.8048145738451531</v>
+            <v>10.887417218543048</v>
           </cell>
           <cell r="AC19">
-            <v>0.98048145738451531</v>
+            <v>1.0887417218543047</v>
           </cell>
           <cell r="AD19">
-            <v>-30</v>
+            <v>122.83333333333348</v>
           </cell>
           <cell r="AE19">
-            <v>768.5</v>
+            <v>692.08333333333326</v>
           </cell>
           <cell r="AF19">
-            <v>798.5</v>
+            <v>569.24999999999977</v>
           </cell>
           <cell r="AG19">
             <v>25.116666666666667</v>
@@ -6409,22 +6410,22 @@
             <v>2498.58</v>
           </cell>
           <cell r="AA20">
-            <v>3403</v>
+            <v>3075.833333333333</v>
           </cell>
           <cell r="AB20">
-            <v>11.654422568322069</v>
+            <v>12.894066648604715</v>
           </cell>
           <cell r="AC20">
-            <v>1.1654422568322069</v>
+            <v>1.2894066648604716</v>
           </cell>
           <cell r="AD20">
-            <v>563</v>
+            <v>890.16666666666697</v>
           </cell>
           <cell r="AE20">
-            <v>1701.5</v>
+            <v>1537.9166666666665</v>
           </cell>
           <cell r="AF20">
-            <v>1138.5</v>
+            <v>647.74999999999955</v>
           </cell>
           <cell r="AG20">
             <v>66.099999999999994</v>
@@ -6501,22 +6502,22 @@
             <v>8325.42</v>
           </cell>
           <cell r="AA21">
-            <v>7625</v>
+            <v>7126.6666666666661</v>
           </cell>
           <cell r="AB21">
-            <v>10.017049180327868</v>
+            <v>10.717492984097287</v>
           </cell>
           <cell r="AC21">
-            <v>1.0017049180327868</v>
+            <v>1.0717492984097288</v>
           </cell>
           <cell r="AD21">
-            <v>13</v>
+            <v>511.33333333333394</v>
           </cell>
           <cell r="AE21">
-            <v>3812.5</v>
+            <v>3563.333333333333</v>
           </cell>
           <cell r="AF21">
-            <v>3799.5</v>
+            <v>3051.9999999999991</v>
           </cell>
           <cell r="AG21">
             <v>141.44444444444446</v>
@@ -6593,22 +6594,22 @@
             <v>4099.4900000000007</v>
           </cell>
           <cell r="AA22">
-            <v>3542</v>
+            <v>3344.166666666667</v>
           </cell>
           <cell r="AB22">
-            <v>10.618294748729532</v>
+            <v>11.246449040617991</v>
           </cell>
           <cell r="AC22">
-            <v>1.0618294748729531</v>
+            <v>1.124644904061799</v>
           </cell>
           <cell r="AD22">
-            <v>219</v>
+            <v>416.83333333333303</v>
           </cell>
           <cell r="AE22">
-            <v>1771</v>
+            <v>1672.0833333333335</v>
           </cell>
           <cell r="AF22">
-            <v>1552</v>
+            <v>1255.2500000000005</v>
           </cell>
           <cell r="AG22">
             <v>69.648148148148152</v>
@@ -6685,22 +6686,22 @@
             <v>38473.719999999994</v>
           </cell>
           <cell r="AA23">
-            <v>39911</v>
+            <v>36112.5</v>
           </cell>
           <cell r="AB23">
-            <v>8.3102402846333092</v>
+            <v>9.1843544479058501</v>
           </cell>
           <cell r="AC23">
-            <v>0.8310240284633309</v>
+            <v>0.91843544479058503</v>
           </cell>
           <cell r="AD23">
-            <v>-6744</v>
+            <v>-2945.5</v>
           </cell>
           <cell r="AE23">
-            <v>19955.5</v>
+            <v>18056.25</v>
           </cell>
           <cell r="AF23">
-            <v>26699.5</v>
+            <v>21001.75</v>
           </cell>
           <cell r="AG23">
             <v>614.2037037037037</v>
@@ -6777,22 +6778,22 @@
             <v>29054.519999999997</v>
           </cell>
           <cell r="AA24">
-            <v>26342</v>
+            <v>23759.166666666664</v>
           </cell>
           <cell r="AB24">
-            <v>9.5083896439146613</v>
+            <v>10.542036407000808</v>
           </cell>
           <cell r="AC24">
-            <v>0.95083896439146609</v>
+            <v>1.0542036407000808</v>
           </cell>
           <cell r="AD24">
-            <v>-1295</v>
+            <v>1287.8333333333358</v>
           </cell>
           <cell r="AE24">
-            <v>13171</v>
+            <v>11879.583333333332</v>
           </cell>
           <cell r="AF24">
-            <v>14466</v>
+            <v>10591.749999999996</v>
           </cell>
           <cell r="AG24">
             <v>463.83333333333331</v>
@@ -6869,22 +6870,22 @@
             <v>30040.519999999997</v>
           </cell>
           <cell r="AA25">
-            <v>25420</v>
+            <v>22936.666666666664</v>
           </cell>
           <cell r="AB25">
-            <v>10.187647521636507</v>
+            <v>11.290655427990119</v>
           </cell>
           <cell r="AC25">
-            <v>1.0187647521636507</v>
+            <v>1.1290655427990119</v>
           </cell>
           <cell r="AD25">
-            <v>477</v>
+            <v>2960.3333333333358</v>
           </cell>
           <cell r="AE25">
-            <v>12710</v>
+            <v>11468.333333333332</v>
           </cell>
           <cell r="AF25">
-            <v>12233</v>
+            <v>8507.9999999999964</v>
           </cell>
           <cell r="AG25">
             <v>479.57407407407408</v>
@@ -6961,22 +6962,22 @@
             <v>34369.64</v>
           </cell>
           <cell r="AA26">
-            <v>30373</v>
+            <v>27655.833333333336</v>
           </cell>
           <cell r="AB26">
-            <v>9.7550455997102681</v>
+            <v>10.713472142706481</v>
           </cell>
           <cell r="AC26">
-            <v>0.97550455997102692</v>
+            <v>1.0713472142706479</v>
           </cell>
           <cell r="AD26">
-            <v>-744</v>
+            <v>1973.1666666666642</v>
           </cell>
           <cell r="AE26">
-            <v>15186.5</v>
+            <v>13827.916666666668</v>
           </cell>
           <cell r="AF26">
-            <v>15930.5</v>
+            <v>11854.750000000004</v>
           </cell>
           <cell r="AG26">
             <v>548.68518518518522</v>
@@ -7053,22 +7054,22 @@
             <v>1758.56</v>
           </cell>
           <cell r="AA27">
-            <v>365</v>
+            <v>320.83333333333337</v>
           </cell>
           <cell r="AB27">
-            <v>41.534246575342465</v>
+            <v>47.251948051948048</v>
           </cell>
           <cell r="AC27">
-            <v>4.1534246575342468</v>
+            <v>4.7251948051948043</v>
           </cell>
           <cell r="AD27">
-            <v>1151</v>
+            <v>1195.1666666666665</v>
           </cell>
           <cell r="AE27">
-            <v>182.5</v>
+            <v>160.41666666666669</v>
           </cell>
           <cell r="AF27">
-            <v>-968.5</v>
+            <v>-1034.7499999999998</v>
           </cell>
           <cell r="AG27">
             <v>28.074074074074073</v>
@@ -7100,13 +7101,13 @@
             <v>3519.4399999999996</v>
           </cell>
           <cell r="L28">
-            <v>17.847058823529412</v>
+            <v>14.75202593192869</v>
           </cell>
           <cell r="M28">
-            <v>3740</v>
+            <v>4524.6666666666661</v>
           </cell>
           <cell r="N28">
-            <v>484</v>
+            <v>-50.999999999999545</v>
           </cell>
           <cell r="O28">
             <v>251</v>
@@ -7145,22 +7146,22 @@
             <v>5583.08</v>
           </cell>
           <cell r="AA28">
-            <v>1700</v>
+            <v>2056.6666666666665</v>
           </cell>
           <cell r="AB28">
-            <v>28.311764705882354</v>
+            <v>23.401944894651542</v>
           </cell>
           <cell r="AC28">
-            <v>2.8311764705882352</v>
+            <v>2.3401944894651541</v>
           </cell>
           <cell r="AD28">
-            <v>3113</v>
+            <v>2756.3333333333335</v>
           </cell>
           <cell r="AE28">
-            <v>850</v>
+            <v>1028.3333333333333</v>
           </cell>
           <cell r="AF28">
-            <v>-2263</v>
+            <v>-1728.0000000000002</v>
           </cell>
           <cell r="AG28">
             <v>89.129629629629633</v>
@@ -7192,13 +7193,13 @@
             <v>3309.4799999999996</v>
           </cell>
           <cell r="L29">
-            <v>13.245125348189415</v>
+            <v>11.609359104781282</v>
           </cell>
           <cell r="M29">
-            <v>4738.8</v>
+            <v>5406.5</v>
           </cell>
           <cell r="N29">
-            <v>-378</v>
+            <v>-833.25</v>
           </cell>
           <cell r="O29">
             <v>236</v>
@@ -7237,22 +7238,22 @@
             <v>5281.48</v>
           </cell>
           <cell r="AA29">
-            <v>2154</v>
+            <v>2457.5</v>
           </cell>
           <cell r="AB29">
-            <v>21.137418755803157</v>
+            <v>18.526958290946084</v>
           </cell>
           <cell r="AC29">
-            <v>2.1137418755803159</v>
+            <v>1.8526958290946083</v>
           </cell>
           <cell r="AD29">
-            <v>2399</v>
+            <v>2095.5</v>
           </cell>
           <cell r="AE29">
-            <v>1077</v>
+            <v>1228.75</v>
           </cell>
           <cell r="AF29">
-            <v>-1322</v>
+            <v>-866.75</v>
           </cell>
           <cell r="AG29">
             <v>84.31481481481481</v>
@@ -7284,13 +7285,13 @@
             <v>3259.6</v>
           </cell>
           <cell r="L30">
-            <v>13.876543209876543</v>
+            <v>12.064400715563508</v>
           </cell>
           <cell r="M30">
-            <v>4455</v>
+            <v>5124.1666666666661</v>
           </cell>
           <cell r="N30">
-            <v>-227.5</v>
+            <v>-683.74999999999955</v>
           </cell>
           <cell r="O30">
             <v>236</v>
@@ -7329,22 +7330,22 @@
             <v>6992.48</v>
           </cell>
           <cell r="AA30">
-            <v>2025</v>
+            <v>2329.1666666666665</v>
           </cell>
           <cell r="AB30">
-            <v>29.767901234567901</v>
+            <v>25.880500894454382</v>
           </cell>
           <cell r="AC30">
-            <v>2.9767901234567899</v>
+            <v>2.5880500894454386</v>
           </cell>
           <cell r="AD30">
-            <v>4003</v>
+            <v>3698.8333333333335</v>
           </cell>
           <cell r="AE30">
-            <v>1012.5</v>
+            <v>1164.5833333333333</v>
           </cell>
           <cell r="AF30">
-            <v>-2990.5</v>
+            <v>-2534.25</v>
           </cell>
           <cell r="AG30">
             <v>111.62962962962963</v>
@@ -7421,22 +7422,22 @@
             <v>5045.2800000000007</v>
           </cell>
           <cell r="AA31">
-            <v>2523</v>
+            <v>2303.3333333333335</v>
           </cell>
           <cell r="AB31">
-            <v>5.4340071343638527</v>
+            <v>5.9522431259044861</v>
           </cell>
           <cell r="AC31">
-            <v>0.5434007134363853</v>
+            <v>0.59522431259044861</v>
           </cell>
           <cell r="AD31">
-            <v>-1152</v>
+            <v>-932.33333333333348</v>
           </cell>
           <cell r="AE31">
-            <v>1261.5</v>
+            <v>1151.6666666666667</v>
           </cell>
           <cell r="AF31">
-            <v>2413.5</v>
+            <v>2084</v>
           </cell>
           <cell r="AG31">
             <v>85.6875</v>
@@ -7513,22 +7514,22 @@
             <v>3606.4</v>
           </cell>
           <cell r="AA32">
-            <v>1391</v>
+            <v>1314.1666666666665</v>
           </cell>
           <cell r="AB32">
-            <v>7.0452911574406905</v>
+            <v>7.4571972098922013</v>
           </cell>
           <cell r="AC32">
-            <v>0.70452911574406907</v>
+            <v>0.74571972098922013</v>
           </cell>
           <cell r="AD32">
-            <v>-411</v>
+            <v>-334.16666666666652</v>
           </cell>
           <cell r="AE32">
-            <v>695.5</v>
+            <v>657.08333333333326</v>
           </cell>
           <cell r="AF32">
-            <v>1106.5</v>
+            <v>991.24999999999977</v>
           </cell>
           <cell r="AG32">
             <v>61.25</v>
@@ -7605,22 +7606,22 @@
             <v>13703.300000000001</v>
           </cell>
           <cell r="AA33">
-            <v>5336</v>
+            <v>5004.166666666667</v>
           </cell>
           <cell r="AB33">
-            <v>6.1881559220389803</v>
+            <v>6.5985012489592005</v>
           </cell>
           <cell r="AC33">
-            <v>0.61881559220389803</v>
+            <v>0.65985012489591999</v>
           </cell>
           <cell r="AD33">
-            <v>-2034</v>
+            <v>-1702.166666666667</v>
           </cell>
           <cell r="AE33">
-            <v>2668</v>
+            <v>2502.0833333333335</v>
           </cell>
           <cell r="AF33">
-            <v>4702</v>
+            <v>4204.25</v>
           </cell>
           <cell r="AG33">
             <v>206.375</v>
@@ -7697,22 +7698,22 @@
             <v>26174.050000000003</v>
           </cell>
           <cell r="AA34">
-            <v>8373</v>
+            <v>7844.1666666666661</v>
           </cell>
           <cell r="AB34">
-            <v>7.5325450853935276</v>
+            <v>8.0403697014766813</v>
           </cell>
           <cell r="AC34">
-            <v>0.75325450853935272</v>
+            <v>0.80403697014766817</v>
           </cell>
           <cell r="AD34">
-            <v>-2066</v>
+            <v>-1537.1666666666661</v>
           </cell>
           <cell r="AE34">
-            <v>4186.5</v>
+            <v>3922.083333333333</v>
           </cell>
           <cell r="AF34">
-            <v>6252.5</v>
+            <v>5459.2499999999991</v>
           </cell>
           <cell r="AG34">
             <v>394.1875</v>
@@ -7789,7 +7790,7 @@
             <v>0</v>
           </cell>
           <cell r="AA35">
-            <v>100</v>
+            <v>83.333333333333343</v>
           </cell>
           <cell r="AB35">
             <v>0</v>
@@ -7798,13 +7799,13 @@
             <v>0</v>
           </cell>
           <cell r="AD35">
-            <v>-100</v>
+            <v>-83.333333333333343</v>
           </cell>
           <cell r="AE35">
-            <v>50</v>
+            <v>41.666666666666671</v>
           </cell>
           <cell r="AF35">
-            <v>150</v>
+            <v>125.00000000000001</v>
           </cell>
           <cell r="AG35">
             <v>0</v>
@@ -7881,22 +7882,22 @@
             <v>2253.4500000000003</v>
           </cell>
           <cell r="AA36">
-            <v>1682</v>
+            <v>1420</v>
           </cell>
           <cell r="AB36">
-            <v>3.2282996432818076</v>
+            <v>3.823943661971831</v>
           </cell>
           <cell r="AC36">
-            <v>0.32282996432818073</v>
+            <v>0.38239436619718309</v>
           </cell>
           <cell r="AD36">
-            <v>-1139</v>
+            <v>-877</v>
           </cell>
           <cell r="AE36">
-            <v>841</v>
+            <v>710</v>
           </cell>
           <cell r="AF36">
-            <v>1980</v>
+            <v>1587</v>
           </cell>
           <cell r="AG36">
             <v>33.9375</v>
@@ -7973,22 +7974,22 @@
             <v>16573.84</v>
           </cell>
           <cell r="AA37">
-            <v>7434</v>
+            <v>6635.8333333333339</v>
           </cell>
           <cell r="AB37">
-            <v>13.677697067527577</v>
+            <v>15.322868265728996</v>
           </cell>
           <cell r="AC37">
-            <v>1.3677697067527577</v>
+            <v>1.5322868265728995</v>
           </cell>
           <cell r="AD37">
-            <v>2734</v>
+            <v>3532.1666666666661</v>
           </cell>
           <cell r="AE37">
-            <v>3717</v>
+            <v>3317.916666666667</v>
           </cell>
           <cell r="AF37">
-            <v>983</v>
+            <v>-214.24999999999909</v>
           </cell>
           <cell r="AG37">
             <v>188.2962962962963</v>
@@ -8065,22 +8066,22 @@
             <v>16068.539999999999</v>
           </cell>
           <cell r="AA38">
-            <v>12107</v>
+            <v>10833.333333333332</v>
           </cell>
           <cell r="AB38">
-            <v>8.1423969604361108</v>
+            <v>9.0996923076923082</v>
           </cell>
           <cell r="AC38">
-            <v>0.81423969604361113</v>
+            <v>0.90996923076923086</v>
           </cell>
           <cell r="AD38">
-            <v>-2249</v>
+            <v>-975.33333333333212</v>
           </cell>
           <cell r="AE38">
-            <v>6053.5</v>
+            <v>5416.6666666666661</v>
           </cell>
           <cell r="AF38">
-            <v>8302.5</v>
+            <v>6391.9999999999982</v>
           </cell>
           <cell r="AG38">
             <v>182.55555555555554</v>
@@ -8157,22 +8158,22 @@
             <v>3204.58</v>
           </cell>
           <cell r="AA39">
-            <v>5311</v>
+            <v>4935</v>
           </cell>
           <cell r="AB39">
-            <v>3.7017510826586331</v>
+            <v>3.9837892603850049</v>
           </cell>
           <cell r="AC39">
-            <v>0.37017510826586331</v>
+            <v>0.3983789260385005</v>
           </cell>
           <cell r="AD39">
-            <v>-3345</v>
+            <v>-2969</v>
           </cell>
           <cell r="AE39">
-            <v>2655.5</v>
+            <v>2467.5</v>
           </cell>
           <cell r="AF39">
-            <v>6000.5</v>
+            <v>5436.5</v>
           </cell>
           <cell r="AG39">
             <v>36.407407407407405</v>
@@ -8249,22 +8250,22 @@
             <v>7409.98</v>
           </cell>
           <cell r="AA40">
-            <v>3730</v>
+            <v>3581.666666666667</v>
           </cell>
           <cell r="AB40">
-            <v>12.187667560321715</v>
+            <v>12.692415076779897</v>
           </cell>
           <cell r="AC40">
-            <v>1.2187667560321715</v>
+            <v>1.2692415076779897</v>
           </cell>
           <cell r="AD40">
-            <v>816</v>
+            <v>964.33333333333303</v>
           </cell>
           <cell r="AE40">
-            <v>1865</v>
+            <v>1790.8333333333335</v>
           </cell>
           <cell r="AF40">
-            <v>1049</v>
+            <v>826.50000000000045</v>
           </cell>
           <cell r="AG40">
             <v>84.18518518518519</v>
@@ -8525,22 +8526,22 @@
             <v>4065.15</v>
           </cell>
           <cell r="AA43">
-            <v>47</v>
+            <v>1317.5</v>
           </cell>
           <cell r="AB43">
-            <v>140.63829787234042</v>
+            <v>5.0170777988614796</v>
           </cell>
           <cell r="AC43">
-            <v>14.063829787234043</v>
+            <v>0.50170777988614801</v>
           </cell>
           <cell r="AD43">
-            <v>614</v>
+            <v>-656.5</v>
           </cell>
           <cell r="AE43">
-            <v>23.5</v>
+            <v>658.75</v>
           </cell>
           <cell r="AF43">
-            <v>-590.5</v>
+            <v>1315.25</v>
           </cell>
           <cell r="AG43">
             <v>12.24074074074074</v>
@@ -8617,22 +8618,22 @@
             <v>6980.25</v>
           </cell>
           <cell r="AA44">
-            <v>46</v>
+            <v>1275.8333333333333</v>
           </cell>
           <cell r="AB44">
-            <v>246.73913043478262</v>
+            <v>8.8961463096015674</v>
           </cell>
           <cell r="AC44">
-            <v>24.673913043478262</v>
+            <v>0.8896146309601568</v>
           </cell>
           <cell r="AD44">
-            <v>1089</v>
+            <v>-140.83333333333326</v>
           </cell>
           <cell r="AE44">
-            <v>23</v>
+            <v>637.91666666666663</v>
           </cell>
           <cell r="AF44">
-            <v>-1066</v>
+            <v>778.74999999999989</v>
           </cell>
           <cell r="AG44">
             <v>21.018518518518519</v>
@@ -8709,22 +8710,22 @@
             <v>4816.32</v>
           </cell>
           <cell r="AA45">
-            <v>1424</v>
+            <v>5877.5</v>
           </cell>
           <cell r="AB45">
-            <v>29.157303370786515</v>
+            <v>7.0642279880901748</v>
           </cell>
           <cell r="AC45">
-            <v>2.9157303370786516</v>
+            <v>0.70642279880901748</v>
           </cell>
           <cell r="AD45">
-            <v>2728</v>
+            <v>-1725.5</v>
           </cell>
           <cell r="AE45">
-            <v>712</v>
+            <v>2938.75</v>
           </cell>
           <cell r="AF45">
-            <v>-2016</v>
+            <v>4664.25</v>
           </cell>
           <cell r="AG45">
             <v>76.888888888888886</v>
@@ -8801,22 +8802,22 @@
             <v>9920.32</v>
           </cell>
           <cell r="AA46">
-            <v>1357</v>
+            <v>6554.1666666666661</v>
           </cell>
           <cell r="AB46">
-            <v>63.021370670596909</v>
+            <v>13.048188175460904</v>
           </cell>
           <cell r="AC46">
-            <v>6.3021370670596903</v>
+            <v>1.3048188175460904</v>
           </cell>
           <cell r="AD46">
-            <v>7195</v>
+            <v>1997.8333333333339</v>
           </cell>
           <cell r="AE46">
-            <v>678.5</v>
+            <v>3277.083333333333</v>
           </cell>
           <cell r="AF46">
-            <v>-6516.5</v>
+            <v>1279.2499999999991</v>
           </cell>
           <cell r="AG46">
             <v>158.37037037037038</v>
@@ -8893,22 +8894,22 @@
             <v>7810.28</v>
           </cell>
           <cell r="AA47">
-            <v>6422</v>
+            <v>8187.5</v>
           </cell>
           <cell r="AB47">
-            <v>10.484272812208035</v>
+            <v>8.2235114503816789</v>
           </cell>
           <cell r="AC47">
-            <v>1.0484272812208035</v>
+            <v>0.82235114503816797</v>
           </cell>
           <cell r="AD47">
-            <v>311</v>
+            <v>-1454.5</v>
           </cell>
           <cell r="AE47">
-            <v>3211</v>
+            <v>4093.75</v>
           </cell>
           <cell r="AF47">
-            <v>2900</v>
+            <v>5548.25</v>
           </cell>
           <cell r="AG47">
             <v>124.68518518518519</v>
@@ -8985,22 +8986,22 @@
             <v>6063.32</v>
           </cell>
           <cell r="AA48">
-            <v>7168</v>
+            <v>5705</v>
           </cell>
           <cell r="AB48">
-            <v>7.2921316964285721</v>
+            <v>9.1621384750219104</v>
           </cell>
           <cell r="AC48">
-            <v>0.7292131696428571</v>
+            <v>0.91621384750219104</v>
           </cell>
           <cell r="AD48">
-            <v>-1941</v>
+            <v>-478</v>
           </cell>
           <cell r="AE48">
-            <v>3584</v>
+            <v>2852.5</v>
           </cell>
           <cell r="AF48">
-            <v>5525</v>
+            <v>3330.5</v>
           </cell>
           <cell r="AG48">
             <v>96.796296296296291</v>
@@ -9077,22 +9078,22 @@
             <v>216</v>
           </cell>
           <cell r="AA49">
-            <v>476</v>
+            <v>21.666666666666664</v>
           </cell>
           <cell r="AB49">
-            <v>0.25210084033613445</v>
+            <v>5.5384615384615392</v>
           </cell>
           <cell r="AC49">
-            <v>2.5210084033613446E-2</v>
+            <v>0.55384615384615388</v>
           </cell>
           <cell r="AD49">
-            <v>-464</v>
+            <v>-9.6666666666666643</v>
           </cell>
           <cell r="AE49">
-            <v>238</v>
+            <v>10.833333333333332</v>
           </cell>
           <cell r="AF49">
-            <v>702</v>
+            <v>20.499999999999996</v>
           </cell>
           <cell r="AG49">
             <v>6</v>
@@ -9169,7 +9170,7 @@
             <v>198</v>
           </cell>
           <cell r="AA50">
-            <v>612</v>
+            <v>0</v>
           </cell>
           <cell r="AB50">
             <v>0</v>
@@ -9178,13 +9179,13 @@
             <v>0</v>
           </cell>
           <cell r="AD50">
-            <v>-601</v>
+            <v>11</v>
           </cell>
           <cell r="AE50">
-            <v>306</v>
+            <v>0</v>
           </cell>
           <cell r="AF50">
-            <v>907</v>
+            <v>-11</v>
           </cell>
           <cell r="AG50">
             <v>5.5</v>
@@ -9261,22 +9262,22 @@
             <v>49.879999999999995</v>
           </cell>
           <cell r="AA51">
-            <v>8941</v>
+            <v>248.33333333333331</v>
           </cell>
           <cell r="AB51">
-            <v>4.8093054468180289E-2</v>
+            <v>1.731543624161074</v>
           </cell>
           <cell r="AC51">
-            <v>4.8093054468180295E-3</v>
+            <v>0.1731543624161074</v>
           </cell>
           <cell r="AD51">
-            <v>-8898</v>
+            <v>-205.33333333333331</v>
           </cell>
           <cell r="AE51">
-            <v>4470.5</v>
+            <v>124.16666666666666</v>
           </cell>
           <cell r="AF51">
-            <v>13368.5</v>
+            <v>329.5</v>
           </cell>
           <cell r="AG51">
             <v>1.075</v>
@@ -9445,22 +9446,22 @@
             <v>4.6399999999999997</v>
           </cell>
           <cell r="AA53">
-            <v>191</v>
+            <v>593.33333333333337</v>
           </cell>
           <cell r="AB53">
-            <v>0.20942408376963348</v>
+            <v>6.741573033707865E-2</v>
           </cell>
           <cell r="AC53">
-            <v>2.0942408376963352E-2</v>
+            <v>6.7415730337078645E-3</v>
           </cell>
           <cell r="AD53">
-            <v>-187</v>
+            <v>-589.33333333333337</v>
           </cell>
           <cell r="AE53">
-            <v>95.5</v>
+            <v>296.66666666666669</v>
           </cell>
           <cell r="AF53">
-            <v>282.5</v>
+            <v>886</v>
           </cell>
           <cell r="AG53">
             <v>0.1</v>
@@ -9537,22 +9538,22 @@
             <v>18284.13</v>
           </cell>
           <cell r="AA54">
-            <v>6086</v>
+            <v>2998.333333333333</v>
           </cell>
           <cell r="AB54">
-            <v>37.090042720999016</v>
+            <v>75.285158421345201</v>
           </cell>
           <cell r="AC54">
-            <v>3.7090042720999015</v>
+            <v>7.52851584213452</v>
           </cell>
           <cell r="AD54">
-            <v>16487</v>
+            <v>19574.666666666668</v>
           </cell>
           <cell r="AE54">
-            <v>3043</v>
+            <v>1499.1666666666665</v>
           </cell>
           <cell r="AF54">
-            <v>-13444</v>
+            <v>-18075.5</v>
           </cell>
           <cell r="AG54">
             <v>1881.0833333333333</v>
@@ -9629,22 +9630,22 @@
             <v>23675.49</v>
           </cell>
           <cell r="AA55">
-            <v>712</v>
+            <v>5197.5</v>
           </cell>
           <cell r="AB55">
-            <v>410.5196629213483</v>
+            <v>56.236652236652233</v>
           </cell>
           <cell r="AC55">
-            <v>41.051966292134829</v>
+            <v>5.623665223665224</v>
           </cell>
           <cell r="AD55">
-            <v>28517</v>
+            <v>24031.5</v>
           </cell>
           <cell r="AE55">
-            <v>356</v>
+            <v>2598.75</v>
           </cell>
           <cell r="AF55">
-            <v>-28161</v>
+            <v>-21432.75</v>
           </cell>
           <cell r="AG55">
             <v>2435.75</v>
@@ -9721,22 +9722,22 @@
             <v>13081.5</v>
           </cell>
           <cell r="AA56">
-            <v>3447</v>
+            <v>3131.666666666667</v>
           </cell>
           <cell r="AB56">
-            <v>46.852335364084716</v>
+            <v>51.569984034060667</v>
           </cell>
           <cell r="AC56">
-            <v>4.6852335364084707</v>
+            <v>5.1569984034060665</v>
           </cell>
           <cell r="AD56">
-            <v>12703</v>
+            <v>13018.333333333332</v>
           </cell>
           <cell r="AE56">
-            <v>1723.5</v>
+            <v>1565.8333333333335</v>
           </cell>
           <cell r="AF56">
-            <v>-10979.5</v>
+            <v>-11452.499999999998</v>
           </cell>
           <cell r="AG56">
             <v>1345.8333333333333</v>
@@ -9813,22 +9814,22 @@
             <v>15625.710000000001</v>
           </cell>
           <cell r="AA57">
-            <v>5851</v>
+            <v>2761.666666666667</v>
           </cell>
           <cell r="AB57">
-            <v>32.970432404717144</v>
+            <v>69.852745926372961</v>
           </cell>
           <cell r="AC57">
-            <v>3.297043240471714</v>
+            <v>6.9852745926372952</v>
           </cell>
           <cell r="AD57">
-            <v>13440</v>
+            <v>16529.333333333332</v>
           </cell>
           <cell r="AE57">
-            <v>2925.5</v>
+            <v>1380.8333333333335</v>
           </cell>
           <cell r="AF57">
-            <v>-10514.5</v>
+            <v>-15148.499999999998</v>
           </cell>
           <cell r="AG57">
             <v>1607.5833333333333</v>
@@ -9905,22 +9906,22 @@
             <v>1873.3000000000002</v>
           </cell>
           <cell r="AA58">
-            <v>3575</v>
+            <v>461.66666666666663</v>
           </cell>
           <cell r="AB58">
-            <v>2</v>
+            <v>15.48736462093863</v>
           </cell>
           <cell r="AC58">
-            <v>0.2</v>
+            <v>1.5487364620938628</v>
           </cell>
           <cell r="AD58">
-            <v>-2860</v>
+            <v>253.33333333333337</v>
           </cell>
           <cell r="AE58">
-            <v>1787.5</v>
+            <v>230.83333333333331</v>
           </cell>
           <cell r="AF58">
-            <v>4647.5</v>
+            <v>-22.500000000000057</v>
           </cell>
           <cell r="AG58">
             <v>119.16666666666667</v>
@@ -9997,22 +9998,22 @@
             <v>1011.32</v>
           </cell>
           <cell r="AA59">
-            <v>3107</v>
+            <v>896.66666666666674</v>
           </cell>
           <cell r="AB59">
-            <v>1.2423559703894433</v>
+            <v>4.3048327137546467</v>
           </cell>
           <cell r="AC59">
-            <v>0.12423559703894432</v>
+            <v>0.43048327137546466</v>
           </cell>
           <cell r="AD59">
-            <v>-2721</v>
+            <v>-510.66666666666674</v>
           </cell>
           <cell r="AE59">
-            <v>1553.5</v>
+            <v>448.33333333333337</v>
           </cell>
           <cell r="AF59">
-            <v>4274.5</v>
+            <v>959.00000000000011</v>
           </cell>
           <cell r="AG59">
             <v>64.333333333333329</v>
@@ -10089,22 +10090,22 @@
             <v>780.76</v>
           </cell>
           <cell r="AA60">
-            <v>506</v>
+            <v>510</v>
           </cell>
           <cell r="AB60">
-            <v>5.8893280632411065</v>
+            <v>5.8431372549019605</v>
           </cell>
           <cell r="AC60">
-            <v>0.58893280632411071</v>
+            <v>0.58431372549019611</v>
           </cell>
           <cell r="AD60">
-            <v>-208</v>
+            <v>-212</v>
           </cell>
           <cell r="AE60">
-            <v>253</v>
+            <v>255</v>
           </cell>
           <cell r="AF60">
-            <v>461</v>
+            <v>467</v>
           </cell>
           <cell r="AG60">
             <v>49.666666666666664</v>
@@ -10181,22 +10182,22 @@
             <v>382.52000000000004</v>
           </cell>
           <cell r="AA61">
-            <v>1021</v>
+            <v>430</v>
           </cell>
           <cell r="AB61">
-            <v>1.4299706170421156</v>
+            <v>3.3953488372093021</v>
           </cell>
           <cell r="AC61">
-            <v>0.14299706170421156</v>
+            <v>0.33953488372093021</v>
           </cell>
           <cell r="AD61">
-            <v>-875</v>
+            <v>-284</v>
           </cell>
           <cell r="AE61">
-            <v>510.5</v>
+            <v>215</v>
           </cell>
           <cell r="AF61">
-            <v>1385.5</v>
+            <v>499</v>
           </cell>
           <cell r="AG61">
             <v>24.333333333333332</v>
@@ -10207,7 +10208,7 @@
             <v>Units Produce</v>
           </cell>
           <cell r="AF62">
-            <v>180594</v>
+            <v>135034.5</v>
           </cell>
         </row>
       </sheetData>
@@ -10215,6 +10216,7 @@
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10539,212 +10541,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="66" t="s">
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="66"/>
-      <c r="AC1" s="66"/>
-      <c r="AD1" s="66"/>
-      <c r="AE1" s="66"/>
-      <c r="AF1" s="66"/>
-      <c r="AG1" s="66"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="66"/>
-      <c r="AB2" s="66"/>
-      <c r="AC2" s="66"/>
-      <c r="AD2" s="66"/>
-      <c r="AE2" s="66"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
+      <c r="AD2" s="63"/>
+      <c r="AE2" s="63"/>
+      <c r="AF2" s="63"/>
+      <c r="AG2" s="63"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="66"/>
-      <c r="AB3" s="66"/>
-      <c r="AC3" s="66"/>
-      <c r="AD3" s="66"/>
-      <c r="AE3" s="66"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="62"/>
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="63"/>
+      <c r="AD3" s="63"/>
+      <c r="AE3" s="63"/>
+      <c r="AF3" s="63"/>
+      <c r="AG3" s="63"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="66"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="62"/>
+      <c r="Y4" s="62"/>
+      <c r="Z4" s="62"/>
+      <c r="AA4" s="63"/>
+      <c r="AB4" s="63"/>
+      <c r="AC4" s="63"/>
+      <c r="AD4" s="63"/>
+      <c r="AE4" s="63"/>
+      <c r="AF4" s="63"/>
+      <c r="AG4" s="63"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="66"/>
-      <c r="AB5" s="66"/>
-      <c r="AC5" s="66"/>
-      <c r="AD5" s="66"/>
-      <c r="AE5" s="66"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="62"/>
+      <c r="Z5" s="62"/>
+      <c r="AA5" s="63"/>
+      <c r="AB5" s="63"/>
+      <c r="AC5" s="63"/>
+      <c r="AD5" s="63"/>
+      <c r="AE5" s="63"/>
+      <c r="AF5" s="63"/>
+      <c r="AG5" s="63"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="66"/>
-      <c r="AB6" s="66"/>
-      <c r="AC6" s="66"/>
-      <c r="AD6" s="66"/>
-      <c r="AE6" s="66"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="62"/>
+      <c r="X6" s="62"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="63"/>
+      <c r="AB6" s="63"/>
+      <c r="AC6" s="63"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="63"/>
+      <c r="AG6" s="63"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
@@ -11115,27 +11117,27 @@
       </c>
       <c r="AA13" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA13</f>
-        <v>12944</v>
+        <v>11620.833333333332</v>
       </c>
       <c r="AB13" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB13</f>
-        <v>7.7294499381953026</v>
+        <v>8.6095374686267476</v>
       </c>
       <c r="AC13" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC13</f>
-        <v>0.7729449938195303</v>
+        <v>0.8609537468626749</v>
       </c>
       <c r="AD13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD13</f>
-        <v>-2939</v>
+        <v>-1615.8333333333321</v>
       </c>
       <c r="AE13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE13</f>
-        <v>6472</v>
+        <v>5810.4166666666661</v>
       </c>
       <c r="AF13" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF13</f>
-        <v>9411</v>
+        <v>7426.2499999999982</v>
       </c>
       <c r="AG13" s="27">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG13</f>
@@ -11243,27 +11245,27 @@
       </c>
       <c r="AA14" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA14</f>
-        <v>903</v>
+        <v>830.83333333333326</v>
       </c>
       <c r="AB14" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB14</f>
-        <v>6.1904761904761907</v>
+        <v>6.7281845536609834</v>
       </c>
       <c r="AC14" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC14</f>
-        <v>0.61904761904761907</v>
+        <v>0.67281845536609841</v>
       </c>
       <c r="AD14" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD14</f>
-        <v>-344</v>
+        <v>-271.83333333333326</v>
       </c>
       <c r="AE14" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE14</f>
-        <v>451.5</v>
+        <v>415.41666666666663</v>
       </c>
       <c r="AF14" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF14</f>
-        <v>795.5</v>
+        <v>687.24999999999989</v>
       </c>
       <c r="AG14" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG14</f>
@@ -11371,27 +11373,27 @@
       </c>
       <c r="AA15" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA15</f>
-        <v>5279</v>
+        <v>4660.833333333333</v>
       </c>
       <c r="AB15" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB15</f>
-        <v>6.5012312938056454</v>
+        <v>7.363490076881817</v>
       </c>
       <c r="AC15" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC15</f>
-        <v>0.65012312938056449</v>
+        <v>0.73634900768818168</v>
       </c>
       <c r="AD15" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD15</f>
-        <v>-1847</v>
+        <v>-1228.833333333333</v>
       </c>
       <c r="AE15" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE15</f>
-        <v>2639.5</v>
+        <v>2330.4166666666665</v>
       </c>
       <c r="AF15" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF15</f>
-        <v>4486.5</v>
+        <v>3559.2499999999995</v>
       </c>
       <c r="AG15" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG15</f>
@@ -11499,27 +11501,27 @@
       </c>
       <c r="AA16" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA16</f>
-        <v>1061</v>
+        <v>908.33333333333326</v>
       </c>
       <c r="AB16" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB16</f>
-        <v>1.9415645617342132</v>
+        <v>2.2678899082568806</v>
       </c>
       <c r="AC16" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC16</f>
-        <v>0.19415645617342131</v>
+        <v>0.2267889908256881</v>
       </c>
       <c r="AD16" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD16</f>
-        <v>-855</v>
+        <v>-702.33333333333326</v>
       </c>
       <c r="AE16" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE16</f>
-        <v>530.5</v>
+        <v>454.16666666666663</v>
       </c>
       <c r="AF16" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF16</f>
-        <v>1385.5</v>
+        <v>1156.5</v>
       </c>
       <c r="AG16" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG16</f>
@@ -11627,27 +11629,27 @@
       </c>
       <c r="AA17" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA17</f>
-        <v>105</v>
+        <v>94.166666666666657</v>
       </c>
       <c r="AB17" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB17</f>
-        <v>20.19047619047619</v>
+        <v>22.513274336283189</v>
       </c>
       <c r="AC17" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC17</f>
-        <v>2.019047619047619</v>
+        <v>2.2513274336283189</v>
       </c>
       <c r="AD17" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD17</f>
-        <v>107</v>
+        <v>117.83333333333334</v>
       </c>
       <c r="AE17" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE17</f>
-        <v>52.5</v>
+        <v>47.083333333333329</v>
       </c>
       <c r="AF17" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF17</f>
-        <v>-54.5</v>
+        <v>-70.750000000000014</v>
       </c>
       <c r="AG17" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG17</f>
@@ -11755,27 +11757,27 @@
       </c>
       <c r="AA18" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA18</f>
-        <v>15948</v>
+        <v>13972.5</v>
       </c>
       <c r="AB18" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB18</f>
-        <v>5.2526962628542764</v>
+        <v>5.9953480050098404</v>
       </c>
       <c r="AC18" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC18</f>
-        <v>0.52526962628542762</v>
+        <v>0.59953480050098407</v>
       </c>
       <c r="AD18" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD18</f>
-        <v>-7571</v>
+        <v>-5595.5</v>
       </c>
       <c r="AE18" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE18</f>
-        <v>7974</v>
+        <v>6986.25</v>
       </c>
       <c r="AF18" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF18</f>
-        <v>15545</v>
+        <v>12581.75</v>
       </c>
       <c r="AG18" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG18</f>
@@ -11883,27 +11885,27 @@
       </c>
       <c r="AA19" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA19</f>
-        <v>1537</v>
+        <v>1384.1666666666665</v>
       </c>
       <c r="AB19" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB19</f>
-        <v>9.8048145738451531</v>
+        <v>10.887417218543048</v>
       </c>
       <c r="AC19" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC19</f>
-        <v>0.98048145738451531</v>
+        <v>1.0887417218543047</v>
       </c>
       <c r="AD19" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD19</f>
-        <v>-30</v>
+        <v>122.83333333333348</v>
       </c>
       <c r="AE19" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE19</f>
-        <v>768.5</v>
+        <v>692.08333333333326</v>
       </c>
       <c r="AF19" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF19</f>
-        <v>798.5</v>
+        <v>569.24999999999977</v>
       </c>
       <c r="AG19" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG19</f>
@@ -12011,27 +12013,27 @@
       </c>
       <c r="AA20" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA20</f>
-        <v>3403</v>
+        <v>3075.833333333333</v>
       </c>
       <c r="AB20" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB20</f>
-        <v>11.654422568322069</v>
+        <v>12.894066648604715</v>
       </c>
       <c r="AC20" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC20</f>
-        <v>1.1654422568322069</v>
+        <v>1.2894066648604716</v>
       </c>
       <c r="AD20" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD20</f>
-        <v>563</v>
+        <v>890.16666666666697</v>
       </c>
       <c r="AE20" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE20</f>
-        <v>1701.5</v>
+        <v>1537.9166666666665</v>
       </c>
       <c r="AF20" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF20</f>
-        <v>1138.5</v>
+        <v>647.74999999999955</v>
       </c>
       <c r="AG20" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG20</f>
@@ -12139,27 +12141,27 @@
       </c>
       <c r="AA21" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA21</f>
-        <v>7625</v>
+        <v>7126.6666666666661</v>
       </c>
       <c r="AB21" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB21</f>
-        <v>10.017049180327868</v>
+        <v>10.717492984097287</v>
       </c>
       <c r="AC21" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC21</f>
-        <v>1.0017049180327868</v>
+        <v>1.0717492984097288</v>
       </c>
       <c r="AD21" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD21</f>
-        <v>13</v>
+        <v>511.33333333333394</v>
       </c>
       <c r="AE21" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE21</f>
-        <v>3812.5</v>
+        <v>3563.333333333333</v>
       </c>
       <c r="AF21" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF21</f>
-        <v>3799.5</v>
+        <v>3051.9999999999991</v>
       </c>
       <c r="AG21" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG21</f>
@@ -12267,27 +12269,27 @@
       </c>
       <c r="AA22" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA22</f>
-        <v>3542</v>
+        <v>3344.166666666667</v>
       </c>
       <c r="AB22" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB22</f>
-        <v>10.618294748729532</v>
+        <v>11.246449040617991</v>
       </c>
       <c r="AC22" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC22</f>
-        <v>1.0618294748729531</v>
+        <v>1.124644904061799</v>
       </c>
       <c r="AD22" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD22</f>
-        <v>219</v>
+        <v>416.83333333333303</v>
       </c>
       <c r="AE22" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE22</f>
-        <v>1771</v>
+        <v>1672.0833333333335</v>
       </c>
       <c r="AF22" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF22</f>
-        <v>1552</v>
+        <v>1255.2500000000005</v>
       </c>
       <c r="AG22" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG22</f>
@@ -12395,27 +12397,27 @@
       </c>
       <c r="AA23" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA23</f>
-        <v>39911</v>
+        <v>36112.5</v>
       </c>
       <c r="AB23" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB23</f>
-        <v>8.3102402846333092</v>
+        <v>9.1843544479058501</v>
       </c>
       <c r="AC23" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC23</f>
-        <v>0.8310240284633309</v>
+        <v>0.91843544479058503</v>
       </c>
       <c r="AD23" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD23</f>
-        <v>-6744</v>
+        <v>-2945.5</v>
       </c>
       <c r="AE23" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE23</f>
-        <v>19955.5</v>
+        <v>18056.25</v>
       </c>
       <c r="AF23" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF23</f>
-        <v>26699.5</v>
+        <v>21001.75</v>
       </c>
       <c r="AG23" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG23</f>
@@ -12523,27 +12525,27 @@
       </c>
       <c r="AA24" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA24</f>
-        <v>26342</v>
+        <v>23759.166666666664</v>
       </c>
       <c r="AB24" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB24</f>
-        <v>9.5083896439146613</v>
+        <v>10.542036407000808</v>
       </c>
       <c r="AC24" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC24</f>
-        <v>0.95083896439146609</v>
+        <v>1.0542036407000808</v>
       </c>
       <c r="AD24" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD24</f>
-        <v>-1295</v>
+        <v>1287.8333333333358</v>
       </c>
       <c r="AE24" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE24</f>
-        <v>13171</v>
+        <v>11879.583333333332</v>
       </c>
       <c r="AF24" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF24</f>
-        <v>14466</v>
+        <v>10591.749999999996</v>
       </c>
       <c r="AG24" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG24</f>
@@ -12651,27 +12653,27 @@
       </c>
       <c r="AA25" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA25</f>
-        <v>25420</v>
+        <v>22936.666666666664</v>
       </c>
       <c r="AB25" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB25</f>
-        <v>10.187647521636507</v>
+        <v>11.290655427990119</v>
       </c>
       <c r="AC25" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC25</f>
-        <v>1.0187647521636507</v>
+        <v>1.1290655427990119</v>
       </c>
       <c r="AD25" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD25</f>
-        <v>477</v>
+        <v>2960.3333333333358</v>
       </c>
       <c r="AE25" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE25</f>
-        <v>12710</v>
+        <v>11468.333333333332</v>
       </c>
       <c r="AF25" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF25</f>
-        <v>12233</v>
+        <v>8507.9999999999964</v>
       </c>
       <c r="AG25" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG25</f>
@@ -12779,27 +12781,27 @@
       </c>
       <c r="AA26" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA26</f>
-        <v>30373</v>
+        <v>27655.833333333336</v>
       </c>
       <c r="AB26" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB26</f>
-        <v>9.7550455997102681</v>
+        <v>10.713472142706481</v>
       </c>
       <c r="AC26" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC26</f>
-        <v>0.97550455997102692</v>
+        <v>1.0713472142706479</v>
       </c>
       <c r="AD26" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD26</f>
-        <v>-744</v>
+        <v>1973.1666666666642</v>
       </c>
       <c r="AE26" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE26</f>
-        <v>15186.5</v>
+        <v>13827.916666666668</v>
       </c>
       <c r="AF26" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF26</f>
-        <v>15930.5</v>
+        <v>11854.750000000004</v>
       </c>
       <c r="AG26" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG26</f>
@@ -12907,27 +12909,27 @@
       </c>
       <c r="AA27" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA27</f>
-        <v>365</v>
+        <v>320.83333333333337</v>
       </c>
       <c r="AB27" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB27</f>
-        <v>41.534246575342465</v>
+        <v>47.251948051948048</v>
       </c>
       <c r="AC27" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC27</f>
-        <v>4.1534246575342468</v>
+        <v>4.7251948051948043</v>
       </c>
       <c r="AD27" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD27</f>
-        <v>1151</v>
+        <v>1195.1666666666665</v>
       </c>
       <c r="AE27" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE27</f>
-        <v>182.5</v>
+        <v>160.41666666666669</v>
       </c>
       <c r="AF27" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF27</f>
-        <v>-968.5</v>
+        <v>-1034.7499999999998</v>
       </c>
       <c r="AG27" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG27</f>
@@ -12975,15 +12977,15 @@
       </c>
       <c r="L28" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L28</f>
-        <v>17.847058823529412</v>
+        <v>14.75202593192869</v>
       </c>
       <c r="M28" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M28</f>
-        <v>3740</v>
+        <v>4524.6666666666661</v>
       </c>
       <c r="N28" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N28</f>
-        <v>484</v>
+        <v>-50.999999999999545</v>
       </c>
       <c r="O28" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O28</f>
@@ -13035,27 +13037,27 @@
       </c>
       <c r="AA28" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA28</f>
-        <v>1700</v>
+        <v>2056.6666666666665</v>
       </c>
       <c r="AB28" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB28</f>
-        <v>28.311764705882354</v>
+        <v>23.401944894651542</v>
       </c>
       <c r="AC28" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC28</f>
-        <v>2.8311764705882352</v>
+        <v>2.3401944894651541</v>
       </c>
       <c r="AD28" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD28</f>
-        <v>3113</v>
+        <v>2756.3333333333335</v>
       </c>
       <c r="AE28" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE28</f>
-        <v>850</v>
+        <v>1028.3333333333333</v>
       </c>
       <c r="AF28" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF28</f>
-        <v>-2263</v>
+        <v>-1728.0000000000002</v>
       </c>
       <c r="AG28" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG28</f>
@@ -13103,15 +13105,15 @@
       </c>
       <c r="L29" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L29</f>
-        <v>13.245125348189415</v>
+        <v>11.609359104781282</v>
       </c>
       <c r="M29" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M29</f>
-        <v>4738.8</v>
+        <v>5406.5</v>
       </c>
       <c r="N29" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N29</f>
-        <v>-378</v>
+        <v>-833.25</v>
       </c>
       <c r="O29" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O29</f>
@@ -13163,27 +13165,27 @@
       </c>
       <c r="AA29" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA29</f>
-        <v>2154</v>
+        <v>2457.5</v>
       </c>
       <c r="AB29" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB29</f>
-        <v>21.137418755803157</v>
+        <v>18.526958290946084</v>
       </c>
       <c r="AC29" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC29</f>
-        <v>2.1137418755803159</v>
+        <v>1.8526958290946083</v>
       </c>
       <c r="AD29" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD29</f>
-        <v>2399</v>
+        <v>2095.5</v>
       </c>
       <c r="AE29" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE29</f>
-        <v>1077</v>
+        <v>1228.75</v>
       </c>
       <c r="AF29" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF29</f>
-        <v>-1322</v>
+        <v>-866.75</v>
       </c>
       <c r="AG29" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG29</f>
@@ -13231,15 +13233,15 @@
       </c>
       <c r="L30" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L30</f>
-        <v>13.876543209876543</v>
+        <v>12.064400715563508</v>
       </c>
       <c r="M30" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M30</f>
-        <v>4455</v>
+        <v>5124.1666666666661</v>
       </c>
       <c r="N30" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N30</f>
-        <v>-227.5</v>
+        <v>-683.74999999999955</v>
       </c>
       <c r="O30" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O30</f>
@@ -13291,27 +13293,27 @@
       </c>
       <c r="AA30" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA30</f>
-        <v>2025</v>
+        <v>2329.1666666666665</v>
       </c>
       <c r="AB30" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB30</f>
-        <v>29.767901234567901</v>
+        <v>25.880500894454382</v>
       </c>
       <c r="AC30" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC30</f>
-        <v>2.9767901234567899</v>
+        <v>2.5880500894454386</v>
       </c>
       <c r="AD30" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD30</f>
-        <v>4003</v>
+        <v>3698.8333333333335</v>
       </c>
       <c r="AE30" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE30</f>
-        <v>1012.5</v>
+        <v>1164.5833333333333</v>
       </c>
       <c r="AF30" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF30</f>
-        <v>-2990.5</v>
+        <v>-2534.25</v>
       </c>
       <c r="AG30" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG30</f>
@@ -13419,27 +13421,27 @@
       </c>
       <c r="AA31" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA31</f>
-        <v>2523</v>
+        <v>2303.3333333333335</v>
       </c>
       <c r="AB31" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB31</f>
-        <v>5.4340071343638527</v>
+        <v>5.9522431259044861</v>
       </c>
       <c r="AC31" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC31</f>
-        <v>0.5434007134363853</v>
+        <v>0.59522431259044861</v>
       </c>
       <c r="AD31" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD31</f>
-        <v>-1152</v>
+        <v>-932.33333333333348</v>
       </c>
       <c r="AE31" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE31</f>
-        <v>1261.5</v>
+        <v>1151.6666666666667</v>
       </c>
       <c r="AF31" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF31</f>
-        <v>2413.5</v>
+        <v>2084</v>
       </c>
       <c r="AG31" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG31</f>
@@ -13547,27 +13549,27 @@
       </c>
       <c r="AA32" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA32</f>
-        <v>1391</v>
+        <v>1314.1666666666665</v>
       </c>
       <c r="AB32" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB32</f>
-        <v>7.0452911574406905</v>
+        <v>7.4571972098922013</v>
       </c>
       <c r="AC32" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC32</f>
-        <v>0.70452911574406907</v>
+        <v>0.74571972098922013</v>
       </c>
       <c r="AD32" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD32</f>
-        <v>-411</v>
+        <v>-334.16666666666652</v>
       </c>
       <c r="AE32" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE32</f>
-        <v>695.5</v>
+        <v>657.08333333333326</v>
       </c>
       <c r="AF32" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF32</f>
-        <v>1106.5</v>
+        <v>991.24999999999977</v>
       </c>
       <c r="AG32" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG32</f>
@@ -13675,27 +13677,27 @@
       </c>
       <c r="AA33" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA33</f>
-        <v>5336</v>
+        <v>5004.166666666667</v>
       </c>
       <c r="AB33" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB33</f>
-        <v>6.1881559220389803</v>
+        <v>6.5985012489592005</v>
       </c>
       <c r="AC33" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC33</f>
-        <v>0.61881559220389803</v>
+        <v>0.65985012489591999</v>
       </c>
       <c r="AD33" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD33</f>
-        <v>-2034</v>
+        <v>-1702.166666666667</v>
       </c>
       <c r="AE33" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE33</f>
-        <v>2668</v>
+        <v>2502.0833333333335</v>
       </c>
       <c r="AF33" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF33</f>
-        <v>4702</v>
+        <v>4204.25</v>
       </c>
       <c r="AG33" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG33</f>
@@ -13803,27 +13805,27 @@
       </c>
       <c r="AA34" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA34</f>
-        <v>8373</v>
+        <v>7844.1666666666661</v>
       </c>
       <c r="AB34" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB34</f>
-        <v>7.5325450853935276</v>
+        <v>8.0403697014766813</v>
       </c>
       <c r="AC34" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC34</f>
-        <v>0.75325450853935272</v>
+        <v>0.80403697014766817</v>
       </c>
       <c r="AD34" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD34</f>
-        <v>-2066</v>
+        <v>-1537.1666666666661</v>
       </c>
       <c r="AE34" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE34</f>
-        <v>4186.5</v>
+        <v>3922.083333333333</v>
       </c>
       <c r="AF34" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF34</f>
-        <v>6252.5</v>
+        <v>5459.2499999999991</v>
       </c>
       <c r="AG34" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG34</f>
@@ -13931,7 +13933,7 @@
       </c>
       <c r="AA35" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA35</f>
-        <v>100</v>
+        <v>83.333333333333343</v>
       </c>
       <c r="AB35" s="34">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB35</f>
@@ -13943,15 +13945,15 @@
       </c>
       <c r="AD35" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD35</f>
-        <v>-100</v>
+        <v>-83.333333333333343</v>
       </c>
       <c r="AE35" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE35</f>
-        <v>50</v>
+        <v>41.666666666666671</v>
       </c>
       <c r="AF35" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF35</f>
-        <v>150</v>
+        <v>125.00000000000001</v>
       </c>
       <c r="AG35" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG35</f>
@@ -14059,27 +14061,27 @@
       </c>
       <c r="AA36" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA36</f>
-        <v>1682</v>
+        <v>1420</v>
       </c>
       <c r="AB36" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB36</f>
-        <v>3.2282996432818076</v>
+        <v>3.823943661971831</v>
       </c>
       <c r="AC36" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC36</f>
-        <v>0.32282996432818073</v>
+        <v>0.38239436619718309</v>
       </c>
       <c r="AD36" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD36</f>
-        <v>-1139</v>
+        <v>-877</v>
       </c>
       <c r="AE36" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE36</f>
-        <v>841</v>
+        <v>710</v>
       </c>
       <c r="AF36" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF36</f>
-        <v>1980</v>
+        <v>1587</v>
       </c>
       <c r="AG36" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG36</f>
@@ -14187,27 +14189,27 @@
       </c>
       <c r="AA37" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA37</f>
-        <v>7434</v>
+        <v>6635.8333333333339</v>
       </c>
       <c r="AB37" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB37</f>
-        <v>13.677697067527577</v>
+        <v>15.322868265728996</v>
       </c>
       <c r="AC37" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC37</f>
-        <v>1.3677697067527577</v>
+        <v>1.5322868265728995</v>
       </c>
       <c r="AD37" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD37</f>
-        <v>2734</v>
+        <v>3532.1666666666661</v>
       </c>
       <c r="AE37" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE37</f>
-        <v>3717</v>
+        <v>3317.916666666667</v>
       </c>
       <c r="AF37" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF37</f>
-        <v>983</v>
+        <v>-214.24999999999909</v>
       </c>
       <c r="AG37" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG37</f>
@@ -14315,27 +14317,27 @@
       </c>
       <c r="AA38" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA38</f>
-        <v>12107</v>
+        <v>10833.333333333332</v>
       </c>
       <c r="AB38" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB38</f>
-        <v>8.1423969604361108</v>
+        <v>9.0996923076923082</v>
       </c>
       <c r="AC38" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC38</f>
-        <v>0.81423969604361113</v>
+        <v>0.90996923076923086</v>
       </c>
       <c r="AD38" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD38</f>
-        <v>-2249</v>
+        <v>-975.33333333333212</v>
       </c>
       <c r="AE38" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE38</f>
-        <v>6053.5</v>
+        <v>5416.6666666666661</v>
       </c>
       <c r="AF38" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF38</f>
-        <v>8302.5</v>
+        <v>6391.9999999999982</v>
       </c>
       <c r="AG38" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG38</f>
@@ -14443,27 +14445,27 @@
       </c>
       <c r="AA39" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA39</f>
-        <v>5311</v>
+        <v>4935</v>
       </c>
       <c r="AB39" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB39</f>
-        <v>3.7017510826586331</v>
+        <v>3.9837892603850049</v>
       </c>
       <c r="AC39" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC39</f>
-        <v>0.37017510826586331</v>
+        <v>0.3983789260385005</v>
       </c>
       <c r="AD39" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD39</f>
-        <v>-3345</v>
+        <v>-2969</v>
       </c>
       <c r="AE39" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE39</f>
-        <v>2655.5</v>
+        <v>2467.5</v>
       </c>
       <c r="AF39" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF39</f>
-        <v>6000.5</v>
+        <v>5436.5</v>
       </c>
       <c r="AG39" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG39</f>
@@ -14571,27 +14573,27 @@
       </c>
       <c r="AA40" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA40</f>
-        <v>3730</v>
+        <v>3581.666666666667</v>
       </c>
       <c r="AB40" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB40</f>
-        <v>12.187667560321715</v>
+        <v>12.692415076779897</v>
       </c>
       <c r="AC40" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC40</f>
-        <v>1.2187667560321715</v>
+        <v>1.2692415076779897</v>
       </c>
       <c r="AD40" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD40</f>
-        <v>816</v>
+        <v>964.33333333333303</v>
       </c>
       <c r="AE40" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE40</f>
-        <v>1865</v>
+        <v>1790.8333333333335</v>
       </c>
       <c r="AF40" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF40</f>
-        <v>1049</v>
+        <v>826.50000000000045</v>
       </c>
       <c r="AG40" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG40</f>
@@ -14955,27 +14957,27 @@
       </c>
       <c r="AA43" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA43</f>
-        <v>47</v>
+        <v>1317.5</v>
       </c>
       <c r="AB43" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB43</f>
-        <v>140.63829787234042</v>
+        <v>5.0170777988614796</v>
       </c>
       <c r="AC43" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC43</f>
-        <v>14.063829787234043</v>
+        <v>0.50170777988614801</v>
       </c>
       <c r="AD43" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD43</f>
-        <v>614</v>
+        <v>-656.5</v>
       </c>
       <c r="AE43" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE43</f>
-        <v>23.5</v>
+        <v>658.75</v>
       </c>
       <c r="AF43" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF43</f>
-        <v>-590.5</v>
+        <v>1315.25</v>
       </c>
       <c r="AG43" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG43</f>
@@ -15083,27 +15085,27 @@
       </c>
       <c r="AA44" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA44</f>
-        <v>46</v>
+        <v>1275.8333333333333</v>
       </c>
       <c r="AB44" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB44</f>
-        <v>246.73913043478262</v>
+        <v>8.8961463096015674</v>
       </c>
       <c r="AC44" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC44</f>
-        <v>24.673913043478262</v>
+        <v>0.8896146309601568</v>
       </c>
       <c r="AD44" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD44</f>
-        <v>1089</v>
+        <v>-140.83333333333326</v>
       </c>
       <c r="AE44" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE44</f>
-        <v>23</v>
+        <v>637.91666666666663</v>
       </c>
       <c r="AF44" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF44</f>
-        <v>-1066</v>
+        <v>778.74999999999989</v>
       </c>
       <c r="AG44" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG44</f>
@@ -15211,27 +15213,27 @@
       </c>
       <c r="AA45" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA45</f>
-        <v>1424</v>
+        <v>5877.5</v>
       </c>
       <c r="AB45" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB45</f>
-        <v>29.157303370786515</v>
+        <v>7.0642279880901748</v>
       </c>
       <c r="AC45" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC45</f>
-        <v>2.9157303370786516</v>
+        <v>0.70642279880901748</v>
       </c>
       <c r="AD45" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD45</f>
-        <v>2728</v>
+        <v>-1725.5</v>
       </c>
       <c r="AE45" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE45</f>
-        <v>712</v>
+        <v>2938.75</v>
       </c>
       <c r="AF45" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF45</f>
-        <v>-2016</v>
+        <v>4664.25</v>
       </c>
       <c r="AG45" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG45</f>
@@ -15339,27 +15341,27 @@
       </c>
       <c r="AA46" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA46</f>
-        <v>1357</v>
+        <v>6554.1666666666661</v>
       </c>
       <c r="AB46" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB46</f>
-        <v>63.021370670596909</v>
+        <v>13.048188175460904</v>
       </c>
       <c r="AC46" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC46</f>
-        <v>6.3021370670596903</v>
+        <v>1.3048188175460904</v>
       </c>
       <c r="AD46" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD46</f>
-        <v>7195</v>
+        <v>1997.8333333333339</v>
       </c>
       <c r="AE46" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE46</f>
-        <v>678.5</v>
+        <v>3277.083333333333</v>
       </c>
       <c r="AF46" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF46</f>
-        <v>-6516.5</v>
+        <v>1279.2499999999991</v>
       </c>
       <c r="AG46" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG46</f>
@@ -15467,27 +15469,27 @@
       </c>
       <c r="AA47" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA47</f>
-        <v>6422</v>
+        <v>8187.5</v>
       </c>
       <c r="AB47" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB47</f>
-        <v>10.484272812208035</v>
+        <v>8.2235114503816789</v>
       </c>
       <c r="AC47" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC47</f>
-        <v>1.0484272812208035</v>
+        <v>0.82235114503816797</v>
       </c>
       <c r="AD47" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD47</f>
-        <v>311</v>
+        <v>-1454.5</v>
       </c>
       <c r="AE47" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE47</f>
-        <v>3211</v>
+        <v>4093.75</v>
       </c>
       <c r="AF47" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF47</f>
-        <v>2900</v>
+        <v>5548.25</v>
       </c>
       <c r="AG47" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG47</f>
@@ -15595,27 +15597,27 @@
       </c>
       <c r="AA48" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA48</f>
-        <v>7168</v>
+        <v>5705</v>
       </c>
       <c r="AB48" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB48</f>
-        <v>7.2921316964285721</v>
+        <v>9.1621384750219104</v>
       </c>
       <c r="AC48" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC48</f>
-        <v>0.7292131696428571</v>
+        <v>0.91621384750219104</v>
       </c>
       <c r="AD48" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD48</f>
-        <v>-1941</v>
+        <v>-478</v>
       </c>
       <c r="AE48" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE48</f>
-        <v>3584</v>
+        <v>2852.5</v>
       </c>
       <c r="AF48" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF48</f>
-        <v>5525</v>
+        <v>3330.5</v>
       </c>
       <c r="AG48" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG48</f>
@@ -15723,27 +15725,27 @@
       </c>
       <c r="AA49" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA49</f>
-        <v>476</v>
+        <v>21.666666666666664</v>
       </c>
       <c r="AB49" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB49</f>
-        <v>0.25210084033613445</v>
+        <v>5.5384615384615392</v>
       </c>
       <c r="AC49" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC49</f>
-        <v>2.5210084033613446E-2</v>
+        <v>0.55384615384615388</v>
       </c>
       <c r="AD49" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD49</f>
-        <v>-464</v>
+        <v>-9.6666666666666643</v>
       </c>
       <c r="AE49" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE49</f>
-        <v>238</v>
+        <v>10.833333333333332</v>
       </c>
       <c r="AF49" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF49</f>
-        <v>702</v>
+        <v>20.499999999999996</v>
       </c>
       <c r="AG49" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG49</f>
@@ -15851,7 +15853,7 @@
       </c>
       <c r="AA50" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA50</f>
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="AB50" s="25">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB50</f>
@@ -15863,15 +15865,15 @@
       </c>
       <c r="AD50" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD50</f>
-        <v>-601</v>
+        <v>11</v>
       </c>
       <c r="AE50" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE50</f>
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="AF50" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF50</f>
-        <v>907</v>
+        <v>-11</v>
       </c>
       <c r="AG50" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG50</f>
@@ -15979,27 +15981,27 @@
       </c>
       <c r="AA51" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA51</f>
-        <v>8941</v>
+        <v>248.33333333333331</v>
       </c>
       <c r="AB51" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB51</f>
-        <v>4.8093054468180289E-2</v>
+        <v>1.731543624161074</v>
       </c>
       <c r="AC51" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC51</f>
-        <v>4.8093054468180295E-3</v>
+        <v>0.1731543624161074</v>
       </c>
       <c r="AD51" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD51</f>
-        <v>-8898</v>
+        <v>-205.33333333333331</v>
       </c>
       <c r="AE51" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE51</f>
-        <v>4470.5</v>
+        <v>124.16666666666666</v>
       </c>
       <c r="AF51" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF51</f>
-        <v>13368.5</v>
+        <v>329.5</v>
       </c>
       <c r="AG51" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG51</f>
@@ -16235,27 +16237,27 @@
       </c>
       <c r="AA53" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA53</f>
-        <v>191</v>
+        <v>593.33333333333337</v>
       </c>
       <c r="AB53" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB53</f>
-        <v>0.20942408376963348</v>
+        <v>6.741573033707865E-2</v>
       </c>
       <c r="AC53" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC53</f>
-        <v>2.0942408376963352E-2</v>
+        <v>6.7415730337078645E-3</v>
       </c>
       <c r="AD53" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD53</f>
-        <v>-187</v>
+        <v>-589.33333333333337</v>
       </c>
       <c r="AE53" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE53</f>
-        <v>95.5</v>
+        <v>296.66666666666669</v>
       </c>
       <c r="AF53" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF53</f>
-        <v>282.5</v>
+        <v>886</v>
       </c>
       <c r="AG53" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG53</f>
@@ -16363,27 +16365,27 @@
       </c>
       <c r="AA54" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA54</f>
-        <v>6086</v>
+        <v>2998.333333333333</v>
       </c>
       <c r="AB54" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB54</f>
-        <v>37.090042720999016</v>
+        <v>75.285158421345201</v>
       </c>
       <c r="AC54" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC54</f>
-        <v>3.7090042720999015</v>
+        <v>7.52851584213452</v>
       </c>
       <c r="AD54" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD54</f>
-        <v>16487</v>
+        <v>19574.666666666668</v>
       </c>
       <c r="AE54" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE54</f>
-        <v>3043</v>
+        <v>1499.1666666666665</v>
       </c>
       <c r="AF54" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF54</f>
-        <v>-13444</v>
+        <v>-18075.5</v>
       </c>
       <c r="AG54" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG54</f>
@@ -16491,27 +16493,27 @@
       </c>
       <c r="AA55" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA55</f>
-        <v>712</v>
+        <v>5197.5</v>
       </c>
       <c r="AB55" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB55</f>
-        <v>410.5196629213483</v>
+        <v>56.236652236652233</v>
       </c>
       <c r="AC55" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC55</f>
-        <v>41.051966292134829</v>
+        <v>5.623665223665224</v>
       </c>
       <c r="AD55" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD55</f>
-        <v>28517</v>
+        <v>24031.5</v>
       </c>
       <c r="AE55" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE55</f>
-        <v>356</v>
+        <v>2598.75</v>
       </c>
       <c r="AF55" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF55</f>
-        <v>-28161</v>
+        <v>-21432.75</v>
       </c>
       <c r="AG55" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG55</f>
@@ -16619,27 +16621,27 @@
       </c>
       <c r="AA56" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA56</f>
-        <v>3447</v>
+        <v>3131.666666666667</v>
       </c>
       <c r="AB56" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB56</f>
-        <v>46.852335364084716</v>
+        <v>51.569984034060667</v>
       </c>
       <c r="AC56" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC56</f>
-        <v>4.6852335364084707</v>
+        <v>5.1569984034060665</v>
       </c>
       <c r="AD56" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD56</f>
-        <v>12703</v>
+        <v>13018.333333333332</v>
       </c>
       <c r="AE56" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE56</f>
-        <v>1723.5</v>
+        <v>1565.8333333333335</v>
       </c>
       <c r="AF56" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF56</f>
-        <v>-10979.5</v>
+        <v>-11452.499999999998</v>
       </c>
       <c r="AG56" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG56</f>
@@ -16747,27 +16749,27 @@
       </c>
       <c r="AA57" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA57</f>
-        <v>5851</v>
+        <v>2761.666666666667</v>
       </c>
       <c r="AB57" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB57</f>
-        <v>32.970432404717144</v>
+        <v>69.852745926372961</v>
       </c>
       <c r="AC57" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC57</f>
-        <v>3.297043240471714</v>
+        <v>6.9852745926372952</v>
       </c>
       <c r="AD57" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD57</f>
-        <v>13440</v>
+        <v>16529.333333333332</v>
       </c>
       <c r="AE57" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE57</f>
-        <v>2925.5</v>
+        <v>1380.8333333333335</v>
       </c>
       <c r="AF57" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF57</f>
-        <v>-10514.5</v>
+        <v>-15148.499999999998</v>
       </c>
       <c r="AG57" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG57</f>
@@ -16875,27 +16877,27 @@
       </c>
       <c r="AA58" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA58</f>
-        <v>3575</v>
+        <v>461.66666666666663</v>
       </c>
       <c r="AB58" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB58</f>
-        <v>2</v>
+        <v>15.48736462093863</v>
       </c>
       <c r="AC58" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC58</f>
-        <v>0.2</v>
+        <v>1.5487364620938628</v>
       </c>
       <c r="AD58" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD58</f>
-        <v>-2860</v>
+        <v>253.33333333333337</v>
       </c>
       <c r="AE58" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE58</f>
-        <v>1787.5</v>
+        <v>230.83333333333331</v>
       </c>
       <c r="AF58" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF58</f>
-        <v>4647.5</v>
+        <v>-22.500000000000057</v>
       </c>
       <c r="AG58" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG58</f>
@@ -17003,27 +17005,27 @@
       </c>
       <c r="AA59" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA59</f>
-        <v>3107</v>
+        <v>896.66666666666674</v>
       </c>
       <c r="AB59" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB59</f>
-        <v>1.2423559703894433</v>
+        <v>4.3048327137546467</v>
       </c>
       <c r="AC59" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC59</f>
-        <v>0.12423559703894432</v>
+        <v>0.43048327137546466</v>
       </c>
       <c r="AD59" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD59</f>
-        <v>-2721</v>
+        <v>-510.66666666666674</v>
       </c>
       <c r="AE59" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE59</f>
-        <v>1553.5</v>
+        <v>448.33333333333337</v>
       </c>
       <c r="AF59" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF59</f>
-        <v>4274.5</v>
+        <v>959.00000000000011</v>
       </c>
       <c r="AG59" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG59</f>
@@ -17131,27 +17133,27 @@
       </c>
       <c r="AA60" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA60</f>
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AB60" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB60</f>
-        <v>5.8893280632411065</v>
+        <v>5.8431372549019605</v>
       </c>
       <c r="AC60" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC60</f>
-        <v>0.58893280632411071</v>
+        <v>0.58431372549019611</v>
       </c>
       <c r="AD60" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD60</f>
-        <v>-208</v>
+        <v>-212</v>
       </c>
       <c r="AE60" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE60</f>
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AF60" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF60</f>
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="AG60" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG60</f>
@@ -17259,27 +17261,27 @@
       </c>
       <c r="AA61" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA61</f>
-        <v>1021</v>
+        <v>430</v>
       </c>
       <c r="AB61" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB61</f>
-        <v>1.4299706170421156</v>
+        <v>3.3953488372093021</v>
       </c>
       <c r="AC61" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC61</f>
-        <v>0.14299706170421156</v>
+        <v>0.33953488372093021</v>
       </c>
       <c r="AD61" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD61</f>
-        <v>-875</v>
+        <v>-284</v>
       </c>
       <c r="AE61" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE61</f>
-        <v>510.5</v>
+        <v>215</v>
       </c>
       <c r="AF61" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF61</f>
-        <v>1385.5</v>
+        <v>499</v>
       </c>
       <c r="AG61" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG61</f>
@@ -17319,7 +17321,7 @@
       </c>
       <c r="AF62" s="44">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF62</f>
-        <v>180594</v>
+        <v>135034.5</v>
       </c>
     </row>
     <row r="63" spans="2:33" x14ac:dyDescent="0.25">
@@ -17328,10 +17330,10 @@
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
-      <c r="E63" s="67" t="s">
+      <c r="E63" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="F63" s="67"/>
+      <c r="F63" s="64"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -17356,10 +17358,10 @@
       <c r="AB63" s="42"/>
     </row>
     <row r="64" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B64" s="63" t="s">
+      <c r="B64" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="63"/>
+      <c r="C64" s="65"/>
       <c r="D64" s="48">
         <f>SUM(F13:F61)</f>
         <v>144936.54999999999</v>
@@ -17504,19 +17506,19 @@
       <c r="AB67" s="42"/>
     </row>
     <row r="68" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B68" s="63" t="s">
+      <c r="B68" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="C68" s="63"/>
+      <c r="C68" s="65"/>
       <c r="D68" s="50">
         <f>SUM(Z13:Z61)</f>
         <v>421177.93000000017</v>
       </c>
-      <c r="E68" s="64">
+      <c r="E68" s="66">
         <f>D68*100/D68</f>
         <v>100</v>
       </c>
-      <c r="F68" s="64"/>
+      <c r="F68" s="66"/>
       <c r="G68" s="51"/>
       <c r="H68" s="51"/>
       <c r="I68" s="51"/>
@@ -17601,10 +17603,10 @@
       <c r="AB70" s="42"/>
     </row>
     <row r="71" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B71" s="63" t="s">
+      <c r="B71" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="63"/>
+      <c r="C71" s="65"/>
       <c r="D71" s="3">
         <f>SUM(E13:E61)</f>
         <v>112990</v>
@@ -17719,11 +17721,11 @@
         <f>SUM(T13:T61)</f>
         <v>36961</v>
       </c>
-      <c r="E74" s="62">
+      <c r="E74" s="67">
         <f>D74*100/D75</f>
         <v>11.039956032533535</v>
       </c>
-      <c r="F74" s="62"/>
+      <c r="F74" s="67"/>
       <c r="G74" s="56"/>
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
@@ -17748,19 +17750,19 @@
       <c r="AB74" s="42"/>
     </row>
     <row r="75" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B75" s="63" t="s">
+      <c r="B75" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="63"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="55">
         <f>SUM(Y13:Y61)</f>
         <v>334793</v>
       </c>
-      <c r="E75" s="62">
+      <c r="E75" s="67">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="62"/>
+      <c r="F75" s="67"/>
       <c r="G75" s="56"/>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
@@ -18521,23 +18523,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="E71:F71"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="B1:Z6"/>
     <mergeCell ref="AA1:AG6"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G61">
     <cfRule type="colorScale" priority="5">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED352C4B-DD2C-4B50-A022-F18BAA4EC641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEE23FB-3A6A-4BF0-97FE-D98D3D3BDDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -841,6 +841,15 @@
     <xf numFmtId="2" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -849,15 +858,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5639,6 +5639,8 @@
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 19-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 20-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -5766,22 +5768,22 @@
             <v>13606.800000000001</v>
           </cell>
           <cell r="AA13">
-            <v>11620.833333333332</v>
+            <v>10726.923076923076</v>
           </cell>
           <cell r="AB13">
-            <v>8.6095374686267476</v>
+            <v>9.326998924345645</v>
           </cell>
           <cell r="AC13">
-            <v>0.8609537468626749</v>
+            <v>0.93269989243456441</v>
           </cell>
           <cell r="AD13">
-            <v>-1615.8333333333321</v>
+            <v>-721.92307692307622</v>
           </cell>
           <cell r="AE13">
-            <v>5810.4166666666661</v>
+            <v>5363.4615384615381</v>
           </cell>
           <cell r="AF13">
-            <v>7426.2499999999982</v>
+            <v>6085.3846153846143</v>
           </cell>
           <cell r="AG13">
             <v>125.0625</v>
@@ -5858,22 +5860,22 @@
             <v>888.81000000000006</v>
           </cell>
           <cell r="AA14">
-            <v>830.83333333333326</v>
+            <v>766.92307692307691</v>
           </cell>
           <cell r="AB14">
-            <v>6.7281845536609834</v>
+            <v>7.2888665997993982</v>
           </cell>
           <cell r="AC14">
-            <v>0.67281845536609841</v>
+            <v>0.72888665997993984</v>
           </cell>
           <cell r="AD14">
-            <v>-271.83333333333326</v>
+            <v>-207.92307692307691</v>
           </cell>
           <cell r="AE14">
-            <v>415.41666666666663</v>
+            <v>383.46153846153845</v>
           </cell>
           <cell r="AF14">
-            <v>687.24999999999989</v>
+            <v>591.38461538461536</v>
           </cell>
           <cell r="AG14">
             <v>6.9874999999999998</v>
@@ -5950,22 +5952,22 @@
             <v>6966.9599999999991</v>
           </cell>
           <cell r="AA15">
-            <v>4660.833333333333</v>
+            <v>4302.3076923076924</v>
           </cell>
           <cell r="AB15">
-            <v>7.363490076881817</v>
+            <v>7.9771142499553012</v>
           </cell>
           <cell r="AC15">
-            <v>0.73634900768818168</v>
+            <v>0.79771142499553016</v>
           </cell>
           <cell r="AD15">
-            <v>-1228.833333333333</v>
+            <v>-870.30769230769238</v>
           </cell>
           <cell r="AE15">
-            <v>2330.4166666666665</v>
+            <v>2151.1538461538462</v>
           </cell>
           <cell r="AF15">
-            <v>3559.2499999999995</v>
+            <v>3021.4615384615386</v>
           </cell>
           <cell r="AG15">
             <v>57.2</v>
@@ -6042,22 +6044,22 @@
             <v>743.66</v>
           </cell>
           <cell r="AA16">
-            <v>908.33333333333326</v>
+            <v>838.46153846153834</v>
           </cell>
           <cell r="AB16">
-            <v>2.2678899082568806</v>
+            <v>2.4568807339449545</v>
           </cell>
           <cell r="AC16">
-            <v>0.2267889908256881</v>
+            <v>0.24568807339449544</v>
           </cell>
           <cell r="AD16">
-            <v>-702.33333333333326</v>
+            <v>-632.46153846153834</v>
           </cell>
           <cell r="AE16">
-            <v>454.16666666666663</v>
+            <v>419.23076923076917</v>
           </cell>
           <cell r="AF16">
-            <v>1156.5</v>
+            <v>1051.6923076923076</v>
           </cell>
           <cell r="AG16">
             <v>7.3571428571428568</v>
@@ -6134,22 +6136,22 @@
             <v>1861.36</v>
           </cell>
           <cell r="AA17">
-            <v>94.166666666666657</v>
+            <v>86.92307692307692</v>
           </cell>
           <cell r="AB17">
-            <v>22.513274336283189</v>
+            <v>24.389380530973455</v>
           </cell>
           <cell r="AC17">
-            <v>2.2513274336283189</v>
+            <v>2.438938053097345</v>
           </cell>
           <cell r="AD17">
-            <v>117.83333333333334</v>
+            <v>125.07692307692308</v>
           </cell>
           <cell r="AE17">
-            <v>47.083333333333329</v>
+            <v>43.46153846153846</v>
           </cell>
           <cell r="AF17">
-            <v>-70.750000000000014</v>
+            <v>-81.615384615384613</v>
           </cell>
           <cell r="AG17">
             <v>17.666666666666668</v>
@@ -6226,22 +6228,22 @@
             <v>5277.51</v>
           </cell>
           <cell r="AA18">
-            <v>13972.5</v>
+            <v>12897.692307692307</v>
           </cell>
           <cell r="AB18">
-            <v>5.9953480050098404</v>
+            <v>6.4949603387606611</v>
           </cell>
           <cell r="AC18">
-            <v>0.59953480050098407</v>
+            <v>0.64949603387606614</v>
           </cell>
           <cell r="AD18">
-            <v>-5595.5</v>
+            <v>-4520.6923076923067</v>
           </cell>
           <cell r="AE18">
-            <v>6986.25</v>
+            <v>6448.8461538461534</v>
           </cell>
           <cell r="AF18">
-            <v>12581.75</v>
+            <v>10969.538461538461</v>
           </cell>
           <cell r="AG18">
             <v>139.61666666666667</v>
@@ -6318,22 +6320,22 @@
             <v>949.41</v>
           </cell>
           <cell r="AA19">
-            <v>1384.1666666666665</v>
+            <v>1277.6923076923076</v>
           </cell>
           <cell r="AB19">
-            <v>10.887417218543048</v>
+            <v>11.794701986754967</v>
           </cell>
           <cell r="AC19">
-            <v>1.0887417218543047</v>
+            <v>1.1794701986754967</v>
           </cell>
           <cell r="AD19">
-            <v>122.83333333333348</v>
+            <v>229.30769230769238</v>
           </cell>
           <cell r="AE19">
-            <v>692.08333333333326</v>
+            <v>638.84615384615381</v>
           </cell>
           <cell r="AF19">
-            <v>569.24999999999977</v>
+            <v>409.53846153846143</v>
           </cell>
           <cell r="AG19">
             <v>25.116666666666667</v>
@@ -6410,22 +6412,22 @@
             <v>2498.58</v>
           </cell>
           <cell r="AA20">
-            <v>3075.833333333333</v>
+            <v>2839.2307692307691</v>
           </cell>
           <cell r="AB20">
-            <v>12.894066648604715</v>
+            <v>13.968572202655109</v>
           </cell>
           <cell r="AC20">
-            <v>1.2894066648604716</v>
+            <v>1.3968572202655107</v>
           </cell>
           <cell r="AD20">
-            <v>890.16666666666697</v>
+            <v>1126.7692307692309</v>
           </cell>
           <cell r="AE20">
-            <v>1537.9166666666665</v>
+            <v>1419.6153846153845</v>
           </cell>
           <cell r="AF20">
-            <v>647.74999999999955</v>
+            <v>292.84615384615358</v>
           </cell>
           <cell r="AG20">
             <v>66.099999999999994</v>
@@ -6502,22 +6504,22 @@
             <v>8325.42</v>
           </cell>
           <cell r="AA21">
-            <v>7126.6666666666661</v>
+            <v>6578.4615384615381</v>
           </cell>
           <cell r="AB21">
-            <v>10.717492984097287</v>
+            <v>11.610617399438729</v>
           </cell>
           <cell r="AC21">
-            <v>1.0717492984097288</v>
+            <v>1.1610617399438727</v>
           </cell>
           <cell r="AD21">
-            <v>511.33333333333394</v>
+            <v>1059.5384615384619</v>
           </cell>
           <cell r="AE21">
-            <v>3563.333333333333</v>
+            <v>3289.2307692307691</v>
           </cell>
           <cell r="AF21">
-            <v>3051.9999999999991</v>
+            <v>2229.6923076923072</v>
           </cell>
           <cell r="AG21">
             <v>141.44444444444446</v>
@@ -6594,22 +6596,22 @@
             <v>4099.4900000000007</v>
           </cell>
           <cell r="AA22">
-            <v>3344.166666666667</v>
+            <v>3086.9230769230767</v>
           </cell>
           <cell r="AB22">
-            <v>11.246449040617991</v>
+            <v>12.183653127336157</v>
           </cell>
           <cell r="AC22">
-            <v>1.124644904061799</v>
+            <v>1.2183653127336158</v>
           </cell>
           <cell r="AD22">
-            <v>416.83333333333303</v>
+            <v>674.07692307692332</v>
           </cell>
           <cell r="AE22">
-            <v>1672.0833333333335</v>
+            <v>1543.4615384615383</v>
           </cell>
           <cell r="AF22">
-            <v>1255.2500000000005</v>
+            <v>869.38461538461502</v>
           </cell>
           <cell r="AG22">
             <v>69.648148148148152</v>
@@ -6686,22 +6688,22 @@
             <v>38473.719999999994</v>
           </cell>
           <cell r="AA23">
-            <v>36112.5</v>
+            <v>33334.615384615383</v>
           </cell>
           <cell r="AB23">
-            <v>9.1843544479058501</v>
+            <v>9.9497173185646712</v>
           </cell>
           <cell r="AC23">
-            <v>0.91843544479058503</v>
+            <v>0.99497173185646715</v>
           </cell>
           <cell r="AD23">
-            <v>-2945.5</v>
+            <v>-167.61538461538294</v>
           </cell>
           <cell r="AE23">
-            <v>18056.25</v>
+            <v>16667.307692307691</v>
           </cell>
           <cell r="AF23">
-            <v>21001.75</v>
+            <v>16834.923076923074</v>
           </cell>
           <cell r="AG23">
             <v>614.2037037037037</v>
@@ -6778,22 +6780,22 @@
             <v>29054.519999999997</v>
           </cell>
           <cell r="AA24">
-            <v>23759.166666666664</v>
+            <v>21931.538461538461</v>
           </cell>
           <cell r="AB24">
-            <v>10.542036407000808</v>
+            <v>11.42053944091754</v>
           </cell>
           <cell r="AC24">
-            <v>1.0542036407000808</v>
+            <v>1.1420539440917541</v>
           </cell>
           <cell r="AD24">
-            <v>1287.8333333333358</v>
+            <v>3115.461538461539</v>
           </cell>
           <cell r="AE24">
-            <v>11879.583333333332</v>
+            <v>10965.76923076923</v>
           </cell>
           <cell r="AF24">
-            <v>10591.749999999996</v>
+            <v>7850.3076923076915</v>
           </cell>
           <cell r="AG24">
             <v>463.83333333333331</v>
@@ -6870,22 +6872,22 @@
             <v>30040.519999999997</v>
           </cell>
           <cell r="AA25">
-            <v>22936.666666666664</v>
+            <v>21172.307692307691</v>
           </cell>
           <cell r="AB25">
-            <v>11.290655427990119</v>
+            <v>12.231543380322629</v>
           </cell>
           <cell r="AC25">
-            <v>1.1290655427990119</v>
+            <v>1.2231543380322627</v>
           </cell>
           <cell r="AD25">
-            <v>2960.3333333333358</v>
+            <v>4724.6923076923085</v>
           </cell>
           <cell r="AE25">
-            <v>11468.333333333332</v>
+            <v>10586.153846153846</v>
           </cell>
           <cell r="AF25">
-            <v>8507.9999999999964</v>
+            <v>5861.4615384615372</v>
           </cell>
           <cell r="AG25">
             <v>479.57407407407408</v>
@@ -6962,22 +6964,22 @@
             <v>34369.64</v>
           </cell>
           <cell r="AA26">
-            <v>27655.833333333336</v>
+            <v>25528.461538461539</v>
           </cell>
           <cell r="AB26">
-            <v>10.713472142706481</v>
+            <v>11.606261487932022</v>
           </cell>
           <cell r="AC26">
-            <v>1.0713472142706479</v>
+            <v>1.1606261487932021</v>
           </cell>
           <cell r="AD26">
-            <v>1973.1666666666642</v>
+            <v>4100.538461538461</v>
           </cell>
           <cell r="AE26">
-            <v>13827.916666666668</v>
+            <v>12764.23076923077</v>
           </cell>
           <cell r="AF26">
-            <v>11854.750000000004</v>
+            <v>8663.6923076923085</v>
           </cell>
           <cell r="AG26">
             <v>548.68518518518522</v>
@@ -7054,22 +7056,22 @@
             <v>1758.56</v>
           </cell>
           <cell r="AA27">
-            <v>320.83333333333337</v>
+            <v>301.53846153846155</v>
           </cell>
           <cell r="AB27">
-            <v>47.251948051948048</v>
+            <v>50.275510204081634</v>
           </cell>
           <cell r="AC27">
-            <v>4.7251948051948043</v>
+            <v>5.027551020408163</v>
           </cell>
           <cell r="AD27">
-            <v>1195.1666666666665</v>
+            <v>1214.4615384615386</v>
           </cell>
           <cell r="AE27">
-            <v>160.41666666666669</v>
+            <v>150.76923076923077</v>
           </cell>
           <cell r="AF27">
-            <v>-1034.7499999999998</v>
+            <v>-1063.6923076923078</v>
           </cell>
           <cell r="AG27">
             <v>28.074074074074073</v>
@@ -7101,13 +7103,13 @@
             <v>3519.4399999999996</v>
           </cell>
           <cell r="L28">
-            <v>14.75202593192869</v>
+            <v>15.981361426256079</v>
           </cell>
           <cell r="M28">
-            <v>4524.6666666666661</v>
+            <v>4176.6153846153848</v>
           </cell>
           <cell r="N28">
-            <v>-50.999999999999545</v>
+            <v>186.30769230769238</v>
           </cell>
           <cell r="O28">
             <v>251</v>
@@ -7146,22 +7148,22 @@
             <v>5583.08</v>
           </cell>
           <cell r="AA28">
-            <v>2056.6666666666665</v>
+            <v>1898.4615384615383</v>
           </cell>
           <cell r="AB28">
-            <v>23.401944894651542</v>
+            <v>25.352106969205835</v>
           </cell>
           <cell r="AC28">
-            <v>2.3401944894651541</v>
+            <v>2.5352106969205837</v>
           </cell>
           <cell r="AD28">
-            <v>2756.3333333333335</v>
+            <v>2914.5384615384619</v>
           </cell>
           <cell r="AE28">
-            <v>1028.3333333333333</v>
+            <v>949.23076923076917</v>
           </cell>
           <cell r="AF28">
-            <v>-1728.0000000000002</v>
+            <v>-1965.3076923076928</v>
           </cell>
           <cell r="AG28">
             <v>89.129629629629633</v>
@@ -7193,13 +7195,13 @@
             <v>3309.4799999999996</v>
           </cell>
           <cell r="L29">
-            <v>11.609359104781282</v>
+            <v>12.576805696846389</v>
           </cell>
           <cell r="M29">
-            <v>5406.5</v>
+            <v>4990.6153846153848</v>
           </cell>
           <cell r="N29">
-            <v>-833.25</v>
+            <v>-549.69230769230762</v>
           </cell>
           <cell r="O29">
             <v>236</v>
@@ -7238,22 +7240,22 @@
             <v>5281.48</v>
           </cell>
           <cell r="AA29">
-            <v>2457.5</v>
+            <v>2268.4615384615386</v>
           </cell>
           <cell r="AB29">
-            <v>18.526958290946084</v>
+            <v>20.070871481858255</v>
           </cell>
           <cell r="AC29">
-            <v>1.8526958290946083</v>
+            <v>2.0070871481858257</v>
           </cell>
           <cell r="AD29">
-            <v>2095.5</v>
+            <v>2284.5384615384614</v>
           </cell>
           <cell r="AE29">
-            <v>1228.75</v>
+            <v>1134.2307692307693</v>
           </cell>
           <cell r="AF29">
-            <v>-866.75</v>
+            <v>-1150.3076923076922</v>
           </cell>
           <cell r="AG29">
             <v>84.31481481481481</v>
@@ -7285,13 +7287,13 @@
             <v>3259.6</v>
           </cell>
           <cell r="L30">
-            <v>12.064400715563508</v>
+            <v>13.069767441860465</v>
           </cell>
           <cell r="M30">
-            <v>5124.1666666666661</v>
+            <v>4730</v>
           </cell>
           <cell r="N30">
-            <v>-683.74999999999955</v>
+            <v>-415</v>
           </cell>
           <cell r="O30">
             <v>236</v>
@@ -7330,22 +7332,22 @@
             <v>6992.48</v>
           </cell>
           <cell r="AA30">
-            <v>2329.1666666666665</v>
+            <v>2150</v>
           </cell>
           <cell r="AB30">
-            <v>25.880500894454382</v>
+            <v>28.037209302325582</v>
           </cell>
           <cell r="AC30">
-            <v>2.5880500894454386</v>
+            <v>2.8037209302325583</v>
           </cell>
           <cell r="AD30">
-            <v>3698.8333333333335</v>
+            <v>3878</v>
           </cell>
           <cell r="AE30">
-            <v>1164.5833333333333</v>
+            <v>1075</v>
           </cell>
           <cell r="AF30">
-            <v>-2534.25</v>
+            <v>-2803</v>
           </cell>
           <cell r="AG30">
             <v>111.62962962962963</v>
@@ -7422,22 +7424,22 @@
             <v>5045.2800000000007</v>
           </cell>
           <cell r="AA31">
-            <v>2303.3333333333335</v>
+            <v>2126.1538461538462</v>
           </cell>
           <cell r="AB31">
-            <v>5.9522431259044861</v>
+            <v>6.4482633863965271</v>
           </cell>
           <cell r="AC31">
-            <v>0.59522431259044861</v>
+            <v>0.64482633863965266</v>
           </cell>
           <cell r="AD31">
-            <v>-932.33333333333348</v>
+            <v>-755.15384615384619</v>
           </cell>
           <cell r="AE31">
-            <v>1151.6666666666667</v>
+            <v>1063.0769230769231</v>
           </cell>
           <cell r="AF31">
-            <v>2084</v>
+            <v>1818.2307692307693</v>
           </cell>
           <cell r="AG31">
             <v>85.6875</v>
@@ -7514,22 +7516,22 @@
             <v>3606.4</v>
           </cell>
           <cell r="AA32">
-            <v>1314.1666666666665</v>
+            <v>1213.0769230769231</v>
           </cell>
           <cell r="AB32">
-            <v>7.4571972098922013</v>
+            <v>8.0786303107165498</v>
           </cell>
           <cell r="AC32">
-            <v>0.74571972098922013</v>
+            <v>0.80786303107165502</v>
           </cell>
           <cell r="AD32">
-            <v>-334.16666666666652</v>
+            <v>-233.07692307692309</v>
           </cell>
           <cell r="AE32">
-            <v>657.08333333333326</v>
+            <v>606.53846153846155</v>
           </cell>
           <cell r="AF32">
-            <v>991.24999999999977</v>
+            <v>839.61538461538464</v>
           </cell>
           <cell r="AG32">
             <v>61.25</v>
@@ -7606,22 +7608,22 @@
             <v>13703.300000000001</v>
           </cell>
           <cell r="AA33">
-            <v>5004.166666666667</v>
+            <v>4619.2307692307695</v>
           </cell>
           <cell r="AB33">
-            <v>6.5985012489592005</v>
+            <v>7.1483763530391338</v>
           </cell>
           <cell r="AC33">
-            <v>0.65985012489591999</v>
+            <v>0.71483763530391331</v>
           </cell>
           <cell r="AD33">
-            <v>-1702.166666666667</v>
+            <v>-1317.2307692307695</v>
           </cell>
           <cell r="AE33">
-            <v>2502.0833333333335</v>
+            <v>2309.6153846153848</v>
           </cell>
           <cell r="AF33">
-            <v>4204.25</v>
+            <v>3626.8461538461543</v>
           </cell>
           <cell r="AG33">
             <v>206.375</v>
@@ -7698,22 +7700,22 @@
             <v>26174.050000000003</v>
           </cell>
           <cell r="AA34">
-            <v>7844.1666666666661</v>
+            <v>7240.7692307692305</v>
           </cell>
           <cell r="AB34">
-            <v>8.0403697014766813</v>
+            <v>8.7104005099330717</v>
           </cell>
           <cell r="AC34">
-            <v>0.80403697014766817</v>
+            <v>0.87104005099330717</v>
           </cell>
           <cell r="AD34">
-            <v>-1537.1666666666661</v>
+            <v>-933.76923076923049</v>
           </cell>
           <cell r="AE34">
-            <v>3922.083333333333</v>
+            <v>3620.3846153846152</v>
           </cell>
           <cell r="AF34">
-            <v>5459.2499999999991</v>
+            <v>4554.1538461538457</v>
           </cell>
           <cell r="AG34">
             <v>394.1875</v>
@@ -7790,7 +7792,7 @@
             <v>0</v>
           </cell>
           <cell r="AA35">
-            <v>83.333333333333343</v>
+            <v>76.92307692307692</v>
           </cell>
           <cell r="AB35">
             <v>0</v>
@@ -7799,13 +7801,13 @@
             <v>0</v>
           </cell>
           <cell r="AD35">
-            <v>-83.333333333333343</v>
+            <v>-76.92307692307692</v>
           </cell>
           <cell r="AE35">
-            <v>41.666666666666671</v>
+            <v>38.46153846153846</v>
           </cell>
           <cell r="AF35">
-            <v>125.00000000000001</v>
+            <v>115.38461538461539</v>
           </cell>
           <cell r="AG35">
             <v>0</v>
@@ -7882,22 +7884,22 @@
             <v>2253.4500000000003</v>
           </cell>
           <cell r="AA36">
-            <v>1420</v>
+            <v>1310.7692307692307</v>
           </cell>
           <cell r="AB36">
-            <v>3.823943661971831</v>
+            <v>4.142605633802817</v>
           </cell>
           <cell r="AC36">
-            <v>0.38239436619718309</v>
+            <v>0.41426056338028172</v>
           </cell>
           <cell r="AD36">
-            <v>-877</v>
+            <v>-767.76923076923072</v>
           </cell>
           <cell r="AE36">
-            <v>710</v>
+            <v>655.38461538461536</v>
           </cell>
           <cell r="AF36">
-            <v>1587</v>
+            <v>1423.1538461538462</v>
           </cell>
           <cell r="AG36">
             <v>33.9375</v>
@@ -7974,22 +7976,22 @@
             <v>16573.84</v>
           </cell>
           <cell r="AA37">
-            <v>6635.8333333333339</v>
+            <v>6125.3846153846152</v>
           </cell>
           <cell r="AB37">
-            <v>15.322868265728996</v>
+            <v>16.599773954539746</v>
           </cell>
           <cell r="AC37">
-            <v>1.5322868265728995</v>
+            <v>1.6599773954539747</v>
           </cell>
           <cell r="AD37">
-            <v>3532.1666666666661</v>
+            <v>4042.6153846153848</v>
           </cell>
           <cell r="AE37">
-            <v>3317.916666666667</v>
+            <v>3062.6923076923076</v>
           </cell>
           <cell r="AF37">
-            <v>-214.24999999999909</v>
+            <v>-979.92307692307713</v>
           </cell>
           <cell r="AG37">
             <v>188.2962962962963</v>
@@ -8066,22 +8068,22 @@
             <v>16068.539999999999</v>
           </cell>
           <cell r="AA38">
-            <v>10833.333333333332</v>
+            <v>10000</v>
           </cell>
           <cell r="AB38">
-            <v>9.0996923076923082</v>
+            <v>9.8580000000000005</v>
           </cell>
           <cell r="AC38">
-            <v>0.90996923076923086</v>
+            <v>0.98580000000000001</v>
           </cell>
           <cell r="AD38">
-            <v>-975.33333333333212</v>
+            <v>-142</v>
           </cell>
           <cell r="AE38">
-            <v>5416.6666666666661</v>
+            <v>5000</v>
           </cell>
           <cell r="AF38">
-            <v>6391.9999999999982</v>
+            <v>5142</v>
           </cell>
           <cell r="AG38">
             <v>182.55555555555554</v>
@@ -8158,22 +8160,22 @@
             <v>3204.58</v>
           </cell>
           <cell r="AA39">
-            <v>4935</v>
+            <v>4555.3846153846152</v>
           </cell>
           <cell r="AB39">
-            <v>3.9837892603850049</v>
+            <v>4.3157716987504218</v>
           </cell>
           <cell r="AC39">
-            <v>0.3983789260385005</v>
+            <v>0.43157716987504224</v>
           </cell>
           <cell r="AD39">
-            <v>-2969</v>
+            <v>-2589.3846153846152</v>
           </cell>
           <cell r="AE39">
-            <v>2467.5</v>
+            <v>2277.6923076923076</v>
           </cell>
           <cell r="AF39">
-            <v>5436.5</v>
+            <v>4867.0769230769229</v>
           </cell>
           <cell r="AG39">
             <v>36.407407407407405</v>
@@ -8250,22 +8252,22 @@
             <v>7409.98</v>
           </cell>
           <cell r="AA40">
-            <v>3581.666666666667</v>
+            <v>3306.1538461538466</v>
           </cell>
           <cell r="AB40">
-            <v>12.692415076779897</v>
+            <v>13.750116333178221</v>
           </cell>
           <cell r="AC40">
-            <v>1.2692415076779897</v>
+            <v>1.3750116333178219</v>
           </cell>
           <cell r="AD40">
-            <v>964.33333333333303</v>
+            <v>1239.8461538461534</v>
           </cell>
           <cell r="AE40">
-            <v>1790.8333333333335</v>
+            <v>1653.0769230769233</v>
           </cell>
           <cell r="AF40">
-            <v>826.50000000000045</v>
+            <v>413.23076923076997</v>
           </cell>
           <cell r="AG40">
             <v>84.18518518518519</v>
@@ -8526,22 +8528,22 @@
             <v>4065.15</v>
           </cell>
           <cell r="AA43">
-            <v>1317.5</v>
+            <v>1216.1538461538462</v>
           </cell>
           <cell r="AB43">
-            <v>5.0170777988614796</v>
+            <v>5.4351676154332704</v>
           </cell>
           <cell r="AC43">
-            <v>0.50170777988614801</v>
+            <v>0.54351676154332695</v>
           </cell>
           <cell r="AD43">
-            <v>-656.5</v>
+            <v>-555.15384615384619</v>
           </cell>
           <cell r="AE43">
-            <v>658.75</v>
+            <v>608.07692307692309</v>
           </cell>
           <cell r="AF43">
-            <v>1315.25</v>
+            <v>1163.2307692307693</v>
           </cell>
           <cell r="AG43">
             <v>12.24074074074074</v>
@@ -8618,22 +8620,22 @@
             <v>6980.25</v>
           </cell>
           <cell r="AA44">
-            <v>1275.8333333333333</v>
+            <v>1177.6923076923076</v>
           </cell>
           <cell r="AB44">
-            <v>8.8961463096015674</v>
+            <v>9.6374918354016987</v>
           </cell>
           <cell r="AC44">
-            <v>0.8896146309601568</v>
+            <v>0.96374918354016992</v>
           </cell>
           <cell r="AD44">
-            <v>-140.83333333333326</v>
+            <v>-42.692307692307622</v>
           </cell>
           <cell r="AE44">
-            <v>637.91666666666663</v>
+            <v>588.84615384615381</v>
           </cell>
           <cell r="AF44">
-            <v>778.74999999999989</v>
+            <v>631.53846153846143</v>
           </cell>
           <cell r="AG44">
             <v>21.018518518518519</v>
@@ -8710,22 +8712,22 @@
             <v>4816.32</v>
           </cell>
           <cell r="AA45">
-            <v>5877.5</v>
+            <v>5425.3846153846152</v>
           </cell>
           <cell r="AB45">
-            <v>7.0642279880901748</v>
+            <v>7.6529136537643554</v>
           </cell>
           <cell r="AC45">
-            <v>0.70642279880901748</v>
+            <v>0.76529136537643561</v>
           </cell>
           <cell r="AD45">
-            <v>-1725.5</v>
+            <v>-1273.3846153846152</v>
           </cell>
           <cell r="AE45">
-            <v>2938.75</v>
+            <v>2712.6923076923076</v>
           </cell>
           <cell r="AF45">
-            <v>4664.25</v>
+            <v>3986.0769230769229</v>
           </cell>
           <cell r="AG45">
             <v>76.888888888888886</v>
@@ -8802,22 +8804,22 @@
             <v>9920.32</v>
           </cell>
           <cell r="AA46">
-            <v>6554.1666666666661</v>
+            <v>6050</v>
           </cell>
           <cell r="AB46">
-            <v>13.048188175460904</v>
+            <v>14.135537190082644</v>
           </cell>
           <cell r="AC46">
-            <v>1.3048188175460904</v>
+            <v>1.4135537190082645</v>
           </cell>
           <cell r="AD46">
-            <v>1997.8333333333339</v>
+            <v>2502</v>
           </cell>
           <cell r="AE46">
-            <v>3277.083333333333</v>
+            <v>3025</v>
           </cell>
           <cell r="AF46">
-            <v>1279.2499999999991</v>
+            <v>523</v>
           </cell>
           <cell r="AG46">
             <v>158.37037037037038</v>
@@ -8894,22 +8896,22 @@
             <v>7810.28</v>
           </cell>
           <cell r="AA47">
-            <v>8187.5</v>
+            <v>7557.6923076923067</v>
           </cell>
           <cell r="AB47">
-            <v>8.2235114503816789</v>
+            <v>8.9088040712468199</v>
           </cell>
           <cell r="AC47">
-            <v>0.82235114503816797</v>
+            <v>0.89088040712468208</v>
           </cell>
           <cell r="AD47">
-            <v>-1454.5</v>
+            <v>-824.69230769230671</v>
           </cell>
           <cell r="AE47">
-            <v>4093.75</v>
+            <v>3778.8461538461534</v>
           </cell>
           <cell r="AF47">
-            <v>5548.25</v>
+            <v>4603.5384615384601</v>
           </cell>
           <cell r="AG47">
             <v>124.68518518518519</v>
@@ -8986,22 +8988,22 @@
             <v>6063.32</v>
           </cell>
           <cell r="AA48">
-            <v>5705</v>
+            <v>5266.1538461538466</v>
           </cell>
           <cell r="AB48">
-            <v>9.1621384750219104</v>
+            <v>9.9256500146070685</v>
           </cell>
           <cell r="AC48">
-            <v>0.91621384750219104</v>
+            <v>0.99256500146070692</v>
           </cell>
           <cell r="AD48">
-            <v>-478</v>
+            <v>-39.153846153846644</v>
           </cell>
           <cell r="AE48">
-            <v>2852.5</v>
+            <v>2633.0769230769233</v>
           </cell>
           <cell r="AF48">
-            <v>3330.5</v>
+            <v>2672.23076923077</v>
           </cell>
           <cell r="AG48">
             <v>96.796296296296291</v>
@@ -9078,22 +9080,22 @@
             <v>216</v>
           </cell>
           <cell r="AA49">
-            <v>21.666666666666664</v>
+            <v>20</v>
           </cell>
           <cell r="AB49">
-            <v>5.5384615384615392</v>
+            <v>6</v>
           </cell>
           <cell r="AC49">
-            <v>0.55384615384615388</v>
+            <v>0.6</v>
           </cell>
           <cell r="AD49">
-            <v>-9.6666666666666643</v>
+            <v>-8</v>
           </cell>
           <cell r="AE49">
-            <v>10.833333333333332</v>
+            <v>10</v>
           </cell>
           <cell r="AF49">
-            <v>20.499999999999996</v>
+            <v>18</v>
           </cell>
           <cell r="AG49">
             <v>6</v>
@@ -9262,22 +9264,22 @@
             <v>49.879999999999995</v>
           </cell>
           <cell r="AA51">
-            <v>248.33333333333331</v>
+            <v>229.23076923076923</v>
           </cell>
           <cell r="AB51">
-            <v>1.731543624161074</v>
+            <v>1.8758389261744965</v>
           </cell>
           <cell r="AC51">
-            <v>0.1731543624161074</v>
+            <v>0.18758389261744968</v>
           </cell>
           <cell r="AD51">
-            <v>-205.33333333333331</v>
+            <v>-186.23076923076923</v>
           </cell>
           <cell r="AE51">
-            <v>124.16666666666666</v>
+            <v>114.61538461538461</v>
           </cell>
           <cell r="AF51">
-            <v>329.5</v>
+            <v>300.84615384615381</v>
           </cell>
           <cell r="AG51">
             <v>1.075</v>
@@ -9446,22 +9448,22 @@
             <v>4.6399999999999997</v>
           </cell>
           <cell r="AA53">
-            <v>593.33333333333337</v>
+            <v>547.69230769230762</v>
           </cell>
           <cell r="AB53">
-            <v>6.741573033707865E-2</v>
+            <v>7.3033707865168551E-2</v>
           </cell>
           <cell r="AC53">
-            <v>6.7415730337078645E-3</v>
+            <v>7.3033707865168551E-3</v>
           </cell>
           <cell r="AD53">
-            <v>-589.33333333333337</v>
+            <v>-543.69230769230762</v>
           </cell>
           <cell r="AE53">
-            <v>296.66666666666669</v>
+            <v>273.84615384615381</v>
           </cell>
           <cell r="AF53">
-            <v>886</v>
+            <v>817.53846153846143</v>
           </cell>
           <cell r="AG53">
             <v>0.1</v>
@@ -9538,22 +9540,22 @@
             <v>18284.13</v>
           </cell>
           <cell r="AA54">
-            <v>2998.333333333333</v>
+            <v>2767.6923076923076</v>
           </cell>
           <cell r="AB54">
-            <v>75.285158421345201</v>
+            <v>81.55892162312395</v>
           </cell>
           <cell r="AC54">
-            <v>7.52851584213452</v>
+            <v>8.1558921623123961</v>
           </cell>
           <cell r="AD54">
-            <v>19574.666666666668</v>
+            <v>19805.307692307691</v>
           </cell>
           <cell r="AE54">
-            <v>1499.1666666666665</v>
+            <v>1383.8461538461538</v>
           </cell>
           <cell r="AF54">
-            <v>-18075.5</v>
+            <v>-18421.461538461539</v>
           </cell>
           <cell r="AG54">
             <v>1881.0833333333333</v>
@@ -9630,22 +9632,22 @@
             <v>23675.49</v>
           </cell>
           <cell r="AA55">
-            <v>5197.5</v>
+            <v>4797.6923076923076</v>
           </cell>
           <cell r="AB55">
-            <v>56.236652236652233</v>
+            <v>60.923039923039923</v>
           </cell>
           <cell r="AC55">
-            <v>5.623665223665224</v>
+            <v>6.0923039923039921</v>
           </cell>
           <cell r="AD55">
-            <v>24031.5</v>
+            <v>24431.307692307691</v>
           </cell>
           <cell r="AE55">
-            <v>2598.75</v>
+            <v>2398.8461538461538</v>
           </cell>
           <cell r="AF55">
-            <v>-21432.75</v>
+            <v>-22032.461538461539</v>
           </cell>
           <cell r="AG55">
             <v>2435.75</v>
@@ -9722,22 +9724,22 @@
             <v>13081.5</v>
           </cell>
           <cell r="AA56">
-            <v>3131.666666666667</v>
+            <v>2890.7692307692309</v>
           </cell>
           <cell r="AB56">
-            <v>51.569984034060667</v>
+            <v>55.86748270356572</v>
           </cell>
           <cell r="AC56">
-            <v>5.1569984034060665</v>
+            <v>5.5867482703565727</v>
           </cell>
           <cell r="AD56">
-            <v>13018.333333333332</v>
+            <v>13259.23076923077</v>
           </cell>
           <cell r="AE56">
-            <v>1565.8333333333335</v>
+            <v>1445.3846153846155</v>
           </cell>
           <cell r="AF56">
-            <v>-11452.499999999998</v>
+            <v>-11813.846153846154</v>
           </cell>
           <cell r="AG56">
             <v>1345.8333333333333</v>
@@ -9814,22 +9816,22 @@
             <v>15625.710000000001</v>
           </cell>
           <cell r="AA57">
-            <v>2761.666666666667</v>
+            <v>2549.2307692307695</v>
           </cell>
           <cell r="AB57">
-            <v>69.852745926372961</v>
+            <v>75.673808086904032</v>
           </cell>
           <cell r="AC57">
-            <v>6.9852745926372952</v>
+            <v>7.5673808086904035</v>
           </cell>
           <cell r="AD57">
-            <v>16529.333333333332</v>
+            <v>16741.76923076923</v>
           </cell>
           <cell r="AE57">
-            <v>1380.8333333333335</v>
+            <v>1274.6153846153848</v>
           </cell>
           <cell r="AF57">
-            <v>-15148.499999999998</v>
+            <v>-15467.153846153846</v>
           </cell>
           <cell r="AG57">
             <v>1607.5833333333333</v>
@@ -9906,22 +9908,22 @@
             <v>1873.3000000000002</v>
           </cell>
           <cell r="AA58">
-            <v>461.66666666666663</v>
+            <v>426.15384615384613</v>
           </cell>
           <cell r="AB58">
-            <v>15.48736462093863</v>
+            <v>16.777978339350181</v>
           </cell>
           <cell r="AC58">
-            <v>1.5487364620938628</v>
+            <v>1.6777978339350181</v>
           </cell>
           <cell r="AD58">
-            <v>253.33333333333337</v>
+            <v>288.84615384615387</v>
           </cell>
           <cell r="AE58">
-            <v>230.83333333333331</v>
+            <v>213.07692307692307</v>
           </cell>
           <cell r="AF58">
-            <v>-22.500000000000057</v>
+            <v>-75.769230769230802</v>
           </cell>
           <cell r="AG58">
             <v>119.16666666666667</v>
@@ -9998,22 +10000,22 @@
             <v>1011.32</v>
           </cell>
           <cell r="AA59">
-            <v>896.66666666666674</v>
+            <v>827.69230769230774</v>
           </cell>
           <cell r="AB59">
-            <v>4.3048327137546467</v>
+            <v>4.6635687732342008</v>
           </cell>
           <cell r="AC59">
-            <v>0.43048327137546466</v>
+            <v>0.46635687732342007</v>
           </cell>
           <cell r="AD59">
-            <v>-510.66666666666674</v>
+            <v>-441.69230769230774</v>
           </cell>
           <cell r="AE59">
-            <v>448.33333333333337</v>
+            <v>413.84615384615387</v>
           </cell>
           <cell r="AF59">
-            <v>959.00000000000011</v>
+            <v>855.53846153846166</v>
           </cell>
           <cell r="AG59">
             <v>64.333333333333329</v>
@@ -10090,22 +10092,22 @@
             <v>780.76</v>
           </cell>
           <cell r="AA60">
-            <v>510</v>
+            <v>470.76923076923083</v>
           </cell>
           <cell r="AB60">
-            <v>5.8431372549019605</v>
+            <v>6.3300653594771239</v>
           </cell>
           <cell r="AC60">
-            <v>0.58431372549019611</v>
+            <v>0.63300653594771239</v>
           </cell>
           <cell r="AD60">
-            <v>-212</v>
+            <v>-172.76923076923083</v>
           </cell>
           <cell r="AE60">
-            <v>255</v>
+            <v>235.38461538461542</v>
           </cell>
           <cell r="AF60">
-            <v>467</v>
+            <v>408.15384615384625</v>
           </cell>
           <cell r="AG60">
             <v>49.666666666666664</v>
@@ -10182,22 +10184,22 @@
             <v>382.52000000000004</v>
           </cell>
           <cell r="AA61">
-            <v>430</v>
+            <v>396.92307692307691</v>
           </cell>
           <cell r="AB61">
-            <v>3.3953488372093021</v>
+            <v>3.6782945736434107</v>
           </cell>
           <cell r="AC61">
-            <v>0.33953488372093021</v>
+            <v>0.36782945736434108</v>
           </cell>
           <cell r="AD61">
-            <v>-284</v>
+            <v>-250.92307692307691</v>
           </cell>
           <cell r="AE61">
-            <v>215</v>
+            <v>198.46153846153845</v>
           </cell>
           <cell r="AF61">
-            <v>499</v>
+            <v>449.38461538461536</v>
           </cell>
           <cell r="AG61">
             <v>24.333333333333332</v>
@@ -10208,7 +10210,7 @@
             <v>Units Produce</v>
           </cell>
           <cell r="AF62">
-            <v>135034.5</v>
+            <v>108920.07692307689</v>
           </cell>
         </row>
       </sheetData>
@@ -10217,6 +10219,8 @@
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10541,212 +10545,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="63" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="63"/>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="63"/>
+      <c r="AB1" s="66"/>
+      <c r="AC1" s="66"/>
+      <c r="AD1" s="66"/>
+      <c r="AE1" s="66"/>
+      <c r="AF1" s="66"/>
+      <c r="AG1" s="66"/>
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
-      <c r="AA2" s="63"/>
-      <c r="AB2" s="63"/>
-      <c r="AC2" s="63"/>
-      <c r="AD2" s="63"/>
-      <c r="AE2" s="63"/>
-      <c r="AF2" s="63"/>
-      <c r="AG2" s="63"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="66"/>
+      <c r="AC2" s="66"/>
+      <c r="AD2" s="66"/>
+      <c r="AE2" s="66"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="62"/>
-      <c r="U3" s="62"/>
-      <c r="V3" s="62"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="62"/>
-      <c r="AA3" s="63"/>
-      <c r="AB3" s="63"/>
-      <c r="AC3" s="63"/>
-      <c r="AD3" s="63"/>
-      <c r="AE3" s="63"/>
-      <c r="AF3" s="63"/>
-      <c r="AG3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="66"/>
+      <c r="AB3" s="66"/>
+      <c r="AC3" s="66"/>
+      <c r="AD3" s="66"/>
+      <c r="AE3" s="66"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="62"/>
-      <c r="W4" s="62"/>
-      <c r="X4" s="62"/>
-      <c r="Y4" s="62"/>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="63"/>
-      <c r="AB4" s="63"/>
-      <c r="AC4" s="63"/>
-      <c r="AD4" s="63"/>
-      <c r="AE4" s="63"/>
-      <c r="AF4" s="63"/>
-      <c r="AG4" s="63"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="62"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="62"/>
-      <c r="Y5" s="62"/>
-      <c r="Z5" s="62"/>
-      <c r="AA5" s="63"/>
-      <c r="AB5" s="63"/>
-      <c r="AC5" s="63"/>
-      <c r="AD5" s="63"/>
-      <c r="AE5" s="63"/>
-      <c r="AF5" s="63"/>
-      <c r="AG5" s="63"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="66"/>
+      <c r="AB5" s="66"/>
+      <c r="AC5" s="66"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="63"/>
-      <c r="AB6" s="63"/>
-      <c r="AC6" s="63"/>
-      <c r="AD6" s="63"/>
-      <c r="AE6" s="63"/>
-      <c r="AF6" s="63"/>
-      <c r="AG6" s="63"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="66"/>
+      <c r="AB6" s="66"/>
+      <c r="AC6" s="66"/>
+      <c r="AD6" s="66"/>
+      <c r="AE6" s="66"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
@@ -11117,27 +11121,27 @@
       </c>
       <c r="AA13" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA13</f>
-        <v>11620.833333333332</v>
+        <v>10726.923076923076</v>
       </c>
       <c r="AB13" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB13</f>
-        <v>8.6095374686267476</v>
+        <v>9.326998924345645</v>
       </c>
       <c r="AC13" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC13</f>
-        <v>0.8609537468626749</v>
+        <v>0.93269989243456441</v>
       </c>
       <c r="AD13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD13</f>
-        <v>-1615.8333333333321</v>
+        <v>-721.92307692307622</v>
       </c>
       <c r="AE13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE13</f>
-        <v>5810.4166666666661</v>
+        <v>5363.4615384615381</v>
       </c>
       <c r="AF13" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF13</f>
-        <v>7426.2499999999982</v>
+        <v>6085.3846153846143</v>
       </c>
       <c r="AG13" s="27">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG13</f>
@@ -11245,27 +11249,27 @@
       </c>
       <c r="AA14" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA14</f>
-        <v>830.83333333333326</v>
+        <v>766.92307692307691</v>
       </c>
       <c r="AB14" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB14</f>
-        <v>6.7281845536609834</v>
+        <v>7.2888665997993982</v>
       </c>
       <c r="AC14" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC14</f>
-        <v>0.67281845536609841</v>
+        <v>0.72888665997993984</v>
       </c>
       <c r="AD14" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD14</f>
-        <v>-271.83333333333326</v>
+        <v>-207.92307692307691</v>
       </c>
       <c r="AE14" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE14</f>
-        <v>415.41666666666663</v>
+        <v>383.46153846153845</v>
       </c>
       <c r="AF14" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF14</f>
-        <v>687.24999999999989</v>
+        <v>591.38461538461536</v>
       </c>
       <c r="AG14" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG14</f>
@@ -11373,27 +11377,27 @@
       </c>
       <c r="AA15" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA15</f>
-        <v>4660.833333333333</v>
+        <v>4302.3076923076924</v>
       </c>
       <c r="AB15" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB15</f>
-        <v>7.363490076881817</v>
+        <v>7.9771142499553012</v>
       </c>
       <c r="AC15" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC15</f>
-        <v>0.73634900768818168</v>
+        <v>0.79771142499553016</v>
       </c>
       <c r="AD15" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD15</f>
-        <v>-1228.833333333333</v>
+        <v>-870.30769230769238</v>
       </c>
       <c r="AE15" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE15</f>
-        <v>2330.4166666666665</v>
+        <v>2151.1538461538462</v>
       </c>
       <c r="AF15" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF15</f>
-        <v>3559.2499999999995</v>
+        <v>3021.4615384615386</v>
       </c>
       <c r="AG15" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG15</f>
@@ -11501,27 +11505,27 @@
       </c>
       <c r="AA16" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA16</f>
-        <v>908.33333333333326</v>
+        <v>838.46153846153834</v>
       </c>
       <c r="AB16" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB16</f>
-        <v>2.2678899082568806</v>
+        <v>2.4568807339449545</v>
       </c>
       <c r="AC16" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC16</f>
-        <v>0.2267889908256881</v>
+        <v>0.24568807339449544</v>
       </c>
       <c r="AD16" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD16</f>
-        <v>-702.33333333333326</v>
+        <v>-632.46153846153834</v>
       </c>
       <c r="AE16" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE16</f>
-        <v>454.16666666666663</v>
+        <v>419.23076923076917</v>
       </c>
       <c r="AF16" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF16</f>
-        <v>1156.5</v>
+        <v>1051.6923076923076</v>
       </c>
       <c r="AG16" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG16</f>
@@ -11629,27 +11633,27 @@
       </c>
       <c r="AA17" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA17</f>
-        <v>94.166666666666657</v>
+        <v>86.92307692307692</v>
       </c>
       <c r="AB17" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB17</f>
-        <v>22.513274336283189</v>
+        <v>24.389380530973455</v>
       </c>
       <c r="AC17" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC17</f>
-        <v>2.2513274336283189</v>
+        <v>2.438938053097345</v>
       </c>
       <c r="AD17" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD17</f>
-        <v>117.83333333333334</v>
+        <v>125.07692307692308</v>
       </c>
       <c r="AE17" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE17</f>
-        <v>47.083333333333329</v>
+        <v>43.46153846153846</v>
       </c>
       <c r="AF17" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF17</f>
-        <v>-70.750000000000014</v>
+        <v>-81.615384615384613</v>
       </c>
       <c r="AG17" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG17</f>
@@ -11757,27 +11761,27 @@
       </c>
       <c r="AA18" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA18</f>
-        <v>13972.5</v>
+        <v>12897.692307692307</v>
       </c>
       <c r="AB18" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB18</f>
-        <v>5.9953480050098404</v>
+        <v>6.4949603387606611</v>
       </c>
       <c r="AC18" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC18</f>
-        <v>0.59953480050098407</v>
+        <v>0.64949603387606614</v>
       </c>
       <c r="AD18" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD18</f>
-        <v>-5595.5</v>
+        <v>-4520.6923076923067</v>
       </c>
       <c r="AE18" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE18</f>
-        <v>6986.25</v>
+        <v>6448.8461538461534</v>
       </c>
       <c r="AF18" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF18</f>
-        <v>12581.75</v>
+        <v>10969.538461538461</v>
       </c>
       <c r="AG18" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG18</f>
@@ -11885,27 +11889,27 @@
       </c>
       <c r="AA19" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA19</f>
-        <v>1384.1666666666665</v>
+        <v>1277.6923076923076</v>
       </c>
       <c r="AB19" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB19</f>
-        <v>10.887417218543048</v>
+        <v>11.794701986754967</v>
       </c>
       <c r="AC19" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC19</f>
-        <v>1.0887417218543047</v>
+        <v>1.1794701986754967</v>
       </c>
       <c r="AD19" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD19</f>
-        <v>122.83333333333348</v>
+        <v>229.30769230769238</v>
       </c>
       <c r="AE19" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE19</f>
-        <v>692.08333333333326</v>
+        <v>638.84615384615381</v>
       </c>
       <c r="AF19" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF19</f>
-        <v>569.24999999999977</v>
+        <v>409.53846153846143</v>
       </c>
       <c r="AG19" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG19</f>
@@ -12013,27 +12017,27 @@
       </c>
       <c r="AA20" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA20</f>
-        <v>3075.833333333333</v>
+        <v>2839.2307692307691</v>
       </c>
       <c r="AB20" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB20</f>
-        <v>12.894066648604715</v>
+        <v>13.968572202655109</v>
       </c>
       <c r="AC20" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC20</f>
-        <v>1.2894066648604716</v>
+        <v>1.3968572202655107</v>
       </c>
       <c r="AD20" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD20</f>
-        <v>890.16666666666697</v>
+        <v>1126.7692307692309</v>
       </c>
       <c r="AE20" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE20</f>
-        <v>1537.9166666666665</v>
+        <v>1419.6153846153845</v>
       </c>
       <c r="AF20" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF20</f>
-        <v>647.74999999999955</v>
+        <v>292.84615384615358</v>
       </c>
       <c r="AG20" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG20</f>
@@ -12141,27 +12145,27 @@
       </c>
       <c r="AA21" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA21</f>
-        <v>7126.6666666666661</v>
+        <v>6578.4615384615381</v>
       </c>
       <c r="AB21" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB21</f>
-        <v>10.717492984097287</v>
+        <v>11.610617399438729</v>
       </c>
       <c r="AC21" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC21</f>
-        <v>1.0717492984097288</v>
+        <v>1.1610617399438727</v>
       </c>
       <c r="AD21" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD21</f>
-        <v>511.33333333333394</v>
+        <v>1059.5384615384619</v>
       </c>
       <c r="AE21" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE21</f>
-        <v>3563.333333333333</v>
+        <v>3289.2307692307691</v>
       </c>
       <c r="AF21" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF21</f>
-        <v>3051.9999999999991</v>
+        <v>2229.6923076923072</v>
       </c>
       <c r="AG21" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG21</f>
@@ -12269,27 +12273,27 @@
       </c>
       <c r="AA22" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA22</f>
-        <v>3344.166666666667</v>
+        <v>3086.9230769230767</v>
       </c>
       <c r="AB22" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB22</f>
-        <v>11.246449040617991</v>
+        <v>12.183653127336157</v>
       </c>
       <c r="AC22" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC22</f>
-        <v>1.124644904061799</v>
+        <v>1.2183653127336158</v>
       </c>
       <c r="AD22" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD22</f>
-        <v>416.83333333333303</v>
+        <v>674.07692307692332</v>
       </c>
       <c r="AE22" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE22</f>
-        <v>1672.0833333333335</v>
+        <v>1543.4615384615383</v>
       </c>
       <c r="AF22" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF22</f>
-        <v>1255.2500000000005</v>
+        <v>869.38461538461502</v>
       </c>
       <c r="AG22" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG22</f>
@@ -12397,27 +12401,27 @@
       </c>
       <c r="AA23" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA23</f>
-        <v>36112.5</v>
+        <v>33334.615384615383</v>
       </c>
       <c r="AB23" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB23</f>
-        <v>9.1843544479058501</v>
+        <v>9.9497173185646712</v>
       </c>
       <c r="AC23" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC23</f>
-        <v>0.91843544479058503</v>
+        <v>0.99497173185646715</v>
       </c>
       <c r="AD23" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD23</f>
-        <v>-2945.5</v>
+        <v>-167.61538461538294</v>
       </c>
       <c r="AE23" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE23</f>
-        <v>18056.25</v>
+        <v>16667.307692307691</v>
       </c>
       <c r="AF23" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF23</f>
-        <v>21001.75</v>
+        <v>16834.923076923074</v>
       </c>
       <c r="AG23" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG23</f>
@@ -12525,27 +12529,27 @@
       </c>
       <c r="AA24" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA24</f>
-        <v>23759.166666666664</v>
+        <v>21931.538461538461</v>
       </c>
       <c r="AB24" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB24</f>
-        <v>10.542036407000808</v>
+        <v>11.42053944091754</v>
       </c>
       <c r="AC24" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC24</f>
-        <v>1.0542036407000808</v>
+        <v>1.1420539440917541</v>
       </c>
       <c r="AD24" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD24</f>
-        <v>1287.8333333333358</v>
+        <v>3115.461538461539</v>
       </c>
       <c r="AE24" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE24</f>
-        <v>11879.583333333332</v>
+        <v>10965.76923076923</v>
       </c>
       <c r="AF24" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF24</f>
-        <v>10591.749999999996</v>
+        <v>7850.3076923076915</v>
       </c>
       <c r="AG24" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG24</f>
@@ -12653,27 +12657,27 @@
       </c>
       <c r="AA25" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA25</f>
-        <v>22936.666666666664</v>
+        <v>21172.307692307691</v>
       </c>
       <c r="AB25" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB25</f>
-        <v>11.290655427990119</v>
+        <v>12.231543380322629</v>
       </c>
       <c r="AC25" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC25</f>
-        <v>1.1290655427990119</v>
+        <v>1.2231543380322627</v>
       </c>
       <c r="AD25" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD25</f>
-        <v>2960.3333333333358</v>
+        <v>4724.6923076923085</v>
       </c>
       <c r="AE25" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE25</f>
-        <v>11468.333333333332</v>
+        <v>10586.153846153846</v>
       </c>
       <c r="AF25" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF25</f>
-        <v>8507.9999999999964</v>
+        <v>5861.4615384615372</v>
       </c>
       <c r="AG25" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG25</f>
@@ -12781,27 +12785,27 @@
       </c>
       <c r="AA26" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA26</f>
-        <v>27655.833333333336</v>
+        <v>25528.461538461539</v>
       </c>
       <c r="AB26" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB26</f>
-        <v>10.713472142706481</v>
+        <v>11.606261487932022</v>
       </c>
       <c r="AC26" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC26</f>
-        <v>1.0713472142706479</v>
+        <v>1.1606261487932021</v>
       </c>
       <c r="AD26" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD26</f>
-        <v>1973.1666666666642</v>
+        <v>4100.538461538461</v>
       </c>
       <c r="AE26" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE26</f>
-        <v>13827.916666666668</v>
+        <v>12764.23076923077</v>
       </c>
       <c r="AF26" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF26</f>
-        <v>11854.750000000004</v>
+        <v>8663.6923076923085</v>
       </c>
       <c r="AG26" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG26</f>
@@ -12909,27 +12913,27 @@
       </c>
       <c r="AA27" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA27</f>
-        <v>320.83333333333337</v>
+        <v>301.53846153846155</v>
       </c>
       <c r="AB27" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB27</f>
-        <v>47.251948051948048</v>
+        <v>50.275510204081634</v>
       </c>
       <c r="AC27" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC27</f>
-        <v>4.7251948051948043</v>
+        <v>5.027551020408163</v>
       </c>
       <c r="AD27" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD27</f>
-        <v>1195.1666666666665</v>
+        <v>1214.4615384615386</v>
       </c>
       <c r="AE27" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE27</f>
-        <v>160.41666666666669</v>
+        <v>150.76923076923077</v>
       </c>
       <c r="AF27" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF27</f>
-        <v>-1034.7499999999998</v>
+        <v>-1063.6923076923078</v>
       </c>
       <c r="AG27" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG27</f>
@@ -12977,15 +12981,15 @@
       </c>
       <c r="L28" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L28</f>
-        <v>14.75202593192869</v>
+        <v>15.981361426256079</v>
       </c>
       <c r="M28" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M28</f>
-        <v>4524.6666666666661</v>
+        <v>4176.6153846153848</v>
       </c>
       <c r="N28" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N28</f>
-        <v>-50.999999999999545</v>
+        <v>186.30769230769238</v>
       </c>
       <c r="O28" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O28</f>
@@ -13037,27 +13041,27 @@
       </c>
       <c r="AA28" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA28</f>
-        <v>2056.6666666666665</v>
+        <v>1898.4615384615383</v>
       </c>
       <c r="AB28" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB28</f>
-        <v>23.401944894651542</v>
+        <v>25.352106969205835</v>
       </c>
       <c r="AC28" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC28</f>
-        <v>2.3401944894651541</v>
+        <v>2.5352106969205837</v>
       </c>
       <c r="AD28" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD28</f>
-        <v>2756.3333333333335</v>
+        <v>2914.5384615384619</v>
       </c>
       <c r="AE28" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE28</f>
-        <v>1028.3333333333333</v>
+        <v>949.23076923076917</v>
       </c>
       <c r="AF28" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF28</f>
-        <v>-1728.0000000000002</v>
+        <v>-1965.3076923076928</v>
       </c>
       <c r="AG28" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG28</f>
@@ -13105,15 +13109,15 @@
       </c>
       <c r="L29" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L29</f>
-        <v>11.609359104781282</v>
+        <v>12.576805696846389</v>
       </c>
       <c r="M29" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M29</f>
-        <v>5406.5</v>
+        <v>4990.6153846153848</v>
       </c>
       <c r="N29" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N29</f>
-        <v>-833.25</v>
+        <v>-549.69230769230762</v>
       </c>
       <c r="O29" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O29</f>
@@ -13165,27 +13169,27 @@
       </c>
       <c r="AA29" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA29</f>
-        <v>2457.5</v>
+        <v>2268.4615384615386</v>
       </c>
       <c r="AB29" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB29</f>
-        <v>18.526958290946084</v>
+        <v>20.070871481858255</v>
       </c>
       <c r="AC29" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC29</f>
-        <v>1.8526958290946083</v>
+        <v>2.0070871481858257</v>
       </c>
       <c r="AD29" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD29</f>
-        <v>2095.5</v>
+        <v>2284.5384615384614</v>
       </c>
       <c r="AE29" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE29</f>
-        <v>1228.75</v>
+        <v>1134.2307692307693</v>
       </c>
       <c r="AF29" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF29</f>
-        <v>-866.75</v>
+        <v>-1150.3076923076922</v>
       </c>
       <c r="AG29" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG29</f>
@@ -13233,15 +13237,15 @@
       </c>
       <c r="L30" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L30</f>
-        <v>12.064400715563508</v>
+        <v>13.069767441860465</v>
       </c>
       <c r="M30" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M30</f>
-        <v>5124.1666666666661</v>
+        <v>4730</v>
       </c>
       <c r="N30" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N30</f>
-        <v>-683.74999999999955</v>
+        <v>-415</v>
       </c>
       <c r="O30" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O30</f>
@@ -13293,27 +13297,27 @@
       </c>
       <c r="AA30" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA30</f>
-        <v>2329.1666666666665</v>
+        <v>2150</v>
       </c>
       <c r="AB30" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB30</f>
-        <v>25.880500894454382</v>
+        <v>28.037209302325582</v>
       </c>
       <c r="AC30" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC30</f>
-        <v>2.5880500894454386</v>
+        <v>2.8037209302325583</v>
       </c>
       <c r="AD30" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD30</f>
-        <v>3698.8333333333335</v>
+        <v>3878</v>
       </c>
       <c r="AE30" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE30</f>
-        <v>1164.5833333333333</v>
+        <v>1075</v>
       </c>
       <c r="AF30" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF30</f>
-        <v>-2534.25</v>
+        <v>-2803</v>
       </c>
       <c r="AG30" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG30</f>
@@ -13421,27 +13425,27 @@
       </c>
       <c r="AA31" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA31</f>
-        <v>2303.3333333333335</v>
+        <v>2126.1538461538462</v>
       </c>
       <c r="AB31" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB31</f>
-        <v>5.9522431259044861</v>
+        <v>6.4482633863965271</v>
       </c>
       <c r="AC31" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC31</f>
-        <v>0.59522431259044861</v>
+        <v>0.64482633863965266</v>
       </c>
       <c r="AD31" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD31</f>
-        <v>-932.33333333333348</v>
+        <v>-755.15384615384619</v>
       </c>
       <c r="AE31" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE31</f>
-        <v>1151.6666666666667</v>
+        <v>1063.0769230769231</v>
       </c>
       <c r="AF31" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF31</f>
-        <v>2084</v>
+        <v>1818.2307692307693</v>
       </c>
       <c r="AG31" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG31</f>
@@ -13549,27 +13553,27 @@
       </c>
       <c r="AA32" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA32</f>
-        <v>1314.1666666666665</v>
+        <v>1213.0769230769231</v>
       </c>
       <c r="AB32" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB32</f>
-        <v>7.4571972098922013</v>
+        <v>8.0786303107165498</v>
       </c>
       <c r="AC32" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC32</f>
-        <v>0.74571972098922013</v>
+        <v>0.80786303107165502</v>
       </c>
       <c r="AD32" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD32</f>
-        <v>-334.16666666666652</v>
+        <v>-233.07692307692309</v>
       </c>
       <c r="AE32" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE32</f>
-        <v>657.08333333333326</v>
+        <v>606.53846153846155</v>
       </c>
       <c r="AF32" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF32</f>
-        <v>991.24999999999977</v>
+        <v>839.61538461538464</v>
       </c>
       <c r="AG32" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG32</f>
@@ -13677,27 +13681,27 @@
       </c>
       <c r="AA33" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA33</f>
-        <v>5004.166666666667</v>
+        <v>4619.2307692307695</v>
       </c>
       <c r="AB33" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB33</f>
-        <v>6.5985012489592005</v>
+        <v>7.1483763530391338</v>
       </c>
       <c r="AC33" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC33</f>
-        <v>0.65985012489591999</v>
+        <v>0.71483763530391331</v>
       </c>
       <c r="AD33" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD33</f>
-        <v>-1702.166666666667</v>
+        <v>-1317.2307692307695</v>
       </c>
       <c r="AE33" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE33</f>
-        <v>2502.0833333333335</v>
+        <v>2309.6153846153848</v>
       </c>
       <c r="AF33" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF33</f>
-        <v>4204.25</v>
+        <v>3626.8461538461543</v>
       </c>
       <c r="AG33" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG33</f>
@@ -13805,27 +13809,27 @@
       </c>
       <c r="AA34" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA34</f>
-        <v>7844.1666666666661</v>
+        <v>7240.7692307692305</v>
       </c>
       <c r="AB34" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB34</f>
-        <v>8.0403697014766813</v>
+        <v>8.7104005099330717</v>
       </c>
       <c r="AC34" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC34</f>
-        <v>0.80403697014766817</v>
+        <v>0.87104005099330717</v>
       </c>
       <c r="AD34" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD34</f>
-        <v>-1537.1666666666661</v>
+        <v>-933.76923076923049</v>
       </c>
       <c r="AE34" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE34</f>
-        <v>3922.083333333333</v>
+        <v>3620.3846153846152</v>
       </c>
       <c r="AF34" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF34</f>
-        <v>5459.2499999999991</v>
+        <v>4554.1538461538457</v>
       </c>
       <c r="AG34" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG34</f>
@@ -13933,7 +13937,7 @@
       </c>
       <c r="AA35" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA35</f>
-        <v>83.333333333333343</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="AB35" s="34">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB35</f>
@@ -13945,15 +13949,15 @@
       </c>
       <c r="AD35" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD35</f>
-        <v>-83.333333333333343</v>
+        <v>-76.92307692307692</v>
       </c>
       <c r="AE35" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE35</f>
-        <v>41.666666666666671</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AF35" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF35</f>
-        <v>125.00000000000001</v>
+        <v>115.38461538461539</v>
       </c>
       <c r="AG35" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG35</f>
@@ -14061,27 +14065,27 @@
       </c>
       <c r="AA36" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA36</f>
-        <v>1420</v>
+        <v>1310.7692307692307</v>
       </c>
       <c r="AB36" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB36</f>
-        <v>3.823943661971831</v>
+        <v>4.142605633802817</v>
       </c>
       <c r="AC36" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC36</f>
-        <v>0.38239436619718309</v>
+        <v>0.41426056338028172</v>
       </c>
       <c r="AD36" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD36</f>
-        <v>-877</v>
+        <v>-767.76923076923072</v>
       </c>
       <c r="AE36" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE36</f>
-        <v>710</v>
+        <v>655.38461538461536</v>
       </c>
       <c r="AF36" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF36</f>
-        <v>1587</v>
+        <v>1423.1538461538462</v>
       </c>
       <c r="AG36" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG36</f>
@@ -14189,27 +14193,27 @@
       </c>
       <c r="AA37" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA37</f>
-        <v>6635.8333333333339</v>
+        <v>6125.3846153846152</v>
       </c>
       <c r="AB37" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB37</f>
-        <v>15.322868265728996</v>
+        <v>16.599773954539746</v>
       </c>
       <c r="AC37" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC37</f>
-        <v>1.5322868265728995</v>
+        <v>1.6599773954539747</v>
       </c>
       <c r="AD37" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD37</f>
-        <v>3532.1666666666661</v>
+        <v>4042.6153846153848</v>
       </c>
       <c r="AE37" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE37</f>
-        <v>3317.916666666667</v>
+        <v>3062.6923076923076</v>
       </c>
       <c r="AF37" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF37</f>
-        <v>-214.24999999999909</v>
+        <v>-979.92307692307713</v>
       </c>
       <c r="AG37" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG37</f>
@@ -14317,27 +14321,27 @@
       </c>
       <c r="AA38" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA38</f>
-        <v>10833.333333333332</v>
+        <v>10000</v>
       </c>
       <c r="AB38" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB38</f>
-        <v>9.0996923076923082</v>
+        <v>9.8580000000000005</v>
       </c>
       <c r="AC38" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC38</f>
-        <v>0.90996923076923086</v>
+        <v>0.98580000000000001</v>
       </c>
       <c r="AD38" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD38</f>
-        <v>-975.33333333333212</v>
+        <v>-142</v>
       </c>
       <c r="AE38" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE38</f>
-        <v>5416.6666666666661</v>
+        <v>5000</v>
       </c>
       <c r="AF38" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF38</f>
-        <v>6391.9999999999982</v>
+        <v>5142</v>
       </c>
       <c r="AG38" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG38</f>
@@ -14445,27 +14449,27 @@
       </c>
       <c r="AA39" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA39</f>
-        <v>4935</v>
+        <v>4555.3846153846152</v>
       </c>
       <c r="AB39" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB39</f>
-        <v>3.9837892603850049</v>
+        <v>4.3157716987504218</v>
       </c>
       <c r="AC39" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC39</f>
-        <v>0.3983789260385005</v>
+        <v>0.43157716987504224</v>
       </c>
       <c r="AD39" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD39</f>
-        <v>-2969</v>
+        <v>-2589.3846153846152</v>
       </c>
       <c r="AE39" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE39</f>
-        <v>2467.5</v>
+        <v>2277.6923076923076</v>
       </c>
       <c r="AF39" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF39</f>
-        <v>5436.5</v>
+        <v>4867.0769230769229</v>
       </c>
       <c r="AG39" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG39</f>
@@ -14573,27 +14577,27 @@
       </c>
       <c r="AA40" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA40</f>
-        <v>3581.666666666667</v>
+        <v>3306.1538461538466</v>
       </c>
       <c r="AB40" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB40</f>
-        <v>12.692415076779897</v>
+        <v>13.750116333178221</v>
       </c>
       <c r="AC40" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC40</f>
-        <v>1.2692415076779897</v>
+        <v>1.3750116333178219</v>
       </c>
       <c r="AD40" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD40</f>
-        <v>964.33333333333303</v>
+        <v>1239.8461538461534</v>
       </c>
       <c r="AE40" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE40</f>
-        <v>1790.8333333333335</v>
+        <v>1653.0769230769233</v>
       </c>
       <c r="AF40" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF40</f>
-        <v>826.50000000000045</v>
+        <v>413.23076923076997</v>
       </c>
       <c r="AG40" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG40</f>
@@ -14957,27 +14961,27 @@
       </c>
       <c r="AA43" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA43</f>
-        <v>1317.5</v>
+        <v>1216.1538461538462</v>
       </c>
       <c r="AB43" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB43</f>
-        <v>5.0170777988614796</v>
+        <v>5.4351676154332704</v>
       </c>
       <c r="AC43" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC43</f>
-        <v>0.50170777988614801</v>
+        <v>0.54351676154332695</v>
       </c>
       <c r="AD43" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD43</f>
-        <v>-656.5</v>
+        <v>-555.15384615384619</v>
       </c>
       <c r="AE43" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE43</f>
-        <v>658.75</v>
+        <v>608.07692307692309</v>
       </c>
       <c r="AF43" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF43</f>
-        <v>1315.25</v>
+        <v>1163.2307692307693</v>
       </c>
       <c r="AG43" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG43</f>
@@ -15085,27 +15089,27 @@
       </c>
       <c r="AA44" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA44</f>
-        <v>1275.8333333333333</v>
+        <v>1177.6923076923076</v>
       </c>
       <c r="AB44" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB44</f>
-        <v>8.8961463096015674</v>
+        <v>9.6374918354016987</v>
       </c>
       <c r="AC44" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC44</f>
-        <v>0.8896146309601568</v>
+        <v>0.96374918354016992</v>
       </c>
       <c r="AD44" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD44</f>
-        <v>-140.83333333333326</v>
+        <v>-42.692307692307622</v>
       </c>
       <c r="AE44" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE44</f>
-        <v>637.91666666666663</v>
+        <v>588.84615384615381</v>
       </c>
       <c r="AF44" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF44</f>
-        <v>778.74999999999989</v>
+        <v>631.53846153846143</v>
       </c>
       <c r="AG44" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG44</f>
@@ -15213,27 +15217,27 @@
       </c>
       <c r="AA45" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA45</f>
-        <v>5877.5</v>
+        <v>5425.3846153846152</v>
       </c>
       <c r="AB45" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB45</f>
-        <v>7.0642279880901748</v>
+        <v>7.6529136537643554</v>
       </c>
       <c r="AC45" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC45</f>
-        <v>0.70642279880901748</v>
+        <v>0.76529136537643561</v>
       </c>
       <c r="AD45" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD45</f>
-        <v>-1725.5</v>
+        <v>-1273.3846153846152</v>
       </c>
       <c r="AE45" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE45</f>
-        <v>2938.75</v>
+        <v>2712.6923076923076</v>
       </c>
       <c r="AF45" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF45</f>
-        <v>4664.25</v>
+        <v>3986.0769230769229</v>
       </c>
       <c r="AG45" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG45</f>
@@ -15341,27 +15345,27 @@
       </c>
       <c r="AA46" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA46</f>
-        <v>6554.1666666666661</v>
+        <v>6050</v>
       </c>
       <c r="AB46" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB46</f>
-        <v>13.048188175460904</v>
+        <v>14.135537190082644</v>
       </c>
       <c r="AC46" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC46</f>
-        <v>1.3048188175460904</v>
+        <v>1.4135537190082645</v>
       </c>
       <c r="AD46" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD46</f>
-        <v>1997.8333333333339</v>
+        <v>2502</v>
       </c>
       <c r="AE46" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE46</f>
-        <v>3277.083333333333</v>
+        <v>3025</v>
       </c>
       <c r="AF46" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF46</f>
-        <v>1279.2499999999991</v>
+        <v>523</v>
       </c>
       <c r="AG46" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG46</f>
@@ -15469,27 +15473,27 @@
       </c>
       <c r="AA47" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA47</f>
-        <v>8187.5</v>
+        <v>7557.6923076923067</v>
       </c>
       <c r="AB47" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB47</f>
-        <v>8.2235114503816789</v>
+        <v>8.9088040712468199</v>
       </c>
       <c r="AC47" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC47</f>
-        <v>0.82235114503816797</v>
+        <v>0.89088040712468208</v>
       </c>
       <c r="AD47" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD47</f>
-        <v>-1454.5</v>
+        <v>-824.69230769230671</v>
       </c>
       <c r="AE47" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE47</f>
-        <v>4093.75</v>
+        <v>3778.8461538461534</v>
       </c>
       <c r="AF47" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF47</f>
-        <v>5548.25</v>
+        <v>4603.5384615384601</v>
       </c>
       <c r="AG47" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG47</f>
@@ -15597,27 +15601,27 @@
       </c>
       <c r="AA48" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA48</f>
-        <v>5705</v>
+        <v>5266.1538461538466</v>
       </c>
       <c r="AB48" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB48</f>
-        <v>9.1621384750219104</v>
+        <v>9.9256500146070685</v>
       </c>
       <c r="AC48" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC48</f>
-        <v>0.91621384750219104</v>
+        <v>0.99256500146070692</v>
       </c>
       <c r="AD48" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD48</f>
-        <v>-478</v>
+        <v>-39.153846153846644</v>
       </c>
       <c r="AE48" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE48</f>
-        <v>2852.5</v>
+        <v>2633.0769230769233</v>
       </c>
       <c r="AF48" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF48</f>
-        <v>3330.5</v>
+        <v>2672.23076923077</v>
       </c>
       <c r="AG48" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG48</f>
@@ -15725,27 +15729,27 @@
       </c>
       <c r="AA49" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA49</f>
-        <v>21.666666666666664</v>
+        <v>20</v>
       </c>
       <c r="AB49" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB49</f>
-        <v>5.5384615384615392</v>
+        <v>6</v>
       </c>
       <c r="AC49" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC49</f>
-        <v>0.55384615384615388</v>
+        <v>0.6</v>
       </c>
       <c r="AD49" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD49</f>
-        <v>-9.6666666666666643</v>
+        <v>-8</v>
       </c>
       <c r="AE49" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE49</f>
-        <v>10.833333333333332</v>
+        <v>10</v>
       </c>
       <c r="AF49" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF49</f>
-        <v>20.499999999999996</v>
+        <v>18</v>
       </c>
       <c r="AG49" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG49</f>
@@ -15981,27 +15985,27 @@
       </c>
       <c r="AA51" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA51</f>
-        <v>248.33333333333331</v>
+        <v>229.23076923076923</v>
       </c>
       <c r="AB51" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB51</f>
-        <v>1.731543624161074</v>
+        <v>1.8758389261744965</v>
       </c>
       <c r="AC51" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC51</f>
-        <v>0.1731543624161074</v>
+        <v>0.18758389261744968</v>
       </c>
       <c r="AD51" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD51</f>
-        <v>-205.33333333333331</v>
+        <v>-186.23076923076923</v>
       </c>
       <c r="AE51" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE51</f>
-        <v>124.16666666666666</v>
+        <v>114.61538461538461</v>
       </c>
       <c r="AF51" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF51</f>
-        <v>329.5</v>
+        <v>300.84615384615381</v>
       </c>
       <c r="AG51" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG51</f>
@@ -16237,27 +16241,27 @@
       </c>
       <c r="AA53" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA53</f>
-        <v>593.33333333333337</v>
+        <v>547.69230769230762</v>
       </c>
       <c r="AB53" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB53</f>
-        <v>6.741573033707865E-2</v>
+        <v>7.3033707865168551E-2</v>
       </c>
       <c r="AC53" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC53</f>
-        <v>6.7415730337078645E-3</v>
+        <v>7.3033707865168551E-3</v>
       </c>
       <c r="AD53" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD53</f>
-        <v>-589.33333333333337</v>
+        <v>-543.69230769230762</v>
       </c>
       <c r="AE53" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE53</f>
-        <v>296.66666666666669</v>
+        <v>273.84615384615381</v>
       </c>
       <c r="AF53" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF53</f>
-        <v>886</v>
+        <v>817.53846153846143</v>
       </c>
       <c r="AG53" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG53</f>
@@ -16365,27 +16369,27 @@
       </c>
       <c r="AA54" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA54</f>
-        <v>2998.333333333333</v>
+        <v>2767.6923076923076</v>
       </c>
       <c r="AB54" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB54</f>
-        <v>75.285158421345201</v>
+        <v>81.55892162312395</v>
       </c>
       <c r="AC54" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC54</f>
-        <v>7.52851584213452</v>
+        <v>8.1558921623123961</v>
       </c>
       <c r="AD54" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD54</f>
-        <v>19574.666666666668</v>
+        <v>19805.307692307691</v>
       </c>
       <c r="AE54" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE54</f>
-        <v>1499.1666666666665</v>
+        <v>1383.8461538461538</v>
       </c>
       <c r="AF54" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF54</f>
-        <v>-18075.5</v>
+        <v>-18421.461538461539</v>
       </c>
       <c r="AG54" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG54</f>
@@ -16493,27 +16497,27 @@
       </c>
       <c r="AA55" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA55</f>
-        <v>5197.5</v>
+        <v>4797.6923076923076</v>
       </c>
       <c r="AB55" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB55</f>
-        <v>56.236652236652233</v>
+        <v>60.923039923039923</v>
       </c>
       <c r="AC55" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC55</f>
-        <v>5.623665223665224</v>
+        <v>6.0923039923039921</v>
       </c>
       <c r="AD55" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD55</f>
-        <v>24031.5</v>
+        <v>24431.307692307691</v>
       </c>
       <c r="AE55" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE55</f>
-        <v>2598.75</v>
+        <v>2398.8461538461538</v>
       </c>
       <c r="AF55" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF55</f>
-        <v>-21432.75</v>
+        <v>-22032.461538461539</v>
       </c>
       <c r="AG55" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG55</f>
@@ -16621,27 +16625,27 @@
       </c>
       <c r="AA56" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA56</f>
-        <v>3131.666666666667</v>
+        <v>2890.7692307692309</v>
       </c>
       <c r="AB56" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB56</f>
-        <v>51.569984034060667</v>
+        <v>55.86748270356572</v>
       </c>
       <c r="AC56" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC56</f>
-        <v>5.1569984034060665</v>
+        <v>5.5867482703565727</v>
       </c>
       <c r="AD56" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD56</f>
-        <v>13018.333333333332</v>
+        <v>13259.23076923077</v>
       </c>
       <c r="AE56" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE56</f>
-        <v>1565.8333333333335</v>
+        <v>1445.3846153846155</v>
       </c>
       <c r="AF56" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF56</f>
-        <v>-11452.499999999998</v>
+        <v>-11813.846153846154</v>
       </c>
       <c r="AG56" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG56</f>
@@ -16749,27 +16753,27 @@
       </c>
       <c r="AA57" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA57</f>
-        <v>2761.666666666667</v>
+        <v>2549.2307692307695</v>
       </c>
       <c r="AB57" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB57</f>
-        <v>69.852745926372961</v>
+        <v>75.673808086904032</v>
       </c>
       <c r="AC57" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC57</f>
-        <v>6.9852745926372952</v>
+        <v>7.5673808086904035</v>
       </c>
       <c r="AD57" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD57</f>
-        <v>16529.333333333332</v>
+        <v>16741.76923076923</v>
       </c>
       <c r="AE57" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE57</f>
-        <v>1380.8333333333335</v>
+        <v>1274.6153846153848</v>
       </c>
       <c r="AF57" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF57</f>
-        <v>-15148.499999999998</v>
+        <v>-15467.153846153846</v>
       </c>
       <c r="AG57" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG57</f>
@@ -16877,27 +16881,27 @@
       </c>
       <c r="AA58" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA58</f>
-        <v>461.66666666666663</v>
+        <v>426.15384615384613</v>
       </c>
       <c r="AB58" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB58</f>
-        <v>15.48736462093863</v>
+        <v>16.777978339350181</v>
       </c>
       <c r="AC58" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC58</f>
-        <v>1.5487364620938628</v>
+        <v>1.6777978339350181</v>
       </c>
       <c r="AD58" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD58</f>
-        <v>253.33333333333337</v>
+        <v>288.84615384615387</v>
       </c>
       <c r="AE58" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE58</f>
-        <v>230.83333333333331</v>
+        <v>213.07692307692307</v>
       </c>
       <c r="AF58" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF58</f>
-        <v>-22.500000000000057</v>
+        <v>-75.769230769230802</v>
       </c>
       <c r="AG58" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG58</f>
@@ -17005,27 +17009,27 @@
       </c>
       <c r="AA59" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA59</f>
-        <v>896.66666666666674</v>
+        <v>827.69230769230774</v>
       </c>
       <c r="AB59" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB59</f>
-        <v>4.3048327137546467</v>
+        <v>4.6635687732342008</v>
       </c>
       <c r="AC59" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC59</f>
-        <v>0.43048327137546466</v>
+        <v>0.46635687732342007</v>
       </c>
       <c r="AD59" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD59</f>
-        <v>-510.66666666666674</v>
+        <v>-441.69230769230774</v>
       </c>
       <c r="AE59" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE59</f>
-        <v>448.33333333333337</v>
+        <v>413.84615384615387</v>
       </c>
       <c r="AF59" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF59</f>
-        <v>959.00000000000011</v>
+        <v>855.53846153846166</v>
       </c>
       <c r="AG59" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG59</f>
@@ -17133,27 +17137,27 @@
       </c>
       <c r="AA60" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA60</f>
-        <v>510</v>
+        <v>470.76923076923083</v>
       </c>
       <c r="AB60" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB60</f>
-        <v>5.8431372549019605</v>
+        <v>6.3300653594771239</v>
       </c>
       <c r="AC60" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC60</f>
-        <v>0.58431372549019611</v>
+        <v>0.63300653594771239</v>
       </c>
       <c r="AD60" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD60</f>
-        <v>-212</v>
+        <v>-172.76923076923083</v>
       </c>
       <c r="AE60" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE60</f>
-        <v>255</v>
+        <v>235.38461538461542</v>
       </c>
       <c r="AF60" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF60</f>
-        <v>467</v>
+        <v>408.15384615384625</v>
       </c>
       <c r="AG60" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG60</f>
@@ -17261,27 +17265,27 @@
       </c>
       <c r="AA61" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA61</f>
-        <v>430</v>
+        <v>396.92307692307691</v>
       </c>
       <c r="AB61" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB61</f>
-        <v>3.3953488372093021</v>
+        <v>3.6782945736434107</v>
       </c>
       <c r="AC61" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC61</f>
-        <v>0.33953488372093021</v>
+        <v>0.36782945736434108</v>
       </c>
       <c r="AD61" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD61</f>
-        <v>-284</v>
+        <v>-250.92307692307691</v>
       </c>
       <c r="AE61" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE61</f>
-        <v>215</v>
+        <v>198.46153846153845</v>
       </c>
       <c r="AF61" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF61</f>
-        <v>499</v>
+        <v>449.38461538461536</v>
       </c>
       <c r="AG61" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG61</f>
@@ -17321,7 +17325,7 @@
       </c>
       <c r="AF62" s="44">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF62</f>
-        <v>135034.5</v>
+        <v>108920.07692307689</v>
       </c>
     </row>
     <row r="63" spans="2:33" x14ac:dyDescent="0.25">
@@ -17330,10 +17334,10 @@
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
-      <c r="E63" s="64" t="s">
+      <c r="E63" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="F63" s="64"/>
+      <c r="F63" s="67"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -17358,10 +17362,10 @@
       <c r="AB63" s="42"/>
     </row>
     <row r="64" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B64" s="65" t="s">
+      <c r="B64" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="65"/>
+      <c r="C64" s="63"/>
       <c r="D64" s="48">
         <f>SUM(F13:F61)</f>
         <v>144936.54999999999</v>
@@ -17506,19 +17510,19 @@
       <c r="AB67" s="42"/>
     </row>
     <row r="68" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B68" s="65" t="s">
+      <c r="B68" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="C68" s="65"/>
+      <c r="C68" s="63"/>
       <c r="D68" s="50">
         <f>SUM(Z13:Z61)</f>
         <v>421177.93000000017</v>
       </c>
-      <c r="E68" s="66">
+      <c r="E68" s="64">
         <f>D68*100/D68</f>
         <v>100</v>
       </c>
-      <c r="F68" s="66"/>
+      <c r="F68" s="64"/>
       <c r="G68" s="51"/>
       <c r="H68" s="51"/>
       <c r="I68" s="51"/>
@@ -17603,10 +17607,10 @@
       <c r="AB70" s="42"/>
     </row>
     <row r="71" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="65"/>
+      <c r="C71" s="63"/>
       <c r="D71" s="3">
         <f>SUM(E13:E61)</f>
         <v>112990</v>
@@ -17721,11 +17725,11 @@
         <f>SUM(T13:T61)</f>
         <v>36961</v>
       </c>
-      <c r="E74" s="67">
+      <c r="E74" s="62">
         <f>D74*100/D75</f>
         <v>11.039956032533535</v>
       </c>
-      <c r="F74" s="67"/>
+      <c r="F74" s="62"/>
       <c r="G74" s="56"/>
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
@@ -17750,19 +17754,19 @@
       <c r="AB74" s="42"/>
     </row>
     <row r="75" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="63"/>
       <c r="D75" s="55">
         <f>SUM(Y13:Y61)</f>
         <v>334793</v>
       </c>
-      <c r="E75" s="67">
+      <c r="E75" s="62">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="67"/>
+      <c r="F75" s="62"/>
       <c r="G75" s="56"/>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
@@ -18523,23 +18527,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="B1:Z6"/>
+    <mergeCell ref="AA1:AG6"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="E64:F64"/>
     <mergeCell ref="E66:F66"/>
     <mergeCell ref="E67:F67"/>
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="E68:F68"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="B1:Z6"/>
-    <mergeCell ref="AA1:AG6"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G61">
     <cfRule type="colorScale" priority="5">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEE23FB-3A6A-4BF0-97FE-D98D3D3BDDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB9A6ED-3B9A-4798-BA3B-F02048DDDF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -841,15 +841,6 @@
     <xf numFmtId="2" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -858,6 +849,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5641,6 +5641,9 @@
       <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 19-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 20-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 20-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -5768,22 +5771,22 @@
             <v>13606.800000000001</v>
           </cell>
           <cell r="AA13">
-            <v>10726.923076923076</v>
+            <v>11018.666666666666</v>
           </cell>
           <cell r="AB13">
-            <v>9.326998924345645</v>
+            <v>9.0800459825750259</v>
           </cell>
           <cell r="AC13">
-            <v>0.93269989243456441</v>
+            <v>0.90800459825750246</v>
           </cell>
           <cell r="AD13">
-            <v>-721.92307692307622</v>
+            <v>-1013.6666666666661</v>
           </cell>
           <cell r="AE13">
-            <v>5363.4615384615381</v>
+            <v>5509.333333333333</v>
           </cell>
           <cell r="AF13">
-            <v>6085.3846153846143</v>
+            <v>6522.9999999999991</v>
           </cell>
           <cell r="AG13">
             <v>125.0625</v>
@@ -5860,22 +5863,22 @@
             <v>888.81000000000006</v>
           </cell>
           <cell r="AA14">
-            <v>766.92307692307691</v>
+            <v>791.33333333333337</v>
           </cell>
           <cell r="AB14">
-            <v>7.2888665997993982</v>
+            <v>7.0640269587194604</v>
           </cell>
           <cell r="AC14">
-            <v>0.72888665997993984</v>
+            <v>0.70640269587194604</v>
           </cell>
           <cell r="AD14">
-            <v>-207.92307692307691</v>
+            <v>-232.33333333333337</v>
           </cell>
           <cell r="AE14">
-            <v>383.46153846153845</v>
+            <v>395.66666666666669</v>
           </cell>
           <cell r="AF14">
-            <v>591.38461538461536</v>
+            <v>628</v>
           </cell>
           <cell r="AG14">
             <v>6.9874999999999998</v>
@@ -5952,22 +5955,22 @@
             <v>6966.9599999999991</v>
           </cell>
           <cell r="AA15">
-            <v>4302.3076923076924</v>
+            <v>4536.666666666667</v>
           </cell>
           <cell r="AB15">
-            <v>7.9771142499553012</v>
+            <v>7.5650257163850103</v>
           </cell>
           <cell r="AC15">
-            <v>0.79771142499553016</v>
+            <v>0.7565025716385011</v>
           </cell>
           <cell r="AD15">
-            <v>-870.30769230769238</v>
+            <v>-1104.666666666667</v>
           </cell>
           <cell r="AE15">
-            <v>2151.1538461538462</v>
+            <v>2268.3333333333335</v>
           </cell>
           <cell r="AF15">
-            <v>3021.4615384615386</v>
+            <v>3373.0000000000005</v>
           </cell>
           <cell r="AG15">
             <v>57.2</v>
@@ -6044,22 +6047,22 @@
             <v>743.66</v>
           </cell>
           <cell r="AA16">
-            <v>838.46153846153834</v>
+            <v>928</v>
           </cell>
           <cell r="AB16">
-            <v>2.4568807339449545</v>
+            <v>2.2198275862068968</v>
           </cell>
           <cell r="AC16">
-            <v>0.24568807339449544</v>
+            <v>0.22198275862068967</v>
           </cell>
           <cell r="AD16">
-            <v>-632.46153846153834</v>
+            <v>-722</v>
           </cell>
           <cell r="AE16">
-            <v>419.23076923076917</v>
+            <v>464</v>
           </cell>
           <cell r="AF16">
-            <v>1051.6923076923076</v>
+            <v>1186</v>
           </cell>
           <cell r="AG16">
             <v>7.3571428571428568</v>
@@ -6136,22 +6139,22 @@
             <v>1861.36</v>
           </cell>
           <cell r="AA17">
-            <v>86.92307692307692</v>
+            <v>116.66666666666666</v>
           </cell>
           <cell r="AB17">
-            <v>24.389380530973455</v>
+            <v>18.171428571428571</v>
           </cell>
           <cell r="AC17">
-            <v>2.438938053097345</v>
+            <v>1.8171428571428574</v>
           </cell>
           <cell r="AD17">
-            <v>125.07692307692308</v>
+            <v>95.333333333333343</v>
           </cell>
           <cell r="AE17">
-            <v>43.46153846153846</v>
+            <v>58.333333333333329</v>
           </cell>
           <cell r="AF17">
-            <v>-81.615384615384613</v>
+            <v>-37.000000000000014</v>
           </cell>
           <cell r="AG17">
             <v>17.666666666666668</v>
@@ -6228,22 +6231,22 @@
             <v>5277.51</v>
           </cell>
           <cell r="AA18">
-            <v>12897.692307692307</v>
+            <v>13038</v>
           </cell>
           <cell r="AB18">
-            <v>6.4949603387606611</v>
+            <v>6.4250651940481669</v>
           </cell>
           <cell r="AC18">
-            <v>0.64949603387606614</v>
+            <v>0.64250651940481673</v>
           </cell>
           <cell r="AD18">
-            <v>-4520.6923076923067</v>
+            <v>-4661</v>
           </cell>
           <cell r="AE18">
-            <v>6448.8461538461534</v>
+            <v>6519</v>
           </cell>
           <cell r="AF18">
-            <v>10969.538461538461</v>
+            <v>11180</v>
           </cell>
           <cell r="AG18">
             <v>139.61666666666667</v>
@@ -6320,22 +6323,22 @@
             <v>949.41</v>
           </cell>
           <cell r="AA19">
-            <v>1277.6923076923076</v>
+            <v>1445.3333333333333</v>
           </cell>
           <cell r="AB19">
-            <v>11.794701986754967</v>
+            <v>10.426660516605166</v>
           </cell>
           <cell r="AC19">
-            <v>1.1794701986754967</v>
+            <v>1.0426660516605166</v>
           </cell>
           <cell r="AD19">
-            <v>229.30769230769238</v>
+            <v>61.666666666666742</v>
           </cell>
           <cell r="AE19">
-            <v>638.84615384615381</v>
+            <v>722.66666666666663</v>
           </cell>
           <cell r="AF19">
-            <v>409.53846153846143</v>
+            <v>660.99999999999989</v>
           </cell>
           <cell r="AG19">
             <v>25.116666666666667</v>
@@ -6412,22 +6415,22 @@
             <v>2498.58</v>
           </cell>
           <cell r="AA20">
-            <v>2839.2307692307691</v>
+            <v>3058</v>
           </cell>
           <cell r="AB20">
-            <v>13.968572202655109</v>
+            <v>12.969260954872466</v>
           </cell>
           <cell r="AC20">
-            <v>1.3968572202655107</v>
+            <v>1.2969260954872466</v>
           </cell>
           <cell r="AD20">
-            <v>1126.7692307692309</v>
+            <v>908</v>
           </cell>
           <cell r="AE20">
-            <v>1419.6153846153845</v>
+            <v>1529</v>
           </cell>
           <cell r="AF20">
-            <v>292.84615384615358</v>
+            <v>621</v>
           </cell>
           <cell r="AG20">
             <v>66.099999999999994</v>
@@ -6504,22 +6507,22 @@
             <v>8325.42</v>
           </cell>
           <cell r="AA21">
-            <v>6578.4615384615381</v>
+            <v>7036</v>
           </cell>
           <cell r="AB21">
-            <v>11.610617399438729</v>
+            <v>10.855599772598067</v>
           </cell>
           <cell r="AC21">
-            <v>1.1610617399438727</v>
+            <v>1.0855599772598068</v>
           </cell>
           <cell r="AD21">
-            <v>1059.5384615384619</v>
+            <v>602</v>
           </cell>
           <cell r="AE21">
-            <v>3289.2307692307691</v>
+            <v>3518</v>
           </cell>
           <cell r="AF21">
-            <v>2229.6923076923072</v>
+            <v>2916</v>
           </cell>
           <cell r="AG21">
             <v>141.44444444444446</v>
@@ -6596,22 +6599,22 @@
             <v>4099.4900000000007</v>
           </cell>
           <cell r="AA22">
-            <v>3086.9230769230767</v>
+            <v>3326.666666666667</v>
           </cell>
           <cell r="AB22">
-            <v>12.183653127336157</v>
+            <v>11.30561122244489</v>
           </cell>
           <cell r="AC22">
-            <v>1.2183653127336158</v>
+            <v>1.1305611222444889</v>
           </cell>
           <cell r="AD22">
-            <v>674.07692307692332</v>
+            <v>434.33333333333303</v>
           </cell>
           <cell r="AE22">
-            <v>1543.4615384615383</v>
+            <v>1663.3333333333335</v>
           </cell>
           <cell r="AF22">
-            <v>869.38461538461502</v>
+            <v>1229.0000000000005</v>
           </cell>
           <cell r="AG22">
             <v>69.648148148148152</v>
@@ -6688,22 +6691,22 @@
             <v>38473.719999999994</v>
           </cell>
           <cell r="AA23">
-            <v>33334.615384615383</v>
+            <v>34037.333333333328</v>
           </cell>
           <cell r="AB23">
-            <v>9.9497173185646712</v>
+            <v>9.7443003760576641</v>
           </cell>
           <cell r="AC23">
-            <v>0.99497173185646715</v>
+            <v>0.97443003760576641</v>
           </cell>
           <cell r="AD23">
-            <v>-167.61538461538294</v>
+            <v>-870.33333333332848</v>
           </cell>
           <cell r="AE23">
-            <v>16667.307692307691</v>
+            <v>17018.666666666664</v>
           </cell>
           <cell r="AF23">
-            <v>16834.923076923074</v>
+            <v>17888.999999999993</v>
           </cell>
           <cell r="AG23">
             <v>614.2037037037037</v>
@@ -6780,22 +6783,22 @@
             <v>29054.519999999997</v>
           </cell>
           <cell r="AA24">
-            <v>21931.538461538461</v>
+            <v>22219.333333333336</v>
           </cell>
           <cell r="AB24">
-            <v>11.42053944091754</v>
+            <v>11.272615440007201</v>
           </cell>
           <cell r="AC24">
-            <v>1.1420539440917541</v>
+            <v>1.1272615440007199</v>
           </cell>
           <cell r="AD24">
-            <v>3115.461538461539</v>
+            <v>2827.6666666666642</v>
           </cell>
           <cell r="AE24">
-            <v>10965.76923076923</v>
+            <v>11109.666666666668</v>
           </cell>
           <cell r="AF24">
-            <v>7850.3076923076915</v>
+            <v>8282.0000000000036</v>
           </cell>
           <cell r="AG24">
             <v>463.83333333333331</v>
@@ -6872,22 +6875,22 @@
             <v>30040.519999999997</v>
           </cell>
           <cell r="AA25">
-            <v>21172.307692307691</v>
+            <v>21740.666666666664</v>
           </cell>
           <cell r="AB25">
-            <v>12.231543380322629</v>
+            <v>11.911778234338106</v>
           </cell>
           <cell r="AC25">
-            <v>1.2231543380322627</v>
+            <v>1.1911778234338108</v>
           </cell>
           <cell r="AD25">
-            <v>4724.6923076923085</v>
+            <v>4156.3333333333358</v>
           </cell>
           <cell r="AE25">
-            <v>10586.153846153846</v>
+            <v>10870.333333333332</v>
           </cell>
           <cell r="AF25">
-            <v>5861.4615384615372</v>
+            <v>6713.9999999999964</v>
           </cell>
           <cell r="AG25">
             <v>479.57407407407408</v>
@@ -6964,22 +6967,22 @@
             <v>34369.64</v>
           </cell>
           <cell r="AA26">
-            <v>25528.461538461539</v>
+            <v>25825.333333333332</v>
           </cell>
           <cell r="AB26">
-            <v>11.606261487932022</v>
+            <v>11.472843203056431</v>
           </cell>
           <cell r="AC26">
-            <v>1.1606261487932021</v>
+            <v>1.1472843203056431</v>
           </cell>
           <cell r="AD26">
-            <v>4100.538461538461</v>
+            <v>3803.6666666666679</v>
           </cell>
           <cell r="AE26">
-            <v>12764.23076923077</v>
+            <v>12912.666666666666</v>
           </cell>
           <cell r="AF26">
-            <v>8663.6923076923085</v>
+            <v>9108.9999999999982</v>
           </cell>
           <cell r="AG26">
             <v>548.68518518518522</v>
@@ -7056,22 +7059,22 @@
             <v>1758.56</v>
           </cell>
           <cell r="AA27">
-            <v>301.53846153846155</v>
+            <v>264</v>
           </cell>
           <cell r="AB27">
-            <v>50.275510204081634</v>
+            <v>57.424242424242429</v>
           </cell>
           <cell r="AC27">
-            <v>5.027551020408163</v>
+            <v>5.7424242424242422</v>
           </cell>
           <cell r="AD27">
-            <v>1214.4615384615386</v>
+            <v>1252</v>
           </cell>
           <cell r="AE27">
-            <v>150.76923076923077</v>
+            <v>132</v>
           </cell>
           <cell r="AF27">
-            <v>-1063.6923076923078</v>
+            <v>-1120</v>
           </cell>
           <cell r="AG27">
             <v>28.074074074074073</v>
@@ -7103,13 +7106,13 @@
             <v>3519.4399999999996</v>
           </cell>
           <cell r="L28">
-            <v>15.981361426256079</v>
+            <v>10.953068592057761</v>
           </cell>
           <cell r="M28">
-            <v>4176.6153846153848</v>
+            <v>6094</v>
           </cell>
           <cell r="N28">
-            <v>186.30769230769238</v>
+            <v>-1121</v>
           </cell>
           <cell r="O28">
             <v>251</v>
@@ -7148,22 +7151,22 @@
             <v>5583.08</v>
           </cell>
           <cell r="AA28">
-            <v>1898.4615384615383</v>
+            <v>2770</v>
           </cell>
           <cell r="AB28">
-            <v>25.352106969205835</v>
+            <v>17.375451263537904</v>
           </cell>
           <cell r="AC28">
-            <v>2.5352106969205837</v>
+            <v>1.7375451263537907</v>
           </cell>
           <cell r="AD28">
-            <v>2914.5384615384619</v>
+            <v>2043</v>
           </cell>
           <cell r="AE28">
-            <v>949.23076923076917</v>
+            <v>1385</v>
           </cell>
           <cell r="AF28">
-            <v>-1965.3076923076928</v>
+            <v>-658</v>
           </cell>
           <cell r="AG28">
             <v>89.129629629629633</v>
@@ -7195,13 +7198,13 @@
             <v>3309.4799999999996</v>
           </cell>
           <cell r="L29">
-            <v>12.576805696846389</v>
+            <v>9.0151674741942287</v>
           </cell>
           <cell r="M29">
-            <v>4990.6153846153848</v>
+            <v>6962.2666666666664</v>
           </cell>
           <cell r="N29">
-            <v>-549.69230769230762</v>
+            <v>-1894</v>
           </cell>
           <cell r="O29">
             <v>236</v>
@@ -7240,22 +7243,22 @@
             <v>5281.48</v>
           </cell>
           <cell r="AA29">
-            <v>2268.4615384615386</v>
+            <v>3164.6666666666665</v>
           </cell>
           <cell r="AB29">
-            <v>20.070871481858255</v>
+            <v>14.386981251316623</v>
           </cell>
           <cell r="AC29">
-            <v>2.0070871481858257</v>
+            <v>1.4386981251316622</v>
           </cell>
           <cell r="AD29">
-            <v>2284.5384615384614</v>
+            <v>1388.3333333333335</v>
           </cell>
           <cell r="AE29">
-            <v>1134.2307692307693</v>
+            <v>1582.3333333333333</v>
           </cell>
           <cell r="AF29">
-            <v>-1150.3076923076922</v>
+            <v>193.99999999999977</v>
           </cell>
           <cell r="AG29">
             <v>84.31481481481481</v>
@@ -7287,13 +7290,13 @@
             <v>3259.6</v>
           </cell>
           <cell r="L30">
-            <v>13.069767441860465</v>
+            <v>9.2923280423280428</v>
           </cell>
           <cell r="M30">
-            <v>4730</v>
+            <v>6652.7999999999993</v>
           </cell>
           <cell r="N30">
-            <v>-415</v>
+            <v>-1726</v>
           </cell>
           <cell r="O30">
             <v>236</v>
@@ -7332,22 +7335,22 @@
             <v>6992.48</v>
           </cell>
           <cell r="AA30">
-            <v>2150</v>
+            <v>3024</v>
           </cell>
           <cell r="AB30">
-            <v>28.037209302325582</v>
+            <v>19.933862433862437</v>
           </cell>
           <cell r="AC30">
-            <v>2.8037209302325583</v>
+            <v>1.9933862433862435</v>
           </cell>
           <cell r="AD30">
-            <v>3878</v>
+            <v>3004</v>
           </cell>
           <cell r="AE30">
-            <v>1075</v>
+            <v>1512</v>
           </cell>
           <cell r="AF30">
-            <v>-2803</v>
+            <v>-1492</v>
           </cell>
           <cell r="AG30">
             <v>111.62962962962963</v>
@@ -7424,22 +7427,22 @@
             <v>5045.2800000000007</v>
           </cell>
           <cell r="AA31">
-            <v>2126.1538461538462</v>
+            <v>2249.3333333333335</v>
           </cell>
           <cell r="AB31">
-            <v>6.4482633863965271</v>
+            <v>6.0951393005334911</v>
           </cell>
           <cell r="AC31">
-            <v>0.64482633863965266</v>
+            <v>0.60951393005334908</v>
           </cell>
           <cell r="AD31">
-            <v>-755.15384615384619</v>
+            <v>-878.33333333333348</v>
           </cell>
           <cell r="AE31">
-            <v>1063.0769230769231</v>
+            <v>1124.6666666666667</v>
           </cell>
           <cell r="AF31">
-            <v>1818.2307692307693</v>
+            <v>2003.0000000000002</v>
           </cell>
           <cell r="AG31">
             <v>85.6875</v>
@@ -7516,22 +7519,22 @@
             <v>3606.4</v>
           </cell>
           <cell r="AA32">
-            <v>1213.0769230769231</v>
+            <v>1282</v>
           </cell>
           <cell r="AB32">
-            <v>8.0786303107165498</v>
+            <v>7.64430577223089</v>
           </cell>
           <cell r="AC32">
-            <v>0.80786303107165502</v>
+            <v>0.76443057722308894</v>
           </cell>
           <cell r="AD32">
-            <v>-233.07692307692309</v>
+            <v>-302</v>
           </cell>
           <cell r="AE32">
-            <v>606.53846153846155</v>
+            <v>641</v>
           </cell>
           <cell r="AF32">
-            <v>839.61538461538464</v>
+            <v>943</v>
           </cell>
           <cell r="AG32">
             <v>61.25</v>
@@ -7608,22 +7611,22 @@
             <v>13703.300000000001</v>
           </cell>
           <cell r="AA33">
-            <v>4619.2307692307695</v>
+            <v>4766.666666666667</v>
           </cell>
           <cell r="AB33">
-            <v>7.1483763530391338</v>
+            <v>6.9272727272727268</v>
           </cell>
           <cell r="AC33">
-            <v>0.71483763530391331</v>
+            <v>0.69272727272727264</v>
           </cell>
           <cell r="AD33">
-            <v>-1317.2307692307695</v>
+            <v>-1464.666666666667</v>
           </cell>
           <cell r="AE33">
-            <v>2309.6153846153848</v>
+            <v>2383.3333333333335</v>
           </cell>
           <cell r="AF33">
-            <v>3626.8461538461543</v>
+            <v>3848.0000000000005</v>
           </cell>
           <cell r="AG33">
             <v>206.375</v>
@@ -7700,22 +7703,22 @@
             <v>26174.050000000003</v>
           </cell>
           <cell r="AA34">
-            <v>7240.7692307692305</v>
+            <v>7453.3333333333339</v>
           </cell>
           <cell r="AB34">
-            <v>8.7104005099330717</v>
+            <v>8.4619856887298752</v>
           </cell>
           <cell r="AC34">
-            <v>0.87104005099330717</v>
+            <v>0.84619856887298739</v>
           </cell>
           <cell r="AD34">
-            <v>-933.76923076923049</v>
+            <v>-1146.3333333333339</v>
           </cell>
           <cell r="AE34">
-            <v>3620.3846153846152</v>
+            <v>3726.666666666667</v>
           </cell>
           <cell r="AF34">
-            <v>4554.1538461538457</v>
+            <v>4873.0000000000009</v>
           </cell>
           <cell r="AG34">
             <v>394.1875</v>
@@ -7792,7 +7795,7 @@
             <v>0</v>
           </cell>
           <cell r="AA35">
-            <v>76.92307692307692</v>
+            <v>66.666666666666671</v>
           </cell>
           <cell r="AB35">
             <v>0</v>
@@ -7801,13 +7804,13 @@
             <v>0</v>
           </cell>
           <cell r="AD35">
-            <v>-76.92307692307692</v>
+            <v>-66.666666666666671</v>
           </cell>
           <cell r="AE35">
-            <v>38.46153846153846</v>
+            <v>33.333333333333336</v>
           </cell>
           <cell r="AF35">
-            <v>115.38461538461539</v>
+            <v>100</v>
           </cell>
           <cell r="AG35">
             <v>0</v>
@@ -7884,22 +7887,22 @@
             <v>2253.4500000000003</v>
           </cell>
           <cell r="AA36">
-            <v>1310.7692307692307</v>
+            <v>1136</v>
           </cell>
           <cell r="AB36">
-            <v>4.142605633802817</v>
+            <v>4.779929577464789</v>
           </cell>
           <cell r="AC36">
-            <v>0.41426056338028172</v>
+            <v>0.47799295774647887</v>
           </cell>
           <cell r="AD36">
-            <v>-767.76923076923072</v>
+            <v>-593</v>
           </cell>
           <cell r="AE36">
-            <v>655.38461538461536</v>
+            <v>568</v>
           </cell>
           <cell r="AF36">
-            <v>1423.1538461538462</v>
+            <v>1161</v>
           </cell>
           <cell r="AG36">
             <v>33.9375</v>
@@ -7976,22 +7979,22 @@
             <v>16573.84</v>
           </cell>
           <cell r="AA37">
-            <v>6125.3846153846152</v>
+            <v>6322.6666666666661</v>
           </cell>
           <cell r="AB37">
-            <v>16.599773954539746</v>
+            <v>16.081822016026994</v>
           </cell>
           <cell r="AC37">
-            <v>1.6599773954539747</v>
+            <v>1.6081822016026994</v>
           </cell>
           <cell r="AD37">
-            <v>4042.6153846153848</v>
+            <v>3845.3333333333339</v>
           </cell>
           <cell r="AE37">
-            <v>3062.6923076923076</v>
+            <v>3161.333333333333</v>
           </cell>
           <cell r="AF37">
-            <v>-979.92307692307713</v>
+            <v>-684.00000000000091</v>
           </cell>
           <cell r="AG37">
             <v>188.2962962962963</v>
@@ -8068,22 +8071,22 @@
             <v>16068.539999999999</v>
           </cell>
           <cell r="AA38">
-            <v>10000</v>
+            <v>10202.666666666666</v>
           </cell>
           <cell r="AB38">
-            <v>9.8580000000000005</v>
+            <v>9.6621798222686888</v>
           </cell>
           <cell r="AC38">
-            <v>0.98580000000000001</v>
+            <v>0.96621798222686883</v>
           </cell>
           <cell r="AD38">
-            <v>-142</v>
+            <v>-344.66666666666606</v>
           </cell>
           <cell r="AE38">
-            <v>5000</v>
+            <v>5101.333333333333</v>
           </cell>
           <cell r="AF38">
-            <v>5142</v>
+            <v>5445.9999999999991</v>
           </cell>
           <cell r="AG38">
             <v>182.55555555555554</v>
@@ -8160,22 +8163,22 @@
             <v>3204.58</v>
           </cell>
           <cell r="AA39">
-            <v>4555.3846153846152</v>
+            <v>4895.3333333333339</v>
           </cell>
           <cell r="AB39">
-            <v>4.3157716987504218</v>
+            <v>4.0160697262699161</v>
           </cell>
           <cell r="AC39">
-            <v>0.43157716987504224</v>
+            <v>0.40160697262699163</v>
           </cell>
           <cell r="AD39">
-            <v>-2589.3846153846152</v>
+            <v>-2929.3333333333339</v>
           </cell>
           <cell r="AE39">
-            <v>2277.6923076923076</v>
+            <v>2447.666666666667</v>
           </cell>
           <cell r="AF39">
-            <v>4867.0769230769229</v>
+            <v>5377.0000000000009</v>
           </cell>
           <cell r="AG39">
             <v>36.407407407407405</v>
@@ -8252,22 +8255,22 @@
             <v>7409.98</v>
           </cell>
           <cell r="AA40">
-            <v>3306.1538461538466</v>
+            <v>3359.3333333333335</v>
           </cell>
           <cell r="AB40">
-            <v>13.750116333178221</v>
+            <v>13.532446914070253</v>
           </cell>
           <cell r="AC40">
-            <v>1.3750116333178219</v>
+            <v>1.3532446914070251</v>
           </cell>
           <cell r="AD40">
-            <v>1239.8461538461534</v>
+            <v>1186.6666666666665</v>
           </cell>
           <cell r="AE40">
-            <v>1653.0769230769233</v>
+            <v>1679.6666666666667</v>
           </cell>
           <cell r="AF40">
-            <v>413.23076923076997</v>
+            <v>493.00000000000023</v>
           </cell>
           <cell r="AG40">
             <v>84.18518518518519</v>
@@ -8528,22 +8531,22 @@
             <v>4065.15</v>
           </cell>
           <cell r="AA43">
-            <v>1216.1538461538462</v>
+            <v>1175.3333333333333</v>
           </cell>
           <cell r="AB43">
-            <v>5.4351676154332704</v>
+            <v>5.6239364719228586</v>
           </cell>
           <cell r="AC43">
-            <v>0.54351676154332695</v>
+            <v>0.56239364719228591</v>
           </cell>
           <cell r="AD43">
-            <v>-555.15384615384619</v>
+            <v>-514.33333333333326</v>
           </cell>
           <cell r="AE43">
-            <v>608.07692307692309</v>
+            <v>587.66666666666663</v>
           </cell>
           <cell r="AF43">
-            <v>1163.2307692307693</v>
+            <v>1102</v>
           </cell>
           <cell r="AG43">
             <v>12.24074074074074</v>
@@ -8620,22 +8623,22 @@
             <v>6980.25</v>
           </cell>
           <cell r="AA44">
-            <v>1177.6923076923076</v>
+            <v>1271.3333333333335</v>
           </cell>
           <cell r="AB44">
-            <v>9.6374918354016987</v>
+            <v>8.9276350288411095</v>
           </cell>
           <cell r="AC44">
-            <v>0.96374918354016992</v>
+            <v>0.8927635028841111</v>
           </cell>
           <cell r="AD44">
-            <v>-42.692307692307622</v>
+            <v>-136.33333333333348</v>
           </cell>
           <cell r="AE44">
-            <v>588.84615384615381</v>
+            <v>635.66666666666674</v>
           </cell>
           <cell r="AF44">
-            <v>631.53846153846143</v>
+            <v>772.00000000000023</v>
           </cell>
           <cell r="AG44">
             <v>21.018518518518519</v>
@@ -8712,22 +8715,22 @@
             <v>4816.32</v>
           </cell>
           <cell r="AA45">
-            <v>5425.3846153846152</v>
+            <v>5564</v>
           </cell>
           <cell r="AB45">
-            <v>7.6529136537643554</v>
+            <v>7.4622573687994249</v>
           </cell>
           <cell r="AC45">
-            <v>0.76529136537643561</v>
+            <v>0.74622573687994254</v>
           </cell>
           <cell r="AD45">
-            <v>-1273.3846153846152</v>
+            <v>-1412</v>
           </cell>
           <cell r="AE45">
-            <v>2712.6923076923076</v>
+            <v>2782</v>
           </cell>
           <cell r="AF45">
-            <v>3986.0769230769229</v>
+            <v>4194</v>
           </cell>
           <cell r="AG45">
             <v>76.888888888888886</v>
@@ -8804,22 +8807,22 @@
             <v>9920.32</v>
           </cell>
           <cell r="AA46">
-            <v>6050</v>
+            <v>5998</v>
           </cell>
           <cell r="AB46">
-            <v>14.135537190082644</v>
+            <v>14.258086028676226</v>
           </cell>
           <cell r="AC46">
-            <v>1.4135537190082645</v>
+            <v>1.4258086028676225</v>
           </cell>
           <cell r="AD46">
-            <v>2502</v>
+            <v>2554</v>
           </cell>
           <cell r="AE46">
-            <v>3025</v>
+            <v>2999</v>
           </cell>
           <cell r="AF46">
-            <v>523</v>
+            <v>445</v>
           </cell>
           <cell r="AG46">
             <v>158.37037037037038</v>
@@ -8896,22 +8899,22 @@
             <v>7810.28</v>
           </cell>
           <cell r="AA47">
-            <v>7557.6923076923067</v>
+            <v>7872</v>
           </cell>
           <cell r="AB47">
-            <v>8.9088040712468199</v>
+            <v>8.5530995934959346</v>
           </cell>
           <cell r="AC47">
-            <v>0.89088040712468208</v>
+            <v>0.85530995934959353</v>
           </cell>
           <cell r="AD47">
-            <v>-824.69230769230671</v>
+            <v>-1139</v>
           </cell>
           <cell r="AE47">
-            <v>3778.8461538461534</v>
+            <v>3936</v>
           </cell>
           <cell r="AF47">
-            <v>4603.5384615384601</v>
+            <v>5075</v>
           </cell>
           <cell r="AG47">
             <v>124.68518518518519</v>
@@ -8988,22 +8991,22 @@
             <v>6063.32</v>
           </cell>
           <cell r="AA48">
-            <v>5266.1538461538466</v>
+            <v>5340</v>
           </cell>
           <cell r="AB48">
-            <v>9.9256500146070685</v>
+            <v>9.7883895131086138</v>
           </cell>
           <cell r="AC48">
-            <v>0.99256500146070692</v>
+            <v>0.9788389513108614</v>
           </cell>
           <cell r="AD48">
-            <v>-39.153846153846644</v>
+            <v>-113</v>
           </cell>
           <cell r="AE48">
-            <v>2633.0769230769233</v>
+            <v>2670</v>
           </cell>
           <cell r="AF48">
-            <v>2672.23076923077</v>
+            <v>2783</v>
           </cell>
           <cell r="AG48">
             <v>96.796296296296291</v>
@@ -9080,22 +9083,22 @@
             <v>216</v>
           </cell>
           <cell r="AA49">
-            <v>20</v>
+            <v>23.333333333333336</v>
           </cell>
           <cell r="AB49">
-            <v>6</v>
+            <v>5.1428571428571423</v>
           </cell>
           <cell r="AC49">
-            <v>0.6</v>
+            <v>0.51428571428571423</v>
           </cell>
           <cell r="AD49">
-            <v>-8</v>
+            <v>-11.333333333333336</v>
           </cell>
           <cell r="AE49">
-            <v>10</v>
+            <v>11.666666666666668</v>
           </cell>
           <cell r="AF49">
-            <v>18</v>
+            <v>23.000000000000004</v>
           </cell>
           <cell r="AG49">
             <v>6</v>
@@ -9172,7 +9175,7 @@
             <v>198</v>
           </cell>
           <cell r="AA50">
-            <v>0</v>
+            <v>1.3333333333333333</v>
           </cell>
           <cell r="AB50">
             <v>0</v>
@@ -9181,13 +9184,13 @@
             <v>0</v>
           </cell>
           <cell r="AD50">
-            <v>11</v>
+            <v>9.6666666666666661</v>
           </cell>
           <cell r="AE50">
-            <v>0</v>
+            <v>0.66666666666666663</v>
           </cell>
           <cell r="AF50">
-            <v>-11</v>
+            <v>-9</v>
           </cell>
           <cell r="AG50">
             <v>5.5</v>
@@ -9264,22 +9267,22 @@
             <v>49.879999999999995</v>
           </cell>
           <cell r="AA51">
-            <v>229.23076923076923</v>
+            <v>699.33333333333337</v>
           </cell>
           <cell r="AB51">
-            <v>1.8758389261744965</v>
+            <v>0.61487130600571971</v>
           </cell>
           <cell r="AC51">
-            <v>0.18758389261744968</v>
+            <v>6.1487130600571968E-2</v>
           </cell>
           <cell r="AD51">
-            <v>-186.23076923076923</v>
+            <v>-656.33333333333337</v>
           </cell>
           <cell r="AE51">
-            <v>114.61538461538461</v>
+            <v>349.66666666666669</v>
           </cell>
           <cell r="AF51">
-            <v>300.84615384615381</v>
+            <v>1006</v>
           </cell>
           <cell r="AG51">
             <v>1.075</v>
@@ -9448,22 +9451,22 @@
             <v>4.6399999999999997</v>
           </cell>
           <cell r="AA53">
-            <v>547.69230769230762</v>
+            <v>474.66666666666669</v>
           </cell>
           <cell r="AB53">
-            <v>7.3033707865168551E-2</v>
+            <v>8.4269662921348312E-2</v>
           </cell>
           <cell r="AC53">
-            <v>7.3033707865168551E-3</v>
+            <v>8.4269662921348312E-3</v>
           </cell>
           <cell r="AD53">
-            <v>-543.69230769230762</v>
+            <v>-470.66666666666669</v>
           </cell>
           <cell r="AE53">
-            <v>273.84615384615381</v>
+            <v>237.33333333333334</v>
           </cell>
           <cell r="AF53">
-            <v>817.53846153846143</v>
+            <v>708</v>
           </cell>
           <cell r="AG53">
             <v>0.1</v>
@@ -9540,22 +9543,22 @@
             <v>18284.13</v>
           </cell>
           <cell r="AA54">
-            <v>2767.6923076923076</v>
+            <v>2757.3333333333335</v>
           </cell>
           <cell r="AB54">
-            <v>81.55892162312395</v>
+            <v>81.865328820116048</v>
           </cell>
           <cell r="AC54">
-            <v>8.1558921623123961</v>
+            <v>8.1865328820116048</v>
           </cell>
           <cell r="AD54">
-            <v>19805.307692307691</v>
+            <v>19815.666666666668</v>
           </cell>
           <cell r="AE54">
-            <v>1383.8461538461538</v>
+            <v>1378.6666666666667</v>
           </cell>
           <cell r="AF54">
-            <v>-18421.461538461539</v>
+            <v>-18437</v>
           </cell>
           <cell r="AG54">
             <v>1881.0833333333333</v>
@@ -9632,22 +9635,22 @@
             <v>23675.49</v>
           </cell>
           <cell r="AA55">
-            <v>4797.6923076923076</v>
+            <v>4637.3333333333339</v>
           </cell>
           <cell r="AB55">
-            <v>60.923039923039923</v>
+            <v>63.029758481886134</v>
           </cell>
           <cell r="AC55">
-            <v>6.0923039923039921</v>
+            <v>6.3029758481886136</v>
           </cell>
           <cell r="AD55">
-            <v>24431.307692307691</v>
+            <v>24591.666666666664</v>
           </cell>
           <cell r="AE55">
-            <v>2398.8461538461538</v>
+            <v>2318.666666666667</v>
           </cell>
           <cell r="AF55">
-            <v>-22032.461538461539</v>
+            <v>-22272.999999999996</v>
           </cell>
           <cell r="AG55">
             <v>2435.75</v>
@@ -9724,22 +9727,22 @@
             <v>13081.5</v>
           </cell>
           <cell r="AA56">
-            <v>2890.7692307692309</v>
+            <v>2783.333333333333</v>
           </cell>
           <cell r="AB56">
-            <v>55.86748270356572</v>
+            <v>58.02395209580839</v>
           </cell>
           <cell r="AC56">
-            <v>5.5867482703565727</v>
+            <v>5.8023952095808387</v>
           </cell>
           <cell r="AD56">
-            <v>13259.23076923077</v>
+            <v>13366.666666666668</v>
           </cell>
           <cell r="AE56">
-            <v>1445.3846153846155</v>
+            <v>1391.6666666666665</v>
           </cell>
           <cell r="AF56">
-            <v>-11813.846153846154</v>
+            <v>-11975.000000000002</v>
           </cell>
           <cell r="AG56">
             <v>1345.8333333333333</v>
@@ -9816,22 +9819,22 @@
             <v>15625.710000000001</v>
           </cell>
           <cell r="AA57">
-            <v>2549.2307692307695</v>
+            <v>2464</v>
           </cell>
           <cell r="AB57">
-            <v>75.673808086904032</v>
+            <v>78.291396103896105</v>
           </cell>
           <cell r="AC57">
-            <v>7.5673808086904035</v>
+            <v>7.8291396103896105</v>
           </cell>
           <cell r="AD57">
-            <v>16741.76923076923</v>
+            <v>16827</v>
           </cell>
           <cell r="AE57">
-            <v>1274.6153846153848</v>
+            <v>1232</v>
           </cell>
           <cell r="AF57">
-            <v>-15467.153846153846</v>
+            <v>-15595</v>
           </cell>
           <cell r="AG57">
             <v>1607.5833333333333</v>
@@ -9908,22 +9911,22 @@
             <v>1873.3000000000002</v>
           </cell>
           <cell r="AA58">
-            <v>426.15384615384613</v>
+            <v>428</v>
           </cell>
           <cell r="AB58">
-            <v>16.777978339350181</v>
+            <v>16.705607476635514</v>
           </cell>
           <cell r="AC58">
-            <v>1.6777978339350181</v>
+            <v>1.6705607476635513</v>
           </cell>
           <cell r="AD58">
-            <v>288.84615384615387</v>
+            <v>287</v>
           </cell>
           <cell r="AE58">
-            <v>213.07692307692307</v>
+            <v>214</v>
           </cell>
           <cell r="AF58">
-            <v>-75.769230769230802</v>
+            <v>-73</v>
           </cell>
           <cell r="AG58">
             <v>119.16666666666667</v>
@@ -10000,22 +10003,22 @@
             <v>1011.32</v>
           </cell>
           <cell r="AA59">
-            <v>827.69230769230774</v>
+            <v>840</v>
           </cell>
           <cell r="AB59">
-            <v>4.6635687732342008</v>
+            <v>4.5952380952380949</v>
           </cell>
           <cell r="AC59">
-            <v>0.46635687732342007</v>
+            <v>0.4595238095238095</v>
           </cell>
           <cell r="AD59">
-            <v>-441.69230769230774</v>
+            <v>-454</v>
           </cell>
           <cell r="AE59">
-            <v>413.84615384615387</v>
+            <v>420</v>
           </cell>
           <cell r="AF59">
-            <v>855.53846153846166</v>
+            <v>874</v>
           </cell>
           <cell r="AG59">
             <v>64.333333333333329</v>
@@ -10092,22 +10095,22 @@
             <v>780.76</v>
           </cell>
           <cell r="AA60">
-            <v>470.76923076923083</v>
+            <v>469.33333333333331</v>
           </cell>
           <cell r="AB60">
-            <v>6.3300653594771239</v>
+            <v>6.3494318181818183</v>
           </cell>
           <cell r="AC60">
-            <v>0.63300653594771239</v>
+            <v>0.63494318181818188</v>
           </cell>
           <cell r="AD60">
-            <v>-172.76923076923083</v>
+            <v>-171.33333333333331</v>
           </cell>
           <cell r="AE60">
-            <v>235.38461538461542</v>
+            <v>234.66666666666666</v>
           </cell>
           <cell r="AF60">
-            <v>408.15384615384625</v>
+            <v>406</v>
           </cell>
           <cell r="AG60">
             <v>49.666666666666664</v>
@@ -10184,22 +10187,22 @@
             <v>382.52000000000004</v>
           </cell>
           <cell r="AA61">
-            <v>396.92307692307691</v>
+            <v>382</v>
           </cell>
           <cell r="AB61">
-            <v>3.6782945736434107</v>
+            <v>3.8219895287958114</v>
           </cell>
           <cell r="AC61">
-            <v>0.36782945736434108</v>
+            <v>0.38219895287958117</v>
           </cell>
           <cell r="AD61">
-            <v>-250.92307692307691</v>
+            <v>-236</v>
           </cell>
           <cell r="AE61">
-            <v>198.46153846153845</v>
+            <v>191</v>
           </cell>
           <cell r="AF61">
-            <v>449.38461538461536</v>
+            <v>427</v>
           </cell>
           <cell r="AG61">
             <v>24.333333333333332</v>
@@ -10210,7 +10213,7 @@
             <v>Units Produce</v>
           </cell>
           <cell r="AF62">
-            <v>108920.07692307689</v>
+            <v>117524</v>
           </cell>
         </row>
       </sheetData>
@@ -10221,6 +10224,9 @@
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10545,212 +10551,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="66" t="s">
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="66"/>
-      <c r="AC1" s="66"/>
-      <c r="AD1" s="66"/>
-      <c r="AE1" s="66"/>
-      <c r="AF1" s="66"/>
-      <c r="AG1" s="66"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="66"/>
-      <c r="AB2" s="66"/>
-      <c r="AC2" s="66"/>
-      <c r="AD2" s="66"/>
-      <c r="AE2" s="66"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
+      <c r="AD2" s="63"/>
+      <c r="AE2" s="63"/>
+      <c r="AF2" s="63"/>
+      <c r="AG2" s="63"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="66"/>
-      <c r="AB3" s="66"/>
-      <c r="AC3" s="66"/>
-      <c r="AD3" s="66"/>
-      <c r="AE3" s="66"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="62"/>
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="63"/>
+      <c r="AD3" s="63"/>
+      <c r="AE3" s="63"/>
+      <c r="AF3" s="63"/>
+      <c r="AG3" s="63"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="66"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="62"/>
+      <c r="Y4" s="62"/>
+      <c r="Z4" s="62"/>
+      <c r="AA4" s="63"/>
+      <c r="AB4" s="63"/>
+      <c r="AC4" s="63"/>
+      <c r="AD4" s="63"/>
+      <c r="AE4" s="63"/>
+      <c r="AF4" s="63"/>
+      <c r="AG4" s="63"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="66"/>
-      <c r="AB5" s="66"/>
-      <c r="AC5" s="66"/>
-      <c r="AD5" s="66"/>
-      <c r="AE5" s="66"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="62"/>
+      <c r="Z5" s="62"/>
+      <c r="AA5" s="63"/>
+      <c r="AB5" s="63"/>
+      <c r="AC5" s="63"/>
+      <c r="AD5" s="63"/>
+      <c r="AE5" s="63"/>
+      <c r="AF5" s="63"/>
+      <c r="AG5" s="63"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="66"/>
-      <c r="AB6" s="66"/>
-      <c r="AC6" s="66"/>
-      <c r="AD6" s="66"/>
-      <c r="AE6" s="66"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="62"/>
+      <c r="X6" s="62"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="63"/>
+      <c r="AB6" s="63"/>
+      <c r="AC6" s="63"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="63"/>
+      <c r="AG6" s="63"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
@@ -11121,27 +11127,27 @@
       </c>
       <c r="AA13" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA13</f>
-        <v>10726.923076923076</v>
+        <v>11018.666666666666</v>
       </c>
       <c r="AB13" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB13</f>
-        <v>9.326998924345645</v>
+        <v>9.0800459825750259</v>
       </c>
       <c r="AC13" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC13</f>
-        <v>0.93269989243456441</v>
+        <v>0.90800459825750246</v>
       </c>
       <c r="AD13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD13</f>
-        <v>-721.92307692307622</v>
+        <v>-1013.6666666666661</v>
       </c>
       <c r="AE13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE13</f>
-        <v>5363.4615384615381</v>
+        <v>5509.333333333333</v>
       </c>
       <c r="AF13" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF13</f>
-        <v>6085.3846153846143</v>
+        <v>6522.9999999999991</v>
       </c>
       <c r="AG13" s="27">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG13</f>
@@ -11249,27 +11255,27 @@
       </c>
       <c r="AA14" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA14</f>
-        <v>766.92307692307691</v>
+        <v>791.33333333333337</v>
       </c>
       <c r="AB14" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB14</f>
-        <v>7.2888665997993982</v>
+        <v>7.0640269587194604</v>
       </c>
       <c r="AC14" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC14</f>
-        <v>0.72888665997993984</v>
+        <v>0.70640269587194604</v>
       </c>
       <c r="AD14" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD14</f>
-        <v>-207.92307692307691</v>
+        <v>-232.33333333333337</v>
       </c>
       <c r="AE14" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE14</f>
-        <v>383.46153846153845</v>
+        <v>395.66666666666669</v>
       </c>
       <c r="AF14" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF14</f>
-        <v>591.38461538461536</v>
+        <v>628</v>
       </c>
       <c r="AG14" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG14</f>
@@ -11377,27 +11383,27 @@
       </c>
       <c r="AA15" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA15</f>
-        <v>4302.3076923076924</v>
+        <v>4536.666666666667</v>
       </c>
       <c r="AB15" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB15</f>
-        <v>7.9771142499553012</v>
+        <v>7.5650257163850103</v>
       </c>
       <c r="AC15" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC15</f>
-        <v>0.79771142499553016</v>
+        <v>0.7565025716385011</v>
       </c>
       <c r="AD15" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD15</f>
-        <v>-870.30769230769238</v>
+        <v>-1104.666666666667</v>
       </c>
       <c r="AE15" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE15</f>
-        <v>2151.1538461538462</v>
+        <v>2268.3333333333335</v>
       </c>
       <c r="AF15" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF15</f>
-        <v>3021.4615384615386</v>
+        <v>3373.0000000000005</v>
       </c>
       <c r="AG15" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG15</f>
@@ -11505,27 +11511,27 @@
       </c>
       <c r="AA16" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA16</f>
-        <v>838.46153846153834</v>
+        <v>928</v>
       </c>
       <c r="AB16" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB16</f>
-        <v>2.4568807339449545</v>
+        <v>2.2198275862068968</v>
       </c>
       <c r="AC16" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC16</f>
-        <v>0.24568807339449544</v>
+        <v>0.22198275862068967</v>
       </c>
       <c r="AD16" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD16</f>
-        <v>-632.46153846153834</v>
+        <v>-722</v>
       </c>
       <c r="AE16" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE16</f>
-        <v>419.23076923076917</v>
+        <v>464</v>
       </c>
       <c r="AF16" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF16</f>
-        <v>1051.6923076923076</v>
+        <v>1186</v>
       </c>
       <c r="AG16" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG16</f>
@@ -11633,27 +11639,27 @@
       </c>
       <c r="AA17" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA17</f>
-        <v>86.92307692307692</v>
+        <v>116.66666666666666</v>
       </c>
       <c r="AB17" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB17</f>
-        <v>24.389380530973455</v>
+        <v>18.171428571428571</v>
       </c>
       <c r="AC17" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC17</f>
-        <v>2.438938053097345</v>
+        <v>1.8171428571428574</v>
       </c>
       <c r="AD17" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD17</f>
-        <v>125.07692307692308</v>
+        <v>95.333333333333343</v>
       </c>
       <c r="AE17" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE17</f>
-        <v>43.46153846153846</v>
+        <v>58.333333333333329</v>
       </c>
       <c r="AF17" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF17</f>
-        <v>-81.615384615384613</v>
+        <v>-37.000000000000014</v>
       </c>
       <c r="AG17" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG17</f>
@@ -11761,27 +11767,27 @@
       </c>
       <c r="AA18" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA18</f>
-        <v>12897.692307692307</v>
+        <v>13038</v>
       </c>
       <c r="AB18" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB18</f>
-        <v>6.4949603387606611</v>
+        <v>6.4250651940481669</v>
       </c>
       <c r="AC18" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC18</f>
-        <v>0.64949603387606614</v>
+        <v>0.64250651940481673</v>
       </c>
       <c r="AD18" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD18</f>
-        <v>-4520.6923076923067</v>
+        <v>-4661</v>
       </c>
       <c r="AE18" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE18</f>
-        <v>6448.8461538461534</v>
+        <v>6519</v>
       </c>
       <c r="AF18" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF18</f>
-        <v>10969.538461538461</v>
+        <v>11180</v>
       </c>
       <c r="AG18" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG18</f>
@@ -11889,27 +11895,27 @@
       </c>
       <c r="AA19" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA19</f>
-        <v>1277.6923076923076</v>
+        <v>1445.3333333333333</v>
       </c>
       <c r="AB19" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB19</f>
-        <v>11.794701986754967</v>
+        <v>10.426660516605166</v>
       </c>
       <c r="AC19" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC19</f>
-        <v>1.1794701986754967</v>
+        <v>1.0426660516605166</v>
       </c>
       <c r="AD19" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD19</f>
-        <v>229.30769230769238</v>
+        <v>61.666666666666742</v>
       </c>
       <c r="AE19" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE19</f>
-        <v>638.84615384615381</v>
+        <v>722.66666666666663</v>
       </c>
       <c r="AF19" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF19</f>
-        <v>409.53846153846143</v>
+        <v>660.99999999999989</v>
       </c>
       <c r="AG19" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG19</f>
@@ -12017,27 +12023,27 @@
       </c>
       <c r="AA20" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA20</f>
-        <v>2839.2307692307691</v>
+        <v>3058</v>
       </c>
       <c r="AB20" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB20</f>
-        <v>13.968572202655109</v>
+        <v>12.969260954872466</v>
       </c>
       <c r="AC20" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC20</f>
-        <v>1.3968572202655107</v>
+        <v>1.2969260954872466</v>
       </c>
       <c r="AD20" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD20</f>
-        <v>1126.7692307692309</v>
+        <v>908</v>
       </c>
       <c r="AE20" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE20</f>
-        <v>1419.6153846153845</v>
+        <v>1529</v>
       </c>
       <c r="AF20" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF20</f>
-        <v>292.84615384615358</v>
+        <v>621</v>
       </c>
       <c r="AG20" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG20</f>
@@ -12145,27 +12151,27 @@
       </c>
       <c r="AA21" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA21</f>
-        <v>6578.4615384615381</v>
+        <v>7036</v>
       </c>
       <c r="AB21" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB21</f>
-        <v>11.610617399438729</v>
+        <v>10.855599772598067</v>
       </c>
       <c r="AC21" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC21</f>
-        <v>1.1610617399438727</v>
+        <v>1.0855599772598068</v>
       </c>
       <c r="AD21" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD21</f>
-        <v>1059.5384615384619</v>
+        <v>602</v>
       </c>
       <c r="AE21" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE21</f>
-        <v>3289.2307692307691</v>
+        <v>3518</v>
       </c>
       <c r="AF21" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF21</f>
-        <v>2229.6923076923072</v>
+        <v>2916</v>
       </c>
       <c r="AG21" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG21</f>
@@ -12273,27 +12279,27 @@
       </c>
       <c r="AA22" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA22</f>
-        <v>3086.9230769230767</v>
+        <v>3326.666666666667</v>
       </c>
       <c r="AB22" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB22</f>
-        <v>12.183653127336157</v>
+        <v>11.30561122244489</v>
       </c>
       <c r="AC22" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC22</f>
-        <v>1.2183653127336158</v>
+        <v>1.1305611222444889</v>
       </c>
       <c r="AD22" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD22</f>
-        <v>674.07692307692332</v>
+        <v>434.33333333333303</v>
       </c>
       <c r="AE22" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE22</f>
-        <v>1543.4615384615383</v>
+        <v>1663.3333333333335</v>
       </c>
       <c r="AF22" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF22</f>
-        <v>869.38461538461502</v>
+        <v>1229.0000000000005</v>
       </c>
       <c r="AG22" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG22</f>
@@ -12401,27 +12407,27 @@
       </c>
       <c r="AA23" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA23</f>
-        <v>33334.615384615383</v>
+        <v>34037.333333333328</v>
       </c>
       <c r="AB23" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB23</f>
-        <v>9.9497173185646712</v>
+        <v>9.7443003760576641</v>
       </c>
       <c r="AC23" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC23</f>
-        <v>0.99497173185646715</v>
+        <v>0.97443003760576641</v>
       </c>
       <c r="AD23" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD23</f>
-        <v>-167.61538461538294</v>
+        <v>-870.33333333332848</v>
       </c>
       <c r="AE23" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE23</f>
-        <v>16667.307692307691</v>
+        <v>17018.666666666664</v>
       </c>
       <c r="AF23" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF23</f>
-        <v>16834.923076923074</v>
+        <v>17888.999999999993</v>
       </c>
       <c r="AG23" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG23</f>
@@ -12529,27 +12535,27 @@
       </c>
       <c r="AA24" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA24</f>
-        <v>21931.538461538461</v>
+        <v>22219.333333333336</v>
       </c>
       <c r="AB24" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB24</f>
-        <v>11.42053944091754</v>
+        <v>11.272615440007201</v>
       </c>
       <c r="AC24" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC24</f>
-        <v>1.1420539440917541</v>
+        <v>1.1272615440007199</v>
       </c>
       <c r="AD24" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD24</f>
-        <v>3115.461538461539</v>
+        <v>2827.6666666666642</v>
       </c>
       <c r="AE24" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE24</f>
-        <v>10965.76923076923</v>
+        <v>11109.666666666668</v>
       </c>
       <c r="AF24" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF24</f>
-        <v>7850.3076923076915</v>
+        <v>8282.0000000000036</v>
       </c>
       <c r="AG24" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG24</f>
@@ -12657,27 +12663,27 @@
       </c>
       <c r="AA25" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA25</f>
-        <v>21172.307692307691</v>
+        <v>21740.666666666664</v>
       </c>
       <c r="AB25" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB25</f>
-        <v>12.231543380322629</v>
+        <v>11.911778234338106</v>
       </c>
       <c r="AC25" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC25</f>
-        <v>1.2231543380322627</v>
+        <v>1.1911778234338108</v>
       </c>
       <c r="AD25" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD25</f>
-        <v>4724.6923076923085</v>
+        <v>4156.3333333333358</v>
       </c>
       <c r="AE25" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE25</f>
-        <v>10586.153846153846</v>
+        <v>10870.333333333332</v>
       </c>
       <c r="AF25" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF25</f>
-        <v>5861.4615384615372</v>
+        <v>6713.9999999999964</v>
       </c>
       <c r="AG25" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG25</f>
@@ -12785,27 +12791,27 @@
       </c>
       <c r="AA26" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA26</f>
-        <v>25528.461538461539</v>
+        <v>25825.333333333332</v>
       </c>
       <c r="AB26" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB26</f>
-        <v>11.606261487932022</v>
+        <v>11.472843203056431</v>
       </c>
       <c r="AC26" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC26</f>
-        <v>1.1606261487932021</v>
+        <v>1.1472843203056431</v>
       </c>
       <c r="AD26" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD26</f>
-        <v>4100.538461538461</v>
+        <v>3803.6666666666679</v>
       </c>
       <c r="AE26" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE26</f>
-        <v>12764.23076923077</v>
+        <v>12912.666666666666</v>
       </c>
       <c r="AF26" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF26</f>
-        <v>8663.6923076923085</v>
+        <v>9108.9999999999982</v>
       </c>
       <c r="AG26" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG26</f>
@@ -12913,27 +12919,27 @@
       </c>
       <c r="AA27" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA27</f>
-        <v>301.53846153846155</v>
+        <v>264</v>
       </c>
       <c r="AB27" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB27</f>
-        <v>50.275510204081634</v>
+        <v>57.424242424242429</v>
       </c>
       <c r="AC27" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC27</f>
-        <v>5.027551020408163</v>
+        <v>5.7424242424242422</v>
       </c>
       <c r="AD27" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD27</f>
-        <v>1214.4615384615386</v>
+        <v>1252</v>
       </c>
       <c r="AE27" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE27</f>
-        <v>150.76923076923077</v>
+        <v>132</v>
       </c>
       <c r="AF27" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF27</f>
-        <v>-1063.6923076923078</v>
+        <v>-1120</v>
       </c>
       <c r="AG27" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG27</f>
@@ -12981,15 +12987,15 @@
       </c>
       <c r="L28" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L28</f>
-        <v>15.981361426256079</v>
+        <v>10.953068592057761</v>
       </c>
       <c r="M28" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M28</f>
-        <v>4176.6153846153848</v>
+        <v>6094</v>
       </c>
       <c r="N28" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N28</f>
-        <v>186.30769230769238</v>
+        <v>-1121</v>
       </c>
       <c r="O28" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O28</f>
@@ -13041,27 +13047,27 @@
       </c>
       <c r="AA28" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA28</f>
-        <v>1898.4615384615383</v>
+        <v>2770</v>
       </c>
       <c r="AB28" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB28</f>
-        <v>25.352106969205835</v>
+        <v>17.375451263537904</v>
       </c>
       <c r="AC28" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC28</f>
-        <v>2.5352106969205837</v>
+        <v>1.7375451263537907</v>
       </c>
       <c r="AD28" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD28</f>
-        <v>2914.5384615384619</v>
+        <v>2043</v>
       </c>
       <c r="AE28" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE28</f>
-        <v>949.23076923076917</v>
+        <v>1385</v>
       </c>
       <c r="AF28" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF28</f>
-        <v>-1965.3076923076928</v>
+        <v>-658</v>
       </c>
       <c r="AG28" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG28</f>
@@ -13109,15 +13115,15 @@
       </c>
       <c r="L29" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L29</f>
-        <v>12.576805696846389</v>
+        <v>9.0151674741942287</v>
       </c>
       <c r="M29" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M29</f>
-        <v>4990.6153846153848</v>
+        <v>6962.2666666666664</v>
       </c>
       <c r="N29" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N29</f>
-        <v>-549.69230769230762</v>
+        <v>-1894</v>
       </c>
       <c r="O29" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O29</f>
@@ -13169,27 +13175,27 @@
       </c>
       <c r="AA29" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA29</f>
-        <v>2268.4615384615386</v>
+        <v>3164.6666666666665</v>
       </c>
       <c r="AB29" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB29</f>
-        <v>20.070871481858255</v>
+        <v>14.386981251316623</v>
       </c>
       <c r="AC29" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC29</f>
-        <v>2.0070871481858257</v>
+        <v>1.4386981251316622</v>
       </c>
       <c r="AD29" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD29</f>
-        <v>2284.5384615384614</v>
+        <v>1388.3333333333335</v>
       </c>
       <c r="AE29" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE29</f>
-        <v>1134.2307692307693</v>
+        <v>1582.3333333333333</v>
       </c>
       <c r="AF29" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF29</f>
-        <v>-1150.3076923076922</v>
+        <v>193.99999999999977</v>
       </c>
       <c r="AG29" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG29</f>
@@ -13237,15 +13243,15 @@
       </c>
       <c r="L30" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L30</f>
-        <v>13.069767441860465</v>
+        <v>9.2923280423280428</v>
       </c>
       <c r="M30" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M30</f>
-        <v>4730</v>
+        <v>6652.7999999999993</v>
       </c>
       <c r="N30" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N30</f>
-        <v>-415</v>
+        <v>-1726</v>
       </c>
       <c r="O30" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O30</f>
@@ -13297,27 +13303,27 @@
       </c>
       <c r="AA30" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA30</f>
-        <v>2150</v>
+        <v>3024</v>
       </c>
       <c r="AB30" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB30</f>
-        <v>28.037209302325582</v>
+        <v>19.933862433862437</v>
       </c>
       <c r="AC30" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC30</f>
-        <v>2.8037209302325583</v>
+        <v>1.9933862433862435</v>
       </c>
       <c r="AD30" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD30</f>
-        <v>3878</v>
+        <v>3004</v>
       </c>
       <c r="AE30" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE30</f>
-        <v>1075</v>
+        <v>1512</v>
       </c>
       <c r="AF30" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF30</f>
-        <v>-2803</v>
+        <v>-1492</v>
       </c>
       <c r="AG30" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG30</f>
@@ -13425,27 +13431,27 @@
       </c>
       <c r="AA31" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA31</f>
-        <v>2126.1538461538462</v>
+        <v>2249.3333333333335</v>
       </c>
       <c r="AB31" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB31</f>
-        <v>6.4482633863965271</v>
+        <v>6.0951393005334911</v>
       </c>
       <c r="AC31" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC31</f>
-        <v>0.64482633863965266</v>
+        <v>0.60951393005334908</v>
       </c>
       <c r="AD31" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD31</f>
-        <v>-755.15384615384619</v>
+        <v>-878.33333333333348</v>
       </c>
       <c r="AE31" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE31</f>
-        <v>1063.0769230769231</v>
+        <v>1124.6666666666667</v>
       </c>
       <c r="AF31" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF31</f>
-        <v>1818.2307692307693</v>
+        <v>2003.0000000000002</v>
       </c>
       <c r="AG31" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG31</f>
@@ -13553,27 +13559,27 @@
       </c>
       <c r="AA32" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA32</f>
-        <v>1213.0769230769231</v>
+        <v>1282</v>
       </c>
       <c r="AB32" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB32</f>
-        <v>8.0786303107165498</v>
+        <v>7.64430577223089</v>
       </c>
       <c r="AC32" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC32</f>
-        <v>0.80786303107165502</v>
+        <v>0.76443057722308894</v>
       </c>
       <c r="AD32" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD32</f>
-        <v>-233.07692307692309</v>
+        <v>-302</v>
       </c>
       <c r="AE32" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE32</f>
-        <v>606.53846153846155</v>
+        <v>641</v>
       </c>
       <c r="AF32" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF32</f>
-        <v>839.61538461538464</v>
+        <v>943</v>
       </c>
       <c r="AG32" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG32</f>
@@ -13681,27 +13687,27 @@
       </c>
       <c r="AA33" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA33</f>
-        <v>4619.2307692307695</v>
+        <v>4766.666666666667</v>
       </c>
       <c r="AB33" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB33</f>
-        <v>7.1483763530391338</v>
+        <v>6.9272727272727268</v>
       </c>
       <c r="AC33" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC33</f>
-        <v>0.71483763530391331</v>
+        <v>0.69272727272727264</v>
       </c>
       <c r="AD33" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD33</f>
-        <v>-1317.2307692307695</v>
+        <v>-1464.666666666667</v>
       </c>
       <c r="AE33" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE33</f>
-        <v>2309.6153846153848</v>
+        <v>2383.3333333333335</v>
       </c>
       <c r="AF33" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF33</f>
-        <v>3626.8461538461543</v>
+        <v>3848.0000000000005</v>
       </c>
       <c r="AG33" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG33</f>
@@ -13809,27 +13815,27 @@
       </c>
       <c r="AA34" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA34</f>
-        <v>7240.7692307692305</v>
+        <v>7453.3333333333339</v>
       </c>
       <c r="AB34" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB34</f>
-        <v>8.7104005099330717</v>
+        <v>8.4619856887298752</v>
       </c>
       <c r="AC34" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC34</f>
-        <v>0.87104005099330717</v>
+        <v>0.84619856887298739</v>
       </c>
       <c r="AD34" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD34</f>
-        <v>-933.76923076923049</v>
+        <v>-1146.3333333333339</v>
       </c>
       <c r="AE34" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE34</f>
-        <v>3620.3846153846152</v>
+        <v>3726.666666666667</v>
       </c>
       <c r="AF34" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF34</f>
-        <v>4554.1538461538457</v>
+        <v>4873.0000000000009</v>
       </c>
       <c r="AG34" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG34</f>
@@ -13937,7 +13943,7 @@
       </c>
       <c r="AA35" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA35</f>
-        <v>76.92307692307692</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="AB35" s="34">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB35</f>
@@ -13949,15 +13955,15 @@
       </c>
       <c r="AD35" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD35</f>
-        <v>-76.92307692307692</v>
+        <v>-66.666666666666671</v>
       </c>
       <c r="AE35" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE35</f>
-        <v>38.46153846153846</v>
+        <v>33.333333333333336</v>
       </c>
       <c r="AF35" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF35</f>
-        <v>115.38461538461539</v>
+        <v>100</v>
       </c>
       <c r="AG35" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG35</f>
@@ -14065,27 +14071,27 @@
       </c>
       <c r="AA36" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA36</f>
-        <v>1310.7692307692307</v>
+        <v>1136</v>
       </c>
       <c r="AB36" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB36</f>
-        <v>4.142605633802817</v>
+        <v>4.779929577464789</v>
       </c>
       <c r="AC36" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC36</f>
-        <v>0.41426056338028172</v>
+        <v>0.47799295774647887</v>
       </c>
       <c r="AD36" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD36</f>
-        <v>-767.76923076923072</v>
+        <v>-593</v>
       </c>
       <c r="AE36" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE36</f>
-        <v>655.38461538461536</v>
+        <v>568</v>
       </c>
       <c r="AF36" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF36</f>
-        <v>1423.1538461538462</v>
+        <v>1161</v>
       </c>
       <c r="AG36" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG36</f>
@@ -14193,27 +14199,27 @@
       </c>
       <c r="AA37" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA37</f>
-        <v>6125.3846153846152</v>
+        <v>6322.6666666666661</v>
       </c>
       <c r="AB37" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB37</f>
-        <v>16.599773954539746</v>
+        <v>16.081822016026994</v>
       </c>
       <c r="AC37" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC37</f>
-        <v>1.6599773954539747</v>
+        <v>1.6081822016026994</v>
       </c>
       <c r="AD37" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD37</f>
-        <v>4042.6153846153848</v>
+        <v>3845.3333333333339</v>
       </c>
       <c r="AE37" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE37</f>
-        <v>3062.6923076923076</v>
+        <v>3161.333333333333</v>
       </c>
       <c r="AF37" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF37</f>
-        <v>-979.92307692307713</v>
+        <v>-684.00000000000091</v>
       </c>
       <c r="AG37" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG37</f>
@@ -14321,27 +14327,27 @@
       </c>
       <c r="AA38" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA38</f>
-        <v>10000</v>
+        <v>10202.666666666666</v>
       </c>
       <c r="AB38" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB38</f>
-        <v>9.8580000000000005</v>
+        <v>9.6621798222686888</v>
       </c>
       <c r="AC38" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC38</f>
-        <v>0.98580000000000001</v>
+        <v>0.96621798222686883</v>
       </c>
       <c r="AD38" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD38</f>
-        <v>-142</v>
+        <v>-344.66666666666606</v>
       </c>
       <c r="AE38" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE38</f>
-        <v>5000</v>
+        <v>5101.333333333333</v>
       </c>
       <c r="AF38" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF38</f>
-        <v>5142</v>
+        <v>5445.9999999999991</v>
       </c>
       <c r="AG38" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG38</f>
@@ -14449,27 +14455,27 @@
       </c>
       <c r="AA39" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA39</f>
-        <v>4555.3846153846152</v>
+        <v>4895.3333333333339</v>
       </c>
       <c r="AB39" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB39</f>
-        <v>4.3157716987504218</v>
+        <v>4.0160697262699161</v>
       </c>
       <c r="AC39" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC39</f>
-        <v>0.43157716987504224</v>
+        <v>0.40160697262699163</v>
       </c>
       <c r="AD39" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD39</f>
-        <v>-2589.3846153846152</v>
+        <v>-2929.3333333333339</v>
       </c>
       <c r="AE39" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE39</f>
-        <v>2277.6923076923076</v>
+        <v>2447.666666666667</v>
       </c>
       <c r="AF39" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF39</f>
-        <v>4867.0769230769229</v>
+        <v>5377.0000000000009</v>
       </c>
       <c r="AG39" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG39</f>
@@ -14577,27 +14583,27 @@
       </c>
       <c r="AA40" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA40</f>
-        <v>3306.1538461538466</v>
+        <v>3359.3333333333335</v>
       </c>
       <c r="AB40" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB40</f>
-        <v>13.750116333178221</v>
+        <v>13.532446914070253</v>
       </c>
       <c r="AC40" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC40</f>
-        <v>1.3750116333178219</v>
+        <v>1.3532446914070251</v>
       </c>
       <c r="AD40" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD40</f>
-        <v>1239.8461538461534</v>
+        <v>1186.6666666666665</v>
       </c>
       <c r="AE40" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE40</f>
-        <v>1653.0769230769233</v>
+        <v>1679.6666666666667</v>
       </c>
       <c r="AF40" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF40</f>
-        <v>413.23076923076997</v>
+        <v>493.00000000000023</v>
       </c>
       <c r="AG40" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG40</f>
@@ -14961,27 +14967,27 @@
       </c>
       <c r="AA43" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA43</f>
-        <v>1216.1538461538462</v>
+        <v>1175.3333333333333</v>
       </c>
       <c r="AB43" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB43</f>
-        <v>5.4351676154332704</v>
+        <v>5.6239364719228586</v>
       </c>
       <c r="AC43" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC43</f>
-        <v>0.54351676154332695</v>
+        <v>0.56239364719228591</v>
       </c>
       <c r="AD43" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD43</f>
-        <v>-555.15384615384619</v>
+        <v>-514.33333333333326</v>
       </c>
       <c r="AE43" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE43</f>
-        <v>608.07692307692309</v>
+        <v>587.66666666666663</v>
       </c>
       <c r="AF43" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF43</f>
-        <v>1163.2307692307693</v>
+        <v>1102</v>
       </c>
       <c r="AG43" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG43</f>
@@ -15089,27 +15095,27 @@
       </c>
       <c r="AA44" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA44</f>
-        <v>1177.6923076923076</v>
+        <v>1271.3333333333335</v>
       </c>
       <c r="AB44" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB44</f>
-        <v>9.6374918354016987</v>
+        <v>8.9276350288411095</v>
       </c>
       <c r="AC44" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC44</f>
-        <v>0.96374918354016992</v>
+        <v>0.8927635028841111</v>
       </c>
       <c r="AD44" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD44</f>
-        <v>-42.692307692307622</v>
+        <v>-136.33333333333348</v>
       </c>
       <c r="AE44" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE44</f>
-        <v>588.84615384615381</v>
+        <v>635.66666666666674</v>
       </c>
       <c r="AF44" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF44</f>
-        <v>631.53846153846143</v>
+        <v>772.00000000000023</v>
       </c>
       <c r="AG44" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG44</f>
@@ -15217,27 +15223,27 @@
       </c>
       <c r="AA45" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA45</f>
-        <v>5425.3846153846152</v>
+        <v>5564</v>
       </c>
       <c r="AB45" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB45</f>
-        <v>7.6529136537643554</v>
+        <v>7.4622573687994249</v>
       </c>
       <c r="AC45" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC45</f>
-        <v>0.76529136537643561</v>
+        <v>0.74622573687994254</v>
       </c>
       <c r="AD45" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD45</f>
-        <v>-1273.3846153846152</v>
+        <v>-1412</v>
       </c>
       <c r="AE45" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE45</f>
-        <v>2712.6923076923076</v>
+        <v>2782</v>
       </c>
       <c r="AF45" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF45</f>
-        <v>3986.0769230769229</v>
+        <v>4194</v>
       </c>
       <c r="AG45" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG45</f>
@@ -15345,27 +15351,27 @@
       </c>
       <c r="AA46" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA46</f>
-        <v>6050</v>
+        <v>5998</v>
       </c>
       <c r="AB46" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB46</f>
-        <v>14.135537190082644</v>
+        <v>14.258086028676226</v>
       </c>
       <c r="AC46" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC46</f>
-        <v>1.4135537190082645</v>
+        <v>1.4258086028676225</v>
       </c>
       <c r="AD46" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD46</f>
-        <v>2502</v>
+        <v>2554</v>
       </c>
       <c r="AE46" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE46</f>
-        <v>3025</v>
+        <v>2999</v>
       </c>
       <c r="AF46" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF46</f>
-        <v>523</v>
+        <v>445</v>
       </c>
       <c r="AG46" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG46</f>
@@ -15473,27 +15479,27 @@
       </c>
       <c r="AA47" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA47</f>
-        <v>7557.6923076923067</v>
+        <v>7872</v>
       </c>
       <c r="AB47" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB47</f>
-        <v>8.9088040712468199</v>
+        <v>8.5530995934959346</v>
       </c>
       <c r="AC47" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC47</f>
-        <v>0.89088040712468208</v>
+        <v>0.85530995934959353</v>
       </c>
       <c r="AD47" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD47</f>
-        <v>-824.69230769230671</v>
+        <v>-1139</v>
       </c>
       <c r="AE47" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE47</f>
-        <v>3778.8461538461534</v>
+        <v>3936</v>
       </c>
       <c r="AF47" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF47</f>
-        <v>4603.5384615384601</v>
+        <v>5075</v>
       </c>
       <c r="AG47" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG47</f>
@@ -15601,27 +15607,27 @@
       </c>
       <c r="AA48" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA48</f>
-        <v>5266.1538461538466</v>
+        <v>5340</v>
       </c>
       <c r="AB48" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB48</f>
-        <v>9.9256500146070685</v>
+        <v>9.7883895131086138</v>
       </c>
       <c r="AC48" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC48</f>
-        <v>0.99256500146070692</v>
+        <v>0.9788389513108614</v>
       </c>
       <c r="AD48" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD48</f>
-        <v>-39.153846153846644</v>
+        <v>-113</v>
       </c>
       <c r="AE48" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE48</f>
-        <v>2633.0769230769233</v>
+        <v>2670</v>
       </c>
       <c r="AF48" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF48</f>
-        <v>2672.23076923077</v>
+        <v>2783</v>
       </c>
       <c r="AG48" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG48</f>
@@ -15729,27 +15735,27 @@
       </c>
       <c r="AA49" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA49</f>
-        <v>20</v>
+        <v>23.333333333333336</v>
       </c>
       <c r="AB49" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB49</f>
-        <v>6</v>
+        <v>5.1428571428571423</v>
       </c>
       <c r="AC49" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC49</f>
-        <v>0.6</v>
+        <v>0.51428571428571423</v>
       </c>
       <c r="AD49" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD49</f>
-        <v>-8</v>
+        <v>-11.333333333333336</v>
       </c>
       <c r="AE49" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE49</f>
-        <v>10</v>
+        <v>11.666666666666668</v>
       </c>
       <c r="AF49" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF49</f>
-        <v>18</v>
+        <v>23.000000000000004</v>
       </c>
       <c r="AG49" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG49</f>
@@ -15857,7 +15863,7 @@
       </c>
       <c r="AA50" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA50</f>
-        <v>0</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="AB50" s="25">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB50</f>
@@ -15869,15 +15875,15 @@
       </c>
       <c r="AD50" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD50</f>
-        <v>11</v>
+        <v>9.6666666666666661</v>
       </c>
       <c r="AE50" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE50</f>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AF50" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF50</f>
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="AG50" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG50</f>
@@ -15985,27 +15991,27 @@
       </c>
       <c r="AA51" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA51</f>
-        <v>229.23076923076923</v>
+        <v>699.33333333333337</v>
       </c>
       <c r="AB51" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB51</f>
-        <v>1.8758389261744965</v>
+        <v>0.61487130600571971</v>
       </c>
       <c r="AC51" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC51</f>
-        <v>0.18758389261744968</v>
+        <v>6.1487130600571968E-2</v>
       </c>
       <c r="AD51" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD51</f>
-        <v>-186.23076923076923</v>
+        <v>-656.33333333333337</v>
       </c>
       <c r="AE51" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE51</f>
-        <v>114.61538461538461</v>
+        <v>349.66666666666669</v>
       </c>
       <c r="AF51" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF51</f>
-        <v>300.84615384615381</v>
+        <v>1006</v>
       </c>
       <c r="AG51" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG51</f>
@@ -16241,27 +16247,27 @@
       </c>
       <c r="AA53" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA53</f>
-        <v>547.69230769230762</v>
+        <v>474.66666666666669</v>
       </c>
       <c r="AB53" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB53</f>
-        <v>7.3033707865168551E-2</v>
+        <v>8.4269662921348312E-2</v>
       </c>
       <c r="AC53" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC53</f>
-        <v>7.3033707865168551E-3</v>
+        <v>8.4269662921348312E-3</v>
       </c>
       <c r="AD53" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD53</f>
-        <v>-543.69230769230762</v>
+        <v>-470.66666666666669</v>
       </c>
       <c r="AE53" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE53</f>
-        <v>273.84615384615381</v>
+        <v>237.33333333333334</v>
       </c>
       <c r="AF53" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF53</f>
-        <v>817.53846153846143</v>
+        <v>708</v>
       </c>
       <c r="AG53" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG53</f>
@@ -16369,27 +16375,27 @@
       </c>
       <c r="AA54" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA54</f>
-        <v>2767.6923076923076</v>
+        <v>2757.3333333333335</v>
       </c>
       <c r="AB54" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB54</f>
-        <v>81.55892162312395</v>
+        <v>81.865328820116048</v>
       </c>
       <c r="AC54" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC54</f>
-        <v>8.1558921623123961</v>
+        <v>8.1865328820116048</v>
       </c>
       <c r="AD54" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD54</f>
-        <v>19805.307692307691</v>
+        <v>19815.666666666668</v>
       </c>
       <c r="AE54" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE54</f>
-        <v>1383.8461538461538</v>
+        <v>1378.6666666666667</v>
       </c>
       <c r="AF54" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF54</f>
-        <v>-18421.461538461539</v>
+        <v>-18437</v>
       </c>
       <c r="AG54" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG54</f>
@@ -16497,27 +16503,27 @@
       </c>
       <c r="AA55" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA55</f>
-        <v>4797.6923076923076</v>
+        <v>4637.3333333333339</v>
       </c>
       <c r="AB55" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB55</f>
-        <v>60.923039923039923</v>
+        <v>63.029758481886134</v>
       </c>
       <c r="AC55" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC55</f>
-        <v>6.0923039923039921</v>
+        <v>6.3029758481886136</v>
       </c>
       <c r="AD55" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD55</f>
-        <v>24431.307692307691</v>
+        <v>24591.666666666664</v>
       </c>
       <c r="AE55" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE55</f>
-        <v>2398.8461538461538</v>
+        <v>2318.666666666667</v>
       </c>
       <c r="AF55" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF55</f>
-        <v>-22032.461538461539</v>
+        <v>-22272.999999999996</v>
       </c>
       <c r="AG55" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG55</f>
@@ -16625,27 +16631,27 @@
       </c>
       <c r="AA56" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA56</f>
-        <v>2890.7692307692309</v>
+        <v>2783.333333333333</v>
       </c>
       <c r="AB56" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB56</f>
-        <v>55.86748270356572</v>
+        <v>58.02395209580839</v>
       </c>
       <c r="AC56" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC56</f>
-        <v>5.5867482703565727</v>
+        <v>5.8023952095808387</v>
       </c>
       <c r="AD56" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD56</f>
-        <v>13259.23076923077</v>
+        <v>13366.666666666668</v>
       </c>
       <c r="AE56" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE56</f>
-        <v>1445.3846153846155</v>
+        <v>1391.6666666666665</v>
       </c>
       <c r="AF56" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF56</f>
-        <v>-11813.846153846154</v>
+        <v>-11975.000000000002</v>
       </c>
       <c r="AG56" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG56</f>
@@ -16753,27 +16759,27 @@
       </c>
       <c r="AA57" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA57</f>
-        <v>2549.2307692307695</v>
+        <v>2464</v>
       </c>
       <c r="AB57" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB57</f>
-        <v>75.673808086904032</v>
+        <v>78.291396103896105</v>
       </c>
       <c r="AC57" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC57</f>
-        <v>7.5673808086904035</v>
+        <v>7.8291396103896105</v>
       </c>
       <c r="AD57" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD57</f>
-        <v>16741.76923076923</v>
+        <v>16827</v>
       </c>
       <c r="AE57" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE57</f>
-        <v>1274.6153846153848</v>
+        <v>1232</v>
       </c>
       <c r="AF57" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF57</f>
-        <v>-15467.153846153846</v>
+        <v>-15595</v>
       </c>
       <c r="AG57" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG57</f>
@@ -16881,27 +16887,27 @@
       </c>
       <c r="AA58" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA58</f>
-        <v>426.15384615384613</v>
+        <v>428</v>
       </c>
       <c r="AB58" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB58</f>
-        <v>16.777978339350181</v>
+        <v>16.705607476635514</v>
       </c>
       <c r="AC58" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC58</f>
-        <v>1.6777978339350181</v>
+        <v>1.6705607476635513</v>
       </c>
       <c r="AD58" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD58</f>
-        <v>288.84615384615387</v>
+        <v>287</v>
       </c>
       <c r="AE58" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE58</f>
-        <v>213.07692307692307</v>
+        <v>214</v>
       </c>
       <c r="AF58" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF58</f>
-        <v>-75.769230769230802</v>
+        <v>-73</v>
       </c>
       <c r="AG58" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG58</f>
@@ -17009,27 +17015,27 @@
       </c>
       <c r="AA59" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA59</f>
-        <v>827.69230769230774</v>
+        <v>840</v>
       </c>
       <c r="AB59" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB59</f>
-        <v>4.6635687732342008</v>
+        <v>4.5952380952380949</v>
       </c>
       <c r="AC59" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC59</f>
-        <v>0.46635687732342007</v>
+        <v>0.4595238095238095</v>
       </c>
       <c r="AD59" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD59</f>
-        <v>-441.69230769230774</v>
+        <v>-454</v>
       </c>
       <c r="AE59" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE59</f>
-        <v>413.84615384615387</v>
+        <v>420</v>
       </c>
       <c r="AF59" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF59</f>
-        <v>855.53846153846166</v>
+        <v>874</v>
       </c>
       <c r="AG59" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG59</f>
@@ -17137,27 +17143,27 @@
       </c>
       <c r="AA60" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA60</f>
-        <v>470.76923076923083</v>
+        <v>469.33333333333331</v>
       </c>
       <c r="AB60" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB60</f>
-        <v>6.3300653594771239</v>
+        <v>6.3494318181818183</v>
       </c>
       <c r="AC60" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC60</f>
-        <v>0.63300653594771239</v>
+        <v>0.63494318181818188</v>
       </c>
       <c r="AD60" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD60</f>
-        <v>-172.76923076923083</v>
+        <v>-171.33333333333331</v>
       </c>
       <c r="AE60" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE60</f>
-        <v>235.38461538461542</v>
+        <v>234.66666666666666</v>
       </c>
       <c r="AF60" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF60</f>
-        <v>408.15384615384625</v>
+        <v>406</v>
       </c>
       <c r="AG60" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG60</f>
@@ -17265,27 +17271,27 @@
       </c>
       <c r="AA61" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA61</f>
-        <v>396.92307692307691</v>
+        <v>382</v>
       </c>
       <c r="AB61" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB61</f>
-        <v>3.6782945736434107</v>
+        <v>3.8219895287958114</v>
       </c>
       <c r="AC61" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC61</f>
-        <v>0.36782945736434108</v>
+        <v>0.38219895287958117</v>
       </c>
       <c r="AD61" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD61</f>
-        <v>-250.92307692307691</v>
+        <v>-236</v>
       </c>
       <c r="AE61" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE61</f>
-        <v>198.46153846153845</v>
+        <v>191</v>
       </c>
       <c r="AF61" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF61</f>
-        <v>449.38461538461536</v>
+        <v>427</v>
       </c>
       <c r="AG61" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG61</f>
@@ -17325,7 +17331,7 @@
       </c>
       <c r="AF62" s="44">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF62</f>
-        <v>108920.07692307689</v>
+        <v>117524</v>
       </c>
     </row>
     <row r="63" spans="2:33" x14ac:dyDescent="0.25">
@@ -17334,10 +17340,10 @@
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
-      <c r="E63" s="67" t="s">
+      <c r="E63" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="F63" s="67"/>
+      <c r="F63" s="64"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -17362,10 +17368,10 @@
       <c r="AB63" s="42"/>
     </row>
     <row r="64" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B64" s="63" t="s">
+      <c r="B64" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="63"/>
+      <c r="C64" s="65"/>
       <c r="D64" s="48">
         <f>SUM(F13:F61)</f>
         <v>144936.54999999999</v>
@@ -17510,19 +17516,19 @@
       <c r="AB67" s="42"/>
     </row>
     <row r="68" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B68" s="63" t="s">
+      <c r="B68" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="C68" s="63"/>
+      <c r="C68" s="65"/>
       <c r="D68" s="50">
         <f>SUM(Z13:Z61)</f>
         <v>421177.93000000017</v>
       </c>
-      <c r="E68" s="64">
+      <c r="E68" s="66">
         <f>D68*100/D68</f>
         <v>100</v>
       </c>
-      <c r="F68" s="64"/>
+      <c r="F68" s="66"/>
       <c r="G68" s="51"/>
       <c r="H68" s="51"/>
       <c r="I68" s="51"/>
@@ -17607,10 +17613,10 @@
       <c r="AB70" s="42"/>
     </row>
     <row r="71" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B71" s="63" t="s">
+      <c r="B71" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="63"/>
+      <c r="C71" s="65"/>
       <c r="D71" s="3">
         <f>SUM(E13:E61)</f>
         <v>112990</v>
@@ -17725,11 +17731,11 @@
         <f>SUM(T13:T61)</f>
         <v>36961</v>
       </c>
-      <c r="E74" s="62">
+      <c r="E74" s="67">
         <f>D74*100/D75</f>
         <v>11.039956032533535</v>
       </c>
-      <c r="F74" s="62"/>
+      <c r="F74" s="67"/>
       <c r="G74" s="56"/>
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
@@ -17754,19 +17760,19 @@
       <c r="AB74" s="42"/>
     </row>
     <row r="75" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B75" s="63" t="s">
+      <c r="B75" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="63"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="55">
         <f>SUM(Y13:Y61)</f>
         <v>334793</v>
       </c>
-      <c r="E75" s="62">
+      <c r="E75" s="67">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="62"/>
+      <c r="F75" s="67"/>
       <c r="G75" s="56"/>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
@@ -18527,23 +18533,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="E71:F71"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="B1:Z6"/>
     <mergeCell ref="AA1:AG6"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G61">
     <cfRule type="colorScale" priority="5">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB9A6ED-3B9A-4798-BA3B-F02048DDDF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8335D7-F86F-4BFE-BE29-508B78B70387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -841,6 +841,15 @@
     <xf numFmtId="2" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -849,15 +858,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5644,6 +5644,7 @@
       <sheetName val="INVENTARIO NACIONAL 20-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -5771,22 +5772,22 @@
             <v>13606.800000000001</v>
           </cell>
           <cell r="AA13">
-            <v>11018.666666666666</v>
+            <v>11684.375</v>
           </cell>
           <cell r="AB13">
-            <v>9.0800459825750259</v>
+            <v>8.5627173040920024</v>
           </cell>
           <cell r="AC13">
-            <v>0.90800459825750246</v>
+            <v>0.85627173040920035</v>
           </cell>
           <cell r="AD13">
-            <v>-1013.6666666666661</v>
+            <v>-1679.375</v>
           </cell>
           <cell r="AE13">
-            <v>5509.333333333333</v>
+            <v>5842.1875</v>
           </cell>
           <cell r="AF13">
-            <v>6522.9999999999991</v>
+            <v>7521.5625</v>
           </cell>
           <cell r="AG13">
             <v>125.0625</v>
@@ -5863,22 +5864,22 @@
             <v>888.81000000000006</v>
           </cell>
           <cell r="AA14">
-            <v>791.33333333333337</v>
+            <v>769.375</v>
           </cell>
           <cell r="AB14">
-            <v>7.0640269587194604</v>
+            <v>7.2656376929325752</v>
           </cell>
           <cell r="AC14">
-            <v>0.70640269587194604</v>
+            <v>0.7265637692932575</v>
           </cell>
           <cell r="AD14">
-            <v>-232.33333333333337</v>
+            <v>-210.375</v>
           </cell>
           <cell r="AE14">
-            <v>395.66666666666669</v>
+            <v>384.6875</v>
           </cell>
           <cell r="AF14">
-            <v>628</v>
+            <v>595.0625</v>
           </cell>
           <cell r="AG14">
             <v>6.9874999999999998</v>
@@ -5955,22 +5956,22 @@
             <v>6966.9599999999991</v>
           </cell>
           <cell r="AA15">
-            <v>4536.666666666667</v>
+            <v>4921.25</v>
           </cell>
           <cell r="AB15">
-            <v>7.5650257163850103</v>
+            <v>6.9738379476758956</v>
           </cell>
           <cell r="AC15">
-            <v>0.7565025716385011</v>
+            <v>0.69738379476758949</v>
           </cell>
           <cell r="AD15">
-            <v>-1104.666666666667</v>
+            <v>-1489.25</v>
           </cell>
           <cell r="AE15">
-            <v>2268.3333333333335</v>
+            <v>2460.625</v>
           </cell>
           <cell r="AF15">
-            <v>3373.0000000000005</v>
+            <v>3949.875</v>
           </cell>
           <cell r="AG15">
             <v>57.2</v>
@@ -6047,22 +6048,22 @@
             <v>743.66</v>
           </cell>
           <cell r="AA16">
-            <v>928</v>
+            <v>893.125</v>
           </cell>
           <cell r="AB16">
-            <v>2.2198275862068968</v>
+            <v>2.3065080475857243</v>
           </cell>
           <cell r="AC16">
-            <v>0.22198275862068967</v>
+            <v>0.23065080475857244</v>
           </cell>
           <cell r="AD16">
-            <v>-722</v>
+            <v>-687.125</v>
           </cell>
           <cell r="AE16">
-            <v>464</v>
+            <v>446.5625</v>
           </cell>
           <cell r="AF16">
-            <v>1186</v>
+            <v>1133.6875</v>
           </cell>
           <cell r="AG16">
             <v>7.3571428571428568</v>
@@ -6139,22 +6140,22 @@
             <v>1861.36</v>
           </cell>
           <cell r="AA17">
-            <v>116.66666666666666</v>
+            <v>109.375</v>
           </cell>
           <cell r="AB17">
-            <v>18.171428571428571</v>
+            <v>19.382857142857144</v>
           </cell>
           <cell r="AC17">
-            <v>1.8171428571428574</v>
+            <v>1.9382857142857144</v>
           </cell>
           <cell r="AD17">
-            <v>95.333333333333343</v>
+            <v>102.625</v>
           </cell>
           <cell r="AE17">
-            <v>58.333333333333329</v>
+            <v>54.6875</v>
           </cell>
           <cell r="AF17">
-            <v>-37.000000000000014</v>
+            <v>-47.9375</v>
           </cell>
           <cell r="AG17">
             <v>17.666666666666668</v>
@@ -6231,22 +6232,22 @@
             <v>5277.51</v>
           </cell>
           <cell r="AA18">
-            <v>13038</v>
+            <v>14228.125</v>
           </cell>
           <cell r="AB18">
-            <v>6.4250651940481669</v>
+            <v>5.8876345266857015</v>
           </cell>
           <cell r="AC18">
-            <v>0.64250651940481673</v>
+            <v>0.58876345266857022</v>
           </cell>
           <cell r="AD18">
-            <v>-4661</v>
+            <v>-5851.125</v>
           </cell>
           <cell r="AE18">
-            <v>6519</v>
+            <v>7114.0625</v>
           </cell>
           <cell r="AF18">
-            <v>11180</v>
+            <v>12965.1875</v>
           </cell>
           <cell r="AG18">
             <v>139.61666666666667</v>
@@ -6323,22 +6324,22 @@
             <v>949.41</v>
           </cell>
           <cell r="AA19">
-            <v>1445.3333333333333</v>
+            <v>1448.125</v>
           </cell>
           <cell r="AB19">
-            <v>10.426660516605166</v>
+            <v>10.406560207164437</v>
           </cell>
           <cell r="AC19">
-            <v>1.0426660516605166</v>
+            <v>1.0406560207164437</v>
           </cell>
           <cell r="AD19">
-            <v>61.666666666666742</v>
+            <v>58.875</v>
           </cell>
           <cell r="AE19">
-            <v>722.66666666666663</v>
+            <v>724.0625</v>
           </cell>
           <cell r="AF19">
-            <v>660.99999999999989</v>
+            <v>665.1875</v>
           </cell>
           <cell r="AG19">
             <v>25.116666666666667</v>
@@ -6415,22 +6416,22 @@
             <v>2498.58</v>
           </cell>
           <cell r="AA20">
-            <v>3058</v>
+            <v>3132.5</v>
           </cell>
           <cell r="AB20">
-            <v>12.969260954872466</v>
+            <v>12.660814046288907</v>
           </cell>
           <cell r="AC20">
-            <v>1.2969260954872466</v>
+            <v>1.2660814046288906</v>
           </cell>
           <cell r="AD20">
-            <v>908</v>
+            <v>833.5</v>
           </cell>
           <cell r="AE20">
-            <v>1529</v>
+            <v>1566.25</v>
           </cell>
           <cell r="AF20">
-            <v>621</v>
+            <v>732.75</v>
           </cell>
           <cell r="AG20">
             <v>66.099999999999994</v>
@@ -6507,22 +6508,22 @@
             <v>8325.42</v>
           </cell>
           <cell r="AA21">
-            <v>7036</v>
+            <v>7136.25</v>
           </cell>
           <cell r="AB21">
-            <v>10.855599772598067</v>
+            <v>10.703100367840252</v>
           </cell>
           <cell r="AC21">
-            <v>1.0855599772598068</v>
+            <v>1.0703100367840253</v>
           </cell>
           <cell r="AD21">
-            <v>602</v>
+            <v>501.75</v>
           </cell>
           <cell r="AE21">
-            <v>3518</v>
+            <v>3568.125</v>
           </cell>
           <cell r="AF21">
-            <v>2916</v>
+            <v>3066.375</v>
           </cell>
           <cell r="AG21">
             <v>141.44444444444446</v>
@@ -6599,22 +6600,22 @@
             <v>4099.4900000000007</v>
           </cell>
           <cell r="AA22">
-            <v>3326.666666666667</v>
+            <v>3313.75</v>
           </cell>
           <cell r="AB22">
-            <v>11.30561122244489</v>
+            <v>11.349679366276877</v>
           </cell>
           <cell r="AC22">
-            <v>1.1305611222444889</v>
+            <v>1.1349679366276877</v>
           </cell>
           <cell r="AD22">
-            <v>434.33333333333303</v>
+            <v>447.25</v>
           </cell>
           <cell r="AE22">
-            <v>1663.3333333333335</v>
+            <v>1656.875</v>
           </cell>
           <cell r="AF22">
-            <v>1229.0000000000005</v>
+            <v>1209.625</v>
           </cell>
           <cell r="AG22">
             <v>69.648148148148152</v>
@@ -6691,22 +6692,22 @@
             <v>38473.719999999994</v>
           </cell>
           <cell r="AA23">
-            <v>34037.333333333328</v>
+            <v>34954.375</v>
           </cell>
           <cell r="AB23">
-            <v>9.7443003760576641</v>
+            <v>9.4886548536485069</v>
           </cell>
           <cell r="AC23">
-            <v>0.97443003760576641</v>
+            <v>0.9488654853648506</v>
           </cell>
           <cell r="AD23">
-            <v>-870.33333333332848</v>
+            <v>-1787.375</v>
           </cell>
           <cell r="AE23">
-            <v>17018.666666666664</v>
+            <v>17477.1875</v>
           </cell>
           <cell r="AF23">
-            <v>17888.999999999993</v>
+            <v>19264.5625</v>
           </cell>
           <cell r="AG23">
             <v>614.2037037037037</v>
@@ -6783,22 +6784,22 @@
             <v>29054.519999999997</v>
           </cell>
           <cell r="AA24">
-            <v>22219.333333333336</v>
+            <v>22795.625</v>
           </cell>
           <cell r="AB24">
-            <v>11.272615440007201</v>
+            <v>10.987634688673813</v>
           </cell>
           <cell r="AC24">
-            <v>1.1272615440007199</v>
+            <v>1.0987634688673813</v>
           </cell>
           <cell r="AD24">
-            <v>2827.6666666666642</v>
+            <v>2251.375</v>
           </cell>
           <cell r="AE24">
-            <v>11109.666666666668</v>
+            <v>11397.8125</v>
           </cell>
           <cell r="AF24">
-            <v>8282.0000000000036</v>
+            <v>9146.4375</v>
           </cell>
           <cell r="AG24">
             <v>463.83333333333331</v>
@@ -6875,22 +6876,22 @@
             <v>30040.519999999997</v>
           </cell>
           <cell r="AA25">
-            <v>21740.666666666664</v>
+            <v>22229.375</v>
           </cell>
           <cell r="AB25">
-            <v>11.911778234338106</v>
+            <v>11.649900188376867</v>
           </cell>
           <cell r="AC25">
-            <v>1.1911778234338108</v>
+            <v>1.1649900188376867</v>
           </cell>
           <cell r="AD25">
-            <v>4156.3333333333358</v>
+            <v>3667.625</v>
           </cell>
           <cell r="AE25">
-            <v>10870.333333333332</v>
+            <v>11114.6875</v>
           </cell>
           <cell r="AF25">
-            <v>6713.9999999999964</v>
+            <v>7447.0625</v>
           </cell>
           <cell r="AG25">
             <v>479.57407407407408</v>
@@ -6967,22 +6968,22 @@
             <v>34369.64</v>
           </cell>
           <cell r="AA26">
-            <v>25825.333333333332</v>
+            <v>26338.75</v>
           </cell>
           <cell r="AB26">
-            <v>11.472843203056431</v>
+            <v>11.249205068577666</v>
           </cell>
           <cell r="AC26">
-            <v>1.1472843203056431</v>
+            <v>1.1249205068577666</v>
           </cell>
           <cell r="AD26">
-            <v>3803.6666666666679</v>
+            <v>3290.25</v>
           </cell>
           <cell r="AE26">
-            <v>12912.666666666666</v>
+            <v>13169.375</v>
           </cell>
           <cell r="AF26">
-            <v>9108.9999999999982</v>
+            <v>9879.125</v>
           </cell>
           <cell r="AG26">
             <v>548.68518518518522</v>
@@ -7059,22 +7060,22 @@
             <v>1758.56</v>
           </cell>
           <cell r="AA27">
-            <v>264</v>
+            <v>212.5</v>
           </cell>
           <cell r="AB27">
-            <v>57.424242424242429</v>
+            <v>71.341176470588238</v>
           </cell>
           <cell r="AC27">
-            <v>5.7424242424242422</v>
+            <v>7.1341176470588232</v>
           </cell>
           <cell r="AD27">
-            <v>1252</v>
+            <v>1303.5</v>
           </cell>
           <cell r="AE27">
-            <v>132</v>
+            <v>106.25</v>
           </cell>
           <cell r="AF27">
-            <v>-1120</v>
+            <v>-1197.25</v>
           </cell>
           <cell r="AG27">
             <v>28.074074074074073</v>
@@ -7106,13 +7107,13 @@
             <v>3519.4399999999996</v>
           </cell>
           <cell r="L28">
-            <v>10.953068592057761</v>
+            <v>9.6604975124378107</v>
           </cell>
           <cell r="M28">
-            <v>6094</v>
+            <v>6909.375</v>
           </cell>
           <cell r="N28">
-            <v>-1121</v>
+            <v>-1676.9375</v>
           </cell>
           <cell r="O28">
             <v>251</v>
@@ -7151,22 +7152,22 @@
             <v>5583.08</v>
           </cell>
           <cell r="AA28">
-            <v>2770</v>
+            <v>3140.625</v>
           </cell>
           <cell r="AB28">
-            <v>17.375451263537904</v>
+            <v>15.32497512437811</v>
           </cell>
           <cell r="AC28">
-            <v>1.7375451263537907</v>
+            <v>1.5324975124378108</v>
           </cell>
           <cell r="AD28">
-            <v>2043</v>
+            <v>1672.375</v>
           </cell>
           <cell r="AE28">
-            <v>1385</v>
+            <v>1570.3125</v>
           </cell>
           <cell r="AF28">
-            <v>-658</v>
+            <v>-102.0625</v>
           </cell>
           <cell r="AG28">
             <v>89.129629629629633</v>
@@ -7198,13 +7199,13 @@
             <v>3309.4799999999996</v>
           </cell>
           <cell r="L29">
-            <v>9.0151674741942287</v>
+            <v>8.005612065941774</v>
           </cell>
           <cell r="M29">
-            <v>6962.2666666666664</v>
+            <v>7840.25</v>
           </cell>
           <cell r="N29">
-            <v>-1894</v>
+            <v>-2492.625</v>
           </cell>
           <cell r="O29">
             <v>236</v>
@@ -7243,22 +7244,22 @@
             <v>5281.48</v>
           </cell>
           <cell r="AA29">
-            <v>3164.6666666666665</v>
+            <v>3563.75</v>
           </cell>
           <cell r="AB29">
-            <v>14.386981251316623</v>
+            <v>12.775868116450368</v>
           </cell>
           <cell r="AC29">
-            <v>1.4386981251316622</v>
+            <v>1.2775868116450368</v>
           </cell>
           <cell r="AD29">
-            <v>1388.3333333333335</v>
+            <v>989.25</v>
           </cell>
           <cell r="AE29">
-            <v>1582.3333333333333</v>
+            <v>1781.875</v>
           </cell>
           <cell r="AF29">
-            <v>193.99999999999977</v>
+            <v>792.625</v>
           </cell>
           <cell r="AG29">
             <v>84.31481481481481</v>
@@ -7290,13 +7291,13 @@
             <v>3259.6</v>
           </cell>
           <cell r="L30">
-            <v>9.2923280423280428</v>
+            <v>8.2043795620437958</v>
           </cell>
           <cell r="M30">
-            <v>6652.7999999999993</v>
+            <v>7535</v>
           </cell>
           <cell r="N30">
-            <v>-1726</v>
+            <v>-2327.5</v>
           </cell>
           <cell r="O30">
             <v>236</v>
@@ -7335,22 +7336,22 @@
             <v>6992.48</v>
           </cell>
           <cell r="AA30">
-            <v>3024</v>
+            <v>3425</v>
           </cell>
           <cell r="AB30">
-            <v>19.933862433862437</v>
+            <v>17.600000000000001</v>
           </cell>
           <cell r="AC30">
-            <v>1.9933862433862435</v>
+            <v>1.76</v>
           </cell>
           <cell r="AD30">
-            <v>3004</v>
+            <v>2603</v>
           </cell>
           <cell r="AE30">
-            <v>1512</v>
+            <v>1712.5</v>
           </cell>
           <cell r="AF30">
-            <v>-1492</v>
+            <v>-890.5</v>
           </cell>
           <cell r="AG30">
             <v>111.62962962962963</v>
@@ -7427,22 +7428,22 @@
             <v>5045.2800000000007</v>
           </cell>
           <cell r="AA31">
-            <v>2249.3333333333335</v>
+            <v>2256.875</v>
           </cell>
           <cell r="AB31">
-            <v>6.0951393005334911</v>
+            <v>6.0747715314317361</v>
           </cell>
           <cell r="AC31">
-            <v>0.60951393005334908</v>
+            <v>0.60747715314317363</v>
           </cell>
           <cell r="AD31">
-            <v>-878.33333333333348</v>
+            <v>-885.875</v>
           </cell>
           <cell r="AE31">
-            <v>1124.6666666666667</v>
+            <v>1128.4375</v>
           </cell>
           <cell r="AF31">
-            <v>2003.0000000000002</v>
+            <v>2014.3125</v>
           </cell>
           <cell r="AG31">
             <v>85.6875</v>
@@ -7519,22 +7520,22 @@
             <v>3606.4</v>
           </cell>
           <cell r="AA32">
-            <v>1282</v>
+            <v>1303.75</v>
           </cell>
           <cell r="AB32">
-            <v>7.64430577223089</v>
+            <v>7.5167785234899327</v>
           </cell>
           <cell r="AC32">
-            <v>0.76443057722308894</v>
+            <v>0.75167785234899331</v>
           </cell>
           <cell r="AD32">
-            <v>-302</v>
+            <v>-323.75</v>
           </cell>
           <cell r="AE32">
-            <v>641</v>
+            <v>651.875</v>
           </cell>
           <cell r="AF32">
-            <v>943</v>
+            <v>975.625</v>
           </cell>
           <cell r="AG32">
             <v>61.25</v>
@@ -7611,22 +7612,22 @@
             <v>13703.300000000001</v>
           </cell>
           <cell r="AA33">
-            <v>4766.666666666667</v>
+            <v>4897.5</v>
           </cell>
           <cell r="AB33">
-            <v>6.9272727272727268</v>
+            <v>6.7422154160285857</v>
           </cell>
           <cell r="AC33">
-            <v>0.69272727272727264</v>
+            <v>0.67422154160285863</v>
           </cell>
           <cell r="AD33">
-            <v>-1464.666666666667</v>
+            <v>-1595.5</v>
           </cell>
           <cell r="AE33">
-            <v>2383.3333333333335</v>
+            <v>2448.75</v>
           </cell>
           <cell r="AF33">
-            <v>3848.0000000000005</v>
+            <v>4044.25</v>
           </cell>
           <cell r="AG33">
             <v>206.375</v>
@@ -7703,22 +7704,22 @@
             <v>26174.050000000003</v>
           </cell>
           <cell r="AA34">
-            <v>7453.3333333333339</v>
+            <v>7733.75</v>
           </cell>
           <cell r="AB34">
-            <v>8.4619856887298752</v>
+            <v>8.1551640536609025</v>
           </cell>
           <cell r="AC34">
-            <v>0.84619856887298739</v>
+            <v>0.81551640536609016</v>
           </cell>
           <cell r="AD34">
-            <v>-1146.3333333333339</v>
+            <v>-1426.75</v>
           </cell>
           <cell r="AE34">
-            <v>3726.666666666667</v>
+            <v>3866.875</v>
           </cell>
           <cell r="AF34">
-            <v>4873.0000000000009</v>
+            <v>5293.625</v>
           </cell>
           <cell r="AG34">
             <v>394.1875</v>
@@ -7795,7 +7796,7 @@
             <v>0</v>
           </cell>
           <cell r="AA35">
-            <v>66.666666666666671</v>
+            <v>772.5</v>
           </cell>
           <cell r="AB35">
             <v>0</v>
@@ -7804,13 +7805,13 @@
             <v>0</v>
           </cell>
           <cell r="AD35">
-            <v>-66.666666666666671</v>
+            <v>-772.5</v>
           </cell>
           <cell r="AE35">
-            <v>33.333333333333336</v>
+            <v>386.25</v>
           </cell>
           <cell r="AF35">
-            <v>100</v>
+            <v>1158.75</v>
           </cell>
           <cell r="AG35">
             <v>0</v>
@@ -7887,22 +7888,22 @@
             <v>2253.4500000000003</v>
           </cell>
           <cell r="AA36">
-            <v>1136</v>
+            <v>7180</v>
           </cell>
           <cell r="AB36">
-            <v>4.779929577464789</v>
+            <v>0.75626740947075211</v>
           </cell>
           <cell r="AC36">
-            <v>0.47799295774647887</v>
+            <v>7.5626740947075208E-2</v>
           </cell>
           <cell r="AD36">
-            <v>-593</v>
+            <v>-6637</v>
           </cell>
           <cell r="AE36">
-            <v>568</v>
+            <v>3590</v>
           </cell>
           <cell r="AF36">
-            <v>1161</v>
+            <v>10227</v>
           </cell>
           <cell r="AG36">
             <v>33.9375</v>
@@ -7979,22 +7980,22 @@
             <v>16573.84</v>
           </cell>
           <cell r="AA37">
-            <v>6322.6666666666661</v>
+            <v>11913.75</v>
           </cell>
           <cell r="AB37">
-            <v>16.081822016026994</v>
+            <v>8.5346763193788693</v>
           </cell>
           <cell r="AC37">
-            <v>1.6081822016026994</v>
+            <v>0.85346763193788688</v>
           </cell>
           <cell r="AD37">
-            <v>3845.3333333333339</v>
+            <v>-1745.75</v>
           </cell>
           <cell r="AE37">
-            <v>3161.333333333333</v>
+            <v>5956.875</v>
           </cell>
           <cell r="AF37">
-            <v>-684.00000000000091</v>
+            <v>7702.625</v>
           </cell>
           <cell r="AG37">
             <v>188.2962962962963</v>
@@ -8071,22 +8072,22 @@
             <v>16068.539999999999</v>
           </cell>
           <cell r="AA38">
-            <v>10202.666666666666</v>
+            <v>5083.125</v>
           </cell>
           <cell r="AB38">
-            <v>9.6621798222686888</v>
+            <v>19.393581704168202</v>
           </cell>
           <cell r="AC38">
-            <v>0.96621798222686883</v>
+            <v>1.9393581704168203</v>
           </cell>
           <cell r="AD38">
-            <v>-344.66666666666606</v>
+            <v>4774.875</v>
           </cell>
           <cell r="AE38">
-            <v>5101.333333333333</v>
+            <v>2541.5625</v>
           </cell>
           <cell r="AF38">
-            <v>5445.9999999999991</v>
+            <v>-2233.3125</v>
           </cell>
           <cell r="AG38">
             <v>182.55555555555554</v>
@@ -8163,22 +8164,22 @@
             <v>3204.58</v>
           </cell>
           <cell r="AA39">
-            <v>4895.3333333333339</v>
+            <v>3739.375</v>
           </cell>
           <cell r="AB39">
-            <v>4.0160697262699161</v>
+            <v>5.2575630954370718</v>
           </cell>
           <cell r="AC39">
-            <v>0.40160697262699163</v>
+            <v>0.52575630954370722</v>
           </cell>
           <cell r="AD39">
-            <v>-2929.3333333333339</v>
+            <v>-1773.375</v>
           </cell>
           <cell r="AE39">
-            <v>2447.666666666667</v>
+            <v>1869.6875</v>
           </cell>
           <cell r="AF39">
-            <v>5377.0000000000009</v>
+            <v>3643.0625</v>
           </cell>
           <cell r="AG39">
             <v>36.407407407407405</v>
@@ -8255,22 +8256,22 @@
             <v>7409.98</v>
           </cell>
           <cell r="AA40">
-            <v>3359.3333333333335</v>
+            <v>506.25</v>
           </cell>
           <cell r="AB40">
-            <v>13.532446914070253</v>
+            <v>89.797530864197526</v>
           </cell>
           <cell r="AC40">
-            <v>1.3532446914070251</v>
+            <v>8.9797530864197537</v>
           </cell>
           <cell r="AD40">
-            <v>1186.6666666666665</v>
+            <v>4039.75</v>
           </cell>
           <cell r="AE40">
-            <v>1679.6666666666667</v>
+            <v>253.125</v>
           </cell>
           <cell r="AF40">
-            <v>493.00000000000023</v>
+            <v>-3786.625</v>
           </cell>
           <cell r="AG40">
             <v>84.18518518518519</v>
@@ -8531,22 +8532,22 @@
             <v>4065.15</v>
           </cell>
           <cell r="AA43">
-            <v>1175.3333333333333</v>
+            <v>1314.375</v>
           </cell>
           <cell r="AB43">
-            <v>5.6239364719228586</v>
+            <v>5.0290061816452685</v>
           </cell>
           <cell r="AC43">
-            <v>0.56239364719228591</v>
+            <v>0.50290061816452691</v>
           </cell>
           <cell r="AD43">
-            <v>-514.33333333333326</v>
+            <v>-653.375</v>
           </cell>
           <cell r="AE43">
-            <v>587.66666666666663</v>
+            <v>657.1875</v>
           </cell>
           <cell r="AF43">
-            <v>1102</v>
+            <v>1310.5625</v>
           </cell>
           <cell r="AG43">
             <v>12.24074074074074</v>
@@ -8623,22 +8624,22 @@
             <v>6980.25</v>
           </cell>
           <cell r="AA44">
-            <v>1271.3333333333335</v>
+            <v>5966.875</v>
           </cell>
           <cell r="AB44">
-            <v>8.9276350288411095</v>
+            <v>1.9021682203833665</v>
           </cell>
           <cell r="AC44">
-            <v>0.8927635028841111</v>
+            <v>0.19021682203833665</v>
           </cell>
           <cell r="AD44">
-            <v>-136.33333333333348</v>
+            <v>-4831.875</v>
           </cell>
           <cell r="AE44">
-            <v>635.66666666666674</v>
+            <v>2983.4375</v>
           </cell>
           <cell r="AF44">
-            <v>772.00000000000023</v>
+            <v>7815.3125</v>
           </cell>
           <cell r="AG44">
             <v>21.018518518518519</v>
@@ -8715,22 +8716,22 @@
             <v>4816.32</v>
           </cell>
           <cell r="AA45">
-            <v>5564</v>
+            <v>6235.625</v>
           </cell>
           <cell r="AB45">
-            <v>7.4622573687994249</v>
+            <v>6.6585145835421473</v>
           </cell>
           <cell r="AC45">
-            <v>0.74622573687994254</v>
+            <v>0.66585145835421466</v>
           </cell>
           <cell r="AD45">
-            <v>-1412</v>
+            <v>-2083.625</v>
           </cell>
           <cell r="AE45">
-            <v>2782</v>
+            <v>3117.8125</v>
           </cell>
           <cell r="AF45">
-            <v>4194</v>
+            <v>5201.4375</v>
           </cell>
           <cell r="AG45">
             <v>76.888888888888886</v>
@@ -8807,22 +8808,22 @@
             <v>9920.32</v>
           </cell>
           <cell r="AA46">
-            <v>5998</v>
+            <v>8279.375</v>
           </cell>
           <cell r="AB46">
-            <v>14.258086028676226</v>
+            <v>10.329282101607911</v>
           </cell>
           <cell r="AC46">
-            <v>1.4258086028676225</v>
+            <v>1.0329282101607911</v>
           </cell>
           <cell r="AD46">
-            <v>2554</v>
+            <v>272.625</v>
           </cell>
           <cell r="AE46">
-            <v>2999</v>
+            <v>4139.6875</v>
           </cell>
           <cell r="AF46">
-            <v>445</v>
+            <v>3867.0625</v>
           </cell>
           <cell r="AG46">
             <v>158.37037037037038</v>
@@ -8899,22 +8900,22 @@
             <v>7810.28</v>
           </cell>
           <cell r="AA47">
-            <v>7872</v>
+            <v>5571.875</v>
           </cell>
           <cell r="AB47">
-            <v>8.5530995934959346</v>
+            <v>12.083903533370723</v>
           </cell>
           <cell r="AC47">
-            <v>0.85530995934959353</v>
+            <v>1.2083903533370723</v>
           </cell>
           <cell r="AD47">
-            <v>-1139</v>
+            <v>1161.125</v>
           </cell>
           <cell r="AE47">
-            <v>3936</v>
+            <v>2785.9375</v>
           </cell>
           <cell r="AF47">
-            <v>5075</v>
+            <v>1624.8125</v>
           </cell>
           <cell r="AG47">
             <v>124.68518518518519</v>
@@ -8991,22 +8992,22 @@
             <v>6063.32</v>
           </cell>
           <cell r="AA48">
-            <v>5340</v>
+            <v>26.25</v>
           </cell>
           <cell r="AB48">
-            <v>9.7883895131086138</v>
+            <v>1991.2380952380952</v>
           </cell>
           <cell r="AC48">
-            <v>0.9788389513108614</v>
+            <v>199.12380952380951</v>
           </cell>
           <cell r="AD48">
-            <v>-113</v>
+            <v>5200.75</v>
           </cell>
           <cell r="AE48">
-            <v>2670</v>
+            <v>13.125</v>
           </cell>
           <cell r="AF48">
-            <v>2783</v>
+            <v>-5187.625</v>
           </cell>
           <cell r="AG48">
             <v>96.796296296296291</v>
@@ -9082,23 +9083,23 @@
           <cell r="Z49">
             <v>216</v>
           </cell>
-          <cell r="AA49">
-            <v>23.333333333333336</v>
-          </cell>
-          <cell r="AB49">
-            <v>5.1428571428571423</v>
-          </cell>
-          <cell r="AC49">
-            <v>0.51428571428571423</v>
-          </cell>
-          <cell r="AD49">
-            <v>-11.333333333333336</v>
-          </cell>
-          <cell r="AE49">
-            <v>11.666666666666668</v>
-          </cell>
-          <cell r="AF49">
-            <v>23.000000000000004</v>
+          <cell r="AA49" t="e">
+            <v>#REF!</v>
+          </cell>
+          <cell r="AB49" t="e">
+            <v>#REF!</v>
+          </cell>
+          <cell r="AC49" t="e">
+            <v>#REF!</v>
+          </cell>
+          <cell r="AD49" t="e">
+            <v>#REF!</v>
+          </cell>
+          <cell r="AE49" t="e">
+            <v>#REF!</v>
+          </cell>
+          <cell r="AF49" t="e">
+            <v>#REF!</v>
           </cell>
           <cell r="AG49">
             <v>6</v>
@@ -9175,7 +9176,7 @@
             <v>198</v>
           </cell>
           <cell r="AA50">
-            <v>1.3333333333333333</v>
+            <v>421.875</v>
           </cell>
           <cell r="AB50">
             <v>0</v>
@@ -9184,13 +9185,13 @@
             <v>0</v>
           </cell>
           <cell r="AD50">
-            <v>9.6666666666666661</v>
+            <v>-410.875</v>
           </cell>
           <cell r="AE50">
-            <v>0.66666666666666663</v>
+            <v>210.9375</v>
           </cell>
           <cell r="AF50">
-            <v>-9</v>
+            <v>621.8125</v>
           </cell>
           <cell r="AG50">
             <v>5.5</v>
@@ -9267,22 +9268,22 @@
             <v>49.879999999999995</v>
           </cell>
           <cell r="AA51">
-            <v>699.33333333333337</v>
+            <v>5</v>
           </cell>
           <cell r="AB51">
-            <v>0.61487130600571971</v>
+            <v>86</v>
           </cell>
           <cell r="AC51">
-            <v>6.1487130600571968E-2</v>
+            <v>8.6</v>
           </cell>
           <cell r="AD51">
-            <v>-656.33333333333337</v>
+            <v>38</v>
           </cell>
           <cell r="AE51">
-            <v>349.66666666666669</v>
+            <v>2.5</v>
           </cell>
           <cell r="AF51">
-            <v>1006</v>
+            <v>-35.5</v>
           </cell>
           <cell r="AG51">
             <v>1.075</v>
@@ -9451,22 +9452,22 @@
             <v>4.6399999999999997</v>
           </cell>
           <cell r="AA53">
-            <v>474.66666666666669</v>
+            <v>4965.625</v>
           </cell>
           <cell r="AB53">
-            <v>8.4269662921348312E-2</v>
+            <v>8.0553807426054121E-3</v>
           </cell>
           <cell r="AC53">
-            <v>8.4269662921348312E-3</v>
+            <v>8.0553807426054125E-4</v>
           </cell>
           <cell r="AD53">
-            <v>-470.66666666666669</v>
+            <v>-4961.625</v>
           </cell>
           <cell r="AE53">
-            <v>237.33333333333334</v>
+            <v>2482.8125</v>
           </cell>
           <cell r="AF53">
-            <v>708</v>
+            <v>7444.4375</v>
           </cell>
           <cell r="AG53">
             <v>0.1</v>
@@ -9543,22 +9544,22 @@
             <v>18284.13</v>
           </cell>
           <cell r="AA54">
-            <v>2757.3333333333335</v>
+            <v>415.625</v>
           </cell>
           <cell r="AB54">
-            <v>81.865328820116048</v>
+            <v>543.10977443609022</v>
           </cell>
           <cell r="AC54">
-            <v>8.1865328820116048</v>
+            <v>54.310977443609019</v>
           </cell>
           <cell r="AD54">
-            <v>19815.666666666668</v>
+            <v>22157.375</v>
           </cell>
           <cell r="AE54">
-            <v>1378.6666666666667</v>
+            <v>207.8125</v>
           </cell>
           <cell r="AF54">
-            <v>-18437</v>
+            <v>-21949.5625</v>
           </cell>
           <cell r="AG54">
             <v>1881.0833333333333</v>
@@ -9635,22 +9636,22 @@
             <v>23675.49</v>
           </cell>
           <cell r="AA55">
-            <v>4637.3333333333339</v>
+            <v>2871.25</v>
           </cell>
           <cell r="AB55">
-            <v>63.029758481886134</v>
+            <v>101.79886808881149</v>
           </cell>
           <cell r="AC55">
-            <v>6.3029758481886136</v>
+            <v>10.179886808881148</v>
           </cell>
           <cell r="AD55">
-            <v>24591.666666666664</v>
+            <v>26357.75</v>
           </cell>
           <cell r="AE55">
-            <v>2318.666666666667</v>
+            <v>1435.625</v>
           </cell>
           <cell r="AF55">
-            <v>-22272.999999999996</v>
+            <v>-24922.125</v>
           </cell>
           <cell r="AG55">
             <v>2435.75</v>
@@ -9727,22 +9728,22 @@
             <v>13081.5</v>
           </cell>
           <cell r="AA56">
-            <v>2783.333333333333</v>
+            <v>4826.875</v>
           </cell>
           <cell r="AB56">
-            <v>58.02395209580839</v>
+            <v>33.458500582675128</v>
           </cell>
           <cell r="AC56">
-            <v>5.8023952095808387</v>
+            <v>3.3458500582675126</v>
           </cell>
           <cell r="AD56">
-            <v>13366.666666666668</v>
+            <v>11323.125</v>
           </cell>
           <cell r="AE56">
-            <v>1391.6666666666665</v>
+            <v>2413.4375</v>
           </cell>
           <cell r="AF56">
-            <v>-11975.000000000002</v>
+            <v>-8909.6875</v>
           </cell>
           <cell r="AG56">
             <v>1345.8333333333333</v>
@@ -9819,22 +9820,22 @@
             <v>15625.710000000001</v>
           </cell>
           <cell r="AA57">
-            <v>2464</v>
+            <v>2846.875</v>
           </cell>
           <cell r="AB57">
-            <v>78.291396103896105</v>
+            <v>67.762019758507137</v>
           </cell>
           <cell r="AC57">
-            <v>7.8291396103896105</v>
+            <v>6.7762019758507135</v>
           </cell>
           <cell r="AD57">
-            <v>16827</v>
+            <v>16444.125</v>
           </cell>
           <cell r="AE57">
-            <v>1232</v>
+            <v>1423.4375</v>
           </cell>
           <cell r="AF57">
-            <v>-15595</v>
+            <v>-15020.6875</v>
           </cell>
           <cell r="AG57">
             <v>1607.5833333333333</v>
@@ -9911,22 +9912,22 @@
             <v>1873.3000000000002</v>
           </cell>
           <cell r="AA58">
-            <v>428</v>
+            <v>2563.75</v>
           </cell>
           <cell r="AB58">
-            <v>16.705607476635514</v>
+            <v>2.7888834714773281</v>
           </cell>
           <cell r="AC58">
-            <v>1.6705607476635513</v>
+            <v>0.27888834714773281</v>
           </cell>
           <cell r="AD58">
-            <v>287</v>
+            <v>-1848.75</v>
           </cell>
           <cell r="AE58">
-            <v>214</v>
+            <v>1281.875</v>
           </cell>
           <cell r="AF58">
-            <v>-73</v>
+            <v>3130.625</v>
           </cell>
           <cell r="AG58">
             <v>119.16666666666667</v>
@@ -10003,22 +10004,22 @@
             <v>1011.32</v>
           </cell>
           <cell r="AA59">
-            <v>840</v>
+            <v>471.875</v>
           </cell>
           <cell r="AB59">
-            <v>4.5952380952380949</v>
+            <v>8.1801324503311257</v>
           </cell>
           <cell r="AC59">
-            <v>0.4595238095238095</v>
+            <v>0.81801324503311257</v>
           </cell>
           <cell r="AD59">
-            <v>-454</v>
+            <v>-85.875</v>
           </cell>
           <cell r="AE59">
-            <v>420</v>
+            <v>235.9375</v>
           </cell>
           <cell r="AF59">
-            <v>874</v>
+            <v>321.8125</v>
           </cell>
           <cell r="AG59">
             <v>64.333333333333329</v>
@@ -10095,22 +10096,22 @@
             <v>780.76</v>
           </cell>
           <cell r="AA60">
-            <v>469.33333333333331</v>
+            <v>922.5</v>
           </cell>
           <cell r="AB60">
-            <v>6.3494318181818183</v>
+            <v>3.230352303523035</v>
           </cell>
           <cell r="AC60">
-            <v>0.63494318181818188</v>
+            <v>0.32303523035230353</v>
           </cell>
           <cell r="AD60">
-            <v>-171.33333333333331</v>
+            <v>-624.5</v>
           </cell>
           <cell r="AE60">
-            <v>234.66666666666666</v>
+            <v>461.25</v>
           </cell>
           <cell r="AF60">
-            <v>406</v>
+            <v>1085.75</v>
           </cell>
           <cell r="AG60">
             <v>49.666666666666664</v>
@@ -10187,22 +10188,22 @@
             <v>382.52000000000004</v>
           </cell>
           <cell r="AA61">
-            <v>382</v>
+            <v>493.125</v>
           </cell>
           <cell r="AB61">
-            <v>3.8219895287958114</v>
+            <v>2.9607097591888465</v>
           </cell>
           <cell r="AC61">
-            <v>0.38219895287958117</v>
+            <v>0.29607097591888465</v>
           </cell>
           <cell r="AD61">
-            <v>-236</v>
+            <v>-347.125</v>
           </cell>
           <cell r="AE61">
-            <v>191</v>
+            <v>246.5625</v>
           </cell>
           <cell r="AF61">
-            <v>427</v>
+            <v>593.6875</v>
           </cell>
           <cell r="AG61">
             <v>24.333333333333332</v>
@@ -10213,7 +10214,7 @@
             <v>Units Produce</v>
           </cell>
           <cell r="AF62">
-            <v>117524</v>
+            <v>151405.6875</v>
           </cell>
         </row>
       </sheetData>
@@ -10227,6 +10228,7 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10551,212 +10553,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="63" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="63"/>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="63"/>
+      <c r="AB1" s="66"/>
+      <c r="AC1" s="66"/>
+      <c r="AD1" s="66"/>
+      <c r="AE1" s="66"/>
+      <c r="AF1" s="66"/>
+      <c r="AG1" s="66"/>
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
-      <c r="AA2" s="63"/>
-      <c r="AB2" s="63"/>
-      <c r="AC2" s="63"/>
-      <c r="AD2" s="63"/>
-      <c r="AE2" s="63"/>
-      <c r="AF2" s="63"/>
-      <c r="AG2" s="63"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="66"/>
+      <c r="AC2" s="66"/>
+      <c r="AD2" s="66"/>
+      <c r="AE2" s="66"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="62"/>
-      <c r="U3" s="62"/>
-      <c r="V3" s="62"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="62"/>
-      <c r="AA3" s="63"/>
-      <c r="AB3" s="63"/>
-      <c r="AC3" s="63"/>
-      <c r="AD3" s="63"/>
-      <c r="AE3" s="63"/>
-      <c r="AF3" s="63"/>
-      <c r="AG3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="66"/>
+      <c r="AB3" s="66"/>
+      <c r="AC3" s="66"/>
+      <c r="AD3" s="66"/>
+      <c r="AE3" s="66"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="62"/>
-      <c r="W4" s="62"/>
-      <c r="X4" s="62"/>
-      <c r="Y4" s="62"/>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="63"/>
-      <c r="AB4" s="63"/>
-      <c r="AC4" s="63"/>
-      <c r="AD4" s="63"/>
-      <c r="AE4" s="63"/>
-      <c r="AF4" s="63"/>
-      <c r="AG4" s="63"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="62"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="62"/>
-      <c r="Y5" s="62"/>
-      <c r="Z5" s="62"/>
-      <c r="AA5" s="63"/>
-      <c r="AB5" s="63"/>
-      <c r="AC5" s="63"/>
-      <c r="AD5" s="63"/>
-      <c r="AE5" s="63"/>
-      <c r="AF5" s="63"/>
-      <c r="AG5" s="63"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="66"/>
+      <c r="AB5" s="66"/>
+      <c r="AC5" s="66"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="63"/>
-      <c r="AB6" s="63"/>
-      <c r="AC6" s="63"/>
-      <c r="AD6" s="63"/>
-      <c r="AE6" s="63"/>
-      <c r="AF6" s="63"/>
-      <c r="AG6" s="63"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="66"/>
+      <c r="AB6" s="66"/>
+      <c r="AC6" s="66"/>
+      <c r="AD6" s="66"/>
+      <c r="AE6" s="66"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
@@ -11127,27 +11129,27 @@
       </c>
       <c r="AA13" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA13</f>
-        <v>11018.666666666666</v>
+        <v>11684.375</v>
       </c>
       <c r="AB13" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB13</f>
-        <v>9.0800459825750259</v>
+        <v>8.5627173040920024</v>
       </c>
       <c r="AC13" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC13</f>
-        <v>0.90800459825750246</v>
+        <v>0.85627173040920035</v>
       </c>
       <c r="AD13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD13</f>
-        <v>-1013.6666666666661</v>
+        <v>-1679.375</v>
       </c>
       <c r="AE13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE13</f>
-        <v>5509.333333333333</v>
+        <v>5842.1875</v>
       </c>
       <c r="AF13" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF13</f>
-        <v>6522.9999999999991</v>
+        <v>7521.5625</v>
       </c>
       <c r="AG13" s="27">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG13</f>
@@ -11255,27 +11257,27 @@
       </c>
       <c r="AA14" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA14</f>
-        <v>791.33333333333337</v>
+        <v>769.375</v>
       </c>
       <c r="AB14" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB14</f>
-        <v>7.0640269587194604</v>
+        <v>7.2656376929325752</v>
       </c>
       <c r="AC14" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC14</f>
-        <v>0.70640269587194604</v>
+        <v>0.7265637692932575</v>
       </c>
       <c r="AD14" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD14</f>
-        <v>-232.33333333333337</v>
+        <v>-210.375</v>
       </c>
       <c r="AE14" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE14</f>
-        <v>395.66666666666669</v>
+        <v>384.6875</v>
       </c>
       <c r="AF14" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF14</f>
-        <v>628</v>
+        <v>595.0625</v>
       </c>
       <c r="AG14" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG14</f>
@@ -11383,27 +11385,27 @@
       </c>
       <c r="AA15" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA15</f>
-        <v>4536.666666666667</v>
+        <v>4921.25</v>
       </c>
       <c r="AB15" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB15</f>
-        <v>7.5650257163850103</v>
+        <v>6.9738379476758956</v>
       </c>
       <c r="AC15" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC15</f>
-        <v>0.7565025716385011</v>
+        <v>0.69738379476758949</v>
       </c>
       <c r="AD15" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD15</f>
-        <v>-1104.666666666667</v>
+        <v>-1489.25</v>
       </c>
       <c r="AE15" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE15</f>
-        <v>2268.3333333333335</v>
+        <v>2460.625</v>
       </c>
       <c r="AF15" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF15</f>
-        <v>3373.0000000000005</v>
+        <v>3949.875</v>
       </c>
       <c r="AG15" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG15</f>
@@ -11511,27 +11513,27 @@
       </c>
       <c r="AA16" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA16</f>
-        <v>928</v>
+        <v>893.125</v>
       </c>
       <c r="AB16" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB16</f>
-        <v>2.2198275862068968</v>
+        <v>2.3065080475857243</v>
       </c>
       <c r="AC16" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC16</f>
-        <v>0.22198275862068967</v>
+        <v>0.23065080475857244</v>
       </c>
       <c r="AD16" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD16</f>
-        <v>-722</v>
+        <v>-687.125</v>
       </c>
       <c r="AE16" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE16</f>
-        <v>464</v>
+        <v>446.5625</v>
       </c>
       <c r="AF16" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF16</f>
-        <v>1186</v>
+        <v>1133.6875</v>
       </c>
       <c r="AG16" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG16</f>
@@ -11639,27 +11641,27 @@
       </c>
       <c r="AA17" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA17</f>
-        <v>116.66666666666666</v>
+        <v>109.375</v>
       </c>
       <c r="AB17" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB17</f>
-        <v>18.171428571428571</v>
+        <v>19.382857142857144</v>
       </c>
       <c r="AC17" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC17</f>
-        <v>1.8171428571428574</v>
+        <v>1.9382857142857144</v>
       </c>
       <c r="AD17" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD17</f>
-        <v>95.333333333333343</v>
+        <v>102.625</v>
       </c>
       <c r="AE17" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE17</f>
-        <v>58.333333333333329</v>
+        <v>54.6875</v>
       </c>
       <c r="AF17" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF17</f>
-        <v>-37.000000000000014</v>
+        <v>-47.9375</v>
       </c>
       <c r="AG17" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG17</f>
@@ -11767,27 +11769,27 @@
       </c>
       <c r="AA18" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA18</f>
-        <v>13038</v>
+        <v>14228.125</v>
       </c>
       <c r="AB18" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB18</f>
-        <v>6.4250651940481669</v>
+        <v>5.8876345266857015</v>
       </c>
       <c r="AC18" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC18</f>
-        <v>0.64250651940481673</v>
+        <v>0.58876345266857022</v>
       </c>
       <c r="AD18" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD18</f>
-        <v>-4661</v>
+        <v>-5851.125</v>
       </c>
       <c r="AE18" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE18</f>
-        <v>6519</v>
+        <v>7114.0625</v>
       </c>
       <c r="AF18" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF18</f>
-        <v>11180</v>
+        <v>12965.1875</v>
       </c>
       <c r="AG18" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG18</f>
@@ -11895,27 +11897,27 @@
       </c>
       <c r="AA19" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA19</f>
-        <v>1445.3333333333333</v>
+        <v>1448.125</v>
       </c>
       <c r="AB19" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB19</f>
-        <v>10.426660516605166</v>
+        <v>10.406560207164437</v>
       </c>
       <c r="AC19" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC19</f>
-        <v>1.0426660516605166</v>
+        <v>1.0406560207164437</v>
       </c>
       <c r="AD19" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD19</f>
-        <v>61.666666666666742</v>
+        <v>58.875</v>
       </c>
       <c r="AE19" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE19</f>
-        <v>722.66666666666663</v>
+        <v>724.0625</v>
       </c>
       <c r="AF19" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF19</f>
-        <v>660.99999999999989</v>
+        <v>665.1875</v>
       </c>
       <c r="AG19" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG19</f>
@@ -12023,27 +12025,27 @@
       </c>
       <c r="AA20" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA20</f>
-        <v>3058</v>
+        <v>3132.5</v>
       </c>
       <c r="AB20" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB20</f>
-        <v>12.969260954872466</v>
+        <v>12.660814046288907</v>
       </c>
       <c r="AC20" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC20</f>
-        <v>1.2969260954872466</v>
+        <v>1.2660814046288906</v>
       </c>
       <c r="AD20" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD20</f>
-        <v>908</v>
+        <v>833.5</v>
       </c>
       <c r="AE20" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE20</f>
-        <v>1529</v>
+        <v>1566.25</v>
       </c>
       <c r="AF20" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF20</f>
-        <v>621</v>
+        <v>732.75</v>
       </c>
       <c r="AG20" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG20</f>
@@ -12151,27 +12153,27 @@
       </c>
       <c r="AA21" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA21</f>
-        <v>7036</v>
+        <v>7136.25</v>
       </c>
       <c r="AB21" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB21</f>
-        <v>10.855599772598067</v>
+        <v>10.703100367840252</v>
       </c>
       <c r="AC21" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC21</f>
-        <v>1.0855599772598068</v>
+        <v>1.0703100367840253</v>
       </c>
       <c r="AD21" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD21</f>
-        <v>602</v>
+        <v>501.75</v>
       </c>
       <c r="AE21" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE21</f>
-        <v>3518</v>
+        <v>3568.125</v>
       </c>
       <c r="AF21" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF21</f>
-        <v>2916</v>
+        <v>3066.375</v>
       </c>
       <c r="AG21" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG21</f>
@@ -12279,27 +12281,27 @@
       </c>
       <c r="AA22" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA22</f>
-        <v>3326.666666666667</v>
+        <v>3313.75</v>
       </c>
       <c r="AB22" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB22</f>
-        <v>11.30561122244489</v>
+        <v>11.349679366276877</v>
       </c>
       <c r="AC22" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC22</f>
-        <v>1.1305611222444889</v>
+        <v>1.1349679366276877</v>
       </c>
       <c r="AD22" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD22</f>
-        <v>434.33333333333303</v>
+        <v>447.25</v>
       </c>
       <c r="AE22" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE22</f>
-        <v>1663.3333333333335</v>
+        <v>1656.875</v>
       </c>
       <c r="AF22" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF22</f>
-        <v>1229.0000000000005</v>
+        <v>1209.625</v>
       </c>
       <c r="AG22" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG22</f>
@@ -12407,27 +12409,27 @@
       </c>
       <c r="AA23" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA23</f>
-        <v>34037.333333333328</v>
+        <v>34954.375</v>
       </c>
       <c r="AB23" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB23</f>
-        <v>9.7443003760576641</v>
+        <v>9.4886548536485069</v>
       </c>
       <c r="AC23" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC23</f>
-        <v>0.97443003760576641</v>
+        <v>0.9488654853648506</v>
       </c>
       <c r="AD23" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD23</f>
-        <v>-870.33333333332848</v>
+        <v>-1787.375</v>
       </c>
       <c r="AE23" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE23</f>
-        <v>17018.666666666664</v>
+        <v>17477.1875</v>
       </c>
       <c r="AF23" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF23</f>
-        <v>17888.999999999993</v>
+        <v>19264.5625</v>
       </c>
       <c r="AG23" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG23</f>
@@ -12535,27 +12537,27 @@
       </c>
       <c r="AA24" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA24</f>
-        <v>22219.333333333336</v>
+        <v>22795.625</v>
       </c>
       <c r="AB24" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB24</f>
-        <v>11.272615440007201</v>
+        <v>10.987634688673813</v>
       </c>
       <c r="AC24" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC24</f>
-        <v>1.1272615440007199</v>
+        <v>1.0987634688673813</v>
       </c>
       <c r="AD24" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD24</f>
-        <v>2827.6666666666642</v>
+        <v>2251.375</v>
       </c>
       <c r="AE24" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE24</f>
-        <v>11109.666666666668</v>
+        <v>11397.8125</v>
       </c>
       <c r="AF24" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF24</f>
-        <v>8282.0000000000036</v>
+        <v>9146.4375</v>
       </c>
       <c r="AG24" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG24</f>
@@ -12663,27 +12665,27 @@
       </c>
       <c r="AA25" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA25</f>
-        <v>21740.666666666664</v>
+        <v>22229.375</v>
       </c>
       <c r="AB25" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB25</f>
-        <v>11.911778234338106</v>
+        <v>11.649900188376867</v>
       </c>
       <c r="AC25" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC25</f>
-        <v>1.1911778234338108</v>
+        <v>1.1649900188376867</v>
       </c>
       <c r="AD25" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD25</f>
-        <v>4156.3333333333358</v>
+        <v>3667.625</v>
       </c>
       <c r="AE25" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE25</f>
-        <v>10870.333333333332</v>
+        <v>11114.6875</v>
       </c>
       <c r="AF25" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF25</f>
-        <v>6713.9999999999964</v>
+        <v>7447.0625</v>
       </c>
       <c r="AG25" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG25</f>
@@ -12791,27 +12793,27 @@
       </c>
       <c r="AA26" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA26</f>
-        <v>25825.333333333332</v>
+        <v>26338.75</v>
       </c>
       <c r="AB26" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB26</f>
-        <v>11.472843203056431</v>
+        <v>11.249205068577666</v>
       </c>
       <c r="AC26" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC26</f>
-        <v>1.1472843203056431</v>
+        <v>1.1249205068577666</v>
       </c>
       <c r="AD26" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD26</f>
-        <v>3803.6666666666679</v>
+        <v>3290.25</v>
       </c>
       <c r="AE26" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE26</f>
-        <v>12912.666666666666</v>
+        <v>13169.375</v>
       </c>
       <c r="AF26" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF26</f>
-        <v>9108.9999999999982</v>
+        <v>9879.125</v>
       </c>
       <c r="AG26" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG26</f>
@@ -12919,27 +12921,27 @@
       </c>
       <c r="AA27" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA27</f>
-        <v>264</v>
+        <v>212.5</v>
       </c>
       <c r="AB27" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB27</f>
-        <v>57.424242424242429</v>
+        <v>71.341176470588238</v>
       </c>
       <c r="AC27" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC27</f>
-        <v>5.7424242424242422</v>
+        <v>7.1341176470588232</v>
       </c>
       <c r="AD27" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD27</f>
-        <v>1252</v>
+        <v>1303.5</v>
       </c>
       <c r="AE27" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE27</f>
-        <v>132</v>
+        <v>106.25</v>
       </c>
       <c r="AF27" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF27</f>
-        <v>-1120</v>
+        <v>-1197.25</v>
       </c>
       <c r="AG27" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG27</f>
@@ -12987,15 +12989,15 @@
       </c>
       <c r="L28" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L28</f>
-        <v>10.953068592057761</v>
+        <v>9.6604975124378107</v>
       </c>
       <c r="M28" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M28</f>
-        <v>6094</v>
+        <v>6909.375</v>
       </c>
       <c r="N28" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N28</f>
-        <v>-1121</v>
+        <v>-1676.9375</v>
       </c>
       <c r="O28" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O28</f>
@@ -13047,27 +13049,27 @@
       </c>
       <c r="AA28" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA28</f>
-        <v>2770</v>
+        <v>3140.625</v>
       </c>
       <c r="AB28" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB28</f>
-        <v>17.375451263537904</v>
+        <v>15.32497512437811</v>
       </c>
       <c r="AC28" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC28</f>
-        <v>1.7375451263537907</v>
+        <v>1.5324975124378108</v>
       </c>
       <c r="AD28" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD28</f>
-        <v>2043</v>
+        <v>1672.375</v>
       </c>
       <c r="AE28" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE28</f>
-        <v>1385</v>
+        <v>1570.3125</v>
       </c>
       <c r="AF28" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF28</f>
-        <v>-658</v>
+        <v>-102.0625</v>
       </c>
       <c r="AG28" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG28</f>
@@ -13115,15 +13117,15 @@
       </c>
       <c r="L29" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L29</f>
-        <v>9.0151674741942287</v>
+        <v>8.005612065941774</v>
       </c>
       <c r="M29" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M29</f>
-        <v>6962.2666666666664</v>
+        <v>7840.25</v>
       </c>
       <c r="N29" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N29</f>
-        <v>-1894</v>
+        <v>-2492.625</v>
       </c>
       <c r="O29" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O29</f>
@@ -13175,27 +13177,27 @@
       </c>
       <c r="AA29" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA29</f>
-        <v>3164.6666666666665</v>
+        <v>3563.75</v>
       </c>
       <c r="AB29" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB29</f>
-        <v>14.386981251316623</v>
+        <v>12.775868116450368</v>
       </c>
       <c r="AC29" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC29</f>
-        <v>1.4386981251316622</v>
+        <v>1.2775868116450368</v>
       </c>
       <c r="AD29" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD29</f>
-        <v>1388.3333333333335</v>
+        <v>989.25</v>
       </c>
       <c r="AE29" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE29</f>
-        <v>1582.3333333333333</v>
+        <v>1781.875</v>
       </c>
       <c r="AF29" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF29</f>
-        <v>193.99999999999977</v>
+        <v>792.625</v>
       </c>
       <c r="AG29" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG29</f>
@@ -13243,15 +13245,15 @@
       </c>
       <c r="L30" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L30</f>
-        <v>9.2923280423280428</v>
+        <v>8.2043795620437958</v>
       </c>
       <c r="M30" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M30</f>
-        <v>6652.7999999999993</v>
+        <v>7535</v>
       </c>
       <c r="N30" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N30</f>
-        <v>-1726</v>
+        <v>-2327.5</v>
       </c>
       <c r="O30" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O30</f>
@@ -13303,27 +13305,27 @@
       </c>
       <c r="AA30" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA30</f>
-        <v>3024</v>
+        <v>3425</v>
       </c>
       <c r="AB30" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB30</f>
-        <v>19.933862433862437</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="AC30" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC30</f>
-        <v>1.9933862433862435</v>
+        <v>1.76</v>
       </c>
       <c r="AD30" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD30</f>
-        <v>3004</v>
+        <v>2603</v>
       </c>
       <c r="AE30" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE30</f>
-        <v>1512</v>
+        <v>1712.5</v>
       </c>
       <c r="AF30" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF30</f>
-        <v>-1492</v>
+        <v>-890.5</v>
       </c>
       <c r="AG30" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG30</f>
@@ -13431,27 +13433,27 @@
       </c>
       <c r="AA31" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA31</f>
-        <v>2249.3333333333335</v>
+        <v>2256.875</v>
       </c>
       <c r="AB31" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB31</f>
-        <v>6.0951393005334911</v>
+        <v>6.0747715314317361</v>
       </c>
       <c r="AC31" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC31</f>
-        <v>0.60951393005334908</v>
+        <v>0.60747715314317363</v>
       </c>
       <c r="AD31" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD31</f>
-        <v>-878.33333333333348</v>
+        <v>-885.875</v>
       </c>
       <c r="AE31" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE31</f>
-        <v>1124.6666666666667</v>
+        <v>1128.4375</v>
       </c>
       <c r="AF31" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF31</f>
-        <v>2003.0000000000002</v>
+        <v>2014.3125</v>
       </c>
       <c r="AG31" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG31</f>
@@ -13559,27 +13561,27 @@
       </c>
       <c r="AA32" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA32</f>
-        <v>1282</v>
+        <v>1303.75</v>
       </c>
       <c r="AB32" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB32</f>
-        <v>7.64430577223089</v>
+        <v>7.5167785234899327</v>
       </c>
       <c r="AC32" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC32</f>
-        <v>0.76443057722308894</v>
+        <v>0.75167785234899331</v>
       </c>
       <c r="AD32" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD32</f>
-        <v>-302</v>
+        <v>-323.75</v>
       </c>
       <c r="AE32" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE32</f>
-        <v>641</v>
+        <v>651.875</v>
       </c>
       <c r="AF32" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF32</f>
-        <v>943</v>
+        <v>975.625</v>
       </c>
       <c r="AG32" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG32</f>
@@ -13687,27 +13689,27 @@
       </c>
       <c r="AA33" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA33</f>
-        <v>4766.666666666667</v>
+        <v>4897.5</v>
       </c>
       <c r="AB33" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB33</f>
-        <v>6.9272727272727268</v>
+        <v>6.7422154160285857</v>
       </c>
       <c r="AC33" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC33</f>
-        <v>0.69272727272727264</v>
+        <v>0.67422154160285863</v>
       </c>
       <c r="AD33" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD33</f>
-        <v>-1464.666666666667</v>
+        <v>-1595.5</v>
       </c>
       <c r="AE33" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE33</f>
-        <v>2383.3333333333335</v>
+        <v>2448.75</v>
       </c>
       <c r="AF33" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF33</f>
-        <v>3848.0000000000005</v>
+        <v>4044.25</v>
       </c>
       <c r="AG33" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG33</f>
@@ -13815,27 +13817,27 @@
       </c>
       <c r="AA34" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA34</f>
-        <v>7453.3333333333339</v>
+        <v>7733.75</v>
       </c>
       <c r="AB34" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB34</f>
-        <v>8.4619856887298752</v>
+        <v>8.1551640536609025</v>
       </c>
       <c r="AC34" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC34</f>
-        <v>0.84619856887298739</v>
+        <v>0.81551640536609016</v>
       </c>
       <c r="AD34" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD34</f>
-        <v>-1146.3333333333339</v>
+        <v>-1426.75</v>
       </c>
       <c r="AE34" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE34</f>
-        <v>3726.666666666667</v>
+        <v>3866.875</v>
       </c>
       <c r="AF34" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF34</f>
-        <v>4873.0000000000009</v>
+        <v>5293.625</v>
       </c>
       <c r="AG34" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG34</f>
@@ -13943,7 +13945,7 @@
       </c>
       <c r="AA35" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA35</f>
-        <v>66.666666666666671</v>
+        <v>772.5</v>
       </c>
       <c r="AB35" s="34">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB35</f>
@@ -13955,15 +13957,15 @@
       </c>
       <c r="AD35" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD35</f>
-        <v>-66.666666666666671</v>
+        <v>-772.5</v>
       </c>
       <c r="AE35" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE35</f>
-        <v>33.333333333333336</v>
+        <v>386.25</v>
       </c>
       <c r="AF35" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF35</f>
-        <v>100</v>
+        <v>1158.75</v>
       </c>
       <c r="AG35" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG35</f>
@@ -14071,27 +14073,27 @@
       </c>
       <c r="AA36" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA36</f>
-        <v>1136</v>
+        <v>7180</v>
       </c>
       <c r="AB36" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB36</f>
-        <v>4.779929577464789</v>
+        <v>0.75626740947075211</v>
       </c>
       <c r="AC36" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC36</f>
-        <v>0.47799295774647887</v>
+        <v>7.5626740947075208E-2</v>
       </c>
       <c r="AD36" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD36</f>
-        <v>-593</v>
+        <v>-6637</v>
       </c>
       <c r="AE36" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE36</f>
-        <v>568</v>
+        <v>3590</v>
       </c>
       <c r="AF36" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF36</f>
-        <v>1161</v>
+        <v>10227</v>
       </c>
       <c r="AG36" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG36</f>
@@ -14199,27 +14201,27 @@
       </c>
       <c r="AA37" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA37</f>
-        <v>6322.6666666666661</v>
+        <v>11913.75</v>
       </c>
       <c r="AB37" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB37</f>
-        <v>16.081822016026994</v>
+        <v>8.5346763193788693</v>
       </c>
       <c r="AC37" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC37</f>
-        <v>1.6081822016026994</v>
+        <v>0.85346763193788688</v>
       </c>
       <c r="AD37" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD37</f>
-        <v>3845.3333333333339</v>
+        <v>-1745.75</v>
       </c>
       <c r="AE37" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE37</f>
-        <v>3161.333333333333</v>
+        <v>5956.875</v>
       </c>
       <c r="AF37" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF37</f>
-        <v>-684.00000000000091</v>
+        <v>7702.625</v>
       </c>
       <c r="AG37" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG37</f>
@@ -14327,27 +14329,27 @@
       </c>
       <c r="AA38" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA38</f>
-        <v>10202.666666666666</v>
+        <v>5083.125</v>
       </c>
       <c r="AB38" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB38</f>
-        <v>9.6621798222686888</v>
+        <v>19.393581704168202</v>
       </c>
       <c r="AC38" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC38</f>
-        <v>0.96621798222686883</v>
+        <v>1.9393581704168203</v>
       </c>
       <c r="AD38" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD38</f>
-        <v>-344.66666666666606</v>
+        <v>4774.875</v>
       </c>
       <c r="AE38" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE38</f>
-        <v>5101.333333333333</v>
+        <v>2541.5625</v>
       </c>
       <c r="AF38" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF38</f>
-        <v>5445.9999999999991</v>
+        <v>-2233.3125</v>
       </c>
       <c r="AG38" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG38</f>
@@ -14455,27 +14457,27 @@
       </c>
       <c r="AA39" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA39</f>
-        <v>4895.3333333333339</v>
+        <v>3739.375</v>
       </c>
       <c r="AB39" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB39</f>
-        <v>4.0160697262699161</v>
+        <v>5.2575630954370718</v>
       </c>
       <c r="AC39" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC39</f>
-        <v>0.40160697262699163</v>
+        <v>0.52575630954370722</v>
       </c>
       <c r="AD39" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD39</f>
-        <v>-2929.3333333333339</v>
+        <v>-1773.375</v>
       </c>
       <c r="AE39" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE39</f>
-        <v>2447.666666666667</v>
+        <v>1869.6875</v>
       </c>
       <c r="AF39" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF39</f>
-        <v>5377.0000000000009</v>
+        <v>3643.0625</v>
       </c>
       <c r="AG39" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG39</f>
@@ -14583,27 +14585,27 @@
       </c>
       <c r="AA40" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA40</f>
-        <v>3359.3333333333335</v>
+        <v>506.25</v>
       </c>
       <c r="AB40" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB40</f>
-        <v>13.532446914070253</v>
+        <v>89.797530864197526</v>
       </c>
       <c r="AC40" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC40</f>
-        <v>1.3532446914070251</v>
+        <v>8.9797530864197537</v>
       </c>
       <c r="AD40" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD40</f>
-        <v>1186.6666666666665</v>
+        <v>4039.75</v>
       </c>
       <c r="AE40" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE40</f>
-        <v>1679.6666666666667</v>
+        <v>253.125</v>
       </c>
       <c r="AF40" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF40</f>
-        <v>493.00000000000023</v>
+        <v>-3786.625</v>
       </c>
       <c r="AG40" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG40</f>
@@ -14967,27 +14969,27 @@
       </c>
       <c r="AA43" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA43</f>
-        <v>1175.3333333333333</v>
+        <v>1314.375</v>
       </c>
       <c r="AB43" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB43</f>
-        <v>5.6239364719228586</v>
+        <v>5.0290061816452685</v>
       </c>
       <c r="AC43" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC43</f>
-        <v>0.56239364719228591</v>
+        <v>0.50290061816452691</v>
       </c>
       <c r="AD43" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD43</f>
-        <v>-514.33333333333326</v>
+        <v>-653.375</v>
       </c>
       <c r="AE43" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE43</f>
-        <v>587.66666666666663</v>
+        <v>657.1875</v>
       </c>
       <c r="AF43" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF43</f>
-        <v>1102</v>
+        <v>1310.5625</v>
       </c>
       <c r="AG43" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG43</f>
@@ -15095,27 +15097,27 @@
       </c>
       <c r="AA44" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA44</f>
-        <v>1271.3333333333335</v>
+        <v>5966.875</v>
       </c>
       <c r="AB44" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB44</f>
-        <v>8.9276350288411095</v>
+        <v>1.9021682203833665</v>
       </c>
       <c r="AC44" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC44</f>
-        <v>0.8927635028841111</v>
+        <v>0.19021682203833665</v>
       </c>
       <c r="AD44" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD44</f>
-        <v>-136.33333333333348</v>
+        <v>-4831.875</v>
       </c>
       <c r="AE44" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE44</f>
-        <v>635.66666666666674</v>
+        <v>2983.4375</v>
       </c>
       <c r="AF44" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF44</f>
-        <v>772.00000000000023</v>
+        <v>7815.3125</v>
       </c>
       <c r="AG44" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG44</f>
@@ -15223,27 +15225,27 @@
       </c>
       <c r="AA45" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA45</f>
-        <v>5564</v>
+        <v>6235.625</v>
       </c>
       <c r="AB45" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB45</f>
-        <v>7.4622573687994249</v>
+        <v>6.6585145835421473</v>
       </c>
       <c r="AC45" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC45</f>
-        <v>0.74622573687994254</v>
+        <v>0.66585145835421466</v>
       </c>
       <c r="AD45" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD45</f>
-        <v>-1412</v>
+        <v>-2083.625</v>
       </c>
       <c r="AE45" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE45</f>
-        <v>2782</v>
+        <v>3117.8125</v>
       </c>
       <c r="AF45" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF45</f>
-        <v>4194</v>
+        <v>5201.4375</v>
       </c>
       <c r="AG45" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG45</f>
@@ -15351,27 +15353,27 @@
       </c>
       <c r="AA46" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA46</f>
-        <v>5998</v>
+        <v>8279.375</v>
       </c>
       <c r="AB46" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB46</f>
-        <v>14.258086028676226</v>
+        <v>10.329282101607911</v>
       </c>
       <c r="AC46" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC46</f>
-        <v>1.4258086028676225</v>
+        <v>1.0329282101607911</v>
       </c>
       <c r="AD46" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD46</f>
-        <v>2554</v>
+        <v>272.625</v>
       </c>
       <c r="AE46" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE46</f>
-        <v>2999</v>
+        <v>4139.6875</v>
       </c>
       <c r="AF46" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF46</f>
-        <v>445</v>
+        <v>3867.0625</v>
       </c>
       <c r="AG46" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG46</f>
@@ -15479,27 +15481,27 @@
       </c>
       <c r="AA47" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA47</f>
-        <v>7872</v>
+        <v>5571.875</v>
       </c>
       <c r="AB47" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB47</f>
-        <v>8.5530995934959346</v>
+        <v>12.083903533370723</v>
       </c>
       <c r="AC47" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC47</f>
-        <v>0.85530995934959353</v>
+        <v>1.2083903533370723</v>
       </c>
       <c r="AD47" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD47</f>
-        <v>-1139</v>
+        <v>1161.125</v>
       </c>
       <c r="AE47" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE47</f>
-        <v>3936</v>
+        <v>2785.9375</v>
       </c>
       <c r="AF47" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF47</f>
-        <v>5075</v>
+        <v>1624.8125</v>
       </c>
       <c r="AG47" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG47</f>
@@ -15607,27 +15609,27 @@
       </c>
       <c r="AA48" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA48</f>
-        <v>5340</v>
+        <v>26.25</v>
       </c>
       <c r="AB48" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB48</f>
-        <v>9.7883895131086138</v>
+        <v>1991.2380952380952</v>
       </c>
       <c r="AC48" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC48</f>
-        <v>0.9788389513108614</v>
+        <v>199.12380952380951</v>
       </c>
       <c r="AD48" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD48</f>
-        <v>-113</v>
+        <v>5200.75</v>
       </c>
       <c r="AE48" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE48</f>
-        <v>2670</v>
+        <v>13.125</v>
       </c>
       <c r="AF48" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF48</f>
-        <v>2783</v>
+        <v>-5187.625</v>
       </c>
       <c r="AG48" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG48</f>
@@ -15733,29 +15735,29 @@
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!Z49</f>
         <v>216</v>
       </c>
-      <c r="AA49" s="36">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA49</f>
-        <v>23.333333333333336</v>
-      </c>
-      <c r="AB49" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB49</f>
-        <v>5.1428571428571423</v>
-      </c>
-      <c r="AC49" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC49</f>
-        <v>0.51428571428571423</v>
-      </c>
-      <c r="AD49" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD49</f>
-        <v>-11.333333333333336</v>
-      </c>
-      <c r="AE49" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE49</f>
-        <v>11.666666666666668</v>
-      </c>
-      <c r="AF49" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF49</f>
-        <v>23.000000000000004</v>
+      <c r="AA49" s="36" t="e">
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA49</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AB49" s="25" t="e">
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB49</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AC49" s="26" t="e">
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC49</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AD49" s="29" t="e">
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD49</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AE49" s="30" t="e">
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE49</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AF49" s="28" t="e">
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF49</f>
+        <v>#REF!</v>
       </c>
       <c r="AG49" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG49</f>
@@ -15863,7 +15865,7 @@
       </c>
       <c r="AA50" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA50</f>
-        <v>1.3333333333333333</v>
+        <v>421.875</v>
       </c>
       <c r="AB50" s="25">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB50</f>
@@ -15875,15 +15877,15 @@
       </c>
       <c r="AD50" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD50</f>
-        <v>9.6666666666666661</v>
+        <v>-410.875</v>
       </c>
       <c r="AE50" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE50</f>
-        <v>0.66666666666666663</v>
+        <v>210.9375</v>
       </c>
       <c r="AF50" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF50</f>
-        <v>-9</v>
+        <v>621.8125</v>
       </c>
       <c r="AG50" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG50</f>
@@ -15991,27 +15993,27 @@
       </c>
       <c r="AA51" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA51</f>
-        <v>699.33333333333337</v>
+        <v>5</v>
       </c>
       <c r="AB51" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB51</f>
-        <v>0.61487130600571971</v>
+        <v>86</v>
       </c>
       <c r="AC51" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC51</f>
-        <v>6.1487130600571968E-2</v>
+        <v>8.6</v>
       </c>
       <c r="AD51" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD51</f>
-        <v>-656.33333333333337</v>
+        <v>38</v>
       </c>
       <c r="AE51" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE51</f>
-        <v>349.66666666666669</v>
+        <v>2.5</v>
       </c>
       <c r="AF51" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF51</f>
-        <v>1006</v>
+        <v>-35.5</v>
       </c>
       <c r="AG51" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG51</f>
@@ -16247,27 +16249,27 @@
       </c>
       <c r="AA53" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA53</f>
-        <v>474.66666666666669</v>
+        <v>4965.625</v>
       </c>
       <c r="AB53" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB53</f>
-        <v>8.4269662921348312E-2</v>
+        <v>8.0553807426054121E-3</v>
       </c>
       <c r="AC53" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC53</f>
-        <v>8.4269662921348312E-3</v>
+        <v>8.0553807426054125E-4</v>
       </c>
       <c r="AD53" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD53</f>
-        <v>-470.66666666666669</v>
+        <v>-4961.625</v>
       </c>
       <c r="AE53" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE53</f>
-        <v>237.33333333333334</v>
+        <v>2482.8125</v>
       </c>
       <c r="AF53" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF53</f>
-        <v>708</v>
+        <v>7444.4375</v>
       </c>
       <c r="AG53" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG53</f>
@@ -16375,27 +16377,27 @@
       </c>
       <c r="AA54" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA54</f>
-        <v>2757.3333333333335</v>
+        <v>415.625</v>
       </c>
       <c r="AB54" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB54</f>
-        <v>81.865328820116048</v>
+        <v>543.10977443609022</v>
       </c>
       <c r="AC54" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC54</f>
-        <v>8.1865328820116048</v>
+        <v>54.310977443609019</v>
       </c>
       <c r="AD54" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD54</f>
-        <v>19815.666666666668</v>
+        <v>22157.375</v>
       </c>
       <c r="AE54" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE54</f>
-        <v>1378.6666666666667</v>
+        <v>207.8125</v>
       </c>
       <c r="AF54" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF54</f>
-        <v>-18437</v>
+        <v>-21949.5625</v>
       </c>
       <c r="AG54" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG54</f>
@@ -16503,27 +16505,27 @@
       </c>
       <c r="AA55" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA55</f>
-        <v>4637.3333333333339</v>
+        <v>2871.25</v>
       </c>
       <c r="AB55" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB55</f>
-        <v>63.029758481886134</v>
+        <v>101.79886808881149</v>
       </c>
       <c r="AC55" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC55</f>
-        <v>6.3029758481886136</v>
+        <v>10.179886808881148</v>
       </c>
       <c r="AD55" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD55</f>
-        <v>24591.666666666664</v>
+        <v>26357.75</v>
       </c>
       <c r="AE55" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE55</f>
-        <v>2318.666666666667</v>
+        <v>1435.625</v>
       </c>
       <c r="AF55" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF55</f>
-        <v>-22272.999999999996</v>
+        <v>-24922.125</v>
       </c>
       <c r="AG55" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG55</f>
@@ -16631,27 +16633,27 @@
       </c>
       <c r="AA56" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA56</f>
-        <v>2783.333333333333</v>
+        <v>4826.875</v>
       </c>
       <c r="AB56" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB56</f>
-        <v>58.02395209580839</v>
+        <v>33.458500582675128</v>
       </c>
       <c r="AC56" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC56</f>
-        <v>5.8023952095808387</v>
+        <v>3.3458500582675126</v>
       </c>
       <c r="AD56" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD56</f>
-        <v>13366.666666666668</v>
+        <v>11323.125</v>
       </c>
       <c r="AE56" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE56</f>
-        <v>1391.6666666666665</v>
+        <v>2413.4375</v>
       </c>
       <c r="AF56" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF56</f>
-        <v>-11975.000000000002</v>
+        <v>-8909.6875</v>
       </c>
       <c r="AG56" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG56</f>
@@ -16759,27 +16761,27 @@
       </c>
       <c r="AA57" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA57</f>
-        <v>2464</v>
+        <v>2846.875</v>
       </c>
       <c r="AB57" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB57</f>
-        <v>78.291396103896105</v>
+        <v>67.762019758507137</v>
       </c>
       <c r="AC57" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC57</f>
-        <v>7.8291396103896105</v>
+        <v>6.7762019758507135</v>
       </c>
       <c r="AD57" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD57</f>
-        <v>16827</v>
+        <v>16444.125</v>
       </c>
       <c r="AE57" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE57</f>
-        <v>1232</v>
+        <v>1423.4375</v>
       </c>
       <c r="AF57" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF57</f>
-        <v>-15595</v>
+        <v>-15020.6875</v>
       </c>
       <c r="AG57" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG57</f>
@@ -16887,27 +16889,27 @@
       </c>
       <c r="AA58" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA58</f>
-        <v>428</v>
+        <v>2563.75</v>
       </c>
       <c r="AB58" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB58</f>
-        <v>16.705607476635514</v>
+        <v>2.7888834714773281</v>
       </c>
       <c r="AC58" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC58</f>
-        <v>1.6705607476635513</v>
+        <v>0.27888834714773281</v>
       </c>
       <c r="AD58" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD58</f>
-        <v>287</v>
+        <v>-1848.75</v>
       </c>
       <c r="AE58" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE58</f>
-        <v>214</v>
+        <v>1281.875</v>
       </c>
       <c r="AF58" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF58</f>
-        <v>-73</v>
+        <v>3130.625</v>
       </c>
       <c r="AG58" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG58</f>
@@ -17015,27 +17017,27 @@
       </c>
       <c r="AA59" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA59</f>
-        <v>840</v>
+        <v>471.875</v>
       </c>
       <c r="AB59" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB59</f>
-        <v>4.5952380952380949</v>
+        <v>8.1801324503311257</v>
       </c>
       <c r="AC59" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC59</f>
-        <v>0.4595238095238095</v>
+        <v>0.81801324503311257</v>
       </c>
       <c r="AD59" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD59</f>
-        <v>-454</v>
+        <v>-85.875</v>
       </c>
       <c r="AE59" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE59</f>
-        <v>420</v>
+        <v>235.9375</v>
       </c>
       <c r="AF59" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF59</f>
-        <v>874</v>
+        <v>321.8125</v>
       </c>
       <c r="AG59" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG59</f>
@@ -17143,27 +17145,27 @@
       </c>
       <c r="AA60" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA60</f>
-        <v>469.33333333333331</v>
+        <v>922.5</v>
       </c>
       <c r="AB60" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB60</f>
-        <v>6.3494318181818183</v>
+        <v>3.230352303523035</v>
       </c>
       <c r="AC60" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC60</f>
-        <v>0.63494318181818188</v>
+        <v>0.32303523035230353</v>
       </c>
       <c r="AD60" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD60</f>
-        <v>-171.33333333333331</v>
+        <v>-624.5</v>
       </c>
       <c r="AE60" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE60</f>
-        <v>234.66666666666666</v>
+        <v>461.25</v>
       </c>
       <c r="AF60" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF60</f>
-        <v>406</v>
+        <v>1085.75</v>
       </c>
       <c r="AG60" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG60</f>
@@ -17271,27 +17273,27 @@
       </c>
       <c r="AA61" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA61</f>
-        <v>382</v>
+        <v>493.125</v>
       </c>
       <c r="AB61" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB61</f>
-        <v>3.8219895287958114</v>
+        <v>2.9607097591888465</v>
       </c>
       <c r="AC61" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC61</f>
-        <v>0.38219895287958117</v>
+        <v>0.29607097591888465</v>
       </c>
       <c r="AD61" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD61</f>
-        <v>-236</v>
+        <v>-347.125</v>
       </c>
       <c r="AE61" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE61</f>
-        <v>191</v>
+        <v>246.5625</v>
       </c>
       <c r="AF61" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF61</f>
-        <v>427</v>
+        <v>593.6875</v>
       </c>
       <c r="AG61" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG61</f>
@@ -17331,7 +17333,7 @@
       </c>
       <c r="AF62" s="44">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF62</f>
-        <v>117524</v>
+        <v>151405.6875</v>
       </c>
     </row>
     <row r="63" spans="2:33" x14ac:dyDescent="0.25">
@@ -17340,10 +17342,10 @@
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
-      <c r="E63" s="64" t="s">
+      <c r="E63" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="F63" s="64"/>
+      <c r="F63" s="67"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -17368,10 +17370,10 @@
       <c r="AB63" s="42"/>
     </row>
     <row r="64" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B64" s="65" t="s">
+      <c r="B64" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="65"/>
+      <c r="C64" s="63"/>
       <c r="D64" s="48">
         <f>SUM(F13:F61)</f>
         <v>144936.54999999999</v>
@@ -17516,19 +17518,19 @@
       <c r="AB67" s="42"/>
     </row>
     <row r="68" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B68" s="65" t="s">
+      <c r="B68" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="C68" s="65"/>
+      <c r="C68" s="63"/>
       <c r="D68" s="50">
         <f>SUM(Z13:Z61)</f>
         <v>421177.93000000017</v>
       </c>
-      <c r="E68" s="66">
+      <c r="E68" s="64">
         <f>D68*100/D68</f>
         <v>100</v>
       </c>
-      <c r="F68" s="66"/>
+      <c r="F68" s="64"/>
       <c r="G68" s="51"/>
       <c r="H68" s="51"/>
       <c r="I68" s="51"/>
@@ -17613,10 +17615,10 @@
       <c r="AB70" s="42"/>
     </row>
     <row r="71" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="65"/>
+      <c r="C71" s="63"/>
       <c r="D71" s="3">
         <f>SUM(E13:E61)</f>
         <v>112990</v>
@@ -17731,11 +17733,11 @@
         <f>SUM(T13:T61)</f>
         <v>36961</v>
       </c>
-      <c r="E74" s="67">
+      <c r="E74" s="62">
         <f>D74*100/D75</f>
         <v>11.039956032533535</v>
       </c>
-      <c r="F74" s="67"/>
+      <c r="F74" s="62"/>
       <c r="G74" s="56"/>
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
@@ -17760,19 +17762,19 @@
       <c r="AB74" s="42"/>
     </row>
     <row r="75" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="63"/>
       <c r="D75" s="55">
         <f>SUM(Y13:Y61)</f>
         <v>334793</v>
       </c>
-      <c r="E75" s="67">
+      <c r="E75" s="62">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="67"/>
+      <c r="F75" s="62"/>
       <c r="G75" s="56"/>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
@@ -18533,23 +18535,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="B1:Z6"/>
+    <mergeCell ref="AA1:AG6"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="E64:F64"/>
     <mergeCell ref="E66:F66"/>
     <mergeCell ref="E67:F67"/>
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="E68:F68"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="B1:Z6"/>
-    <mergeCell ref="AA1:AG6"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G61">
     <cfRule type="colorScale" priority="5">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8335D7-F86F-4BFE-BE29-508B78B70387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEECDEE-463A-42F6-A01A-8448DE9F3733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -841,15 +841,6 @@
     <xf numFmtId="2" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -858,6 +849,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5645,6 +5645,9 @@
       <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
+      <sheetName val="Hoja1"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -5772,22 +5775,22 @@
             <v>13606.800000000001</v>
           </cell>
           <cell r="AA13">
-            <v>11684.375</v>
+            <v>11850.555555555557</v>
           </cell>
           <cell r="AB13">
-            <v>8.5627173040920024</v>
+            <v>8.4426421639866849</v>
           </cell>
           <cell r="AC13">
-            <v>0.85627173040920035</v>
+            <v>0.84426421639866855</v>
           </cell>
           <cell r="AD13">
-            <v>-1679.375</v>
+            <v>-1845.5555555555566</v>
           </cell>
           <cell r="AE13">
-            <v>5842.1875</v>
+            <v>5925.2777777777783</v>
           </cell>
           <cell r="AF13">
-            <v>7521.5625</v>
+            <v>7770.8333333333348</v>
           </cell>
           <cell r="AG13">
             <v>125.0625</v>
@@ -5864,22 +5867,22 @@
             <v>888.81000000000006</v>
           </cell>
           <cell r="AA14">
-            <v>769.375</v>
+            <v>719.44444444444446</v>
           </cell>
           <cell r="AB14">
-            <v>7.2656376929325752</v>
+            <v>7.7698841698841701</v>
           </cell>
           <cell r="AC14">
-            <v>0.7265637692932575</v>
+            <v>0.77698841698841703</v>
           </cell>
           <cell r="AD14">
-            <v>-210.375</v>
+            <v>-160.44444444444446</v>
           </cell>
           <cell r="AE14">
-            <v>384.6875</v>
+            <v>359.72222222222223</v>
           </cell>
           <cell r="AF14">
-            <v>595.0625</v>
+            <v>520.16666666666674</v>
           </cell>
           <cell r="AG14">
             <v>6.9874999999999998</v>
@@ -5956,22 +5959,22 @@
             <v>6966.9599999999991</v>
           </cell>
           <cell r="AA15">
-            <v>4921.25</v>
+            <v>4920</v>
           </cell>
           <cell r="AB15">
-            <v>6.9738379476758956</v>
+            <v>6.975609756097561</v>
           </cell>
           <cell r="AC15">
-            <v>0.69738379476758949</v>
+            <v>0.69756097560975605</v>
           </cell>
           <cell r="AD15">
-            <v>-1489.25</v>
+            <v>-1488</v>
           </cell>
           <cell r="AE15">
-            <v>2460.625</v>
+            <v>2460</v>
           </cell>
           <cell r="AF15">
-            <v>3949.875</v>
+            <v>3948</v>
           </cell>
           <cell r="AG15">
             <v>57.2</v>
@@ -6048,22 +6051,22 @@
             <v>743.66</v>
           </cell>
           <cell r="AA16">
-            <v>893.125</v>
+            <v>857.22222222222229</v>
           </cell>
           <cell r="AB16">
-            <v>2.3065080475857243</v>
+            <v>2.4031108230719376</v>
           </cell>
           <cell r="AC16">
-            <v>0.23065080475857244</v>
+            <v>0.24031108230719375</v>
           </cell>
           <cell r="AD16">
-            <v>-687.125</v>
+            <v>-651.22222222222229</v>
           </cell>
           <cell r="AE16">
-            <v>446.5625</v>
+            <v>428.61111111111114</v>
           </cell>
           <cell r="AF16">
-            <v>1133.6875</v>
+            <v>1079.8333333333335</v>
           </cell>
           <cell r="AG16">
             <v>7.3571428571428568</v>
@@ -6140,22 +6143,22 @@
             <v>1861.36</v>
           </cell>
           <cell r="AA17">
-            <v>109.375</v>
+            <v>110</v>
           </cell>
           <cell r="AB17">
-            <v>19.382857142857144</v>
+            <v>19.272727272727273</v>
           </cell>
           <cell r="AC17">
-            <v>1.9382857142857144</v>
+            <v>1.9272727272727272</v>
           </cell>
           <cell r="AD17">
-            <v>102.625</v>
+            <v>102</v>
           </cell>
           <cell r="AE17">
-            <v>54.6875</v>
+            <v>55</v>
           </cell>
           <cell r="AF17">
-            <v>-47.9375</v>
+            <v>-47</v>
           </cell>
           <cell r="AG17">
             <v>17.666666666666668</v>
@@ -6232,22 +6235,22 @@
             <v>5277.51</v>
           </cell>
           <cell r="AA18">
-            <v>14228.125</v>
+            <v>14348.333333333332</v>
           </cell>
           <cell r="AB18">
-            <v>5.8876345266857015</v>
+            <v>5.8383087466604717</v>
           </cell>
           <cell r="AC18">
-            <v>0.58876345266857022</v>
+            <v>0.58383087466604722</v>
           </cell>
           <cell r="AD18">
-            <v>-5851.125</v>
+            <v>-5971.3333333333321</v>
           </cell>
           <cell r="AE18">
-            <v>7114.0625</v>
+            <v>7174.1666666666661</v>
           </cell>
           <cell r="AF18">
-            <v>12965.1875</v>
+            <v>13145.499999999998</v>
           </cell>
           <cell r="AG18">
             <v>139.61666666666667</v>
@@ -6324,22 +6327,22 @@
             <v>949.41</v>
           </cell>
           <cell r="AA19">
-            <v>1448.125</v>
+            <v>1439.4444444444446</v>
           </cell>
           <cell r="AB19">
-            <v>10.406560207164437</v>
+            <v>10.469316866074873</v>
           </cell>
           <cell r="AC19">
-            <v>1.0406560207164437</v>
+            <v>1.0469316866074874</v>
           </cell>
           <cell r="AD19">
-            <v>58.875</v>
+            <v>67.555555555555429</v>
           </cell>
           <cell r="AE19">
-            <v>724.0625</v>
+            <v>719.72222222222229</v>
           </cell>
           <cell r="AF19">
-            <v>665.1875</v>
+            <v>652.16666666666686</v>
           </cell>
           <cell r="AG19">
             <v>25.116666666666667</v>
@@ -6416,22 +6419,22 @@
             <v>2498.58</v>
           </cell>
           <cell r="AA20">
-            <v>3132.5</v>
+            <v>3217.7777777777778</v>
           </cell>
           <cell r="AB20">
-            <v>12.660814046288907</v>
+            <v>12.325276243093922</v>
           </cell>
           <cell r="AC20">
-            <v>1.2660814046288906</v>
+            <v>1.2325276243093923</v>
           </cell>
           <cell r="AD20">
-            <v>833.5</v>
+            <v>748.22222222222217</v>
           </cell>
           <cell r="AE20">
-            <v>1566.25</v>
+            <v>1608.8888888888889</v>
           </cell>
           <cell r="AF20">
-            <v>732.75</v>
+            <v>860.66666666666674</v>
           </cell>
           <cell r="AG20">
             <v>66.099999999999994</v>
@@ -6508,22 +6511,22 @@
             <v>8325.42</v>
           </cell>
           <cell r="AA21">
-            <v>7136.25</v>
+            <v>7480</v>
           </cell>
           <cell r="AB21">
-            <v>10.703100367840252</v>
+            <v>10.211229946524064</v>
           </cell>
           <cell r="AC21">
-            <v>1.0703100367840253</v>
+            <v>1.0211229946524065</v>
           </cell>
           <cell r="AD21">
-            <v>501.75</v>
+            <v>158</v>
           </cell>
           <cell r="AE21">
-            <v>3568.125</v>
+            <v>3740</v>
           </cell>
           <cell r="AF21">
-            <v>3066.375</v>
+            <v>3582</v>
           </cell>
           <cell r="AG21">
             <v>141.44444444444446</v>
@@ -6600,22 +6603,22 @@
             <v>4099.4900000000007</v>
           </cell>
           <cell r="AA22">
-            <v>3313.75</v>
+            <v>3530</v>
           </cell>
           <cell r="AB22">
-            <v>11.349679366276877</v>
+            <v>10.654390934844193</v>
           </cell>
           <cell r="AC22">
-            <v>1.1349679366276877</v>
+            <v>1.0654390934844193</v>
           </cell>
           <cell r="AD22">
-            <v>447.25</v>
+            <v>231</v>
           </cell>
           <cell r="AE22">
-            <v>1656.875</v>
+            <v>1765</v>
           </cell>
           <cell r="AF22">
-            <v>1209.625</v>
+            <v>1534</v>
           </cell>
           <cell r="AG22">
             <v>69.648148148148152</v>
@@ -6692,22 +6695,22 @@
             <v>38473.719999999994</v>
           </cell>
           <cell r="AA23">
-            <v>34954.375</v>
+            <v>34777.777777777781</v>
           </cell>
           <cell r="AB23">
-            <v>9.4886548536485069</v>
+            <v>9.5368370607028741</v>
           </cell>
           <cell r="AC23">
-            <v>0.9488654853648506</v>
+            <v>0.95368370607028741</v>
           </cell>
           <cell r="AD23">
-            <v>-1787.375</v>
+            <v>-1610.777777777781</v>
           </cell>
           <cell r="AE23">
-            <v>17477.1875</v>
+            <v>17388.888888888891</v>
           </cell>
           <cell r="AF23">
-            <v>19264.5625</v>
+            <v>18999.666666666672</v>
           </cell>
           <cell r="AG23">
             <v>614.2037037037037</v>
@@ -6784,22 +6787,22 @@
             <v>29054.519999999997</v>
           </cell>
           <cell r="AA24">
-            <v>22795.625</v>
+            <v>22680.555555555555</v>
           </cell>
           <cell r="AB24">
-            <v>10.987634688673813</v>
+            <v>11.043380281690141</v>
           </cell>
           <cell r="AC24">
-            <v>1.0987634688673813</v>
+            <v>1.1043380281690141</v>
           </cell>
           <cell r="AD24">
-            <v>2251.375</v>
+            <v>2366.4444444444453</v>
           </cell>
           <cell r="AE24">
-            <v>11397.8125</v>
+            <v>11340.277777777777</v>
           </cell>
           <cell r="AF24">
-            <v>9146.4375</v>
+            <v>8973.8333333333321</v>
           </cell>
           <cell r="AG24">
             <v>463.83333333333331</v>
@@ -6876,22 +6879,22 @@
             <v>30040.519999999997</v>
           </cell>
           <cell r="AA25">
-            <v>22229.375</v>
+            <v>22049.444444444445</v>
           </cell>
           <cell r="AB25">
-            <v>11.649900188376867</v>
+            <v>11.744967119352969</v>
           </cell>
           <cell r="AC25">
-            <v>1.1649900188376867</v>
+            <v>1.1744967119352969</v>
           </cell>
           <cell r="AD25">
-            <v>3667.625</v>
+            <v>3847.5555555555547</v>
           </cell>
           <cell r="AE25">
-            <v>11114.6875</v>
+            <v>11024.722222222223</v>
           </cell>
           <cell r="AF25">
-            <v>7447.0625</v>
+            <v>7177.1666666666679</v>
           </cell>
           <cell r="AG25">
             <v>479.57407407407408</v>
@@ -6968,22 +6971,22 @@
             <v>34369.64</v>
           </cell>
           <cell r="AA26">
-            <v>26338.75</v>
+            <v>26370</v>
           </cell>
           <cell r="AB26">
-            <v>11.249205068577666</v>
+            <v>11.235874099355328</v>
           </cell>
           <cell r="AC26">
-            <v>1.1249205068577666</v>
+            <v>1.1235874099355327</v>
           </cell>
           <cell r="AD26">
-            <v>3290.25</v>
+            <v>3259</v>
           </cell>
           <cell r="AE26">
-            <v>13169.375</v>
+            <v>13185</v>
           </cell>
           <cell r="AF26">
-            <v>9879.125</v>
+            <v>9926</v>
           </cell>
           <cell r="AG26">
             <v>548.68518518518522</v>
@@ -7060,22 +7063,22 @@
             <v>1758.56</v>
           </cell>
           <cell r="AA27">
-            <v>212.5</v>
+            <v>178.33333333333331</v>
           </cell>
           <cell r="AB27">
-            <v>71.341176470588238</v>
+            <v>85.00934579439253</v>
           </cell>
           <cell r="AC27">
-            <v>7.1341176470588232</v>
+            <v>8.500934579439253</v>
           </cell>
           <cell r="AD27">
-            <v>1303.5</v>
+            <v>1337.6666666666667</v>
           </cell>
           <cell r="AE27">
-            <v>106.25</v>
+            <v>89.166666666666657</v>
           </cell>
           <cell r="AF27">
-            <v>-1197.25</v>
+            <v>-1248.5</v>
           </cell>
           <cell r="AG27">
             <v>28.074074074074073</v>
@@ -7107,13 +7110,13 @@
             <v>3519.4399999999996</v>
           </cell>
           <cell r="L28">
-            <v>9.6604975124378107</v>
+            <v>8.4591078066914491</v>
           </cell>
           <cell r="M28">
-            <v>6909.375</v>
+            <v>7890.666666666667</v>
           </cell>
           <cell r="N28">
-            <v>-1676.9375</v>
+            <v>-2346</v>
           </cell>
           <cell r="O28">
             <v>251</v>
@@ -7152,22 +7155,22 @@
             <v>5583.08</v>
           </cell>
           <cell r="AA28">
-            <v>3140.625</v>
+            <v>3586.666666666667</v>
           </cell>
           <cell r="AB28">
-            <v>15.32497512437811</v>
+            <v>13.419144981412639</v>
           </cell>
           <cell r="AC28">
-            <v>1.5324975124378108</v>
+            <v>1.3419144981412638</v>
           </cell>
           <cell r="AD28">
-            <v>1672.375</v>
+            <v>1226.333333333333</v>
           </cell>
           <cell r="AE28">
-            <v>1570.3125</v>
+            <v>1793.3333333333335</v>
           </cell>
           <cell r="AF28">
-            <v>-102.0625</v>
+            <v>567.00000000000045</v>
           </cell>
           <cell r="AG28">
             <v>89.129629629629633</v>
@@ -7199,13 +7202,13 @@
             <v>3309.4799999999996</v>
           </cell>
           <cell r="L29">
-            <v>8.005612065941774</v>
+            <v>6.9613664091093952</v>
           </cell>
           <cell r="M29">
-            <v>7840.25</v>
+            <v>9016.3333333333321</v>
           </cell>
           <cell r="N29">
-            <v>-2492.625</v>
+            <v>-3294.4999999999991</v>
           </cell>
           <cell r="O29">
             <v>236</v>
@@ -7244,22 +7247,22 @@
             <v>5281.48</v>
           </cell>
           <cell r="AA29">
-            <v>3563.75</v>
+            <v>4098.333333333333</v>
           </cell>
           <cell r="AB29">
-            <v>12.775868116450368</v>
+            <v>11.109394062627084</v>
           </cell>
           <cell r="AC29">
-            <v>1.2775868116450368</v>
+            <v>1.1109394062627085</v>
           </cell>
           <cell r="AD29">
-            <v>989.25</v>
+            <v>454.66666666666697</v>
           </cell>
           <cell r="AE29">
-            <v>1781.875</v>
+            <v>2049.1666666666665</v>
           </cell>
           <cell r="AF29">
-            <v>792.625</v>
+            <v>1594.4999999999995</v>
           </cell>
           <cell r="AG29">
             <v>84.31481481481481</v>
@@ -7291,13 +7294,13 @@
             <v>3259.6</v>
           </cell>
           <cell r="L30">
-            <v>8.2043795620437958</v>
+            <v>7.1653208669783242</v>
           </cell>
           <cell r="M30">
-            <v>7535</v>
+            <v>8627.6666666666679</v>
           </cell>
           <cell r="N30">
-            <v>-2327.5</v>
+            <v>-3072.5000000000009</v>
           </cell>
           <cell r="O30">
             <v>236</v>
@@ -7336,22 +7339,22 @@
             <v>6992.48</v>
           </cell>
           <cell r="AA30">
-            <v>3425</v>
+            <v>3921.666666666667</v>
           </cell>
           <cell r="AB30">
-            <v>17.600000000000001</v>
+            <v>15.371015724606885</v>
           </cell>
           <cell r="AC30">
-            <v>1.76</v>
+            <v>1.5371015724606885</v>
           </cell>
           <cell r="AD30">
-            <v>2603</v>
+            <v>2106.333333333333</v>
           </cell>
           <cell r="AE30">
-            <v>1712.5</v>
+            <v>1960.8333333333335</v>
           </cell>
           <cell r="AF30">
-            <v>-890.5</v>
+            <v>-145.49999999999955</v>
           </cell>
           <cell r="AG30">
             <v>111.62962962962963</v>
@@ -7428,22 +7431,22 @@
             <v>5045.2800000000007</v>
           </cell>
           <cell r="AA31">
-            <v>2256.875</v>
+            <v>2288.8888888888887</v>
           </cell>
           <cell r="AB31">
-            <v>6.0747715314317361</v>
+            <v>5.9898058252427191</v>
           </cell>
           <cell r="AC31">
-            <v>0.60747715314317363</v>
+            <v>0.59898058252427189</v>
           </cell>
           <cell r="AD31">
-            <v>-885.875</v>
+            <v>-917.88888888888869</v>
           </cell>
           <cell r="AE31">
-            <v>1128.4375</v>
+            <v>1144.4444444444443</v>
           </cell>
           <cell r="AF31">
-            <v>2014.3125</v>
+            <v>2062.333333333333</v>
           </cell>
           <cell r="AG31">
             <v>85.6875</v>
@@ -7520,22 +7523,22 @@
             <v>3606.4</v>
           </cell>
           <cell r="AA32">
-            <v>1303.75</v>
+            <v>1353.3333333333335</v>
           </cell>
           <cell r="AB32">
-            <v>7.5167785234899327</v>
+            <v>7.2413793103448274</v>
           </cell>
           <cell r="AC32">
-            <v>0.75167785234899331</v>
+            <v>0.72413793103448265</v>
           </cell>
           <cell r="AD32">
-            <v>-323.75</v>
+            <v>-373.33333333333348</v>
           </cell>
           <cell r="AE32">
-            <v>651.875</v>
+            <v>676.66666666666674</v>
           </cell>
           <cell r="AF32">
-            <v>975.625</v>
+            <v>1050.0000000000002</v>
           </cell>
           <cell r="AG32">
             <v>61.25</v>
@@ -7612,22 +7615,22 @@
             <v>13703.300000000001</v>
           </cell>
           <cell r="AA33">
-            <v>4897.5</v>
+            <v>5106.666666666667</v>
           </cell>
           <cell r="AB33">
-            <v>6.7422154160285857</v>
+            <v>6.4660574412532634</v>
           </cell>
           <cell r="AC33">
-            <v>0.67422154160285863</v>
+            <v>0.64660574412532634</v>
           </cell>
           <cell r="AD33">
-            <v>-1595.5</v>
+            <v>-1804.666666666667</v>
           </cell>
           <cell r="AE33">
-            <v>2448.75</v>
+            <v>2553.3333333333335</v>
           </cell>
           <cell r="AF33">
-            <v>4044.25</v>
+            <v>4358</v>
           </cell>
           <cell r="AG33">
             <v>206.375</v>
@@ -7704,22 +7707,22 @@
             <v>26174.050000000003</v>
           </cell>
           <cell r="AA34">
-            <v>7733.75</v>
+            <v>8115.5555555555557</v>
           </cell>
           <cell r="AB34">
-            <v>8.1551640536609025</v>
+            <v>7.7714950711938666</v>
           </cell>
           <cell r="AC34">
-            <v>0.81551640536609016</v>
+            <v>0.77714950711938657</v>
           </cell>
           <cell r="AD34">
-            <v>-1426.75</v>
+            <v>-1808.5555555555557</v>
           </cell>
           <cell r="AE34">
-            <v>3866.875</v>
+            <v>4057.7777777777778</v>
           </cell>
           <cell r="AF34">
-            <v>5293.625</v>
+            <v>5866.3333333333339</v>
           </cell>
           <cell r="AG34">
             <v>394.1875</v>
@@ -7796,7 +7799,7 @@
             <v>0</v>
           </cell>
           <cell r="AA35">
-            <v>772.5</v>
+            <v>696.66666666666674</v>
           </cell>
           <cell r="AB35">
             <v>0</v>
@@ -7805,13 +7808,13 @@
             <v>0</v>
           </cell>
           <cell r="AD35">
-            <v>-772.5</v>
+            <v>-696.66666666666674</v>
           </cell>
           <cell r="AE35">
-            <v>386.25</v>
+            <v>348.33333333333337</v>
           </cell>
           <cell r="AF35">
-            <v>1158.75</v>
+            <v>1045</v>
           </cell>
           <cell r="AG35">
             <v>0</v>
@@ -7888,22 +7891,22 @@
             <v>2253.4500000000003</v>
           </cell>
           <cell r="AA36">
-            <v>7180</v>
+            <v>7091.6666666666661</v>
           </cell>
           <cell r="AB36">
-            <v>0.75626740947075211</v>
+            <v>0.76568742655699185</v>
           </cell>
           <cell r="AC36">
-            <v>7.5626740947075208E-2</v>
+            <v>7.6568742655699185E-2</v>
           </cell>
           <cell r="AD36">
-            <v>-6637</v>
+            <v>-6548.6666666666661</v>
           </cell>
           <cell r="AE36">
-            <v>3590</v>
+            <v>3545.833333333333</v>
           </cell>
           <cell r="AF36">
-            <v>10227</v>
+            <v>10094.5</v>
           </cell>
           <cell r="AG36">
             <v>33.9375</v>
@@ -7980,22 +7983,22 @@
             <v>16573.84</v>
           </cell>
           <cell r="AA37">
-            <v>11913.75</v>
+            <v>11621.666666666668</v>
           </cell>
           <cell r="AB37">
-            <v>8.5346763193788693</v>
+            <v>8.7491753907930576</v>
           </cell>
           <cell r="AC37">
-            <v>0.85346763193788688</v>
+            <v>0.87491753907930581</v>
           </cell>
           <cell r="AD37">
-            <v>-1745.75</v>
+            <v>-1453.6666666666679</v>
           </cell>
           <cell r="AE37">
-            <v>5956.875</v>
+            <v>5810.8333333333339</v>
           </cell>
           <cell r="AF37">
-            <v>7702.625</v>
+            <v>7264.5000000000018</v>
           </cell>
           <cell r="AG37">
             <v>188.2962962962963</v>
@@ -8072,22 +8075,22 @@
             <v>16068.539999999999</v>
           </cell>
           <cell r="AA38">
-            <v>5083.125</v>
+            <v>5161.1111111111113</v>
           </cell>
           <cell r="AB38">
-            <v>19.393581704168202</v>
+            <v>19.100538213132403</v>
           </cell>
           <cell r="AC38">
-            <v>1.9393581704168203</v>
+            <v>1.9100538213132399</v>
           </cell>
           <cell r="AD38">
-            <v>4774.875</v>
+            <v>4696.8888888888887</v>
           </cell>
           <cell r="AE38">
-            <v>2541.5625</v>
+            <v>2580.5555555555557</v>
           </cell>
           <cell r="AF38">
-            <v>-2233.3125</v>
+            <v>-2116.333333333333</v>
           </cell>
           <cell r="AG38">
             <v>182.55555555555554</v>
@@ -8164,22 +8167,22 @@
             <v>3204.58</v>
           </cell>
           <cell r="AA39">
-            <v>3739.375</v>
+            <v>3957.2222222222222</v>
           </cell>
           <cell r="AB39">
-            <v>5.2575630954370718</v>
+            <v>4.9681314053067531</v>
           </cell>
           <cell r="AC39">
-            <v>0.52575630954370722</v>
+            <v>0.49681314053067527</v>
           </cell>
           <cell r="AD39">
-            <v>-1773.375</v>
+            <v>-1991.2222222222222</v>
           </cell>
           <cell r="AE39">
-            <v>1869.6875</v>
+            <v>1978.6111111111111</v>
           </cell>
           <cell r="AF39">
-            <v>3643.0625</v>
+            <v>3969.833333333333</v>
           </cell>
           <cell r="AG39">
             <v>36.407407407407405</v>
@@ -8256,22 +8259,22 @@
             <v>7409.98</v>
           </cell>
           <cell r="AA40">
-            <v>506.25</v>
+            <v>677.22222222222229</v>
           </cell>
           <cell r="AB40">
-            <v>89.797530864197526</v>
+            <v>67.127153404429848</v>
           </cell>
           <cell r="AC40">
-            <v>8.9797530864197537</v>
+            <v>6.7127153404429851</v>
           </cell>
           <cell r="AD40">
-            <v>4039.75</v>
+            <v>3868.7777777777778</v>
           </cell>
           <cell r="AE40">
-            <v>253.125</v>
+            <v>338.61111111111114</v>
           </cell>
           <cell r="AF40">
-            <v>-3786.625</v>
+            <v>-3530.1666666666665</v>
           </cell>
           <cell r="AG40">
             <v>84.18518518518519</v>
@@ -8532,22 +8535,22 @@
             <v>4065.15</v>
           </cell>
           <cell r="AA43">
-            <v>1314.375</v>
+            <v>1343.8888888888889</v>
           </cell>
           <cell r="AB43">
-            <v>5.0290061816452685</v>
+            <v>4.9185613890037203</v>
           </cell>
           <cell r="AC43">
-            <v>0.50290061816452691</v>
+            <v>0.49185613890037205</v>
           </cell>
           <cell r="AD43">
-            <v>-653.375</v>
+            <v>-682.88888888888891</v>
           </cell>
           <cell r="AE43">
-            <v>657.1875</v>
+            <v>671.94444444444446</v>
           </cell>
           <cell r="AF43">
-            <v>1310.5625</v>
+            <v>1354.8333333333335</v>
           </cell>
           <cell r="AG43">
             <v>12.24074074074074</v>
@@ -8624,22 +8627,22 @@
             <v>6980.25</v>
           </cell>
           <cell r="AA44">
-            <v>5966.875</v>
+            <v>6372.2222222222217</v>
           </cell>
           <cell r="AB44">
-            <v>1.9021682203833665</v>
+            <v>1.7811682650392329</v>
           </cell>
           <cell r="AC44">
-            <v>0.19021682203833665</v>
+            <v>0.1781168265039233</v>
           </cell>
           <cell r="AD44">
-            <v>-4831.875</v>
+            <v>-5237.2222222222217</v>
           </cell>
           <cell r="AE44">
-            <v>2983.4375</v>
+            <v>3186.1111111111109</v>
           </cell>
           <cell r="AF44">
-            <v>7815.3125</v>
+            <v>8423.3333333333321</v>
           </cell>
           <cell r="AG44">
             <v>21.018518518518519</v>
@@ -8716,22 +8719,22 @@
             <v>4816.32</v>
           </cell>
           <cell r="AA45">
-            <v>6235.625</v>
+            <v>6313.8888888888887</v>
           </cell>
           <cell r="AB45">
-            <v>6.6585145835421473</v>
+            <v>6.5759788825340957</v>
           </cell>
           <cell r="AC45">
-            <v>0.66585145835421466</v>
+            <v>0.65759788825340959</v>
           </cell>
           <cell r="AD45">
-            <v>-2083.625</v>
+            <v>-2161.8888888888887</v>
           </cell>
           <cell r="AE45">
-            <v>3117.8125</v>
+            <v>3156.9444444444443</v>
           </cell>
           <cell r="AF45">
-            <v>5201.4375</v>
+            <v>5318.833333333333</v>
           </cell>
           <cell r="AG45">
             <v>76.888888888888886</v>
@@ -8808,22 +8811,22 @@
             <v>9920.32</v>
           </cell>
           <cell r="AA46">
-            <v>8279.375</v>
+            <v>8413.3333333333339</v>
           </cell>
           <cell r="AB46">
-            <v>10.329282101607911</v>
+            <v>10.164817749603802</v>
           </cell>
           <cell r="AC46">
-            <v>1.0329282101607911</v>
+            <v>1.0164817749603803</v>
           </cell>
           <cell r="AD46">
-            <v>272.625</v>
+            <v>138.66666666666606</v>
           </cell>
           <cell r="AE46">
-            <v>4139.6875</v>
+            <v>4206.666666666667</v>
           </cell>
           <cell r="AF46">
-            <v>3867.0625</v>
+            <v>4068.0000000000009</v>
           </cell>
           <cell r="AG46">
             <v>158.37037037037038</v>
@@ -8900,22 +8903,22 @@
             <v>7810.28</v>
           </cell>
           <cell r="AA47">
-            <v>5571.875</v>
+            <v>5701.6666666666661</v>
           </cell>
           <cell r="AB47">
-            <v>12.083903533370723</v>
+            <v>11.808827828120434</v>
           </cell>
           <cell r="AC47">
-            <v>1.2083903533370723</v>
+            <v>1.1808827828120434</v>
           </cell>
           <cell r="AD47">
-            <v>1161.125</v>
+            <v>1031.3333333333339</v>
           </cell>
           <cell r="AE47">
-            <v>2785.9375</v>
+            <v>2850.833333333333</v>
           </cell>
           <cell r="AF47">
-            <v>1624.8125</v>
+            <v>1819.4999999999991</v>
           </cell>
           <cell r="AG47">
             <v>124.68518518518519</v>
@@ -8992,22 +8995,22 @@
             <v>6063.32</v>
           </cell>
           <cell r="AA48">
-            <v>26.25</v>
+            <v>24.444444444444446</v>
           </cell>
           <cell r="AB48">
-            <v>1991.2380952380952</v>
+            <v>2138.3181818181815</v>
           </cell>
           <cell r="AC48">
-            <v>199.12380952380951</v>
+            <v>213.83181818181816</v>
           </cell>
           <cell r="AD48">
-            <v>5200.75</v>
+            <v>5202.5555555555557</v>
           </cell>
           <cell r="AE48">
-            <v>13.125</v>
+            <v>12.222222222222223</v>
           </cell>
           <cell r="AF48">
-            <v>-5187.625</v>
+            <v>-5190.333333333333</v>
           </cell>
           <cell r="AG48">
             <v>96.796296296296291</v>
@@ -9176,7 +9179,7 @@
             <v>198</v>
           </cell>
           <cell r="AA50">
-            <v>421.875</v>
+            <v>575</v>
           </cell>
           <cell r="AB50">
             <v>0</v>
@@ -9185,13 +9188,13 @@
             <v>0</v>
           </cell>
           <cell r="AD50">
-            <v>-410.875</v>
+            <v>-564</v>
           </cell>
           <cell r="AE50">
-            <v>210.9375</v>
+            <v>287.5</v>
           </cell>
           <cell r="AF50">
-            <v>621.8125</v>
+            <v>851.5</v>
           </cell>
           <cell r="AG50">
             <v>5.5</v>
@@ -9452,22 +9455,22 @@
             <v>4.6399999999999997</v>
           </cell>
           <cell r="AA53">
-            <v>4965.625</v>
+            <v>5255.5555555555557</v>
           </cell>
           <cell r="AB53">
-            <v>8.0553807426054121E-3</v>
+            <v>7.6109936575052854E-3</v>
           </cell>
           <cell r="AC53">
-            <v>8.0553807426054125E-4</v>
+            <v>7.610993657505285E-4</v>
           </cell>
           <cell r="AD53">
-            <v>-4961.625</v>
+            <v>-5251.5555555555557</v>
           </cell>
           <cell r="AE53">
-            <v>2482.8125</v>
+            <v>2627.7777777777778</v>
           </cell>
           <cell r="AF53">
-            <v>7444.4375</v>
+            <v>7879.3333333333339</v>
           </cell>
           <cell r="AG53">
             <v>0.1</v>
@@ -9544,22 +9547,22 @@
             <v>18284.13</v>
           </cell>
           <cell r="AA54">
-            <v>415.625</v>
+            <v>380.55555555555554</v>
           </cell>
           <cell r="AB54">
-            <v>543.10977443609022</v>
+            <v>593.15912408759118</v>
           </cell>
           <cell r="AC54">
-            <v>54.310977443609019</v>
+            <v>59.315912408759125</v>
           </cell>
           <cell r="AD54">
-            <v>22157.375</v>
+            <v>22192.444444444445</v>
           </cell>
           <cell r="AE54">
-            <v>207.8125</v>
+            <v>190.27777777777777</v>
           </cell>
           <cell r="AF54">
-            <v>-21949.5625</v>
+            <v>-22002.166666666668</v>
           </cell>
           <cell r="AG54">
             <v>1881.0833333333333</v>
@@ -9636,22 +9639,22 @@
             <v>23675.49</v>
           </cell>
           <cell r="AA55">
-            <v>2871.25</v>
+            <v>3025.5555555555557</v>
           </cell>
           <cell r="AB55">
-            <v>101.79886808881149</v>
+            <v>96.607051046639739</v>
           </cell>
           <cell r="AC55">
-            <v>10.179886808881148</v>
+            <v>9.6607051046639736</v>
           </cell>
           <cell r="AD55">
-            <v>26357.75</v>
+            <v>26203.444444444445</v>
           </cell>
           <cell r="AE55">
-            <v>1435.625</v>
+            <v>1512.7777777777778</v>
           </cell>
           <cell r="AF55">
-            <v>-24922.125</v>
+            <v>-24690.666666666668</v>
           </cell>
           <cell r="AG55">
             <v>2435.75</v>
@@ -9728,22 +9731,22 @@
             <v>13081.5</v>
           </cell>
           <cell r="AA56">
-            <v>4826.875</v>
+            <v>5395.5555555555557</v>
           </cell>
           <cell r="AB56">
-            <v>33.458500582675128</v>
+            <v>29.932042833607909</v>
           </cell>
           <cell r="AC56">
-            <v>3.3458500582675126</v>
+            <v>2.9932042833607908</v>
           </cell>
           <cell r="AD56">
-            <v>11323.125</v>
+            <v>10754.444444444445</v>
           </cell>
           <cell r="AE56">
-            <v>2413.4375</v>
+            <v>2697.7777777777778</v>
           </cell>
           <cell r="AF56">
-            <v>-8909.6875</v>
+            <v>-8056.6666666666679</v>
           </cell>
           <cell r="AG56">
             <v>1345.8333333333333</v>
@@ -9820,22 +9823,22 @@
             <v>15625.710000000001</v>
           </cell>
           <cell r="AA57">
-            <v>2846.875</v>
+            <v>3161.666666666667</v>
           </cell>
           <cell r="AB57">
-            <v>67.762019758507137</v>
+            <v>61.015287295730097</v>
           </cell>
           <cell r="AC57">
-            <v>6.7762019758507135</v>
+            <v>6.1015287295730092</v>
           </cell>
           <cell r="AD57">
-            <v>16444.125</v>
+            <v>16129.333333333332</v>
           </cell>
           <cell r="AE57">
-            <v>1423.4375</v>
+            <v>1580.8333333333335</v>
           </cell>
           <cell r="AF57">
-            <v>-15020.6875</v>
+            <v>-14548.499999999998</v>
           </cell>
           <cell r="AG57">
             <v>1607.5833333333333</v>
@@ -9912,22 +9915,22 @@
             <v>1873.3000000000002</v>
           </cell>
           <cell r="AA58">
-            <v>2563.75</v>
+            <v>2933.8888888888891</v>
           </cell>
           <cell r="AB58">
-            <v>2.7888834714773281</v>
+            <v>2.4370384396894527</v>
           </cell>
           <cell r="AC58">
-            <v>0.27888834714773281</v>
+            <v>0.24370384396894526</v>
           </cell>
           <cell r="AD58">
-            <v>-1848.75</v>
+            <v>-2218.8888888888891</v>
           </cell>
           <cell r="AE58">
-            <v>1281.875</v>
+            <v>1466.9444444444446</v>
           </cell>
           <cell r="AF58">
-            <v>3130.625</v>
+            <v>3685.8333333333339</v>
           </cell>
           <cell r="AG58">
             <v>119.16666666666667</v>
@@ -10004,22 +10007,22 @@
             <v>1011.32</v>
           </cell>
           <cell r="AA59">
-            <v>471.875</v>
+            <v>608.33333333333337</v>
           </cell>
           <cell r="AB59">
-            <v>8.1801324503311257</v>
+            <v>6.3452054794520549</v>
           </cell>
           <cell r="AC59">
-            <v>0.81801324503311257</v>
+            <v>0.6345205479452054</v>
           </cell>
           <cell r="AD59">
-            <v>-85.875</v>
+            <v>-222.33333333333337</v>
           </cell>
           <cell r="AE59">
-            <v>235.9375</v>
+            <v>304.16666666666669</v>
           </cell>
           <cell r="AF59">
-            <v>321.8125</v>
+            <v>526.5</v>
           </cell>
           <cell r="AG59">
             <v>64.333333333333329</v>
@@ -10096,22 +10099,22 @@
             <v>780.76</v>
           </cell>
           <cell r="AA60">
-            <v>922.5</v>
+            <v>1091.6666666666667</v>
           </cell>
           <cell r="AB60">
-            <v>3.230352303523035</v>
+            <v>2.729770992366412</v>
           </cell>
           <cell r="AC60">
-            <v>0.32303523035230353</v>
+            <v>0.27297709923664121</v>
           </cell>
           <cell r="AD60">
-            <v>-624.5</v>
+            <v>-793.66666666666674</v>
           </cell>
           <cell r="AE60">
-            <v>461.25</v>
+            <v>545.83333333333337</v>
           </cell>
           <cell r="AF60">
-            <v>1085.75</v>
+            <v>1339.5</v>
           </cell>
           <cell r="AG60">
             <v>49.666666666666664</v>
@@ -10188,22 +10191,22 @@
             <v>382.52000000000004</v>
           </cell>
           <cell r="AA61">
-            <v>493.125</v>
+            <v>517.77777777777783</v>
           </cell>
           <cell r="AB61">
-            <v>2.9607097591888465</v>
+            <v>2.8197424892703857</v>
           </cell>
           <cell r="AC61">
-            <v>0.29607097591888465</v>
+            <v>0.2819742489270386</v>
           </cell>
           <cell r="AD61">
-            <v>-347.125</v>
+            <v>-371.77777777777783</v>
           </cell>
           <cell r="AE61">
-            <v>246.5625</v>
+            <v>258.88888888888891</v>
           </cell>
           <cell r="AF61">
-            <v>593.6875</v>
+            <v>630.66666666666674</v>
           </cell>
           <cell r="AG61">
             <v>24.333333333333332</v>
@@ -10214,7 +10217,7 @@
             <v>Units Produce</v>
           </cell>
           <cell r="AF62">
-            <v>151405.6875</v>
+            <v>156899.66666666666</v>
           </cell>
         </row>
       </sheetData>
@@ -10229,6 +10232,9 @@
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10553,212 +10559,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="66" t="s">
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="66"/>
-      <c r="AC1" s="66"/>
-      <c r="AD1" s="66"/>
-      <c r="AE1" s="66"/>
-      <c r="AF1" s="66"/>
-      <c r="AG1" s="66"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="66"/>
-      <c r="AB2" s="66"/>
-      <c r="AC2" s="66"/>
-      <c r="AD2" s="66"/>
-      <c r="AE2" s="66"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
+      <c r="AD2" s="63"/>
+      <c r="AE2" s="63"/>
+      <c r="AF2" s="63"/>
+      <c r="AG2" s="63"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="66"/>
-      <c r="AB3" s="66"/>
-      <c r="AC3" s="66"/>
-      <c r="AD3" s="66"/>
-      <c r="AE3" s="66"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="62"/>
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="63"/>
+      <c r="AD3" s="63"/>
+      <c r="AE3" s="63"/>
+      <c r="AF3" s="63"/>
+      <c r="AG3" s="63"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="66"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="62"/>
+      <c r="Y4" s="62"/>
+      <c r="Z4" s="62"/>
+      <c r="AA4" s="63"/>
+      <c r="AB4" s="63"/>
+      <c r="AC4" s="63"/>
+      <c r="AD4" s="63"/>
+      <c r="AE4" s="63"/>
+      <c r="AF4" s="63"/>
+      <c r="AG4" s="63"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="66"/>
-      <c r="AB5" s="66"/>
-      <c r="AC5" s="66"/>
-      <c r="AD5" s="66"/>
-      <c r="AE5" s="66"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="62"/>
+      <c r="Z5" s="62"/>
+      <c r="AA5" s="63"/>
+      <c r="AB5" s="63"/>
+      <c r="AC5" s="63"/>
+      <c r="AD5" s="63"/>
+      <c r="AE5" s="63"/>
+      <c r="AF5" s="63"/>
+      <c r="AG5" s="63"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="66"/>
-      <c r="AB6" s="66"/>
-      <c r="AC6" s="66"/>
-      <c r="AD6" s="66"/>
-      <c r="AE6" s="66"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="62"/>
+      <c r="X6" s="62"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="63"/>
+      <c r="AB6" s="63"/>
+      <c r="AC6" s="63"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="63"/>
+      <c r="AG6" s="63"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
@@ -11129,27 +11135,27 @@
       </c>
       <c r="AA13" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA13</f>
-        <v>11684.375</v>
+        <v>11850.555555555557</v>
       </c>
       <c r="AB13" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB13</f>
-        <v>8.5627173040920024</v>
+        <v>8.4426421639866849</v>
       </c>
       <c r="AC13" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC13</f>
-        <v>0.85627173040920035</v>
+        <v>0.84426421639866855</v>
       </c>
       <c r="AD13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD13</f>
-        <v>-1679.375</v>
+        <v>-1845.5555555555566</v>
       </c>
       <c r="AE13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE13</f>
-        <v>5842.1875</v>
+        <v>5925.2777777777783</v>
       </c>
       <c r="AF13" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF13</f>
-        <v>7521.5625</v>
+        <v>7770.8333333333348</v>
       </c>
       <c r="AG13" s="27">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG13</f>
@@ -11257,27 +11263,27 @@
       </c>
       <c r="AA14" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA14</f>
-        <v>769.375</v>
+        <v>719.44444444444446</v>
       </c>
       <c r="AB14" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB14</f>
-        <v>7.2656376929325752</v>
+        <v>7.7698841698841701</v>
       </c>
       <c r="AC14" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC14</f>
-        <v>0.7265637692932575</v>
+        <v>0.77698841698841703</v>
       </c>
       <c r="AD14" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD14</f>
-        <v>-210.375</v>
+        <v>-160.44444444444446</v>
       </c>
       <c r="AE14" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE14</f>
-        <v>384.6875</v>
+        <v>359.72222222222223</v>
       </c>
       <c r="AF14" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF14</f>
-        <v>595.0625</v>
+        <v>520.16666666666674</v>
       </c>
       <c r="AG14" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG14</f>
@@ -11385,27 +11391,27 @@
       </c>
       <c r="AA15" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA15</f>
-        <v>4921.25</v>
+        <v>4920</v>
       </c>
       <c r="AB15" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB15</f>
-        <v>6.9738379476758956</v>
+        <v>6.975609756097561</v>
       </c>
       <c r="AC15" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC15</f>
-        <v>0.69738379476758949</v>
+        <v>0.69756097560975605</v>
       </c>
       <c r="AD15" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD15</f>
-        <v>-1489.25</v>
+        <v>-1488</v>
       </c>
       <c r="AE15" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE15</f>
-        <v>2460.625</v>
+        <v>2460</v>
       </c>
       <c r="AF15" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF15</f>
-        <v>3949.875</v>
+        <v>3948</v>
       </c>
       <c r="AG15" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG15</f>
@@ -11513,27 +11519,27 @@
       </c>
       <c r="AA16" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA16</f>
-        <v>893.125</v>
+        <v>857.22222222222229</v>
       </c>
       <c r="AB16" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB16</f>
-        <v>2.3065080475857243</v>
+        <v>2.4031108230719376</v>
       </c>
       <c r="AC16" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC16</f>
-        <v>0.23065080475857244</v>
+        <v>0.24031108230719375</v>
       </c>
       <c r="AD16" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD16</f>
-        <v>-687.125</v>
+        <v>-651.22222222222229</v>
       </c>
       <c r="AE16" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE16</f>
-        <v>446.5625</v>
+        <v>428.61111111111114</v>
       </c>
       <c r="AF16" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF16</f>
-        <v>1133.6875</v>
+        <v>1079.8333333333335</v>
       </c>
       <c r="AG16" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG16</f>
@@ -11641,27 +11647,27 @@
       </c>
       <c r="AA17" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA17</f>
-        <v>109.375</v>
+        <v>110</v>
       </c>
       <c r="AB17" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB17</f>
-        <v>19.382857142857144</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="AC17" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC17</f>
-        <v>1.9382857142857144</v>
+        <v>1.9272727272727272</v>
       </c>
       <c r="AD17" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD17</f>
-        <v>102.625</v>
+        <v>102</v>
       </c>
       <c r="AE17" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE17</f>
-        <v>54.6875</v>
+        <v>55</v>
       </c>
       <c r="AF17" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF17</f>
-        <v>-47.9375</v>
+        <v>-47</v>
       </c>
       <c r="AG17" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG17</f>
@@ -11769,27 +11775,27 @@
       </c>
       <c r="AA18" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA18</f>
-        <v>14228.125</v>
+        <v>14348.333333333332</v>
       </c>
       <c r="AB18" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB18</f>
-        <v>5.8876345266857015</v>
+        <v>5.8383087466604717</v>
       </c>
       <c r="AC18" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC18</f>
-        <v>0.58876345266857022</v>
+        <v>0.58383087466604722</v>
       </c>
       <c r="AD18" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD18</f>
-        <v>-5851.125</v>
+        <v>-5971.3333333333321</v>
       </c>
       <c r="AE18" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE18</f>
-        <v>7114.0625</v>
+        <v>7174.1666666666661</v>
       </c>
       <c r="AF18" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF18</f>
-        <v>12965.1875</v>
+        <v>13145.499999999998</v>
       </c>
       <c r="AG18" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG18</f>
@@ -11897,27 +11903,27 @@
       </c>
       <c r="AA19" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA19</f>
-        <v>1448.125</v>
+        <v>1439.4444444444446</v>
       </c>
       <c r="AB19" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB19</f>
-        <v>10.406560207164437</v>
+        <v>10.469316866074873</v>
       </c>
       <c r="AC19" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC19</f>
-        <v>1.0406560207164437</v>
+        <v>1.0469316866074874</v>
       </c>
       <c r="AD19" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD19</f>
-        <v>58.875</v>
+        <v>67.555555555555429</v>
       </c>
       <c r="AE19" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE19</f>
-        <v>724.0625</v>
+        <v>719.72222222222229</v>
       </c>
       <c r="AF19" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF19</f>
-        <v>665.1875</v>
+        <v>652.16666666666686</v>
       </c>
       <c r="AG19" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG19</f>
@@ -12025,27 +12031,27 @@
       </c>
       <c r="AA20" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA20</f>
-        <v>3132.5</v>
+        <v>3217.7777777777778</v>
       </c>
       <c r="AB20" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB20</f>
-        <v>12.660814046288907</v>
+        <v>12.325276243093922</v>
       </c>
       <c r="AC20" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC20</f>
-        <v>1.2660814046288906</v>
+        <v>1.2325276243093923</v>
       </c>
       <c r="AD20" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD20</f>
-        <v>833.5</v>
+        <v>748.22222222222217</v>
       </c>
       <c r="AE20" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE20</f>
-        <v>1566.25</v>
+        <v>1608.8888888888889</v>
       </c>
       <c r="AF20" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF20</f>
-        <v>732.75</v>
+        <v>860.66666666666674</v>
       </c>
       <c r="AG20" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG20</f>
@@ -12153,27 +12159,27 @@
       </c>
       <c r="AA21" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA21</f>
-        <v>7136.25</v>
+        <v>7480</v>
       </c>
       <c r="AB21" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB21</f>
-        <v>10.703100367840252</v>
+        <v>10.211229946524064</v>
       </c>
       <c r="AC21" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC21</f>
-        <v>1.0703100367840253</v>
+        <v>1.0211229946524065</v>
       </c>
       <c r="AD21" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD21</f>
-        <v>501.75</v>
+        <v>158</v>
       </c>
       <c r="AE21" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE21</f>
-        <v>3568.125</v>
+        <v>3740</v>
       </c>
       <c r="AF21" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF21</f>
-        <v>3066.375</v>
+        <v>3582</v>
       </c>
       <c r="AG21" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG21</f>
@@ -12281,27 +12287,27 @@
       </c>
       <c r="AA22" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA22</f>
-        <v>3313.75</v>
+        <v>3530</v>
       </c>
       <c r="AB22" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB22</f>
-        <v>11.349679366276877</v>
+        <v>10.654390934844193</v>
       </c>
       <c r="AC22" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC22</f>
-        <v>1.1349679366276877</v>
+        <v>1.0654390934844193</v>
       </c>
       <c r="AD22" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD22</f>
-        <v>447.25</v>
+        <v>231</v>
       </c>
       <c r="AE22" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE22</f>
-        <v>1656.875</v>
+        <v>1765</v>
       </c>
       <c r="AF22" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF22</f>
-        <v>1209.625</v>
+        <v>1534</v>
       </c>
       <c r="AG22" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG22</f>
@@ -12409,27 +12415,27 @@
       </c>
       <c r="AA23" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA23</f>
-        <v>34954.375</v>
+        <v>34777.777777777781</v>
       </c>
       <c r="AB23" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB23</f>
-        <v>9.4886548536485069</v>
+        <v>9.5368370607028741</v>
       </c>
       <c r="AC23" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC23</f>
-        <v>0.9488654853648506</v>
+        <v>0.95368370607028741</v>
       </c>
       <c r="AD23" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD23</f>
-        <v>-1787.375</v>
+        <v>-1610.777777777781</v>
       </c>
       <c r="AE23" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE23</f>
-        <v>17477.1875</v>
+        <v>17388.888888888891</v>
       </c>
       <c r="AF23" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF23</f>
-        <v>19264.5625</v>
+        <v>18999.666666666672</v>
       </c>
       <c r="AG23" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG23</f>
@@ -12537,27 +12543,27 @@
       </c>
       <c r="AA24" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA24</f>
-        <v>22795.625</v>
+        <v>22680.555555555555</v>
       </c>
       <c r="AB24" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB24</f>
-        <v>10.987634688673813</v>
+        <v>11.043380281690141</v>
       </c>
       <c r="AC24" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC24</f>
-        <v>1.0987634688673813</v>
+        <v>1.1043380281690141</v>
       </c>
       <c r="AD24" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD24</f>
-        <v>2251.375</v>
+        <v>2366.4444444444453</v>
       </c>
       <c r="AE24" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE24</f>
-        <v>11397.8125</v>
+        <v>11340.277777777777</v>
       </c>
       <c r="AF24" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF24</f>
-        <v>9146.4375</v>
+        <v>8973.8333333333321</v>
       </c>
       <c r="AG24" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG24</f>
@@ -12665,27 +12671,27 @@
       </c>
       <c r="AA25" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA25</f>
-        <v>22229.375</v>
+        <v>22049.444444444445</v>
       </c>
       <c r="AB25" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB25</f>
-        <v>11.649900188376867</v>
+        <v>11.744967119352969</v>
       </c>
       <c r="AC25" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC25</f>
-        <v>1.1649900188376867</v>
+        <v>1.1744967119352969</v>
       </c>
       <c r="AD25" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD25</f>
-        <v>3667.625</v>
+        <v>3847.5555555555547</v>
       </c>
       <c r="AE25" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE25</f>
-        <v>11114.6875</v>
+        <v>11024.722222222223</v>
       </c>
       <c r="AF25" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF25</f>
-        <v>7447.0625</v>
+        <v>7177.1666666666679</v>
       </c>
       <c r="AG25" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG25</f>
@@ -12793,27 +12799,27 @@
       </c>
       <c r="AA26" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA26</f>
-        <v>26338.75</v>
+        <v>26370</v>
       </c>
       <c r="AB26" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB26</f>
-        <v>11.249205068577666</v>
+        <v>11.235874099355328</v>
       </c>
       <c r="AC26" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC26</f>
-        <v>1.1249205068577666</v>
+        <v>1.1235874099355327</v>
       </c>
       <c r="AD26" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD26</f>
-        <v>3290.25</v>
+        <v>3259</v>
       </c>
       <c r="AE26" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE26</f>
-        <v>13169.375</v>
+        <v>13185</v>
       </c>
       <c r="AF26" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF26</f>
-        <v>9879.125</v>
+        <v>9926</v>
       </c>
       <c r="AG26" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG26</f>
@@ -12921,27 +12927,27 @@
       </c>
       <c r="AA27" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA27</f>
-        <v>212.5</v>
+        <v>178.33333333333331</v>
       </c>
       <c r="AB27" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB27</f>
-        <v>71.341176470588238</v>
+        <v>85.00934579439253</v>
       </c>
       <c r="AC27" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC27</f>
-        <v>7.1341176470588232</v>
+        <v>8.500934579439253</v>
       </c>
       <c r="AD27" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD27</f>
-        <v>1303.5</v>
+        <v>1337.6666666666667</v>
       </c>
       <c r="AE27" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE27</f>
-        <v>106.25</v>
+        <v>89.166666666666657</v>
       </c>
       <c r="AF27" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF27</f>
-        <v>-1197.25</v>
+        <v>-1248.5</v>
       </c>
       <c r="AG27" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG27</f>
@@ -12989,15 +12995,15 @@
       </c>
       <c r="L28" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L28</f>
-        <v>9.6604975124378107</v>
+        <v>8.4591078066914491</v>
       </c>
       <c r="M28" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M28</f>
-        <v>6909.375</v>
+        <v>7890.666666666667</v>
       </c>
       <c r="N28" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N28</f>
-        <v>-1676.9375</v>
+        <v>-2346</v>
       </c>
       <c r="O28" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O28</f>
@@ -13049,27 +13055,27 @@
       </c>
       <c r="AA28" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA28</f>
-        <v>3140.625</v>
+        <v>3586.666666666667</v>
       </c>
       <c r="AB28" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB28</f>
-        <v>15.32497512437811</v>
+        <v>13.419144981412639</v>
       </c>
       <c r="AC28" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC28</f>
-        <v>1.5324975124378108</v>
+        <v>1.3419144981412638</v>
       </c>
       <c r="AD28" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD28</f>
-        <v>1672.375</v>
+        <v>1226.333333333333</v>
       </c>
       <c r="AE28" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE28</f>
-        <v>1570.3125</v>
+        <v>1793.3333333333335</v>
       </c>
       <c r="AF28" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF28</f>
-        <v>-102.0625</v>
+        <v>567.00000000000045</v>
       </c>
       <c r="AG28" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG28</f>
@@ -13117,15 +13123,15 @@
       </c>
       <c r="L29" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L29</f>
-        <v>8.005612065941774</v>
+        <v>6.9613664091093952</v>
       </c>
       <c r="M29" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M29</f>
-        <v>7840.25</v>
+        <v>9016.3333333333321</v>
       </c>
       <c r="N29" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N29</f>
-        <v>-2492.625</v>
+        <v>-3294.4999999999991</v>
       </c>
       <c r="O29" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O29</f>
@@ -13177,27 +13183,27 @@
       </c>
       <c r="AA29" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA29</f>
-        <v>3563.75</v>
+        <v>4098.333333333333</v>
       </c>
       <c r="AB29" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB29</f>
-        <v>12.775868116450368</v>
+        <v>11.109394062627084</v>
       </c>
       <c r="AC29" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC29</f>
-        <v>1.2775868116450368</v>
+        <v>1.1109394062627085</v>
       </c>
       <c r="AD29" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD29</f>
-        <v>989.25</v>
+        <v>454.66666666666697</v>
       </c>
       <c r="AE29" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE29</f>
-        <v>1781.875</v>
+        <v>2049.1666666666665</v>
       </c>
       <c r="AF29" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF29</f>
-        <v>792.625</v>
+        <v>1594.4999999999995</v>
       </c>
       <c r="AG29" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG29</f>
@@ -13245,15 +13251,15 @@
       </c>
       <c r="L30" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L30</f>
-        <v>8.2043795620437958</v>
+        <v>7.1653208669783242</v>
       </c>
       <c r="M30" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M30</f>
-        <v>7535</v>
+        <v>8627.6666666666679</v>
       </c>
       <c r="N30" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N30</f>
-        <v>-2327.5</v>
+        <v>-3072.5000000000009</v>
       </c>
       <c r="O30" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O30</f>
@@ -13305,27 +13311,27 @@
       </c>
       <c r="AA30" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA30</f>
-        <v>3425</v>
+        <v>3921.666666666667</v>
       </c>
       <c r="AB30" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB30</f>
-        <v>17.600000000000001</v>
+        <v>15.371015724606885</v>
       </c>
       <c r="AC30" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC30</f>
-        <v>1.76</v>
+        <v>1.5371015724606885</v>
       </c>
       <c r="AD30" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD30</f>
-        <v>2603</v>
+        <v>2106.333333333333</v>
       </c>
       <c r="AE30" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE30</f>
-        <v>1712.5</v>
+        <v>1960.8333333333335</v>
       </c>
       <c r="AF30" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF30</f>
-        <v>-890.5</v>
+        <v>-145.49999999999955</v>
       </c>
       <c r="AG30" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG30</f>
@@ -13433,27 +13439,27 @@
       </c>
       <c r="AA31" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA31</f>
-        <v>2256.875</v>
+        <v>2288.8888888888887</v>
       </c>
       <c r="AB31" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB31</f>
-        <v>6.0747715314317361</v>
+        <v>5.9898058252427191</v>
       </c>
       <c r="AC31" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC31</f>
-        <v>0.60747715314317363</v>
+        <v>0.59898058252427189</v>
       </c>
       <c r="AD31" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD31</f>
-        <v>-885.875</v>
+        <v>-917.88888888888869</v>
       </c>
       <c r="AE31" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE31</f>
-        <v>1128.4375</v>
+        <v>1144.4444444444443</v>
       </c>
       <c r="AF31" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF31</f>
-        <v>2014.3125</v>
+        <v>2062.333333333333</v>
       </c>
       <c r="AG31" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG31</f>
@@ -13561,27 +13567,27 @@
       </c>
       <c r="AA32" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA32</f>
-        <v>1303.75</v>
+        <v>1353.3333333333335</v>
       </c>
       <c r="AB32" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB32</f>
-        <v>7.5167785234899327</v>
+        <v>7.2413793103448274</v>
       </c>
       <c r="AC32" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC32</f>
-        <v>0.75167785234899331</v>
+        <v>0.72413793103448265</v>
       </c>
       <c r="AD32" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD32</f>
-        <v>-323.75</v>
+        <v>-373.33333333333348</v>
       </c>
       <c r="AE32" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE32</f>
-        <v>651.875</v>
+        <v>676.66666666666674</v>
       </c>
       <c r="AF32" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF32</f>
-        <v>975.625</v>
+        <v>1050.0000000000002</v>
       </c>
       <c r="AG32" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG32</f>
@@ -13689,27 +13695,27 @@
       </c>
       <c r="AA33" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA33</f>
-        <v>4897.5</v>
+        <v>5106.666666666667</v>
       </c>
       <c r="AB33" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB33</f>
-        <v>6.7422154160285857</v>
+        <v>6.4660574412532634</v>
       </c>
       <c r="AC33" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC33</f>
-        <v>0.67422154160285863</v>
+        <v>0.64660574412532634</v>
       </c>
       <c r="AD33" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD33</f>
-        <v>-1595.5</v>
+        <v>-1804.666666666667</v>
       </c>
       <c r="AE33" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE33</f>
-        <v>2448.75</v>
+        <v>2553.3333333333335</v>
       </c>
       <c r="AF33" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF33</f>
-        <v>4044.25</v>
+        <v>4358</v>
       </c>
       <c r="AG33" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG33</f>
@@ -13817,27 +13823,27 @@
       </c>
       <c r="AA34" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA34</f>
-        <v>7733.75</v>
+        <v>8115.5555555555557</v>
       </c>
       <c r="AB34" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB34</f>
-        <v>8.1551640536609025</v>
+        <v>7.7714950711938666</v>
       </c>
       <c r="AC34" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC34</f>
-        <v>0.81551640536609016</v>
+        <v>0.77714950711938657</v>
       </c>
       <c r="AD34" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD34</f>
-        <v>-1426.75</v>
+        <v>-1808.5555555555557</v>
       </c>
       <c r="AE34" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE34</f>
-        <v>3866.875</v>
+        <v>4057.7777777777778</v>
       </c>
       <c r="AF34" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF34</f>
-        <v>5293.625</v>
+        <v>5866.3333333333339</v>
       </c>
       <c r="AG34" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG34</f>
@@ -13945,7 +13951,7 @@
       </c>
       <c r="AA35" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA35</f>
-        <v>772.5</v>
+        <v>696.66666666666674</v>
       </c>
       <c r="AB35" s="34">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB35</f>
@@ -13957,15 +13963,15 @@
       </c>
       <c r="AD35" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD35</f>
-        <v>-772.5</v>
+        <v>-696.66666666666674</v>
       </c>
       <c r="AE35" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE35</f>
-        <v>386.25</v>
+        <v>348.33333333333337</v>
       </c>
       <c r="AF35" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF35</f>
-        <v>1158.75</v>
+        <v>1045</v>
       </c>
       <c r="AG35" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG35</f>
@@ -14073,27 +14079,27 @@
       </c>
       <c r="AA36" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA36</f>
-        <v>7180</v>
+        <v>7091.6666666666661</v>
       </c>
       <c r="AB36" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB36</f>
-        <v>0.75626740947075211</v>
+        <v>0.76568742655699185</v>
       </c>
       <c r="AC36" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC36</f>
-        <v>7.5626740947075208E-2</v>
+        <v>7.6568742655699185E-2</v>
       </c>
       <c r="AD36" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD36</f>
-        <v>-6637</v>
+        <v>-6548.6666666666661</v>
       </c>
       <c r="AE36" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE36</f>
-        <v>3590</v>
+        <v>3545.833333333333</v>
       </c>
       <c r="AF36" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF36</f>
-        <v>10227</v>
+        <v>10094.5</v>
       </c>
       <c r="AG36" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG36</f>
@@ -14201,27 +14207,27 @@
       </c>
       <c r="AA37" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA37</f>
-        <v>11913.75</v>
+        <v>11621.666666666668</v>
       </c>
       <c r="AB37" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB37</f>
-        <v>8.5346763193788693</v>
+        <v>8.7491753907930576</v>
       </c>
       <c r="AC37" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC37</f>
-        <v>0.85346763193788688</v>
+        <v>0.87491753907930581</v>
       </c>
       <c r="AD37" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD37</f>
-        <v>-1745.75</v>
+        <v>-1453.6666666666679</v>
       </c>
       <c r="AE37" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE37</f>
-        <v>5956.875</v>
+        <v>5810.8333333333339</v>
       </c>
       <c r="AF37" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF37</f>
-        <v>7702.625</v>
+        <v>7264.5000000000018</v>
       </c>
       <c r="AG37" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG37</f>
@@ -14329,27 +14335,27 @@
       </c>
       <c r="AA38" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA38</f>
-        <v>5083.125</v>
+        <v>5161.1111111111113</v>
       </c>
       <c r="AB38" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB38</f>
-        <v>19.393581704168202</v>
+        <v>19.100538213132403</v>
       </c>
       <c r="AC38" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC38</f>
-        <v>1.9393581704168203</v>
+        <v>1.9100538213132399</v>
       </c>
       <c r="AD38" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD38</f>
-        <v>4774.875</v>
+        <v>4696.8888888888887</v>
       </c>
       <c r="AE38" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE38</f>
-        <v>2541.5625</v>
+        <v>2580.5555555555557</v>
       </c>
       <c r="AF38" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF38</f>
-        <v>-2233.3125</v>
+        <v>-2116.333333333333</v>
       </c>
       <c r="AG38" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG38</f>
@@ -14457,27 +14463,27 @@
       </c>
       <c r="AA39" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA39</f>
-        <v>3739.375</v>
+        <v>3957.2222222222222</v>
       </c>
       <c r="AB39" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB39</f>
-        <v>5.2575630954370718</v>
+        <v>4.9681314053067531</v>
       </c>
       <c r="AC39" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC39</f>
-        <v>0.52575630954370722</v>
+        <v>0.49681314053067527</v>
       </c>
       <c r="AD39" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD39</f>
-        <v>-1773.375</v>
+        <v>-1991.2222222222222</v>
       </c>
       <c r="AE39" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE39</f>
-        <v>1869.6875</v>
+        <v>1978.6111111111111</v>
       </c>
       <c r="AF39" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF39</f>
-        <v>3643.0625</v>
+        <v>3969.833333333333</v>
       </c>
       <c r="AG39" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG39</f>
@@ -14585,27 +14591,27 @@
       </c>
       <c r="AA40" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA40</f>
-        <v>506.25</v>
+        <v>677.22222222222229</v>
       </c>
       <c r="AB40" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB40</f>
-        <v>89.797530864197526</v>
+        <v>67.127153404429848</v>
       </c>
       <c r="AC40" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC40</f>
-        <v>8.9797530864197537</v>
+        <v>6.7127153404429851</v>
       </c>
       <c r="AD40" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD40</f>
-        <v>4039.75</v>
+        <v>3868.7777777777778</v>
       </c>
       <c r="AE40" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE40</f>
-        <v>253.125</v>
+        <v>338.61111111111114</v>
       </c>
       <c r="AF40" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF40</f>
-        <v>-3786.625</v>
+        <v>-3530.1666666666665</v>
       </c>
       <c r="AG40" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG40</f>
@@ -14969,27 +14975,27 @@
       </c>
       <c r="AA43" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA43</f>
-        <v>1314.375</v>
+        <v>1343.8888888888889</v>
       </c>
       <c r="AB43" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB43</f>
-        <v>5.0290061816452685</v>
+        <v>4.9185613890037203</v>
       </c>
       <c r="AC43" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC43</f>
-        <v>0.50290061816452691</v>
+        <v>0.49185613890037205</v>
       </c>
       <c r="AD43" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD43</f>
-        <v>-653.375</v>
+        <v>-682.88888888888891</v>
       </c>
       <c r="AE43" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE43</f>
-        <v>657.1875</v>
+        <v>671.94444444444446</v>
       </c>
       <c r="AF43" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF43</f>
-        <v>1310.5625</v>
+        <v>1354.8333333333335</v>
       </c>
       <c r="AG43" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG43</f>
@@ -15097,27 +15103,27 @@
       </c>
       <c r="AA44" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA44</f>
-        <v>5966.875</v>
+        <v>6372.2222222222217</v>
       </c>
       <c r="AB44" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB44</f>
-        <v>1.9021682203833665</v>
+        <v>1.7811682650392329</v>
       </c>
       <c r="AC44" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC44</f>
-        <v>0.19021682203833665</v>
+        <v>0.1781168265039233</v>
       </c>
       <c r="AD44" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD44</f>
-        <v>-4831.875</v>
+        <v>-5237.2222222222217</v>
       </c>
       <c r="AE44" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE44</f>
-        <v>2983.4375</v>
+        <v>3186.1111111111109</v>
       </c>
       <c r="AF44" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF44</f>
-        <v>7815.3125</v>
+        <v>8423.3333333333321</v>
       </c>
       <c r="AG44" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG44</f>
@@ -15225,27 +15231,27 @@
       </c>
       <c r="AA45" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA45</f>
-        <v>6235.625</v>
+        <v>6313.8888888888887</v>
       </c>
       <c r="AB45" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB45</f>
-        <v>6.6585145835421473</v>
+        <v>6.5759788825340957</v>
       </c>
       <c r="AC45" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC45</f>
-        <v>0.66585145835421466</v>
+        <v>0.65759788825340959</v>
       </c>
       <c r="AD45" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD45</f>
-        <v>-2083.625</v>
+        <v>-2161.8888888888887</v>
       </c>
       <c r="AE45" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE45</f>
-        <v>3117.8125</v>
+        <v>3156.9444444444443</v>
       </c>
       <c r="AF45" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF45</f>
-        <v>5201.4375</v>
+        <v>5318.833333333333</v>
       </c>
       <c r="AG45" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG45</f>
@@ -15353,27 +15359,27 @@
       </c>
       <c r="AA46" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA46</f>
-        <v>8279.375</v>
+        <v>8413.3333333333339</v>
       </c>
       <c r="AB46" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB46</f>
-        <v>10.329282101607911</v>
+        <v>10.164817749603802</v>
       </c>
       <c r="AC46" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC46</f>
-        <v>1.0329282101607911</v>
+        <v>1.0164817749603803</v>
       </c>
       <c r="AD46" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD46</f>
-        <v>272.625</v>
+        <v>138.66666666666606</v>
       </c>
       <c r="AE46" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE46</f>
-        <v>4139.6875</v>
+        <v>4206.666666666667</v>
       </c>
       <c r="AF46" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF46</f>
-        <v>3867.0625</v>
+        <v>4068.0000000000009</v>
       </c>
       <c r="AG46" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG46</f>
@@ -15481,27 +15487,27 @@
       </c>
       <c r="AA47" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA47</f>
-        <v>5571.875</v>
+        <v>5701.6666666666661</v>
       </c>
       <c r="AB47" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB47</f>
-        <v>12.083903533370723</v>
+        <v>11.808827828120434</v>
       </c>
       <c r="AC47" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC47</f>
-        <v>1.2083903533370723</v>
+        <v>1.1808827828120434</v>
       </c>
       <c r="AD47" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD47</f>
-        <v>1161.125</v>
+        <v>1031.3333333333339</v>
       </c>
       <c r="AE47" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE47</f>
-        <v>2785.9375</v>
+        <v>2850.833333333333</v>
       </c>
       <c r="AF47" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF47</f>
-        <v>1624.8125</v>
+        <v>1819.4999999999991</v>
       </c>
       <c r="AG47" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG47</f>
@@ -15609,27 +15615,27 @@
       </c>
       <c r="AA48" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA48</f>
-        <v>26.25</v>
+        <v>24.444444444444446</v>
       </c>
       <c r="AB48" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB48</f>
-        <v>1991.2380952380952</v>
+        <v>2138.3181818181815</v>
       </c>
       <c r="AC48" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC48</f>
-        <v>199.12380952380951</v>
+        <v>213.83181818181816</v>
       </c>
       <c r="AD48" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD48</f>
-        <v>5200.75</v>
+        <v>5202.5555555555557</v>
       </c>
       <c r="AE48" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE48</f>
-        <v>13.125</v>
+        <v>12.222222222222223</v>
       </c>
       <c r="AF48" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF48</f>
-        <v>-5187.625</v>
+        <v>-5190.333333333333</v>
       </c>
       <c r="AG48" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG48</f>
@@ -15865,7 +15871,7 @@
       </c>
       <c r="AA50" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA50</f>
-        <v>421.875</v>
+        <v>575</v>
       </c>
       <c r="AB50" s="25">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB50</f>
@@ -15877,15 +15883,15 @@
       </c>
       <c r="AD50" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD50</f>
-        <v>-410.875</v>
+        <v>-564</v>
       </c>
       <c r="AE50" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE50</f>
-        <v>210.9375</v>
+        <v>287.5</v>
       </c>
       <c r="AF50" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF50</f>
-        <v>621.8125</v>
+        <v>851.5</v>
       </c>
       <c r="AG50" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG50</f>
@@ -16249,27 +16255,27 @@
       </c>
       <c r="AA53" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA53</f>
-        <v>4965.625</v>
+        <v>5255.5555555555557</v>
       </c>
       <c r="AB53" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB53</f>
-        <v>8.0553807426054121E-3</v>
+        <v>7.6109936575052854E-3</v>
       </c>
       <c r="AC53" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC53</f>
-        <v>8.0553807426054125E-4</v>
+        <v>7.610993657505285E-4</v>
       </c>
       <c r="AD53" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD53</f>
-        <v>-4961.625</v>
+        <v>-5251.5555555555557</v>
       </c>
       <c r="AE53" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE53</f>
-        <v>2482.8125</v>
+        <v>2627.7777777777778</v>
       </c>
       <c r="AF53" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF53</f>
-        <v>7444.4375</v>
+        <v>7879.3333333333339</v>
       </c>
       <c r="AG53" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG53</f>
@@ -16377,27 +16383,27 @@
       </c>
       <c r="AA54" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA54</f>
-        <v>415.625</v>
+        <v>380.55555555555554</v>
       </c>
       <c r="AB54" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB54</f>
-        <v>543.10977443609022</v>
+        <v>593.15912408759118</v>
       </c>
       <c r="AC54" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC54</f>
-        <v>54.310977443609019</v>
+        <v>59.315912408759125</v>
       </c>
       <c r="AD54" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD54</f>
-        <v>22157.375</v>
+        <v>22192.444444444445</v>
       </c>
       <c r="AE54" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE54</f>
-        <v>207.8125</v>
+        <v>190.27777777777777</v>
       </c>
       <c r="AF54" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF54</f>
-        <v>-21949.5625</v>
+        <v>-22002.166666666668</v>
       </c>
       <c r="AG54" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG54</f>
@@ -16505,27 +16511,27 @@
       </c>
       <c r="AA55" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA55</f>
-        <v>2871.25</v>
+        <v>3025.5555555555557</v>
       </c>
       <c r="AB55" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB55</f>
-        <v>101.79886808881149</v>
+        <v>96.607051046639739</v>
       </c>
       <c r="AC55" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC55</f>
-        <v>10.179886808881148</v>
+        <v>9.6607051046639736</v>
       </c>
       <c r="AD55" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD55</f>
-        <v>26357.75</v>
+        <v>26203.444444444445</v>
       </c>
       <c r="AE55" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE55</f>
-        <v>1435.625</v>
+        <v>1512.7777777777778</v>
       </c>
       <c r="AF55" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF55</f>
-        <v>-24922.125</v>
+        <v>-24690.666666666668</v>
       </c>
       <c r="AG55" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG55</f>
@@ -16633,27 +16639,27 @@
       </c>
       <c r="AA56" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA56</f>
-        <v>4826.875</v>
+        <v>5395.5555555555557</v>
       </c>
       <c r="AB56" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB56</f>
-        <v>33.458500582675128</v>
+        <v>29.932042833607909</v>
       </c>
       <c r="AC56" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC56</f>
-        <v>3.3458500582675126</v>
+        <v>2.9932042833607908</v>
       </c>
       <c r="AD56" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD56</f>
-        <v>11323.125</v>
+        <v>10754.444444444445</v>
       </c>
       <c r="AE56" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE56</f>
-        <v>2413.4375</v>
+        <v>2697.7777777777778</v>
       </c>
       <c r="AF56" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF56</f>
-        <v>-8909.6875</v>
+        <v>-8056.6666666666679</v>
       </c>
       <c r="AG56" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG56</f>
@@ -16761,27 +16767,27 @@
       </c>
       <c r="AA57" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA57</f>
-        <v>2846.875</v>
+        <v>3161.666666666667</v>
       </c>
       <c r="AB57" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB57</f>
-        <v>67.762019758507137</v>
+        <v>61.015287295730097</v>
       </c>
       <c r="AC57" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC57</f>
-        <v>6.7762019758507135</v>
+        <v>6.1015287295730092</v>
       </c>
       <c r="AD57" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD57</f>
-        <v>16444.125</v>
+        <v>16129.333333333332</v>
       </c>
       <c r="AE57" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE57</f>
-        <v>1423.4375</v>
+        <v>1580.8333333333335</v>
       </c>
       <c r="AF57" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF57</f>
-        <v>-15020.6875</v>
+        <v>-14548.499999999998</v>
       </c>
       <c r="AG57" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG57</f>
@@ -16889,27 +16895,27 @@
       </c>
       <c r="AA58" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA58</f>
-        <v>2563.75</v>
+        <v>2933.8888888888891</v>
       </c>
       <c r="AB58" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB58</f>
-        <v>2.7888834714773281</v>
+        <v>2.4370384396894527</v>
       </c>
       <c r="AC58" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC58</f>
-        <v>0.27888834714773281</v>
+        <v>0.24370384396894526</v>
       </c>
       <c r="AD58" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD58</f>
-        <v>-1848.75</v>
+        <v>-2218.8888888888891</v>
       </c>
       <c r="AE58" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE58</f>
-        <v>1281.875</v>
+        <v>1466.9444444444446</v>
       </c>
       <c r="AF58" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF58</f>
-        <v>3130.625</v>
+        <v>3685.8333333333339</v>
       </c>
       <c r="AG58" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG58</f>
@@ -17017,27 +17023,27 @@
       </c>
       <c r="AA59" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA59</f>
-        <v>471.875</v>
+        <v>608.33333333333337</v>
       </c>
       <c r="AB59" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB59</f>
-        <v>8.1801324503311257</v>
+        <v>6.3452054794520549</v>
       </c>
       <c r="AC59" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC59</f>
-        <v>0.81801324503311257</v>
+        <v>0.6345205479452054</v>
       </c>
       <c r="AD59" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD59</f>
-        <v>-85.875</v>
+        <v>-222.33333333333337</v>
       </c>
       <c r="AE59" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE59</f>
-        <v>235.9375</v>
+        <v>304.16666666666669</v>
       </c>
       <c r="AF59" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF59</f>
-        <v>321.8125</v>
+        <v>526.5</v>
       </c>
       <c r="AG59" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG59</f>
@@ -17145,27 +17151,27 @@
       </c>
       <c r="AA60" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA60</f>
-        <v>922.5</v>
+        <v>1091.6666666666667</v>
       </c>
       <c r="AB60" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB60</f>
-        <v>3.230352303523035</v>
+        <v>2.729770992366412</v>
       </c>
       <c r="AC60" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC60</f>
-        <v>0.32303523035230353</v>
+        <v>0.27297709923664121</v>
       </c>
       <c r="AD60" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD60</f>
-        <v>-624.5</v>
+        <v>-793.66666666666674</v>
       </c>
       <c r="AE60" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE60</f>
-        <v>461.25</v>
+        <v>545.83333333333337</v>
       </c>
       <c r="AF60" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF60</f>
-        <v>1085.75</v>
+        <v>1339.5</v>
       </c>
       <c r="AG60" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG60</f>
@@ -17273,27 +17279,27 @@
       </c>
       <c r="AA61" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA61</f>
-        <v>493.125</v>
+        <v>517.77777777777783</v>
       </c>
       <c r="AB61" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB61</f>
-        <v>2.9607097591888465</v>
+        <v>2.8197424892703857</v>
       </c>
       <c r="AC61" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC61</f>
-        <v>0.29607097591888465</v>
+        <v>0.2819742489270386</v>
       </c>
       <c r="AD61" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD61</f>
-        <v>-347.125</v>
+        <v>-371.77777777777783</v>
       </c>
       <c r="AE61" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE61</f>
-        <v>246.5625</v>
+        <v>258.88888888888891</v>
       </c>
       <c r="AF61" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF61</f>
-        <v>593.6875</v>
+        <v>630.66666666666674</v>
       </c>
       <c r="AG61" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG61</f>
@@ -17333,7 +17339,7 @@
       </c>
       <c r="AF62" s="44">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF62</f>
-        <v>151405.6875</v>
+        <v>156899.66666666666</v>
       </c>
     </row>
     <row r="63" spans="2:33" x14ac:dyDescent="0.25">
@@ -17342,10 +17348,10 @@
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
-      <c r="E63" s="67" t="s">
+      <c r="E63" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="F63" s="67"/>
+      <c r="F63" s="64"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -17370,10 +17376,10 @@
       <c r="AB63" s="42"/>
     </row>
     <row r="64" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B64" s="63" t="s">
+      <c r="B64" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="63"/>
+      <c r="C64" s="65"/>
       <c r="D64" s="48">
         <f>SUM(F13:F61)</f>
         <v>144936.54999999999</v>
@@ -17518,19 +17524,19 @@
       <c r="AB67" s="42"/>
     </row>
     <row r="68" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B68" s="63" t="s">
+      <c r="B68" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="C68" s="63"/>
+      <c r="C68" s="65"/>
       <c r="D68" s="50">
         <f>SUM(Z13:Z61)</f>
         <v>421177.93000000017</v>
       </c>
-      <c r="E68" s="64">
+      <c r="E68" s="66">
         <f>D68*100/D68</f>
         <v>100</v>
       </c>
-      <c r="F68" s="64"/>
+      <c r="F68" s="66"/>
       <c r="G68" s="51"/>
       <c r="H68" s="51"/>
       <c r="I68" s="51"/>
@@ -17615,10 +17621,10 @@
       <c r="AB70" s="42"/>
     </row>
     <row r="71" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B71" s="63" t="s">
+      <c r="B71" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="63"/>
+      <c r="C71" s="65"/>
       <c r="D71" s="3">
         <f>SUM(E13:E61)</f>
         <v>112990</v>
@@ -17733,11 +17739,11 @@
         <f>SUM(T13:T61)</f>
         <v>36961</v>
       </c>
-      <c r="E74" s="62">
+      <c r="E74" s="67">
         <f>D74*100/D75</f>
         <v>11.039956032533535</v>
       </c>
-      <c r="F74" s="62"/>
+      <c r="F74" s="67"/>
       <c r="G74" s="56"/>
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
@@ -17762,19 +17768,19 @@
       <c r="AB74" s="42"/>
     </row>
     <row r="75" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B75" s="63" t="s">
+      <c r="B75" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="63"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="55">
         <f>SUM(Y13:Y61)</f>
         <v>334793</v>
       </c>
-      <c r="E75" s="62">
+      <c r="E75" s="67">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="62"/>
+      <c r="F75" s="67"/>
       <c r="G75" s="56"/>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
@@ -18535,23 +18541,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="E71:F71"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="B1:Z6"/>
     <mergeCell ref="AA1:AG6"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G61">
     <cfRule type="colorScale" priority="5">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEECDEE-463A-42F6-A01A-8448DE9F3733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6FA20D-EC61-4E1C-A820-0DAA49CEBE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -841,6 +841,15 @@
     <xf numFmtId="2" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -849,15 +858,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5647,6 +5647,7 @@
       <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
       <sheetName val="Hoja1"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -5775,22 +5776,22 @@
             <v>13606.800000000001</v>
           </cell>
           <cell r="AA13">
-            <v>11850.555555555557</v>
+            <v>11712.105263157893</v>
           </cell>
           <cell r="AB13">
-            <v>8.4426421639866849</v>
+            <v>8.5424437154540964</v>
           </cell>
           <cell r="AC13">
-            <v>0.84426421639866855</v>
+            <v>0.85424437154540966</v>
           </cell>
           <cell r="AD13">
-            <v>-1845.5555555555566</v>
+            <v>-1707.1052631578932</v>
           </cell>
           <cell r="AE13">
-            <v>5925.2777777777783</v>
+            <v>5856.0526315789466</v>
           </cell>
           <cell r="AF13">
-            <v>7770.8333333333348</v>
+            <v>7563.1578947368398</v>
           </cell>
           <cell r="AG13">
             <v>125.0625</v>
@@ -5867,22 +5868,22 @@
             <v>888.81000000000006</v>
           </cell>
           <cell r="AA14">
-            <v>719.44444444444446</v>
+            <v>722.1052631578948</v>
           </cell>
           <cell r="AB14">
-            <v>7.7698841698841701</v>
+            <v>7.7412536443148685</v>
           </cell>
           <cell r="AC14">
-            <v>0.77698841698841703</v>
+            <v>0.77412536443148683</v>
           </cell>
           <cell r="AD14">
-            <v>-160.44444444444446</v>
+            <v>-163.1052631578948</v>
           </cell>
           <cell r="AE14">
-            <v>359.72222222222223</v>
+            <v>361.0526315789474</v>
           </cell>
           <cell r="AF14">
-            <v>520.16666666666674</v>
+            <v>524.1578947368422</v>
           </cell>
           <cell r="AG14">
             <v>6.9874999999999998</v>
@@ -5959,22 +5960,22 @@
             <v>6966.9599999999991</v>
           </cell>
           <cell r="AA15">
-            <v>4920</v>
+            <v>4932.6315789473683</v>
           </cell>
           <cell r="AB15">
-            <v>6.975609756097561</v>
+            <v>6.9577464788732399</v>
           </cell>
           <cell r="AC15">
-            <v>0.69756097560975605</v>
+            <v>0.6957746478873239</v>
           </cell>
           <cell r="AD15">
-            <v>-1488</v>
+            <v>-1500.6315789473683</v>
           </cell>
           <cell r="AE15">
-            <v>2460</v>
+            <v>2466.3157894736842</v>
           </cell>
           <cell r="AF15">
-            <v>3948</v>
+            <v>3966.9473684210525</v>
           </cell>
           <cell r="AG15">
             <v>57.2</v>
@@ -6051,22 +6052,22 @@
             <v>743.66</v>
           </cell>
           <cell r="AA16">
-            <v>857.22222222222229</v>
+            <v>872.1052631578948</v>
           </cell>
           <cell r="AB16">
-            <v>2.4031108230719376</v>
+            <v>2.3621001810500903</v>
           </cell>
           <cell r="AC16">
-            <v>0.24031108230719375</v>
+            <v>0.23621001810500902</v>
           </cell>
           <cell r="AD16">
-            <v>-651.22222222222229</v>
+            <v>-666.1052631578948</v>
           </cell>
           <cell r="AE16">
-            <v>428.61111111111114</v>
+            <v>436.0526315789474</v>
           </cell>
           <cell r="AF16">
-            <v>1079.8333333333335</v>
+            <v>1102.1578947368421</v>
           </cell>
           <cell r="AG16">
             <v>7.3571428571428568</v>
@@ -6143,22 +6144,22 @@
             <v>1861.36</v>
           </cell>
           <cell r="AA17">
-            <v>110</v>
+            <v>115.26315789473685</v>
           </cell>
           <cell r="AB17">
-            <v>19.272727272727273</v>
+            <v>18.392694063926939</v>
           </cell>
           <cell r="AC17">
-            <v>1.9272727272727272</v>
+            <v>1.839269406392694</v>
           </cell>
           <cell r="AD17">
-            <v>102</v>
+            <v>96.73684210526315</v>
           </cell>
           <cell r="AE17">
-            <v>55</v>
+            <v>57.631578947368425</v>
           </cell>
           <cell r="AF17">
-            <v>-47</v>
+            <v>-39.105263157894726</v>
           </cell>
           <cell r="AG17">
             <v>17.666666666666668</v>
@@ -6235,22 +6236,22 @@
             <v>5277.51</v>
           </cell>
           <cell r="AA18">
-            <v>14348.333333333332</v>
+            <v>14376.315789473683</v>
           </cell>
           <cell r="AB18">
-            <v>5.8383087466604717</v>
+            <v>5.8269449020684609</v>
           </cell>
           <cell r="AC18">
-            <v>0.58383087466604722</v>
+            <v>0.58269449020684605</v>
           </cell>
           <cell r="AD18">
-            <v>-5971.3333333333321</v>
+            <v>-5999.3157894736833</v>
           </cell>
           <cell r="AE18">
-            <v>7174.1666666666661</v>
+            <v>7188.1578947368416</v>
           </cell>
           <cell r="AF18">
-            <v>13145.499999999998</v>
+            <v>13187.473684210525</v>
           </cell>
           <cell r="AG18">
             <v>139.61666666666667</v>
@@ -6327,22 +6328,22 @@
             <v>949.41</v>
           </cell>
           <cell r="AA19">
-            <v>1439.4444444444446</v>
+            <v>1421.578947368421</v>
           </cell>
           <cell r="AB19">
-            <v>10.469316866074873</v>
+            <v>10.600888559792669</v>
           </cell>
           <cell r="AC19">
-            <v>1.0469316866074874</v>
+            <v>1.0600888559792669</v>
           </cell>
           <cell r="AD19">
-            <v>67.555555555555429</v>
+            <v>85.421052631578959</v>
           </cell>
           <cell r="AE19">
-            <v>719.72222222222229</v>
+            <v>710.78947368421052</v>
           </cell>
           <cell r="AF19">
-            <v>652.16666666666686</v>
+            <v>625.36842105263156</v>
           </cell>
           <cell r="AG19">
             <v>25.116666666666667</v>
@@ -6419,22 +6420,22 @@
             <v>2498.58</v>
           </cell>
           <cell r="AA20">
-            <v>3217.7777777777778</v>
+            <v>3270.5263157894733</v>
           </cell>
           <cell r="AB20">
-            <v>12.325276243093922</v>
+            <v>12.12648857418732</v>
           </cell>
           <cell r="AC20">
-            <v>1.2325276243093923</v>
+            <v>1.212648857418732</v>
           </cell>
           <cell r="AD20">
-            <v>748.22222222222217</v>
+            <v>695.4736842105267</v>
           </cell>
           <cell r="AE20">
-            <v>1608.8888888888889</v>
+            <v>1635.2631578947367</v>
           </cell>
           <cell r="AF20">
-            <v>860.66666666666674</v>
+            <v>939.78947368420995</v>
           </cell>
           <cell r="AG20">
             <v>66.099999999999994</v>
@@ -6511,22 +6512,22 @@
             <v>8325.42</v>
           </cell>
           <cell r="AA21">
-            <v>7480</v>
+            <v>7474.7368421052633</v>
           </cell>
           <cell r="AB21">
-            <v>10.211229946524064</v>
+            <v>10.2184199408534</v>
           </cell>
           <cell r="AC21">
-            <v>1.0211229946524065</v>
+            <v>1.02184199408534</v>
           </cell>
           <cell r="AD21">
-            <v>158</v>
+            <v>163.26315789473665</v>
           </cell>
           <cell r="AE21">
-            <v>3740</v>
+            <v>3737.3684210526317</v>
           </cell>
           <cell r="AF21">
-            <v>3582</v>
+            <v>3574.105263157895</v>
           </cell>
           <cell r="AG21">
             <v>141.44444444444446</v>
@@ -6603,22 +6604,22 @@
             <v>4099.4900000000007</v>
           </cell>
           <cell r="AA22">
-            <v>3530</v>
+            <v>3484.2105263157896</v>
           </cell>
           <cell r="AB22">
-            <v>10.654390934844193</v>
+            <v>10.794410876132931</v>
           </cell>
           <cell r="AC22">
-            <v>1.0654390934844193</v>
+            <v>1.0794410876132929</v>
           </cell>
           <cell r="AD22">
-            <v>231</v>
+            <v>276.78947368421041</v>
           </cell>
           <cell r="AE22">
-            <v>1765</v>
+            <v>1742.1052631578948</v>
           </cell>
           <cell r="AF22">
-            <v>1534</v>
+            <v>1465.3157894736844</v>
           </cell>
           <cell r="AG22">
             <v>69.648148148148152</v>
@@ -6695,22 +6696,22 @@
             <v>38473.719999999994</v>
           </cell>
           <cell r="AA23">
-            <v>34777.777777777781</v>
+            <v>34597.368421052633</v>
           </cell>
           <cell r="AB23">
-            <v>9.5368370607028741</v>
+            <v>9.5865672777059405</v>
           </cell>
           <cell r="AC23">
-            <v>0.95368370607028741</v>
+            <v>0.95865672777059396</v>
           </cell>
           <cell r="AD23">
-            <v>-1610.777777777781</v>
+            <v>-1430.3684210526335</v>
           </cell>
           <cell r="AE23">
-            <v>17388.888888888891</v>
+            <v>17298.684210526317</v>
           </cell>
           <cell r="AF23">
-            <v>18999.666666666672</v>
+            <v>18729.05263157895</v>
           </cell>
           <cell r="AG23">
             <v>614.2037037037037</v>
@@ -6787,22 +6788,22 @@
             <v>29054.519999999997</v>
           </cell>
           <cell r="AA24">
-            <v>22680.555555555555</v>
+            <v>22536.315789473683</v>
           </cell>
           <cell r="AB24">
-            <v>11.043380281690141</v>
+            <v>11.114061514748126</v>
           </cell>
           <cell r="AC24">
-            <v>1.1043380281690141</v>
+            <v>1.1114061514748126</v>
           </cell>
           <cell r="AD24">
-            <v>2366.4444444444453</v>
+            <v>2510.6842105263167</v>
           </cell>
           <cell r="AE24">
-            <v>11340.277777777777</v>
+            <v>11268.157894736842</v>
           </cell>
           <cell r="AF24">
-            <v>8973.8333333333321</v>
+            <v>8757.4736842105249</v>
           </cell>
           <cell r="AG24">
             <v>463.83333333333331</v>
@@ -6879,22 +6880,22 @@
             <v>30040.519999999997</v>
           </cell>
           <cell r="AA25">
-            <v>22049.444444444445</v>
+            <v>21916.315789473683</v>
           </cell>
           <cell r="AB25">
-            <v>11.744967119352969</v>
+            <v>11.816310847482049</v>
           </cell>
           <cell r="AC25">
-            <v>1.1744967119352969</v>
+            <v>1.181631084748205</v>
           </cell>
           <cell r="AD25">
-            <v>3847.5555555555547</v>
+            <v>3980.6842105263167</v>
           </cell>
           <cell r="AE25">
-            <v>11024.722222222223</v>
+            <v>10958.157894736842</v>
           </cell>
           <cell r="AF25">
-            <v>7177.1666666666679</v>
+            <v>6977.4736842105249</v>
           </cell>
           <cell r="AG25">
             <v>479.57407407407408</v>
@@ -6971,22 +6972,22 @@
             <v>34369.64</v>
           </cell>
           <cell r="AA26">
-            <v>26370</v>
+            <v>26250</v>
           </cell>
           <cell r="AB26">
-            <v>11.235874099355328</v>
+            <v>11.287238095238095</v>
           </cell>
           <cell r="AC26">
-            <v>1.1235874099355327</v>
+            <v>1.1287238095238095</v>
           </cell>
           <cell r="AD26">
-            <v>3259</v>
+            <v>3379</v>
           </cell>
           <cell r="AE26">
-            <v>13185</v>
+            <v>13125</v>
           </cell>
           <cell r="AF26">
-            <v>9926</v>
+            <v>9746</v>
           </cell>
           <cell r="AG26">
             <v>548.68518518518522</v>
@@ -7063,22 +7064,22 @@
             <v>1758.56</v>
           </cell>
           <cell r="AA27">
-            <v>178.33333333333331</v>
+            <v>150.52631578947367</v>
           </cell>
           <cell r="AB27">
-            <v>85.00934579439253</v>
+            <v>100.71328671328672</v>
           </cell>
           <cell r="AC27">
-            <v>8.500934579439253</v>
+            <v>10.071328671328672</v>
           </cell>
           <cell r="AD27">
-            <v>1337.6666666666667</v>
+            <v>1365.4736842105262</v>
           </cell>
           <cell r="AE27">
-            <v>89.166666666666657</v>
+            <v>75.263157894736835</v>
           </cell>
           <cell r="AF27">
-            <v>-1248.5</v>
+            <v>-1290.2105263157894</v>
           </cell>
           <cell r="AG27">
             <v>28.074074074074073</v>
@@ -7110,13 +7111,13 @@
             <v>3519.4399999999996</v>
           </cell>
           <cell r="L28">
-            <v>8.4591078066914491</v>
+            <v>8.3015552995391708</v>
           </cell>
           <cell r="M28">
-            <v>7890.666666666667</v>
+            <v>8040.4210526315783</v>
           </cell>
           <cell r="N28">
-            <v>-2346</v>
+            <v>-2448.1052631578941</v>
           </cell>
           <cell r="O28">
             <v>251</v>
@@ -7155,22 +7156,22 @@
             <v>5583.08</v>
           </cell>
           <cell r="AA28">
-            <v>3586.666666666667</v>
+            <v>3654.7368421052629</v>
           </cell>
           <cell r="AB28">
-            <v>13.419144981412639</v>
+            <v>13.169210829493089</v>
           </cell>
           <cell r="AC28">
-            <v>1.3419144981412638</v>
+            <v>1.3169210829493088</v>
           </cell>
           <cell r="AD28">
-            <v>1226.333333333333</v>
+            <v>1158.2631578947371</v>
           </cell>
           <cell r="AE28">
-            <v>1793.3333333333335</v>
+            <v>1827.3684210526314</v>
           </cell>
           <cell r="AF28">
-            <v>567.00000000000045</v>
+            <v>669.10526315789434</v>
           </cell>
           <cell r="AG28">
             <v>89.129629629629633</v>
@@ -7202,13 +7203,13 @@
             <v>3309.4799999999996</v>
           </cell>
           <cell r="L29">
-            <v>6.9613664091093952</v>
+            <v>6.9176875957120982</v>
           </cell>
           <cell r="M29">
-            <v>9016.3333333333321</v>
+            <v>9073.2631578947367</v>
           </cell>
           <cell r="N29">
-            <v>-3294.4999999999991</v>
+            <v>-3333.3157894736842</v>
           </cell>
           <cell r="O29">
             <v>236</v>
@@ -7247,22 +7248,22 @@
             <v>5281.48</v>
           </cell>
           <cell r="AA29">
-            <v>4098.333333333333</v>
+            <v>4124.21052631579</v>
           </cell>
           <cell r="AB29">
-            <v>11.109394062627084</v>
+            <v>11.039688616641142</v>
           </cell>
           <cell r="AC29">
-            <v>1.1109394062627085</v>
+            <v>1.1039688616641141</v>
           </cell>
           <cell r="AD29">
-            <v>454.66666666666697</v>
+            <v>428.78947368420995</v>
           </cell>
           <cell r="AE29">
-            <v>2049.1666666666665</v>
+            <v>2062.105263157895</v>
           </cell>
           <cell r="AF29">
-            <v>1594.4999999999995</v>
+            <v>1633.3157894736851</v>
           </cell>
           <cell r="AG29">
             <v>84.31481481481481</v>
@@ -7294,13 +7295,13 @@
             <v>3259.6</v>
           </cell>
           <cell r="L30">
-            <v>7.1653208669783242</v>
+            <v>7.1837997847147461</v>
           </cell>
           <cell r="M30">
-            <v>8627.6666666666679</v>
+            <v>8605.4736842105267</v>
           </cell>
           <cell r="N30">
-            <v>-3072.5000000000009</v>
+            <v>-3057.3684210526317</v>
           </cell>
           <cell r="O30">
             <v>236</v>
@@ -7339,22 +7340,22 @@
             <v>6992.48</v>
           </cell>
           <cell r="AA30">
-            <v>3921.666666666667</v>
+            <v>3911.5789473684208</v>
           </cell>
           <cell r="AB30">
-            <v>15.371015724606885</v>
+            <v>15.410656620021529</v>
           </cell>
           <cell r="AC30">
-            <v>1.5371015724606885</v>
+            <v>1.541065662002153</v>
           </cell>
           <cell r="AD30">
-            <v>2106.333333333333</v>
+            <v>2116.4210526315792</v>
           </cell>
           <cell r="AE30">
-            <v>1960.8333333333335</v>
+            <v>1955.7894736842104</v>
           </cell>
           <cell r="AF30">
-            <v>-145.49999999999955</v>
+            <v>-160.63157894736878</v>
           </cell>
           <cell r="AG30">
             <v>111.62962962962963</v>
@@ -7431,22 +7432,22 @@
             <v>5045.2800000000007</v>
           </cell>
           <cell r="AA31">
-            <v>2288.8888888888887</v>
+            <v>2312.6315789473683</v>
           </cell>
           <cell r="AB31">
-            <v>5.9898058252427191</v>
+            <v>5.9283113336367776</v>
           </cell>
           <cell r="AC31">
-            <v>0.59898058252427189</v>
+            <v>0.59283113336367776</v>
           </cell>
           <cell r="AD31">
-            <v>-917.88888888888869</v>
+            <v>-941.63157894736833</v>
           </cell>
           <cell r="AE31">
-            <v>1144.4444444444443</v>
+            <v>1156.3157894736842</v>
           </cell>
           <cell r="AF31">
-            <v>2062.333333333333</v>
+            <v>2097.9473684210525</v>
           </cell>
           <cell r="AG31">
             <v>85.6875</v>
@@ -7523,22 +7524,22 @@
             <v>3606.4</v>
           </cell>
           <cell r="AA32">
-            <v>1353.3333333333335</v>
+            <v>1350.5263157894738</v>
           </cell>
           <cell r="AB32">
-            <v>7.2413793103448274</v>
+            <v>7.2564302416212003</v>
           </cell>
           <cell r="AC32">
-            <v>0.72413793103448265</v>
+            <v>0.72564302416212001</v>
           </cell>
           <cell r="AD32">
-            <v>-373.33333333333348</v>
+            <v>-370.52631578947376</v>
           </cell>
           <cell r="AE32">
-            <v>676.66666666666674</v>
+            <v>675.26315789473688</v>
           </cell>
           <cell r="AF32">
-            <v>1050.0000000000002</v>
+            <v>1045.7894736842106</v>
           </cell>
           <cell r="AG32">
             <v>61.25</v>
@@ -7615,22 +7616,22 @@
             <v>13703.300000000001</v>
           </cell>
           <cell r="AA33">
-            <v>5106.666666666667</v>
+            <v>5045.78947368421</v>
           </cell>
           <cell r="AB33">
-            <v>6.4660574412532634</v>
+            <v>6.5440700949202055</v>
           </cell>
           <cell r="AC33">
-            <v>0.64660574412532634</v>
+            <v>0.65440700949202046</v>
           </cell>
           <cell r="AD33">
-            <v>-1804.666666666667</v>
+            <v>-1743.78947368421</v>
           </cell>
           <cell r="AE33">
-            <v>2553.3333333333335</v>
+            <v>2522.894736842105</v>
           </cell>
           <cell r="AF33">
-            <v>4358</v>
+            <v>4266.6842105263149</v>
           </cell>
           <cell r="AG33">
             <v>206.375</v>
@@ -7707,22 +7708,22 @@
             <v>26174.050000000003</v>
           </cell>
           <cell r="AA34">
-            <v>8115.5555555555557</v>
+            <v>7976.3157894736842</v>
           </cell>
           <cell r="AB34">
-            <v>7.7714950711938666</v>
+            <v>7.9071593533487299</v>
           </cell>
           <cell r="AC34">
-            <v>0.77714950711938657</v>
+            <v>0.79071593533487294</v>
           </cell>
           <cell r="AD34">
-            <v>-1808.5555555555557</v>
+            <v>-1669.3157894736842</v>
           </cell>
           <cell r="AE34">
-            <v>4057.7777777777778</v>
+            <v>3988.1578947368421</v>
           </cell>
           <cell r="AF34">
-            <v>5866.3333333333339</v>
+            <v>5657.4736842105267</v>
           </cell>
           <cell r="AG34">
             <v>394.1875</v>
@@ -7799,7 +7800,7 @@
             <v>0</v>
           </cell>
           <cell r="AA35">
-            <v>696.66666666666674</v>
+            <v>670.52631578947376</v>
           </cell>
           <cell r="AB35">
             <v>0</v>
@@ -7808,13 +7809,13 @@
             <v>0</v>
           </cell>
           <cell r="AD35">
-            <v>-696.66666666666674</v>
+            <v>-670.52631578947376</v>
           </cell>
           <cell r="AE35">
-            <v>348.33333333333337</v>
+            <v>335.26315789473688</v>
           </cell>
           <cell r="AF35">
-            <v>1045</v>
+            <v>1005.7894736842106</v>
           </cell>
           <cell r="AG35">
             <v>0</v>
@@ -7891,22 +7892,22 @@
             <v>2253.4500000000003</v>
           </cell>
           <cell r="AA36">
-            <v>7091.6666666666661</v>
+            <v>7127.894736842105</v>
           </cell>
           <cell r="AB36">
-            <v>0.76568742655699185</v>
+            <v>0.76179576164808394</v>
           </cell>
           <cell r="AC36">
-            <v>7.6568742655699185E-2</v>
+            <v>7.6179576164808388E-2</v>
           </cell>
           <cell r="AD36">
-            <v>-6548.6666666666661</v>
+            <v>-6584.894736842105</v>
           </cell>
           <cell r="AE36">
-            <v>3545.833333333333</v>
+            <v>3563.9473684210525</v>
           </cell>
           <cell r="AF36">
-            <v>10094.5</v>
+            <v>10148.842105263157</v>
           </cell>
           <cell r="AG36">
             <v>33.9375</v>
@@ -7983,22 +7984,22 @@
             <v>16573.84</v>
           </cell>
           <cell r="AA37">
-            <v>11621.666666666668</v>
+            <v>11818.42105263158</v>
           </cell>
           <cell r="AB37">
-            <v>8.7491753907930576</v>
+            <v>8.6035181474059232</v>
           </cell>
           <cell r="AC37">
-            <v>0.87491753907930581</v>
+            <v>0.86035181474059219</v>
           </cell>
           <cell r="AD37">
-            <v>-1453.6666666666679</v>
+            <v>-1650.4210526315801</v>
           </cell>
           <cell r="AE37">
-            <v>5810.8333333333339</v>
+            <v>5909.21052631579</v>
           </cell>
           <cell r="AF37">
-            <v>7264.5000000000018</v>
+            <v>7559.6315789473701</v>
           </cell>
           <cell r="AG37">
             <v>188.2962962962963</v>
@@ -8075,22 +8076,22 @@
             <v>16068.539999999999</v>
           </cell>
           <cell r="AA38">
-            <v>5161.1111111111113</v>
+            <v>5122.6315789473683</v>
           </cell>
           <cell r="AB38">
-            <v>19.100538213132403</v>
+            <v>19.244015206000203</v>
           </cell>
           <cell r="AC38">
-            <v>1.9100538213132399</v>
+            <v>1.9244015206000207</v>
           </cell>
           <cell r="AD38">
-            <v>4696.8888888888887</v>
+            <v>4735.3684210526317</v>
           </cell>
           <cell r="AE38">
-            <v>2580.5555555555557</v>
+            <v>2561.3157894736842</v>
           </cell>
           <cell r="AF38">
-            <v>-2116.333333333333</v>
+            <v>-2174.0526315789475</v>
           </cell>
           <cell r="AG38">
             <v>182.55555555555554</v>
@@ -8167,22 +8168,22 @@
             <v>3204.58</v>
           </cell>
           <cell r="AA39">
-            <v>3957.2222222222222</v>
+            <v>3974.2105263157896</v>
           </cell>
           <cell r="AB39">
-            <v>4.9681314053067531</v>
+            <v>4.9468944510660835</v>
           </cell>
           <cell r="AC39">
-            <v>0.49681314053067527</v>
+            <v>0.49468944510660839</v>
           </cell>
           <cell r="AD39">
-            <v>-1991.2222222222222</v>
+            <v>-2008.2105263157896</v>
           </cell>
           <cell r="AE39">
-            <v>1978.6111111111111</v>
+            <v>1987.1052631578948</v>
           </cell>
           <cell r="AF39">
-            <v>3969.833333333333</v>
+            <v>3995.3157894736842</v>
           </cell>
           <cell r="AG39">
             <v>36.407407407407405</v>
@@ -8259,22 +8260,22 @@
             <v>7409.98</v>
           </cell>
           <cell r="AA40">
-            <v>677.22222222222229</v>
+            <v>734.73684210526312</v>
           </cell>
           <cell r="AB40">
-            <v>67.127153404429848</v>
+            <v>61.872492836676216</v>
           </cell>
           <cell r="AC40">
-            <v>6.7127153404429851</v>
+            <v>6.1872492836676223</v>
           </cell>
           <cell r="AD40">
-            <v>3868.7777777777778</v>
+            <v>3811.2631578947367</v>
           </cell>
           <cell r="AE40">
-            <v>338.61111111111114</v>
+            <v>367.36842105263156</v>
           </cell>
           <cell r="AF40">
-            <v>-3530.1666666666665</v>
+            <v>-3443.894736842105</v>
           </cell>
           <cell r="AG40">
             <v>84.18518518518519</v>
@@ -8535,22 +8536,22 @@
             <v>4065.15</v>
           </cell>
           <cell r="AA43">
-            <v>1343.8888888888889</v>
+            <v>1321.578947368421</v>
           </cell>
           <cell r="AB43">
-            <v>4.9185613890037203</v>
+            <v>5.0015929908403027</v>
           </cell>
           <cell r="AC43">
-            <v>0.49185613890037205</v>
+            <v>0.50015929908403023</v>
           </cell>
           <cell r="AD43">
-            <v>-682.88888888888891</v>
+            <v>-660.57894736842104</v>
           </cell>
           <cell r="AE43">
-            <v>671.94444444444446</v>
+            <v>660.78947368421052</v>
           </cell>
           <cell r="AF43">
-            <v>1354.8333333333335</v>
+            <v>1321.3684210526317</v>
           </cell>
           <cell r="AG43">
             <v>12.24074074074074</v>
@@ -8627,22 +8628,22 @@
             <v>6980.25</v>
           </cell>
           <cell r="AA44">
-            <v>6372.2222222222217</v>
+            <v>6458.4210526315792</v>
           </cell>
           <cell r="AB44">
-            <v>1.7811682650392329</v>
+            <v>1.7573954852905223</v>
           </cell>
           <cell r="AC44">
-            <v>0.1781168265039233</v>
+            <v>0.17573954852905224</v>
           </cell>
           <cell r="AD44">
-            <v>-5237.2222222222217</v>
+            <v>-5323.4210526315792</v>
           </cell>
           <cell r="AE44">
-            <v>3186.1111111111109</v>
+            <v>3229.2105263157896</v>
           </cell>
           <cell r="AF44">
-            <v>8423.3333333333321</v>
+            <v>8552.6315789473683</v>
           </cell>
           <cell r="AG44">
             <v>21.018518518518519</v>
@@ -8719,22 +8720,22 @@
             <v>4816.32</v>
           </cell>
           <cell r="AA45">
-            <v>6313.8888888888887</v>
+            <v>6298.4210526315792</v>
           </cell>
           <cell r="AB45">
-            <v>6.5759788825340957</v>
+            <v>6.5921283529706693</v>
           </cell>
           <cell r="AC45">
-            <v>0.65759788825340959</v>
+            <v>0.65921283529706687</v>
           </cell>
           <cell r="AD45">
-            <v>-2161.8888888888887</v>
+            <v>-2146.4210526315792</v>
           </cell>
           <cell r="AE45">
-            <v>3156.9444444444443</v>
+            <v>3149.2105263157896</v>
           </cell>
           <cell r="AF45">
-            <v>5318.833333333333</v>
+            <v>5295.6315789473683</v>
           </cell>
           <cell r="AG45">
             <v>76.888888888888886</v>
@@ -8811,22 +8812,22 @@
             <v>9920.32</v>
           </cell>
           <cell r="AA46">
-            <v>8413.3333333333339</v>
+            <v>8365.2631578947367</v>
           </cell>
           <cell r="AB46">
-            <v>10.164817749603802</v>
+            <v>10.223228891405562</v>
           </cell>
           <cell r="AC46">
-            <v>1.0164817749603803</v>
+            <v>1.0223228891405562</v>
           </cell>
           <cell r="AD46">
-            <v>138.66666666666606</v>
+            <v>186.73684210526335</v>
           </cell>
           <cell r="AE46">
-            <v>4206.666666666667</v>
+            <v>4182.6315789473683</v>
           </cell>
           <cell r="AF46">
-            <v>4068.0000000000009</v>
+            <v>3995.894736842105</v>
           </cell>
           <cell r="AG46">
             <v>158.37037037037038</v>
@@ -8903,22 +8904,22 @@
             <v>7810.28</v>
           </cell>
           <cell r="AA47">
-            <v>5701.6666666666661</v>
+            <v>5688.4210526315792</v>
           </cell>
           <cell r="AB47">
-            <v>11.808827828120434</v>
+            <v>11.836324944485566</v>
           </cell>
           <cell r="AC47">
-            <v>1.1808827828120434</v>
+            <v>1.1836324944485566</v>
           </cell>
           <cell r="AD47">
-            <v>1031.3333333333339</v>
+            <v>1044.5789473684208</v>
           </cell>
           <cell r="AE47">
-            <v>2850.833333333333</v>
+            <v>2844.2105263157896</v>
           </cell>
           <cell r="AF47">
-            <v>1819.4999999999991</v>
+            <v>1799.6315789473688</v>
           </cell>
           <cell r="AG47">
             <v>124.68518518518519</v>
@@ -8995,22 +8996,22 @@
             <v>6063.32</v>
           </cell>
           <cell r="AA48">
-            <v>24.444444444444446</v>
+            <v>24.736842105263158</v>
           </cell>
           <cell r="AB48">
-            <v>2138.3181818181815</v>
+            <v>2113.0425531914893</v>
           </cell>
           <cell r="AC48">
-            <v>213.83181818181816</v>
+            <v>211.30425531914895</v>
           </cell>
           <cell r="AD48">
-            <v>5202.5555555555557</v>
+            <v>5202.2631578947367</v>
           </cell>
           <cell r="AE48">
-            <v>12.222222222222223</v>
+            <v>12.368421052631579</v>
           </cell>
           <cell r="AF48">
-            <v>-5190.333333333333</v>
+            <v>-5189.894736842105</v>
           </cell>
           <cell r="AG48">
             <v>96.796296296296291</v>
@@ -9179,7 +9180,7 @@
             <v>198</v>
           </cell>
           <cell r="AA50">
-            <v>575</v>
+            <v>567.89473684210532</v>
           </cell>
           <cell r="AB50">
             <v>0</v>
@@ -9188,13 +9189,13 @@
             <v>0</v>
           </cell>
           <cell r="AD50">
-            <v>-564</v>
+            <v>-556.89473684210532</v>
           </cell>
           <cell r="AE50">
-            <v>287.5</v>
+            <v>283.94736842105266</v>
           </cell>
           <cell r="AF50">
-            <v>851.5</v>
+            <v>840.84210526315792</v>
           </cell>
           <cell r="AG50">
             <v>5.5</v>
@@ -9271,22 +9272,22 @@
             <v>49.879999999999995</v>
           </cell>
           <cell r="AA51">
-            <v>5</v>
+            <v>4.7368421052631575</v>
           </cell>
           <cell r="AB51">
-            <v>86</v>
+            <v>90.777777777777786</v>
           </cell>
           <cell r="AC51">
-            <v>8.6</v>
+            <v>9.0777777777777793</v>
           </cell>
           <cell r="AD51">
-            <v>38</v>
+            <v>38.263157894736842</v>
           </cell>
           <cell r="AE51">
-            <v>2.5</v>
+            <v>2.3684210526315788</v>
           </cell>
           <cell r="AF51">
-            <v>-35.5</v>
+            <v>-35.89473684210526</v>
           </cell>
           <cell r="AG51">
             <v>1.075</v>
@@ -9455,22 +9456,22 @@
             <v>4.6399999999999997</v>
           </cell>
           <cell r="AA53">
-            <v>5255.5555555555557</v>
+            <v>5240.5263157894742</v>
           </cell>
           <cell r="AB53">
-            <v>7.6109936575052854E-3</v>
+            <v>7.6328211308627093E-3</v>
           </cell>
           <cell r="AC53">
-            <v>7.610993657505285E-4</v>
+            <v>7.6328211308627093E-4</v>
           </cell>
           <cell r="AD53">
-            <v>-5251.5555555555557</v>
+            <v>-5236.5263157894742</v>
           </cell>
           <cell r="AE53">
-            <v>2627.7777777777778</v>
+            <v>2620.2631578947371</v>
           </cell>
           <cell r="AF53">
-            <v>7879.3333333333339</v>
+            <v>7856.7894736842118</v>
           </cell>
           <cell r="AG53">
             <v>0.1</v>
@@ -9547,22 +9548,22 @@
             <v>18284.13</v>
           </cell>
           <cell r="AA54">
-            <v>380.55555555555554</v>
+            <v>590.52631578947376</v>
           </cell>
           <cell r="AB54">
-            <v>593.15912408759118</v>
+            <v>382.25222816399281</v>
           </cell>
           <cell r="AC54">
-            <v>59.315912408759125</v>
+            <v>38.225222816399281</v>
           </cell>
           <cell r="AD54">
-            <v>22192.444444444445</v>
+            <v>21982.473684210527</v>
           </cell>
           <cell r="AE54">
-            <v>190.27777777777777</v>
+            <v>295.26315789473688</v>
           </cell>
           <cell r="AF54">
-            <v>-22002.166666666668</v>
+            <v>-21687.21052631579</v>
           </cell>
           <cell r="AG54">
             <v>1881.0833333333333</v>
@@ -9639,22 +9640,22 @@
             <v>23675.49</v>
           </cell>
           <cell r="AA55">
-            <v>3025.5555555555557</v>
+            <v>3006.3157894736842</v>
           </cell>
           <cell r="AB55">
-            <v>96.607051046639739</v>
+            <v>97.225315126050418</v>
           </cell>
           <cell r="AC55">
-            <v>9.6607051046639736</v>
+            <v>9.7225315126050429</v>
           </cell>
           <cell r="AD55">
-            <v>26203.444444444445</v>
+            <v>26222.684210526317</v>
           </cell>
           <cell r="AE55">
-            <v>1512.7777777777778</v>
+            <v>1503.1578947368421</v>
           </cell>
           <cell r="AF55">
-            <v>-24690.666666666668</v>
+            <v>-24719.526315789473</v>
           </cell>
           <cell r="AG55">
             <v>2435.75</v>
@@ -9731,22 +9732,22 @@
             <v>13081.5</v>
           </cell>
           <cell r="AA56">
-            <v>5395.5555555555557</v>
+            <v>5310.5263157894742</v>
           </cell>
           <cell r="AB56">
-            <v>29.932042833607909</v>
+            <v>30.411298315163528</v>
           </cell>
           <cell r="AC56">
-            <v>2.9932042833607908</v>
+            <v>3.0411298315163524</v>
           </cell>
           <cell r="AD56">
-            <v>10754.444444444445</v>
+            <v>10839.473684210527</v>
           </cell>
           <cell r="AE56">
-            <v>2697.7777777777778</v>
+            <v>2655.2631578947371</v>
           </cell>
           <cell r="AF56">
-            <v>-8056.6666666666679</v>
+            <v>-8184.21052631579</v>
           </cell>
           <cell r="AG56">
             <v>1345.8333333333333</v>
@@ -9823,22 +9824,22 @@
             <v>15625.710000000001</v>
           </cell>
           <cell r="AA57">
-            <v>3161.666666666667</v>
+            <v>3101.0526315789475</v>
           </cell>
           <cell r="AB57">
-            <v>61.015287295730097</v>
+            <v>62.207909029192123</v>
           </cell>
           <cell r="AC57">
-            <v>6.1015287295730092</v>
+            <v>6.2207909029192123</v>
           </cell>
           <cell r="AD57">
-            <v>16129.333333333332</v>
+            <v>16189.947368421053</v>
           </cell>
           <cell r="AE57">
-            <v>1580.8333333333335</v>
+            <v>1550.5263157894738</v>
           </cell>
           <cell r="AF57">
-            <v>-14548.499999999998</v>
+            <v>-14639.42105263158</v>
           </cell>
           <cell r="AG57">
             <v>1607.5833333333333</v>
@@ -9915,22 +9916,22 @@
             <v>1873.3000000000002</v>
           </cell>
           <cell r="AA58">
-            <v>2933.8888888888891</v>
+            <v>2907.894736842105</v>
           </cell>
           <cell r="AB58">
-            <v>2.4370384396894527</v>
+            <v>2.4588235294117649</v>
           </cell>
           <cell r="AC58">
-            <v>0.24370384396894526</v>
+            <v>0.2458823529411765</v>
           </cell>
           <cell r="AD58">
-            <v>-2218.8888888888891</v>
+            <v>-2192.894736842105</v>
           </cell>
           <cell r="AE58">
-            <v>1466.9444444444446</v>
+            <v>1453.9473684210525</v>
           </cell>
           <cell r="AF58">
-            <v>3685.8333333333339</v>
+            <v>3646.8421052631575</v>
           </cell>
           <cell r="AG58">
             <v>119.16666666666667</v>
@@ -10007,22 +10008,22 @@
             <v>1011.32</v>
           </cell>
           <cell r="AA59">
-            <v>608.33333333333337</v>
+            <v>587.36842105263156</v>
           </cell>
           <cell r="AB59">
-            <v>6.3452054794520549</v>
+            <v>6.5716845878136203</v>
           </cell>
           <cell r="AC59">
-            <v>0.6345205479452054</v>
+            <v>0.65716845878136199</v>
           </cell>
           <cell r="AD59">
-            <v>-222.33333333333337</v>
+            <v>-201.36842105263156</v>
           </cell>
           <cell r="AE59">
-            <v>304.16666666666669</v>
+            <v>293.68421052631578</v>
           </cell>
           <cell r="AF59">
-            <v>526.5</v>
+            <v>495.05263157894734</v>
           </cell>
           <cell r="AG59">
             <v>64.333333333333329</v>
@@ -10099,22 +10100,22 @@
             <v>780.76</v>
           </cell>
           <cell r="AA60">
-            <v>1091.6666666666667</v>
+            <v>1076.8421052631579</v>
           </cell>
           <cell r="AB60">
-            <v>2.729770992366412</v>
+            <v>2.767350928641251</v>
           </cell>
           <cell r="AC60">
-            <v>0.27297709923664121</v>
+            <v>0.27673509286412512</v>
           </cell>
           <cell r="AD60">
-            <v>-793.66666666666674</v>
+            <v>-778.84210526315792</v>
           </cell>
           <cell r="AE60">
-            <v>545.83333333333337</v>
+            <v>538.42105263157896</v>
           </cell>
           <cell r="AF60">
-            <v>1339.5</v>
+            <v>1317.2631578947369</v>
           </cell>
           <cell r="AG60">
             <v>49.666666666666664</v>
@@ -10191,22 +10192,22 @@
             <v>382.52000000000004</v>
           </cell>
           <cell r="AA61">
-            <v>517.77777777777783</v>
+            <v>511.0526315789474</v>
           </cell>
           <cell r="AB61">
-            <v>2.8197424892703857</v>
+            <v>2.8568486096807413</v>
           </cell>
           <cell r="AC61">
-            <v>0.2819742489270386</v>
+            <v>0.28568486096807416</v>
           </cell>
           <cell r="AD61">
-            <v>-371.77777777777783</v>
+            <v>-365.0526315789474</v>
           </cell>
           <cell r="AE61">
-            <v>258.88888888888891</v>
+            <v>255.5263157894737</v>
           </cell>
           <cell r="AF61">
-            <v>630.66666666666674</v>
+            <v>620.57894736842104</v>
           </cell>
           <cell r="AG61">
             <v>24.333333333333332</v>
@@ -10217,7 +10218,7 @@
             <v>Units Produce</v>
           </cell>
           <cell r="AF62">
-            <v>156899.66666666666</v>
+            <v>155940.89473684211</v>
           </cell>
         </row>
       </sheetData>
@@ -10235,6 +10236,7 @@
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10559,212 +10561,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="63" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="63"/>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="63"/>
+      <c r="AB1" s="66"/>
+      <c r="AC1" s="66"/>
+      <c r="AD1" s="66"/>
+      <c r="AE1" s="66"/>
+      <c r="AF1" s="66"/>
+      <c r="AG1" s="66"/>
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
-      <c r="AA2" s="63"/>
-      <c r="AB2" s="63"/>
-      <c r="AC2" s="63"/>
-      <c r="AD2" s="63"/>
-      <c r="AE2" s="63"/>
-      <c r="AF2" s="63"/>
-      <c r="AG2" s="63"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="66"/>
+      <c r="AC2" s="66"/>
+      <c r="AD2" s="66"/>
+      <c r="AE2" s="66"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="62"/>
-      <c r="U3" s="62"/>
-      <c r="V3" s="62"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="62"/>
-      <c r="AA3" s="63"/>
-      <c r="AB3" s="63"/>
-      <c r="AC3" s="63"/>
-      <c r="AD3" s="63"/>
-      <c r="AE3" s="63"/>
-      <c r="AF3" s="63"/>
-      <c r="AG3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="66"/>
+      <c r="AB3" s="66"/>
+      <c r="AC3" s="66"/>
+      <c r="AD3" s="66"/>
+      <c r="AE3" s="66"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="62"/>
-      <c r="W4" s="62"/>
-      <c r="X4" s="62"/>
-      <c r="Y4" s="62"/>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="63"/>
-      <c r="AB4" s="63"/>
-      <c r="AC4" s="63"/>
-      <c r="AD4" s="63"/>
-      <c r="AE4" s="63"/>
-      <c r="AF4" s="63"/>
-      <c r="AG4" s="63"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="62"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="62"/>
-      <c r="Y5" s="62"/>
-      <c r="Z5" s="62"/>
-      <c r="AA5" s="63"/>
-      <c r="AB5" s="63"/>
-      <c r="AC5" s="63"/>
-      <c r="AD5" s="63"/>
-      <c r="AE5" s="63"/>
-      <c r="AF5" s="63"/>
-      <c r="AG5" s="63"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="66"/>
+      <c r="AB5" s="66"/>
+      <c r="AC5" s="66"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="63"/>
-      <c r="AB6" s="63"/>
-      <c r="AC6" s="63"/>
-      <c r="AD6" s="63"/>
-      <c r="AE6" s="63"/>
-      <c r="AF6" s="63"/>
-      <c r="AG6" s="63"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="66"/>
+      <c r="AB6" s="66"/>
+      <c r="AC6" s="66"/>
+      <c r="AD6" s="66"/>
+      <c r="AE6" s="66"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
@@ -11135,27 +11137,27 @@
       </c>
       <c r="AA13" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA13</f>
-        <v>11850.555555555557</v>
+        <v>11712.105263157893</v>
       </c>
       <c r="AB13" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB13</f>
-        <v>8.4426421639866849</v>
+        <v>8.5424437154540964</v>
       </c>
       <c r="AC13" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC13</f>
-        <v>0.84426421639866855</v>
+        <v>0.85424437154540966</v>
       </c>
       <c r="AD13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD13</f>
-        <v>-1845.5555555555566</v>
+        <v>-1707.1052631578932</v>
       </c>
       <c r="AE13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE13</f>
-        <v>5925.2777777777783</v>
+        <v>5856.0526315789466</v>
       </c>
       <c r="AF13" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF13</f>
-        <v>7770.8333333333348</v>
+        <v>7563.1578947368398</v>
       </c>
       <c r="AG13" s="27">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG13</f>
@@ -11263,27 +11265,27 @@
       </c>
       <c r="AA14" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA14</f>
-        <v>719.44444444444446</v>
+        <v>722.1052631578948</v>
       </c>
       <c r="AB14" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB14</f>
-        <v>7.7698841698841701</v>
+        <v>7.7412536443148685</v>
       </c>
       <c r="AC14" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC14</f>
-        <v>0.77698841698841703</v>
+        <v>0.77412536443148683</v>
       </c>
       <c r="AD14" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD14</f>
-        <v>-160.44444444444446</v>
+        <v>-163.1052631578948</v>
       </c>
       <c r="AE14" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE14</f>
-        <v>359.72222222222223</v>
+        <v>361.0526315789474</v>
       </c>
       <c r="AF14" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF14</f>
-        <v>520.16666666666674</v>
+        <v>524.1578947368422</v>
       </c>
       <c r="AG14" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG14</f>
@@ -11391,27 +11393,27 @@
       </c>
       <c r="AA15" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA15</f>
-        <v>4920</v>
+        <v>4932.6315789473683</v>
       </c>
       <c r="AB15" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB15</f>
-        <v>6.975609756097561</v>
+        <v>6.9577464788732399</v>
       </c>
       <c r="AC15" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC15</f>
-        <v>0.69756097560975605</v>
+        <v>0.6957746478873239</v>
       </c>
       <c r="AD15" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD15</f>
-        <v>-1488</v>
+        <v>-1500.6315789473683</v>
       </c>
       <c r="AE15" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE15</f>
-        <v>2460</v>
+        <v>2466.3157894736842</v>
       </c>
       <c r="AF15" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF15</f>
-        <v>3948</v>
+        <v>3966.9473684210525</v>
       </c>
       <c r="AG15" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG15</f>
@@ -11519,27 +11521,27 @@
       </c>
       <c r="AA16" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA16</f>
-        <v>857.22222222222229</v>
+        <v>872.1052631578948</v>
       </c>
       <c r="AB16" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB16</f>
-        <v>2.4031108230719376</v>
+        <v>2.3621001810500903</v>
       </c>
       <c r="AC16" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC16</f>
-        <v>0.24031108230719375</v>
+        <v>0.23621001810500902</v>
       </c>
       <c r="AD16" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD16</f>
-        <v>-651.22222222222229</v>
+        <v>-666.1052631578948</v>
       </c>
       <c r="AE16" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE16</f>
-        <v>428.61111111111114</v>
+        <v>436.0526315789474</v>
       </c>
       <c r="AF16" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF16</f>
-        <v>1079.8333333333335</v>
+        <v>1102.1578947368421</v>
       </c>
       <c r="AG16" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG16</f>
@@ -11647,27 +11649,27 @@
       </c>
       <c r="AA17" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA17</f>
-        <v>110</v>
+        <v>115.26315789473685</v>
       </c>
       <c r="AB17" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB17</f>
-        <v>19.272727272727273</v>
+        <v>18.392694063926939</v>
       </c>
       <c r="AC17" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC17</f>
-        <v>1.9272727272727272</v>
+        <v>1.839269406392694</v>
       </c>
       <c r="AD17" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD17</f>
-        <v>102</v>
+        <v>96.73684210526315</v>
       </c>
       <c r="AE17" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE17</f>
-        <v>55</v>
+        <v>57.631578947368425</v>
       </c>
       <c r="AF17" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF17</f>
-        <v>-47</v>
+        <v>-39.105263157894726</v>
       </c>
       <c r="AG17" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG17</f>
@@ -11775,27 +11777,27 @@
       </c>
       <c r="AA18" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA18</f>
-        <v>14348.333333333332</v>
+        <v>14376.315789473683</v>
       </c>
       <c r="AB18" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB18</f>
-        <v>5.8383087466604717</v>
+        <v>5.8269449020684609</v>
       </c>
       <c r="AC18" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC18</f>
-        <v>0.58383087466604722</v>
+        <v>0.58269449020684605</v>
       </c>
       <c r="AD18" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD18</f>
-        <v>-5971.3333333333321</v>
+        <v>-5999.3157894736833</v>
       </c>
       <c r="AE18" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE18</f>
-        <v>7174.1666666666661</v>
+        <v>7188.1578947368416</v>
       </c>
       <c r="AF18" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF18</f>
-        <v>13145.499999999998</v>
+        <v>13187.473684210525</v>
       </c>
       <c r="AG18" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG18</f>
@@ -11903,27 +11905,27 @@
       </c>
       <c r="AA19" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA19</f>
-        <v>1439.4444444444446</v>
+        <v>1421.578947368421</v>
       </c>
       <c r="AB19" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB19</f>
-        <v>10.469316866074873</v>
+        <v>10.600888559792669</v>
       </c>
       <c r="AC19" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC19</f>
-        <v>1.0469316866074874</v>
+        <v>1.0600888559792669</v>
       </c>
       <c r="AD19" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD19</f>
-        <v>67.555555555555429</v>
+        <v>85.421052631578959</v>
       </c>
       <c r="AE19" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE19</f>
-        <v>719.72222222222229</v>
+        <v>710.78947368421052</v>
       </c>
       <c r="AF19" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF19</f>
-        <v>652.16666666666686</v>
+        <v>625.36842105263156</v>
       </c>
       <c r="AG19" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG19</f>
@@ -12031,27 +12033,27 @@
       </c>
       <c r="AA20" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA20</f>
-        <v>3217.7777777777778</v>
+        <v>3270.5263157894733</v>
       </c>
       <c r="AB20" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB20</f>
-        <v>12.325276243093922</v>
+        <v>12.12648857418732</v>
       </c>
       <c r="AC20" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC20</f>
-        <v>1.2325276243093923</v>
+        <v>1.212648857418732</v>
       </c>
       <c r="AD20" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD20</f>
-        <v>748.22222222222217</v>
+        <v>695.4736842105267</v>
       </c>
       <c r="AE20" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE20</f>
-        <v>1608.8888888888889</v>
+        <v>1635.2631578947367</v>
       </c>
       <c r="AF20" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF20</f>
-        <v>860.66666666666674</v>
+        <v>939.78947368420995</v>
       </c>
       <c r="AG20" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG20</f>
@@ -12159,27 +12161,27 @@
       </c>
       <c r="AA21" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA21</f>
-        <v>7480</v>
+        <v>7474.7368421052633</v>
       </c>
       <c r="AB21" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB21</f>
-        <v>10.211229946524064</v>
+        <v>10.2184199408534</v>
       </c>
       <c r="AC21" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC21</f>
-        <v>1.0211229946524065</v>
+        <v>1.02184199408534</v>
       </c>
       <c r="AD21" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD21</f>
-        <v>158</v>
+        <v>163.26315789473665</v>
       </c>
       <c r="AE21" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE21</f>
-        <v>3740</v>
+        <v>3737.3684210526317</v>
       </c>
       <c r="AF21" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF21</f>
-        <v>3582</v>
+        <v>3574.105263157895</v>
       </c>
       <c r="AG21" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG21</f>
@@ -12287,27 +12289,27 @@
       </c>
       <c r="AA22" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA22</f>
-        <v>3530</v>
+        <v>3484.2105263157896</v>
       </c>
       <c r="AB22" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB22</f>
-        <v>10.654390934844193</v>
+        <v>10.794410876132931</v>
       </c>
       <c r="AC22" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC22</f>
-        <v>1.0654390934844193</v>
+        <v>1.0794410876132929</v>
       </c>
       <c r="AD22" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD22</f>
-        <v>231</v>
+        <v>276.78947368421041</v>
       </c>
       <c r="AE22" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE22</f>
-        <v>1765</v>
+        <v>1742.1052631578948</v>
       </c>
       <c r="AF22" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF22</f>
-        <v>1534</v>
+        <v>1465.3157894736844</v>
       </c>
       <c r="AG22" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG22</f>
@@ -12415,27 +12417,27 @@
       </c>
       <c r="AA23" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA23</f>
-        <v>34777.777777777781</v>
+        <v>34597.368421052633</v>
       </c>
       <c r="AB23" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB23</f>
-        <v>9.5368370607028741</v>
+        <v>9.5865672777059405</v>
       </c>
       <c r="AC23" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC23</f>
-        <v>0.95368370607028741</v>
+        <v>0.95865672777059396</v>
       </c>
       <c r="AD23" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD23</f>
-        <v>-1610.777777777781</v>
+        <v>-1430.3684210526335</v>
       </c>
       <c r="AE23" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE23</f>
-        <v>17388.888888888891</v>
+        <v>17298.684210526317</v>
       </c>
       <c r="AF23" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF23</f>
-        <v>18999.666666666672</v>
+        <v>18729.05263157895</v>
       </c>
       <c r="AG23" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG23</f>
@@ -12543,27 +12545,27 @@
       </c>
       <c r="AA24" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA24</f>
-        <v>22680.555555555555</v>
+        <v>22536.315789473683</v>
       </c>
       <c r="AB24" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB24</f>
-        <v>11.043380281690141</v>
+        <v>11.114061514748126</v>
       </c>
       <c r="AC24" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC24</f>
-        <v>1.1043380281690141</v>
+        <v>1.1114061514748126</v>
       </c>
       <c r="AD24" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD24</f>
-        <v>2366.4444444444453</v>
+        <v>2510.6842105263167</v>
       </c>
       <c r="AE24" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE24</f>
-        <v>11340.277777777777</v>
+        <v>11268.157894736842</v>
       </c>
       <c r="AF24" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF24</f>
-        <v>8973.8333333333321</v>
+        <v>8757.4736842105249</v>
       </c>
       <c r="AG24" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG24</f>
@@ -12671,27 +12673,27 @@
       </c>
       <c r="AA25" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA25</f>
-        <v>22049.444444444445</v>
+        <v>21916.315789473683</v>
       </c>
       <c r="AB25" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB25</f>
-        <v>11.744967119352969</v>
+        <v>11.816310847482049</v>
       </c>
       <c r="AC25" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC25</f>
-        <v>1.1744967119352969</v>
+        <v>1.181631084748205</v>
       </c>
       <c r="AD25" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD25</f>
-        <v>3847.5555555555547</v>
+        <v>3980.6842105263167</v>
       </c>
       <c r="AE25" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE25</f>
-        <v>11024.722222222223</v>
+        <v>10958.157894736842</v>
       </c>
       <c r="AF25" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF25</f>
-        <v>7177.1666666666679</v>
+        <v>6977.4736842105249</v>
       </c>
       <c r="AG25" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG25</f>
@@ -12799,27 +12801,27 @@
       </c>
       <c r="AA26" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA26</f>
-        <v>26370</v>
+        <v>26250</v>
       </c>
       <c r="AB26" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB26</f>
-        <v>11.235874099355328</v>
+        <v>11.287238095238095</v>
       </c>
       <c r="AC26" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC26</f>
-        <v>1.1235874099355327</v>
+        <v>1.1287238095238095</v>
       </c>
       <c r="AD26" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD26</f>
-        <v>3259</v>
+        <v>3379</v>
       </c>
       <c r="AE26" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE26</f>
-        <v>13185</v>
+        <v>13125</v>
       </c>
       <c r="AF26" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF26</f>
-        <v>9926</v>
+        <v>9746</v>
       </c>
       <c r="AG26" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG26</f>
@@ -12927,27 +12929,27 @@
       </c>
       <c r="AA27" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA27</f>
-        <v>178.33333333333331</v>
+        <v>150.52631578947367</v>
       </c>
       <c r="AB27" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB27</f>
-        <v>85.00934579439253</v>
+        <v>100.71328671328672</v>
       </c>
       <c r="AC27" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC27</f>
-        <v>8.500934579439253</v>
+        <v>10.071328671328672</v>
       </c>
       <c r="AD27" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD27</f>
-        <v>1337.6666666666667</v>
+        <v>1365.4736842105262</v>
       </c>
       <c r="AE27" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE27</f>
-        <v>89.166666666666657</v>
+        <v>75.263157894736835</v>
       </c>
       <c r="AF27" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF27</f>
-        <v>-1248.5</v>
+        <v>-1290.2105263157894</v>
       </c>
       <c r="AG27" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG27</f>
@@ -12995,15 +12997,15 @@
       </c>
       <c r="L28" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L28</f>
-        <v>8.4591078066914491</v>
+        <v>8.3015552995391708</v>
       </c>
       <c r="M28" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M28</f>
-        <v>7890.666666666667</v>
+        <v>8040.4210526315783</v>
       </c>
       <c r="N28" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N28</f>
-        <v>-2346</v>
+        <v>-2448.1052631578941</v>
       </c>
       <c r="O28" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O28</f>
@@ -13055,27 +13057,27 @@
       </c>
       <c r="AA28" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA28</f>
-        <v>3586.666666666667</v>
+        <v>3654.7368421052629</v>
       </c>
       <c r="AB28" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB28</f>
-        <v>13.419144981412639</v>
+        <v>13.169210829493089</v>
       </c>
       <c r="AC28" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC28</f>
-        <v>1.3419144981412638</v>
+        <v>1.3169210829493088</v>
       </c>
       <c r="AD28" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD28</f>
-        <v>1226.333333333333</v>
+        <v>1158.2631578947371</v>
       </c>
       <c r="AE28" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE28</f>
-        <v>1793.3333333333335</v>
+        <v>1827.3684210526314</v>
       </c>
       <c r="AF28" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF28</f>
-        <v>567.00000000000045</v>
+        <v>669.10526315789434</v>
       </c>
       <c r="AG28" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG28</f>
@@ -13123,15 +13125,15 @@
       </c>
       <c r="L29" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L29</f>
-        <v>6.9613664091093952</v>
+        <v>6.9176875957120982</v>
       </c>
       <c r="M29" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M29</f>
-        <v>9016.3333333333321</v>
+        <v>9073.2631578947367</v>
       </c>
       <c r="N29" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N29</f>
-        <v>-3294.4999999999991</v>
+        <v>-3333.3157894736842</v>
       </c>
       <c r="O29" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O29</f>
@@ -13183,27 +13185,27 @@
       </c>
       <c r="AA29" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA29</f>
-        <v>4098.333333333333</v>
+        <v>4124.21052631579</v>
       </c>
       <c r="AB29" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB29</f>
-        <v>11.109394062627084</v>
+        <v>11.039688616641142</v>
       </c>
       <c r="AC29" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC29</f>
-        <v>1.1109394062627085</v>
+        <v>1.1039688616641141</v>
       </c>
       <c r="AD29" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD29</f>
-        <v>454.66666666666697</v>
+        <v>428.78947368420995</v>
       </c>
       <c r="AE29" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE29</f>
-        <v>2049.1666666666665</v>
+        <v>2062.105263157895</v>
       </c>
       <c r="AF29" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF29</f>
-        <v>1594.4999999999995</v>
+        <v>1633.3157894736851</v>
       </c>
       <c r="AG29" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG29</f>
@@ -13251,15 +13253,15 @@
       </c>
       <c r="L30" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L30</f>
-        <v>7.1653208669783242</v>
+        <v>7.1837997847147461</v>
       </c>
       <c r="M30" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M30</f>
-        <v>8627.6666666666679</v>
+        <v>8605.4736842105267</v>
       </c>
       <c r="N30" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N30</f>
-        <v>-3072.5000000000009</v>
+        <v>-3057.3684210526317</v>
       </c>
       <c r="O30" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O30</f>
@@ -13311,27 +13313,27 @@
       </c>
       <c r="AA30" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA30</f>
-        <v>3921.666666666667</v>
+        <v>3911.5789473684208</v>
       </c>
       <c r="AB30" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB30</f>
-        <v>15.371015724606885</v>
+        <v>15.410656620021529</v>
       </c>
       <c r="AC30" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC30</f>
-        <v>1.5371015724606885</v>
+        <v>1.541065662002153</v>
       </c>
       <c r="AD30" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD30</f>
-        <v>2106.333333333333</v>
+        <v>2116.4210526315792</v>
       </c>
       <c r="AE30" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE30</f>
-        <v>1960.8333333333335</v>
+        <v>1955.7894736842104</v>
       </c>
       <c r="AF30" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF30</f>
-        <v>-145.49999999999955</v>
+        <v>-160.63157894736878</v>
       </c>
       <c r="AG30" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG30</f>
@@ -13439,27 +13441,27 @@
       </c>
       <c r="AA31" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA31</f>
-        <v>2288.8888888888887</v>
+        <v>2312.6315789473683</v>
       </c>
       <c r="AB31" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB31</f>
-        <v>5.9898058252427191</v>
+        <v>5.9283113336367776</v>
       </c>
       <c r="AC31" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC31</f>
-        <v>0.59898058252427189</v>
+        <v>0.59283113336367776</v>
       </c>
       <c r="AD31" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD31</f>
-        <v>-917.88888888888869</v>
+        <v>-941.63157894736833</v>
       </c>
       <c r="AE31" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE31</f>
-        <v>1144.4444444444443</v>
+        <v>1156.3157894736842</v>
       </c>
       <c r="AF31" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF31</f>
-        <v>2062.333333333333</v>
+        <v>2097.9473684210525</v>
       </c>
       <c r="AG31" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG31</f>
@@ -13567,27 +13569,27 @@
       </c>
       <c r="AA32" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA32</f>
-        <v>1353.3333333333335</v>
+        <v>1350.5263157894738</v>
       </c>
       <c r="AB32" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB32</f>
-        <v>7.2413793103448274</v>
+        <v>7.2564302416212003</v>
       </c>
       <c r="AC32" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC32</f>
-        <v>0.72413793103448265</v>
+        <v>0.72564302416212001</v>
       </c>
       <c r="AD32" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD32</f>
-        <v>-373.33333333333348</v>
+        <v>-370.52631578947376</v>
       </c>
       <c r="AE32" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE32</f>
-        <v>676.66666666666674</v>
+        <v>675.26315789473688</v>
       </c>
       <c r="AF32" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF32</f>
-        <v>1050.0000000000002</v>
+        <v>1045.7894736842106</v>
       </c>
       <c r="AG32" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG32</f>
@@ -13695,27 +13697,27 @@
       </c>
       <c r="AA33" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA33</f>
-        <v>5106.666666666667</v>
+        <v>5045.78947368421</v>
       </c>
       <c r="AB33" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB33</f>
-        <v>6.4660574412532634</v>
+        <v>6.5440700949202055</v>
       </c>
       <c r="AC33" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC33</f>
-        <v>0.64660574412532634</v>
+        <v>0.65440700949202046</v>
       </c>
       <c r="AD33" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD33</f>
-        <v>-1804.666666666667</v>
+        <v>-1743.78947368421</v>
       </c>
       <c r="AE33" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE33</f>
-        <v>2553.3333333333335</v>
+        <v>2522.894736842105</v>
       </c>
       <c r="AF33" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF33</f>
-        <v>4358</v>
+        <v>4266.6842105263149</v>
       </c>
       <c r="AG33" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG33</f>
@@ -13823,27 +13825,27 @@
       </c>
       <c r="AA34" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA34</f>
-        <v>8115.5555555555557</v>
+        <v>7976.3157894736842</v>
       </c>
       <c r="AB34" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB34</f>
-        <v>7.7714950711938666</v>
+        <v>7.9071593533487299</v>
       </c>
       <c r="AC34" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC34</f>
-        <v>0.77714950711938657</v>
+        <v>0.79071593533487294</v>
       </c>
       <c r="AD34" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD34</f>
-        <v>-1808.5555555555557</v>
+        <v>-1669.3157894736842</v>
       </c>
       <c r="AE34" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE34</f>
-        <v>4057.7777777777778</v>
+        <v>3988.1578947368421</v>
       </c>
       <c r="AF34" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF34</f>
-        <v>5866.3333333333339</v>
+        <v>5657.4736842105267</v>
       </c>
       <c r="AG34" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG34</f>
@@ -13951,7 +13953,7 @@
       </c>
       <c r="AA35" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA35</f>
-        <v>696.66666666666674</v>
+        <v>670.52631578947376</v>
       </c>
       <c r="AB35" s="34">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB35</f>
@@ -13963,15 +13965,15 @@
       </c>
       <c r="AD35" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD35</f>
-        <v>-696.66666666666674</v>
+        <v>-670.52631578947376</v>
       </c>
       <c r="AE35" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE35</f>
-        <v>348.33333333333337</v>
+        <v>335.26315789473688</v>
       </c>
       <c r="AF35" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF35</f>
-        <v>1045</v>
+        <v>1005.7894736842106</v>
       </c>
       <c r="AG35" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG35</f>
@@ -14079,27 +14081,27 @@
       </c>
       <c r="AA36" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA36</f>
-        <v>7091.6666666666661</v>
+        <v>7127.894736842105</v>
       </c>
       <c r="AB36" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB36</f>
-        <v>0.76568742655699185</v>
+        <v>0.76179576164808394</v>
       </c>
       <c r="AC36" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC36</f>
-        <v>7.6568742655699185E-2</v>
+        <v>7.6179576164808388E-2</v>
       </c>
       <c r="AD36" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD36</f>
-        <v>-6548.6666666666661</v>
+        <v>-6584.894736842105</v>
       </c>
       <c r="AE36" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE36</f>
-        <v>3545.833333333333</v>
+        <v>3563.9473684210525</v>
       </c>
       <c r="AF36" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF36</f>
-        <v>10094.5</v>
+        <v>10148.842105263157</v>
       </c>
       <c r="AG36" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG36</f>
@@ -14207,27 +14209,27 @@
       </c>
       <c r="AA37" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA37</f>
-        <v>11621.666666666668</v>
+        <v>11818.42105263158</v>
       </c>
       <c r="AB37" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB37</f>
-        <v>8.7491753907930576</v>
+        <v>8.6035181474059232</v>
       </c>
       <c r="AC37" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC37</f>
-        <v>0.87491753907930581</v>
+        <v>0.86035181474059219</v>
       </c>
       <c r="AD37" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD37</f>
-        <v>-1453.6666666666679</v>
+        <v>-1650.4210526315801</v>
       </c>
       <c r="AE37" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE37</f>
-        <v>5810.8333333333339</v>
+        <v>5909.21052631579</v>
       </c>
       <c r="AF37" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF37</f>
-        <v>7264.5000000000018</v>
+        <v>7559.6315789473701</v>
       </c>
       <c r="AG37" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG37</f>
@@ -14335,27 +14337,27 @@
       </c>
       <c r="AA38" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA38</f>
-        <v>5161.1111111111113</v>
+        <v>5122.6315789473683</v>
       </c>
       <c r="AB38" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB38</f>
-        <v>19.100538213132403</v>
+        <v>19.244015206000203</v>
       </c>
       <c r="AC38" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC38</f>
-        <v>1.9100538213132399</v>
+        <v>1.9244015206000207</v>
       </c>
       <c r="AD38" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD38</f>
-        <v>4696.8888888888887</v>
+        <v>4735.3684210526317</v>
       </c>
       <c r="AE38" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE38</f>
-        <v>2580.5555555555557</v>
+        <v>2561.3157894736842</v>
       </c>
       <c r="AF38" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF38</f>
-        <v>-2116.333333333333</v>
+        <v>-2174.0526315789475</v>
       </c>
       <c r="AG38" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG38</f>
@@ -14463,27 +14465,27 @@
       </c>
       <c r="AA39" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA39</f>
-        <v>3957.2222222222222</v>
+        <v>3974.2105263157896</v>
       </c>
       <c r="AB39" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB39</f>
-        <v>4.9681314053067531</v>
+        <v>4.9468944510660835</v>
       </c>
       <c r="AC39" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC39</f>
-        <v>0.49681314053067527</v>
+        <v>0.49468944510660839</v>
       </c>
       <c r="AD39" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD39</f>
-        <v>-1991.2222222222222</v>
+        <v>-2008.2105263157896</v>
       </c>
       <c r="AE39" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE39</f>
-        <v>1978.6111111111111</v>
+        <v>1987.1052631578948</v>
       </c>
       <c r="AF39" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF39</f>
-        <v>3969.833333333333</v>
+        <v>3995.3157894736842</v>
       </c>
       <c r="AG39" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG39</f>
@@ -14591,27 +14593,27 @@
       </c>
       <c r="AA40" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA40</f>
-        <v>677.22222222222229</v>
+        <v>734.73684210526312</v>
       </c>
       <c r="AB40" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB40</f>
-        <v>67.127153404429848</v>
+        <v>61.872492836676216</v>
       </c>
       <c r="AC40" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC40</f>
-        <v>6.7127153404429851</v>
+        <v>6.1872492836676223</v>
       </c>
       <c r="AD40" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD40</f>
-        <v>3868.7777777777778</v>
+        <v>3811.2631578947367</v>
       </c>
       <c r="AE40" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE40</f>
-        <v>338.61111111111114</v>
+        <v>367.36842105263156</v>
       </c>
       <c r="AF40" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF40</f>
-        <v>-3530.1666666666665</v>
+        <v>-3443.894736842105</v>
       </c>
       <c r="AG40" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG40</f>
@@ -14975,27 +14977,27 @@
       </c>
       <c r="AA43" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA43</f>
-        <v>1343.8888888888889</v>
+        <v>1321.578947368421</v>
       </c>
       <c r="AB43" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB43</f>
-        <v>4.9185613890037203</v>
+        <v>5.0015929908403027</v>
       </c>
       <c r="AC43" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC43</f>
-        <v>0.49185613890037205</v>
+        <v>0.50015929908403023</v>
       </c>
       <c r="AD43" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD43</f>
-        <v>-682.88888888888891</v>
+        <v>-660.57894736842104</v>
       </c>
       <c r="AE43" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE43</f>
-        <v>671.94444444444446</v>
+        <v>660.78947368421052</v>
       </c>
       <c r="AF43" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF43</f>
-        <v>1354.8333333333335</v>
+        <v>1321.3684210526317</v>
       </c>
       <c r="AG43" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG43</f>
@@ -15103,27 +15105,27 @@
       </c>
       <c r="AA44" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA44</f>
-        <v>6372.2222222222217</v>
+        <v>6458.4210526315792</v>
       </c>
       <c r="AB44" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB44</f>
-        <v>1.7811682650392329</v>
+        <v>1.7573954852905223</v>
       </c>
       <c r="AC44" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC44</f>
-        <v>0.1781168265039233</v>
+        <v>0.17573954852905224</v>
       </c>
       <c r="AD44" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD44</f>
-        <v>-5237.2222222222217</v>
+        <v>-5323.4210526315792</v>
       </c>
       <c r="AE44" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE44</f>
-        <v>3186.1111111111109</v>
+        <v>3229.2105263157896</v>
       </c>
       <c r="AF44" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF44</f>
-        <v>8423.3333333333321</v>
+        <v>8552.6315789473683</v>
       </c>
       <c r="AG44" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG44</f>
@@ -15231,27 +15233,27 @@
       </c>
       <c r="AA45" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA45</f>
-        <v>6313.8888888888887</v>
+        <v>6298.4210526315792</v>
       </c>
       <c r="AB45" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB45</f>
-        <v>6.5759788825340957</v>
+        <v>6.5921283529706693</v>
       </c>
       <c r="AC45" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC45</f>
-        <v>0.65759788825340959</v>
+        <v>0.65921283529706687</v>
       </c>
       <c r="AD45" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD45</f>
-        <v>-2161.8888888888887</v>
+        <v>-2146.4210526315792</v>
       </c>
       <c r="AE45" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE45</f>
-        <v>3156.9444444444443</v>
+        <v>3149.2105263157896</v>
       </c>
       <c r="AF45" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF45</f>
-        <v>5318.833333333333</v>
+        <v>5295.6315789473683</v>
       </c>
       <c r="AG45" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG45</f>
@@ -15359,27 +15361,27 @@
       </c>
       <c r="AA46" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA46</f>
-        <v>8413.3333333333339</v>
+        <v>8365.2631578947367</v>
       </c>
       <c r="AB46" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB46</f>
-        <v>10.164817749603802</v>
+        <v>10.223228891405562</v>
       </c>
       <c r="AC46" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC46</f>
-        <v>1.0164817749603803</v>
+        <v>1.0223228891405562</v>
       </c>
       <c r="AD46" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD46</f>
-        <v>138.66666666666606</v>
+        <v>186.73684210526335</v>
       </c>
       <c r="AE46" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE46</f>
-        <v>4206.666666666667</v>
+        <v>4182.6315789473683</v>
       </c>
       <c r="AF46" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF46</f>
-        <v>4068.0000000000009</v>
+        <v>3995.894736842105</v>
       </c>
       <c r="AG46" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG46</f>
@@ -15487,27 +15489,27 @@
       </c>
       <c r="AA47" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA47</f>
-        <v>5701.6666666666661</v>
+        <v>5688.4210526315792</v>
       </c>
       <c r="AB47" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB47</f>
-        <v>11.808827828120434</v>
+        <v>11.836324944485566</v>
       </c>
       <c r="AC47" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC47</f>
-        <v>1.1808827828120434</v>
+        <v>1.1836324944485566</v>
       </c>
       <c r="AD47" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD47</f>
-        <v>1031.3333333333339</v>
+        <v>1044.5789473684208</v>
       </c>
       <c r="AE47" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE47</f>
-        <v>2850.833333333333</v>
+        <v>2844.2105263157896</v>
       </c>
       <c r="AF47" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF47</f>
-        <v>1819.4999999999991</v>
+        <v>1799.6315789473688</v>
       </c>
       <c r="AG47" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG47</f>
@@ -15615,27 +15617,27 @@
       </c>
       <c r="AA48" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA48</f>
-        <v>24.444444444444446</v>
+        <v>24.736842105263158</v>
       </c>
       <c r="AB48" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB48</f>
-        <v>2138.3181818181815</v>
+        <v>2113.0425531914893</v>
       </c>
       <c r="AC48" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC48</f>
-        <v>213.83181818181816</v>
+        <v>211.30425531914895</v>
       </c>
       <c r="AD48" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD48</f>
-        <v>5202.5555555555557</v>
+        <v>5202.2631578947367</v>
       </c>
       <c r="AE48" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE48</f>
-        <v>12.222222222222223</v>
+        <v>12.368421052631579</v>
       </c>
       <c r="AF48" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF48</f>
-        <v>-5190.333333333333</v>
+        <v>-5189.894736842105</v>
       </c>
       <c r="AG48" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG48</f>
@@ -15871,7 +15873,7 @@
       </c>
       <c r="AA50" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA50</f>
-        <v>575</v>
+        <v>567.89473684210532</v>
       </c>
       <c r="AB50" s="25">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB50</f>
@@ -15883,15 +15885,15 @@
       </c>
       <c r="AD50" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD50</f>
-        <v>-564</v>
+        <v>-556.89473684210532</v>
       </c>
       <c r="AE50" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE50</f>
-        <v>287.5</v>
+        <v>283.94736842105266</v>
       </c>
       <c r="AF50" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF50</f>
-        <v>851.5</v>
+        <v>840.84210526315792</v>
       </c>
       <c r="AG50" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG50</f>
@@ -15999,27 +16001,27 @@
       </c>
       <c r="AA51" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA51</f>
-        <v>5</v>
+        <v>4.7368421052631575</v>
       </c>
       <c r="AB51" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB51</f>
-        <v>86</v>
+        <v>90.777777777777786</v>
       </c>
       <c r="AC51" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC51</f>
-        <v>8.6</v>
+        <v>9.0777777777777793</v>
       </c>
       <c r="AD51" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD51</f>
-        <v>38</v>
+        <v>38.263157894736842</v>
       </c>
       <c r="AE51" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE51</f>
-        <v>2.5</v>
+        <v>2.3684210526315788</v>
       </c>
       <c r="AF51" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF51</f>
-        <v>-35.5</v>
+        <v>-35.89473684210526</v>
       </c>
       <c r="AG51" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG51</f>
@@ -16255,27 +16257,27 @@
       </c>
       <c r="AA53" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA53</f>
-        <v>5255.5555555555557</v>
+        <v>5240.5263157894742</v>
       </c>
       <c r="AB53" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB53</f>
-        <v>7.6109936575052854E-3</v>
+        <v>7.6328211308627093E-3</v>
       </c>
       <c r="AC53" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC53</f>
-        <v>7.610993657505285E-4</v>
+        <v>7.6328211308627093E-4</v>
       </c>
       <c r="AD53" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD53</f>
-        <v>-5251.5555555555557</v>
+        <v>-5236.5263157894742</v>
       </c>
       <c r="AE53" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE53</f>
-        <v>2627.7777777777778</v>
+        <v>2620.2631578947371</v>
       </c>
       <c r="AF53" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF53</f>
-        <v>7879.3333333333339</v>
+        <v>7856.7894736842118</v>
       </c>
       <c r="AG53" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG53</f>
@@ -16383,27 +16385,27 @@
       </c>
       <c r="AA54" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA54</f>
-        <v>380.55555555555554</v>
+        <v>590.52631578947376</v>
       </c>
       <c r="AB54" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB54</f>
-        <v>593.15912408759118</v>
+        <v>382.25222816399281</v>
       </c>
       <c r="AC54" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC54</f>
-        <v>59.315912408759125</v>
+        <v>38.225222816399281</v>
       </c>
       <c r="AD54" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD54</f>
-        <v>22192.444444444445</v>
+        <v>21982.473684210527</v>
       </c>
       <c r="AE54" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE54</f>
-        <v>190.27777777777777</v>
+        <v>295.26315789473688</v>
       </c>
       <c r="AF54" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF54</f>
-        <v>-22002.166666666668</v>
+        <v>-21687.21052631579</v>
       </c>
       <c r="AG54" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG54</f>
@@ -16511,27 +16513,27 @@
       </c>
       <c r="AA55" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA55</f>
-        <v>3025.5555555555557</v>
+        <v>3006.3157894736842</v>
       </c>
       <c r="AB55" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB55</f>
-        <v>96.607051046639739</v>
+        <v>97.225315126050418</v>
       </c>
       <c r="AC55" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC55</f>
-        <v>9.6607051046639736</v>
+        <v>9.7225315126050429</v>
       </c>
       <c r="AD55" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD55</f>
-        <v>26203.444444444445</v>
+        <v>26222.684210526317</v>
       </c>
       <c r="AE55" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE55</f>
-        <v>1512.7777777777778</v>
+        <v>1503.1578947368421</v>
       </c>
       <c r="AF55" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF55</f>
-        <v>-24690.666666666668</v>
+        <v>-24719.526315789473</v>
       </c>
       <c r="AG55" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG55</f>
@@ -16639,27 +16641,27 @@
       </c>
       <c r="AA56" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA56</f>
-        <v>5395.5555555555557</v>
+        <v>5310.5263157894742</v>
       </c>
       <c r="AB56" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB56</f>
-        <v>29.932042833607909</v>
+        <v>30.411298315163528</v>
       </c>
       <c r="AC56" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC56</f>
-        <v>2.9932042833607908</v>
+        <v>3.0411298315163524</v>
       </c>
       <c r="AD56" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD56</f>
-        <v>10754.444444444445</v>
+        <v>10839.473684210527</v>
       </c>
       <c r="AE56" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE56</f>
-        <v>2697.7777777777778</v>
+        <v>2655.2631578947371</v>
       </c>
       <c r="AF56" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF56</f>
-        <v>-8056.6666666666679</v>
+        <v>-8184.21052631579</v>
       </c>
       <c r="AG56" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG56</f>
@@ -16767,27 +16769,27 @@
       </c>
       <c r="AA57" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA57</f>
-        <v>3161.666666666667</v>
+        <v>3101.0526315789475</v>
       </c>
       <c r="AB57" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB57</f>
-        <v>61.015287295730097</v>
+        <v>62.207909029192123</v>
       </c>
       <c r="AC57" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC57</f>
-        <v>6.1015287295730092</v>
+        <v>6.2207909029192123</v>
       </c>
       <c r="AD57" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD57</f>
-        <v>16129.333333333332</v>
+        <v>16189.947368421053</v>
       </c>
       <c r="AE57" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE57</f>
-        <v>1580.8333333333335</v>
+        <v>1550.5263157894738</v>
       </c>
       <c r="AF57" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF57</f>
-        <v>-14548.499999999998</v>
+        <v>-14639.42105263158</v>
       </c>
       <c r="AG57" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG57</f>
@@ -16895,27 +16897,27 @@
       </c>
       <c r="AA58" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA58</f>
-        <v>2933.8888888888891</v>
+        <v>2907.894736842105</v>
       </c>
       <c r="AB58" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB58</f>
-        <v>2.4370384396894527</v>
+        <v>2.4588235294117649</v>
       </c>
       <c r="AC58" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC58</f>
-        <v>0.24370384396894526</v>
+        <v>0.2458823529411765</v>
       </c>
       <c r="AD58" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD58</f>
-        <v>-2218.8888888888891</v>
+        <v>-2192.894736842105</v>
       </c>
       <c r="AE58" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE58</f>
-        <v>1466.9444444444446</v>
+        <v>1453.9473684210525</v>
       </c>
       <c r="AF58" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF58</f>
-        <v>3685.8333333333339</v>
+        <v>3646.8421052631575</v>
       </c>
       <c r="AG58" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG58</f>
@@ -17023,27 +17025,27 @@
       </c>
       <c r="AA59" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA59</f>
-        <v>608.33333333333337</v>
+        <v>587.36842105263156</v>
       </c>
       <c r="AB59" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB59</f>
-        <v>6.3452054794520549</v>
+        <v>6.5716845878136203</v>
       </c>
       <c r="AC59" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC59</f>
-        <v>0.6345205479452054</v>
+        <v>0.65716845878136199</v>
       </c>
       <c r="AD59" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD59</f>
-        <v>-222.33333333333337</v>
+        <v>-201.36842105263156</v>
       </c>
       <c r="AE59" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE59</f>
-        <v>304.16666666666669</v>
+        <v>293.68421052631578</v>
       </c>
       <c r="AF59" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF59</f>
-        <v>526.5</v>
+        <v>495.05263157894734</v>
       </c>
       <c r="AG59" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG59</f>
@@ -17151,27 +17153,27 @@
       </c>
       <c r="AA60" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA60</f>
-        <v>1091.6666666666667</v>
+        <v>1076.8421052631579</v>
       </c>
       <c r="AB60" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB60</f>
-        <v>2.729770992366412</v>
+        <v>2.767350928641251</v>
       </c>
       <c r="AC60" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC60</f>
-        <v>0.27297709923664121</v>
+        <v>0.27673509286412512</v>
       </c>
       <c r="AD60" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD60</f>
-        <v>-793.66666666666674</v>
+        <v>-778.84210526315792</v>
       </c>
       <c r="AE60" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE60</f>
-        <v>545.83333333333337</v>
+        <v>538.42105263157896</v>
       </c>
       <c r="AF60" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF60</f>
-        <v>1339.5</v>
+        <v>1317.2631578947369</v>
       </c>
       <c r="AG60" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG60</f>
@@ -17279,27 +17281,27 @@
       </c>
       <c r="AA61" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA61</f>
-        <v>517.77777777777783</v>
+        <v>511.0526315789474</v>
       </c>
       <c r="AB61" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB61</f>
-        <v>2.8197424892703857</v>
+        <v>2.8568486096807413</v>
       </c>
       <c r="AC61" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC61</f>
-        <v>0.2819742489270386</v>
+        <v>0.28568486096807416</v>
       </c>
       <c r="AD61" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD61</f>
-        <v>-371.77777777777783</v>
+        <v>-365.0526315789474</v>
       </c>
       <c r="AE61" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE61</f>
-        <v>258.88888888888891</v>
+        <v>255.5263157894737</v>
       </c>
       <c r="AF61" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF61</f>
-        <v>630.66666666666674</v>
+        <v>620.57894736842104</v>
       </c>
       <c r="AG61" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG61</f>
@@ -17339,7 +17341,7 @@
       </c>
       <c r="AF62" s="44">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF62</f>
-        <v>156899.66666666666</v>
+        <v>155940.89473684211</v>
       </c>
     </row>
     <row r="63" spans="2:33" x14ac:dyDescent="0.25">
@@ -17348,10 +17350,10 @@
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
-      <c r="E63" s="64" t="s">
+      <c r="E63" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="F63" s="64"/>
+      <c r="F63" s="67"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -17376,10 +17378,10 @@
       <c r="AB63" s="42"/>
     </row>
     <row r="64" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B64" s="65" t="s">
+      <c r="B64" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="65"/>
+      <c r="C64" s="63"/>
       <c r="D64" s="48">
         <f>SUM(F13:F61)</f>
         <v>144936.54999999999</v>
@@ -17524,19 +17526,19 @@
       <c r="AB67" s="42"/>
     </row>
     <row r="68" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B68" s="65" t="s">
+      <c r="B68" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="C68" s="65"/>
+      <c r="C68" s="63"/>
       <c r="D68" s="50">
         <f>SUM(Z13:Z61)</f>
         <v>421177.93000000017</v>
       </c>
-      <c r="E68" s="66">
+      <c r="E68" s="64">
         <f>D68*100/D68</f>
         <v>100</v>
       </c>
-      <c r="F68" s="66"/>
+      <c r="F68" s="64"/>
       <c r="G68" s="51"/>
       <c r="H68" s="51"/>
       <c r="I68" s="51"/>
@@ -17621,10 +17623,10 @@
       <c r="AB70" s="42"/>
     </row>
     <row r="71" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="65"/>
+      <c r="C71" s="63"/>
       <c r="D71" s="3">
         <f>SUM(E13:E61)</f>
         <v>112990</v>
@@ -17739,11 +17741,11 @@
         <f>SUM(T13:T61)</f>
         <v>36961</v>
       </c>
-      <c r="E74" s="67">
+      <c r="E74" s="62">
         <f>D74*100/D75</f>
         <v>11.039956032533535</v>
       </c>
-      <c r="F74" s="67"/>
+      <c r="F74" s="62"/>
       <c r="G74" s="56"/>
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
@@ -17768,19 +17770,19 @@
       <c r="AB74" s="42"/>
     </row>
     <row r="75" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="63"/>
       <c r="D75" s="55">
         <f>SUM(Y13:Y61)</f>
         <v>334793</v>
       </c>
-      <c r="E75" s="67">
+      <c r="E75" s="62">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="67"/>
+      <c r="F75" s="62"/>
       <c r="G75" s="56"/>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
@@ -18541,23 +18543,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="B1:Z6"/>
+    <mergeCell ref="AA1:AG6"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="E64:F64"/>
     <mergeCell ref="E66:F66"/>
     <mergeCell ref="E67:F67"/>
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="E68:F68"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="B1:Z6"/>
-    <mergeCell ref="AA1:AG6"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G61">
     <cfRule type="colorScale" priority="5">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6FA20D-EC61-4E1C-A820-0DAA49CEBE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F1F596-F236-4609-AFC9-D9E8697974F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -841,15 +841,6 @@
     <xf numFmtId="2" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -858,6 +849,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5648,7 +5648,8 @@
       <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
-      <sheetName val="Hoja1"/>
+      <sheetName val="INVENTARIO NACIONAL 31-08-26"/>
+      <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -5776,22 +5777,22 @@
             <v>13606.800000000001</v>
           </cell>
           <cell r="AA13">
-            <v>11712.105263157893</v>
+            <v>11472.5</v>
           </cell>
           <cell r="AB13">
-            <v>8.5424437154540964</v>
+            <v>8.7208542166049252</v>
           </cell>
           <cell r="AC13">
-            <v>0.85424437154540966</v>
+            <v>0.87208542166049252</v>
           </cell>
           <cell r="AD13">
-            <v>-1707.1052631578932</v>
+            <v>-1467.5</v>
           </cell>
           <cell r="AE13">
-            <v>5856.0526315789466</v>
+            <v>5736.25</v>
           </cell>
           <cell r="AF13">
-            <v>7563.1578947368398</v>
+            <v>7203.75</v>
           </cell>
           <cell r="AG13">
             <v>125.0625</v>
@@ -5868,22 +5869,22 @@
             <v>888.81000000000006</v>
           </cell>
           <cell r="AA14">
-            <v>722.1052631578948</v>
+            <v>750.5</v>
           </cell>
           <cell r="AB14">
-            <v>7.7412536443148685</v>
+            <v>7.4483677548301133</v>
           </cell>
           <cell r="AC14">
-            <v>0.77412536443148683</v>
+            <v>0.7448367754830113</v>
           </cell>
           <cell r="AD14">
-            <v>-163.1052631578948</v>
+            <v>-191.5</v>
           </cell>
           <cell r="AE14">
-            <v>361.0526315789474</v>
+            <v>375.25</v>
           </cell>
           <cell r="AF14">
-            <v>524.1578947368422</v>
+            <v>566.75</v>
           </cell>
           <cell r="AG14">
             <v>6.9874999999999998</v>
@@ -5960,22 +5961,22 @@
             <v>6966.9599999999991</v>
           </cell>
           <cell r="AA15">
-            <v>4932.6315789473683</v>
+            <v>4851.5</v>
           </cell>
           <cell r="AB15">
-            <v>6.9577464788732399</v>
+            <v>7.0741007935689995</v>
           </cell>
           <cell r="AC15">
-            <v>0.6957746478873239</v>
+            <v>0.70741007935689992</v>
           </cell>
           <cell r="AD15">
-            <v>-1500.6315789473683</v>
+            <v>-1419.5</v>
           </cell>
           <cell r="AE15">
-            <v>2466.3157894736842</v>
+            <v>2425.75</v>
           </cell>
           <cell r="AF15">
-            <v>3966.9473684210525</v>
+            <v>3845.25</v>
           </cell>
           <cell r="AG15">
             <v>57.2</v>
@@ -6052,22 +6053,22 @@
             <v>743.66</v>
           </cell>
           <cell r="AA16">
-            <v>872.1052631578948</v>
+            <v>882.5</v>
           </cell>
           <cell r="AB16">
-            <v>2.3621001810500903</v>
+            <v>2.3342776203966005</v>
           </cell>
           <cell r="AC16">
-            <v>0.23621001810500902</v>
+            <v>0.23342776203966006</v>
           </cell>
           <cell r="AD16">
-            <v>-666.1052631578948</v>
+            <v>-676.5</v>
           </cell>
           <cell r="AE16">
-            <v>436.0526315789474</v>
+            <v>441.25</v>
           </cell>
           <cell r="AF16">
-            <v>1102.1578947368421</v>
+            <v>1117.75</v>
           </cell>
           <cell r="AG16">
             <v>7.3571428571428568</v>
@@ -6144,22 +6145,22 @@
             <v>1861.36</v>
           </cell>
           <cell r="AA17">
-            <v>115.26315789473685</v>
+            <v>122</v>
           </cell>
           <cell r="AB17">
-            <v>18.392694063926939</v>
+            <v>17.377049180327869</v>
           </cell>
           <cell r="AC17">
-            <v>1.839269406392694</v>
+            <v>1.7377049180327868</v>
           </cell>
           <cell r="AD17">
-            <v>96.73684210526315</v>
+            <v>90</v>
           </cell>
           <cell r="AE17">
-            <v>57.631578947368425</v>
+            <v>61</v>
           </cell>
           <cell r="AF17">
-            <v>-39.105263157894726</v>
+            <v>-29</v>
           </cell>
           <cell r="AG17">
             <v>17.666666666666668</v>
@@ -6236,22 +6237,22 @@
             <v>5277.51</v>
           </cell>
           <cell r="AA18">
-            <v>14376.315789473683</v>
+            <v>14153</v>
           </cell>
           <cell r="AB18">
-            <v>5.8269449020684609</v>
+            <v>5.9188864551685159</v>
           </cell>
           <cell r="AC18">
-            <v>0.58269449020684605</v>
+            <v>0.5918886455168515</v>
           </cell>
           <cell r="AD18">
-            <v>-5999.3157894736833</v>
+            <v>-5776</v>
           </cell>
           <cell r="AE18">
-            <v>7188.1578947368416</v>
+            <v>7076.5</v>
           </cell>
           <cell r="AF18">
-            <v>13187.473684210525</v>
+            <v>12852.5</v>
           </cell>
           <cell r="AG18">
             <v>139.61666666666667</v>
@@ -6328,22 +6329,22 @@
             <v>949.41</v>
           </cell>
           <cell r="AA19">
-            <v>1421.578947368421</v>
+            <v>1398.5</v>
           </cell>
           <cell r="AB19">
-            <v>10.600888559792669</v>
+            <v>10.775831247765463</v>
           </cell>
           <cell r="AC19">
-            <v>1.0600888559792669</v>
+            <v>1.0775831247765464</v>
           </cell>
           <cell r="AD19">
-            <v>85.421052631578959</v>
+            <v>108.5</v>
           </cell>
           <cell r="AE19">
-            <v>710.78947368421052</v>
+            <v>699.25</v>
           </cell>
           <cell r="AF19">
-            <v>625.36842105263156</v>
+            <v>590.75</v>
           </cell>
           <cell r="AG19">
             <v>25.116666666666667</v>
@@ -6420,22 +6421,22 @@
             <v>2498.58</v>
           </cell>
           <cell r="AA20">
-            <v>3270.5263157894733</v>
+            <v>3218.5</v>
           </cell>
           <cell r="AB20">
-            <v>12.12648857418732</v>
+            <v>12.322510486251359</v>
           </cell>
           <cell r="AC20">
-            <v>1.212648857418732</v>
+            <v>1.2322510486251359</v>
           </cell>
           <cell r="AD20">
-            <v>695.4736842105267</v>
+            <v>747.5</v>
           </cell>
           <cell r="AE20">
-            <v>1635.2631578947367</v>
+            <v>1609.25</v>
           </cell>
           <cell r="AF20">
-            <v>939.78947368420995</v>
+            <v>861.75</v>
           </cell>
           <cell r="AG20">
             <v>66.099999999999994</v>
@@ -6512,22 +6513,22 @@
             <v>8325.42</v>
           </cell>
           <cell r="AA21">
-            <v>7474.7368421052633</v>
+            <v>7476</v>
           </cell>
           <cell r="AB21">
-            <v>10.2184199408534</v>
+            <v>10.21669341894061</v>
           </cell>
           <cell r="AC21">
-            <v>1.02184199408534</v>
+            <v>1.021669341894061</v>
           </cell>
           <cell r="AD21">
-            <v>163.26315789473665</v>
+            <v>162</v>
           </cell>
           <cell r="AE21">
-            <v>3737.3684210526317</v>
+            <v>3738</v>
           </cell>
           <cell r="AF21">
-            <v>3574.105263157895</v>
+            <v>3576</v>
           </cell>
           <cell r="AG21">
             <v>141.44444444444446</v>
@@ -6604,22 +6605,22 @@
             <v>4099.4900000000007</v>
           </cell>
           <cell r="AA22">
-            <v>3484.2105263157896</v>
+            <v>3506.5</v>
           </cell>
           <cell r="AB22">
-            <v>10.794410876132931</v>
+            <v>10.725794952231571</v>
           </cell>
           <cell r="AC22">
-            <v>1.0794410876132929</v>
+            <v>1.0725794952231571</v>
           </cell>
           <cell r="AD22">
-            <v>276.78947368421041</v>
+            <v>254.5</v>
           </cell>
           <cell r="AE22">
-            <v>1742.1052631578948</v>
+            <v>1753.25</v>
           </cell>
           <cell r="AF22">
-            <v>1465.3157894736844</v>
+            <v>1498.75</v>
           </cell>
           <cell r="AG22">
             <v>69.648148148148152</v>
@@ -6696,22 +6697,22 @@
             <v>38473.719999999994</v>
           </cell>
           <cell r="AA23">
-            <v>34597.368421052633</v>
+            <v>34029.5</v>
           </cell>
           <cell r="AB23">
-            <v>9.5865672777059405</v>
+            <v>9.7465434402503721</v>
           </cell>
           <cell r="AC23">
-            <v>0.95865672777059396</v>
+            <v>0.97465434402503714</v>
           </cell>
           <cell r="AD23">
-            <v>-1430.3684210526335</v>
+            <v>-862.5</v>
           </cell>
           <cell r="AE23">
-            <v>17298.684210526317</v>
+            <v>17014.75</v>
           </cell>
           <cell r="AF23">
-            <v>18729.05263157895</v>
+            <v>17877.25</v>
           </cell>
           <cell r="AG23">
             <v>614.2037037037037</v>
@@ -6788,22 +6789,22 @@
             <v>29054.519999999997</v>
           </cell>
           <cell r="AA24">
-            <v>22536.315789473683</v>
+            <v>22193</v>
           </cell>
           <cell r="AB24">
-            <v>11.114061514748126</v>
+            <v>11.285991078267921</v>
           </cell>
           <cell r="AC24">
-            <v>1.1114061514748126</v>
+            <v>1.1285991078267923</v>
           </cell>
           <cell r="AD24">
-            <v>2510.6842105263167</v>
+            <v>2854</v>
           </cell>
           <cell r="AE24">
-            <v>11268.157894736842</v>
+            <v>11096.5</v>
           </cell>
           <cell r="AF24">
-            <v>8757.4736842105249</v>
+            <v>8242.5</v>
           </cell>
           <cell r="AG24">
             <v>463.83333333333331</v>
@@ -6880,22 +6881,22 @@
             <v>30040.519999999997</v>
           </cell>
           <cell r="AA25">
-            <v>21916.315789473683</v>
+            <v>21481.5</v>
           </cell>
           <cell r="AB25">
-            <v>11.816310847482049</v>
+            <v>12.055489607336545</v>
           </cell>
           <cell r="AC25">
-            <v>1.181631084748205</v>
+            <v>1.2055489607336545</v>
           </cell>
           <cell r="AD25">
-            <v>3980.6842105263167</v>
+            <v>4415.5</v>
           </cell>
           <cell r="AE25">
-            <v>10958.157894736842</v>
+            <v>10740.75</v>
           </cell>
           <cell r="AF25">
-            <v>6977.4736842105249</v>
+            <v>6325.25</v>
           </cell>
           <cell r="AG25">
             <v>479.57407407407408</v>
@@ -6972,22 +6973,22 @@
             <v>34369.64</v>
           </cell>
           <cell r="AA26">
-            <v>26250</v>
+            <v>25732.5</v>
           </cell>
           <cell r="AB26">
-            <v>11.287238095238095</v>
+            <v>11.514232973865735</v>
           </cell>
           <cell r="AC26">
-            <v>1.1287238095238095</v>
+            <v>1.1514232973865735</v>
           </cell>
           <cell r="AD26">
-            <v>3379</v>
+            <v>3896.5</v>
           </cell>
           <cell r="AE26">
-            <v>13125</v>
+            <v>12866.25</v>
           </cell>
           <cell r="AF26">
-            <v>9746</v>
+            <v>8969.75</v>
           </cell>
           <cell r="AG26">
             <v>548.68518518518522</v>
@@ -7064,22 +7065,22 @@
             <v>1758.56</v>
           </cell>
           <cell r="AA27">
-            <v>150.52631578947367</v>
+            <v>97</v>
           </cell>
           <cell r="AB27">
-            <v>100.71328671328672</v>
+            <v>156.28865979381445</v>
           </cell>
           <cell r="AC27">
-            <v>10.071328671328672</v>
+            <v>15.628865979381443</v>
           </cell>
           <cell r="AD27">
-            <v>1365.4736842105262</v>
+            <v>1419</v>
           </cell>
           <cell r="AE27">
-            <v>75.263157894736835</v>
+            <v>48.5</v>
           </cell>
           <cell r="AF27">
-            <v>-1290.2105263157894</v>
+            <v>-1370.5</v>
           </cell>
           <cell r="AG27">
             <v>28.074074074074073</v>
@@ -7111,13 +7112,13 @@
             <v>3519.4399999999996</v>
           </cell>
           <cell r="L28">
-            <v>8.3015552995391708</v>
+            <v>8.2647779896485964</v>
           </cell>
           <cell r="M28">
-            <v>8040.4210526315783</v>
+            <v>8076.2000000000007</v>
           </cell>
           <cell r="N28">
-            <v>-2448.1052631578941</v>
+            <v>-2472.5</v>
           </cell>
           <cell r="O28">
             <v>251</v>
@@ -7156,22 +7157,22 @@
             <v>5583.08</v>
           </cell>
           <cell r="AA28">
-            <v>3654.7368421052629</v>
+            <v>3671</v>
           </cell>
           <cell r="AB28">
-            <v>13.169210829493089</v>
+            <v>13.11086897303187</v>
           </cell>
           <cell r="AC28">
-            <v>1.3169210829493088</v>
+            <v>1.3110868973031871</v>
           </cell>
           <cell r="AD28">
-            <v>1158.2631578947371</v>
+            <v>1142</v>
           </cell>
           <cell r="AE28">
-            <v>1827.3684210526314</v>
+            <v>1835.5</v>
           </cell>
           <cell r="AF28">
-            <v>669.10526315789434</v>
+            <v>693.5</v>
           </cell>
           <cell r="AG28">
             <v>89.129629629629633</v>
@@ -7203,13 +7204,13 @@
             <v>3309.4799999999996</v>
           </cell>
           <cell r="L29">
-            <v>6.9176875957120982</v>
+            <v>6.8796720520858452</v>
           </cell>
           <cell r="M29">
-            <v>9073.2631578947367</v>
+            <v>9123.4</v>
           </cell>
           <cell r="N29">
-            <v>-3333.3157894736842</v>
+            <v>-3367.5</v>
           </cell>
           <cell r="O29">
             <v>236</v>
@@ -7248,22 +7249,22 @@
             <v>5281.48</v>
           </cell>
           <cell r="AA29">
-            <v>4124.21052631579</v>
+            <v>4147</v>
           </cell>
           <cell r="AB29">
-            <v>11.039688616641142</v>
+            <v>10.97902097902098</v>
           </cell>
           <cell r="AC29">
-            <v>1.1039688616641141</v>
+            <v>1.0979020979020979</v>
           </cell>
           <cell r="AD29">
-            <v>428.78947368420995</v>
+            <v>406</v>
           </cell>
           <cell r="AE29">
-            <v>2062.105263157895</v>
+            <v>2073.5</v>
           </cell>
           <cell r="AF29">
-            <v>1633.3157894736851</v>
+            <v>1667.5</v>
           </cell>
           <cell r="AG29">
             <v>84.31481481481481</v>
@@ -7295,13 +7296,13 @@
             <v>3259.6</v>
           </cell>
           <cell r="L30">
-            <v>7.1837997847147461</v>
+            <v>7.3148509696733051</v>
           </cell>
           <cell r="M30">
-            <v>8605.4736842105267</v>
+            <v>8451.2999999999993</v>
           </cell>
           <cell r="N30">
-            <v>-3057.3684210526317</v>
+            <v>-2952.25</v>
           </cell>
           <cell r="O30">
             <v>236</v>
@@ -7340,22 +7341,22 @@
             <v>6992.48</v>
           </cell>
           <cell r="AA30">
-            <v>3911.5789473684208</v>
+            <v>3841.5</v>
           </cell>
           <cell r="AB30">
-            <v>15.410656620021529</v>
+            <v>15.691787062345439</v>
           </cell>
           <cell r="AC30">
-            <v>1.541065662002153</v>
+            <v>1.5691787062345437</v>
           </cell>
           <cell r="AD30">
-            <v>2116.4210526315792</v>
+            <v>2186.5</v>
           </cell>
           <cell r="AE30">
-            <v>1955.7894736842104</v>
+            <v>1920.75</v>
           </cell>
           <cell r="AF30">
-            <v>-160.63157894736878</v>
+            <v>-265.75</v>
           </cell>
           <cell r="AG30">
             <v>111.62962962962963</v>
@@ -7432,22 +7433,22 @@
             <v>5045.2800000000007</v>
           </cell>
           <cell r="AA31">
-            <v>2312.6315789473683</v>
+            <v>2327.5</v>
           </cell>
           <cell r="AB31">
-            <v>5.9283113336367776</v>
+            <v>5.8904403866809885</v>
           </cell>
           <cell r="AC31">
-            <v>0.59283113336367776</v>
+            <v>0.58904403866809885</v>
           </cell>
           <cell r="AD31">
-            <v>-941.63157894736833</v>
+            <v>-956.5</v>
           </cell>
           <cell r="AE31">
-            <v>1156.3157894736842</v>
+            <v>1163.75</v>
           </cell>
           <cell r="AF31">
-            <v>2097.9473684210525</v>
+            <v>2120.25</v>
           </cell>
           <cell r="AG31">
             <v>85.6875</v>
@@ -7524,22 +7525,22 @@
             <v>3606.4</v>
           </cell>
           <cell r="AA32">
-            <v>1350.5263157894738</v>
+            <v>1355.5</v>
           </cell>
           <cell r="AB32">
-            <v>7.2564302416212003</v>
+            <v>7.2298045001844331</v>
           </cell>
           <cell r="AC32">
-            <v>0.72564302416212001</v>
+            <v>0.72298045001844335</v>
           </cell>
           <cell r="AD32">
-            <v>-370.52631578947376</v>
+            <v>-375.5</v>
           </cell>
           <cell r="AE32">
-            <v>675.26315789473688</v>
+            <v>677.75</v>
           </cell>
           <cell r="AF32">
-            <v>1045.7894736842106</v>
+            <v>1053.25</v>
           </cell>
           <cell r="AG32">
             <v>61.25</v>
@@ -7616,22 +7617,22 @@
             <v>13703.300000000001</v>
           </cell>
           <cell r="AA33">
-            <v>5045.78947368421</v>
+            <v>4963.5</v>
           </cell>
           <cell r="AB33">
-            <v>6.5440700949202055</v>
+            <v>6.6525637151203787</v>
           </cell>
           <cell r="AC33">
-            <v>0.65440700949202046</v>
+            <v>0.66525637151203787</v>
           </cell>
           <cell r="AD33">
-            <v>-1743.78947368421</v>
+            <v>-1661.5</v>
           </cell>
           <cell r="AE33">
-            <v>2522.894736842105</v>
+            <v>2481.75</v>
           </cell>
           <cell r="AF33">
-            <v>4266.6842105263149</v>
+            <v>4143.25</v>
           </cell>
           <cell r="AG33">
             <v>206.375</v>
@@ -7708,22 +7709,22 @@
             <v>26174.050000000003</v>
           </cell>
           <cell r="AA34">
-            <v>7976.3157894736842</v>
+            <v>7850</v>
           </cell>
           <cell r="AB34">
-            <v>7.9071593533487299</v>
+            <v>8.0343949044585994</v>
           </cell>
           <cell r="AC34">
-            <v>0.79071593533487294</v>
+            <v>0.80343949044585983</v>
           </cell>
           <cell r="AD34">
-            <v>-1669.3157894736842</v>
+            <v>-1543</v>
           </cell>
           <cell r="AE34">
-            <v>3988.1578947368421</v>
+            <v>3925</v>
           </cell>
           <cell r="AF34">
-            <v>5657.4736842105267</v>
+            <v>5468</v>
           </cell>
           <cell r="AG34">
             <v>394.1875</v>
@@ -7800,7 +7801,7 @@
             <v>0</v>
           </cell>
           <cell r="AA35">
-            <v>670.52631578947376</v>
+            <v>637</v>
           </cell>
           <cell r="AB35">
             <v>0</v>
@@ -7809,13 +7810,13 @@
             <v>0</v>
           </cell>
           <cell r="AD35">
-            <v>-670.52631578947376</v>
+            <v>-637</v>
           </cell>
           <cell r="AE35">
-            <v>335.26315789473688</v>
+            <v>318.5</v>
           </cell>
           <cell r="AF35">
-            <v>1005.7894736842106</v>
+            <v>955.5</v>
           </cell>
           <cell r="AG35">
             <v>0</v>
@@ -7892,22 +7893,22 @@
             <v>2253.4500000000003</v>
           </cell>
           <cell r="AA36">
-            <v>7127.894736842105</v>
+            <v>7096.5</v>
           </cell>
           <cell r="AB36">
-            <v>0.76179576164808394</v>
+            <v>0.76516592686535623</v>
           </cell>
           <cell r="AC36">
-            <v>7.6179576164808388E-2</v>
+            <v>7.6516592686535614E-2</v>
           </cell>
           <cell r="AD36">
-            <v>-6584.894736842105</v>
+            <v>-6553.5</v>
           </cell>
           <cell r="AE36">
-            <v>3563.9473684210525</v>
+            <v>3548.25</v>
           </cell>
           <cell r="AF36">
-            <v>10148.842105263157</v>
+            <v>10101.75</v>
           </cell>
           <cell r="AG36">
             <v>33.9375</v>
@@ -7984,22 +7985,22 @@
             <v>16573.84</v>
           </cell>
           <cell r="AA37">
-            <v>11818.42105263158</v>
+            <v>11629.5</v>
           </cell>
           <cell r="AB37">
-            <v>8.6035181474059232</v>
+            <v>8.7432821703426633</v>
           </cell>
           <cell r="AC37">
-            <v>0.86035181474059219</v>
+            <v>0.87432821703426633</v>
           </cell>
           <cell r="AD37">
-            <v>-1650.4210526315801</v>
+            <v>-1461.5</v>
           </cell>
           <cell r="AE37">
-            <v>5909.21052631579</v>
+            <v>5814.75</v>
           </cell>
           <cell r="AF37">
-            <v>7559.6315789473701</v>
+            <v>7276.25</v>
           </cell>
           <cell r="AG37">
             <v>188.2962962962963</v>
@@ -8076,22 +8077,22 @@
             <v>16068.539999999999</v>
           </cell>
           <cell r="AA38">
-            <v>5122.6315789473683</v>
+            <v>5102.5</v>
           </cell>
           <cell r="AB38">
-            <v>19.244015206000203</v>
+            <v>19.319941205291524</v>
           </cell>
           <cell r="AC38">
-            <v>1.9244015206000207</v>
+            <v>1.9319941205291524</v>
           </cell>
           <cell r="AD38">
-            <v>4735.3684210526317</v>
+            <v>4755.5</v>
           </cell>
           <cell r="AE38">
-            <v>2561.3157894736842</v>
+            <v>2551.25</v>
           </cell>
           <cell r="AF38">
-            <v>-2174.0526315789475</v>
+            <v>-2204.25</v>
           </cell>
           <cell r="AG38">
             <v>182.55555555555554</v>
@@ -8168,22 +8169,22 @@
             <v>3204.58</v>
           </cell>
           <cell r="AA39">
-            <v>3974.2105263157896</v>
+            <v>4006</v>
           </cell>
           <cell r="AB39">
-            <v>4.9468944510660835</v>
+            <v>4.9076385421867199</v>
           </cell>
           <cell r="AC39">
-            <v>0.49468944510660839</v>
+            <v>0.49076385421867197</v>
           </cell>
           <cell r="AD39">
-            <v>-2008.2105263157896</v>
+            <v>-2040</v>
           </cell>
           <cell r="AE39">
-            <v>1987.1052631578948</v>
+            <v>2003</v>
           </cell>
           <cell r="AF39">
-            <v>3995.3157894736842</v>
+            <v>4043</v>
           </cell>
           <cell r="AG39">
             <v>36.407407407407405</v>
@@ -8260,22 +8261,22 @@
             <v>7409.98</v>
           </cell>
           <cell r="AA40">
-            <v>734.73684210526312</v>
+            <v>709</v>
           </cell>
           <cell r="AB40">
-            <v>61.872492836676216</v>
+            <v>64.118476727785605</v>
           </cell>
           <cell r="AC40">
-            <v>6.1872492836676223</v>
+            <v>6.4118476727785616</v>
           </cell>
           <cell r="AD40">
-            <v>3811.2631578947367</v>
+            <v>3837</v>
           </cell>
           <cell r="AE40">
-            <v>367.36842105263156</v>
+            <v>354.5</v>
           </cell>
           <cell r="AF40">
-            <v>-3443.894736842105</v>
+            <v>-3482.5</v>
           </cell>
           <cell r="AG40">
             <v>84.18518518518519</v>
@@ -8536,22 +8537,22 @@
             <v>4065.15</v>
           </cell>
           <cell r="AA43">
-            <v>1321.578947368421</v>
+            <v>1342.5</v>
           </cell>
           <cell r="AB43">
-            <v>5.0015929908403027</v>
+            <v>4.9236499068901303</v>
           </cell>
           <cell r="AC43">
-            <v>0.50015929908403023</v>
+            <v>0.49236499068901302</v>
           </cell>
           <cell r="AD43">
-            <v>-660.57894736842104</v>
+            <v>-681.5</v>
           </cell>
           <cell r="AE43">
-            <v>660.78947368421052</v>
+            <v>671.25</v>
           </cell>
           <cell r="AF43">
-            <v>1321.3684210526317</v>
+            <v>1352.75</v>
           </cell>
           <cell r="AG43">
             <v>12.24074074074074</v>
@@ -8628,22 +8629,22 @@
             <v>6980.25</v>
           </cell>
           <cell r="AA44">
-            <v>6458.4210526315792</v>
+            <v>6411</v>
           </cell>
           <cell r="AB44">
-            <v>1.7573954852905223</v>
+            <v>1.7703946342224302</v>
           </cell>
           <cell r="AC44">
-            <v>0.17573954852905224</v>
+            <v>0.17703946342224303</v>
           </cell>
           <cell r="AD44">
-            <v>-5323.4210526315792</v>
+            <v>-5276</v>
           </cell>
           <cell r="AE44">
-            <v>3229.2105263157896</v>
+            <v>3205.5</v>
           </cell>
           <cell r="AF44">
-            <v>8552.6315789473683</v>
+            <v>8481.5</v>
           </cell>
           <cell r="AG44">
             <v>21.018518518518519</v>
@@ -8720,22 +8721,22 @@
             <v>4816.32</v>
           </cell>
           <cell r="AA45">
-            <v>6298.4210526315792</v>
+            <v>6201</v>
           </cell>
           <cell r="AB45">
-            <v>6.5921283529706693</v>
+            <v>6.6956942428640538</v>
           </cell>
           <cell r="AC45">
-            <v>0.65921283529706687</v>
+            <v>0.66956942428640542</v>
           </cell>
           <cell r="AD45">
-            <v>-2146.4210526315792</v>
+            <v>-2049</v>
           </cell>
           <cell r="AE45">
-            <v>3149.2105263157896</v>
+            <v>3100.5</v>
           </cell>
           <cell r="AF45">
-            <v>5295.6315789473683</v>
+            <v>5149.5</v>
           </cell>
           <cell r="AG45">
             <v>76.888888888888886</v>
@@ -8812,22 +8813,22 @@
             <v>9920.32</v>
           </cell>
           <cell r="AA46">
-            <v>8365.2631578947367</v>
+            <v>8288.5</v>
           </cell>
           <cell r="AB46">
-            <v>10.223228891405562</v>
+            <v>10.317910357724557</v>
           </cell>
           <cell r="AC46">
-            <v>1.0223228891405562</v>
+            <v>1.0317910357724558</v>
           </cell>
           <cell r="AD46">
-            <v>186.73684210526335</v>
+            <v>263.5</v>
           </cell>
           <cell r="AE46">
-            <v>4182.6315789473683</v>
+            <v>4144.25</v>
           </cell>
           <cell r="AF46">
-            <v>3995.894736842105</v>
+            <v>3880.75</v>
           </cell>
           <cell r="AG46">
             <v>158.37037037037038</v>
@@ -8904,22 +8905,22 @@
             <v>7810.28</v>
           </cell>
           <cell r="AA47">
-            <v>5688.4210526315792</v>
+            <v>5643.5</v>
           </cell>
           <cell r="AB47">
-            <v>11.836324944485566</v>
+            <v>11.930539558784442</v>
           </cell>
           <cell r="AC47">
-            <v>1.1836324944485566</v>
+            <v>1.1930539558784443</v>
           </cell>
           <cell r="AD47">
-            <v>1044.5789473684208</v>
+            <v>1089.5</v>
           </cell>
           <cell r="AE47">
-            <v>2844.2105263157896</v>
+            <v>2821.75</v>
           </cell>
           <cell r="AF47">
-            <v>1799.6315789473688</v>
+            <v>1732.25</v>
           </cell>
           <cell r="AG47">
             <v>124.68518518518519</v>
@@ -8996,22 +8997,22 @@
             <v>6063.32</v>
           </cell>
           <cell r="AA48">
-            <v>24.736842105263158</v>
+            <v>23.5</v>
           </cell>
           <cell r="AB48">
-            <v>2113.0425531914893</v>
+            <v>2224.255319148936</v>
           </cell>
           <cell r="AC48">
-            <v>211.30425531914895</v>
+            <v>222.42553191489361</v>
           </cell>
           <cell r="AD48">
-            <v>5202.2631578947367</v>
+            <v>5203.5</v>
           </cell>
           <cell r="AE48">
-            <v>12.368421052631579</v>
+            <v>11.75</v>
           </cell>
           <cell r="AF48">
-            <v>-5189.894736842105</v>
+            <v>-5191.75</v>
           </cell>
           <cell r="AG48">
             <v>96.796296296296291</v>
@@ -9180,7 +9181,7 @@
             <v>198</v>
           </cell>
           <cell r="AA50">
-            <v>567.89473684210532</v>
+            <v>544</v>
           </cell>
           <cell r="AB50">
             <v>0</v>
@@ -9189,13 +9190,13 @@
             <v>0</v>
           </cell>
           <cell r="AD50">
-            <v>-556.89473684210532</v>
+            <v>-533</v>
           </cell>
           <cell r="AE50">
-            <v>283.94736842105266</v>
+            <v>272</v>
           </cell>
           <cell r="AF50">
-            <v>840.84210526315792</v>
+            <v>805</v>
           </cell>
           <cell r="AG50">
             <v>5.5</v>
@@ -9272,22 +9273,22 @@
             <v>49.879999999999995</v>
           </cell>
           <cell r="AA51">
-            <v>4.7368421052631575</v>
+            <v>4.5</v>
           </cell>
           <cell r="AB51">
-            <v>90.777777777777786</v>
+            <v>95.555555555555557</v>
           </cell>
           <cell r="AC51">
-            <v>9.0777777777777793</v>
+            <v>9.5555555555555554</v>
           </cell>
           <cell r="AD51">
-            <v>38.263157894736842</v>
+            <v>38.5</v>
           </cell>
           <cell r="AE51">
-            <v>2.3684210526315788</v>
+            <v>2.25</v>
           </cell>
           <cell r="AF51">
-            <v>-35.89473684210526</v>
+            <v>-36.25</v>
           </cell>
           <cell r="AG51">
             <v>1.075</v>
@@ -9456,22 +9457,22 @@
             <v>4.6399999999999997</v>
           </cell>
           <cell r="AA53">
-            <v>5240.5263157894742</v>
+            <v>5290</v>
           </cell>
           <cell r="AB53">
-            <v>7.6328211308627093E-3</v>
+            <v>7.5614366729678641E-3</v>
           </cell>
           <cell r="AC53">
-            <v>7.6328211308627093E-4</v>
+            <v>7.5614366729678643E-4</v>
           </cell>
           <cell r="AD53">
-            <v>-5236.5263157894742</v>
+            <v>-5286</v>
           </cell>
           <cell r="AE53">
-            <v>2620.2631578947371</v>
+            <v>2645</v>
           </cell>
           <cell r="AF53">
-            <v>7856.7894736842118</v>
+            <v>7931</v>
           </cell>
           <cell r="AG53">
             <v>0.1</v>
@@ -9548,22 +9549,22 @@
             <v>18284.13</v>
           </cell>
           <cell r="AA54">
-            <v>590.52631578947376</v>
+            <v>788.5</v>
           </cell>
           <cell r="AB54">
-            <v>382.25222816399281</v>
+            <v>286.27774254914397</v>
           </cell>
           <cell r="AC54">
-            <v>38.225222816399281</v>
+            <v>28.627774254914396</v>
           </cell>
           <cell r="AD54">
-            <v>21982.473684210527</v>
+            <v>21784.5</v>
           </cell>
           <cell r="AE54">
-            <v>295.26315789473688</v>
+            <v>394.25</v>
           </cell>
           <cell r="AF54">
-            <v>-21687.21052631579</v>
+            <v>-21390.25</v>
           </cell>
           <cell r="AG54">
             <v>1881.0833333333333</v>
@@ -9640,22 +9641,22 @@
             <v>23675.49</v>
           </cell>
           <cell r="AA55">
-            <v>3006.3157894736842</v>
+            <v>2964.5</v>
           </cell>
           <cell r="AB55">
-            <v>97.225315126050418</v>
+            <v>98.596727947377303</v>
           </cell>
           <cell r="AC55">
-            <v>9.7225315126050429</v>
+            <v>9.8596727947377296</v>
           </cell>
           <cell r="AD55">
-            <v>26222.684210526317</v>
+            <v>26264.5</v>
           </cell>
           <cell r="AE55">
-            <v>1503.1578947368421</v>
+            <v>1482.25</v>
           </cell>
           <cell r="AF55">
-            <v>-24719.526315789473</v>
+            <v>-24782.25</v>
           </cell>
           <cell r="AG55">
             <v>2435.75</v>
@@ -9732,22 +9733,22 @@
             <v>13081.5</v>
           </cell>
           <cell r="AA56">
-            <v>5310.5263157894742</v>
+            <v>5246</v>
           </cell>
           <cell r="AB56">
-            <v>30.411298315163528</v>
+            <v>30.785360274494852</v>
           </cell>
           <cell r="AC56">
-            <v>3.0411298315163524</v>
+            <v>3.0785360274494855</v>
           </cell>
           <cell r="AD56">
-            <v>10839.473684210527</v>
+            <v>10904</v>
           </cell>
           <cell r="AE56">
-            <v>2655.2631578947371</v>
+            <v>2623</v>
           </cell>
           <cell r="AF56">
-            <v>-8184.21052631579</v>
+            <v>-8281</v>
           </cell>
           <cell r="AG56">
             <v>1345.8333333333333</v>
@@ -9824,22 +9825,22 @@
             <v>15625.710000000001</v>
           </cell>
           <cell r="AA57">
-            <v>3101.0526315789475</v>
+            <v>3077</v>
           </cell>
           <cell r="AB57">
-            <v>62.207909029192123</v>
+            <v>62.69418264543387</v>
           </cell>
           <cell r="AC57">
-            <v>6.2207909029192123</v>
+            <v>6.2694182645433862</v>
           </cell>
           <cell r="AD57">
-            <v>16189.947368421053</v>
+            <v>16214</v>
           </cell>
           <cell r="AE57">
-            <v>1550.5263157894738</v>
+            <v>1538.5</v>
           </cell>
           <cell r="AF57">
-            <v>-14639.42105263158</v>
+            <v>-14675.5</v>
           </cell>
           <cell r="AG57">
             <v>1607.5833333333333</v>
@@ -9916,22 +9917,22 @@
             <v>1873.3000000000002</v>
           </cell>
           <cell r="AA58">
-            <v>2907.894736842105</v>
+            <v>2912</v>
           </cell>
           <cell r="AB58">
-            <v>2.4588235294117649</v>
+            <v>2.4553571428571428</v>
           </cell>
           <cell r="AC58">
-            <v>0.2458823529411765</v>
+            <v>0.24553571428571427</v>
           </cell>
           <cell r="AD58">
-            <v>-2192.894736842105</v>
+            <v>-2197</v>
           </cell>
           <cell r="AE58">
-            <v>1453.9473684210525</v>
+            <v>1456</v>
           </cell>
           <cell r="AF58">
-            <v>3646.8421052631575</v>
+            <v>3653</v>
           </cell>
           <cell r="AG58">
             <v>119.16666666666667</v>
@@ -10008,22 +10009,22 @@
             <v>1011.32</v>
           </cell>
           <cell r="AA59">
-            <v>587.36842105263156</v>
+            <v>563</v>
           </cell>
           <cell r="AB59">
-            <v>6.5716845878136203</v>
+            <v>6.8561278863232689</v>
           </cell>
           <cell r="AC59">
-            <v>0.65716845878136199</v>
+            <v>0.68561278863232678</v>
           </cell>
           <cell r="AD59">
-            <v>-201.36842105263156</v>
+            <v>-177</v>
           </cell>
           <cell r="AE59">
-            <v>293.68421052631578</v>
+            <v>281.5</v>
           </cell>
           <cell r="AF59">
-            <v>495.05263157894734</v>
+            <v>458.5</v>
           </cell>
           <cell r="AG59">
             <v>64.333333333333329</v>
@@ -10100,22 +10101,22 @@
             <v>780.76</v>
           </cell>
           <cell r="AA60">
-            <v>1076.8421052631579</v>
+            <v>1045.5</v>
           </cell>
           <cell r="AB60">
-            <v>2.767350928641251</v>
+            <v>2.8503108560497372</v>
           </cell>
           <cell r="AC60">
-            <v>0.27673509286412512</v>
+            <v>0.2850310856049737</v>
           </cell>
           <cell r="AD60">
-            <v>-778.84210526315792</v>
+            <v>-747.5</v>
           </cell>
           <cell r="AE60">
-            <v>538.42105263157896</v>
+            <v>522.75</v>
           </cell>
           <cell r="AF60">
-            <v>1317.2631578947369</v>
+            <v>1270.25</v>
           </cell>
           <cell r="AG60">
             <v>49.666666666666664</v>
@@ -10192,22 +10193,22 @@
             <v>382.52000000000004</v>
           </cell>
           <cell r="AA61">
-            <v>511.0526315789474</v>
+            <v>492</v>
           </cell>
           <cell r="AB61">
-            <v>2.8568486096807413</v>
+            <v>2.9674796747967478</v>
           </cell>
           <cell r="AC61">
-            <v>0.28568486096807416</v>
+            <v>0.2967479674796748</v>
           </cell>
           <cell r="AD61">
-            <v>-365.0526315789474</v>
+            <v>-346</v>
           </cell>
           <cell r="AE61">
-            <v>255.5263157894737</v>
+            <v>246</v>
           </cell>
           <cell r="AF61">
-            <v>620.57894736842104</v>
+            <v>592</v>
           </cell>
           <cell r="AG61">
             <v>24.333333333333332</v>
@@ -10218,7 +10219,7 @@
             <v>Units Produce</v>
           </cell>
           <cell r="AF62">
-            <v>155940.89473684211</v>
+            <v>151316.75</v>
           </cell>
         </row>
       </sheetData>
@@ -10237,6 +10238,7 @@
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
       <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10561,212 +10563,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="66" t="s">
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="66"/>
-      <c r="AC1" s="66"/>
-      <c r="AD1" s="66"/>
-      <c r="AE1" s="66"/>
-      <c r="AF1" s="66"/>
-      <c r="AG1" s="66"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="66"/>
-      <c r="AB2" s="66"/>
-      <c r="AC2" s="66"/>
-      <c r="AD2" s="66"/>
-      <c r="AE2" s="66"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
+      <c r="AD2" s="63"/>
+      <c r="AE2" s="63"/>
+      <c r="AF2" s="63"/>
+      <c r="AG2" s="63"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="66"/>
-      <c r="AB3" s="66"/>
-      <c r="AC3" s="66"/>
-      <c r="AD3" s="66"/>
-      <c r="AE3" s="66"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="62"/>
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="63"/>
+      <c r="AD3" s="63"/>
+      <c r="AE3" s="63"/>
+      <c r="AF3" s="63"/>
+      <c r="AG3" s="63"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="66"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="62"/>
+      <c r="Y4" s="62"/>
+      <c r="Z4" s="62"/>
+      <c r="AA4" s="63"/>
+      <c r="AB4" s="63"/>
+      <c r="AC4" s="63"/>
+      <c r="AD4" s="63"/>
+      <c r="AE4" s="63"/>
+      <c r="AF4" s="63"/>
+      <c r="AG4" s="63"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="66"/>
-      <c r="AB5" s="66"/>
-      <c r="AC5" s="66"/>
-      <c r="AD5" s="66"/>
-      <c r="AE5" s="66"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="62"/>
+      <c r="Z5" s="62"/>
+      <c r="AA5" s="63"/>
+      <c r="AB5" s="63"/>
+      <c r="AC5" s="63"/>
+      <c r="AD5" s="63"/>
+      <c r="AE5" s="63"/>
+      <c r="AF5" s="63"/>
+      <c r="AG5" s="63"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="66"/>
-      <c r="AB6" s="66"/>
-      <c r="AC6" s="66"/>
-      <c r="AD6" s="66"/>
-      <c r="AE6" s="66"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="62"/>
+      <c r="X6" s="62"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="63"/>
+      <c r="AB6" s="63"/>
+      <c r="AC6" s="63"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="63"/>
+      <c r="AG6" s="63"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
@@ -11137,27 +11139,27 @@
       </c>
       <c r="AA13" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA13</f>
-        <v>11712.105263157893</v>
+        <v>11472.5</v>
       </c>
       <c r="AB13" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB13</f>
-        <v>8.5424437154540964</v>
+        <v>8.7208542166049252</v>
       </c>
       <c r="AC13" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC13</f>
-        <v>0.85424437154540966</v>
+        <v>0.87208542166049252</v>
       </c>
       <c r="AD13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD13</f>
-        <v>-1707.1052631578932</v>
+        <v>-1467.5</v>
       </c>
       <c r="AE13" s="27">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE13</f>
-        <v>5856.0526315789466</v>
+        <v>5736.25</v>
       </c>
       <c r="AF13" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF13</f>
-        <v>7563.1578947368398</v>
+        <v>7203.75</v>
       </c>
       <c r="AG13" s="27">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG13</f>
@@ -11265,27 +11267,27 @@
       </c>
       <c r="AA14" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA14</f>
-        <v>722.1052631578948</v>
+        <v>750.5</v>
       </c>
       <c r="AB14" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB14</f>
-        <v>7.7412536443148685</v>
+        <v>7.4483677548301133</v>
       </c>
       <c r="AC14" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC14</f>
-        <v>0.77412536443148683</v>
+        <v>0.7448367754830113</v>
       </c>
       <c r="AD14" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD14</f>
-        <v>-163.1052631578948</v>
+        <v>-191.5</v>
       </c>
       <c r="AE14" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE14</f>
-        <v>361.0526315789474</v>
+        <v>375.25</v>
       </c>
       <c r="AF14" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF14</f>
-        <v>524.1578947368422</v>
+        <v>566.75</v>
       </c>
       <c r="AG14" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG14</f>
@@ -11393,27 +11395,27 @@
       </c>
       <c r="AA15" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA15</f>
-        <v>4932.6315789473683</v>
+        <v>4851.5</v>
       </c>
       <c r="AB15" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB15</f>
-        <v>6.9577464788732399</v>
+        <v>7.0741007935689995</v>
       </c>
       <c r="AC15" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC15</f>
-        <v>0.6957746478873239</v>
+        <v>0.70741007935689992</v>
       </c>
       <c r="AD15" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD15</f>
-        <v>-1500.6315789473683</v>
+        <v>-1419.5</v>
       </c>
       <c r="AE15" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE15</f>
-        <v>2466.3157894736842</v>
+        <v>2425.75</v>
       </c>
       <c r="AF15" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF15</f>
-        <v>3966.9473684210525</v>
+        <v>3845.25</v>
       </c>
       <c r="AG15" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG15</f>
@@ -11521,27 +11523,27 @@
       </c>
       <c r="AA16" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA16</f>
-        <v>872.1052631578948</v>
+        <v>882.5</v>
       </c>
       <c r="AB16" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB16</f>
-        <v>2.3621001810500903</v>
+        <v>2.3342776203966005</v>
       </c>
       <c r="AC16" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC16</f>
-        <v>0.23621001810500902</v>
+        <v>0.23342776203966006</v>
       </c>
       <c r="AD16" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD16</f>
-        <v>-666.1052631578948</v>
+        <v>-676.5</v>
       </c>
       <c r="AE16" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE16</f>
-        <v>436.0526315789474</v>
+        <v>441.25</v>
       </c>
       <c r="AF16" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF16</f>
-        <v>1102.1578947368421</v>
+        <v>1117.75</v>
       </c>
       <c r="AG16" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG16</f>
@@ -11649,27 +11651,27 @@
       </c>
       <c r="AA17" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA17</f>
-        <v>115.26315789473685</v>
+        <v>122</v>
       </c>
       <c r="AB17" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB17</f>
-        <v>18.392694063926939</v>
+        <v>17.377049180327869</v>
       </c>
       <c r="AC17" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC17</f>
-        <v>1.839269406392694</v>
+        <v>1.7377049180327868</v>
       </c>
       <c r="AD17" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD17</f>
-        <v>96.73684210526315</v>
+        <v>90</v>
       </c>
       <c r="AE17" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE17</f>
-        <v>57.631578947368425</v>
+        <v>61</v>
       </c>
       <c r="AF17" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF17</f>
-        <v>-39.105263157894726</v>
+        <v>-29</v>
       </c>
       <c r="AG17" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG17</f>
@@ -11777,27 +11779,27 @@
       </c>
       <c r="AA18" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA18</f>
-        <v>14376.315789473683</v>
+        <v>14153</v>
       </c>
       <c r="AB18" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB18</f>
-        <v>5.8269449020684609</v>
+        <v>5.9188864551685159</v>
       </c>
       <c r="AC18" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC18</f>
-        <v>0.58269449020684605</v>
+        <v>0.5918886455168515</v>
       </c>
       <c r="AD18" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD18</f>
-        <v>-5999.3157894736833</v>
+        <v>-5776</v>
       </c>
       <c r="AE18" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE18</f>
-        <v>7188.1578947368416</v>
+        <v>7076.5</v>
       </c>
       <c r="AF18" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF18</f>
-        <v>13187.473684210525</v>
+        <v>12852.5</v>
       </c>
       <c r="AG18" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG18</f>
@@ -11905,27 +11907,27 @@
       </c>
       <c r="AA19" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA19</f>
-        <v>1421.578947368421</v>
+        <v>1398.5</v>
       </c>
       <c r="AB19" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB19</f>
-        <v>10.600888559792669</v>
+        <v>10.775831247765463</v>
       </c>
       <c r="AC19" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC19</f>
-        <v>1.0600888559792669</v>
+        <v>1.0775831247765464</v>
       </c>
       <c r="AD19" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD19</f>
-        <v>85.421052631578959</v>
+        <v>108.5</v>
       </c>
       <c r="AE19" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE19</f>
-        <v>710.78947368421052</v>
+        <v>699.25</v>
       </c>
       <c r="AF19" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF19</f>
-        <v>625.36842105263156</v>
+        <v>590.75</v>
       </c>
       <c r="AG19" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG19</f>
@@ -12033,27 +12035,27 @@
       </c>
       <c r="AA20" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA20</f>
-        <v>3270.5263157894733</v>
+        <v>3218.5</v>
       </c>
       <c r="AB20" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB20</f>
-        <v>12.12648857418732</v>
+        <v>12.322510486251359</v>
       </c>
       <c r="AC20" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC20</f>
-        <v>1.212648857418732</v>
+        <v>1.2322510486251359</v>
       </c>
       <c r="AD20" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD20</f>
-        <v>695.4736842105267</v>
+        <v>747.5</v>
       </c>
       <c r="AE20" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE20</f>
-        <v>1635.2631578947367</v>
+        <v>1609.25</v>
       </c>
       <c r="AF20" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF20</f>
-        <v>939.78947368420995</v>
+        <v>861.75</v>
       </c>
       <c r="AG20" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG20</f>
@@ -12161,27 +12163,27 @@
       </c>
       <c r="AA21" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA21</f>
-        <v>7474.7368421052633</v>
+        <v>7476</v>
       </c>
       <c r="AB21" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB21</f>
-        <v>10.2184199408534</v>
+        <v>10.21669341894061</v>
       </c>
       <c r="AC21" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC21</f>
-        <v>1.02184199408534</v>
+        <v>1.021669341894061</v>
       </c>
       <c r="AD21" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD21</f>
-        <v>163.26315789473665</v>
+        <v>162</v>
       </c>
       <c r="AE21" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE21</f>
-        <v>3737.3684210526317</v>
+        <v>3738</v>
       </c>
       <c r="AF21" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF21</f>
-        <v>3574.105263157895</v>
+        <v>3576</v>
       </c>
       <c r="AG21" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG21</f>
@@ -12289,27 +12291,27 @@
       </c>
       <c r="AA22" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA22</f>
-        <v>3484.2105263157896</v>
+        <v>3506.5</v>
       </c>
       <c r="AB22" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB22</f>
-        <v>10.794410876132931</v>
+        <v>10.725794952231571</v>
       </c>
       <c r="AC22" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC22</f>
-        <v>1.0794410876132929</v>
+        <v>1.0725794952231571</v>
       </c>
       <c r="AD22" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD22</f>
-        <v>276.78947368421041</v>
+        <v>254.5</v>
       </c>
       <c r="AE22" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE22</f>
-        <v>1742.1052631578948</v>
+        <v>1753.25</v>
       </c>
       <c r="AF22" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF22</f>
-        <v>1465.3157894736844</v>
+        <v>1498.75</v>
       </c>
       <c r="AG22" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG22</f>
@@ -12417,27 +12419,27 @@
       </c>
       <c r="AA23" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA23</f>
-        <v>34597.368421052633</v>
+        <v>34029.5</v>
       </c>
       <c r="AB23" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB23</f>
-        <v>9.5865672777059405</v>
+        <v>9.7465434402503721</v>
       </c>
       <c r="AC23" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC23</f>
-        <v>0.95865672777059396</v>
+        <v>0.97465434402503714</v>
       </c>
       <c r="AD23" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD23</f>
-        <v>-1430.3684210526335</v>
+        <v>-862.5</v>
       </c>
       <c r="AE23" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE23</f>
-        <v>17298.684210526317</v>
+        <v>17014.75</v>
       </c>
       <c r="AF23" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF23</f>
-        <v>18729.05263157895</v>
+        <v>17877.25</v>
       </c>
       <c r="AG23" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG23</f>
@@ -12545,27 +12547,27 @@
       </c>
       <c r="AA24" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA24</f>
-        <v>22536.315789473683</v>
+        <v>22193</v>
       </c>
       <c r="AB24" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB24</f>
-        <v>11.114061514748126</v>
+        <v>11.285991078267921</v>
       </c>
       <c r="AC24" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC24</f>
-        <v>1.1114061514748126</v>
+        <v>1.1285991078267923</v>
       </c>
       <c r="AD24" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD24</f>
-        <v>2510.6842105263167</v>
+        <v>2854</v>
       </c>
       <c r="AE24" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE24</f>
-        <v>11268.157894736842</v>
+        <v>11096.5</v>
       </c>
       <c r="AF24" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF24</f>
-        <v>8757.4736842105249</v>
+        <v>8242.5</v>
       </c>
       <c r="AG24" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG24</f>
@@ -12673,27 +12675,27 @@
       </c>
       <c r="AA25" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA25</f>
-        <v>21916.315789473683</v>
+        <v>21481.5</v>
       </c>
       <c r="AB25" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB25</f>
-        <v>11.816310847482049</v>
+        <v>12.055489607336545</v>
       </c>
       <c r="AC25" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC25</f>
-        <v>1.181631084748205</v>
+        <v>1.2055489607336545</v>
       </c>
       <c r="AD25" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD25</f>
-        <v>3980.6842105263167</v>
+        <v>4415.5</v>
       </c>
       <c r="AE25" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE25</f>
-        <v>10958.157894736842</v>
+        <v>10740.75</v>
       </c>
       <c r="AF25" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF25</f>
-        <v>6977.4736842105249</v>
+        <v>6325.25</v>
       </c>
       <c r="AG25" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG25</f>
@@ -12801,27 +12803,27 @@
       </c>
       <c r="AA26" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA26</f>
-        <v>26250</v>
+        <v>25732.5</v>
       </c>
       <c r="AB26" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB26</f>
-        <v>11.287238095238095</v>
+        <v>11.514232973865735</v>
       </c>
       <c r="AC26" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC26</f>
-        <v>1.1287238095238095</v>
+        <v>1.1514232973865735</v>
       </c>
       <c r="AD26" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD26</f>
-        <v>3379</v>
+        <v>3896.5</v>
       </c>
       <c r="AE26" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE26</f>
-        <v>13125</v>
+        <v>12866.25</v>
       </c>
       <c r="AF26" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF26</f>
-        <v>9746</v>
+        <v>8969.75</v>
       </c>
       <c r="AG26" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG26</f>
@@ -12929,27 +12931,27 @@
       </c>
       <c r="AA27" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA27</f>
-        <v>150.52631578947367</v>
+        <v>97</v>
       </c>
       <c r="AB27" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB27</f>
-        <v>100.71328671328672</v>
+        <v>156.28865979381445</v>
       </c>
       <c r="AC27" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC27</f>
-        <v>10.071328671328672</v>
+        <v>15.628865979381443</v>
       </c>
       <c r="AD27" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD27</f>
-        <v>1365.4736842105262</v>
+        <v>1419</v>
       </c>
       <c r="AE27" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE27</f>
-        <v>75.263157894736835</v>
+        <v>48.5</v>
       </c>
       <c r="AF27" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF27</f>
-        <v>-1290.2105263157894</v>
+        <v>-1370.5</v>
       </c>
       <c r="AG27" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG27</f>
@@ -12997,15 +12999,15 @@
       </c>
       <c r="L28" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L28</f>
-        <v>8.3015552995391708</v>
+        <v>8.2647779896485964</v>
       </c>
       <c r="M28" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M28</f>
-        <v>8040.4210526315783</v>
+        <v>8076.2000000000007</v>
       </c>
       <c r="N28" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N28</f>
-        <v>-2448.1052631578941</v>
+        <v>-2472.5</v>
       </c>
       <c r="O28" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O28</f>
@@ -13057,27 +13059,27 @@
       </c>
       <c r="AA28" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA28</f>
-        <v>3654.7368421052629</v>
+        <v>3671</v>
       </c>
       <c r="AB28" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB28</f>
-        <v>13.169210829493089</v>
+        <v>13.11086897303187</v>
       </c>
       <c r="AC28" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC28</f>
-        <v>1.3169210829493088</v>
+        <v>1.3110868973031871</v>
       </c>
       <c r="AD28" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD28</f>
-        <v>1158.2631578947371</v>
+        <v>1142</v>
       </c>
       <c r="AE28" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE28</f>
-        <v>1827.3684210526314</v>
+        <v>1835.5</v>
       </c>
       <c r="AF28" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF28</f>
-        <v>669.10526315789434</v>
+        <v>693.5</v>
       </c>
       <c r="AG28" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG28</f>
@@ -13125,15 +13127,15 @@
       </c>
       <c r="L29" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L29</f>
-        <v>6.9176875957120982</v>
+        <v>6.8796720520858452</v>
       </c>
       <c r="M29" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M29</f>
-        <v>9073.2631578947367</v>
+        <v>9123.4</v>
       </c>
       <c r="N29" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N29</f>
-        <v>-3333.3157894736842</v>
+        <v>-3367.5</v>
       </c>
       <c r="O29" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O29</f>
@@ -13185,27 +13187,27 @@
       </c>
       <c r="AA29" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA29</f>
-        <v>4124.21052631579</v>
+        <v>4147</v>
       </c>
       <c r="AB29" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB29</f>
-        <v>11.039688616641142</v>
+        <v>10.97902097902098</v>
       </c>
       <c r="AC29" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC29</f>
-        <v>1.1039688616641141</v>
+        <v>1.0979020979020979</v>
       </c>
       <c r="AD29" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD29</f>
-        <v>428.78947368420995</v>
+        <v>406</v>
       </c>
       <c r="AE29" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE29</f>
-        <v>2062.105263157895</v>
+        <v>2073.5</v>
       </c>
       <c r="AF29" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF29</f>
-        <v>1633.3157894736851</v>
+        <v>1667.5</v>
       </c>
       <c r="AG29" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG29</f>
@@ -13253,15 +13255,15 @@
       </c>
       <c r="L30" s="17">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L30</f>
-        <v>7.1837997847147461</v>
+        <v>7.3148509696733051</v>
       </c>
       <c r="M30" s="33">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M30</f>
-        <v>8605.4736842105267</v>
+        <v>8451.2999999999993</v>
       </c>
       <c r="N30" s="18">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N30</f>
-        <v>-3057.3684210526317</v>
+        <v>-2952.25</v>
       </c>
       <c r="O30" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O30</f>
@@ -13313,27 +13315,27 @@
       </c>
       <c r="AA30" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA30</f>
-        <v>3911.5789473684208</v>
+        <v>3841.5</v>
       </c>
       <c r="AB30" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB30</f>
-        <v>15.410656620021529</v>
+        <v>15.691787062345439</v>
       </c>
       <c r="AC30" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC30</f>
-        <v>1.541065662002153</v>
+        <v>1.5691787062345437</v>
       </c>
       <c r="AD30" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD30</f>
-        <v>2116.4210526315792</v>
+        <v>2186.5</v>
       </c>
       <c r="AE30" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE30</f>
-        <v>1955.7894736842104</v>
+        <v>1920.75</v>
       </c>
       <c r="AF30" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF30</f>
-        <v>-160.63157894736878</v>
+        <v>-265.75</v>
       </c>
       <c r="AG30" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG30</f>
@@ -13441,27 +13443,27 @@
       </c>
       <c r="AA31" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA31</f>
-        <v>2312.6315789473683</v>
+        <v>2327.5</v>
       </c>
       <c r="AB31" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB31</f>
-        <v>5.9283113336367776</v>
+        <v>5.8904403866809885</v>
       </c>
       <c r="AC31" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC31</f>
-        <v>0.59283113336367776</v>
+        <v>0.58904403866809885</v>
       </c>
       <c r="AD31" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD31</f>
-        <v>-941.63157894736833</v>
+        <v>-956.5</v>
       </c>
       <c r="AE31" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE31</f>
-        <v>1156.3157894736842</v>
+        <v>1163.75</v>
       </c>
       <c r="AF31" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF31</f>
-        <v>2097.9473684210525</v>
+        <v>2120.25</v>
       </c>
       <c r="AG31" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG31</f>
@@ -13569,27 +13571,27 @@
       </c>
       <c r="AA32" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA32</f>
-        <v>1350.5263157894738</v>
+        <v>1355.5</v>
       </c>
       <c r="AB32" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB32</f>
-        <v>7.2564302416212003</v>
+        <v>7.2298045001844331</v>
       </c>
       <c r="AC32" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC32</f>
-        <v>0.72564302416212001</v>
+        <v>0.72298045001844335</v>
       </c>
       <c r="AD32" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD32</f>
-        <v>-370.52631578947376</v>
+        <v>-375.5</v>
       </c>
       <c r="AE32" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE32</f>
-        <v>675.26315789473688</v>
+        <v>677.75</v>
       </c>
       <c r="AF32" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF32</f>
-        <v>1045.7894736842106</v>
+        <v>1053.25</v>
       </c>
       <c r="AG32" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG32</f>
@@ -13697,27 +13699,27 @@
       </c>
       <c r="AA33" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA33</f>
-        <v>5045.78947368421</v>
+        <v>4963.5</v>
       </c>
       <c r="AB33" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB33</f>
-        <v>6.5440700949202055</v>
+        <v>6.6525637151203787</v>
       </c>
       <c r="AC33" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC33</f>
-        <v>0.65440700949202046</v>
+        <v>0.66525637151203787</v>
       </c>
       <c r="AD33" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD33</f>
-        <v>-1743.78947368421</v>
+        <v>-1661.5</v>
       </c>
       <c r="AE33" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE33</f>
-        <v>2522.894736842105</v>
+        <v>2481.75</v>
       </c>
       <c r="AF33" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF33</f>
-        <v>4266.6842105263149</v>
+        <v>4143.25</v>
       </c>
       <c r="AG33" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG33</f>
@@ -13825,27 +13827,27 @@
       </c>
       <c r="AA34" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA34</f>
-        <v>7976.3157894736842</v>
+        <v>7850</v>
       </c>
       <c r="AB34" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB34</f>
-        <v>7.9071593533487299</v>
+        <v>8.0343949044585994</v>
       </c>
       <c r="AC34" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC34</f>
-        <v>0.79071593533487294</v>
+        <v>0.80343949044585983</v>
       </c>
       <c r="AD34" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD34</f>
-        <v>-1669.3157894736842</v>
+        <v>-1543</v>
       </c>
       <c r="AE34" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE34</f>
-        <v>3988.1578947368421</v>
+        <v>3925</v>
       </c>
       <c r="AF34" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF34</f>
-        <v>5657.4736842105267</v>
+        <v>5468</v>
       </c>
       <c r="AG34" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG34</f>
@@ -13953,7 +13955,7 @@
       </c>
       <c r="AA35" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA35</f>
-        <v>670.52631578947376</v>
+        <v>637</v>
       </c>
       <c r="AB35" s="34">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB35</f>
@@ -13965,15 +13967,15 @@
       </c>
       <c r="AD35" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD35</f>
-        <v>-670.52631578947376</v>
+        <v>-637</v>
       </c>
       <c r="AE35" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE35</f>
-        <v>335.26315789473688</v>
+        <v>318.5</v>
       </c>
       <c r="AF35" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF35</f>
-        <v>1005.7894736842106</v>
+        <v>955.5</v>
       </c>
       <c r="AG35" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG35</f>
@@ -14081,27 +14083,27 @@
       </c>
       <c r="AA36" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA36</f>
-        <v>7127.894736842105</v>
+        <v>7096.5</v>
       </c>
       <c r="AB36" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB36</f>
-        <v>0.76179576164808394</v>
+        <v>0.76516592686535623</v>
       </c>
       <c r="AC36" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC36</f>
-        <v>7.6179576164808388E-2</v>
+        <v>7.6516592686535614E-2</v>
       </c>
       <c r="AD36" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD36</f>
-        <v>-6584.894736842105</v>
+        <v>-6553.5</v>
       </c>
       <c r="AE36" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE36</f>
-        <v>3563.9473684210525</v>
+        <v>3548.25</v>
       </c>
       <c r="AF36" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF36</f>
-        <v>10148.842105263157</v>
+        <v>10101.75</v>
       </c>
       <c r="AG36" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG36</f>
@@ -14209,27 +14211,27 @@
       </c>
       <c r="AA37" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA37</f>
-        <v>11818.42105263158</v>
+        <v>11629.5</v>
       </c>
       <c r="AB37" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB37</f>
-        <v>8.6035181474059232</v>
+        <v>8.7432821703426633</v>
       </c>
       <c r="AC37" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC37</f>
-        <v>0.86035181474059219</v>
+        <v>0.87432821703426633</v>
       </c>
       <c r="AD37" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD37</f>
-        <v>-1650.4210526315801</v>
+        <v>-1461.5</v>
       </c>
       <c r="AE37" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE37</f>
-        <v>5909.21052631579</v>
+        <v>5814.75</v>
       </c>
       <c r="AF37" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF37</f>
-        <v>7559.6315789473701</v>
+        <v>7276.25</v>
       </c>
       <c r="AG37" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG37</f>
@@ -14337,27 +14339,27 @@
       </c>
       <c r="AA38" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA38</f>
-        <v>5122.6315789473683</v>
+        <v>5102.5</v>
       </c>
       <c r="AB38" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB38</f>
-        <v>19.244015206000203</v>
+        <v>19.319941205291524</v>
       </c>
       <c r="AC38" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC38</f>
-        <v>1.9244015206000207</v>
+        <v>1.9319941205291524</v>
       </c>
       <c r="AD38" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD38</f>
-        <v>4735.3684210526317</v>
+        <v>4755.5</v>
       </c>
       <c r="AE38" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE38</f>
-        <v>2561.3157894736842</v>
+        <v>2551.25</v>
       </c>
       <c r="AF38" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF38</f>
-        <v>-2174.0526315789475</v>
+        <v>-2204.25</v>
       </c>
       <c r="AG38" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG38</f>
@@ -14465,27 +14467,27 @@
       </c>
       <c r="AA39" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA39</f>
-        <v>3974.2105263157896</v>
+        <v>4006</v>
       </c>
       <c r="AB39" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB39</f>
-        <v>4.9468944510660835</v>
+        <v>4.9076385421867199</v>
       </c>
       <c r="AC39" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC39</f>
-        <v>0.49468944510660839</v>
+        <v>0.49076385421867197</v>
       </c>
       <c r="AD39" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD39</f>
-        <v>-2008.2105263157896</v>
+        <v>-2040</v>
       </c>
       <c r="AE39" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE39</f>
-        <v>1987.1052631578948</v>
+        <v>2003</v>
       </c>
       <c r="AF39" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF39</f>
-        <v>3995.3157894736842</v>
+        <v>4043</v>
       </c>
       <c r="AG39" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG39</f>
@@ -14593,27 +14595,27 @@
       </c>
       <c r="AA40" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA40</f>
-        <v>734.73684210526312</v>
+        <v>709</v>
       </c>
       <c r="AB40" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB40</f>
-        <v>61.872492836676216</v>
+        <v>64.118476727785605</v>
       </c>
       <c r="AC40" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC40</f>
-        <v>6.1872492836676223</v>
+        <v>6.4118476727785616</v>
       </c>
       <c r="AD40" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD40</f>
-        <v>3811.2631578947367</v>
+        <v>3837</v>
       </c>
       <c r="AE40" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE40</f>
-        <v>367.36842105263156</v>
+        <v>354.5</v>
       </c>
       <c r="AF40" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF40</f>
-        <v>-3443.894736842105</v>
+        <v>-3482.5</v>
       </c>
       <c r="AG40" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG40</f>
@@ -14977,27 +14979,27 @@
       </c>
       <c r="AA43" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA43</f>
-        <v>1321.578947368421</v>
+        <v>1342.5</v>
       </c>
       <c r="AB43" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB43</f>
-        <v>5.0015929908403027</v>
+        <v>4.9236499068901303</v>
       </c>
       <c r="AC43" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC43</f>
-        <v>0.50015929908403023</v>
+        <v>0.49236499068901302</v>
       </c>
       <c r="AD43" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD43</f>
-        <v>-660.57894736842104</v>
+        <v>-681.5</v>
       </c>
       <c r="AE43" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE43</f>
-        <v>660.78947368421052</v>
+        <v>671.25</v>
       </c>
       <c r="AF43" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF43</f>
-        <v>1321.3684210526317</v>
+        <v>1352.75</v>
       </c>
       <c r="AG43" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG43</f>
@@ -15105,27 +15107,27 @@
       </c>
       <c r="AA44" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA44</f>
-        <v>6458.4210526315792</v>
+        <v>6411</v>
       </c>
       <c r="AB44" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB44</f>
-        <v>1.7573954852905223</v>
+        <v>1.7703946342224302</v>
       </c>
       <c r="AC44" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC44</f>
-        <v>0.17573954852905224</v>
+        <v>0.17703946342224303</v>
       </c>
       <c r="AD44" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD44</f>
-        <v>-5323.4210526315792</v>
+        <v>-5276</v>
       </c>
       <c r="AE44" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE44</f>
-        <v>3229.2105263157896</v>
+        <v>3205.5</v>
       </c>
       <c r="AF44" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF44</f>
-        <v>8552.6315789473683</v>
+        <v>8481.5</v>
       </c>
       <c r="AG44" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG44</f>
@@ -15233,27 +15235,27 @@
       </c>
       <c r="AA45" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA45</f>
-        <v>6298.4210526315792</v>
+        <v>6201</v>
       </c>
       <c r="AB45" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB45</f>
-        <v>6.5921283529706693</v>
+        <v>6.6956942428640538</v>
       </c>
       <c r="AC45" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC45</f>
-        <v>0.65921283529706687</v>
+        <v>0.66956942428640542</v>
       </c>
       <c r="AD45" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD45</f>
-        <v>-2146.4210526315792</v>
+        <v>-2049</v>
       </c>
       <c r="AE45" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE45</f>
-        <v>3149.2105263157896</v>
+        <v>3100.5</v>
       </c>
       <c r="AF45" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF45</f>
-        <v>5295.6315789473683</v>
+        <v>5149.5</v>
       </c>
       <c r="AG45" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG45</f>
@@ -15361,27 +15363,27 @@
       </c>
       <c r="AA46" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA46</f>
-        <v>8365.2631578947367</v>
+        <v>8288.5</v>
       </c>
       <c r="AB46" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB46</f>
-        <v>10.223228891405562</v>
+        <v>10.317910357724557</v>
       </c>
       <c r="AC46" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC46</f>
-        <v>1.0223228891405562</v>
+        <v>1.0317910357724558</v>
       </c>
       <c r="AD46" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD46</f>
-        <v>186.73684210526335</v>
+        <v>263.5</v>
       </c>
       <c r="AE46" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE46</f>
-        <v>4182.6315789473683</v>
+        <v>4144.25</v>
       </c>
       <c r="AF46" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF46</f>
-        <v>3995.894736842105</v>
+        <v>3880.75</v>
       </c>
       <c r="AG46" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG46</f>
@@ -15489,27 +15491,27 @@
       </c>
       <c r="AA47" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA47</f>
-        <v>5688.4210526315792</v>
+        <v>5643.5</v>
       </c>
       <c r="AB47" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB47</f>
-        <v>11.836324944485566</v>
+        <v>11.930539558784442</v>
       </c>
       <c r="AC47" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC47</f>
-        <v>1.1836324944485566</v>
+        <v>1.1930539558784443</v>
       </c>
       <c r="AD47" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD47</f>
-        <v>1044.5789473684208</v>
+        <v>1089.5</v>
       </c>
       <c r="AE47" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE47</f>
-        <v>2844.2105263157896</v>
+        <v>2821.75</v>
       </c>
       <c r="AF47" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF47</f>
-        <v>1799.6315789473688</v>
+        <v>1732.25</v>
       </c>
       <c r="AG47" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG47</f>
@@ -15617,27 +15619,27 @@
       </c>
       <c r="AA48" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA48</f>
-        <v>24.736842105263158</v>
+        <v>23.5</v>
       </c>
       <c r="AB48" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB48</f>
-        <v>2113.0425531914893</v>
+        <v>2224.255319148936</v>
       </c>
       <c r="AC48" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC48</f>
-        <v>211.30425531914895</v>
+        <v>222.42553191489361</v>
       </c>
       <c r="AD48" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD48</f>
-        <v>5202.2631578947367</v>
+        <v>5203.5</v>
       </c>
       <c r="AE48" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE48</f>
-        <v>12.368421052631579</v>
+        <v>11.75</v>
       </c>
       <c r="AF48" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF48</f>
-        <v>-5189.894736842105</v>
+        <v>-5191.75</v>
       </c>
       <c r="AG48" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG48</f>
@@ -15873,7 +15875,7 @@
       </c>
       <c r="AA50" s="36">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA50</f>
-        <v>567.89473684210532</v>
+        <v>544</v>
       </c>
       <c r="AB50" s="25">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB50</f>
@@ -15885,15 +15887,15 @@
       </c>
       <c r="AD50" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD50</f>
-        <v>-556.89473684210532</v>
+        <v>-533</v>
       </c>
       <c r="AE50" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE50</f>
-        <v>283.94736842105266</v>
+        <v>272</v>
       </c>
       <c r="AF50" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF50</f>
-        <v>840.84210526315792</v>
+        <v>805</v>
       </c>
       <c r="AG50" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG50</f>
@@ -16001,27 +16003,27 @@
       </c>
       <c r="AA51" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA51</f>
-        <v>4.7368421052631575</v>
+        <v>4.5</v>
       </c>
       <c r="AB51" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB51</f>
-        <v>90.777777777777786</v>
+        <v>95.555555555555557</v>
       </c>
       <c r="AC51" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC51</f>
-        <v>9.0777777777777793</v>
+        <v>9.5555555555555554</v>
       </c>
       <c r="AD51" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD51</f>
-        <v>38.263157894736842</v>
+        <v>38.5</v>
       </c>
       <c r="AE51" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE51</f>
-        <v>2.3684210526315788</v>
+        <v>2.25</v>
       </c>
       <c r="AF51" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF51</f>
-        <v>-35.89473684210526</v>
+        <v>-36.25</v>
       </c>
       <c r="AG51" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG51</f>
@@ -16257,27 +16259,27 @@
       </c>
       <c r="AA53" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA53</f>
-        <v>5240.5263157894742</v>
+        <v>5290</v>
       </c>
       <c r="AB53" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB53</f>
-        <v>7.6328211308627093E-3</v>
+        <v>7.5614366729678641E-3</v>
       </c>
       <c r="AC53" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC53</f>
-        <v>7.6328211308627093E-4</v>
+        <v>7.5614366729678643E-4</v>
       </c>
       <c r="AD53" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD53</f>
-        <v>-5236.5263157894742</v>
+        <v>-5286</v>
       </c>
       <c r="AE53" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE53</f>
-        <v>2620.2631578947371</v>
+        <v>2645</v>
       </c>
       <c r="AF53" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF53</f>
-        <v>7856.7894736842118</v>
+        <v>7931</v>
       </c>
       <c r="AG53" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG53</f>
@@ -16385,27 +16387,27 @@
       </c>
       <c r="AA54" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA54</f>
-        <v>590.52631578947376</v>
+        <v>788.5</v>
       </c>
       <c r="AB54" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB54</f>
-        <v>382.25222816399281</v>
+        <v>286.27774254914397</v>
       </c>
       <c r="AC54" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC54</f>
-        <v>38.225222816399281</v>
+        <v>28.627774254914396</v>
       </c>
       <c r="AD54" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD54</f>
-        <v>21982.473684210527</v>
+        <v>21784.5</v>
       </c>
       <c r="AE54" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE54</f>
-        <v>295.26315789473688</v>
+        <v>394.25</v>
       </c>
       <c r="AF54" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF54</f>
-        <v>-21687.21052631579</v>
+        <v>-21390.25</v>
       </c>
       <c r="AG54" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG54</f>
@@ -16513,27 +16515,27 @@
       </c>
       <c r="AA55" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA55</f>
-        <v>3006.3157894736842</v>
+        <v>2964.5</v>
       </c>
       <c r="AB55" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB55</f>
-        <v>97.225315126050418</v>
+        <v>98.596727947377303</v>
       </c>
       <c r="AC55" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC55</f>
-        <v>9.7225315126050429</v>
+        <v>9.8596727947377296</v>
       </c>
       <c r="AD55" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD55</f>
-        <v>26222.684210526317</v>
+        <v>26264.5</v>
       </c>
       <c r="AE55" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE55</f>
-        <v>1503.1578947368421</v>
+        <v>1482.25</v>
       </c>
       <c r="AF55" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF55</f>
-        <v>-24719.526315789473</v>
+        <v>-24782.25</v>
       </c>
       <c r="AG55" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG55</f>
@@ -16641,27 +16643,27 @@
       </c>
       <c r="AA56" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA56</f>
-        <v>5310.5263157894742</v>
+        <v>5246</v>
       </c>
       <c r="AB56" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB56</f>
-        <v>30.411298315163528</v>
+        <v>30.785360274494852</v>
       </c>
       <c r="AC56" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC56</f>
-        <v>3.0411298315163524</v>
+        <v>3.0785360274494855</v>
       </c>
       <c r="AD56" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD56</f>
-        <v>10839.473684210527</v>
+        <v>10904</v>
       </c>
       <c r="AE56" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE56</f>
-        <v>2655.2631578947371</v>
+        <v>2623</v>
       </c>
       <c r="AF56" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF56</f>
-        <v>-8184.21052631579</v>
+        <v>-8281</v>
       </c>
       <c r="AG56" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG56</f>
@@ -16769,27 +16771,27 @@
       </c>
       <c r="AA57" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA57</f>
-        <v>3101.0526315789475</v>
+        <v>3077</v>
       </c>
       <c r="AB57" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB57</f>
-        <v>62.207909029192123</v>
+        <v>62.69418264543387</v>
       </c>
       <c r="AC57" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC57</f>
-        <v>6.2207909029192123</v>
+        <v>6.2694182645433862</v>
       </c>
       <c r="AD57" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD57</f>
-        <v>16189.947368421053</v>
+        <v>16214</v>
       </c>
       <c r="AE57" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE57</f>
-        <v>1550.5263157894738</v>
+        <v>1538.5</v>
       </c>
       <c r="AF57" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF57</f>
-        <v>-14639.42105263158</v>
+        <v>-14675.5</v>
       </c>
       <c r="AG57" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG57</f>
@@ -16897,27 +16899,27 @@
       </c>
       <c r="AA58" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA58</f>
-        <v>2907.894736842105</v>
+        <v>2912</v>
       </c>
       <c r="AB58" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB58</f>
-        <v>2.4588235294117649</v>
+        <v>2.4553571428571428</v>
       </c>
       <c r="AC58" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC58</f>
-        <v>0.2458823529411765</v>
+        <v>0.24553571428571427</v>
       </c>
       <c r="AD58" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD58</f>
-        <v>-2192.894736842105</v>
+        <v>-2197</v>
       </c>
       <c r="AE58" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE58</f>
-        <v>1453.9473684210525</v>
+        <v>1456</v>
       </c>
       <c r="AF58" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF58</f>
-        <v>3646.8421052631575</v>
+        <v>3653</v>
       </c>
       <c r="AG58" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG58</f>
@@ -17025,27 +17027,27 @@
       </c>
       <c r="AA59" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA59</f>
-        <v>587.36842105263156</v>
+        <v>563</v>
       </c>
       <c r="AB59" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB59</f>
-        <v>6.5716845878136203</v>
+        <v>6.8561278863232689</v>
       </c>
       <c r="AC59" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC59</f>
-        <v>0.65716845878136199</v>
+        <v>0.68561278863232678</v>
       </c>
       <c r="AD59" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD59</f>
-        <v>-201.36842105263156</v>
+        <v>-177</v>
       </c>
       <c r="AE59" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE59</f>
-        <v>293.68421052631578</v>
+        <v>281.5</v>
       </c>
       <c r="AF59" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF59</f>
-        <v>495.05263157894734</v>
+        <v>458.5</v>
       </c>
       <c r="AG59" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG59</f>
@@ -17153,27 +17155,27 @@
       </c>
       <c r="AA60" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA60</f>
-        <v>1076.8421052631579</v>
+        <v>1045.5</v>
       </c>
       <c r="AB60" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB60</f>
-        <v>2.767350928641251</v>
+        <v>2.8503108560497372</v>
       </c>
       <c r="AC60" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC60</f>
-        <v>0.27673509286412512</v>
+        <v>0.2850310856049737</v>
       </c>
       <c r="AD60" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD60</f>
-        <v>-778.84210526315792</v>
+        <v>-747.5</v>
       </c>
       <c r="AE60" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE60</f>
-        <v>538.42105263157896</v>
+        <v>522.75</v>
       </c>
       <c r="AF60" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF60</f>
-        <v>1317.2631578947369</v>
+        <v>1270.25</v>
       </c>
       <c r="AG60" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG60</f>
@@ -17281,27 +17283,27 @@
       </c>
       <c r="AA61" s="24">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA61</f>
-        <v>511.0526315789474</v>
+        <v>492</v>
       </c>
       <c r="AB61" s="25">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB61</f>
-        <v>2.8568486096807413</v>
+        <v>2.9674796747967478</v>
       </c>
       <c r="AC61" s="26">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC61</f>
-        <v>0.28568486096807416</v>
+        <v>0.2967479674796748</v>
       </c>
       <c r="AD61" s="29">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD61</f>
-        <v>-365.0526315789474</v>
+        <v>-346</v>
       </c>
       <c r="AE61" s="30">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE61</f>
-        <v>255.5263157894737</v>
+        <v>246</v>
       </c>
       <c r="AF61" s="28">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF61</f>
-        <v>620.57894736842104</v>
+        <v>592</v>
       </c>
       <c r="AG61" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG61</f>
@@ -17341,7 +17343,7 @@
       </c>
       <c r="AF62" s="44">
         <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF62</f>
-        <v>155940.89473684211</v>
+        <v>151316.75</v>
       </c>
     </row>
     <row r="63" spans="2:33" x14ac:dyDescent="0.25">
@@ -17350,10 +17352,10 @@
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
-      <c r="E63" s="67" t="s">
+      <c r="E63" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="F63" s="67"/>
+      <c r="F63" s="64"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -17378,10 +17380,10 @@
       <c r="AB63" s="42"/>
     </row>
     <row r="64" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B64" s="63" t="s">
+      <c r="B64" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="63"/>
+      <c r="C64" s="65"/>
       <c r="D64" s="48">
         <f>SUM(F13:F61)</f>
         <v>144936.54999999999</v>
@@ -17526,19 +17528,19 @@
       <c r="AB67" s="42"/>
     </row>
     <row r="68" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B68" s="63" t="s">
+      <c r="B68" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="C68" s="63"/>
+      <c r="C68" s="65"/>
       <c r="D68" s="50">
         <f>SUM(Z13:Z61)</f>
         <v>421177.93000000017</v>
       </c>
-      <c r="E68" s="64">
+      <c r="E68" s="66">
         <f>D68*100/D68</f>
         <v>100</v>
       </c>
-      <c r="F68" s="64"/>
+      <c r="F68" s="66"/>
       <c r="G68" s="51"/>
       <c r="H68" s="51"/>
       <c r="I68" s="51"/>
@@ -17623,10 +17625,10 @@
       <c r="AB70" s="42"/>
     </row>
     <row r="71" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B71" s="63" t="s">
+      <c r="B71" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="63"/>
+      <c r="C71" s="65"/>
       <c r="D71" s="3">
         <f>SUM(E13:E61)</f>
         <v>112990</v>
@@ -17741,11 +17743,11 @@
         <f>SUM(T13:T61)</f>
         <v>36961</v>
       </c>
-      <c r="E74" s="62">
+      <c r="E74" s="67">
         <f>D74*100/D75</f>
         <v>11.039956032533535</v>
       </c>
-      <c r="F74" s="62"/>
+      <c r="F74" s="67"/>
       <c r="G74" s="56"/>
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
@@ -17770,19 +17772,19 @@
       <c r="AB74" s="42"/>
     </row>
     <row r="75" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B75" s="63" t="s">
+      <c r="B75" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="63"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="55">
         <f>SUM(Y13:Y61)</f>
         <v>334793</v>
       </c>
-      <c r="E75" s="62">
+      <c r="E75" s="67">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="62"/>
+      <c r="F75" s="67"/>
       <c r="G75" s="56"/>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
@@ -18543,23 +18545,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="E71:F71"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="B1:Z6"/>
     <mergeCell ref="AA1:AG6"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G61">
     <cfRule type="colorScale" priority="5">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F1F596-F236-4609-AFC9-D9E8697974F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054F7903-ACEE-4819-86B8-9772FF165BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -841,6 +841,15 @@
     <xf numFmtId="2" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -849,15 +858,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5649,6 +5649,7 @@
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 31-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL CIERRE"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -5777,22 +5778,22 @@
             <v>13606.800000000001</v>
           </cell>
           <cell r="AA13">
-            <v>11472.5</v>
+            <v>11880.952380952382</v>
           </cell>
           <cell r="AB13">
-            <v>8.7208542166049252</v>
+            <v>8.4210420841683362</v>
           </cell>
           <cell r="AC13">
-            <v>0.87208542166049252</v>
+            <v>0.84210420841683364</v>
           </cell>
           <cell r="AD13">
-            <v>-1467.5</v>
+            <v>-1875.9523809523816</v>
           </cell>
           <cell r="AE13">
-            <v>5736.25</v>
+            <v>5940.4761904761908</v>
           </cell>
           <cell r="AF13">
-            <v>7203.75</v>
+            <v>7816.4285714285725</v>
           </cell>
           <cell r="AG13">
             <v>125.0625</v>
@@ -5869,22 +5870,22 @@
             <v>888.81000000000006</v>
           </cell>
           <cell r="AA14">
-            <v>750.5</v>
+            <v>763.80952380952385</v>
           </cell>
           <cell r="AB14">
-            <v>7.4483677548301133</v>
+            <v>7.3185785536159607</v>
           </cell>
           <cell r="AC14">
-            <v>0.7448367754830113</v>
+            <v>0.73185785536159598</v>
           </cell>
           <cell r="AD14">
-            <v>-191.5</v>
+            <v>-204.80952380952385</v>
           </cell>
           <cell r="AE14">
-            <v>375.25</v>
+            <v>381.90476190476193</v>
           </cell>
           <cell r="AF14">
-            <v>566.75</v>
+            <v>586.71428571428578</v>
           </cell>
           <cell r="AG14">
             <v>6.9874999999999998</v>
@@ -5961,22 +5962,22 @@
             <v>6966.9599999999991</v>
           </cell>
           <cell r="AA15">
-            <v>4851.5</v>
+            <v>5094.7619047619046</v>
           </cell>
           <cell r="AB15">
-            <v>7.0741007935689995</v>
+            <v>6.7363304981773995</v>
           </cell>
           <cell r="AC15">
-            <v>0.70741007935689992</v>
+            <v>0.67363304981773997</v>
           </cell>
           <cell r="AD15">
-            <v>-1419.5</v>
+            <v>-1662.7619047619046</v>
           </cell>
           <cell r="AE15">
-            <v>2425.75</v>
+            <v>2547.3809523809523</v>
           </cell>
           <cell r="AF15">
-            <v>3845.25</v>
+            <v>4210.1428571428569</v>
           </cell>
           <cell r="AG15">
             <v>57.2</v>
@@ -6053,22 +6054,22 @@
             <v>743.66</v>
           </cell>
           <cell r="AA16">
-            <v>882.5</v>
+            <v>980</v>
           </cell>
           <cell r="AB16">
-            <v>2.3342776203966005</v>
+            <v>2.1020408163265305</v>
           </cell>
           <cell r="AC16">
-            <v>0.23342776203966006</v>
+            <v>0.21020408163265306</v>
           </cell>
           <cell r="AD16">
-            <v>-676.5</v>
+            <v>-774</v>
           </cell>
           <cell r="AE16">
-            <v>441.25</v>
+            <v>490</v>
           </cell>
           <cell r="AF16">
-            <v>1117.75</v>
+            <v>1264</v>
           </cell>
           <cell r="AG16">
             <v>7.3571428571428568</v>
@@ -6145,22 +6146,22 @@
             <v>1861.36</v>
           </cell>
           <cell r="AA17">
-            <v>122</v>
+            <v>119.52380952380952</v>
           </cell>
           <cell r="AB17">
-            <v>17.377049180327869</v>
+            <v>17.737051792828684</v>
           </cell>
           <cell r="AC17">
-            <v>1.7377049180327868</v>
+            <v>1.7737051792828686</v>
           </cell>
           <cell r="AD17">
-            <v>90</v>
+            <v>92.476190476190482</v>
           </cell>
           <cell r="AE17">
-            <v>61</v>
+            <v>59.761904761904759</v>
           </cell>
           <cell r="AF17">
-            <v>-29</v>
+            <v>-32.714285714285722</v>
           </cell>
           <cell r="AG17">
             <v>17.666666666666668</v>
@@ -6237,22 +6238,22 @@
             <v>5277.51</v>
           </cell>
           <cell r="AA18">
-            <v>14153</v>
+            <v>14603.333333333332</v>
           </cell>
           <cell r="AB18">
-            <v>5.9188864551685159</v>
+            <v>5.736361561287378</v>
           </cell>
           <cell r="AC18">
-            <v>0.5918886455168515</v>
+            <v>0.57363615612873775</v>
           </cell>
           <cell r="AD18">
-            <v>-5776</v>
+            <v>-6226.3333333333321</v>
           </cell>
           <cell r="AE18">
-            <v>7076.5</v>
+            <v>7301.6666666666661</v>
           </cell>
           <cell r="AF18">
-            <v>12852.5</v>
+            <v>13527.999999999998</v>
           </cell>
           <cell r="AG18">
             <v>139.61666666666667</v>
@@ -6329,22 +6330,22 @@
             <v>949.41</v>
           </cell>
           <cell r="AA19">
-            <v>1398.5</v>
+            <v>1503.8095238095239</v>
           </cell>
           <cell r="AB19">
-            <v>10.775831247765463</v>
+            <v>10.021215959468018</v>
           </cell>
           <cell r="AC19">
-            <v>1.0775831247765464</v>
+            <v>1.0021215959468017</v>
           </cell>
           <cell r="AD19">
-            <v>108.5</v>
+            <v>3.1904761904761472</v>
           </cell>
           <cell r="AE19">
-            <v>699.25</v>
+            <v>751.90476190476193</v>
           </cell>
           <cell r="AF19">
-            <v>590.75</v>
+            <v>748.71428571428578</v>
           </cell>
           <cell r="AG19">
             <v>25.116666666666667</v>
@@ -6421,22 +6422,22 @@
             <v>2498.58</v>
           </cell>
           <cell r="AA20">
-            <v>3218.5</v>
+            <v>3435.7142857142853</v>
           </cell>
           <cell r="AB20">
-            <v>12.322510486251359</v>
+            <v>11.543451143451144</v>
           </cell>
           <cell r="AC20">
-            <v>1.2322510486251359</v>
+            <v>1.1543451143451144</v>
           </cell>
           <cell r="AD20">
-            <v>747.5</v>
+            <v>530.28571428571468</v>
           </cell>
           <cell r="AE20">
-            <v>1609.25</v>
+            <v>1717.8571428571427</v>
           </cell>
           <cell r="AF20">
-            <v>861.75</v>
+            <v>1187.571428571428</v>
           </cell>
           <cell r="AG20">
             <v>66.099999999999994</v>
@@ -6513,22 +6514,22 @@
             <v>8325.42</v>
           </cell>
           <cell r="AA21">
-            <v>7476</v>
+            <v>7661.9047619047615</v>
           </cell>
           <cell r="AB21">
-            <v>10.21669341894061</v>
+            <v>9.9688004972032331</v>
           </cell>
           <cell r="AC21">
-            <v>1.021669341894061</v>
+            <v>0.99688004972032329</v>
           </cell>
           <cell r="AD21">
-            <v>162</v>
+            <v>-23.904761904761472</v>
           </cell>
           <cell r="AE21">
-            <v>3738</v>
+            <v>3830.9523809523807</v>
           </cell>
           <cell r="AF21">
-            <v>3576</v>
+            <v>3854.8571428571422</v>
           </cell>
           <cell r="AG21">
             <v>141.44444444444446</v>
@@ -6605,22 +6606,22 @@
             <v>4099.4900000000007</v>
           </cell>
           <cell r="AA22">
-            <v>3506.5</v>
+            <v>3628.0952380952381</v>
           </cell>
           <cell r="AB22">
-            <v>10.725794952231571</v>
+            <v>10.366321039506497</v>
           </cell>
           <cell r="AC22">
-            <v>1.0725794952231571</v>
+            <v>1.0366321039506496</v>
           </cell>
           <cell r="AD22">
-            <v>254.5</v>
+            <v>132.90476190476193</v>
           </cell>
           <cell r="AE22">
-            <v>1753.25</v>
+            <v>1814.047619047619</v>
           </cell>
           <cell r="AF22">
-            <v>1498.75</v>
+            <v>1681.1428571428571</v>
           </cell>
           <cell r="AG22">
             <v>69.648148148148152</v>
@@ -6697,22 +6698,22 @@
             <v>38473.719999999994</v>
           </cell>
           <cell r="AA23">
-            <v>34029.5</v>
+            <v>35215.238095238099</v>
           </cell>
           <cell r="AB23">
-            <v>9.7465434402503721</v>
+            <v>9.418365967113802</v>
           </cell>
           <cell r="AC23">
-            <v>0.97465434402503714</v>
+            <v>0.9418365967113802</v>
           </cell>
           <cell r="AD23">
-            <v>-862.5</v>
+            <v>-2048.238095238099</v>
           </cell>
           <cell r="AE23">
-            <v>17014.75</v>
+            <v>17607.61904761905</v>
           </cell>
           <cell r="AF23">
-            <v>17877.25</v>
+            <v>19655.857142857149</v>
           </cell>
           <cell r="AG23">
             <v>614.2037037037037</v>
@@ -6789,22 +6790,22 @@
             <v>29054.519999999997</v>
           </cell>
           <cell r="AA24">
-            <v>22193</v>
+            <v>23050</v>
           </cell>
           <cell r="AB24">
-            <v>11.285991078267921</v>
+            <v>10.866377440347071</v>
           </cell>
           <cell r="AC24">
-            <v>1.1285991078267923</v>
+            <v>1.0866377440347073</v>
           </cell>
           <cell r="AD24">
-            <v>2854</v>
+            <v>1997</v>
           </cell>
           <cell r="AE24">
-            <v>11096.5</v>
+            <v>11525</v>
           </cell>
           <cell r="AF24">
-            <v>8242.5</v>
+            <v>9528</v>
           </cell>
           <cell r="AG24">
             <v>463.83333333333331</v>
@@ -6881,22 +6882,22 @@
             <v>30040.519999999997</v>
           </cell>
           <cell r="AA25">
-            <v>21481.5</v>
+            <v>22664.761904761905</v>
           </cell>
           <cell r="AB25">
-            <v>12.055489607336545</v>
+            <v>11.426107235902178</v>
           </cell>
           <cell r="AC25">
-            <v>1.2055489607336545</v>
+            <v>1.1426107235902176</v>
           </cell>
           <cell r="AD25">
-            <v>4415.5</v>
+            <v>3232.2380952380954</v>
           </cell>
           <cell r="AE25">
-            <v>10740.75</v>
+            <v>11332.380952380952</v>
           </cell>
           <cell r="AF25">
-            <v>6325.25</v>
+            <v>8100.1428571428569</v>
           </cell>
           <cell r="AG25">
             <v>479.57407407407408</v>
@@ -6973,22 +6974,22 @@
             <v>34369.64</v>
           </cell>
           <cell r="AA26">
-            <v>25732.5</v>
+            <v>26740</v>
           </cell>
           <cell r="AB26">
-            <v>11.514232973865735</v>
+            <v>11.080403889304414</v>
           </cell>
           <cell r="AC26">
-            <v>1.1514232973865735</v>
+            <v>1.1080403889304413</v>
           </cell>
           <cell r="AD26">
-            <v>3896.5</v>
+            <v>2889</v>
           </cell>
           <cell r="AE26">
-            <v>12866.25</v>
+            <v>13370</v>
           </cell>
           <cell r="AF26">
-            <v>8969.75</v>
+            <v>10481</v>
           </cell>
           <cell r="AG26">
             <v>548.68518518518522</v>
@@ -7065,22 +7066,22 @@
             <v>1758.56</v>
           </cell>
           <cell r="AA27">
-            <v>97</v>
+            <v>116.66666666666666</v>
           </cell>
           <cell r="AB27">
-            <v>156.28865979381445</v>
+            <v>129.94285714285715</v>
           </cell>
           <cell r="AC27">
-            <v>15.628865979381443</v>
+            <v>12.994285714285715</v>
           </cell>
           <cell r="AD27">
-            <v>1419</v>
+            <v>1399.3333333333333</v>
           </cell>
           <cell r="AE27">
-            <v>48.5</v>
+            <v>58.333333333333329</v>
           </cell>
           <cell r="AF27">
-            <v>-1370.5</v>
+            <v>-1341</v>
           </cell>
           <cell r="AG27">
             <v>28.074074074074073</v>
@@ -7112,13 +7113,13 @@
             <v>3519.4399999999996</v>
           </cell>
           <cell r="L28">
-            <v>8.2647779896485964</v>
+            <v>7.7956686651168479</v>
           </cell>
           <cell r="M28">
-            <v>8076.2000000000007</v>
+            <v>8562.1904761904771</v>
           </cell>
           <cell r="N28">
-            <v>-2472.5</v>
+            <v>-2803.8571428571431</v>
           </cell>
           <cell r="O28">
             <v>251</v>
@@ -7157,22 +7158,22 @@
             <v>5583.08</v>
           </cell>
           <cell r="AA28">
-            <v>3671</v>
+            <v>3891.9047619047619</v>
           </cell>
           <cell r="AB28">
-            <v>13.11086897303187</v>
+            <v>12.366695215954973</v>
           </cell>
           <cell r="AC28">
-            <v>1.3110868973031871</v>
+            <v>1.2366695215954973</v>
           </cell>
           <cell r="AD28">
-            <v>1142</v>
+            <v>921.09523809523807</v>
           </cell>
           <cell r="AE28">
-            <v>1835.5</v>
+            <v>1945.952380952381</v>
           </cell>
           <cell r="AF28">
-            <v>693.5</v>
+            <v>1024.8571428571429</v>
           </cell>
           <cell r="AG28">
             <v>89.129629629629633</v>
@@ -7204,13 +7205,13 @@
             <v>3309.4799999999996</v>
           </cell>
           <cell r="L29">
-            <v>6.8796720520858452</v>
+            <v>6.6599599822143176</v>
           </cell>
           <cell r="M29">
-            <v>9123.4</v>
+            <v>9424.3809523809523</v>
           </cell>
           <cell r="N29">
-            <v>-3367.5</v>
+            <v>-3572.7142857142853</v>
           </cell>
           <cell r="O29">
             <v>236</v>
@@ -7249,22 +7250,22 @@
             <v>5281.48</v>
           </cell>
           <cell r="AA29">
-            <v>4147</v>
+            <v>4283.8095238095239</v>
           </cell>
           <cell r="AB29">
-            <v>10.97902097902098</v>
+            <v>10.628390395731435</v>
           </cell>
           <cell r="AC29">
-            <v>1.0979020979020979</v>
+            <v>1.0628390395731435</v>
           </cell>
           <cell r="AD29">
-            <v>406</v>
+            <v>269.19047619047615</v>
           </cell>
           <cell r="AE29">
-            <v>2073.5</v>
+            <v>2141.9047619047619</v>
           </cell>
           <cell r="AF29">
-            <v>1667.5</v>
+            <v>1872.7142857142858</v>
           </cell>
           <cell r="AG29">
             <v>84.31481481481481</v>
@@ -7296,13 +7297,13 @@
             <v>3259.6</v>
           </cell>
           <cell r="L30">
-            <v>7.3148509696733051</v>
+            <v>7.1910796977821105</v>
           </cell>
           <cell r="M30">
-            <v>8451.2999999999993</v>
+            <v>8596.7619047619046</v>
           </cell>
           <cell r="N30">
-            <v>-2952.25</v>
+            <v>-3051.4285714285716</v>
           </cell>
           <cell r="O30">
             <v>236</v>
@@ -7341,22 +7342,22 @@
             <v>6992.48</v>
           </cell>
           <cell r="AA30">
-            <v>3841.5</v>
+            <v>3907.6190476190477</v>
           </cell>
           <cell r="AB30">
-            <v>15.691787062345439</v>
+            <v>15.42627345844504</v>
           </cell>
           <cell r="AC30">
-            <v>1.5691787062345437</v>
+            <v>1.5426273458445039</v>
           </cell>
           <cell r="AD30">
-            <v>2186.5</v>
+            <v>2120.3809523809523</v>
           </cell>
           <cell r="AE30">
-            <v>1920.75</v>
+            <v>1953.8095238095239</v>
           </cell>
           <cell r="AF30">
-            <v>-265.75</v>
+            <v>-166.57142857142844</v>
           </cell>
           <cell r="AG30">
             <v>111.62962962962963</v>
@@ -7433,22 +7434,22 @@
             <v>5045.2800000000007</v>
           </cell>
           <cell r="AA31">
-            <v>2327.5</v>
+            <v>2420</v>
           </cell>
           <cell r="AB31">
-            <v>5.8904403866809885</v>
+            <v>5.6652892561983474</v>
           </cell>
           <cell r="AC31">
-            <v>0.58904403866809885</v>
+            <v>0.5665289256198347</v>
           </cell>
           <cell r="AD31">
-            <v>-956.5</v>
+            <v>-1049</v>
           </cell>
           <cell r="AE31">
-            <v>1163.75</v>
+            <v>1210</v>
           </cell>
           <cell r="AF31">
-            <v>2120.25</v>
+            <v>2259</v>
           </cell>
           <cell r="AG31">
             <v>85.6875</v>
@@ -7525,22 +7526,22 @@
             <v>3606.4</v>
           </cell>
           <cell r="AA32">
-            <v>1355.5</v>
+            <v>1421.9047619047619</v>
           </cell>
           <cell r="AB32">
-            <v>7.2298045001844331</v>
+            <v>6.8921634293369047</v>
           </cell>
           <cell r="AC32">
-            <v>0.72298045001844335</v>
+            <v>0.6892163429336905</v>
           </cell>
           <cell r="AD32">
-            <v>-375.5</v>
+            <v>-441.90476190476193</v>
           </cell>
           <cell r="AE32">
-            <v>677.75</v>
+            <v>710.95238095238096</v>
           </cell>
           <cell r="AF32">
-            <v>1053.25</v>
+            <v>1152.8571428571429</v>
           </cell>
           <cell r="AG32">
             <v>61.25</v>
@@ -7617,22 +7618,22 @@
             <v>13703.300000000001</v>
           </cell>
           <cell r="AA33">
-            <v>4963.5</v>
+            <v>5130.9523809523807</v>
           </cell>
           <cell r="AB33">
-            <v>6.6525637151203787</v>
+            <v>6.4354524361948959</v>
           </cell>
           <cell r="AC33">
-            <v>0.66525637151203787</v>
+            <v>0.64354524361948962</v>
           </cell>
           <cell r="AD33">
-            <v>-1661.5</v>
+            <v>-1828.9523809523807</v>
           </cell>
           <cell r="AE33">
-            <v>2481.75</v>
+            <v>2565.4761904761904</v>
           </cell>
           <cell r="AF33">
-            <v>4143.25</v>
+            <v>4394.4285714285706</v>
           </cell>
           <cell r="AG33">
             <v>206.375</v>
@@ -7709,22 +7710,22 @@
             <v>26174.050000000003</v>
           </cell>
           <cell r="AA34">
-            <v>7850</v>
+            <v>8113.8095238095239</v>
           </cell>
           <cell r="AB34">
-            <v>8.0343949044585994</v>
+            <v>7.7731674394037205</v>
           </cell>
           <cell r="AC34">
-            <v>0.80343949044585983</v>
+            <v>0.77731674394037209</v>
           </cell>
           <cell r="AD34">
-            <v>-1543</v>
+            <v>-1806.8095238095239</v>
           </cell>
           <cell r="AE34">
-            <v>3925</v>
+            <v>4056.9047619047619</v>
           </cell>
           <cell r="AF34">
-            <v>5468</v>
+            <v>5863.7142857142862</v>
           </cell>
           <cell r="AG34">
             <v>394.1875</v>
@@ -7801,7 +7802,7 @@
             <v>0</v>
           </cell>
           <cell r="AA35">
-            <v>637</v>
+            <v>749.52380952380952</v>
           </cell>
           <cell r="AB35">
             <v>0</v>
@@ -7810,13 +7811,13 @@
             <v>0</v>
           </cell>
           <cell r="AD35">
-            <v>-637</v>
+            <v>-749.52380952380952</v>
           </cell>
           <cell r="AE35">
-            <v>318.5</v>
+            <v>374.76190476190476</v>
           </cell>
           <cell r="AF35">
-            <v>955.5</v>
+            <v>1124.2857142857142</v>
           </cell>
           <cell r="AG35">
             <v>0</v>
@@ -7893,22 +7894,22 @@
             <v>2253.4500000000003</v>
           </cell>
           <cell r="AA36">
-            <v>7096.5</v>
+            <v>7879.5238095238092</v>
           </cell>
           <cell r="AB36">
-            <v>0.76516592686535623</v>
+            <v>0.68912793859914179</v>
           </cell>
           <cell r="AC36">
-            <v>7.6516592686535614E-2</v>
+            <v>6.8912793859914181E-2</v>
           </cell>
           <cell r="AD36">
-            <v>-6553.5</v>
+            <v>-7336.5238095238092</v>
           </cell>
           <cell r="AE36">
-            <v>3548.25</v>
+            <v>3939.7619047619046</v>
           </cell>
           <cell r="AF36">
-            <v>10101.75</v>
+            <v>11276.285714285714</v>
           </cell>
           <cell r="AG36">
             <v>33.9375</v>
@@ -7985,22 +7986,22 @@
             <v>16573.84</v>
           </cell>
           <cell r="AA37">
-            <v>11629.5</v>
+            <v>12737.142857142859</v>
           </cell>
           <cell r="AB37">
-            <v>8.7432821703426633</v>
+            <v>7.9829519964109465</v>
           </cell>
           <cell r="AC37">
-            <v>0.87432821703426633</v>
+            <v>0.79829519964109452</v>
           </cell>
           <cell r="AD37">
-            <v>-1461.5</v>
+            <v>-2569.1428571428587</v>
           </cell>
           <cell r="AE37">
-            <v>5814.75</v>
+            <v>6368.5714285714294</v>
           </cell>
           <cell r="AF37">
-            <v>7276.25</v>
+            <v>8937.7142857142881</v>
           </cell>
           <cell r="AG37">
             <v>188.2962962962963</v>
@@ -8077,22 +8078,22 @@
             <v>16068.539999999999</v>
           </cell>
           <cell r="AA38">
-            <v>5102.5</v>
+            <v>5291.9047619047615</v>
           </cell>
           <cell r="AB38">
-            <v>19.319941205291524</v>
+            <v>18.628453162962298</v>
           </cell>
           <cell r="AC38">
-            <v>1.9319941205291524</v>
+            <v>1.8628453162962297</v>
           </cell>
           <cell r="AD38">
-            <v>4755.5</v>
+            <v>4566.0952380952385</v>
           </cell>
           <cell r="AE38">
-            <v>2551.25</v>
+            <v>2645.9523809523807</v>
           </cell>
           <cell r="AF38">
-            <v>-2204.25</v>
+            <v>-1920.1428571428578</v>
           </cell>
           <cell r="AG38">
             <v>182.55555555555554</v>
@@ -8169,22 +8170,22 @@
             <v>3204.58</v>
           </cell>
           <cell r="AA39">
-            <v>4006</v>
+            <v>4018.5714285714284</v>
           </cell>
           <cell r="AB39">
-            <v>4.9076385421867199</v>
+            <v>4.8922858158549598</v>
           </cell>
           <cell r="AC39">
-            <v>0.49076385421867197</v>
+            <v>0.48922858158549593</v>
           </cell>
           <cell r="AD39">
-            <v>-2040</v>
+            <v>-2052.5714285714284</v>
           </cell>
           <cell r="AE39">
-            <v>2003</v>
+            <v>2009.2857142857142</v>
           </cell>
           <cell r="AF39">
-            <v>4043</v>
+            <v>4061.8571428571427</v>
           </cell>
           <cell r="AG39">
             <v>36.407407407407405</v>
@@ -8261,22 +8262,22 @@
             <v>7409.98</v>
           </cell>
           <cell r="AA40">
-            <v>709</v>
+            <v>760.95238095238096</v>
           </cell>
           <cell r="AB40">
-            <v>64.118476727785605</v>
+            <v>59.740926157697118</v>
           </cell>
           <cell r="AC40">
-            <v>6.4118476727785616</v>
+            <v>5.9740926157697123</v>
           </cell>
           <cell r="AD40">
-            <v>3837</v>
+            <v>3785.0476190476193</v>
           </cell>
           <cell r="AE40">
-            <v>354.5</v>
+            <v>380.47619047619048</v>
           </cell>
           <cell r="AF40">
-            <v>-3482.5</v>
+            <v>-3404.5714285714289</v>
           </cell>
           <cell r="AG40">
             <v>84.18518518518519</v>
@@ -8537,22 +8538,22 @@
             <v>4065.15</v>
           </cell>
           <cell r="AA43">
-            <v>1342.5</v>
+            <v>1433.3333333333335</v>
           </cell>
           <cell r="AB43">
-            <v>4.9236499068901303</v>
+            <v>4.6116279069767439</v>
           </cell>
           <cell r="AC43">
-            <v>0.49236499068901302</v>
+            <v>0.46116279069767435</v>
           </cell>
           <cell r="AD43">
-            <v>-681.5</v>
+            <v>-772.33333333333348</v>
           </cell>
           <cell r="AE43">
-            <v>671.25</v>
+            <v>716.66666666666674</v>
           </cell>
           <cell r="AF43">
-            <v>1352.75</v>
+            <v>1489.0000000000002</v>
           </cell>
           <cell r="AG43">
             <v>12.24074074074074</v>
@@ -8629,22 +8630,22 @@
             <v>6980.25</v>
           </cell>
           <cell r="AA44">
-            <v>6411</v>
+            <v>6521.9047619047615</v>
           </cell>
           <cell r="AB44">
-            <v>1.7703946342224302</v>
+            <v>1.7402891355140189</v>
           </cell>
           <cell r="AC44">
-            <v>0.17703946342224303</v>
+            <v>0.17402891355140188</v>
           </cell>
           <cell r="AD44">
-            <v>-5276</v>
+            <v>-5386.9047619047615</v>
           </cell>
           <cell r="AE44">
-            <v>3205.5</v>
+            <v>3260.9523809523807</v>
           </cell>
           <cell r="AF44">
-            <v>8481.5</v>
+            <v>8647.8571428571413</v>
           </cell>
           <cell r="AG44">
             <v>21.018518518518519</v>
@@ -8721,22 +8722,22 @@
             <v>4816.32</v>
           </cell>
           <cell r="AA45">
-            <v>6201</v>
+            <v>6290.4761904761908</v>
           </cell>
           <cell r="AB45">
-            <v>6.6956942428640538</v>
+            <v>6.600454201362604</v>
           </cell>
           <cell r="AC45">
-            <v>0.66956942428640542</v>
+            <v>0.66004542013626033</v>
           </cell>
           <cell r="AD45">
-            <v>-2049</v>
+            <v>-2138.4761904761908</v>
           </cell>
           <cell r="AE45">
-            <v>3100.5</v>
+            <v>3145.2380952380954</v>
           </cell>
           <cell r="AF45">
-            <v>5149.5</v>
+            <v>5283.7142857142862</v>
           </cell>
           <cell r="AG45">
             <v>76.888888888888886</v>
@@ -8813,22 +8814,22 @@
             <v>9920.32</v>
           </cell>
           <cell r="AA46">
-            <v>8288.5</v>
+            <v>8521.9047619047615</v>
           </cell>
           <cell r="AB46">
-            <v>10.317910357724557</v>
+            <v>10.035315154224408</v>
           </cell>
           <cell r="AC46">
-            <v>1.0317910357724558</v>
+            <v>1.0035315154224409</v>
           </cell>
           <cell r="AD46">
-            <v>263.5</v>
+            <v>30.095238095238528</v>
           </cell>
           <cell r="AE46">
-            <v>4144.25</v>
+            <v>4260.9523809523807</v>
           </cell>
           <cell r="AF46">
-            <v>3880.75</v>
+            <v>4230.8571428571422</v>
           </cell>
           <cell r="AG46">
             <v>158.37037037037038</v>
@@ -8905,22 +8906,22 @@
             <v>7810.28</v>
           </cell>
           <cell r="AA47">
-            <v>5643.5</v>
+            <v>5790</v>
           </cell>
           <cell r="AB47">
-            <v>11.930539558784442</v>
+            <v>11.6286701208981</v>
           </cell>
           <cell r="AC47">
-            <v>1.1930539558784443</v>
+            <v>1.1628670120898099</v>
           </cell>
           <cell r="AD47">
-            <v>1089.5</v>
+            <v>943</v>
           </cell>
           <cell r="AE47">
-            <v>2821.75</v>
+            <v>2895</v>
           </cell>
           <cell r="AF47">
-            <v>1732.25</v>
+            <v>1952</v>
           </cell>
           <cell r="AG47">
             <v>124.68518518518519</v>
@@ -8997,22 +8998,22 @@
             <v>6063.32</v>
           </cell>
           <cell r="AA48">
-            <v>23.5</v>
+            <v>24.761904761904763</v>
           </cell>
           <cell r="AB48">
-            <v>2224.255319148936</v>
+            <v>2110.9038461538462</v>
           </cell>
           <cell r="AC48">
-            <v>222.42553191489361</v>
+            <v>211.09038461538461</v>
           </cell>
           <cell r="AD48">
-            <v>5203.5</v>
+            <v>5202.2380952380954</v>
           </cell>
           <cell r="AE48">
-            <v>11.75</v>
+            <v>12.380952380952381</v>
           </cell>
           <cell r="AF48">
-            <v>-5191.75</v>
+            <v>-5189.8571428571431</v>
           </cell>
           <cell r="AG48">
             <v>96.796296296296291</v>
@@ -9181,7 +9182,7 @@
             <v>198</v>
           </cell>
           <cell r="AA50">
-            <v>544</v>
+            <v>553.33333333333337</v>
           </cell>
           <cell r="AB50">
             <v>0</v>
@@ -9190,13 +9191,13 @@
             <v>0</v>
           </cell>
           <cell r="AD50">
-            <v>-533</v>
+            <v>-542.33333333333337</v>
           </cell>
           <cell r="AE50">
-            <v>272</v>
+            <v>276.66666666666669</v>
           </cell>
           <cell r="AF50">
-            <v>805</v>
+            <v>819</v>
           </cell>
           <cell r="AG50">
             <v>5.5</v>
@@ -9273,22 +9274,22 @@
             <v>49.879999999999995</v>
           </cell>
           <cell r="AA51">
-            <v>4.5</v>
+            <v>4.2857142857142856</v>
           </cell>
           <cell r="AB51">
-            <v>95.555555555555557</v>
+            <v>100.33333333333334</v>
           </cell>
           <cell r="AC51">
-            <v>9.5555555555555554</v>
+            <v>10.033333333333333</v>
           </cell>
           <cell r="AD51">
-            <v>38.5</v>
+            <v>38.714285714285715</v>
           </cell>
           <cell r="AE51">
-            <v>2.25</v>
+            <v>2.1428571428571428</v>
           </cell>
           <cell r="AF51">
-            <v>-36.25</v>
+            <v>-36.571428571428569</v>
           </cell>
           <cell r="AG51">
             <v>1.075</v>
@@ -9457,22 +9458,22 @@
             <v>4.6399999999999997</v>
           </cell>
           <cell r="AA53">
-            <v>5290</v>
+            <v>5544.2857142857147</v>
           </cell>
           <cell r="AB53">
-            <v>7.5614366729678641E-3</v>
+            <v>7.2146354032465859E-3</v>
           </cell>
           <cell r="AC53">
-            <v>7.5614366729678643E-4</v>
+            <v>7.2146354032465859E-4</v>
           </cell>
           <cell r="AD53">
-            <v>-5286</v>
+            <v>-5540.2857142857147</v>
           </cell>
           <cell r="AE53">
-            <v>2645</v>
+            <v>2772.1428571428573</v>
           </cell>
           <cell r="AF53">
-            <v>7931</v>
+            <v>8312.4285714285725</v>
           </cell>
           <cell r="AG53">
             <v>0.1</v>
@@ -9549,22 +9550,22 @@
             <v>18284.13</v>
           </cell>
           <cell r="AA54">
-            <v>788.5</v>
+            <v>1328.0952380952381</v>
           </cell>
           <cell r="AB54">
-            <v>286.27774254914397</v>
+            <v>169.96522050914308</v>
           </cell>
           <cell r="AC54">
-            <v>28.627774254914396</v>
+            <v>16.996522050914308</v>
           </cell>
           <cell r="AD54">
-            <v>21784.5</v>
+            <v>21244.904761904763</v>
           </cell>
           <cell r="AE54">
-            <v>394.25</v>
+            <v>664.04761904761904</v>
           </cell>
           <cell r="AF54">
-            <v>-21390.25</v>
+            <v>-20580.857142857145</v>
           </cell>
           <cell r="AG54">
             <v>1881.0833333333333</v>
@@ -9641,22 +9642,22 @@
             <v>23675.49</v>
           </cell>
           <cell r="AA55">
-            <v>2964.5</v>
+            <v>2961.4285714285716</v>
           </cell>
           <cell r="AB55">
-            <v>98.596727947377303</v>
+            <v>98.698986975397972</v>
           </cell>
           <cell r="AC55">
-            <v>9.8596727947377296</v>
+            <v>9.8698986975397975</v>
           </cell>
           <cell r="AD55">
-            <v>26264.5</v>
+            <v>26267.571428571428</v>
           </cell>
           <cell r="AE55">
-            <v>1482.25</v>
+            <v>1480.7142857142858</v>
           </cell>
           <cell r="AF55">
-            <v>-24782.25</v>
+            <v>-24786.857142857141</v>
           </cell>
           <cell r="AG55">
             <v>2435.75</v>
@@ -9733,22 +9734,22 @@
             <v>13081.5</v>
           </cell>
           <cell r="AA56">
-            <v>5246</v>
+            <v>5287.1428571428569</v>
           </cell>
           <cell r="AB56">
-            <v>30.785360274494852</v>
+            <v>30.545798432855989</v>
           </cell>
           <cell r="AC56">
-            <v>3.0785360274494855</v>
+            <v>3.0545798432855986</v>
           </cell>
           <cell r="AD56">
-            <v>10904</v>
+            <v>10862.857142857143</v>
           </cell>
           <cell r="AE56">
-            <v>2623</v>
+            <v>2643.5714285714284</v>
           </cell>
           <cell r="AF56">
-            <v>-8281</v>
+            <v>-8219.2857142857138</v>
           </cell>
           <cell r="AG56">
             <v>1345.8333333333333</v>
@@ -9825,22 +9826,22 @@
             <v>15625.710000000001</v>
           </cell>
           <cell r="AA57">
-            <v>3077</v>
+            <v>3055.7142857142853</v>
           </cell>
           <cell r="AB57">
-            <v>62.69418264543387</v>
+            <v>63.13090229079009</v>
           </cell>
           <cell r="AC57">
-            <v>6.2694182645433862</v>
+            <v>6.3130902290790099</v>
           </cell>
           <cell r="AD57">
-            <v>16214</v>
+            <v>16235.285714285714</v>
           </cell>
           <cell r="AE57">
-            <v>1538.5</v>
+            <v>1527.8571428571427</v>
           </cell>
           <cell r="AF57">
-            <v>-14675.5</v>
+            <v>-14707.428571428571</v>
           </cell>
           <cell r="AG57">
             <v>1607.5833333333333</v>
@@ -9917,22 +9918,22 @@
             <v>1873.3000000000002</v>
           </cell>
           <cell r="AA58">
-            <v>2912</v>
+            <v>2899.0476190476193</v>
           </cell>
           <cell r="AB58">
-            <v>2.4553571428571428</v>
+            <v>2.4663272010512483</v>
           </cell>
           <cell r="AC58">
-            <v>0.24553571428571427</v>
+            <v>0.24663272010512483</v>
           </cell>
           <cell r="AD58">
-            <v>-2197</v>
+            <v>-2184.0476190476193</v>
           </cell>
           <cell r="AE58">
-            <v>1456</v>
+            <v>1449.5238095238096</v>
           </cell>
           <cell r="AF58">
-            <v>3653</v>
+            <v>3633.5714285714289</v>
           </cell>
           <cell r="AG58">
             <v>119.16666666666667</v>
@@ -10009,22 +10010,22 @@
             <v>1011.32</v>
           </cell>
           <cell r="AA59">
-            <v>563</v>
+            <v>577.14285714285711</v>
           </cell>
           <cell r="AB59">
-            <v>6.8561278863232689</v>
+            <v>6.6881188118811892</v>
           </cell>
           <cell r="AC59">
-            <v>0.68561278863232678</v>
+            <v>0.66881188118811885</v>
           </cell>
           <cell r="AD59">
-            <v>-177</v>
+            <v>-191.14285714285711</v>
           </cell>
           <cell r="AE59">
-            <v>281.5</v>
+            <v>288.57142857142856</v>
           </cell>
           <cell r="AF59">
-            <v>458.5</v>
+            <v>479.71428571428567</v>
           </cell>
           <cell r="AG59">
             <v>64.333333333333329</v>
@@ -10101,22 +10102,22 @@
             <v>780.76</v>
           </cell>
           <cell r="AA60">
-            <v>1045.5</v>
+            <v>1047.1428571428571</v>
           </cell>
           <cell r="AB60">
-            <v>2.8503108560497372</v>
+            <v>2.8458390177353343</v>
           </cell>
           <cell r="AC60">
-            <v>0.2850310856049737</v>
+            <v>0.28458390177353343</v>
           </cell>
           <cell r="AD60">
-            <v>-747.5</v>
+            <v>-749.14285714285711</v>
           </cell>
           <cell r="AE60">
-            <v>522.75</v>
+            <v>523.57142857142856</v>
           </cell>
           <cell r="AF60">
-            <v>1270.25</v>
+            <v>1272.7142857142858</v>
           </cell>
           <cell r="AG60">
             <v>49.666666666666664</v>
@@ -10193,22 +10194,22 @@
             <v>382.52000000000004</v>
           </cell>
           <cell r="AA61">
-            <v>492</v>
+            <v>493.33333333333337</v>
           </cell>
           <cell r="AB61">
-            <v>2.9674796747967478</v>
+            <v>2.9594594594594592</v>
           </cell>
           <cell r="AC61">
-            <v>0.2967479674796748</v>
+            <v>0.29594594594594592</v>
           </cell>
           <cell r="AD61">
-            <v>-346</v>
+            <v>-347.33333333333337</v>
           </cell>
           <cell r="AE61">
-            <v>246</v>
+            <v>246.66666666666669</v>
           </cell>
           <cell r="AF61">
-            <v>592</v>
+            <v>594</v>
           </cell>
           <cell r="AG61">
             <v>24.333333333333332</v>
@@ -10219,7 +10220,7 @@
             <v>Units Produce</v>
           </cell>
           <cell r="AF62">
-            <v>151316.75</v>
+            <v>166285.14285714287</v>
           </cell>
         </row>
       </sheetData>
@@ -10239,6 +10240,7 @@
       <sheetData sheetId="23"/>
       <sheetData sheetId="24"/>
       <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10563,212 +10565,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="63" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="63"/>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="63"/>
+      <c r="AB1" s="66"/>
+      <c r="AC1" s="66"/>
+      <c r="AD1" s="66"/>
+      <c r="AE1" s="66"/>
+      <c r="AF1" s="66"/>
+      <c r="AG1" s="66"/>
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
-      <c r="AA2" s="63"/>
-      <c r="AB2" s="63"/>
-      <c r="AC2" s="63"/>
-      <c r="AD2" s="63"/>
-      <c r="AE2" s="63"/>
-      <c r="AF2" s="63"/>
-      <c r="AG2" s="63"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="66"/>
+      <c r="AC2" s="66"/>
+      <c r="AD2" s="66"/>
+      <c r="AE2" s="66"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="62"/>
-      <c r="U3" s="62"/>
-      <c r="V3" s="62"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="62"/>
-      <c r="AA3" s="63"/>
-      <c r="AB3" s="63"/>
-      <c r="AC3" s="63"/>
-      <c r="AD3" s="63"/>
-      <c r="AE3" s="63"/>
-      <c r="AF3" s="63"/>
-      <c r="AG3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="66"/>
+      <c r="AB3" s="66"/>
+      <c r="AC3" s="66"/>
+      <c r="AD3" s="66"/>
+      <c r="AE3" s="66"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="62"/>
-      <c r="W4" s="62"/>
-      <c r="X4" s="62"/>
-      <c r="Y4" s="62"/>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="63"/>
-      <c r="AB4" s="63"/>
-      <c r="AC4" s="63"/>
-      <c r="AD4" s="63"/>
-      <c r="AE4" s="63"/>
-      <c r="AF4" s="63"/>
-      <c r="AG4" s="63"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="62"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="62"/>
-      <c r="X5" s="62"/>
-      <c r="Y5" s="62"/>
-      <c r="Z5" s="62"/>
-      <c r="AA5" s="63"/>
-      <c r="AB5" s="63"/>
-      <c r="AC5" s="63"/>
-      <c r="AD5" s="63"/>
-      <c r="AE5" s="63"/>
-      <c r="AF5" s="63"/>
-      <c r="AG5" s="63"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="66"/>
+      <c r="AB5" s="66"/>
+      <c r="AC5" s="66"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="62"/>
-      <c r="X6" s="62"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="63"/>
-      <c r="AB6" s="63"/>
-      <c r="AC6" s="63"/>
-      <c r="AD6" s="63"/>
-      <c r="AE6" s="63"/>
-      <c r="AF6" s="63"/>
-      <c r="AG6" s="63"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="66"/>
+      <c r="AB6" s="66"/>
+      <c r="AC6" s="66"/>
+      <c r="AD6" s="66"/>
+      <c r="AE6" s="66"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
@@ -11138,28 +11140,28 @@
         <v>13606.800000000001</v>
       </c>
       <c r="AA13" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA13</f>
-        <v>11472.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA13</f>
+        <v>11880.952380952382</v>
       </c>
       <c r="AB13" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB13</f>
-        <v>8.7208542166049252</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB13</f>
+        <v>8.4210420841683362</v>
       </c>
       <c r="AC13" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC13</f>
-        <v>0.87208542166049252</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC13</f>
+        <v>0.84210420841683364</v>
       </c>
       <c r="AD13" s="27">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD13</f>
-        <v>-1467.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD13</f>
+        <v>-1875.9523809523816</v>
       </c>
       <c r="AE13" s="27">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE13</f>
-        <v>5736.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE13</f>
+        <v>5940.4761904761908</v>
       </c>
       <c r="AF13" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF13</f>
-        <v>7203.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF13</f>
+        <v>7816.4285714285725</v>
       </c>
       <c r="AG13" s="27">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG13</f>
@@ -11266,28 +11268,28 @@
         <v>888.81000000000006</v>
       </c>
       <c r="AA14" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA14</f>
-        <v>750.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA14</f>
+        <v>763.80952380952385</v>
       </c>
       <c r="AB14" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB14</f>
-        <v>7.4483677548301133</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB14</f>
+        <v>7.3185785536159607</v>
       </c>
       <c r="AC14" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC14</f>
-        <v>0.7448367754830113</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC14</f>
+        <v>0.73185785536159598</v>
       </c>
       <c r="AD14" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD14</f>
-        <v>-191.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD14</f>
+        <v>-204.80952380952385</v>
       </c>
       <c r="AE14" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE14</f>
-        <v>375.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE14</f>
+        <v>381.90476190476193</v>
       </c>
       <c r="AF14" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF14</f>
-        <v>566.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF14</f>
+        <v>586.71428571428578</v>
       </c>
       <c r="AG14" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG14</f>
@@ -11394,28 +11396,28 @@
         <v>6966.9599999999991</v>
       </c>
       <c r="AA15" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA15</f>
-        <v>4851.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA15</f>
+        <v>5094.7619047619046</v>
       </c>
       <c r="AB15" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB15</f>
-        <v>7.0741007935689995</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB15</f>
+        <v>6.7363304981773995</v>
       </c>
       <c r="AC15" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC15</f>
-        <v>0.70741007935689992</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC15</f>
+        <v>0.67363304981773997</v>
       </c>
       <c r="AD15" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD15</f>
-        <v>-1419.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD15</f>
+        <v>-1662.7619047619046</v>
       </c>
       <c r="AE15" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE15</f>
-        <v>2425.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE15</f>
+        <v>2547.3809523809523</v>
       </c>
       <c r="AF15" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF15</f>
-        <v>3845.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF15</f>
+        <v>4210.1428571428569</v>
       </c>
       <c r="AG15" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG15</f>
@@ -11522,28 +11524,28 @@
         <v>743.66</v>
       </c>
       <c r="AA16" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA16</f>
-        <v>882.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA16</f>
+        <v>980</v>
       </c>
       <c r="AB16" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB16</f>
-        <v>2.3342776203966005</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB16</f>
+        <v>2.1020408163265305</v>
       </c>
       <c r="AC16" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC16</f>
-        <v>0.23342776203966006</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC16</f>
+        <v>0.21020408163265306</v>
       </c>
       <c r="AD16" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD16</f>
-        <v>-676.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD16</f>
+        <v>-774</v>
       </c>
       <c r="AE16" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE16</f>
-        <v>441.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE16</f>
+        <v>490</v>
       </c>
       <c r="AF16" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF16</f>
-        <v>1117.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF16</f>
+        <v>1264</v>
       </c>
       <c r="AG16" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG16</f>
@@ -11650,28 +11652,28 @@
         <v>1861.36</v>
       </c>
       <c r="AA17" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA17</f>
-        <v>122</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA17</f>
+        <v>119.52380952380952</v>
       </c>
       <c r="AB17" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB17</f>
-        <v>17.377049180327869</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB17</f>
+        <v>17.737051792828684</v>
       </c>
       <c r="AC17" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC17</f>
-        <v>1.7377049180327868</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC17</f>
+        <v>1.7737051792828686</v>
       </c>
       <c r="AD17" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD17</f>
-        <v>90</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD17</f>
+        <v>92.476190476190482</v>
       </c>
       <c r="AE17" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE17</f>
-        <v>61</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE17</f>
+        <v>59.761904761904759</v>
       </c>
       <c r="AF17" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF17</f>
-        <v>-29</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF17</f>
+        <v>-32.714285714285722</v>
       </c>
       <c r="AG17" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG17</f>
@@ -11778,28 +11780,28 @@
         <v>5277.51</v>
       </c>
       <c r="AA18" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA18</f>
-        <v>14153</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA18</f>
+        <v>14603.333333333332</v>
       </c>
       <c r="AB18" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB18</f>
-        <v>5.9188864551685159</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB18</f>
+        <v>5.736361561287378</v>
       </c>
       <c r="AC18" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC18</f>
-        <v>0.5918886455168515</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC18</f>
+        <v>0.57363615612873775</v>
       </c>
       <c r="AD18" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD18</f>
-        <v>-5776</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD18</f>
+        <v>-6226.3333333333321</v>
       </c>
       <c r="AE18" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE18</f>
-        <v>7076.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE18</f>
+        <v>7301.6666666666661</v>
       </c>
       <c r="AF18" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF18</f>
-        <v>12852.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF18</f>
+        <v>13527.999999999998</v>
       </c>
       <c r="AG18" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG18</f>
@@ -11906,28 +11908,28 @@
         <v>949.41</v>
       </c>
       <c r="AA19" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA19</f>
-        <v>1398.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA19</f>
+        <v>1503.8095238095239</v>
       </c>
       <c r="AB19" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB19</f>
-        <v>10.775831247765463</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB19</f>
+        <v>10.021215959468018</v>
       </c>
       <c r="AC19" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC19</f>
-        <v>1.0775831247765464</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC19</f>
+        <v>1.0021215959468017</v>
       </c>
       <c r="AD19" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD19</f>
-        <v>108.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD19</f>
+        <v>3.1904761904761472</v>
       </c>
       <c r="AE19" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE19</f>
-        <v>699.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE19</f>
+        <v>751.90476190476193</v>
       </c>
       <c r="AF19" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF19</f>
-        <v>590.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF19</f>
+        <v>748.71428571428578</v>
       </c>
       <c r="AG19" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG19</f>
@@ -12034,28 +12036,28 @@
         <v>2498.58</v>
       </c>
       <c r="AA20" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA20</f>
-        <v>3218.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA20</f>
+        <v>3435.7142857142853</v>
       </c>
       <c r="AB20" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB20</f>
-        <v>12.322510486251359</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB20</f>
+        <v>11.543451143451144</v>
       </c>
       <c r="AC20" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC20</f>
-        <v>1.2322510486251359</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC20</f>
+        <v>1.1543451143451144</v>
       </c>
       <c r="AD20" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD20</f>
-        <v>747.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD20</f>
+        <v>530.28571428571468</v>
       </c>
       <c r="AE20" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE20</f>
-        <v>1609.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE20</f>
+        <v>1717.8571428571427</v>
       </c>
       <c r="AF20" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF20</f>
-        <v>861.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF20</f>
+        <v>1187.571428571428</v>
       </c>
       <c r="AG20" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG20</f>
@@ -12162,28 +12164,28 @@
         <v>8325.42</v>
       </c>
       <c r="AA21" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA21</f>
-        <v>7476</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA21</f>
+        <v>7661.9047619047615</v>
       </c>
       <c r="AB21" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB21</f>
-        <v>10.21669341894061</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB21</f>
+        <v>9.9688004972032331</v>
       </c>
       <c r="AC21" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC21</f>
-        <v>1.021669341894061</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC21</f>
+        <v>0.99688004972032329</v>
       </c>
       <c r="AD21" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD21</f>
-        <v>162</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD21</f>
+        <v>-23.904761904761472</v>
       </c>
       <c r="AE21" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE21</f>
-        <v>3738</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE21</f>
+        <v>3830.9523809523807</v>
       </c>
       <c r="AF21" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF21</f>
-        <v>3576</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF21</f>
+        <v>3854.8571428571422</v>
       </c>
       <c r="AG21" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG21</f>
@@ -12290,28 +12292,28 @@
         <v>4099.4900000000007</v>
       </c>
       <c r="AA22" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA22</f>
-        <v>3506.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA22</f>
+        <v>3628.0952380952381</v>
       </c>
       <c r="AB22" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB22</f>
-        <v>10.725794952231571</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB22</f>
+        <v>10.366321039506497</v>
       </c>
       <c r="AC22" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC22</f>
-        <v>1.0725794952231571</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC22</f>
+        <v>1.0366321039506496</v>
       </c>
       <c r="AD22" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD22</f>
-        <v>254.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD22</f>
+        <v>132.90476190476193</v>
       </c>
       <c r="AE22" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE22</f>
-        <v>1753.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE22</f>
+        <v>1814.047619047619</v>
       </c>
       <c r="AF22" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF22</f>
-        <v>1498.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF22</f>
+        <v>1681.1428571428571</v>
       </c>
       <c r="AG22" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG22</f>
@@ -12418,28 +12420,28 @@
         <v>38473.719999999994</v>
       </c>
       <c r="AA23" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA23</f>
-        <v>34029.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA23</f>
+        <v>35215.238095238099</v>
       </c>
       <c r="AB23" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB23</f>
-        <v>9.7465434402503721</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB23</f>
+        <v>9.418365967113802</v>
       </c>
       <c r="AC23" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC23</f>
-        <v>0.97465434402503714</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC23</f>
+        <v>0.9418365967113802</v>
       </c>
       <c r="AD23" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD23</f>
-        <v>-862.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD23</f>
+        <v>-2048.238095238099</v>
       </c>
       <c r="AE23" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE23</f>
-        <v>17014.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE23</f>
+        <v>17607.61904761905</v>
       </c>
       <c r="AF23" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF23</f>
-        <v>17877.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF23</f>
+        <v>19655.857142857149</v>
       </c>
       <c r="AG23" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG23</f>
@@ -12546,28 +12548,28 @@
         <v>29054.519999999997</v>
       </c>
       <c r="AA24" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA24</f>
-        <v>22193</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA24</f>
+        <v>23050</v>
       </c>
       <c r="AB24" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB24</f>
-        <v>11.285991078267921</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB24</f>
+        <v>10.866377440347071</v>
       </c>
       <c r="AC24" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC24</f>
-        <v>1.1285991078267923</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC24</f>
+        <v>1.0866377440347073</v>
       </c>
       <c r="AD24" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD24</f>
-        <v>2854</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD24</f>
+        <v>1997</v>
       </c>
       <c r="AE24" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE24</f>
-        <v>11096.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE24</f>
+        <v>11525</v>
       </c>
       <c r="AF24" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF24</f>
-        <v>8242.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF24</f>
+        <v>9528</v>
       </c>
       <c r="AG24" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG24</f>
@@ -12674,28 +12676,28 @@
         <v>30040.519999999997</v>
       </c>
       <c r="AA25" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA25</f>
-        <v>21481.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA25</f>
+        <v>22664.761904761905</v>
       </c>
       <c r="AB25" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB25</f>
-        <v>12.055489607336545</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB25</f>
+        <v>11.426107235902178</v>
       </c>
       <c r="AC25" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC25</f>
-        <v>1.2055489607336545</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC25</f>
+        <v>1.1426107235902176</v>
       </c>
       <c r="AD25" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD25</f>
-        <v>4415.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD25</f>
+        <v>3232.2380952380954</v>
       </c>
       <c r="AE25" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE25</f>
-        <v>10740.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE25</f>
+        <v>11332.380952380952</v>
       </c>
       <c r="AF25" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF25</f>
-        <v>6325.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF25</f>
+        <v>8100.1428571428569</v>
       </c>
       <c r="AG25" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG25</f>
@@ -12802,28 +12804,28 @@
         <v>34369.64</v>
       </c>
       <c r="AA26" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA26</f>
-        <v>25732.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA26</f>
+        <v>26740</v>
       </c>
       <c r="AB26" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB26</f>
-        <v>11.514232973865735</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB26</f>
+        <v>11.080403889304414</v>
       </c>
       <c r="AC26" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC26</f>
-        <v>1.1514232973865735</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC26</f>
+        <v>1.1080403889304413</v>
       </c>
       <c r="AD26" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD26</f>
-        <v>3896.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD26</f>
+        <v>2889</v>
       </c>
       <c r="AE26" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE26</f>
-        <v>12866.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE26</f>
+        <v>13370</v>
       </c>
       <c r="AF26" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF26</f>
-        <v>8969.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF26</f>
+        <v>10481</v>
       </c>
       <c r="AG26" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG26</f>
@@ -12930,28 +12932,28 @@
         <v>1758.56</v>
       </c>
       <c r="AA27" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA27</f>
-        <v>97</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA27</f>
+        <v>116.66666666666666</v>
       </c>
       <c r="AB27" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB27</f>
-        <v>156.28865979381445</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB27</f>
+        <v>129.94285714285715</v>
       </c>
       <c r="AC27" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC27</f>
-        <v>15.628865979381443</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC27</f>
+        <v>12.994285714285715</v>
       </c>
       <c r="AD27" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD27</f>
-        <v>1419</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD27</f>
+        <v>1399.3333333333333</v>
       </c>
       <c r="AE27" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE27</f>
-        <v>48.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE27</f>
+        <v>58.333333333333329</v>
       </c>
       <c r="AF27" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF27</f>
-        <v>-1370.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF27</f>
+        <v>-1341</v>
       </c>
       <c r="AG27" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG27</f>
@@ -12998,16 +13000,16 @@
         <v>3519.4399999999996</v>
       </c>
       <c r="L28" s="17">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L28</f>
-        <v>8.2647779896485964</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!L28</f>
+        <v>7.7956686651168479</v>
       </c>
       <c r="M28" s="33">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M28</f>
-        <v>8076.2000000000007</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!M28</f>
+        <v>8562.1904761904771</v>
       </c>
       <c r="N28" s="18">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N28</f>
-        <v>-2472.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!N28</f>
+        <v>-2803.8571428571431</v>
       </c>
       <c r="O28" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O28</f>
@@ -13058,28 +13060,28 @@
         <v>5583.08</v>
       </c>
       <c r="AA28" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA28</f>
-        <v>3671</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA28</f>
+        <v>3891.9047619047619</v>
       </c>
       <c r="AB28" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB28</f>
-        <v>13.11086897303187</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB28</f>
+        <v>12.366695215954973</v>
       </c>
       <c r="AC28" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC28</f>
-        <v>1.3110868973031871</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC28</f>
+        <v>1.2366695215954973</v>
       </c>
       <c r="AD28" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD28</f>
-        <v>1142</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD28</f>
+        <v>921.09523809523807</v>
       </c>
       <c r="AE28" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE28</f>
-        <v>1835.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE28</f>
+        <v>1945.952380952381</v>
       </c>
       <c r="AF28" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF28</f>
-        <v>693.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF28</f>
+        <v>1024.8571428571429</v>
       </c>
       <c r="AG28" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG28</f>
@@ -13126,16 +13128,16 @@
         <v>3309.4799999999996</v>
       </c>
       <c r="L29" s="17">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L29</f>
-        <v>6.8796720520858452</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!L29</f>
+        <v>6.6599599822143176</v>
       </c>
       <c r="M29" s="33">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M29</f>
-        <v>9123.4</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!M29</f>
+        <v>9424.3809523809523</v>
       </c>
       <c r="N29" s="18">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N29</f>
-        <v>-3367.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!N29</f>
+        <v>-3572.7142857142853</v>
       </c>
       <c r="O29" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O29</f>
@@ -13186,28 +13188,28 @@
         <v>5281.48</v>
       </c>
       <c r="AA29" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA29</f>
-        <v>4147</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA29</f>
+        <v>4283.8095238095239</v>
       </c>
       <c r="AB29" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB29</f>
-        <v>10.97902097902098</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB29</f>
+        <v>10.628390395731435</v>
       </c>
       <c r="AC29" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC29</f>
-        <v>1.0979020979020979</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC29</f>
+        <v>1.0628390395731435</v>
       </c>
       <c r="AD29" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD29</f>
-        <v>406</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD29</f>
+        <v>269.19047619047615</v>
       </c>
       <c r="AE29" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE29</f>
-        <v>2073.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE29</f>
+        <v>2141.9047619047619</v>
       </c>
       <c r="AF29" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF29</f>
-        <v>1667.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF29</f>
+        <v>1872.7142857142858</v>
       </c>
       <c r="AG29" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG29</f>
@@ -13254,16 +13256,16 @@
         <v>3259.6</v>
       </c>
       <c r="L30" s="17">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!L30</f>
-        <v>7.3148509696733051</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!L30</f>
+        <v>7.1910796977821105</v>
       </c>
       <c r="M30" s="33">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!M30</f>
-        <v>8451.2999999999993</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!M30</f>
+        <v>8596.7619047619046</v>
       </c>
       <c r="N30" s="18">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!N30</f>
-        <v>-2952.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!N30</f>
+        <v>-3051.4285714285716</v>
       </c>
       <c r="O30" s="19">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!O30</f>
@@ -13314,28 +13316,28 @@
         <v>6992.48</v>
       </c>
       <c r="AA30" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA30</f>
-        <v>3841.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA30</f>
+        <v>3907.6190476190477</v>
       </c>
       <c r="AB30" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB30</f>
-        <v>15.691787062345439</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB30</f>
+        <v>15.42627345844504</v>
       </c>
       <c r="AC30" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC30</f>
-        <v>1.5691787062345437</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC30</f>
+        <v>1.5426273458445039</v>
       </c>
       <c r="AD30" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD30</f>
-        <v>2186.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD30</f>
+        <v>2120.3809523809523</v>
       </c>
       <c r="AE30" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE30</f>
-        <v>1920.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE30</f>
+        <v>1953.8095238095239</v>
       </c>
       <c r="AF30" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF30</f>
-        <v>-265.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF30</f>
+        <v>-166.57142857142844</v>
       </c>
       <c r="AG30" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG30</f>
@@ -13442,28 +13444,28 @@
         <v>5045.2800000000007</v>
       </c>
       <c r="AA31" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA31</f>
-        <v>2327.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA31</f>
+        <v>2420</v>
       </c>
       <c r="AB31" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB31</f>
-        <v>5.8904403866809885</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB31</f>
+        <v>5.6652892561983474</v>
       </c>
       <c r="AC31" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC31</f>
-        <v>0.58904403866809885</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC31</f>
+        <v>0.5665289256198347</v>
       </c>
       <c r="AD31" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD31</f>
-        <v>-956.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD31</f>
+        <v>-1049</v>
       </c>
       <c r="AE31" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE31</f>
-        <v>1163.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE31</f>
+        <v>1210</v>
       </c>
       <c r="AF31" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF31</f>
-        <v>2120.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF31</f>
+        <v>2259</v>
       </c>
       <c r="AG31" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG31</f>
@@ -13570,28 +13572,28 @@
         <v>3606.4</v>
       </c>
       <c r="AA32" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA32</f>
-        <v>1355.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA32</f>
+        <v>1421.9047619047619</v>
       </c>
       <c r="AB32" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB32</f>
-        <v>7.2298045001844331</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB32</f>
+        <v>6.8921634293369047</v>
       </c>
       <c r="AC32" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC32</f>
-        <v>0.72298045001844335</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC32</f>
+        <v>0.6892163429336905</v>
       </c>
       <c r="AD32" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD32</f>
-        <v>-375.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD32</f>
+        <v>-441.90476190476193</v>
       </c>
       <c r="AE32" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE32</f>
-        <v>677.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE32</f>
+        <v>710.95238095238096</v>
       </c>
       <c r="AF32" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF32</f>
-        <v>1053.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF32</f>
+        <v>1152.8571428571429</v>
       </c>
       <c r="AG32" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG32</f>
@@ -13698,28 +13700,28 @@
         <v>13703.300000000001</v>
       </c>
       <c r="AA33" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA33</f>
-        <v>4963.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA33</f>
+        <v>5130.9523809523807</v>
       </c>
       <c r="AB33" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB33</f>
-        <v>6.6525637151203787</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB33</f>
+        <v>6.4354524361948959</v>
       </c>
       <c r="AC33" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC33</f>
-        <v>0.66525637151203787</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC33</f>
+        <v>0.64354524361948962</v>
       </c>
       <c r="AD33" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD33</f>
-        <v>-1661.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD33</f>
+        <v>-1828.9523809523807</v>
       </c>
       <c r="AE33" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE33</f>
-        <v>2481.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE33</f>
+        <v>2565.4761904761904</v>
       </c>
       <c r="AF33" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF33</f>
-        <v>4143.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF33</f>
+        <v>4394.4285714285706</v>
       </c>
       <c r="AG33" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG33</f>
@@ -13826,28 +13828,28 @@
         <v>26174.050000000003</v>
       </c>
       <c r="AA34" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA34</f>
-        <v>7850</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA34</f>
+        <v>8113.8095238095239</v>
       </c>
       <c r="AB34" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB34</f>
-        <v>8.0343949044585994</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB34</f>
+        <v>7.7731674394037205</v>
       </c>
       <c r="AC34" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC34</f>
-        <v>0.80343949044585983</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC34</f>
+        <v>0.77731674394037209</v>
       </c>
       <c r="AD34" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD34</f>
-        <v>-1543</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD34</f>
+        <v>-1806.8095238095239</v>
       </c>
       <c r="AE34" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE34</f>
-        <v>3925</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE34</f>
+        <v>4056.9047619047619</v>
       </c>
       <c r="AF34" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF34</f>
-        <v>5468</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF34</f>
+        <v>5863.7142857142862</v>
       </c>
       <c r="AG34" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG34</f>
@@ -13954,28 +13956,28 @@
         <v>0</v>
       </c>
       <c r="AA35" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA35</f>
-        <v>637</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA35</f>
+        <v>749.52380952380952</v>
       </c>
       <c r="AB35" s="34">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB35</f>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB35</f>
         <v>0</v>
       </c>
       <c r="AC35" s="35">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC35</f>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC35</f>
         <v>0</v>
       </c>
       <c r="AD35" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD35</f>
-        <v>-637</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD35</f>
+        <v>-749.52380952380952</v>
       </c>
       <c r="AE35" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE35</f>
-        <v>318.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE35</f>
+        <v>374.76190476190476</v>
       </c>
       <c r="AF35" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF35</f>
-        <v>955.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF35</f>
+        <v>1124.2857142857142</v>
       </c>
       <c r="AG35" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG35</f>
@@ -14082,28 +14084,28 @@
         <v>2253.4500000000003</v>
       </c>
       <c r="AA36" s="36">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA36</f>
-        <v>7096.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA36</f>
+        <v>7879.5238095238092</v>
       </c>
       <c r="AB36" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB36</f>
-        <v>0.76516592686535623</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB36</f>
+        <v>0.68912793859914179</v>
       </c>
       <c r="AC36" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC36</f>
-        <v>7.6516592686535614E-2</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC36</f>
+        <v>6.8912793859914181E-2</v>
       </c>
       <c r="AD36" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD36</f>
-        <v>-6553.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD36</f>
+        <v>-7336.5238095238092</v>
       </c>
       <c r="AE36" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE36</f>
-        <v>3548.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE36</f>
+        <v>3939.7619047619046</v>
       </c>
       <c r="AF36" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF36</f>
-        <v>10101.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF36</f>
+        <v>11276.285714285714</v>
       </c>
       <c r="AG36" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG36</f>
@@ -14210,28 +14212,28 @@
         <v>16573.84</v>
       </c>
       <c r="AA37" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA37</f>
-        <v>11629.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA37</f>
+        <v>12737.142857142859</v>
       </c>
       <c r="AB37" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB37</f>
-        <v>8.7432821703426633</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB37</f>
+        <v>7.9829519964109465</v>
       </c>
       <c r="AC37" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC37</f>
-        <v>0.87432821703426633</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC37</f>
+        <v>0.79829519964109452</v>
       </c>
       <c r="AD37" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD37</f>
-        <v>-1461.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD37</f>
+        <v>-2569.1428571428587</v>
       </c>
       <c r="AE37" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE37</f>
-        <v>5814.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE37</f>
+        <v>6368.5714285714294</v>
       </c>
       <c r="AF37" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF37</f>
-        <v>7276.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF37</f>
+        <v>8937.7142857142881</v>
       </c>
       <c r="AG37" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG37</f>
@@ -14338,28 +14340,28 @@
         <v>16068.539999999999</v>
       </c>
       <c r="AA38" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA38</f>
-        <v>5102.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA38</f>
+        <v>5291.9047619047615</v>
       </c>
       <c r="AB38" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB38</f>
-        <v>19.319941205291524</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB38</f>
+        <v>18.628453162962298</v>
       </c>
       <c r="AC38" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC38</f>
-        <v>1.9319941205291524</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC38</f>
+        <v>1.8628453162962297</v>
       </c>
       <c r="AD38" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD38</f>
-        <v>4755.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD38</f>
+        <v>4566.0952380952385</v>
       </c>
       <c r="AE38" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE38</f>
-        <v>2551.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE38</f>
+        <v>2645.9523809523807</v>
       </c>
       <c r="AF38" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF38</f>
-        <v>-2204.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF38</f>
+        <v>-1920.1428571428578</v>
       </c>
       <c r="AG38" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG38</f>
@@ -14466,28 +14468,28 @@
         <v>3204.58</v>
       </c>
       <c r="AA39" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA39</f>
-        <v>4006</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA39</f>
+        <v>4018.5714285714284</v>
       </c>
       <c r="AB39" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB39</f>
-        <v>4.9076385421867199</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB39</f>
+        <v>4.8922858158549598</v>
       </c>
       <c r="AC39" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC39</f>
-        <v>0.49076385421867197</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC39</f>
+        <v>0.48922858158549593</v>
       </c>
       <c r="AD39" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD39</f>
-        <v>-2040</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD39</f>
+        <v>-2052.5714285714284</v>
       </c>
       <c r="AE39" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE39</f>
-        <v>2003</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE39</f>
+        <v>2009.2857142857142</v>
       </c>
       <c r="AF39" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF39</f>
-        <v>4043</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF39</f>
+        <v>4061.8571428571427</v>
       </c>
       <c r="AG39" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG39</f>
@@ -14594,28 +14596,28 @@
         <v>7409.98</v>
       </c>
       <c r="AA40" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA40</f>
-        <v>709</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA40</f>
+        <v>760.95238095238096</v>
       </c>
       <c r="AB40" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB40</f>
-        <v>64.118476727785605</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB40</f>
+        <v>59.740926157697118</v>
       </c>
       <c r="AC40" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC40</f>
-        <v>6.4118476727785616</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC40</f>
+        <v>5.9740926157697123</v>
       </c>
       <c r="AD40" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD40</f>
-        <v>3837</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD40</f>
+        <v>3785.0476190476193</v>
       </c>
       <c r="AE40" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE40</f>
-        <v>354.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE40</f>
+        <v>380.47619047619048</v>
       </c>
       <c r="AF40" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF40</f>
-        <v>-3482.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF40</f>
+        <v>-3404.5714285714289</v>
       </c>
       <c r="AG40" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG40</f>
@@ -14978,28 +14980,28 @@
         <v>4065.15</v>
       </c>
       <c r="AA43" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA43</f>
-        <v>1342.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA43</f>
+        <v>1433.3333333333335</v>
       </c>
       <c r="AB43" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB43</f>
-        <v>4.9236499068901303</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB43</f>
+        <v>4.6116279069767439</v>
       </c>
       <c r="AC43" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC43</f>
-        <v>0.49236499068901302</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC43</f>
+        <v>0.46116279069767435</v>
       </c>
       <c r="AD43" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD43</f>
-        <v>-681.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD43</f>
+        <v>-772.33333333333348</v>
       </c>
       <c r="AE43" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE43</f>
-        <v>671.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE43</f>
+        <v>716.66666666666674</v>
       </c>
       <c r="AF43" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF43</f>
-        <v>1352.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF43</f>
+        <v>1489.0000000000002</v>
       </c>
       <c r="AG43" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG43</f>
@@ -15106,28 +15108,28 @@
         <v>6980.25</v>
       </c>
       <c r="AA44" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA44</f>
-        <v>6411</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA44</f>
+        <v>6521.9047619047615</v>
       </c>
       <c r="AB44" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB44</f>
-        <v>1.7703946342224302</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB44</f>
+        <v>1.7402891355140189</v>
       </c>
       <c r="AC44" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC44</f>
-        <v>0.17703946342224303</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC44</f>
+        <v>0.17402891355140188</v>
       </c>
       <c r="AD44" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD44</f>
-        <v>-5276</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD44</f>
+        <v>-5386.9047619047615</v>
       </c>
       <c r="AE44" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE44</f>
-        <v>3205.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE44</f>
+        <v>3260.9523809523807</v>
       </c>
       <c r="AF44" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF44</f>
-        <v>8481.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF44</f>
+        <v>8647.8571428571413</v>
       </c>
       <c r="AG44" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG44</f>
@@ -15234,28 +15236,28 @@
         <v>4816.32</v>
       </c>
       <c r="AA45" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA45</f>
-        <v>6201</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA45</f>
+        <v>6290.4761904761908</v>
       </c>
       <c r="AB45" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB45</f>
-        <v>6.6956942428640538</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB45</f>
+        <v>6.600454201362604</v>
       </c>
       <c r="AC45" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC45</f>
-        <v>0.66956942428640542</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC45</f>
+        <v>0.66004542013626033</v>
       </c>
       <c r="AD45" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD45</f>
-        <v>-2049</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD45</f>
+        <v>-2138.4761904761908</v>
       </c>
       <c r="AE45" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE45</f>
-        <v>3100.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE45</f>
+        <v>3145.2380952380954</v>
       </c>
       <c r="AF45" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF45</f>
-        <v>5149.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF45</f>
+        <v>5283.7142857142862</v>
       </c>
       <c r="AG45" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG45</f>
@@ -15362,28 +15364,28 @@
         <v>9920.32</v>
       </c>
       <c r="AA46" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA46</f>
-        <v>8288.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA46</f>
+        <v>8521.9047619047615</v>
       </c>
       <c r="AB46" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB46</f>
-        <v>10.317910357724557</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB46</f>
+        <v>10.035315154224408</v>
       </c>
       <c r="AC46" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC46</f>
-        <v>1.0317910357724558</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC46</f>
+        <v>1.0035315154224409</v>
       </c>
       <c r="AD46" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD46</f>
-        <v>263.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD46</f>
+        <v>30.095238095238528</v>
       </c>
       <c r="AE46" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE46</f>
-        <v>4144.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE46</f>
+        <v>4260.9523809523807</v>
       </c>
       <c r="AF46" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF46</f>
-        <v>3880.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF46</f>
+        <v>4230.8571428571422</v>
       </c>
       <c r="AG46" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG46</f>
@@ -15490,28 +15492,28 @@
         <v>7810.28</v>
       </c>
       <c r="AA47" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA47</f>
-        <v>5643.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA47</f>
+        <v>5790</v>
       </c>
       <c r="AB47" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB47</f>
-        <v>11.930539558784442</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB47</f>
+        <v>11.6286701208981</v>
       </c>
       <c r="AC47" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC47</f>
-        <v>1.1930539558784443</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC47</f>
+        <v>1.1628670120898099</v>
       </c>
       <c r="AD47" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD47</f>
-        <v>1089.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD47</f>
+        <v>943</v>
       </c>
       <c r="AE47" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE47</f>
-        <v>2821.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE47</f>
+        <v>2895</v>
       </c>
       <c r="AF47" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF47</f>
-        <v>1732.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF47</f>
+        <v>1952</v>
       </c>
       <c r="AG47" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG47</f>
@@ -15618,28 +15620,28 @@
         <v>6063.32</v>
       </c>
       <c r="AA48" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA48</f>
-        <v>23.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA48</f>
+        <v>24.761904761904763</v>
       </c>
       <c r="AB48" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB48</f>
-        <v>2224.255319148936</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB48</f>
+        <v>2110.9038461538462</v>
       </c>
       <c r="AC48" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC48</f>
-        <v>222.42553191489361</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC48</f>
+        <v>211.09038461538461</v>
       </c>
       <c r="AD48" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD48</f>
-        <v>5203.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD48</f>
+        <v>5202.2380952380954</v>
       </c>
       <c r="AE48" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE48</f>
-        <v>11.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE48</f>
+        <v>12.380952380952381</v>
       </c>
       <c r="AF48" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF48</f>
-        <v>-5191.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF48</f>
+        <v>-5189.8571428571431</v>
       </c>
       <c r="AG48" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG48</f>
@@ -15874,8 +15876,8 @@
         <v>198</v>
       </c>
       <c r="AA50" s="36">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA50</f>
-        <v>544</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA50</f>
+        <v>553.33333333333337</v>
       </c>
       <c r="AB50" s="25">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB50</f>
@@ -15886,16 +15888,16 @@
         <v>0</v>
       </c>
       <c r="AD50" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD50</f>
-        <v>-533</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD50</f>
+        <v>-542.33333333333337</v>
       </c>
       <c r="AE50" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE50</f>
-        <v>272</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE50</f>
+        <v>276.66666666666669</v>
       </c>
       <c r="AF50" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF50</f>
-        <v>805</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF50</f>
+        <v>819</v>
       </c>
       <c r="AG50" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG50</f>
@@ -16002,28 +16004,28 @@
         <v>49.879999999999995</v>
       </c>
       <c r="AA51" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA51</f>
-        <v>4.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA51</f>
+        <v>4.2857142857142856</v>
       </c>
       <c r="AB51" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB51</f>
-        <v>95.555555555555557</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB51</f>
+        <v>100.33333333333334</v>
       </c>
       <c r="AC51" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC51</f>
-        <v>9.5555555555555554</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC51</f>
+        <v>10.033333333333333</v>
       </c>
       <c r="AD51" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD51</f>
-        <v>38.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD51</f>
+        <v>38.714285714285715</v>
       </c>
       <c r="AE51" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE51</f>
-        <v>2.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE51</f>
+        <v>2.1428571428571428</v>
       </c>
       <c r="AF51" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF51</f>
-        <v>-36.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF51</f>
+        <v>-36.571428571428569</v>
       </c>
       <c r="AG51" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG51</f>
@@ -16258,28 +16260,28 @@
         <v>4.6399999999999997</v>
       </c>
       <c r="AA53" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA53</f>
-        <v>5290</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA53</f>
+        <v>5544.2857142857147</v>
       </c>
       <c r="AB53" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB53</f>
-        <v>7.5614366729678641E-3</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB53</f>
+        <v>7.2146354032465859E-3</v>
       </c>
       <c r="AC53" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC53</f>
-        <v>7.5614366729678643E-4</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC53</f>
+        <v>7.2146354032465859E-4</v>
       </c>
       <c r="AD53" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD53</f>
-        <v>-5286</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD53</f>
+        <v>-5540.2857142857147</v>
       </c>
       <c r="AE53" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE53</f>
-        <v>2645</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE53</f>
+        <v>2772.1428571428573</v>
       </c>
       <c r="AF53" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF53</f>
-        <v>7931</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF53</f>
+        <v>8312.4285714285725</v>
       </c>
       <c r="AG53" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG53</f>
@@ -16386,28 +16388,28 @@
         <v>18284.13</v>
       </c>
       <c r="AA54" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA54</f>
-        <v>788.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA54</f>
+        <v>1328.0952380952381</v>
       </c>
       <c r="AB54" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB54</f>
-        <v>286.27774254914397</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB54</f>
+        <v>169.96522050914308</v>
       </c>
       <c r="AC54" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC54</f>
-        <v>28.627774254914396</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC54</f>
+        <v>16.996522050914308</v>
       </c>
       <c r="AD54" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD54</f>
-        <v>21784.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD54</f>
+        <v>21244.904761904763</v>
       </c>
       <c r="AE54" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE54</f>
-        <v>394.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE54</f>
+        <v>664.04761904761904</v>
       </c>
       <c r="AF54" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF54</f>
-        <v>-21390.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF54</f>
+        <v>-20580.857142857145</v>
       </c>
       <c r="AG54" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG54</f>
@@ -16514,28 +16516,28 @@
         <v>23675.49</v>
       </c>
       <c r="AA55" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA55</f>
-        <v>2964.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA55</f>
+        <v>2961.4285714285716</v>
       </c>
       <c r="AB55" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB55</f>
-        <v>98.596727947377303</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB55</f>
+        <v>98.698986975397972</v>
       </c>
       <c r="AC55" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC55</f>
-        <v>9.8596727947377296</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC55</f>
+        <v>9.8698986975397975</v>
       </c>
       <c r="AD55" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD55</f>
-        <v>26264.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD55</f>
+        <v>26267.571428571428</v>
       </c>
       <c r="AE55" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE55</f>
-        <v>1482.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE55</f>
+        <v>1480.7142857142858</v>
       </c>
       <c r="AF55" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF55</f>
-        <v>-24782.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF55</f>
+        <v>-24786.857142857141</v>
       </c>
       <c r="AG55" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG55</f>
@@ -16642,28 +16644,28 @@
         <v>13081.5</v>
       </c>
       <c r="AA56" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA56</f>
-        <v>5246</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA56</f>
+        <v>5287.1428571428569</v>
       </c>
       <c r="AB56" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB56</f>
-        <v>30.785360274494852</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB56</f>
+        <v>30.545798432855989</v>
       </c>
       <c r="AC56" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC56</f>
-        <v>3.0785360274494855</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC56</f>
+        <v>3.0545798432855986</v>
       </c>
       <c r="AD56" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD56</f>
-        <v>10904</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD56</f>
+        <v>10862.857142857143</v>
       </c>
       <c r="AE56" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE56</f>
-        <v>2623</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE56</f>
+        <v>2643.5714285714284</v>
       </c>
       <c r="AF56" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF56</f>
-        <v>-8281</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF56</f>
+        <v>-8219.2857142857138</v>
       </c>
       <c r="AG56" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG56</f>
@@ -16770,28 +16772,28 @@
         <v>15625.710000000001</v>
       </c>
       <c r="AA57" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA57</f>
-        <v>3077</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA57</f>
+        <v>3055.7142857142853</v>
       </c>
       <c r="AB57" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB57</f>
-        <v>62.69418264543387</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB57</f>
+        <v>63.13090229079009</v>
       </c>
       <c r="AC57" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC57</f>
-        <v>6.2694182645433862</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC57</f>
+        <v>6.3130902290790099</v>
       </c>
       <c r="AD57" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD57</f>
-        <v>16214</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD57</f>
+        <v>16235.285714285714</v>
       </c>
       <c r="AE57" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE57</f>
-        <v>1538.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE57</f>
+        <v>1527.8571428571427</v>
       </c>
       <c r="AF57" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF57</f>
-        <v>-14675.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF57</f>
+        <v>-14707.428571428571</v>
       </c>
       <c r="AG57" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG57</f>
@@ -16898,28 +16900,28 @@
         <v>1873.3000000000002</v>
       </c>
       <c r="AA58" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA58</f>
-        <v>2912</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA58</f>
+        <v>2899.0476190476193</v>
       </c>
       <c r="AB58" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB58</f>
-        <v>2.4553571428571428</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB58</f>
+        <v>2.4663272010512483</v>
       </c>
       <c r="AC58" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC58</f>
-        <v>0.24553571428571427</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC58</f>
+        <v>0.24663272010512483</v>
       </c>
       <c r="AD58" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD58</f>
-        <v>-2197</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD58</f>
+        <v>-2184.0476190476193</v>
       </c>
       <c r="AE58" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE58</f>
-        <v>1456</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE58</f>
+        <v>1449.5238095238096</v>
       </c>
       <c r="AF58" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF58</f>
-        <v>3653</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF58</f>
+        <v>3633.5714285714289</v>
       </c>
       <c r="AG58" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG58</f>
@@ -17026,28 +17028,28 @@
         <v>1011.32</v>
       </c>
       <c r="AA59" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA59</f>
-        <v>563</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA59</f>
+        <v>577.14285714285711</v>
       </c>
       <c r="AB59" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB59</f>
-        <v>6.8561278863232689</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB59</f>
+        <v>6.6881188118811892</v>
       </c>
       <c r="AC59" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC59</f>
-        <v>0.68561278863232678</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC59</f>
+        <v>0.66881188118811885</v>
       </c>
       <c r="AD59" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD59</f>
-        <v>-177</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD59</f>
+        <v>-191.14285714285711</v>
       </c>
       <c r="AE59" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE59</f>
-        <v>281.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE59</f>
+        <v>288.57142857142856</v>
       </c>
       <c r="AF59" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF59</f>
-        <v>458.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF59</f>
+        <v>479.71428571428567</v>
       </c>
       <c r="AG59" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG59</f>
@@ -17154,28 +17156,28 @@
         <v>780.76</v>
       </c>
       <c r="AA60" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA60</f>
-        <v>1045.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA60</f>
+        <v>1047.1428571428571</v>
       </c>
       <c r="AB60" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB60</f>
-        <v>2.8503108560497372</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB60</f>
+        <v>2.8458390177353343</v>
       </c>
       <c r="AC60" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC60</f>
-        <v>0.2850310856049737</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC60</f>
+        <v>0.28458390177353343</v>
       </c>
       <c r="AD60" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD60</f>
-        <v>-747.5</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD60</f>
+        <v>-749.14285714285711</v>
       </c>
       <c r="AE60" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE60</f>
-        <v>522.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE60</f>
+        <v>523.57142857142856</v>
       </c>
       <c r="AF60" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF60</f>
-        <v>1270.25</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF60</f>
+        <v>1272.7142857142858</v>
       </c>
       <c r="AG60" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG60</f>
@@ -17282,28 +17284,28 @@
         <v>382.52000000000004</v>
       </c>
       <c r="AA61" s="24">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AA61</f>
-        <v>492</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AA61</f>
+        <v>493.33333333333337</v>
       </c>
       <c r="AB61" s="25">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AB61</f>
-        <v>2.9674796747967478</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AB61</f>
+        <v>2.9594594594594592</v>
       </c>
       <c r="AC61" s="26">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AC61</f>
-        <v>0.2967479674796748</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AC61</f>
+        <v>0.29594594594594592</v>
       </c>
       <c r="AD61" s="29">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AD61</f>
-        <v>-346</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AD61</f>
+        <v>-347.33333333333337</v>
       </c>
       <c r="AE61" s="30">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AE61</f>
-        <v>246</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AE61</f>
+        <v>246.66666666666669</v>
       </c>
       <c r="AF61" s="28">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF61</f>
-        <v>592</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF61</f>
+        <v>594</v>
       </c>
       <c r="AG61" s="31">
         <f>'[1]INVENTARIO NACIONAL 17-08-26'!AG61</f>
@@ -17342,8 +17344,8 @@
         <v>Units Produce</v>
       </c>
       <c r="AF62" s="44">
-        <f ca="1">'[1]INVENTARIO NACIONAL 17-08-26'!AF62</f>
-        <v>151316.75</v>
+        <f>'[1]INVENTARIO NACIONAL 17-08-26'!AF62</f>
+        <v>166285.14285714287</v>
       </c>
     </row>
     <row r="63" spans="2:33" x14ac:dyDescent="0.25">
@@ -17352,10 +17354,10 @@
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
-      <c r="E63" s="64" t="s">
+      <c r="E63" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="F63" s="64"/>
+      <c r="F63" s="67"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -17380,10 +17382,10 @@
       <c r="AB63" s="42"/>
     </row>
     <row r="64" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B64" s="65" t="s">
+      <c r="B64" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="65"/>
+      <c r="C64" s="63"/>
       <c r="D64" s="48">
         <f>SUM(F13:F61)</f>
         <v>144936.54999999999</v>
@@ -17528,19 +17530,19 @@
       <c r="AB67" s="42"/>
     </row>
     <row r="68" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B68" s="65" t="s">
+      <c r="B68" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="C68" s="65"/>
+      <c r="C68" s="63"/>
       <c r="D68" s="50">
         <f>SUM(Z13:Z61)</f>
         <v>421177.93000000017</v>
       </c>
-      <c r="E68" s="66">
+      <c r="E68" s="64">
         <f>D68*100/D68</f>
         <v>100</v>
       </c>
-      <c r="F68" s="66"/>
+      <c r="F68" s="64"/>
       <c r="G68" s="51"/>
       <c r="H68" s="51"/>
       <c r="I68" s="51"/>
@@ -17625,10 +17627,10 @@
       <c r="AB70" s="42"/>
     </row>
     <row r="71" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="65"/>
+      <c r="C71" s="63"/>
       <c r="D71" s="3">
         <f>SUM(E13:E61)</f>
         <v>112990</v>
@@ -17743,11 +17745,11 @@
         <f>SUM(T13:T61)</f>
         <v>36961</v>
       </c>
-      <c r="E74" s="67">
+      <c r="E74" s="62">
         <f>D74*100/D75</f>
         <v>11.039956032533535</v>
       </c>
-      <c r="F74" s="67"/>
+      <c r="F74" s="62"/>
       <c r="G74" s="56"/>
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
@@ -17772,19 +17774,19 @@
       <c r="AB74" s="42"/>
     </row>
     <row r="75" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="63"/>
       <c r="D75" s="55">
         <f>SUM(Y13:Y61)</f>
         <v>334793</v>
       </c>
-      <c r="E75" s="67">
+      <c r="E75" s="62">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="67"/>
+      <c r="F75" s="62"/>
       <c r="G75" s="56"/>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
@@ -18545,23 +18547,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="B1:Z6"/>
+    <mergeCell ref="AA1:AG6"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="E64:F64"/>
     <mergeCell ref="E66:F66"/>
     <mergeCell ref="E67:F67"/>
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="E68:F68"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="B1:Z6"/>
-    <mergeCell ref="AA1:AG6"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G61">
     <cfRule type="colorScale" priority="5">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B188CD-7F07-444E-B6ED-32D0CF955CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52282731-CBDE-4332-A475-AD5C62D151CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -1173,6 +1173,7 @@
       <sheetName val="INVENTARIO NACIONAL 02-09-2026"/>
       <sheetName val="INVENTARIO NACIONAL 03-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 04-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1301,6 +1302,7 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52282731-CBDE-4332-A475-AD5C62D151CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F062716-DE19-4A23-8606-24417D77238D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -805,6 +805,12 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -813,12 +819,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1630,242 +1630,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="66" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="66"/>
-      <c r="AH1" s="66"/>
-      <c r="AI1" s="66"/>
-      <c r="AJ1" s="66"/>
-      <c r="AK1" s="66"/>
-      <c r="AL1" s="66"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
+      <c r="AJ1" s="68"/>
+      <c r="AK1" s="68"/>
+      <c r="AL1" s="68"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65"/>
-      <c r="AC2" s="65"/>
-      <c r="AD2" s="65"/>
-      <c r="AE2" s="65"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
-      <c r="AH2" s="66"/>
-      <c r="AI2" s="66"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="66"/>
-      <c r="AL2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
-      <c r="AH3" s="66"/>
-      <c r="AI3" s="66"/>
-      <c r="AJ3" s="66"/>
-      <c r="AK3" s="66"/>
-      <c r="AL3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="68"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="65"/>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
-      <c r="AE4" s="65"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="68"/>
+      <c r="AG4" s="68"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="68"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="65"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="65"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="67"/>
+      <c r="Y5" s="67"/>
+      <c r="Z5" s="67"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="67"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="65"/>
-      <c r="AB6" s="65"/>
-      <c r="AC6" s="65"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="65"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
-      <c r="AH6" s="66"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="66"/>
-      <c r="AK6" s="66"/>
-      <c r="AL6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="68"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2230,106 +2230,106 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>1576</v>
+        <v>4686</v>
       </c>
       <c r="F13" s="14">
-        <v>2143.36</v>
+        <v>6372.96</v>
       </c>
       <c r="G13" s="14">
-        <v>2.0225164790293415</v>
+        <v>6.0136498862509473</v>
       </c>
       <c r="H13" s="30">
         <v>17143</v>
       </c>
       <c r="I13" s="15">
-        <v>-6216.2727272727279</v>
+        <v>-3106.2727272727279</v>
       </c>
       <c r="J13" s="16">
-        <v>5807</v>
+        <v>2641</v>
       </c>
       <c r="K13" s="13">
-        <v>7897.52</v>
+        <v>3591.76</v>
       </c>
       <c r="L13" s="14">
-        <v>23.852501867064973</v>
+        <v>10.848020911127707</v>
       </c>
       <c r="M13" s="30">
         <v>5356</v>
       </c>
       <c r="N13" s="15">
-        <v>3372.4545454545455</v>
+        <v>206.4545454545455</v>
       </c>
       <c r="O13" s="16">
-        <v>120</v>
+        <v>629</v>
       </c>
       <c r="P13" s="17">
-        <v>163.20000000000002</v>
+        <v>855.44</v>
       </c>
       <c r="Q13" s="14">
-        <v>3.0662020905923346</v>
+        <v>16.072009291521489</v>
       </c>
       <c r="R13" s="16">
         <v>861</v>
       </c>
       <c r="S13" s="15">
-        <v>-467.0454545454545</v>
+        <v>41.954545454545496</v>
       </c>
       <c r="T13" s="18">
-        <v>359</v>
+        <v>289</v>
       </c>
       <c r="U13" s="17">
-        <v>488.24</v>
+        <v>393.04</v>
       </c>
       <c r="V13" s="14">
-        <v>6.6147403685092128</v>
+        <v>5.324958123953099</v>
       </c>
       <c r="W13" s="16">
         <v>1194</v>
       </c>
       <c r="X13" s="15">
-        <v>-455.09090909090912</v>
+        <v>-525.09090909090912</v>
       </c>
       <c r="Y13" s="18">
-        <v>402</v>
+        <v>507</v>
       </c>
       <c r="Z13" s="17">
-        <v>546.72</v>
+        <v>689.5200000000001</v>
       </c>
       <c r="AA13" s="14">
-        <v>22.333333333333332</v>
+        <v>23.472222222222221</v>
       </c>
       <c r="AB13" s="16">
-        <v>396</v>
+        <v>475.20000000000005</v>
       </c>
       <c r="AC13" s="15">
-        <v>132</v>
+        <v>183</v>
       </c>
       <c r="AD13" s="19">
-        <v>8264</v>
+        <v>8752</v>
       </c>
       <c r="AE13" s="20">
-        <v>11239.04</v>
+        <v>11902.720000000001</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
       </c>
       <c r="AG13" s="22">
-        <v>6.9556713426853705</v>
+        <v>7.3664128256513024</v>
       </c>
       <c r="AH13" s="23">
-        <v>0.695567134268537</v>
+        <v>0.73664128256513017</v>
       </c>
       <c r="AI13" s="24">
-        <v>-3616.9523809523816</v>
+        <v>-3128.9523809523816</v>
       </c>
       <c r="AJ13" s="24">
         <v>5940.4761904761908</v>
       </c>
       <c r="AK13" s="25">
-        <v>9557.4285714285725</v>
+        <v>9069.4285714285725</v>
       </c>
       <c r="AL13" s="24">
-        <v>103.3</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2344,106 +2344,106 @@
         <v>1.59</v>
       </c>
       <c r="E14" s="13">
-        <v>162</v>
+        <v>264</v>
       </c>
       <c r="F14" s="14">
-        <v>257.58000000000004</v>
+        <v>419.76000000000005</v>
       </c>
       <c r="G14" s="14">
-        <v>4.6771653543307092</v>
+        <v>7.6220472440944889</v>
       </c>
       <c r="H14" s="30">
         <v>762</v>
       </c>
       <c r="I14" s="15">
-        <v>-184.36363636363632</v>
+        <v>-82.363636363636317</v>
       </c>
       <c r="J14" s="16">
-        <v>560</v>
+        <v>101</v>
       </c>
       <c r="K14" s="13">
-        <v>890.40000000000009</v>
+        <v>160.59</v>
       </c>
       <c r="L14" s="14">
-        <v>21.463414634146343</v>
+        <v>3.8710801393728222</v>
       </c>
       <c r="M14" s="30">
         <v>574</v>
       </c>
       <c r="N14" s="15">
-        <v>299.09090909090912</v>
+        <v>-159.90909090909088</v>
       </c>
       <c r="O14" s="16">
-        <v>9</v>
+        <v>148</v>
       </c>
       <c r="P14" s="17">
-        <v>14.31</v>
+        <v>235.32000000000002</v>
       </c>
       <c r="Q14" s="14">
-        <v>1.164705882352941</v>
+        <v>19.152941176470588</v>
       </c>
       <c r="R14" s="16">
         <v>170</v>
       </c>
       <c r="S14" s="15">
-        <v>-106.90909090909091</v>
+        <v>32.090909090909093</v>
       </c>
       <c r="T14" s="18">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="U14" s="17">
-        <v>55.650000000000006</v>
+        <v>49.29</v>
       </c>
       <c r="V14" s="14">
-        <v>13.75</v>
+        <v>12.178571428571429</v>
       </c>
       <c r="W14" s="16">
         <v>56</v>
       </c>
       <c r="X14" s="15">
-        <v>-3.1818181818181799</v>
+        <v>-7.1818181818181799</v>
       </c>
       <c r="Y14" s="18">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="Z14" s="17">
-        <v>44.52</v>
+        <v>166.95000000000002</v>
       </c>
       <c r="AA14" s="14">
-        <v>14.666666666666666</v>
+        <v>65.625</v>
       </c>
       <c r="AB14" s="16">
-        <v>42</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="AC14" s="15">
-        <v>-0.63636363636363669</v>
+        <v>81</v>
       </c>
       <c r="AD14" s="19">
-        <v>794</v>
+        <v>649</v>
       </c>
       <c r="AE14" s="20">
-        <v>1262.46</v>
+        <v>1031.9100000000001</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
       </c>
       <c r="AG14" s="22">
-        <v>10.395261845386534</v>
+        <v>8.4968827930174573</v>
       </c>
       <c r="AH14" s="23">
-        <v>1.0395261845386532</v>
+        <v>0.84968827930174562</v>
       </c>
       <c r="AI14" s="26">
-        <v>30.190476190476147</v>
+        <v>-114.80952380952385</v>
       </c>
       <c r="AJ14" s="27">
         <v>381.90476190476193</v>
       </c>
       <c r="AK14" s="25">
-        <v>351.71428571428578</v>
+        <v>496.71428571428578</v>
       </c>
       <c r="AL14" s="28">
-        <v>9.9250000000000007</v>
+        <v>8.1125000000000007</v>
       </c>
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2458,106 +2458,106 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>250</v>
+        <v>1860</v>
       </c>
       <c r="F15" s="14">
-        <v>507.49999999999994</v>
+        <v>3775.7999999999997</v>
       </c>
       <c r="G15" s="14">
-        <v>0.79710144927536231</v>
+        <v>5.9304347826086961</v>
       </c>
       <c r="H15" s="30">
         <v>6900</v>
       </c>
       <c r="I15" s="15">
-        <v>-2886.363636363636</v>
+        <v>-1276.363636363636</v>
       </c>
       <c r="J15" s="16">
-        <v>1272</v>
+        <v>35</v>
       </c>
       <c r="K15" s="13">
-        <v>2582.16</v>
+        <v>71.05</v>
       </c>
       <c r="L15" s="14">
-        <v>9.2692944683670095</v>
+        <v>0.2550513415038092</v>
       </c>
       <c r="M15" s="30">
         <v>3019</v>
       </c>
       <c r="N15" s="15">
-        <v>-100.27272727272725</v>
+        <v>-1337.2727272727273</v>
       </c>
       <c r="O15" s="16">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="P15" s="17">
-        <v>4.0599999999999996</v>
+        <v>487.19999999999993</v>
       </c>
       <c r="Q15" s="14">
-        <v>0.14814814814814814</v>
+        <v>17.777777777777779</v>
       </c>
       <c r="R15" s="16">
         <v>297</v>
       </c>
       <c r="S15" s="15">
-        <v>-200.5</v>
+        <v>37.5</v>
       </c>
       <c r="T15" s="18">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="U15" s="17">
-        <v>142.1</v>
+        <v>71.05</v>
       </c>
       <c r="V15" s="14">
-        <v>4.4380403458213253</v>
+        <v>2.2190201729106627</v>
       </c>
       <c r="W15" s="16">
         <v>347.00000000000006</v>
       </c>
       <c r="X15" s="15">
-        <v>-166.59090909090912</v>
+        <v>-201.59090909090912</v>
       </c>
       <c r="Y15" s="18">
-        <v>84</v>
+        <v>255</v>
       </c>
       <c r="Z15" s="17">
-        <v>170.51999999999998</v>
+        <v>517.65</v>
       </c>
       <c r="AA15" s="14">
-        <v>13.588235294117647</v>
+        <v>60.714285714285708</v>
       </c>
       <c r="AB15" s="16">
-        <v>136</v>
+        <v>92.4</v>
       </c>
       <c r="AC15" s="15">
-        <v>-8.7272727272727195</v>
+        <v>192</v>
       </c>
       <c r="AD15" s="19">
-        <v>1678</v>
+        <v>2425</v>
       </c>
       <c r="AE15" s="20">
-        <v>3406.3399999999997</v>
+        <v>4922.7499999999991</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
       </c>
       <c r="AG15" s="22">
-        <v>3.2935788391438452</v>
+        <v>4.7597906346387511</v>
       </c>
       <c r="AH15" s="23">
-        <v>0.32935788391438453</v>
+        <v>0.47597906346387514</v>
       </c>
       <c r="AI15" s="26">
-        <v>-3416.7619047619046</v>
+        <v>-2669.7619047619046</v>
       </c>
       <c r="AJ15" s="27">
         <v>2547.3809523809523</v>
       </c>
       <c r="AK15" s="25">
-        <v>5964.1428571428569</v>
+        <v>5217.1428571428569</v>
       </c>
       <c r="AL15" s="28">
-        <v>27.966666666666665</v>
+        <v>40.416666666666664</v>
       </c>
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2571,106 +2571,106 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>22</v>
+        <v>303</v>
       </c>
       <c r="F16" s="14">
-        <v>79.42</v>
+        <v>1093.83</v>
       </c>
       <c r="G16" s="14">
-        <v>0.34645669291338582</v>
+        <v>4.771653543307087</v>
       </c>
       <c r="H16" s="30">
         <v>1397</v>
       </c>
       <c r="I16" s="15">
-        <v>-613</v>
+        <v>-332</v>
       </c>
       <c r="J16" s="16">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="K16" s="13">
-        <v>924.16</v>
+        <v>877.23</v>
       </c>
       <c r="L16" s="14">
-        <v>10.333944954128441</v>
+        <v>9.8091743119266059</v>
       </c>
       <c r="M16" s="30">
         <v>545</v>
       </c>
       <c r="N16" s="15">
-        <v>8.2727272727272521</v>
+        <v>-4.7272727272727479</v>
       </c>
       <c r="O16" s="16">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="P16" s="17">
-        <v>0</v>
+        <v>126.35</v>
       </c>
       <c r="Q16" s="14">
-        <v>0</v>
+        <v>16.739130434782606</v>
       </c>
       <c r="R16" s="16">
         <v>46.000000000000007</v>
       </c>
       <c r="S16" s="15">
-        <v>-31.36363636363637</v>
+        <v>3.6363636363636296</v>
       </c>
       <c r="T16" s="18">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="U16" s="17">
-        <v>115.52</v>
+        <v>101.08</v>
       </c>
       <c r="V16" s="14">
-        <v>14.367346938775512</v>
+        <v>12.571428571428573</v>
       </c>
       <c r="W16" s="16">
         <v>49</v>
       </c>
       <c r="X16" s="15">
-        <v>-1.4090909090909065</v>
+        <v>-5.4090909090909065</v>
       </c>
       <c r="Y16" s="18">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="Z16" s="17">
-        <v>93.86</v>
+        <v>296.02</v>
       </c>
       <c r="AA16" s="14">
-        <v>27.238095238095237</v>
+        <v>136.66666666666669</v>
       </c>
       <c r="AB16" s="16">
-        <v>21</v>
+        <v>13.2</v>
       </c>
       <c r="AC16" s="15">
-        <v>11.681818181818182</v>
+        <v>73</v>
       </c>
       <c r="AD16" s="19">
-        <v>336</v>
+        <v>691</v>
       </c>
       <c r="AE16" s="20">
-        <v>1212.96</v>
+        <v>2494.5099999999998</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
       </c>
       <c r="AG16" s="22">
-        <v>3.4285714285714284</v>
+        <v>7.0510204081632653</v>
       </c>
       <c r="AH16" s="23">
-        <v>0.34285714285714286</v>
+        <v>0.70510204081632655</v>
       </c>
       <c r="AI16" s="26">
-        <v>-644</v>
+        <v>-289</v>
       </c>
       <c r="AJ16" s="27">
         <v>490</v>
       </c>
       <c r="AK16" s="25">
-        <v>1134</v>
+        <v>779</v>
       </c>
       <c r="AL16" s="28">
-        <v>12</v>
+        <v>24.678571428571427</v>
       </c>
     </row>
     <row r="17" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2684,64 +2684,64 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F17" s="14">
-        <v>131.69999999999999</v>
+        <v>158.04</v>
       </c>
       <c r="G17" s="14">
-        <v>1.9760479041916168</v>
+        <v>2.3712574850299402</v>
       </c>
       <c r="H17" s="30">
         <v>167</v>
       </c>
       <c r="I17" s="15">
-        <v>-60.909090909090907</v>
+        <v>-57.909090909090907</v>
       </c>
       <c r="J17" s="16">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="K17" s="13">
-        <v>491.67999999999995</v>
+        <v>237.05999999999997</v>
       </c>
       <c r="L17" s="14">
-        <v>17.855072463768117</v>
+        <v>8.608695652173914</v>
       </c>
       <c r="M17" s="30">
         <v>69</v>
       </c>
       <c r="N17" s="15">
-        <v>24.636363636363637</v>
+        <v>-4.3636363636363633</v>
       </c>
       <c r="O17" s="16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P17" s="17">
-        <v>26.339999999999996</v>
+        <v>52.679999999999993</v>
       </c>
       <c r="Q17" s="14">
-        <v>8.25</v>
+        <v>16.5</v>
       </c>
       <c r="R17" s="16">
         <v>8</v>
       </c>
       <c r="S17" s="15">
-        <v>-2.454545454545455</v>
+        <v>0.54545454545454497</v>
       </c>
       <c r="T17" s="18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U17" s="17">
-        <v>158.04</v>
+        <v>149.26</v>
       </c>
       <c r="V17" s="14">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="W17" s="16">
         <v>2</v>
       </c>
       <c r="X17" s="15">
-        <v>16.636363636363637</v>
+        <v>15.636363636363637</v>
       </c>
       <c r="Y17" s="18">
         <v>14</v>
@@ -2750,40 +2750,40 @@
         <v>122.91999999999999</v>
       </c>
       <c r="AA17" s="14">
-        <v>61.6</v>
+        <v>23.333333333333336</v>
       </c>
       <c r="AB17" s="16">
+        <v>13.2</v>
+      </c>
+      <c r="AC17" s="15">
         <v>5</v>
       </c>
-      <c r="AC17" s="15">
-        <v>10.59090909090909</v>
-      </c>
       <c r="AD17" s="19">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AE17" s="20">
-        <v>930.68</v>
+        <v>719.95999999999992</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
       </c>
       <c r="AG17" s="22">
-        <v>8.8685258964143419</v>
+        <v>6.8605577689243029</v>
       </c>
       <c r="AH17" s="23">
-        <v>0.88685258964143432</v>
+        <v>0.68605577689243036</v>
       </c>
       <c r="AI17" s="26">
-        <v>-13.523809523809518</v>
+        <v>-37.523809523809518</v>
       </c>
       <c r="AJ17" s="27">
         <v>59.761904761904759</v>
       </c>
       <c r="AK17" s="25">
-        <v>73.285714285714278</v>
+        <v>97.285714285714278</v>
       </c>
       <c r="AL17" s="28">
-        <v>8.8333333333333339</v>
+        <v>6.833333333333333</v>
       </c>
     </row>
     <row r="18" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2797,106 +2797,106 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>5006</v>
+        <v>7800</v>
       </c>
       <c r="F18" s="14">
-        <v>3153.78</v>
+        <v>4914</v>
       </c>
       <c r="G18" s="14">
-        <v>6.0329772665023285</v>
+        <v>9.4001643385373868</v>
       </c>
       <c r="H18" s="30">
         <v>18255</v>
       </c>
       <c r="I18" s="15">
-        <v>-3291.7272727272721</v>
+        <v>-497.72727272727207</v>
       </c>
       <c r="J18" s="16">
-        <v>7127</v>
+        <v>3869</v>
       </c>
       <c r="K18" s="13">
-        <v>4490.01</v>
+        <v>2437.4699999999998</v>
       </c>
       <c r="L18" s="14">
-        <v>22.658092485549133</v>
+        <v>12.30028901734104</v>
       </c>
       <c r="M18" s="30">
         <v>6920</v>
       </c>
       <c r="N18" s="15">
-        <v>3981.5454545454545</v>
+        <v>723.5454545454545</v>
       </c>
       <c r="O18" s="16">
-        <v>270</v>
+        <v>961</v>
       </c>
       <c r="P18" s="17">
-        <v>170.1</v>
+        <v>605.42999999999995</v>
       </c>
       <c r="Q18" s="14">
-        <v>4.1107266435986158</v>
+        <v>14.63114186851211</v>
       </c>
       <c r="R18" s="16">
         <v>1445</v>
       </c>
       <c r="S18" s="15">
-        <v>-715.22727272727275</v>
+        <v>-24.227272727272748</v>
       </c>
       <c r="T18" s="18">
-        <v>1398</v>
+        <v>1124</v>
       </c>
       <c r="U18" s="17">
-        <v>880.74</v>
+        <v>708.12</v>
       </c>
       <c r="V18" s="14">
-        <v>7.9720062208398126</v>
+        <v>6.4095386210471741</v>
       </c>
       <c r="W18" s="16">
         <v>3858</v>
       </c>
       <c r="X18" s="15">
-        <v>-1232.4545454545455</v>
+        <v>-1506.4545454545455</v>
       </c>
       <c r="Y18" s="18">
-        <v>13</v>
+        <v>373</v>
       </c>
       <c r="Z18" s="17">
-        <v>8.19</v>
+        <v>234.99</v>
       </c>
       <c r="AA18" s="14">
-        <v>1.513227513227513</v>
+        <v>50.405405405405403</v>
       </c>
       <c r="AB18" s="16">
-        <v>189</v>
+        <v>162.80000000000001</v>
       </c>
       <c r="AC18" s="15">
-        <v>-115.86363636363637</v>
+        <v>262</v>
       </c>
       <c r="AD18" s="19">
-        <v>13814</v>
+        <v>14127</v>
       </c>
       <c r="AE18" s="20">
-        <v>8702.82</v>
+        <v>8900.01</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
       </c>
       <c r="AG18" s="22">
-        <v>9.4594841360420006</v>
+        <v>9.6738187628395345</v>
       </c>
       <c r="AH18" s="23">
-        <v>0.94594841360420001</v>
+        <v>0.96738187628395356</v>
       </c>
       <c r="AI18" s="26">
-        <v>-789.33333333333212</v>
+        <v>-476.33333333333212</v>
       </c>
       <c r="AJ18" s="27">
         <v>7301.6666666666661</v>
       </c>
       <c r="AK18" s="25">
-        <v>8090.9999999999982</v>
+        <v>7777.9999999999982</v>
       </c>
       <c r="AL18" s="28">
-        <v>230.23333333333332</v>
+        <v>235.45</v>
       </c>
     </row>
     <row r="19" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2910,106 +2910,106 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>46</v>
+        <v>1176</v>
       </c>
       <c r="F19" s="14">
-        <v>28.98</v>
+        <v>740.88</v>
       </c>
       <c r="G19" s="14">
-        <v>0.68148148148148158</v>
+        <v>17.422222222222224</v>
       </c>
       <c r="H19" s="30">
         <v>1484.9999999999998</v>
       </c>
       <c r="I19" s="15">
-        <v>-628.99999999999989</v>
+        <v>501.00000000000011</v>
       </c>
       <c r="J19" s="16">
-        <v>1109</v>
+        <v>227</v>
       </c>
       <c r="K19" s="13">
-        <v>698.67</v>
+        <v>143.01</v>
       </c>
       <c r="L19" s="14">
-        <v>21.706405693950177</v>
+        <v>4.4430604982206408</v>
       </c>
       <c r="M19" s="30">
         <v>1124</v>
       </c>
       <c r="N19" s="15">
-        <v>598.09090909090901</v>
+        <v>-283.90909090909093</v>
       </c>
       <c r="O19" s="16">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="P19" s="17">
-        <v>17.010000000000002</v>
+        <v>54.81</v>
       </c>
       <c r="Q19" s="14">
-        <v>6.3191489361702136</v>
+        <v>20.361702127659576</v>
       </c>
       <c r="R19" s="16">
         <v>94</v>
       </c>
       <c r="S19" s="15">
-        <v>-37.090909090909093</v>
+        <v>22.909090909090907</v>
       </c>
       <c r="T19" s="18">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="U19" s="17">
-        <v>56.7</v>
+        <v>32.130000000000003</v>
       </c>
       <c r="V19" s="14">
-        <v>5.8407079646017701</v>
+        <v>3.3097345132743365</v>
       </c>
       <c r="W19" s="16">
         <v>339</v>
       </c>
       <c r="X19" s="15">
-        <v>-141.13636363636363</v>
+        <v>-180.13636363636363</v>
       </c>
       <c r="Y19" s="18">
-        <v>69</v>
+        <v>240</v>
       </c>
       <c r="Z19" s="17">
-        <v>43.47</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="AA19" s="14">
-        <v>13.086206896551724</v>
+        <v>18.75</v>
       </c>
       <c r="AB19" s="16">
-        <v>116</v>
+        <v>281.60000000000002</v>
       </c>
       <c r="AC19" s="15">
-        <v>-10.090909090909093</v>
+        <v>48</v>
       </c>
       <c r="AD19" s="19">
-        <v>1341</v>
+        <v>1781</v>
       </c>
       <c r="AE19" s="20">
-        <v>844.83</v>
+        <v>1122.03</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
       </c>
       <c r="AG19" s="22">
-        <v>8.917352754908169</v>
+        <v>11.843255224825839</v>
       </c>
       <c r="AH19" s="23">
-        <v>0.89173527549081699</v>
+        <v>1.1843255224825839</v>
       </c>
       <c r="AI19" s="26">
-        <v>-162.80952380952385</v>
+        <v>277.19047619047615</v>
       </c>
       <c r="AJ19" s="27">
         <v>751.90476190476193</v>
       </c>
       <c r="AK19" s="25">
-        <v>914.71428571428578</v>
+        <v>474.71428571428578</v>
       </c>
       <c r="AL19" s="28">
-        <v>22.35</v>
+        <v>29.683333333333334</v>
       </c>
     </row>
     <row r="20" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3023,106 +3023,104 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1659</v>
+        <v>2248</v>
       </c>
       <c r="F20" s="14">
-        <v>1045.17</v>
+        <v>1416.24</v>
       </c>
       <c r="G20" s="14">
-        <v>10.814222222222222</v>
+        <v>14.653629629629631</v>
       </c>
       <c r="H20" s="30">
         <v>3375</v>
       </c>
       <c r="I20" s="15">
-        <v>124.90909090909099</v>
+        <v>713.90909090909099</v>
       </c>
       <c r="J20" s="16">
-        <v>1184</v>
+        <v>284</v>
       </c>
       <c r="K20" s="13">
-        <v>745.92</v>
+        <v>178.92</v>
       </c>
       <c r="L20" s="14">
-        <v>11.781094527363184</v>
+        <v>2.8258706467661692</v>
       </c>
       <c r="M20" s="30">
         <v>2211</v>
       </c>
       <c r="N20" s="15">
-        <v>179</v>
+        <v>-721</v>
       </c>
       <c r="O20" s="16">
-        <v>16</v>
+        <v>241</v>
       </c>
       <c r="P20" s="17">
-        <v>10.08</v>
+        <v>151.83000000000001</v>
       </c>
       <c r="Q20" s="14">
-        <v>1.2616487455197132</v>
+        <v>19.003584229390682</v>
       </c>
       <c r="R20" s="16">
         <v>279</v>
       </c>
       <c r="S20" s="15">
-        <v>-174.22727272727272</v>
-      </c>
-      <c r="T20" s="18">
-        <v>34</v>
-      </c>
+        <v>50.77272727272728</v>
+      </c>
+      <c r="T20" s="18"/>
       <c r="U20" s="17">
-        <v>21.42</v>
+        <v>0</v>
       </c>
       <c r="V20" s="14">
-        <v>0.63822525597269619</v>
+        <v>0</v>
       </c>
       <c r="W20" s="16">
         <v>1172</v>
       </c>
       <c r="X20" s="15">
-        <v>-765.09090909090912</v>
+        <v>-799.09090909090912</v>
       </c>
       <c r="Y20" s="18">
-        <v>11</v>
+        <v>371</v>
       </c>
       <c r="Z20" s="17">
-        <v>6.93</v>
+        <v>233.73</v>
       </c>
       <c r="AA20" s="14">
-        <v>1.3595505617977526</v>
+        <v>38.645833333333336</v>
       </c>
       <c r="AB20" s="16">
-        <v>178</v>
+        <v>211.2</v>
       </c>
       <c r="AC20" s="15">
-        <v>-110.36363636363637</v>
+        <v>227</v>
       </c>
       <c r="AD20" s="19">
-        <v>2904</v>
+        <v>3144</v>
       </c>
       <c r="AE20" s="20">
-        <v>1829.52</v>
+        <v>1980.72</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
       </c>
       <c r="AG20" s="22">
-        <v>8.4523908523908524</v>
+        <v>9.1509355509355519</v>
       </c>
       <c r="AH20" s="23">
-        <v>0.84523908523908531</v>
+        <v>0.91509355509355517</v>
       </c>
       <c r="AI20" s="26">
-        <v>-531.71428571428532</v>
+        <v>-291.71428571428532</v>
       </c>
       <c r="AJ20" s="27">
         <v>1717.8571428571427</v>
       </c>
       <c r="AK20" s="25">
-        <v>2249.571428571428</v>
+        <v>2009.571428571428</v>
       </c>
       <c r="AL20" s="28">
-        <v>48.4</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="21" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3136,106 +3134,106 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>1670</v>
+        <v>3094</v>
       </c>
       <c r="F21" s="14">
-        <v>1820.3000000000002</v>
+        <v>3372.46</v>
       </c>
       <c r="G21" s="14">
-        <v>5.7568160451269197</v>
+        <v>10.665622062049515</v>
       </c>
       <c r="H21" s="30">
         <v>6382</v>
       </c>
       <c r="I21" s="15">
-        <v>-1230.9090909090905</v>
+        <v>193.09090909090946</v>
       </c>
       <c r="J21" s="16">
-        <v>3766</v>
+        <v>2029</v>
       </c>
       <c r="K21" s="13">
-        <v>4104.9400000000005</v>
+        <v>2211.61</v>
       </c>
       <c r="L21" s="14">
-        <v>12.227272727272727</v>
+        <v>6.587662337662338</v>
       </c>
       <c r="M21" s="30">
         <v>6776</v>
       </c>
       <c r="N21" s="15">
-        <v>686</v>
+        <v>-1051</v>
       </c>
       <c r="O21" s="16">
-        <v>66</v>
+        <v>384</v>
       </c>
       <c r="P21" s="17">
-        <v>71.940000000000012</v>
+        <v>418.56000000000006</v>
       </c>
       <c r="Q21" s="14">
-        <v>2.7552182163187857</v>
+        <v>16.030360531309299</v>
       </c>
       <c r="R21" s="16">
         <v>527</v>
       </c>
       <c r="S21" s="15">
-        <v>-293.31818181818181</v>
+        <v>24.681818181818187</v>
       </c>
       <c r="T21" s="18">
-        <v>536</v>
+        <v>440</v>
       </c>
       <c r="U21" s="17">
-        <v>584.24</v>
+        <v>479.6</v>
       </c>
       <c r="V21" s="14">
-        <v>5.6938676967648476</v>
+        <v>4.6740704973442782</v>
       </c>
       <c r="W21" s="16">
         <v>2071</v>
       </c>
       <c r="X21" s="15">
-        <v>-876.0454545454545</v>
+        <v>-972.0454545454545</v>
       </c>
       <c r="Y21" s="18">
-        <v>123</v>
+        <v>418</v>
       </c>
       <c r="Z21" s="17">
-        <v>134.07000000000002</v>
+        <v>455.62000000000006</v>
       </c>
       <c r="AA21" s="14">
-        <v>8.1017964071856294</v>
+        <v>18.173913043478262</v>
       </c>
       <c r="AB21" s="16">
-        <v>334</v>
+        <v>506</v>
       </c>
       <c r="AC21" s="15">
-        <v>-104.72727272727272</v>
+        <v>73</v>
       </c>
       <c r="AD21" s="19">
-        <v>6161</v>
+        <v>6365</v>
       </c>
       <c r="AE21" s="20">
-        <v>6715.4900000000007</v>
+        <v>6937.85</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
       </c>
       <c r="AG21" s="22">
-        <v>8.0410814170292113</v>
+        <v>8.3073337476693609</v>
       </c>
       <c r="AH21" s="23">
-        <v>0.80410814170292111</v>
+        <v>0.83073337476693598</v>
       </c>
       <c r="AI21" s="26">
-        <v>-1500.9047619047615</v>
+        <v>-1296.9047619047615</v>
       </c>
       <c r="AJ21" s="27">
         <v>3830.9523809523807</v>
       </c>
       <c r="AK21" s="25">
-        <v>5331.8571428571422</v>
+        <v>5127.8571428571422</v>
       </c>
       <c r="AL21" s="28">
-        <v>114.0925925925926</v>
+        <v>117.87037037037037</v>
       </c>
     </row>
     <row r="22" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3249,70 +3247,70 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1580</v>
+        <v>1343</v>
       </c>
       <c r="F22" s="14">
-        <v>1722.2</v>
+        <v>1463.8700000000001</v>
       </c>
       <c r="G22" s="14">
-        <v>8.1044532525064117</v>
+        <v>6.8887852646304495</v>
       </c>
       <c r="H22" s="30">
         <v>4289</v>
       </c>
       <c r="I22" s="15">
-        <v>-369.54545454545473</v>
+        <v>-606.54545454545473</v>
       </c>
       <c r="J22" s="16">
-        <v>1378</v>
+        <v>661</v>
       </c>
       <c r="K22" s="13">
-        <v>1502.0200000000002</v>
+        <v>720.49</v>
       </c>
       <c r="L22" s="14">
-        <v>12.542821679768307</v>
+        <v>6.016549441456351</v>
       </c>
       <c r="M22" s="30">
         <v>2417</v>
       </c>
       <c r="N22" s="15">
-        <v>279.36363636363649</v>
+        <v>-437.63636363636351</v>
       </c>
       <c r="O22" s="16">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="P22" s="17">
-        <v>25.07</v>
+        <v>201.65</v>
       </c>
       <c r="Q22" s="14">
-        <v>2.4803921568627456</v>
+        <v>19.950980392156865</v>
       </c>
       <c r="R22" s="16">
         <v>203.99999999999997</v>
       </c>
       <c r="S22" s="15">
-        <v>-116.09090909090907</v>
+        <v>45.909090909090935</v>
       </c>
       <c r="T22" s="18">
-        <v>382</v>
+        <v>300</v>
       </c>
       <c r="U22" s="17">
-        <v>416.38000000000005</v>
+        <v>327</v>
       </c>
       <c r="V22" s="14">
-        <v>11.853314527503526</v>
+        <v>9.3088857545839208</v>
       </c>
       <c r="W22" s="16">
         <v>709</v>
       </c>
       <c r="X22" s="15">
-        <v>-101.40909090909088</v>
+        <v>-183.40909090909088</v>
       </c>
       <c r="Y22" s="18">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="Z22" s="17">
-        <v>0</v>
+        <v>235.44000000000003</v>
       </c>
       <c r="AA22" s="14">
         <v>0</v>
@@ -3321,34 +3319,34 @@
         <v>0</v>
       </c>
       <c r="AC22" s="15">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="AD22" s="19">
-        <v>3363</v>
+        <v>2705</v>
       </c>
       <c r="AE22" s="20">
-        <v>3665.67</v>
+        <v>2948.4500000000003</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
       </c>
       <c r="AG22" s="22">
-        <v>9.2693266832917711</v>
+        <v>7.4557028481428009</v>
       </c>
       <c r="AH22" s="23">
-        <v>0.92693266832917709</v>
+        <v>0.74557028481428012</v>
       </c>
       <c r="AI22" s="26">
-        <v>-265.09523809523807</v>
+        <v>-923.09523809523807</v>
       </c>
       <c r="AJ22" s="27">
         <v>1814.047619047619</v>
       </c>
       <c r="AK22" s="25">
-        <v>2079.1428571428569</v>
+        <v>2737.1428571428569</v>
       </c>
       <c r="AL22" s="28">
-        <v>62.277777777777779</v>
+        <v>50.092592592592595</v>
       </c>
     </row>
     <row r="23" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3362,106 +3360,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>10109</v>
+        <v>9667</v>
       </c>
       <c r="F23" s="14">
-        <v>11726.439999999999</v>
+        <v>11213.72</v>
       </c>
       <c r="G23" s="14">
-        <v>5.8996206594689236</v>
+        <v>5.6416690983367372</v>
       </c>
       <c r="H23" s="30">
         <v>37697</v>
       </c>
       <c r="I23" s="15">
-        <v>-7026</v>
+        <v>-7468</v>
       </c>
       <c r="J23" s="16">
-        <v>15737</v>
+        <v>20171</v>
       </c>
       <c r="K23" s="13">
-        <v>18254.919999999998</v>
+        <v>23398.359999999997</v>
       </c>
       <c r="L23" s="14">
-        <v>18.093232296838256</v>
+        <v>23.191115756467209</v>
       </c>
       <c r="M23" s="30">
         <v>19135</v>
       </c>
       <c r="N23" s="15">
-        <v>7039.2727272727279</v>
+        <v>11473.272727272728</v>
       </c>
       <c r="O23" s="16">
-        <v>770</v>
+        <v>2186</v>
       </c>
       <c r="P23" s="17">
-        <v>893.19999999999993</v>
+        <v>2535.7599999999998</v>
       </c>
       <c r="Q23" s="14">
-        <v>5.3726609578179509</v>
+        <v>15.252775134792262</v>
       </c>
       <c r="R23" s="16">
         <v>3153</v>
       </c>
       <c r="S23" s="15">
-        <v>-1379.772727272727</v>
+        <v>36.227272727272975</v>
       </c>
       <c r="T23" s="18">
-        <v>5085</v>
+        <v>4060</v>
       </c>
       <c r="U23" s="17">
-        <v>5898.5999999999995</v>
+        <v>4709.5999999999995</v>
       </c>
       <c r="V23" s="14">
-        <v>8.4545042321644495</v>
+        <v>6.750302297460701</v>
       </c>
       <c r="W23" s="16">
         <v>13232</v>
       </c>
       <c r="X23" s="15">
-        <v>-3936.818181818182</v>
+        <v>-4961.818181818182</v>
       </c>
       <c r="Y23" s="18">
-        <v>450</v>
+        <v>747</v>
       </c>
       <c r="Z23" s="17">
-        <v>522</v>
+        <v>866.52</v>
       </c>
       <c r="AA23" s="14">
-        <v>13.469387755102042</v>
+        <v>14.880478087649401</v>
       </c>
       <c r="AB23" s="16">
-        <v>735</v>
+        <v>1104.4000000000001</v>
       </c>
       <c r="AC23" s="15">
-        <v>-51.136363636363626</v>
+        <v>-6</v>
       </c>
       <c r="AD23" s="19">
-        <v>32151</v>
+        <v>36831</v>
       </c>
       <c r="AE23" s="20">
-        <v>37295.159999999996</v>
+        <v>42723.96</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
       </c>
       <c r="AG23" s="22">
-        <v>9.1298545002163554</v>
+        <v>10.458824643011681</v>
       </c>
       <c r="AH23" s="23">
-        <v>0.91298545002163556</v>
+        <v>1.0458824643011682</v>
       </c>
       <c r="AI23" s="26">
-        <v>-3064.238095238099</v>
+        <v>1615.761904761901</v>
       </c>
       <c r="AJ23" s="27">
         <v>17607.61904761905</v>
       </c>
       <c r="AK23" s="25">
-        <v>20671.857142857149</v>
+        <v>15991.857142857149</v>
       </c>
       <c r="AL23" s="28">
-        <v>595.38888888888891</v>
+        <v>682.05555555555554</v>
       </c>
     </row>
     <row r="24" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3475,106 +3473,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>7599</v>
+        <v>8018</v>
       </c>
       <c r="F24" s="14">
-        <v>8814.84</v>
+        <v>9300.8799999999992</v>
       </c>
       <c r="G24" s="14">
-        <v>6.2245141112517688</v>
+        <v>6.5677265619182368</v>
       </c>
       <c r="H24" s="30">
         <v>26858</v>
       </c>
       <c r="I24" s="15">
-        <v>-4609.181818181818</v>
+        <v>-4190.181818181818</v>
       </c>
       <c r="J24" s="16">
-        <v>10555</v>
+        <v>8904</v>
       </c>
       <c r="K24" s="13">
-        <v>12243.8</v>
+        <v>10328.64</v>
       </c>
       <c r="L24" s="14">
-        <v>19.461112973516595</v>
+        <v>16.417029835735836</v>
       </c>
       <c r="M24" s="30">
         <v>11932</v>
       </c>
       <c r="N24" s="15">
-        <v>5131.363636363636</v>
+        <v>3480.363636363636</v>
       </c>
       <c r="O24" s="16">
-        <v>520</v>
+        <v>1288</v>
       </c>
       <c r="P24" s="17">
-        <v>603.19999999999993</v>
+        <v>1494.08</v>
       </c>
       <c r="Q24" s="14">
-        <v>6.0561143462149287</v>
+        <v>15.00052938062467</v>
       </c>
       <c r="R24" s="16">
         <v>1889</v>
       </c>
       <c r="S24" s="15">
-        <v>-767.9545454545455</v>
+        <v>4.5454545454504114E-2</v>
       </c>
       <c r="T24" s="18">
-        <v>4403</v>
+        <v>3824</v>
       </c>
       <c r="U24" s="17">
-        <v>5107.4799999999996</v>
+        <v>4435.84</v>
       </c>
       <c r="V24" s="14">
-        <v>13.320407040704071</v>
+        <v>11.568756875687567</v>
       </c>
       <c r="W24" s="16">
         <v>7272</v>
       </c>
       <c r="X24" s="15">
-        <v>-555.18181818181802</v>
+        <v>-1134.181818181818</v>
       </c>
       <c r="Y24" s="18">
-        <v>499</v>
+        <v>816</v>
       </c>
       <c r="Z24" s="17">
-        <v>578.83999999999992</v>
+        <v>946.56</v>
       </c>
       <c r="AA24" s="14">
-        <v>24.180616740088105</v>
+        <v>23.314285714285713</v>
       </c>
       <c r="AB24" s="16">
-        <v>454</v>
+        <v>770</v>
       </c>
       <c r="AC24" s="15">
-        <v>189.45454545454544</v>
+        <v>291</v>
       </c>
       <c r="AD24" s="19">
-        <v>23576</v>
+        <v>22850</v>
       </c>
       <c r="AE24" s="20">
-        <v>27348.16</v>
+        <v>26505.999999999996</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
       </c>
       <c r="AG24" s="22">
-        <v>10.228199566160521</v>
+        <v>9.9132321041214748</v>
       </c>
       <c r="AH24" s="23">
-        <v>1.0228199566160521</v>
+        <v>0.99132321041214755</v>
       </c>
       <c r="AI24" s="26">
-        <v>526</v>
+        <v>-200</v>
       </c>
       <c r="AJ24" s="27">
         <v>11525</v>
       </c>
       <c r="AK24" s="25">
-        <v>10999</v>
+        <v>11725</v>
       </c>
       <c r="AL24" s="28">
-        <v>436.59259259259261</v>
+        <v>423.14814814814815</v>
       </c>
     </row>
     <row r="25" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3588,106 +3586,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>9638</v>
+        <v>8261</v>
       </c>
       <c r="F25" s="14">
-        <v>11180.08</v>
+        <v>9582.76</v>
       </c>
       <c r="G25" s="14">
-        <v>8.2108116480793072</v>
+        <v>7.0377168525402727</v>
       </c>
       <c r="H25" s="30">
         <v>25824</v>
       </c>
       <c r="I25" s="15">
-        <v>-2100.181818181818</v>
+        <v>-3477.181818181818</v>
       </c>
       <c r="J25" s="16">
-        <v>6217</v>
+        <v>4167</v>
       </c>
       <c r="K25" s="13">
-        <v>7211.7199999999993</v>
+        <v>4833.7199999999993</v>
       </c>
       <c r="L25" s="14">
-        <v>11.48299890857191</v>
+        <v>7.6965829905129715</v>
       </c>
       <c r="M25" s="30">
         <v>11911</v>
       </c>
       <c r="N25" s="15">
-        <v>802.90909090909099</v>
+        <v>-1247.090909090909</v>
       </c>
       <c r="O25" s="16">
-        <v>725</v>
+        <v>1408</v>
       </c>
       <c r="P25" s="17">
-        <v>840.99999999999989</v>
+        <v>1633.28</v>
       </c>
       <c r="Q25" s="14">
-        <v>7.2598998634501593</v>
+        <v>14.099226217569413</v>
       </c>
       <c r="R25" s="16">
         <v>2197</v>
       </c>
       <c r="S25" s="15">
-        <v>-772.9545454545455</v>
+        <v>-89.954545454545496</v>
       </c>
       <c r="T25" s="18">
-        <v>4283</v>
+        <v>3663</v>
       </c>
       <c r="U25" s="17">
-        <v>4968.28</v>
+        <v>4249.08</v>
       </c>
       <c r="V25" s="14">
-        <v>13.076047737996113</v>
+        <v>11.183180682764363</v>
       </c>
       <c r="W25" s="16">
         <v>7206.0000000000009</v>
       </c>
       <c r="X25" s="15">
-        <v>-630.18181818181802</v>
+        <v>-1250.181818181818</v>
       </c>
       <c r="Y25" s="18">
-        <v>512</v>
+        <v>848</v>
       </c>
       <c r="Z25" s="17">
-        <v>593.91999999999996</v>
+        <v>983.68</v>
       </c>
       <c r="AA25" s="14">
-        <v>24.593886462882097</v>
+        <v>27.006369426751593</v>
       </c>
       <c r="AB25" s="16">
-        <v>458</v>
+        <v>690.8</v>
       </c>
       <c r="AC25" s="15">
-        <v>199.72727272727275</v>
+        <v>377</v>
       </c>
       <c r="AD25" s="19">
-        <v>21375</v>
+        <v>18347</v>
       </c>
       <c r="AE25" s="20">
-        <v>24795</v>
+        <v>21282.519999999997</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
       </c>
       <c r="AG25" s="22">
-        <v>9.4309395747541807</v>
+        <v>8.0949449533574249</v>
       </c>
       <c r="AH25" s="23">
-        <v>0.94309395747541813</v>
+        <v>0.80949449533574247</v>
       </c>
       <c r="AI25" s="26">
-        <v>-1289.7619047619046</v>
+        <v>-4317.7619047619046</v>
       </c>
       <c r="AJ25" s="27">
         <v>11332.380952380952</v>
       </c>
       <c r="AK25" s="25">
-        <v>12622.142857142857</v>
+        <v>15650.142857142857</v>
       </c>
       <c r="AL25" s="28">
-        <v>395.83333333333331</v>
+        <v>339.75925925925924</v>
       </c>
     </row>
     <row r="26" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3701,106 +3699,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>9062</v>
+        <v>6157</v>
       </c>
       <c r="F26" s="14">
-        <v>10511.92</v>
+        <v>7142.12</v>
       </c>
       <c r="G26" s="14">
-        <v>6.3542310756972107</v>
+        <v>4.3172589641434262</v>
       </c>
       <c r="H26" s="30">
         <v>31375</v>
       </c>
       <c r="I26" s="15">
-        <v>-5199.3636363636379</v>
+        <v>-8104.3636363636379</v>
       </c>
       <c r="J26" s="16">
-        <v>13137</v>
+        <v>11022</v>
       </c>
       <c r="K26" s="13">
-        <v>15238.919999999998</v>
+        <v>12785.519999999999</v>
       </c>
       <c r="L26" s="14">
-        <v>20.498900631250443</v>
+        <v>17.198666572097313</v>
       </c>
       <c r="M26" s="30">
         <v>14099</v>
       </c>
       <c r="N26" s="15">
-        <v>6728.363636363636</v>
+        <v>4613.363636363636</v>
       </c>
       <c r="O26" s="16">
-        <v>568</v>
+        <v>1240</v>
       </c>
       <c r="P26" s="17">
-        <v>658.88</v>
+        <v>1438.3999999999999</v>
       </c>
       <c r="Q26" s="14">
-        <v>6.8659340659340655</v>
+        <v>14.989010989010987</v>
       </c>
       <c r="R26" s="16">
         <v>1820</v>
       </c>
       <c r="S26" s="15">
-        <v>-672.90909090909099</v>
+        <v>-0.90909090909099177</v>
       </c>
       <c r="T26" s="18">
-        <v>4900</v>
+        <v>4327</v>
       </c>
       <c r="U26" s="17">
-        <v>5684</v>
+        <v>5019.32</v>
       </c>
       <c r="V26" s="14">
-        <v>12.947393706461687</v>
+        <v>11.433341340379535</v>
       </c>
       <c r="W26" s="16">
         <v>8326</v>
       </c>
       <c r="X26" s="15">
-        <v>-776.81818181818198</v>
+        <v>-1349.818181818182</v>
       </c>
       <c r="Y26" s="18">
-        <v>577</v>
+        <v>925</v>
       </c>
       <c r="Z26" s="17">
-        <v>669.31999999999994</v>
+        <v>1073</v>
       </c>
       <c r="AA26" s="14">
-        <v>23.771535580524343</v>
+        <v>18.877551020408163</v>
       </c>
       <c r="AB26" s="16">
-        <v>534</v>
+        <v>1078</v>
       </c>
       <c r="AC26" s="15">
-        <v>212.90909090909088</v>
+        <v>190</v>
       </c>
       <c r="AD26" s="19">
-        <v>28244</v>
+        <v>23671</v>
       </c>
       <c r="AE26" s="20">
-        <v>32763.039999999997</v>
+        <v>27458.359999999997</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
       </c>
       <c r="AG26" s="22">
-        <v>10.56245325355273</v>
+        <v>8.8522812266267756</v>
       </c>
       <c r="AH26" s="23">
-        <v>1.056245325355273</v>
+        <v>0.88522812266267759</v>
       </c>
       <c r="AI26" s="26">
-        <v>1504</v>
+        <v>-3069</v>
       </c>
       <c r="AJ26" s="27">
         <v>13370</v>
       </c>
       <c r="AK26" s="25">
-        <v>11866</v>
+        <v>16439</v>
       </c>
       <c r="AL26" s="28">
-        <v>523.03703703703707</v>
+        <v>438.35185185185185</v>
       </c>
     </row>
     <row r="27" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3814,106 +3812,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>1826</v>
+        <v>1164</v>
       </c>
       <c r="F27" s="14">
-        <v>2118.16</v>
+        <v>1350.24</v>
       </c>
       <c r="G27" s="14">
-        <v>11.075820237110559</v>
+        <v>7.0603804797353176</v>
       </c>
       <c r="H27" s="30">
         <v>3627</v>
       </c>
       <c r="I27" s="15">
-        <v>177.36363636363626</v>
+        <v>-484.63636363636374</v>
       </c>
       <c r="J27" s="16">
-        <v>3950</v>
+        <v>5278</v>
       </c>
       <c r="K27" s="13">
-        <v>4582</v>
+        <v>6122.48</v>
       </c>
       <c r="L27" s="14">
-        <v>34.307145677062771</v>
+        <v>45.841294907224636</v>
       </c>
       <c r="M27" s="30">
         <v>2533</v>
       </c>
       <c r="N27" s="15">
-        <v>2798.6363636363635</v>
+        <v>4126.636363636364</v>
       </c>
       <c r="O27" s="16">
-        <v>6</v>
+        <v>649</v>
       </c>
       <c r="P27" s="17">
-        <v>6.9599999999999991</v>
+        <v>752.83999999999992</v>
       </c>
       <c r="Q27" s="14">
-        <v>0.31428571428571428</v>
+        <v>33.995238095238093</v>
       </c>
       <c r="R27" s="16">
         <v>420</v>
       </c>
       <c r="S27" s="15">
-        <v>-280.36363636363637</v>
+        <v>362.63636363636363</v>
       </c>
       <c r="T27" s="18">
-        <v>780</v>
+        <v>660</v>
       </c>
       <c r="U27" s="17">
-        <v>904.8</v>
+        <v>765.59999999999991</v>
       </c>
       <c r="V27" s="14">
-        <v>11.237721021611005</v>
+        <v>9.5088408644400815</v>
       </c>
       <c r="W27" s="16">
         <v>1526.9999999999998</v>
       </c>
       <c r="X27" s="15">
-        <v>-261.13636363636328</v>
+        <v>-381.13636363636328</v>
       </c>
       <c r="Y27" s="18">
-        <v>289</v>
+        <v>496</v>
       </c>
       <c r="Z27" s="17">
-        <v>335.23999999999995</v>
+        <v>575.36</v>
       </c>
       <c r="AA27" s="14">
-        <v>96.333333333333329</v>
+        <v>42.03389830508474</v>
       </c>
       <c r="AB27" s="16">
-        <v>66</v>
+        <v>259.60000000000002</v>
       </c>
       <c r="AC27" s="15">
-        <v>244</v>
+        <v>319</v>
       </c>
       <c r="AD27" s="19">
-        <v>6851</v>
+        <v>8247</v>
       </c>
       <c r="AE27" s="20">
-        <v>7947.16</v>
+        <v>9566.5199999999986</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
       </c>
       <c r="AG27" s="22">
-        <v>17.603205677229901</v>
+        <v>21.190138260124801</v>
       </c>
       <c r="AH27" s="23">
-        <v>1.7603205677229903</v>
+        <v>2.11901382601248</v>
       </c>
       <c r="AI27" s="26">
-        <v>2959.0952380952381</v>
+        <v>4355.0952380952385</v>
       </c>
       <c r="AJ27" s="27">
         <v>1945.952380952381</v>
       </c>
       <c r="AK27" s="25">
-        <v>-1013.1428571428571</v>
+        <v>-2409.1428571428578</v>
       </c>
       <c r="AL27" s="28">
-        <v>126.87037037037037</v>
+        <v>152.72222222222223</v>
       </c>
     </row>
     <row r="28" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3927,106 +3925,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>1744</v>
+        <v>1060</v>
       </c>
       <c r="F28" s="14">
-        <v>2023.04</v>
+        <v>1229.5999999999999</v>
       </c>
       <c r="G28" s="14">
-        <v>10.223288036237676</v>
+        <v>6.2136957100985875</v>
       </c>
       <c r="H28" s="30">
         <v>3753</v>
       </c>
       <c r="I28" s="15">
-        <v>38.090909090909008</v>
+        <v>-645.90909090909099</v>
       </c>
       <c r="J28" s="16">
-        <v>2527</v>
+        <v>1124</v>
       </c>
       <c r="K28" s="13">
-        <v>2931.3199999999997</v>
+        <v>1303.8399999999999</v>
       </c>
       <c r="L28" s="14">
-        <v>16.659874138447709</v>
+        <v>7.4102487264009591</v>
       </c>
       <c r="M28" s="30">
         <v>3337</v>
       </c>
       <c r="N28" s="15">
-        <v>1010.181818181818</v>
+        <v>-392.81818181818198</v>
       </c>
       <c r="O28" s="16">
-        <v>8</v>
+        <v>656</v>
       </c>
       <c r="P28" s="17">
-        <v>9.2799999999999994</v>
+        <v>760.95999999999992</v>
       </c>
       <c r="Q28" s="14">
-        <v>0.33333333333333331</v>
+        <v>27.333333333333332</v>
       </c>
       <c r="R28" s="16">
         <v>528</v>
       </c>
       <c r="S28" s="15">
-        <v>-352</v>
+        <v>296</v>
       </c>
       <c r="T28" s="18">
-        <v>551</v>
+        <v>334</v>
       </c>
       <c r="U28" s="17">
-        <v>639.16</v>
+        <v>387.44</v>
       </c>
       <c r="V28" s="14">
-        <v>9.3461835003855054</v>
+        <v>5.66538164996145</v>
       </c>
       <c r="W28" s="16">
         <v>1297</v>
       </c>
       <c r="X28" s="15">
-        <v>-333.31818181818176</v>
+        <v>-550.31818181818176</v>
       </c>
       <c r="Y28" s="18">
-        <v>248</v>
+        <v>455</v>
       </c>
       <c r="Z28" s="17">
-        <v>287.68</v>
+        <v>527.79999999999995</v>
       </c>
       <c r="AA28" s="14">
-        <v>67.358024691358025</v>
+        <v>25.852272727272727</v>
       </c>
       <c r="AB28" s="16">
-        <v>81</v>
+        <v>387.20000000000005</v>
       </c>
       <c r="AC28" s="15">
-        <v>192.77272727272728</v>
+        <v>191</v>
       </c>
       <c r="AD28" s="19">
-        <v>5078</v>
+        <v>3629</v>
       </c>
       <c r="AE28" s="20">
-        <v>5890.48</v>
+        <v>4209.6399999999994</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
       </c>
       <c r="AG28" s="22">
-        <v>11.853935082258781</v>
+        <v>8.4714317474433081</v>
       </c>
       <c r="AH28" s="23">
-        <v>1.1853935082258782</v>
+        <v>0.84714317474433076</v>
       </c>
       <c r="AI28" s="26">
-        <v>794.19047619047615</v>
+        <v>-654.80952380952385</v>
       </c>
       <c r="AJ28" s="27">
         <v>2141.9047619047619</v>
       </c>
       <c r="AK28" s="25">
-        <v>1347.7142857142858</v>
+        <v>2796.7142857142858</v>
       </c>
       <c r="AL28" s="28">
-        <v>94.037037037037038</v>
+        <v>67.203703703703709</v>
       </c>
     </row>
     <row r="29" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4040,106 +4038,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>1591</v>
+        <v>890</v>
       </c>
       <c r="F29" s="14">
-        <v>1845.56</v>
+        <v>1032.3999999999999</v>
       </c>
       <c r="G29" s="14">
-        <v>9.1989487516425754</v>
+        <v>5.1458607095926405</v>
       </c>
       <c r="H29" s="30">
         <v>3805.0000000000005</v>
       </c>
       <c r="I29" s="15">
-        <v>-138.54545454545473</v>
+        <v>-839.54545454545473</v>
       </c>
       <c r="J29" s="16">
-        <v>3248</v>
+        <v>5730</v>
       </c>
       <c r="K29" s="13">
-        <v>3767.68</v>
+        <v>6646.7999999999993</v>
       </c>
       <c r="L29" s="14">
-        <v>26.318968692449356</v>
+        <v>46.430939226519335</v>
       </c>
       <c r="M29" s="30">
         <v>2715</v>
       </c>
       <c r="N29" s="15">
-        <v>2013.909090909091</v>
+        <v>4495.909090909091</v>
       </c>
       <c r="O29" s="16">
-        <v>4</v>
+        <v>652</v>
       </c>
       <c r="P29" s="17">
-        <v>4.6399999999999997</v>
+        <v>756.31999999999994</v>
       </c>
       <c r="Q29" s="14">
-        <v>0.1837160751565762</v>
+        <v>29.945720250521919</v>
       </c>
       <c r="R29" s="16">
         <v>479</v>
       </c>
       <c r="S29" s="15">
-        <v>-322.59090909090912</v>
+        <v>325.40909090909088</v>
       </c>
       <c r="T29" s="18">
-        <v>507</v>
+        <v>290</v>
       </c>
       <c r="U29" s="17">
-        <v>588.12</v>
+        <v>336.4</v>
       </c>
       <c r="V29" s="14">
-        <v>9.7756354075372478</v>
+        <v>5.5915863277826467</v>
       </c>
       <c r="W29" s="16">
         <v>1141</v>
       </c>
       <c r="X29" s="15">
-        <v>-270.9545454545455</v>
+        <v>-487.9545454545455</v>
       </c>
       <c r="Y29" s="18">
-        <v>252</v>
+        <v>454</v>
       </c>
       <c r="Z29" s="17">
-        <v>292.32</v>
+        <v>526.64</v>
       </c>
       <c r="AA29" s="14">
-        <v>84</v>
+        <v>19.401709401709404</v>
       </c>
       <c r="AB29" s="16">
-        <v>66</v>
+        <v>514.79999999999995</v>
       </c>
       <c r="AC29" s="15">
-        <v>207</v>
+        <v>103</v>
       </c>
       <c r="AD29" s="19">
-        <v>5602</v>
+        <v>8016</v>
       </c>
       <c r="AE29" s="20">
-        <v>6498.32</v>
+        <v>9298.56</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
       </c>
       <c r="AG29" s="22">
-        <v>14.336095539848891</v>
+        <v>20.513770411893738</v>
       </c>
       <c r="AH29" s="23">
-        <v>1.433609553984889</v>
+        <v>2.0513770411893737</v>
       </c>
       <c r="AI29" s="26">
-        <v>1694.3809523809523</v>
+        <v>4108.3809523809523</v>
       </c>
       <c r="AJ29" s="27">
         <v>1953.8095238095239</v>
       </c>
       <c r="AK29" s="25">
-        <v>259.42857142857156</v>
+        <v>-2154.5714285714284</v>
       </c>
       <c r="AL29" s="28">
-        <v>103.74074074074075</v>
+        <v>148.44444444444446</v>
       </c>
     </row>
     <row r="30" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4153,106 +4151,106 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>255</v>
+        <v>701</v>
       </c>
       <c r="F30" s="14">
-        <v>938.40000000000009</v>
+        <v>2579.6800000000003</v>
       </c>
       <c r="G30" s="14">
-        <v>2.8261964735516369</v>
+        <v>7.7692695214105791</v>
       </c>
       <c r="H30" s="30">
         <v>1985</v>
       </c>
       <c r="I30" s="15">
-        <v>-647.27272727272737</v>
+        <v>-201.27272727272737</v>
       </c>
       <c r="J30" s="16">
-        <v>1881</v>
+        <v>1670</v>
       </c>
       <c r="K30" s="13">
-        <v>6922.08</v>
+        <v>6145.6</v>
       </c>
       <c r="L30" s="14">
-        <v>18.615384615384617</v>
+        <v>16.527215474583894</v>
       </c>
       <c r="M30" s="30">
         <v>2223</v>
       </c>
       <c r="N30" s="15">
-        <v>870.5454545454545</v>
+        <v>659.5454545454545</v>
       </c>
       <c r="O30" s="16">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="P30" s="17">
-        <v>11.040000000000001</v>
+        <v>294.40000000000003</v>
       </c>
       <c r="Q30" s="14">
-        <v>0.80487804878048785</v>
+        <v>21.463414634146343</v>
       </c>
       <c r="R30" s="16">
         <v>82</v>
       </c>
       <c r="S30" s="15">
-        <v>-52.909090909090907</v>
+        <v>24.090909090909093</v>
       </c>
       <c r="T30" s="18">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="U30" s="17">
-        <v>953.12</v>
+        <v>938.40000000000009</v>
       </c>
       <c r="V30" s="14">
-        <v>8.1633237822349578</v>
+        <v>8.0372492836676219</v>
       </c>
       <c r="W30" s="16">
         <v>698</v>
       </c>
       <c r="X30" s="15">
-        <v>-216.90909090909088</v>
+        <v>-220.90909090909088</v>
       </c>
       <c r="Y30" s="18">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="Z30" s="17">
-        <v>11.040000000000001</v>
+        <v>364.32</v>
       </c>
       <c r="AA30" s="14">
-        <v>0.7021276595744681</v>
+        <v>165</v>
       </c>
       <c r="AB30" s="16">
-        <v>94</v>
+        <v>13.2</v>
       </c>
       <c r="AC30" s="15">
-        <v>-61.090909090909093</v>
+        <v>90</v>
       </c>
       <c r="AD30" s="19">
-        <v>2401</v>
+        <v>2805</v>
       </c>
       <c r="AE30" s="20">
-        <v>8835.68</v>
+        <v>10322.4</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
       </c>
       <c r="AG30" s="22">
-        <v>9.9214876033057848</v>
+        <v>11.590909090909092</v>
       </c>
       <c r="AH30" s="23">
-        <v>0.99214876033057853</v>
+        <v>1.1590909090909092</v>
       </c>
       <c r="AI30" s="26">
-        <v>-19</v>
+        <v>385</v>
       </c>
       <c r="AJ30" s="27">
         <v>1210</v>
       </c>
       <c r="AK30" s="25">
-        <v>1229</v>
+        <v>825</v>
       </c>
       <c r="AL30" s="28">
-        <v>150.0625</v>
+        <v>175.3125</v>
       </c>
     </row>
     <row r="31" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4266,106 +4264,106 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>184</v>
+        <v>117</v>
       </c>
       <c r="F31" s="14">
-        <v>677.12</v>
+        <v>430.56</v>
       </c>
       <c r="G31" s="14">
-        <v>3.3761467889908259</v>
+        <v>2.1467889908256881</v>
       </c>
       <c r="H31" s="30">
         <v>1199</v>
       </c>
       <c r="I31" s="15">
-        <v>-361</v>
+        <v>-428</v>
       </c>
       <c r="J31" s="16">
-        <v>219</v>
+        <v>1150</v>
       </c>
       <c r="K31" s="13">
-        <v>805.92000000000007</v>
+        <v>4232</v>
       </c>
       <c r="L31" s="14">
-        <v>3.2909836065573779</v>
+        <v>17.281420765027327</v>
       </c>
       <c r="M31" s="30">
         <v>1463.9999999999998</v>
       </c>
       <c r="N31" s="15">
-        <v>-446.45454545454527</v>
+        <v>484.54545454545473</v>
       </c>
       <c r="O31" s="16">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="P31" s="17">
-        <v>62.56</v>
+        <v>121.44000000000001</v>
       </c>
       <c r="Q31" s="14">
-        <v>9.35</v>
+        <v>18.150000000000002</v>
       </c>
       <c r="R31" s="16">
         <v>40</v>
       </c>
       <c r="S31" s="15">
-        <v>-10.272727272727273</v>
+        <v>5.7272727272727266</v>
       </c>
       <c r="T31" s="18">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="U31" s="17">
-        <v>544.64</v>
+        <v>522.56000000000006</v>
       </c>
       <c r="V31" s="14">
-        <v>12.380228136882129</v>
+        <v>11.878326996197718</v>
       </c>
       <c r="W31" s="16">
         <v>263</v>
       </c>
       <c r="X31" s="15">
-        <v>-31.318181818181813</v>
+        <v>-37.318181818181813</v>
       </c>
       <c r="Y31" s="18">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="Z31" s="17">
-        <v>73.600000000000009</v>
+        <v>250.24</v>
       </c>
       <c r="AA31" s="14">
-        <v>22</v>
+        <v>56.666666666666671</v>
       </c>
       <c r="AB31" s="16">
-        <v>20</v>
+        <v>26.4</v>
       </c>
       <c r="AC31" s="15">
-        <v>6.3636363636363633</v>
+        <v>50</v>
       </c>
       <c r="AD31" s="19">
-        <v>588</v>
+        <v>1510</v>
       </c>
       <c r="AE31" s="20">
-        <v>2163.84</v>
+        <v>5556.8</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
       </c>
       <c r="AG31" s="22">
-        <v>4.1352980576021432</v>
+        <v>10.619557937039517</v>
       </c>
       <c r="AH31" s="23">
-        <v>0.41352980576021431</v>
+        <v>1.0619557937039517</v>
       </c>
       <c r="AI31" s="26">
-        <v>-833.90476190476193</v>
+        <v>88.095238095238074</v>
       </c>
       <c r="AJ31" s="27">
         <v>710.95238095238096</v>
       </c>
       <c r="AK31" s="25">
-        <v>1544.8571428571429</v>
+        <v>622.85714285714289</v>
       </c>
       <c r="AL31" s="28">
-        <v>36.75</v>
+        <v>94.375</v>
       </c>
     </row>
     <row r="32" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4379,106 +4377,106 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>1714</v>
+        <v>3098</v>
       </c>
       <c r="F32" s="14">
-        <v>7113.1</v>
+        <v>12856.7</v>
       </c>
       <c r="G32" s="14">
-        <v>7.8476586888657653</v>
+        <v>14.1843912591051</v>
       </c>
       <c r="H32" s="30">
         <v>4805</v>
       </c>
       <c r="I32" s="15">
-        <v>-470.09090909090901</v>
+        <v>913.90909090909099</v>
       </c>
       <c r="J32" s="16">
-        <v>1640</v>
+        <v>1043</v>
       </c>
       <c r="K32" s="13">
-        <v>6806.0000000000009</v>
+        <v>4328.4500000000007</v>
       </c>
       <c r="L32" s="14">
-        <v>9.5677539114293282</v>
+        <v>6.0848581278175544</v>
       </c>
       <c r="M32" s="30">
         <v>3771.0000000000005</v>
       </c>
       <c r="N32" s="15">
-        <v>-74.090909090909463</v>
+        <v>-671.09090909090946</v>
       </c>
       <c r="O32" s="16">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="P32" s="17">
-        <v>240.70000000000002</v>
+        <v>871.50000000000011</v>
       </c>
       <c r="Q32" s="14">
-        <v>4.5409252669039146</v>
+        <v>16.441281138790035</v>
       </c>
       <c r="R32" s="16">
         <v>281</v>
       </c>
       <c r="S32" s="15">
-        <v>-133.59090909090909</v>
+        <v>18.409090909090907</v>
       </c>
       <c r="T32" s="18">
-        <v>557</v>
+        <v>427</v>
       </c>
       <c r="U32" s="17">
-        <v>2311.5500000000002</v>
+        <v>1772.0500000000002</v>
       </c>
       <c r="V32" s="14">
-        <v>6.6925177498634625</v>
+        <v>5.1305297651556518</v>
       </c>
       <c r="W32" s="16">
         <v>1831</v>
       </c>
       <c r="X32" s="15">
-        <v>-691.40909090909099</v>
+        <v>-821.40909090909099</v>
       </c>
       <c r="Y32" s="18">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="Z32" s="17">
-        <v>423.3</v>
+        <v>643.25</v>
       </c>
       <c r="AA32" s="14">
-        <v>25.793103448275861</v>
+        <v>29.807692307692307</v>
       </c>
       <c r="AB32" s="16">
-        <v>87</v>
+        <v>114.4</v>
       </c>
       <c r="AC32" s="15">
-        <v>42.68181818181818</v>
+        <v>77</v>
       </c>
       <c r="AD32" s="19">
-        <v>4071</v>
+        <v>4933</v>
       </c>
       <c r="AE32" s="20">
-        <v>16894.650000000001</v>
+        <v>20471.95</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
       </c>
       <c r="AG32" s="22">
-        <v>7.9341995359628772</v>
+        <v>9.6141995359628769</v>
       </c>
       <c r="AH32" s="23">
-        <v>0.7934199535962877</v>
+        <v>0.96141995359628774</v>
       </c>
       <c r="AI32" s="26">
-        <v>-1059.9523809523807</v>
+        <v>-197.95238095238074</v>
       </c>
       <c r="AJ32" s="27">
         <v>2565.4761904761904</v>
       </c>
       <c r="AK32" s="25">
-        <v>3625.4285714285711</v>
+        <v>2763.4285714285711</v>
       </c>
       <c r="AL32" s="28">
-        <v>254.4375</v>
+        <v>308.3125</v>
       </c>
     </row>
     <row r="33" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4492,106 +4490,106 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>1214</v>
+        <v>1675</v>
       </c>
       <c r="F33" s="14">
-        <v>5038.1000000000004</v>
+        <v>6951.2500000000009</v>
       </c>
       <c r="G33" s="14">
-        <v>3.0315550510783202</v>
+        <v>4.182746878547106</v>
       </c>
       <c r="H33" s="30">
         <v>8810</v>
       </c>
       <c r="I33" s="15">
-        <v>-2790.5454545454545</v>
+        <v>-2329.5454545454545</v>
       </c>
       <c r="J33" s="16">
-        <v>3796</v>
+        <v>4267</v>
       </c>
       <c r="K33" s="13">
-        <v>15753.400000000001</v>
+        <v>17708.050000000003</v>
       </c>
       <c r="L33" s="14">
-        <v>16.462054011433075</v>
+        <v>18.504632367435441</v>
       </c>
       <c r="M33" s="30">
         <v>5073</v>
       </c>
       <c r="N33" s="15">
-        <v>1490.090909090909</v>
+        <v>1961.090909090909</v>
       </c>
       <c r="O33" s="16">
-        <v>66</v>
+        <v>266</v>
       </c>
       <c r="P33" s="17">
-        <v>273.90000000000003</v>
+        <v>1103.9000000000001</v>
       </c>
       <c r="Q33" s="14">
-        <v>4.0445682451253484</v>
+        <v>16.300835654596103</v>
       </c>
       <c r="R33" s="16">
         <v>359</v>
       </c>
       <c r="S33" s="15">
-        <v>-178.77272727272725</v>
+        <v>21.227272727272748</v>
       </c>
       <c r="T33" s="18">
-        <v>963</v>
+        <v>772</v>
       </c>
       <c r="U33" s="17">
-        <v>3996.4500000000003</v>
+        <v>3203.8</v>
       </c>
       <c r="V33" s="14">
-        <v>8.2693208430913359</v>
+        <v>6.6291959406713508</v>
       </c>
       <c r="W33" s="16">
         <v>2562</v>
       </c>
       <c r="X33" s="15">
-        <v>-783.81818181818176</v>
+        <v>-974.81818181818176</v>
       </c>
       <c r="Y33" s="18">
-        <v>10</v>
+        <v>252</v>
       </c>
       <c r="Z33" s="17">
-        <v>41.5</v>
+        <v>1045.8000000000002</v>
       </c>
       <c r="AA33" s="14">
-        <v>0.93617021276595747</v>
+        <v>96.92307692307692</v>
       </c>
       <c r="AB33" s="16">
-        <v>235</v>
+        <v>57.2</v>
       </c>
       <c r="AC33" s="15">
-        <v>-150.22727272727272</v>
+        <v>213</v>
       </c>
       <c r="AD33" s="19">
-        <v>6049</v>
+        <v>7232</v>
       </c>
       <c r="AE33" s="20">
-        <v>25103.350000000002</v>
+        <v>30012.800000000003</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
       </c>
       <c r="AG33" s="22">
-        <v>7.4551910323375781</v>
+        <v>8.9131991314044257</v>
       </c>
       <c r="AH33" s="23">
-        <v>0.74551910323375781</v>
+        <v>0.89131991314044245</v>
       </c>
       <c r="AI33" s="26">
-        <v>-2064.8095238095239</v>
+        <v>-881.80952380952385</v>
       </c>
       <c r="AJ33" s="27">
         <v>4056.9047619047619</v>
       </c>
       <c r="AK33" s="25">
-        <v>6121.7142857142862</v>
+        <v>4938.7142857142862</v>
       </c>
       <c r="AL33" s="28">
-        <v>378.0625</v>
+        <v>452</v>
       </c>
     </row>
     <row r="34" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4620,10 +4618,10 @@
         <v>-403.72727272727263</v>
       </c>
       <c r="J34" s="16">
-        <v>80</v>
+        <v>618</v>
       </c>
       <c r="K34" s="13">
-        <v>332</v>
+        <v>2564.7000000000003</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4632,11 +4630,9 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>80</v>
-      </c>
-      <c r="O34" s="16">
-        <v>0</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="O34" s="16"/>
       <c r="P34" s="17">
         <v>0</v>
       </c>
@@ -4665,10 +4661,10 @@
         <v>-44.090909090909093</v>
       </c>
       <c r="Y34" s="18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z34" s="17">
-        <v>0</v>
+        <v>132.80000000000001</v>
       </c>
       <c r="AA34" s="14">
         <v>0</v>
@@ -4677,34 +4673,34 @@
         <v>0</v>
       </c>
       <c r="AC34" s="15">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>369</v>
+        <v>939</v>
       </c>
       <c r="AE34" s="20">
-        <v>1531.3500000000001</v>
+        <v>3896.8500000000004</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
       </c>
       <c r="AG34" s="22">
-        <v>4.9231257941550197</v>
+        <v>12.527954256670903</v>
       </c>
       <c r="AH34" s="23">
-        <v>0.49231257941550188</v>
+        <v>1.2527954256670901</v>
       </c>
       <c r="AI34" s="26">
-        <v>-380.52380952380952</v>
+        <v>189.47619047619048</v>
       </c>
       <c r="AJ34" s="27">
         <v>374.76190476190476</v>
       </c>
       <c r="AK34" s="25">
-        <v>755.28571428571422</v>
+        <v>185.28571428571428</v>
       </c>
       <c r="AL34" s="28">
-        <v>23.0625</v>
+        <v>58.6875</v>
       </c>
     </row>
     <row r="35" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4718,106 +4714,106 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>1679</v>
+        <v>2451</v>
       </c>
       <c r="F35" s="14">
-        <v>2736.77</v>
+        <v>3995.1299999999997</v>
       </c>
       <c r="G35" s="14">
-        <v>3.4540864035907988</v>
+        <v>5.0422666916027685</v>
       </c>
       <c r="H35" s="30">
         <v>10694</v>
       </c>
       <c r="I35" s="15">
-        <v>-3181.909090909091</v>
+        <v>-2409.909090909091</v>
       </c>
       <c r="J35" s="16">
-        <v>4619</v>
+        <v>1309</v>
       </c>
       <c r="K35" s="13">
-        <v>7528.9699999999993</v>
+        <v>2133.67</v>
       </c>
       <c r="L35" s="14">
-        <v>31.548587395218878</v>
+        <v>8.940701645451723</v>
       </c>
       <c r="M35" s="30">
         <v>3221</v>
       </c>
       <c r="N35" s="15">
-        <v>3154.909090909091</v>
+        <v>-155.09090909090901</v>
       </c>
       <c r="O35" s="16">
-        <v>176</v>
+        <v>693</v>
       </c>
       <c r="P35" s="17">
-        <v>286.88</v>
+        <v>1129.5899999999999</v>
       </c>
       <c r="Q35" s="14">
-        <v>4.0544502617801053</v>
+        <v>15.964397905759164</v>
       </c>
       <c r="R35" s="16">
         <v>955</v>
       </c>
       <c r="S35" s="15">
-        <v>-475.13636363636363</v>
+        <v>41.863636363636374</v>
       </c>
       <c r="T35" s="18">
-        <v>590</v>
+        <v>445</v>
       </c>
       <c r="U35" s="17">
-        <v>961.69999999999993</v>
+        <v>725.34999999999991</v>
       </c>
       <c r="V35" s="14">
-        <v>9.5301027900146842</v>
+        <v>7.1879588839941269</v>
       </c>
       <c r="W35" s="16">
         <v>1362</v>
       </c>
       <c r="X35" s="15">
-        <v>-338.63636363636363</v>
+        <v>-483.63636363636363</v>
       </c>
       <c r="Y35" s="18">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="Z35" s="17">
-        <v>127.13999999999999</v>
+        <v>717.19999999999993</v>
       </c>
       <c r="AA35" s="14">
-        <v>5.4476190476190478</v>
+        <v>36.065573770491802</v>
       </c>
       <c r="AB35" s="16">
-        <v>315</v>
+        <v>268.39999999999998</v>
       </c>
       <c r="AC35" s="15">
-        <v>-136.77272727272728</v>
+        <v>257</v>
       </c>
       <c r="AD35" s="19">
-        <v>7142</v>
+        <v>5338</v>
       </c>
       <c r="AE35" s="20">
-        <v>11641.46</v>
+        <v>8700.9399999999987</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
       </c>
       <c r="AG35" s="22">
-        <v>9.0639995165286766</v>
+        <v>6.7745210612195566</v>
       </c>
       <c r="AH35" s="23">
-        <v>0.90639995165286757</v>
+        <v>0.67745210612195572</v>
       </c>
       <c r="AI35" s="26">
-        <v>-737.52380952380918</v>
+        <v>-2541.5238095238092</v>
       </c>
       <c r="AJ35" s="27">
         <v>3939.7619047619046</v>
       </c>
       <c r="AK35" s="25">
-        <v>4677.2857142857138</v>
+        <v>6481.2857142857138</v>
       </c>
       <c r="AL35" s="28">
-        <v>132.25925925925927</v>
+        <v>98.851851851851848</v>
       </c>
     </row>
     <row r="36" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4831,106 +4827,106 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>0</v>
+        <v>1196</v>
       </c>
       <c r="F36" s="14">
-        <v>0</v>
+        <v>1949.4799999999998</v>
       </c>
       <c r="G36" s="14">
-        <v>0</v>
+        <v>1.5998054356417584</v>
       </c>
       <c r="H36" s="30">
         <v>16447</v>
       </c>
       <c r="I36" s="15">
-        <v>-7475.909090909091</v>
+        <v>-6279.909090909091</v>
       </c>
       <c r="J36" s="16">
-        <v>4631</v>
+        <v>5663</v>
       </c>
       <c r="K36" s="13">
-        <v>7548.53</v>
+        <v>9230.6899999999987</v>
       </c>
       <c r="L36" s="14">
-        <v>20.648966355897851</v>
+        <v>25.250506688285366</v>
       </c>
       <c r="M36" s="30">
         <v>4934</v>
       </c>
       <c r="N36" s="15">
-        <v>2388.272727272727</v>
+        <v>3420.272727272727</v>
       </c>
       <c r="O36" s="16">
-        <v>965</v>
+        <v>789</v>
       </c>
       <c r="P36" s="17">
-        <v>1572.9499999999998</v>
+        <v>1286.07</v>
       </c>
       <c r="Q36" s="14">
-        <v>10.599101347978033</v>
+        <v>8.6660009985022466</v>
       </c>
       <c r="R36" s="16">
         <v>2003</v>
       </c>
       <c r="S36" s="15">
-        <v>-400.68181818181824</v>
+        <v>-576.68181818181824</v>
       </c>
       <c r="T36" s="18">
-        <v>1121</v>
+        <v>871</v>
       </c>
       <c r="U36" s="17">
-        <v>1827.2299999999998</v>
+        <v>1419.73</v>
       </c>
       <c r="V36" s="14">
-        <v>8.3941456773315188</v>
+        <v>6.5221238938053103</v>
       </c>
       <c r="W36" s="16">
         <v>2938</v>
       </c>
       <c r="X36" s="15">
-        <v>-882.18181818181802</v>
+        <v>-1132.181818181818</v>
       </c>
       <c r="Y36" s="18">
-        <v>255</v>
+        <v>571</v>
       </c>
       <c r="Z36" s="17">
-        <v>415.65</v>
+        <v>930.7299999999999</v>
       </c>
       <c r="AA36" s="14">
-        <v>13.169014084507042</v>
+        <v>21.793893129770993</v>
       </c>
       <c r="AB36" s="16">
-        <v>426</v>
+        <v>576.4</v>
       </c>
       <c r="AC36" s="15">
-        <v>-35.454545454545439</v>
+        <v>178</v>
       </c>
       <c r="AD36" s="19">
-        <v>6972</v>
+        <v>9090</v>
       </c>
       <c r="AE36" s="20">
-        <v>11364.359999999999</v>
+        <v>14816.699999999999</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
       </c>
       <c r="AG36" s="22">
-        <v>5.4737550471063257</v>
+        <v>7.1366083445491251</v>
       </c>
       <c r="AH36" s="23">
-        <v>0.54737550471063245</v>
+        <v>0.71366083445491246</v>
       </c>
       <c r="AI36" s="26">
-        <v>-5765.1428571428587</v>
+        <v>-3647.1428571428587</v>
       </c>
       <c r="AJ36" s="27">
         <v>6368.5714285714294</v>
       </c>
       <c r="AK36" s="25">
-        <v>12133.714285714288</v>
+        <v>10015.714285714288</v>
       </c>
       <c r="AL36" s="28">
-        <v>129.11111111111111</v>
+        <v>168.33333333333334</v>
       </c>
     </row>
     <row r="37" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4944,106 +4940,106 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>2042</v>
+        <v>1750</v>
       </c>
       <c r="F37" s="14">
-        <v>3328.4599999999996</v>
+        <v>2852.5</v>
       </c>
       <c r="G37" s="14">
-        <v>7.5388488001342502</v>
+        <v>6.4608155730827317</v>
       </c>
       <c r="H37" s="30">
         <v>5959</v>
       </c>
       <c r="I37" s="15">
-        <v>-666.63636363636397</v>
+        <v>-958.63636363636397</v>
       </c>
       <c r="J37" s="16">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="K37" s="13">
-        <v>958.43999999999994</v>
+        <v>0</v>
       </c>
       <c r="L37" s="14">
-        <v>5.3410404624277454</v>
+        <v>0</v>
       </c>
       <c r="M37" s="30">
         <v>2422</v>
       </c>
       <c r="N37" s="15">
-        <v>-512.90909090909099</v>
+        <v>-1100.909090909091</v>
       </c>
       <c r="O37" s="16">
-        <v>227</v>
+        <v>374</v>
       </c>
       <c r="P37" s="17">
-        <v>370.01</v>
+        <v>609.62</v>
       </c>
       <c r="Q37" s="14">
-        <v>4.9105211406096361</v>
+        <v>8.0904621435594883</v>
       </c>
       <c r="R37" s="16">
         <v>1017</v>
       </c>
       <c r="S37" s="15">
-        <v>-466.40909090909088</v>
+        <v>-319.40909090909088</v>
       </c>
       <c r="T37" s="18">
-        <v>900</v>
+        <v>841</v>
       </c>
       <c r="U37" s="17">
-        <v>1467</v>
+        <v>1370.83</v>
       </c>
       <c r="V37" s="14">
-        <v>13.000656598818122</v>
+        <v>12.148391332895599</v>
       </c>
       <c r="W37" s="16">
         <v>1523</v>
       </c>
       <c r="X37" s="15">
-        <v>-138.40909090909099</v>
+        <v>-197.40909090909099</v>
       </c>
       <c r="Y37" s="18">
-        <v>3</v>
+        <v>273</v>
       </c>
       <c r="Z37" s="17">
-        <v>4.8899999999999997</v>
+        <v>444.98999999999995</v>
       </c>
       <c r="AA37" s="14">
-        <v>0.34375</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="AC37" s="15">
-        <v>-127.90909090909091</v>
+        <v>273</v>
       </c>
       <c r="AD37" s="19">
-        <v>3760</v>
+        <v>3238</v>
       </c>
       <c r="AE37" s="20">
-        <v>6128.7999999999993</v>
+        <v>5277.94</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
       </c>
       <c r="AG37" s="22">
-        <v>7.105192117340053</v>
+        <v>6.1187798074327366</v>
       </c>
       <c r="AH37" s="23">
-        <v>0.71051921173400523</v>
+        <v>0.61187798074327371</v>
       </c>
       <c r="AI37" s="26">
-        <v>-1531.9047619047615</v>
+        <v>-2053.9047619047615</v>
       </c>
       <c r="AJ37" s="27">
         <v>2645.9523809523807</v>
       </c>
       <c r="AK37" s="25">
-        <v>4177.8571428571422</v>
+        <v>4699.8571428571422</v>
       </c>
       <c r="AL37" s="28">
-        <v>69.629629629629633</v>
+        <v>59.962962962962962</v>
       </c>
     </row>
     <row r="38" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5057,106 +5053,106 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>1365</v>
+        <v>1881</v>
       </c>
       <c r="F38" s="14">
-        <v>2224.9499999999998</v>
+        <v>3066.0299999999997</v>
       </c>
       <c r="G38" s="14">
-        <v>7.3083475298126066</v>
+        <v>10.071063519104404</v>
       </c>
       <c r="H38" s="30">
         <v>4109</v>
       </c>
       <c r="I38" s="15">
-        <v>-502.72727272727275</v>
+        <v>13.272727272727252</v>
       </c>
       <c r="J38" s="16">
-        <v>1436</v>
+        <v>46</v>
       </c>
       <c r="K38" s="13">
-        <v>2340.6799999999998</v>
+        <v>74.97999999999999</v>
       </c>
       <c r="L38" s="14">
-        <v>15.144774688398851</v>
+        <v>0.48513902205177378</v>
       </c>
       <c r="M38" s="30">
         <v>2086</v>
       </c>
       <c r="N38" s="15">
-        <v>487.81818181818187</v>
+        <v>-902.18181818181813</v>
       </c>
       <c r="O38" s="16">
-        <v>8</v>
+        <v>544</v>
       </c>
       <c r="P38" s="17">
-        <v>13.04</v>
+        <v>886.71999999999991</v>
       </c>
       <c r="Q38" s="14">
-        <v>0.23435419440745675</v>
+        <v>15.936085219707058</v>
       </c>
       <c r="R38" s="16">
         <v>751</v>
       </c>
       <c r="S38" s="15">
-        <v>-504.0454545454545</v>
+        <v>31.954545454545496</v>
       </c>
       <c r="T38" s="18">
-        <v>668</v>
+        <v>572</v>
       </c>
       <c r="U38" s="17">
-        <v>1088.8399999999999</v>
+        <v>932.3599999999999</v>
       </c>
       <c r="V38" s="14">
-        <v>14.337560975609755</v>
+        <v>12.277073170731706</v>
       </c>
       <c r="W38" s="16">
         <v>1025</v>
       </c>
       <c r="X38" s="15">
-        <v>-30.863636363636374</v>
+        <v>-126.86363636363637</v>
       </c>
       <c r="Y38" s="18">
-        <v>205</v>
+        <v>549</v>
       </c>
       <c r="Z38" s="17">
-        <v>334.15</v>
+        <v>894.86999999999989</v>
       </c>
       <c r="AA38" s="14">
-        <v>9.6367521367521363</v>
+        <v>27.727272727272727</v>
       </c>
       <c r="AB38" s="16">
-        <v>468</v>
+        <v>435.6</v>
       </c>
       <c r="AC38" s="15">
-        <v>-114.09090909090912</v>
+        <v>252</v>
       </c>
       <c r="AD38" s="19">
-        <v>3682</v>
+        <v>3592</v>
       </c>
       <c r="AE38" s="20">
-        <v>6001.66</v>
+        <v>5854.96</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
       </c>
       <c r="AG38" s="22">
-        <v>9.1624600071098481</v>
+        <v>8.9384998222538226</v>
       </c>
       <c r="AH38" s="23">
-        <v>0.91624600071098472</v>
+        <v>0.89384998222538214</v>
       </c>
       <c r="AI38" s="26">
-        <v>-336.57142857142844</v>
+        <v>-426.57142857142844</v>
       </c>
       <c r="AJ38" s="27">
         <v>2009.2857142857142</v>
       </c>
       <c r="AK38" s="25">
-        <v>2345.8571428571427</v>
+        <v>2435.8571428571427</v>
       </c>
       <c r="AL38" s="28">
-        <v>68.18518518518519</v>
+        <v>66.518518518518519</v>
       </c>
     </row>
     <row r="39" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5170,106 +5166,106 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>899</v>
+        <v>715</v>
       </c>
       <c r="F39" s="14">
-        <v>1465.37</v>
+        <v>1165.4499999999998</v>
       </c>
       <c r="G39" s="14">
-        <v>105.76470588235294</v>
+        <v>84.117647058823536</v>
       </c>
       <c r="H39" s="30">
         <v>187</v>
       </c>
       <c r="I39" s="15">
-        <v>814</v>
+        <v>630</v>
       </c>
       <c r="J39" s="16">
-        <v>3558</v>
+        <v>7082</v>
       </c>
       <c r="K39" s="13">
-        <v>5799.54</v>
+        <v>11543.66</v>
       </c>
       <c r="L39" s="14">
-        <v>95.926470588235304</v>
+        <v>190.93627450980395</v>
       </c>
       <c r="M39" s="30">
         <v>815.99999999999989</v>
       </c>
       <c r="N39" s="15">
-        <v>3187.090909090909</v>
+        <v>6711.090909090909</v>
       </c>
       <c r="O39" s="16">
-        <v>439</v>
+        <v>558</v>
       </c>
       <c r="P39" s="17">
-        <v>715.56999999999994</v>
+        <v>909.54</v>
       </c>
       <c r="Q39" s="14">
-        <v>878</v>
+        <v>1116</v>
       </c>
       <c r="R39" s="16">
         <v>11</v>
       </c>
       <c r="S39" s="15">
-        <v>431.5</v>
+        <v>550.5</v>
       </c>
       <c r="T39" s="18">
-        <v>296</v>
+        <v>123</v>
       </c>
       <c r="U39" s="17">
-        <v>482.47999999999996</v>
+        <v>200.48999999999998</v>
       </c>
       <c r="V39" s="14">
-        <v>12.104089219330856</v>
+        <v>5.029739776951673</v>
       </c>
       <c r="W39" s="16">
         <v>538</v>
       </c>
       <c r="X39" s="15">
-        <v>-70.818181818181813</v>
+        <v>-243.81818181818181</v>
       </c>
       <c r="Y39" s="18">
-        <v>137</v>
+        <v>510</v>
       </c>
       <c r="Z39" s="17">
-        <v>223.30999999999997</v>
+        <v>831.3</v>
       </c>
       <c r="AA39" s="14">
-        <v>65.521739130434781</v>
+        <v>170</v>
       </c>
       <c r="AB39" s="16">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="AC39" s="15">
-        <v>105.63636363636364</v>
+        <v>465</v>
       </c>
       <c r="AD39" s="19">
-        <v>5329</v>
+        <v>8988</v>
       </c>
       <c r="AE39" s="20">
-        <v>8686.2699999999986</v>
+        <v>14650.439999999999</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
       </c>
       <c r="AG39" s="22">
-        <v>70.030663329161442</v>
+        <v>118.11514392991238</v>
       </c>
       <c r="AH39" s="23">
-        <v>7.0030663329161449</v>
+        <v>11.811514392991239</v>
       </c>
       <c r="AI39" s="26">
-        <v>4568.0476190476193</v>
+        <v>8227.0476190476184</v>
       </c>
       <c r="AJ39" s="27">
         <v>380.47619047619048</v>
       </c>
       <c r="AK39" s="25">
-        <v>-4187.5714285714284</v>
+        <v>-7846.5714285714275</v>
       </c>
       <c r="AL39" s="28">
-        <v>98.68518518518519</v>
+        <v>166.44444444444446</v>
       </c>
     </row>
     <row r="40" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5283,106 +5279,106 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>850</v>
+        <v>621</v>
       </c>
       <c r="F40" s="14">
-        <v>1385.5</v>
+        <v>1012.2299999999999</v>
       </c>
       <c r="G40" s="14">
-        <v>101.08108108108109</v>
+        <v>73.848648648648663</v>
       </c>
       <c r="H40" s="30">
         <v>185</v>
       </c>
       <c r="I40" s="15">
-        <v>765.90909090909088</v>
+        <v>536.90909090909088</v>
       </c>
       <c r="J40" s="16">
-        <v>3651</v>
+        <v>7076</v>
       </c>
       <c r="K40" s="13">
-        <v>5951.1299999999992</v>
+        <v>11533.88</v>
       </c>
       <c r="L40" s="14">
-        <v>112.49579831932773</v>
+        <v>218.0280112044818</v>
       </c>
       <c r="M40" s="30">
         <v>714</v>
       </c>
       <c r="N40" s="15">
-        <v>3326.4545454545455</v>
+        <v>6751.454545454546</v>
       </c>
       <c r="O40" s="16">
-        <v>440</v>
+        <v>517</v>
       </c>
       <c r="P40" s="17">
-        <v>717.19999999999993</v>
+        <v>842.70999999999992</v>
       </c>
       <c r="Q40" s="14">
-        <v>880</v>
+        <v>1034</v>
       </c>
       <c r="R40" s="16">
         <v>11</v>
       </c>
       <c r="S40" s="15">
-        <v>432.5</v>
+        <v>509.5</v>
       </c>
       <c r="T40" s="18">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="U40" s="17">
-        <v>428.69</v>
+        <v>104.32</v>
       </c>
       <c r="V40" s="14">
-        <v>10.27708703374778</v>
+        <v>2.5008880994671405</v>
       </c>
       <c r="W40" s="16">
         <v>563</v>
       </c>
       <c r="X40" s="15">
-        <v>-120.86363636363637</v>
+        <v>-319.86363636363637</v>
       </c>
       <c r="Y40" s="18">
-        <v>143</v>
+        <v>519</v>
       </c>
       <c r="Z40" s="17">
-        <v>233.08999999999997</v>
+        <v>845.96999999999991</v>
       </c>
       <c r="AA40" s="14">
-        <v>76.731707317073173</v>
+        <v>173</v>
       </c>
       <c r="AB40" s="16">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="AC40" s="15">
-        <v>115.04545454545455</v>
+        <v>474</v>
       </c>
       <c r="AD40" s="19">
-        <v>5347</v>
+        <v>8797</v>
       </c>
       <c r="AE40" s="20">
-        <v>8715.6099999999988</v>
+        <v>14339.109999999999</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
       </c>
       <c r="AG40" s="22">
-        <v>74.165785997357986</v>
+        <v>122.01915455746366</v>
       </c>
       <c r="AH40" s="23">
-        <v>7.4165785997357991</v>
+        <v>12.201915455746366</v>
       </c>
       <c r="AI40" s="26">
-        <v>4626.0476190476193</v>
+        <v>8076.0476190476193</v>
       </c>
       <c r="AJ40" s="27">
         <v>360.47619047619048</v>
       </c>
       <c r="AK40" s="25">
-        <v>-4265.5714285714284</v>
+        <v>-7715.5714285714284</v>
       </c>
       <c r="AL40" s="28">
-        <v>99.018518518518519</v>
+        <v>162.90740740740742</v>
       </c>
     </row>
     <row r="41" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5396,106 +5392,106 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="F41" s="14">
-        <v>1254.6000000000001</v>
+        <v>854.85</v>
       </c>
       <c r="G41" s="14">
-        <v>3.3442622950819674</v>
+        <v>2.278688524590164</v>
       </c>
       <c r="H41" s="30">
         <v>1342</v>
       </c>
       <c r="I41" s="15">
-        <v>-406</v>
+        <v>-471</v>
       </c>
       <c r="J41" s="16">
-        <v>229</v>
+        <v>920</v>
       </c>
       <c r="K41" s="13">
-        <v>1408.3500000000001</v>
+        <v>5658</v>
       </c>
       <c r="L41" s="14">
-        <v>6.3611111111111107</v>
+        <v>25.555555555555557</v>
       </c>
       <c r="M41" s="30">
         <v>792</v>
       </c>
       <c r="N41" s="15">
-        <v>-131</v>
+        <v>560</v>
       </c>
       <c r="O41" s="16">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="P41" s="17">
-        <v>43.050000000000004</v>
+        <v>430.5</v>
       </c>
       <c r="Q41" s="14">
-        <v>1.8554216867469879</v>
+        <v>18.554216867469879</v>
       </c>
       <c r="R41" s="16">
         <v>83</v>
       </c>
       <c r="S41" s="15">
-        <v>-49.590909090909093</v>
+        <v>13.409090909090907</v>
       </c>
       <c r="T41" s="18">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="U41" s="17">
-        <v>897.90000000000009</v>
+        <v>719.55000000000007</v>
       </c>
       <c r="V41" s="14">
-        <v>8.634408602150538</v>
+        <v>6.919354838709677</v>
       </c>
       <c r="W41" s="16">
         <v>372</v>
       </c>
       <c r="X41" s="15">
-        <v>-107.63636363636365</v>
+        <v>-136.63636363636365</v>
       </c>
       <c r="Y41" s="18">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="Z41" s="17">
-        <v>6.15</v>
+        <v>596.55000000000007</v>
       </c>
       <c r="AA41" s="14">
-        <v>0.22916666666666669</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="16">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="AC41" s="15">
-        <v>-64.454545454545453</v>
+        <v>97</v>
       </c>
       <c r="AD41" s="19">
-        <v>587</v>
+        <v>1343</v>
       </c>
       <c r="AE41" s="20">
-        <v>3610.05</v>
+        <v>8259.4500000000007</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
       </c>
       <c r="AG41" s="22">
-        <v>4.5910614525139666</v>
+        <v>10.50391061452514</v>
       </c>
       <c r="AH41" s="23">
-        <v>0.45910614525139659</v>
+        <v>1.0503910614525138</v>
       </c>
       <c r="AI41" s="26">
-        <v>-691.57142857142867</v>
+        <v>64.428571428571331</v>
       </c>
       <c r="AJ41" s="27">
         <v>639.28571428571433</v>
       </c>
       <c r="AK41" s="25">
-        <v>1330.8571428571431</v>
+        <v>574.857142857143</v>
       </c>
       <c r="AL41" s="28">
-        <v>10.87037037037037</v>
+        <v>24.87037037037037</v>
       </c>
     </row>
     <row r="42" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5509,106 +5505,106 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="F42" s="14">
-        <v>0</v>
+        <v>861</v>
       </c>
       <c r="G42" s="14">
-        <v>0</v>
+        <v>2.1813031161473084</v>
       </c>
       <c r="H42" s="30">
         <v>1412</v>
       </c>
       <c r="I42" s="15">
-        <v>-641.81818181818187</v>
+        <v>-501.81818181818187</v>
       </c>
       <c r="J42" s="16">
-        <v>421</v>
+        <v>147</v>
       </c>
       <c r="K42" s="13">
-        <v>2589.15</v>
+        <v>904.05000000000007</v>
       </c>
       <c r="L42" s="14">
-        <v>10.002159827213822</v>
+        <v>3.4924406047516197</v>
       </c>
       <c r="M42" s="30">
         <v>926</v>
       </c>
       <c r="N42" s="15">
-        <v>9.0909090909065071E-2</v>
+        <v>-273.90909090909093</v>
       </c>
       <c r="O42" s="16">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="P42" s="17">
-        <v>73.800000000000011</v>
+        <v>350.55</v>
       </c>
       <c r="Q42" s="14">
-        <v>3.2592592592592595</v>
+        <v>15.481481481481483</v>
       </c>
       <c r="R42" s="16">
         <v>81</v>
       </c>
       <c r="S42" s="15">
-        <v>-43.227272727272727</v>
+        <v>1.7727272727272734</v>
       </c>
       <c r="T42" s="18">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="U42" s="17">
-        <v>1051.6500000000001</v>
+        <v>910.2</v>
       </c>
       <c r="V42" s="14">
-        <v>7.0981132075471702</v>
+        <v>6.1433962264150948</v>
       </c>
       <c r="W42" s="16">
         <v>530</v>
       </c>
       <c r="X42" s="15">
-        <v>-190.36363636363637</v>
+        <v>-213.36363636363637</v>
       </c>
       <c r="Y42" s="18">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="Z42" s="17">
-        <v>436.65000000000003</v>
+        <v>719.55000000000007</v>
       </c>
       <c r="AA42" s="14">
-        <v>25.606557377049178</v>
+        <v>21.666666666666664</v>
       </c>
       <c r="AB42" s="16">
-        <v>61</v>
+        <v>118.80000000000001</v>
       </c>
       <c r="AC42" s="15">
-        <v>29.409090909090907</v>
+        <v>36</v>
       </c>
       <c r="AD42" s="19">
-        <v>675</v>
+        <v>609</v>
       </c>
       <c r="AE42" s="20">
-        <v>4151.25</v>
+        <v>3745.3500000000004</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
       </c>
       <c r="AG42" s="22">
-        <v>4.7093023255813948</v>
+        <v>4.2488372093023257</v>
       </c>
       <c r="AH42" s="23">
-        <v>0.47093023255813948</v>
+        <v>0.42488372093023252</v>
       </c>
       <c r="AI42" s="26">
-        <v>-758.33333333333348</v>
+        <v>-824.33333333333348</v>
       </c>
       <c r="AJ42" s="27">
         <v>716.66666666666674</v>
       </c>
       <c r="AK42" s="25">
-        <v>1475.0000000000002</v>
+        <v>1541.0000000000002</v>
       </c>
       <c r="AL42" s="28">
-        <v>12.5</v>
+        <v>11.277777777777779</v>
       </c>
     </row>
     <row r="43" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5622,106 +5618,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2635</v>
+        <v>2201</v>
       </c>
       <c r="F43" s="14">
-        <v>3056.6</v>
+        <v>2553.16</v>
       </c>
       <c r="G43" s="14">
-        <v>7.8539493293591658</v>
+        <v>6.5603576751117734</v>
       </c>
       <c r="H43" s="30">
         <v>7381</v>
       </c>
       <c r="I43" s="15">
-        <v>-720</v>
+        <v>-1154</v>
       </c>
       <c r="J43" s="16">
-        <v>678</v>
+        <v>4568</v>
       </c>
       <c r="K43" s="13">
-        <v>786.4799999999999</v>
+        <v>5298.8799999999992</v>
       </c>
       <c r="L43" s="14">
-        <v>5.4338797814207656</v>
+        <v>36.610564663023681</v>
       </c>
       <c r="M43" s="30">
         <v>2745</v>
       </c>
       <c r="N43" s="15">
-        <v>-569.72727272727275</v>
+        <v>3320.272727272727</v>
       </c>
       <c r="O43" s="16">
-        <v>332</v>
+        <v>506</v>
       </c>
       <c r="P43" s="17">
-        <v>385.11999999999995</v>
+        <v>586.95999999999992</v>
       </c>
       <c r="Q43" s="14">
-        <v>6.4239226033421284</v>
+        <v>9.7906772207563773</v>
       </c>
       <c r="R43" s="16">
         <v>1137</v>
       </c>
       <c r="S43" s="15">
-        <v>-443.22727272727275</v>
+        <v>-269.22727272727275</v>
       </c>
       <c r="T43" s="18">
-        <v>1259</v>
+        <v>1073</v>
       </c>
       <c r="U43" s="17">
-        <v>1460.4399999999998</v>
+        <v>1244.6799999999998</v>
       </c>
       <c r="V43" s="14">
-        <v>13.348433734939761</v>
+        <v>11.376385542168675</v>
       </c>
       <c r="W43" s="16">
         <v>2075</v>
       </c>
       <c r="X43" s="15">
-        <v>-155.77272727272725</v>
+        <v>-341.77272727272725</v>
       </c>
       <c r="Y43" s="18">
-        <v>52</v>
+        <v>432</v>
       </c>
       <c r="Z43" s="17">
-        <v>60.319999999999993</v>
+        <v>501.11999999999995</v>
       </c>
       <c r="AA43" s="14">
-        <v>3.1955307262569832</v>
+        <v>12.781065088757398</v>
       </c>
       <c r="AB43" s="16">
-        <v>358</v>
+        <v>743.59999999999991</v>
       </c>
       <c r="AC43" s="15">
-        <v>-192.09090909090909</v>
+        <v>-74.999999999999943</v>
       </c>
       <c r="AD43" s="19">
-        <v>4956</v>
+        <v>8780</v>
       </c>
       <c r="AE43" s="20">
-        <v>5748.96</v>
+        <v>10184.799999999999</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
       </c>
       <c r="AG43" s="22">
-        <v>7.5990070093457946</v>
+        <v>13.462324766355142</v>
       </c>
       <c r="AH43" s="23">
-        <v>0.75990070093457951</v>
+        <v>1.346232476635514</v>
       </c>
       <c r="AI43" s="26">
-        <v>-1565.9047619047615</v>
+        <v>2258.0952380952385</v>
       </c>
       <c r="AJ43" s="27">
         <v>3260.9523809523807</v>
       </c>
       <c r="AK43" s="25">
-        <v>4826.8571428571422</v>
+        <v>1002.8571428571422</v>
       </c>
       <c r="AL43" s="28">
-        <v>91.777777777777771</v>
+        <v>162.59259259259258</v>
       </c>
     </row>
     <row r="44" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5735,106 +5731,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2325</v>
+        <v>2001</v>
       </c>
       <c r="F44" s="14">
-        <v>2697</v>
+        <v>2321.16</v>
       </c>
       <c r="G44" s="14">
-        <v>7.9450139794967383</v>
+        <v>6.8378378378378377</v>
       </c>
       <c r="H44" s="30">
         <v>6438</v>
       </c>
       <c r="I44" s="15">
-        <v>-601.36363636363603</v>
+        <v>-925.36363636363603</v>
       </c>
       <c r="J44" s="16">
-        <v>932</v>
+        <v>2714</v>
       </c>
       <c r="K44" s="13">
-        <v>1081.1199999999999</v>
+        <v>3148.24</v>
       </c>
       <c r="L44" s="14">
-        <v>5.4416135881104042</v>
+        <v>15.846072186836519</v>
       </c>
       <c r="M44" s="30">
         <v>3767.9999999999995</v>
       </c>
       <c r="N44" s="15">
-        <v>-780.72727272727252</v>
+        <v>1001.2727272727275</v>
       </c>
       <c r="O44" s="16">
-        <v>535</v>
+        <v>501</v>
       </c>
       <c r="P44" s="17">
-        <v>620.59999999999991</v>
+        <v>581.16</v>
       </c>
       <c r="Q44" s="14">
-        <v>15.651595744680852</v>
+        <v>14.656914893617023</v>
       </c>
       <c r="R44" s="16">
         <v>752</v>
       </c>
       <c r="S44" s="15">
-        <v>22.272727272727252</v>
+        <v>-11.727272727272748</v>
       </c>
       <c r="T44" s="18">
-        <v>1194</v>
+        <v>1054</v>
       </c>
       <c r="U44" s="17">
-        <v>1385.04</v>
+        <v>1222.6399999999999</v>
       </c>
       <c r="V44" s="14">
-        <v>14.122580645161291</v>
+        <v>12.466666666666667</v>
       </c>
       <c r="W44" s="16">
         <v>1860</v>
       </c>
       <c r="X44" s="15">
-        <v>-74.181818181818244</v>
+        <v>-214.18181818181824</v>
       </c>
       <c r="Y44" s="18">
-        <v>162</v>
+        <v>558</v>
       </c>
       <c r="Z44" s="17">
-        <v>187.92</v>
+        <v>647.28</v>
       </c>
       <c r="AA44" s="14">
-        <v>9.091836734693878</v>
+        <v>22.68292682926829</v>
       </c>
       <c r="AB44" s="16">
-        <v>392</v>
+        <v>541.20000000000005</v>
       </c>
       <c r="AC44" s="15">
-        <v>-105.27272727272725</v>
+        <v>189</v>
       </c>
       <c r="AD44" s="19">
-        <v>5148</v>
+        <v>6828</v>
       </c>
       <c r="AE44" s="20">
-        <v>5971.6799999999994</v>
+        <v>7920.48</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
       </c>
       <c r="AG44" s="22">
-        <v>8.1838001514004546</v>
+        <v>10.854504163512491</v>
       </c>
       <c r="AH44" s="23">
-        <v>0.81838001514004532</v>
+        <v>1.0854504163512491</v>
       </c>
       <c r="AI44" s="26">
-        <v>-1142.4761904761908</v>
+        <v>537.52380952380918</v>
       </c>
       <c r="AJ44" s="27">
         <v>3145.2380952380954</v>
       </c>
       <c r="AK44" s="25">
-        <v>4287.7142857142862</v>
+        <v>2607.7142857142862</v>
       </c>
       <c r="AL44" s="28">
-        <v>95.333333333333329</v>
+        <v>126.44444444444444</v>
       </c>
     </row>
     <row r="45" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5848,106 +5844,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>3247</v>
+        <v>2214</v>
       </c>
       <c r="F45" s="14">
-        <v>3766.5199999999995</v>
+        <v>2568.2399999999998</v>
       </c>
       <c r="G45" s="14">
-        <v>8.427796130250119</v>
+        <v>5.7465785747994342</v>
       </c>
       <c r="H45" s="30">
         <v>8476</v>
       </c>
       <c r="I45" s="15">
-        <v>-605.72727272727252</v>
+        <v>-1638.7272727272725</v>
       </c>
       <c r="J45" s="16">
-        <v>2425</v>
+        <v>3615</v>
       </c>
       <c r="K45" s="13">
-        <v>2813</v>
+        <v>4193.3999999999996</v>
       </c>
       <c r="L45" s="14">
-        <v>9.8650147928994087</v>
+        <v>14.705991124260356</v>
       </c>
       <c r="M45" s="30">
         <v>5408</v>
       </c>
       <c r="N45" s="15">
-        <v>-33.181818181818016</v>
+        <v>1156.818181818182</v>
       </c>
       <c r="O45" s="16">
-        <v>266</v>
+        <v>793</v>
       </c>
       <c r="P45" s="17">
-        <v>308.56</v>
+        <v>919.87999999999988</v>
       </c>
       <c r="Q45" s="14">
-        <v>5.2296693476318135</v>
+        <v>15.590705987488828</v>
       </c>
       <c r="R45" s="16">
         <v>1119</v>
       </c>
       <c r="S45" s="15">
-        <v>-496.9545454545455</v>
+        <v>30.045454545454504</v>
       </c>
       <c r="T45" s="18">
-        <v>1460</v>
+        <v>1260</v>
       </c>
       <c r="U45" s="17">
-        <v>1693.6</v>
+        <v>1461.6</v>
       </c>
       <c r="V45" s="14">
-        <v>12.695652173913043</v>
+        <v>10.956521739130435</v>
       </c>
       <c r="W45" s="16">
         <v>2530</v>
       </c>
       <c r="X45" s="15">
-        <v>-265</v>
+        <v>-465</v>
       </c>
       <c r="Y45" s="18">
-        <v>79</v>
+        <v>457</v>
       </c>
       <c r="Z45" s="17">
-        <v>91.64</v>
+        <v>530.12</v>
       </c>
       <c r="AA45" s="14">
-        <v>4.7878787878787881</v>
+        <v>15.758620689655173</v>
       </c>
       <c r="AB45" s="16">
-        <v>363</v>
+        <v>638</v>
       </c>
       <c r="AC45" s="15">
-        <v>-168.5</v>
+        <v>22</v>
       </c>
       <c r="AD45" s="19">
-        <v>7477</v>
+        <v>8339</v>
       </c>
       <c r="AE45" s="20">
-        <v>8673.32</v>
+        <v>9673.24</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
       </c>
       <c r="AG45" s="22">
-        <v>8.7738600804649085</v>
+        <v>9.785371032632991</v>
       </c>
       <c r="AH45" s="23">
-        <v>0.87738600804649092</v>
+        <v>0.97853710326329912</v>
       </c>
       <c r="AI45" s="26">
-        <v>-1044.9047619047615</v>
+        <v>-182.90476190476147</v>
       </c>
       <c r="AJ45" s="27">
         <v>4260.9523809523807</v>
       </c>
       <c r="AK45" s="25">
-        <v>5305.8571428571422</v>
+        <v>4443.8571428571422</v>
       </c>
       <c r="AL45" s="28">
-        <v>138.46296296296296</v>
+        <v>154.42592592592592</v>
       </c>
     </row>
     <row r="46" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5961,106 +5957,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>2083</v>
+        <v>3490</v>
       </c>
       <c r="F46" s="14">
-        <v>2416.2799999999997</v>
+        <v>4048.3999999999996</v>
       </c>
       <c r="G46" s="14">
-        <v>8.0679577464788732</v>
+        <v>13.517605633802816</v>
       </c>
       <c r="H46" s="30">
         <v>5680</v>
       </c>
       <c r="I46" s="15">
-        <v>-498.81818181818198</v>
+        <v>908.18181818181802</v>
       </c>
       <c r="J46" s="16">
-        <v>3556</v>
+        <v>1038</v>
       </c>
       <c r="K46" s="13">
-        <v>4124.96</v>
+        <v>1204.08</v>
       </c>
       <c r="L46" s="14">
-        <v>19.705793450881611</v>
+        <v>5.7521410579345087</v>
       </c>
       <c r="M46" s="30">
         <v>3970</v>
       </c>
       <c r="N46" s="15">
-        <v>1751.4545454545453</v>
+        <v>-766.54545454545473</v>
       </c>
       <c r="O46" s="16">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="P46" s="17">
-        <v>0</v>
+        <v>754</v>
       </c>
       <c r="Q46" s="14">
-        <v>0</v>
+        <v>17.396593673965935</v>
       </c>
       <c r="R46" s="16">
         <v>822.00000000000011</v>
       </c>
       <c r="S46" s="15">
-        <v>-560.4545454545455</v>
+        <v>89.545454545454504</v>
       </c>
       <c r="T46" s="18">
-        <v>787</v>
+        <v>674</v>
       </c>
       <c r="U46" s="17">
-        <v>912.92</v>
+        <v>781.83999999999992</v>
       </c>
       <c r="V46" s="14">
-        <v>13.918006430868166</v>
+        <v>11.919614147909968</v>
       </c>
       <c r="W46" s="16">
         <v>1244</v>
       </c>
       <c r="X46" s="15">
-        <v>-61.181818181818244</v>
+        <v>-174.18181818181824</v>
       </c>
       <c r="Y46" s="18">
-        <v>13</v>
+        <v>383</v>
       </c>
       <c r="Z46" s="17">
-        <v>15.079999999999998</v>
+        <v>444.28</v>
       </c>
       <c r="AA46" s="14">
-        <v>0.64559819413092545</v>
+        <v>23.9375</v>
       </c>
       <c r="AB46" s="16">
-        <v>443</v>
+        <v>352</v>
       </c>
       <c r="AC46" s="15">
-        <v>-289.04545454545456</v>
+        <v>143</v>
       </c>
       <c r="AD46" s="19">
-        <v>6439</v>
+        <v>6235</v>
       </c>
       <c r="AE46" s="20">
-        <v>7469.24</v>
+        <v>7232.5999999999995</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
       </c>
       <c r="AG46" s="22">
-        <v>11.120898100172711</v>
+        <v>10.768566493955095</v>
       </c>
       <c r="AH46" s="23">
-        <v>1.1120898100172711</v>
+        <v>1.0768566493955094</v>
       </c>
       <c r="AI46" s="26">
-        <v>649</v>
+        <v>445</v>
       </c>
       <c r="AJ46" s="27">
         <v>2895</v>
       </c>
       <c r="AK46" s="25">
-        <v>2246</v>
+        <v>2450</v>
       </c>
       <c r="AL46" s="28">
-        <v>119.24074074074075</v>
+        <v>115.46296296296296</v>
       </c>
     </row>
     <row r="47" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6073,9 +6069,7 @@
       <c r="D47" s="12">
         <v>18</v>
       </c>
-      <c r="E47" s="13">
-        <v>0</v>
-      </c>
+      <c r="E47" s="13"/>
       <c r="F47" s="14">
         <v>0</v>
       </c>
@@ -6089,23 +6083,21 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K47" s="13">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="L47" s="14">
-        <v>2.0625</v>
+        <v>0.6875</v>
       </c>
       <c r="M47" s="30">
         <v>32</v>
       </c>
       <c r="N47" s="15">
-        <v>-11.545454545454547</v>
-      </c>
-      <c r="O47" s="16">
-        <v>0</v>
-      </c>
+        <v>-13.545454545454547</v>
+      </c>
+      <c r="O47" s="16"/>
       <c r="P47" s="17">
         <v>0</v>
       </c>
@@ -6119,19 +6111,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U47" s="17">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="V47" s="14">
-        <v>14.3</v>
+        <v>13.200000000000001</v>
       </c>
       <c r="W47" s="16">
         <v>20</v>
       </c>
       <c r="X47" s="15">
-        <v>-0.63636363636363669</v>
+        <v>-1.6363636363636367</v>
       </c>
       <c r="Y47" s="18">
         <v>4</v>
@@ -6149,31 +6141,31 @@
         <v>4</v>
       </c>
       <c r="AD47" s="19">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE47" s="20">
-        <v>360</v>
+        <v>306</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
       </c>
       <c r="AG47" s="22">
-        <v>8.0769230769230766</v>
+        <v>6.865384615384615</v>
       </c>
       <c r="AH47" s="23">
-        <v>0.80769230769230771</v>
+        <v>0.68653846153846154</v>
       </c>
       <c r="AI47" s="26">
-        <v>-4.7619047619047628</v>
+        <v>-7.7619047619047628</v>
       </c>
       <c r="AJ47" s="27">
         <v>12.380952380952381</v>
       </c>
       <c r="AK47" s="25">
-        <v>17.142857142857146</v>
+        <v>20.142857142857146</v>
       </c>
       <c r="AL47" s="28">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="48" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6186,9 +6178,7 @@
       <c r="D48" s="12">
         <v>18</v>
       </c>
-      <c r="E48" s="13">
-        <v>0</v>
-      </c>
+      <c r="E48" s="13"/>
       <c r="F48" s="14">
         <v>0</v>
       </c>
@@ -6202,23 +6192,21 @@
         <v>0</v>
       </c>
       <c r="J48" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48" s="13">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="L48" s="14">
-        <v>4.8888888888888884</v>
+        <v>2.4444444444444442</v>
       </c>
       <c r="M48" s="30">
         <v>9</v>
       </c>
       <c r="N48" s="15">
-        <v>-2.0909090909090908</v>
-      </c>
-      <c r="O48" s="16">
-        <v>0</v>
-      </c>
+        <v>-3.0909090909090908</v>
+      </c>
+      <c r="O48" s="16"/>
       <c r="P48" s="17">
         <v>0</v>
       </c>
@@ -6262,10 +6250,10 @@
         <v>0</v>
       </c>
       <c r="AD48" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE48" s="20">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AF48" s="31">
         <v>4.2857142857142856</v>
@@ -6277,16 +6265,16 @@
         <v>0</v>
       </c>
       <c r="AI48" s="26">
-        <v>-2.2857142857142856</v>
+        <v>-3.2857142857142856</v>
       </c>
       <c r="AJ48" s="27">
         <v>2.1428571428571428</v>
       </c>
       <c r="AK48" s="25">
-        <v>4.4285714285714288</v>
+        <v>5.4285714285714288</v>
       </c>
       <c r="AL48" s="28">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6300,106 +6288,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>0</v>
+        <v>1062</v>
       </c>
       <c r="F49" s="14">
-        <v>0</v>
+        <v>1231.9199999999998</v>
       </c>
       <c r="G49" s="14">
-        <v>0</v>
+        <v>18.88763136620857</v>
       </c>
       <c r="H49" s="30">
         <v>1237</v>
       </c>
       <c r="I49" s="15">
-        <v>-562.27272727272725</v>
+        <v>499.72727272727275</v>
       </c>
       <c r="J49" s="16">
-        <v>9</v>
+        <v>726</v>
       </c>
       <c r="K49" s="13">
-        <v>10.44</v>
+        <v>842.16</v>
       </c>
       <c r="L49" s="14">
-        <v>0.16058394160583941</v>
+        <v>12.953771289537713</v>
       </c>
       <c r="M49" s="30">
         <v>1233</v>
       </c>
       <c r="N49" s="15">
-        <v>-551.4545454545455</v>
+        <v>165.5454545454545</v>
       </c>
       <c r="O49" s="16">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="P49" s="17">
-        <v>52.199999999999996</v>
+        <v>47.559999999999995</v>
       </c>
       <c r="Q49" s="14">
-        <v>8.8392857142857153</v>
+        <v>8.0535714285714288</v>
       </c>
       <c r="R49" s="16">
         <v>112</v>
       </c>
       <c r="S49" s="15">
-        <v>-31.36363636363636</v>
+        <v>-35.36363636363636</v>
       </c>
       <c r="T49" s="18">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="U49" s="17">
-        <v>295.79999999999995</v>
+        <v>257.52</v>
       </c>
       <c r="V49" s="14">
-        <v>24.181034482758623</v>
+        <v>21.051724137931036</v>
       </c>
       <c r="W49" s="16">
         <v>232</v>
       </c>
       <c r="X49" s="15">
-        <v>96.818181818181813</v>
+        <v>63.818181818181813</v>
       </c>
       <c r="Y49" s="18">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Z49" s="17">
-        <v>114.83999999999999</v>
+        <v>111.35999999999999</v>
       </c>
       <c r="AA49" s="14">
-        <v>33</v>
+        <v>18.46153846153846</v>
       </c>
       <c r="AB49" s="16">
-        <v>66</v>
+        <v>114.4</v>
       </c>
       <c r="AC49" s="15">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="AD49" s="19">
-        <v>408</v>
+        <v>2147</v>
       </c>
       <c r="AE49" s="20">
-        <v>473.28</v>
+        <v>2490.52</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
       </c>
       <c r="AG49" s="22">
-        <v>2.9750000000000001</v>
+        <v>15.655208333333334</v>
       </c>
       <c r="AH49" s="23">
-        <v>0.29750000000000004</v>
+        <v>1.5655208333333335</v>
       </c>
       <c r="AI49" s="26">
-        <v>-963.42857142857133</v>
+        <v>775.57142857142867</v>
       </c>
       <c r="AJ49" s="27">
         <v>685.71428571428567</v>
       </c>
       <c r="AK49" s="25">
-        <v>1649.1428571428569</v>
+        <v>-89.857142857143003</v>
       </c>
       <c r="AL49" s="28">
-        <v>10.199999999999999</v>
+        <v>53.674999999999997</v>
       </c>
     </row>
     <row r="50" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6413,106 +6401,106 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>847</v>
+        <v>2326</v>
       </c>
       <c r="F50" s="14">
-        <v>982.52</v>
+        <v>2698.16</v>
       </c>
       <c r="G50" s="14">
-        <v>3.3227532097004282</v>
+        <v>9.1248216833095572</v>
       </c>
       <c r="H50" s="30">
         <v>5608</v>
       </c>
       <c r="I50" s="15">
-        <v>-1702.090909090909</v>
+        <v>-223.09090909090901</v>
       </c>
       <c r="J50" s="16">
-        <v>2033</v>
+        <v>919</v>
       </c>
       <c r="K50" s="13">
-        <v>2358.2799999999997</v>
+        <v>1066.04</v>
       </c>
       <c r="L50" s="14">
-        <v>12.507270693512305</v>
+        <v>5.6538031319910518</v>
       </c>
       <c r="M50" s="30">
         <v>3576</v>
       </c>
       <c r="N50" s="15">
-        <v>407.54545454545473</v>
+        <v>-706.45454545454527</v>
       </c>
       <c r="O50" s="16">
-        <v>25</v>
+        <v>387</v>
       </c>
       <c r="P50" s="17">
-        <v>28.999999999999996</v>
+        <v>448.91999999999996</v>
       </c>
       <c r="Q50" s="14">
-        <v>1.1458333333333335</v>
+        <v>17.737500000000001</v>
       </c>
       <c r="R50" s="16">
         <v>480</v>
       </c>
       <c r="S50" s="15">
-        <v>-302.27272727272725</v>
+        <v>59.727272727272748</v>
       </c>
       <c r="T50" s="18">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="U50" s="17">
-        <v>64.959999999999994</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="V50" s="14">
-        <v>0.7003979533826038</v>
+        <v>2.5014212620807278E-2</v>
       </c>
       <c r="W50" s="16">
         <v>1759</v>
       </c>
       <c r="X50" s="15">
-        <v>-1143.3181818181818</v>
+        <v>-1197.3181818181818</v>
       </c>
       <c r="Y50" s="18">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="Z50" s="17">
-        <v>32.479999999999997</v>
+        <v>213.44</v>
       </c>
       <c r="AA50" s="14">
-        <v>2.8</v>
+        <v>14.838709677419354</v>
       </c>
       <c r="AB50" s="16">
-        <v>220</v>
+        <v>272.8</v>
       </c>
       <c r="AC50" s="15">
-        <v>-122</v>
+        <v>-2</v>
       </c>
       <c r="AD50" s="19">
-        <v>2989</v>
+        <v>3818</v>
       </c>
       <c r="AE50" s="20">
-        <v>3467.24</v>
+        <v>4428.88</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
       </c>
       <c r="AG50" s="22">
-        <v>5.391136305076011</v>
+        <v>6.8863694923988659</v>
       </c>
       <c r="AH50" s="23">
-        <v>0.53911363050760108</v>
+        <v>0.68863694923988661</v>
       </c>
       <c r="AI50" s="26">
-        <v>-2555.2857142857147</v>
+        <v>-1726.2857142857147</v>
       </c>
       <c r="AJ50" s="27">
         <v>2772.1428571428573</v>
       </c>
       <c r="AK50" s="25">
-        <v>5327.4285714285725</v>
+        <v>4498.4285714285725</v>
       </c>
       <c r="AL50" s="28">
-        <v>74.724999999999994</v>
+        <v>95.45</v>
       </c>
       <c r="AM50" s="62" t="s">
         <v>15</v>
@@ -6529,40 +6517,40 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>0</v>
+        <v>1223</v>
       </c>
       <c r="F51" s="14">
-        <v>0</v>
+        <v>1418.6799999999998</v>
       </c>
       <c r="G51" s="14">
-        <v>0</v>
+        <v>21.169158143194334</v>
       </c>
       <c r="H51" s="30">
         <v>1271</v>
       </c>
       <c r="I51" s="15">
-        <v>-577.72727272727275</v>
+        <v>645.27272727272725</v>
       </c>
       <c r="J51" s="16">
-        <v>3311</v>
+        <v>1524</v>
       </c>
       <c r="K51" s="13">
-        <v>3840.7599999999998</v>
+        <v>1767.84</v>
       </c>
       <c r="L51" s="14">
-        <v>74.328571428571422</v>
+        <v>34.212244897959181</v>
       </c>
       <c r="M51" s="30">
         <v>980</v>
       </c>
       <c r="N51" s="15">
-        <v>2865.5454545454545</v>
+        <v>1078.5454545454545</v>
       </c>
       <c r="O51" s="16">
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="P51" s="17">
-        <v>0</v>
+        <v>438.47999999999996</v>
       </c>
       <c r="Q51" s="14">
         <v>0</v>
@@ -6571,28 +6559,28 @@
         <v>0</v>
       </c>
       <c r="S51" s="15">
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="T51" s="18">
-        <v>368</v>
+        <v>274</v>
       </c>
       <c r="U51" s="17">
-        <v>426.88</v>
+        <v>317.83999999999997</v>
       </c>
       <c r="V51" s="14">
-        <v>15.048327137546469</v>
+        <v>11.204460966542751</v>
       </c>
       <c r="W51" s="16">
         <v>538</v>
       </c>
       <c r="X51" s="15">
-        <v>1.181818181818187</v>
+        <v>-92.818181818181813</v>
       </c>
       <c r="Y51" s="18">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="Z51" s="17">
-        <v>0</v>
+        <v>187.92</v>
       </c>
       <c r="AA51" s="14">
         <v>0</v>
@@ -6601,38 +6589,38 @@
         <v>0</v>
       </c>
       <c r="AC51" s="15">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="AD51" s="19">
-        <v>3679</v>
+        <v>3561</v>
       </c>
       <c r="AE51" s="20">
-        <v>4267.6399999999994</v>
+        <v>4130.7599999999993</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
       </c>
       <c r="AG51" s="22">
-        <v>27.701326640372898</v>
+        <v>26.812836141986377</v>
       </c>
       <c r="AH51" s="23">
-        <v>2.7701326640372894</v>
+        <v>2.6812836141986374</v>
       </c>
       <c r="AI51" s="26">
-        <v>2350.9047619047619</v>
+        <v>2232.9047619047619</v>
       </c>
       <c r="AJ51" s="27">
         <v>664.04761904761904</v>
       </c>
       <c r="AK51" s="25">
-        <v>-1686.8571428571429</v>
+        <v>-1568.8571428571429</v>
       </c>
       <c r="AL51" s="28">
-        <v>91.974999999999994</v>
+        <v>89.025000000000006</v>
       </c>
       <c r="AM51" s="63">
         <f>SUM(AL13:AL51)</f>
-        <v>5010.2277777777772</v>
+        <v>5580.5526455026438</v>
       </c>
     </row>
     <row r="52" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6646,19 +6634,19 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>3396</v>
+        <v>3820</v>
       </c>
       <c r="F52" s="14">
-        <v>2750.76</v>
+        <v>3094.2000000000003</v>
       </c>
       <c r="G52" s="14">
-        <v>28.235827664399096</v>
+        <v>31.761148904006049</v>
       </c>
       <c r="H52" s="30">
         <v>2646</v>
       </c>
       <c r="I52" s="15">
-        <v>2193.272727272727</v>
+        <v>2617.272727272727</v>
       </c>
       <c r="J52" s="16">
         <v>0</v>
@@ -6691,19 +6679,19 @@
         <v>-339.54545454545456</v>
       </c>
       <c r="T52" s="18">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="U52" s="17">
-        <v>167.67000000000002</v>
+        <v>180.63000000000002</v>
       </c>
       <c r="V52" s="14">
-        <v>5.0543840177580464</v>
+        <v>5.4450610432852384</v>
       </c>
       <c r="W52" s="16">
         <v>901</v>
       </c>
       <c r="X52" s="15">
-        <v>-407.31818181818176</v>
+        <v>-391.31818181818176</v>
       </c>
       <c r="Y52" s="18">
         <v>0</v>
@@ -6715,37 +6703,37 @@
         <v>0</v>
       </c>
       <c r="AB52" s="16">
-        <v>238</v>
+        <v>101.19999999999999</v>
       </c>
       <c r="AC52" s="15">
-        <v>-162.27272727272728</v>
+        <v>-69</v>
       </c>
       <c r="AD52" s="19">
-        <v>3603</v>
+        <v>4043</v>
       </c>
       <c r="AE52" s="20">
-        <v>2918.4300000000003</v>
+        <v>3274.8300000000004</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
       </c>
       <c r="AG52" s="22">
-        <v>12.16642547033285</v>
+        <v>13.652194886637721</v>
       </c>
       <c r="AH52" s="23">
-        <v>1.2166425470332851</v>
+        <v>1.3652194886637723</v>
       </c>
       <c r="AI52" s="26">
-        <v>641.57142857142844</v>
+        <v>1081.5714285714284</v>
       </c>
       <c r="AJ52" s="27">
         <v>1480.7142857142858</v>
       </c>
       <c r="AK52" s="25">
-        <v>839.14285714285734</v>
+        <v>399.14285714285734</v>
       </c>
       <c r="AL52" s="28">
-        <v>300.25</v>
+        <v>336.91666666666669</v>
       </c>
     </row>
     <row r="53" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6759,106 +6747,106 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>3519</v>
+        <v>2924</v>
       </c>
       <c r="F53" s="14">
-        <v>2850.3900000000003</v>
+        <v>2368.44</v>
       </c>
       <c r="G53" s="14">
-        <v>15.076533592989289</v>
+        <v>12.527361246348589</v>
       </c>
       <c r="H53" s="30">
         <v>5135</v>
       </c>
       <c r="I53" s="15">
-        <v>1184.909090909091</v>
+        <v>589.90909090909099</v>
       </c>
       <c r="J53" s="16">
-        <v>5975</v>
+        <v>4925</v>
       </c>
       <c r="K53" s="13">
-        <v>4839.75</v>
+        <v>3989.2500000000005</v>
       </c>
       <c r="L53" s="14">
-        <v>41.4015748031496</v>
+        <v>34.125984251968497</v>
       </c>
       <c r="M53" s="30">
         <v>3175.0000000000005</v>
       </c>
       <c r="N53" s="15">
-        <v>4531.818181818182</v>
+        <v>3481.8181818181815</v>
       </c>
       <c r="O53" s="16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="P53" s="17">
-        <v>0</v>
+        <v>486.00000000000006</v>
       </c>
       <c r="Q53" s="14">
-        <v>0</v>
+        <v>14.94903737259343</v>
       </c>
       <c r="R53" s="16">
         <v>883.00000000000011</v>
       </c>
       <c r="S53" s="15">
-        <v>-602.04545454545462</v>
+        <v>-2.0454545454546178</v>
       </c>
       <c r="T53" s="18">
-        <v>114</v>
+        <v>325</v>
       </c>
       <c r="U53" s="17">
-        <v>92.34</v>
+        <v>263.25</v>
       </c>
       <c r="V53" s="14">
-        <v>1.5190793458509995</v>
+        <v>4.3307086614173231</v>
       </c>
       <c r="W53" s="16">
         <v>1651</v>
       </c>
       <c r="X53" s="15">
-        <v>-1011.6818181818182</v>
+        <v>-800.68181818181824</v>
       </c>
       <c r="Y53" s="18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Z53" s="17">
-        <v>0</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="AA53" s="14">
-        <v>0</v>
+        <v>20.869565217391305</v>
       </c>
       <c r="AB53" s="16">
-        <v>259</v>
+        <v>101.19999999999999</v>
       </c>
       <c r="AC53" s="15">
-        <v>-176.59090909090909</v>
+        <v>27</v>
       </c>
       <c r="AD53" s="19">
-        <v>9608</v>
+        <v>8870</v>
       </c>
       <c r="AE53" s="20">
-        <v>7782.4800000000005</v>
+        <v>7184.7000000000007</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
       </c>
       <c r="AG53" s="22">
-        <v>18.172385841664418</v>
+        <v>16.776546879221833</v>
       </c>
       <c r="AH53" s="23">
-        <v>1.8172385841664416</v>
+        <v>1.6776546879221832</v>
       </c>
       <c r="AI53" s="26">
-        <v>4320.8571428571431</v>
+        <v>3582.8571428571431</v>
       </c>
       <c r="AJ53" s="27">
         <v>2643.5714285714284</v>
       </c>
       <c r="AK53" s="25">
-        <v>-1677.2857142857147</v>
+        <v>-939.28571428571468</v>
       </c>
       <c r="AL53" s="28">
-        <v>800.66666666666663</v>
+        <v>739.16666666666663</v>
       </c>
     </row>
     <row r="54" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6872,34 +6860,34 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>3331</v>
+        <v>3183</v>
       </c>
       <c r="F54" s="14">
-        <v>2698.11</v>
+        <v>2578.23</v>
       </c>
       <c r="G54" s="14">
-        <v>21.290528762347471</v>
+        <v>20.344567112144102</v>
       </c>
       <c r="H54" s="30">
         <v>3442</v>
       </c>
       <c r="I54" s="15">
-        <v>1766.4545454545453</v>
+        <v>1618.4545454545453</v>
       </c>
       <c r="J54" s="16">
-        <v>5588</v>
+        <v>7566</v>
       </c>
       <c r="K54" s="13">
-        <v>4526.2800000000007</v>
+        <v>6128.46</v>
       </c>
       <c r="L54" s="14">
-        <v>70.410080183276065</v>
+        <v>95.333333333333343</v>
       </c>
       <c r="M54" s="30">
         <v>1746</v>
       </c>
       <c r="N54" s="15">
-        <v>4794.363636363636</v>
+        <v>6772.363636363636</v>
       </c>
       <c r="O54" s="16">
         <v>370</v>
@@ -6917,61 +6905,61 @@
         <v>136.81818181818181</v>
       </c>
       <c r="T54" s="18">
-        <v>879</v>
+        <v>855</v>
       </c>
       <c r="U54" s="17">
-        <v>711.99</v>
+        <v>692.55000000000007</v>
       </c>
       <c r="V54" s="14">
-        <v>31.291262135922331</v>
+        <v>30.436893203883496</v>
       </c>
       <c r="W54" s="16">
         <v>618</v>
       </c>
       <c r="X54" s="15">
-        <v>457.63636363636363</v>
+        <v>433.63636363636363</v>
       </c>
       <c r="Y54" s="18">
-        <v>114</v>
+        <v>211</v>
       </c>
       <c r="Z54" s="17">
-        <v>92.34</v>
+        <v>170.91000000000003</v>
       </c>
       <c r="AA54" s="14">
-        <v>9.3234200743494426</v>
+        <v>23.977272727272727</v>
       </c>
       <c r="AB54" s="16">
-        <v>269</v>
+        <v>193.60000000000002</v>
       </c>
       <c r="AC54" s="15">
-        <v>-69.409090909090907</v>
+        <v>79</v>
       </c>
       <c r="AD54" s="19">
-        <v>10282</v>
+        <v>12185</v>
       </c>
       <c r="AE54" s="20">
-        <v>8328.42</v>
+        <v>9869.85</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
       </c>
       <c r="AG54" s="22">
-        <v>33.648433847592337</v>
+        <v>39.876110331930811</v>
       </c>
       <c r="AH54" s="23">
-        <v>3.3648433847592338</v>
+        <v>3.9876110331930814</v>
       </c>
       <c r="AI54" s="26">
-        <v>7226.2857142857147</v>
+        <v>9129.2857142857138</v>
       </c>
       <c r="AJ54" s="27">
         <v>1527.8571428571427</v>
       </c>
       <c r="AK54" s="25">
-        <v>-5698.4285714285725</v>
+        <v>-7601.4285714285706</v>
       </c>
       <c r="AL54" s="28">
-        <v>856.83333333333337</v>
+        <v>1015.4166666666666</v>
       </c>
     </row>
     <row r="55" spans="2:39" x14ac:dyDescent="0.25">
@@ -6985,34 +6973,34 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>4329</v>
+        <v>4560</v>
       </c>
       <c r="F55" s="14">
-        <v>3506.4900000000002</v>
+        <v>3693.6000000000004</v>
       </c>
       <c r="G55" s="14">
-        <v>34.962555066079297</v>
+        <v>36.828193832599119</v>
       </c>
       <c r="H55" s="30">
         <v>2724</v>
       </c>
       <c r="I55" s="15">
-        <v>3090.818181818182</v>
+        <v>3321.818181818182</v>
       </c>
       <c r="J55" s="16">
-        <v>8458</v>
+        <v>8196</v>
       </c>
       <c r="K55" s="13">
-        <v>6850.9800000000005</v>
+        <v>6638.76</v>
       </c>
       <c r="L55" s="14">
-        <v>95.17953964194372</v>
+        <v>92.23120204603579</v>
       </c>
       <c r="M55" s="30">
         <v>1955.0000000000002</v>
       </c>
       <c r="N55" s="15">
-        <v>7569.363636363636</v>
+        <v>7307.363636363636</v>
       </c>
       <c r="O55" s="16">
         <v>237</v>
@@ -7030,61 +7018,61 @@
         <v>-69.818181818181813</v>
       </c>
       <c r="T55" s="18">
-        <v>521</v>
+        <v>489</v>
       </c>
       <c r="U55" s="17">
-        <v>422.01000000000005</v>
+        <v>396.09000000000003</v>
       </c>
       <c r="V55" s="14">
-        <v>16.166431593794076</v>
+        <v>15.173483779971791</v>
       </c>
       <c r="W55" s="16">
         <v>709</v>
       </c>
       <c r="X55" s="15">
-        <v>37.590909090909122</v>
+        <v>5.5909090909091219</v>
       </c>
       <c r="Y55" s="18">
-        <v>126</v>
+        <v>222</v>
       </c>
       <c r="Z55" s="17">
-        <v>102.06</v>
+        <v>179.82000000000002</v>
       </c>
       <c r="AA55" s="14">
-        <v>11.087999999999999</v>
+        <v>25.227272727272727</v>
       </c>
       <c r="AB55" s="16">
-        <v>250.00000000000003</v>
+        <v>193.60000000000002</v>
       </c>
       <c r="AC55" s="15">
-        <v>-44.454545454545467</v>
+        <v>90</v>
       </c>
       <c r="AD55" s="19">
-        <v>13671</v>
+        <v>13704</v>
       </c>
       <c r="AE55" s="20">
-        <v>11073.51</v>
+        <v>11100.240000000002</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
       </c>
       <c r="AG55" s="22">
-        <v>47.156865965834427</v>
+        <v>47.270696452036788</v>
       </c>
       <c r="AH55" s="23">
-        <v>4.7156865965834429</v>
+        <v>4.7270696452036791</v>
       </c>
       <c r="AI55" s="26">
-        <v>10771.952380952382</v>
+        <v>10804.952380952382</v>
       </c>
       <c r="AJ55" s="27">
         <v>1449.5238095238096</v>
       </c>
       <c r="AK55" s="25">
-        <v>-9322.4285714285725</v>
+        <v>-9355.4285714285725</v>
       </c>
       <c r="AL55" s="28">
-        <v>1139.25</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="56" spans="2:39" x14ac:dyDescent="0.25">
@@ -7098,34 +7086,34 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="F56" s="14">
-        <v>427.06</v>
+        <v>395.62</v>
       </c>
       <c r="G56" s="14">
-        <v>7.1863727454909814</v>
+        <v>6.6573146292585168</v>
       </c>
       <c r="H56" s="30">
         <v>499</v>
       </c>
       <c r="I56" s="15">
-        <v>-63.818181818181841</v>
+        <v>-75.818181818181841</v>
       </c>
       <c r="J56" s="32">
-        <v>620</v>
+        <v>584</v>
       </c>
       <c r="K56" s="13">
-        <v>1624.4</v>
+        <v>1530.0800000000002</v>
       </c>
       <c r="L56" s="14">
-        <v>30.651685393258429</v>
+        <v>28.871910112359551</v>
       </c>
       <c r="M56" s="30">
         <v>445</v>
       </c>
       <c r="N56" s="15">
-        <v>417.72727272727275</v>
+        <v>381.72727272727275</v>
       </c>
       <c r="O56" s="32">
         <v>28</v>
@@ -7143,61 +7131,61 @@
         <v>7.5454545454545467</v>
       </c>
       <c r="T56" s="18">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="U56" s="17">
-        <v>96.94</v>
+        <v>75.98</v>
       </c>
       <c r="V56" s="14">
-        <v>4.3297872340425538</v>
+        <v>3.3936170212765959</v>
       </c>
       <c r="W56" s="16">
         <v>188</v>
       </c>
       <c r="X56" s="15">
-        <v>-91.181818181818187</v>
+        <v>-99.181818181818187</v>
       </c>
       <c r="Y56" s="18">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="Z56" s="17">
-        <v>104.80000000000001</v>
+        <v>167.68</v>
       </c>
       <c r="AA56" s="14">
-        <v>17.599999999999998</v>
+        <v>26.666666666666668</v>
       </c>
       <c r="AB56" s="16">
-        <v>50</v>
+        <v>52.8</v>
       </c>
       <c r="AC56" s="15">
-        <v>5.9090909090909065</v>
+        <v>28</v>
       </c>
       <c r="AD56" s="19">
-        <v>888</v>
+        <v>856</v>
       </c>
       <c r="AE56" s="20">
-        <v>2326.56</v>
+        <v>2242.7200000000003</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
       </c>
       <c r="AG56" s="22">
-        <v>15.386138613861387</v>
+        <v>14.831683168316832</v>
       </c>
       <c r="AH56" s="23">
-        <v>1.5386138613861386</v>
+        <v>1.4831683168316832</v>
       </c>
       <c r="AI56" s="26">
-        <v>310.85714285714289</v>
+        <v>278.85714285714289</v>
       </c>
       <c r="AJ56" s="27">
         <v>288.57142857142856</v>
       </c>
       <c r="AK56" s="25">
-        <v>-22.285714285714334</v>
+        <v>9.7142857142856656</v>
       </c>
       <c r="AL56" s="28">
-        <v>148</v>
+        <v>142.66666666666666</v>
       </c>
     </row>
     <row r="57" spans="2:39" x14ac:dyDescent="0.25">
@@ -7211,106 +7199,106 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="F57" s="14">
-        <v>272.48</v>
+        <v>131</v>
       </c>
       <c r="G57" s="14">
-        <v>2.517051705170517</v>
+        <v>1.21012101210121</v>
       </c>
       <c r="H57" s="30">
         <v>909</v>
       </c>
       <c r="I57" s="15">
-        <v>-309.18181818181819</v>
+        <v>-363.18181818181819</v>
       </c>
       <c r="J57" s="32">
-        <v>912</v>
+        <v>780</v>
       </c>
       <c r="K57" s="13">
-        <v>2389.44</v>
+        <v>2043.6000000000001</v>
       </c>
       <c r="L57" s="14">
-        <v>23.330232558139539</v>
+        <v>19.953488372093027</v>
       </c>
       <c r="M57" s="30">
         <v>859.99999999999989</v>
       </c>
       <c r="N57" s="15">
-        <v>521.09090909090912</v>
+        <v>389.09090909090912</v>
       </c>
       <c r="O57" s="32">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="P57" s="17">
-        <v>31.44</v>
+        <v>172.92000000000002</v>
       </c>
       <c r="Q57" s="14">
-        <v>3.8260869565217392</v>
+        <v>21.043478260869566</v>
       </c>
       <c r="R57" s="16">
         <v>69</v>
       </c>
       <c r="S57" s="15">
-        <v>-35.045454545454547</v>
+        <v>18.954545454545453</v>
       </c>
       <c r="T57" s="18">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="U57" s="17">
-        <v>337.98</v>
+        <v>60.260000000000005</v>
       </c>
       <c r="V57" s="14">
-        <v>9.1844660194174761</v>
+        <v>1.6375404530744337</v>
       </c>
       <c r="W57" s="16">
         <v>309</v>
       </c>
       <c r="X57" s="15">
-        <v>-81.681818181818187</v>
+        <v>-187.68181818181819</v>
       </c>
       <c r="Y57" s="18">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="Z57" s="17">
-        <v>146.72</v>
+        <v>209.60000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>23.69230769230769</v>
+        <v>33.333333333333336</v>
       </c>
       <c r="AB57" s="16">
-        <v>52</v>
+        <v>52.8</v>
       </c>
       <c r="AC57" s="15">
-        <v>20.545454545454547</v>
+        <v>44</v>
       </c>
       <c r="AD57" s="19">
-        <v>1213</v>
+        <v>999</v>
       </c>
       <c r="AE57" s="20">
-        <v>3178.06</v>
+        <v>2617.38</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
       </c>
       <c r="AG57" s="22">
-        <v>11.583901773533425</v>
+        <v>9.5402455661664405</v>
       </c>
       <c r="AH57" s="23">
-        <v>1.1583901773533425</v>
+        <v>0.95402455661664398</v>
       </c>
       <c r="AI57" s="26">
-        <v>165.85714285714289</v>
+        <v>-48.14285714285711</v>
       </c>
       <c r="AJ57" s="27">
         <v>523.57142857142856</v>
       </c>
       <c r="AK57" s="25">
-        <v>357.71428571428567</v>
+        <v>571.71428571428567</v>
       </c>
       <c r="AL57" s="28">
-        <v>202.16666666666666</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="58" spans="2:39" x14ac:dyDescent="0.25">
@@ -7324,106 +7312,106 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="F58" s="14">
-        <v>618.32000000000005</v>
+        <v>539.72</v>
       </c>
       <c r="G58" s="14">
-        <v>12.303317535545023</v>
+        <v>10.739336492890994</v>
       </c>
       <c r="H58" s="30">
         <v>422</v>
       </c>
       <c r="I58" s="15">
-        <v>44.181818181818159</v>
+        <v>14.181818181818159</v>
       </c>
       <c r="J58" s="32">
-        <v>321</v>
+        <v>209</v>
       </c>
       <c r="K58" s="13">
-        <v>841.02</v>
+        <v>547.58000000000004</v>
       </c>
       <c r="L58" s="14">
-        <v>17.351351351351351</v>
+        <v>11.297297297297296</v>
       </c>
       <c r="M58" s="30">
         <v>407</v>
       </c>
       <c r="N58" s="15">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="O58" s="32">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="P58" s="17">
-        <v>55.02</v>
+        <v>96.94</v>
       </c>
       <c r="Q58" s="14">
-        <v>10.266666666666667</v>
+        <v>18.088888888888889</v>
       </c>
       <c r="R58" s="16">
         <v>45</v>
       </c>
       <c r="S58" s="15">
-        <v>-9.6818181818181799</v>
+        <v>6.3181818181818201</v>
       </c>
       <c r="T58" s="18">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U58" s="17">
-        <v>178.16</v>
+        <v>175.54000000000002</v>
       </c>
       <c r="V58" s="14">
-        <v>13.477477477477477</v>
+        <v>13.279279279279278</v>
       </c>
       <c r="W58" s="16">
         <v>111</v>
       </c>
       <c r="X58" s="15">
-        <v>-7.681818181818187</v>
+        <v>-8.681818181818187</v>
       </c>
       <c r="Y58" s="18">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="Z58" s="17">
-        <v>102.18</v>
+        <v>165.06</v>
       </c>
       <c r="AA58" s="14">
-        <v>16.823529411764703</v>
+        <v>26.25</v>
       </c>
       <c r="AB58" s="16">
-        <v>51</v>
+        <v>52.8</v>
       </c>
       <c r="AC58" s="15">
-        <v>4.2272727272727266</v>
+        <v>27</v>
       </c>
       <c r="AD58" s="19">
-        <v>685</v>
+        <v>582</v>
       </c>
       <c r="AE58" s="20">
-        <v>1794.7</v>
+        <v>1524.8400000000001</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
       </c>
       <c r="AG58" s="22">
-        <v>13.885135135135135</v>
+        <v>11.797297297297296</v>
       </c>
       <c r="AH58" s="23">
-        <v>1.3885135135135134</v>
+        <v>1.1797297297297296</v>
       </c>
       <c r="AI58" s="26">
-        <v>191.66666666666663</v>
+        <v>88.666666666666629</v>
       </c>
       <c r="AJ58" s="27">
         <v>246.66666666666669</v>
       </c>
       <c r="AK58" s="25">
-        <v>55.000000000000057</v>
+        <v>158.00000000000006</v>
       </c>
       <c r="AL58" s="28">
-        <v>114.16666666666667</v>
+        <v>97</v>
       </c>
       <c r="AM58" s="62" t="s">
         <v>16</v>
@@ -7440,110 +7428,110 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F59" s="14">
-        <v>222.70000000000002</v>
+        <v>159.82</v>
       </c>
       <c r="G59" s="14">
-        <v>3.6738703339882122</v>
+        <v>2.6365422396856579</v>
       </c>
       <c r="H59" s="30">
         <v>509</v>
       </c>
       <c r="I59" s="15">
-        <v>-146.36363636363637</v>
+        <v>-170.36363636363637</v>
       </c>
       <c r="J59" s="32">
-        <v>131</v>
+        <v>470</v>
       </c>
       <c r="K59" s="13">
-        <v>343.22</v>
+        <v>1231.4000000000001</v>
       </c>
       <c r="L59" s="14">
-        <v>7.1336633663366342</v>
+        <v>25.594059405940595</v>
       </c>
       <c r="M59" s="30">
         <v>404</v>
       </c>
       <c r="N59" s="15">
-        <v>-52.636363636363626</v>
+        <v>286.36363636363637</v>
       </c>
       <c r="O59" s="32">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P59" s="17">
-        <v>0</v>
+        <v>62.88</v>
       </c>
       <c r="Q59" s="14">
-        <v>0</v>
+        <v>20.307692307692307</v>
       </c>
       <c r="R59" s="16">
         <v>26</v>
       </c>
       <c r="S59" s="15">
-        <v>-17.727272727272727</v>
+        <v>6.2727272727272734</v>
       </c>
       <c r="T59" s="18">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U59" s="17">
-        <v>183.4</v>
+        <v>180.78</v>
       </c>
       <c r="V59" s="14">
-        <v>7.897435897435896</v>
+        <v>7.7846153846153836</v>
       </c>
       <c r="W59" s="16">
         <v>195.00000000000003</v>
       </c>
       <c r="X59" s="15">
-        <v>-62.954545454545467</v>
+        <v>-63.954545454545467</v>
       </c>
       <c r="Y59" s="18">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="Z59" s="17">
-        <v>83.84</v>
+        <v>146.72</v>
       </c>
       <c r="AA59" s="14">
-        <v>25.142857142857142</v>
+        <v>23.333333333333336</v>
       </c>
       <c r="AB59" s="16">
-        <v>28</v>
+        <v>52.8</v>
       </c>
       <c r="AC59" s="15">
-        <v>12.90909090909091</v>
+        <v>20</v>
       </c>
       <c r="AD59" s="19">
-        <v>318</v>
+        <v>680</v>
       </c>
       <c r="AE59" s="20">
-        <v>833.16000000000008</v>
+        <v>1781.6000000000001</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
       </c>
       <c r="AG59" s="22">
-        <v>5.7469879518072284</v>
+        <v>12.289156626506024</v>
       </c>
       <c r="AH59" s="23">
-        <v>0.57469879518072287</v>
+        <v>1.2289156626506024</v>
       </c>
       <c r="AI59" s="26">
-        <v>-235.33333333333337</v>
+        <v>126.66666666666663</v>
       </c>
       <c r="AJ59" s="27">
         <v>276.66666666666669</v>
       </c>
       <c r="AK59" s="25">
-        <v>512</v>
+        <v>150.00000000000006</v>
       </c>
       <c r="AL59" s="28">
-        <v>53</v>
+        <v>113.33333333333333</v>
       </c>
       <c r="AM59" s="63">
         <f>SUM(AL52:AL59)</f>
-        <v>3614.333333333333</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="60" spans="2:39" x14ac:dyDescent="0.25">
@@ -7583,7 +7571,7 @@
       </c>
       <c r="AK60" s="38">
         <f>SUMIF(AK13:AK59,"&gt;0")</f>
-        <v>158358.28571428574</v>
+        <v>147790.42857142861</v>
       </c>
     </row>
     <row r="61" spans="2:39" x14ac:dyDescent="0.25">
@@ -7592,10 +7580,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="67"/>
+      <c r="F61" s="69"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7625,17 +7613,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="68" t="s">
+      <c r="B62" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="68"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>112653.98000000003</v>
+        <v>134071.12</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>30.293251439839953</v>
+        <v>32.236879817337901</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7673,11 +7661,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>189822.16</v>
+        <v>191772.04999999996</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>51.044183452138384</v>
+        <v>46.110844215924459</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7715,11 +7703,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>9946.9400000000023</v>
+        <v>26558.179999999997</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>2.674784809884228</v>
+        <v>6.38581117862838</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7757,11 +7745,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>51467.850000000006</v>
+        <v>42646.009999999987</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>13.839977257065987</v>
+        <v>10.254067386466154</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7799,11 +7787,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>7987.2100000000009</v>
+        <v>20846.239999999991</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>2.1478030410714655</v>
+        <v>5.0123974016431116</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7835,19 +7823,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="68" t="s">
+      <c r="B67" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="68"/>
+      <c r="C67" s="65"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>371878.13999999996</v>
-      </c>
-      <c r="E67" s="69">
+        <v>415893.59999999992</v>
+      </c>
+      <c r="E67" s="66">
         <f>D67*100/D67</f>
-        <v>99.999999999999986</v>
-      </c>
-      <c r="F67" s="69"/>
+        <v>100</v>
+      </c>
+      <c r="F67" s="66"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7947,17 +7935,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="68"/>
+      <c r="C70" s="65"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>90530</v>
+        <v>102234</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>32.332604751496447</v>
+        <v>33.81078211865556</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -7994,11 +7982,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>139589</v>
+        <v>135340</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>49.853926484664065</v>
+        <v>44.759583425659208</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8036,11 +8024,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>7426</v>
+        <v>19804</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>2.6521807454392206</v>
+        <v>6.5495698992297537</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8078,11 +8066,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>36982</v>
+        <v>30921</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>13.208045829226132</v>
+        <v>10.226179097863222</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8120,11 +8108,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>5469</v>
+        <v>14072</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>1.9532421891741309</v>
+        <v>4.6538854585922591</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8156,19 +8144,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="68" t="s">
+      <c r="B75" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="68"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>279996</v>
-      </c>
-      <c r="E75" s="69">
+        <v>302371</v>
+      </c>
+      <c r="E75" s="66">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="69"/>
+      <c r="F75" s="66"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8715,17 +8703,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8734,6 +8711,17 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F062716-DE19-4A23-8606-24417D77238D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4330D84F-A5C8-4AE4-B121-894A541D1EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -1174,6 +1174,7 @@
       <sheetName val="INVENTARIO NACIONAL 03-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 04-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 09-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1303,6 +1304,7 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4330D84F-A5C8-4AE4-B121-894A541D1EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F462BC7-3C32-47F6-810E-BCCD2E4F9BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -805,12 +805,6 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -819,6 +813,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1632,242 +1632,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="68" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
-      <c r="AI1" s="68"/>
-      <c r="AJ1" s="68"/>
-      <c r="AK1" s="68"/>
-      <c r="AL1" s="68"/>
+      <c r="AG1" s="66"/>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="66"/>
+      <c r="AJ1" s="66"/>
+      <c r="AK1" s="66"/>
+      <c r="AL1" s="66"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="65"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
+      <c r="AH2" s="66"/>
+      <c r="AI2" s="66"/>
+      <c r="AJ2" s="66"/>
+      <c r="AK2" s="66"/>
+      <c r="AL2" s="66"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
+      <c r="AH3" s="66"/>
+      <c r="AI3" s="66"/>
+      <c r="AJ3" s="66"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="66"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="65"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="66"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="67"/>
-      <c r="Z5" s="67"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="65"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
+      <c r="AL5" s="66"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="68"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="65"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
+      <c r="AL6" s="66"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2232,85 +2232,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>4686</v>
+        <v>5943</v>
       </c>
       <c r="F13" s="14">
-        <v>6372.96</v>
+        <v>8082.4800000000005</v>
       </c>
       <c r="G13" s="14">
-        <v>6.0136498862509473</v>
+        <v>7.6267864434463046</v>
       </c>
       <c r="H13" s="30">
         <v>17143</v>
       </c>
       <c r="I13" s="15">
-        <v>-3106.2727272727279</v>
+        <v>-1849.2727272727279</v>
       </c>
       <c r="J13" s="16">
-        <v>2641</v>
+        <v>5646</v>
       </c>
       <c r="K13" s="13">
-        <v>3591.76</v>
+        <v>7678.56</v>
       </c>
       <c r="L13" s="14">
-        <v>10.848020911127707</v>
+        <v>23.191187453323373</v>
       </c>
       <c r="M13" s="30">
         <v>5356</v>
       </c>
       <c r="N13" s="15">
-        <v>206.4545454545455</v>
+        <v>3211.4545454545455</v>
       </c>
       <c r="O13" s="16">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="P13" s="17">
-        <v>855.44</v>
+        <v>832.32</v>
       </c>
       <c r="Q13" s="14">
-        <v>16.072009291521489</v>
+        <v>15.637630662020907</v>
       </c>
       <c r="R13" s="16">
         <v>861</v>
       </c>
       <c r="S13" s="15">
-        <v>41.954545454545496</v>
+        <v>24.954545454545496</v>
       </c>
       <c r="T13" s="18">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="U13" s="17">
-        <v>393.04</v>
+        <v>346.8</v>
       </c>
       <c r="V13" s="14">
-        <v>5.324958123953099</v>
+        <v>4.6984924623115578</v>
       </c>
       <c r="W13" s="16">
         <v>1194</v>
       </c>
       <c r="X13" s="15">
-        <v>-525.09090909090912</v>
+        <v>-559.09090909090912</v>
       </c>
       <c r="Y13" s="18">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="Z13" s="17">
-        <v>689.5200000000001</v>
+        <v>644.6400000000001</v>
       </c>
       <c r="AA13" s="14">
-        <v>23.472222222222221</v>
+        <v>16.067796610169491</v>
       </c>
       <c r="AB13" s="16">
-        <v>475.20000000000005</v>
+        <v>649</v>
       </c>
       <c r="AC13" s="15">
-        <v>183</v>
+        <v>31.5</v>
       </c>
       <c r="AD13" s="19">
-        <v>8752</v>
+        <v>12930</v>
       </c>
       <c r="AE13" s="20">
-        <v>11902.720000000001</v>
+        <v>17584.800000000003</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2346,49 +2346,49 @@
         <v>1.59</v>
       </c>
       <c r="E14" s="13">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="F14" s="14">
-        <v>419.76000000000005</v>
+        <v>337.08000000000004</v>
       </c>
       <c r="G14" s="14">
-        <v>7.6220472440944889</v>
+        <v>6.1207349081364839</v>
       </c>
       <c r="H14" s="30">
         <v>762</v>
       </c>
       <c r="I14" s="15">
-        <v>-82.363636363636317</v>
+        <v>-134.36363636363632</v>
       </c>
       <c r="J14" s="16">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K14" s="13">
-        <v>160.59</v>
+        <v>0</v>
       </c>
       <c r="L14" s="14">
-        <v>3.8710801393728222</v>
+        <v>0</v>
       </c>
       <c r="M14" s="30">
         <v>574</v>
       </c>
       <c r="N14" s="15">
-        <v>-159.90909090909088</v>
+        <v>-260.90909090909088</v>
       </c>
       <c r="O14" s="16">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="P14" s="17">
-        <v>235.32000000000002</v>
+        <v>248.04000000000002</v>
       </c>
       <c r="Q14" s="14">
-        <v>19.152941176470588</v>
+        <v>20.188235294117646</v>
       </c>
       <c r="R14" s="16">
         <v>170</v>
       </c>
       <c r="S14" s="15">
-        <v>32.090909090909093</v>
+        <v>40.090909090909093</v>
       </c>
       <c r="T14" s="18">
         <v>31</v>
@@ -2406,25 +2406,25 @@
         <v>-7.1818181818181799</v>
       </c>
       <c r="Y14" s="18">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Z14" s="17">
-        <v>166.95000000000002</v>
+        <v>162.18</v>
       </c>
       <c r="AA14" s="14">
-        <v>65.625</v>
+        <v>43.714285714285708</v>
       </c>
       <c r="AB14" s="16">
-        <v>35.200000000000003</v>
+        <v>51.333333333333336</v>
       </c>
       <c r="AC14" s="15">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="AD14" s="19">
-        <v>649</v>
+        <v>501</v>
       </c>
       <c r="AE14" s="20">
-        <v>1031.9100000000001</v>
+        <v>796.59</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2460,34 +2460,34 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>1860</v>
+        <v>1743</v>
       </c>
       <c r="F15" s="14">
-        <v>3775.7999999999997</v>
+        <v>3538.2899999999995</v>
       </c>
       <c r="G15" s="14">
-        <v>5.9304347826086961</v>
+        <v>5.557391304347826</v>
       </c>
       <c r="H15" s="30">
         <v>6900</v>
       </c>
       <c r="I15" s="15">
-        <v>-1276.363636363636</v>
+        <v>-1393.363636363636</v>
       </c>
       <c r="J15" s="16">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K15" s="13">
-        <v>71.05</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>0.2550513415038092</v>
+        <v>0</v>
       </c>
       <c r="M15" s="30">
         <v>3019</v>
       </c>
       <c r="N15" s="15">
-        <v>-1337.2727272727273</v>
+        <v>-1372.2727272727273</v>
       </c>
       <c r="O15" s="16">
         <v>240</v>
@@ -2505,40 +2505,40 @@
         <v>37.5</v>
       </c>
       <c r="T15" s="18">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="U15" s="17">
-        <v>71.05</v>
+        <v>64.959999999999994</v>
       </c>
       <c r="V15" s="14">
-        <v>2.2190201729106627</v>
+        <v>2.0288184438040342</v>
       </c>
       <c r="W15" s="16">
         <v>347.00000000000006</v>
       </c>
       <c r="X15" s="15">
-        <v>-201.59090909090912</v>
+        <v>-204.59090909090912</v>
       </c>
       <c r="Y15" s="18">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Z15" s="17">
-        <v>517.65</v>
+        <v>513.58999999999992</v>
       </c>
       <c r="AA15" s="14">
-        <v>60.714285714285708</v>
+        <v>37.024390243902445</v>
       </c>
       <c r="AB15" s="16">
-        <v>92.4</v>
+        <v>150.33333333333331</v>
       </c>
       <c r="AC15" s="15">
-        <v>192</v>
+        <v>150.5</v>
       </c>
       <c r="AD15" s="19">
-        <v>2425</v>
+        <v>2268</v>
       </c>
       <c r="AE15" s="20">
-        <v>4922.7499999999991</v>
+        <v>4604.04</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2573,49 +2573,49 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>303</v>
+        <v>420</v>
       </c>
       <c r="F16" s="14">
-        <v>1093.83</v>
+        <v>1516.2</v>
       </c>
       <c r="G16" s="14">
-        <v>4.771653543307087</v>
+        <v>6.6141732283464565</v>
       </c>
       <c r="H16" s="30">
         <v>1397</v>
       </c>
       <c r="I16" s="15">
-        <v>-332</v>
+        <v>-215</v>
       </c>
       <c r="J16" s="16">
-        <v>243</v>
+        <v>730</v>
       </c>
       <c r="K16" s="13">
-        <v>877.23</v>
+        <v>2635.2999999999997</v>
       </c>
       <c r="L16" s="14">
-        <v>9.8091743119266059</v>
+        <v>29.467889908256879</v>
       </c>
       <c r="M16" s="30">
         <v>545</v>
       </c>
       <c r="N16" s="15">
-        <v>-4.7272727272727479</v>
+        <v>482.27272727272725</v>
       </c>
       <c r="O16" s="16">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="P16" s="17">
-        <v>126.35</v>
+        <v>101.08</v>
       </c>
       <c r="Q16" s="14">
-        <v>16.739130434782606</v>
+        <v>13.391304347826084</v>
       </c>
       <c r="R16" s="16">
         <v>46.000000000000007</v>
       </c>
       <c r="S16" s="15">
-        <v>3.6363636363636296</v>
+        <v>-3.3636363636363704</v>
       </c>
       <c r="T16" s="18">
         <v>28</v>
@@ -2633,25 +2633,25 @@
         <v>-5.4090909090909065</v>
       </c>
       <c r="Y16" s="18">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="Z16" s="17">
-        <v>296.02</v>
+        <v>267.14</v>
       </c>
       <c r="AA16" s="14">
-        <v>136.66666666666669</v>
+        <v>34.153846153846153</v>
       </c>
       <c r="AB16" s="16">
-        <v>13.2</v>
+        <v>47.666666666666664</v>
       </c>
       <c r="AC16" s="15">
-        <v>73</v>
+        <v>41.5</v>
       </c>
       <c r="AD16" s="19">
-        <v>691</v>
+        <v>1280</v>
       </c>
       <c r="AE16" s="20">
-        <v>2494.5099999999998</v>
+        <v>4620.8</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2686,49 +2686,49 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
-        <v>158.04</v>
+        <v>351.2</v>
       </c>
       <c r="G17" s="14">
-        <v>2.3712574850299402</v>
+        <v>5.2694610778443112</v>
       </c>
       <c r="H17" s="30">
         <v>167</v>
       </c>
       <c r="I17" s="15">
-        <v>-57.909090909090907</v>
+        <v>-35.909090909090907</v>
       </c>
       <c r="J17" s="16">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="K17" s="13">
-        <v>237.05999999999997</v>
+        <v>939.45999999999992</v>
       </c>
       <c r="L17" s="14">
-        <v>8.608695652173914</v>
+        <v>34.115942028985508</v>
       </c>
       <c r="M17" s="30">
         <v>69</v>
       </c>
       <c r="N17" s="15">
-        <v>-4.3636363636363633</v>
+        <v>75.63636363636364</v>
       </c>
       <c r="O17" s="16">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="P17" s="17">
-        <v>52.679999999999993</v>
+        <v>114.13999999999999</v>
       </c>
       <c r="Q17" s="14">
-        <v>16.5</v>
+        <v>35.75</v>
       </c>
       <c r="R17" s="16">
         <v>8</v>
       </c>
       <c r="S17" s="15">
-        <v>0.54545454545454497</v>
+        <v>7.545454545454545</v>
       </c>
       <c r="T17" s="18">
         <v>17</v>
@@ -2752,19 +2752,19 @@
         <v>122.91999999999999</v>
       </c>
       <c r="AA17" s="14">
-        <v>23.333333333333336</v>
+        <v>14</v>
       </c>
       <c r="AB17" s="16">
-        <v>13.2</v>
+        <v>22</v>
       </c>
       <c r="AC17" s="15">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AD17" s="19">
-        <v>82</v>
+        <v>191</v>
       </c>
       <c r="AE17" s="20">
-        <v>719.95999999999992</v>
+        <v>1676.9799999999998</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2799,85 +2799,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>7800</v>
+        <v>9753</v>
       </c>
       <c r="F18" s="14">
-        <v>4914</v>
+        <v>6144.39</v>
       </c>
       <c r="G18" s="14">
-        <v>9.4001643385373868</v>
+        <v>11.753820870994248</v>
       </c>
       <c r="H18" s="30">
         <v>18255</v>
       </c>
       <c r="I18" s="15">
-        <v>-497.72727272727207</v>
+        <v>1455.2727272727279</v>
       </c>
       <c r="J18" s="16">
-        <v>3869</v>
+        <v>6928</v>
       </c>
       <c r="K18" s="13">
-        <v>2437.4699999999998</v>
+        <v>4364.6400000000003</v>
       </c>
       <c r="L18" s="14">
-        <v>12.30028901734104</v>
+        <v>22.025433526011561</v>
       </c>
       <c r="M18" s="30">
         <v>6920</v>
       </c>
       <c r="N18" s="15">
-        <v>723.5454545454545</v>
+        <v>3782.5454545454545</v>
       </c>
       <c r="O18" s="16">
-        <v>961</v>
+        <v>927</v>
       </c>
       <c r="P18" s="17">
-        <v>605.42999999999995</v>
+        <v>584.01</v>
       </c>
       <c r="Q18" s="14">
-        <v>14.63114186851211</v>
+        <v>14.11349480968858</v>
       </c>
       <c r="R18" s="16">
         <v>1445</v>
       </c>
       <c r="S18" s="15">
-        <v>-24.227272727272748</v>
+        <v>-58.227272727272748</v>
       </c>
       <c r="T18" s="18">
-        <v>1124</v>
+        <v>962</v>
       </c>
       <c r="U18" s="17">
-        <v>708.12</v>
+        <v>606.06000000000006</v>
       </c>
       <c r="V18" s="14">
-        <v>6.4095386210471741</v>
+        <v>5.485743908761016</v>
       </c>
       <c r="W18" s="16">
         <v>3858</v>
       </c>
       <c r="X18" s="15">
-        <v>-1506.4545454545455</v>
+        <v>-1668.4545454545455</v>
       </c>
       <c r="Y18" s="18">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="Z18" s="17">
-        <v>234.99</v>
+        <v>231.84</v>
       </c>
       <c r="AA18" s="14">
-        <v>50.405405405405403</v>
+        <v>25.379310344827587</v>
       </c>
       <c r="AB18" s="16">
-        <v>162.80000000000001</v>
+        <v>319</v>
       </c>
       <c r="AC18" s="15">
-        <v>262</v>
+        <v>150.5</v>
       </c>
       <c r="AD18" s="19">
-        <v>14127</v>
+        <v>18938</v>
       </c>
       <c r="AE18" s="20">
-        <v>8900.01</v>
+        <v>11930.94</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2912,85 +2912,85 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>1176</v>
+        <v>155</v>
       </c>
       <c r="F19" s="14">
-        <v>740.88</v>
+        <v>97.65</v>
       </c>
       <c r="G19" s="14">
-        <v>17.422222222222224</v>
+        <v>2.2962962962962967</v>
       </c>
       <c r="H19" s="30">
         <v>1484.9999999999998</v>
       </c>
       <c r="I19" s="15">
-        <v>501.00000000000011</v>
+        <v>-519.99999999999989</v>
       </c>
       <c r="J19" s="16">
-        <v>227</v>
+        <v>1028</v>
       </c>
       <c r="K19" s="13">
-        <v>143.01</v>
+        <v>647.64</v>
       </c>
       <c r="L19" s="14">
-        <v>4.4430604982206408</v>
+        <v>20.12099644128114</v>
       </c>
       <c r="M19" s="30">
         <v>1124</v>
       </c>
       <c r="N19" s="15">
-        <v>-283.90909090909093</v>
+        <v>517.09090909090901</v>
       </c>
       <c r="O19" s="16">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P19" s="17">
-        <v>54.81</v>
+        <v>53.55</v>
       </c>
       <c r="Q19" s="14">
-        <v>20.361702127659576</v>
+        <v>19.893617021276597</v>
       </c>
       <c r="R19" s="16">
         <v>94</v>
       </c>
       <c r="S19" s="15">
-        <v>22.909090909090907</v>
+        <v>20.909090909090907</v>
       </c>
       <c r="T19" s="18">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U19" s="17">
-        <v>32.130000000000003</v>
+        <v>34.020000000000003</v>
       </c>
       <c r="V19" s="14">
-        <v>3.3097345132743365</v>
+        <v>3.5044247787610621</v>
       </c>
       <c r="W19" s="16">
         <v>339</v>
       </c>
       <c r="X19" s="15">
-        <v>-180.13636363636363</v>
+        <v>-177.13636363636363</v>
       </c>
       <c r="Y19" s="18">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Z19" s="17">
-        <v>151.19999999999999</v>
+        <v>149.31</v>
       </c>
       <c r="AA19" s="14">
-        <v>18.75</v>
+        <v>15.290322580645162</v>
       </c>
       <c r="AB19" s="16">
-        <v>281.60000000000002</v>
+        <v>341</v>
       </c>
       <c r="AC19" s="15">
-        <v>48</v>
+        <v>4.5</v>
       </c>
       <c r="AD19" s="19">
-        <v>1781</v>
+        <v>1559</v>
       </c>
       <c r="AE19" s="20">
-        <v>1122.03</v>
+        <v>982.17</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3025,51 +3025,53 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>2248</v>
+        <v>2180</v>
       </c>
       <c r="F20" s="14">
-        <v>1416.24</v>
+        <v>1373.4</v>
       </c>
       <c r="G20" s="14">
-        <v>14.653629629629631</v>
+        <v>14.21037037037037</v>
       </c>
       <c r="H20" s="30">
         <v>3375</v>
       </c>
       <c r="I20" s="15">
-        <v>713.90909090909099</v>
+        <v>645.90909090909099</v>
       </c>
       <c r="J20" s="16">
-        <v>284</v>
+        <v>1130</v>
       </c>
       <c r="K20" s="13">
-        <v>178.92</v>
+        <v>711.9</v>
       </c>
       <c r="L20" s="14">
-        <v>2.8258706467661692</v>
+        <v>11.243781094527364</v>
       </c>
       <c r="M20" s="30">
         <v>2211</v>
       </c>
       <c r="N20" s="15">
-        <v>-721</v>
+        <v>125</v>
       </c>
       <c r="O20" s="16">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="P20" s="17">
-        <v>151.83000000000001</v>
+        <v>148.05000000000001</v>
       </c>
       <c r="Q20" s="14">
-        <v>19.003584229390682</v>
+        <v>18.53046594982079</v>
       </c>
       <c r="R20" s="16">
         <v>279</v>
       </c>
       <c r="S20" s="15">
-        <v>50.77272727272728</v>
-      </c>
-      <c r="T20" s="18"/>
+        <v>44.77272727272728</v>
+      </c>
+      <c r="T20" s="18">
+        <v>0</v>
+      </c>
       <c r="U20" s="17">
         <v>0</v>
       </c>
@@ -3083,25 +3085,25 @@
         <v>-799.09090909090912</v>
       </c>
       <c r="Y20" s="18">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="Z20" s="17">
-        <v>233.73</v>
+        <v>230.58</v>
       </c>
       <c r="AA20" s="14">
-        <v>38.645833333333336</v>
+        <v>22.875</v>
       </c>
       <c r="AB20" s="16">
-        <v>211.2</v>
+        <v>352</v>
       </c>
       <c r="AC20" s="15">
-        <v>227</v>
+        <v>126</v>
       </c>
       <c r="AD20" s="19">
-        <v>3144</v>
+        <v>3911</v>
       </c>
       <c r="AE20" s="20">
-        <v>1980.72</v>
+        <v>2463.9299999999998</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3136,85 +3138,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>3094</v>
+        <v>4060</v>
       </c>
       <c r="F21" s="14">
-        <v>3372.46</v>
+        <v>4425.4000000000005</v>
       </c>
       <c r="G21" s="14">
-        <v>10.665622062049515</v>
+        <v>13.995612660607961</v>
       </c>
       <c r="H21" s="30">
         <v>6382</v>
       </c>
       <c r="I21" s="15">
-        <v>193.09090909090946</v>
+        <v>1159.0909090909095</v>
       </c>
       <c r="J21" s="16">
-        <v>2029</v>
+        <v>142</v>
       </c>
       <c r="K21" s="13">
-        <v>2211.61</v>
+        <v>154.78</v>
       </c>
       <c r="L21" s="14">
-        <v>6.587662337662338</v>
+        <v>0.46103896103896103</v>
       </c>
       <c r="M21" s="30">
         <v>6776</v>
       </c>
       <c r="N21" s="15">
-        <v>-1051</v>
+        <v>-2938</v>
       </c>
       <c r="O21" s="16">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="P21" s="17">
-        <v>418.56000000000006</v>
+        <v>386.95000000000005</v>
       </c>
       <c r="Q21" s="14">
-        <v>16.030360531309299</v>
+        <v>14.819734345351044</v>
       </c>
       <c r="R21" s="16">
         <v>527</v>
       </c>
       <c r="S21" s="15">
-        <v>24.681818181818187</v>
+        <v>-4.318181818181813</v>
       </c>
       <c r="T21" s="18">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="U21" s="17">
-        <v>479.6</v>
+        <v>439.27000000000004</v>
       </c>
       <c r="V21" s="14">
-        <v>4.6740704973442782</v>
+        <v>4.2810236600675999</v>
       </c>
       <c r="W21" s="16">
         <v>2071</v>
       </c>
       <c r="X21" s="15">
-        <v>-972.0454545454545</v>
+        <v>-1009.0454545454545</v>
       </c>
       <c r="Y21" s="18">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="Z21" s="17">
-        <v>455.62000000000006</v>
+        <v>439.27000000000004</v>
       </c>
       <c r="AA21" s="14">
-        <v>18.173913043478262</v>
+        <v>16.013245033112579</v>
       </c>
       <c r="AB21" s="16">
-        <v>506</v>
+        <v>553.66666666666674</v>
       </c>
       <c r="AC21" s="15">
-        <v>73</v>
+        <v>25.499999999999943</v>
       </c>
       <c r="AD21" s="19">
-        <v>6365</v>
+        <v>5363</v>
       </c>
       <c r="AE21" s="20">
-        <v>6937.85</v>
+        <v>5845.67</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3249,34 +3251,34 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1343</v>
+        <v>1242</v>
       </c>
       <c r="F22" s="14">
-        <v>1463.8700000000001</v>
+        <v>1353.7800000000002</v>
       </c>
       <c r="G22" s="14">
-        <v>6.8887852646304495</v>
+        <v>6.3707157845651663</v>
       </c>
       <c r="H22" s="30">
         <v>4289</v>
       </c>
       <c r="I22" s="15">
-        <v>-606.54545454545473</v>
+        <v>-707.54545454545473</v>
       </c>
       <c r="J22" s="16">
-        <v>661</v>
+        <v>2630</v>
       </c>
       <c r="K22" s="13">
-        <v>720.49</v>
+        <v>2866.7000000000003</v>
       </c>
       <c r="L22" s="14">
-        <v>6.016549441456351</v>
+        <v>23.938767066611504</v>
       </c>
       <c r="M22" s="30">
         <v>2417</v>
       </c>
       <c r="N22" s="15">
-        <v>-437.63636363636351</v>
+        <v>1531.3636363636365</v>
       </c>
       <c r="O22" s="16">
         <v>185</v>
@@ -3294,40 +3296,40 @@
         <v>45.909090909090935</v>
       </c>
       <c r="T22" s="18">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="U22" s="17">
-        <v>327</v>
+        <v>294.3</v>
       </c>
       <c r="V22" s="14">
-        <v>9.3088857545839208</v>
+        <v>8.3779971791255292</v>
       </c>
       <c r="W22" s="16">
         <v>709</v>
       </c>
       <c r="X22" s="15">
-        <v>-183.40909090909088</v>
+        <v>-213.40909090909088</v>
       </c>
       <c r="Y22" s="18">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="Z22" s="17">
-        <v>235.44000000000003</v>
+        <v>229.99</v>
       </c>
       <c r="AA22" s="14">
         <v>0</v>
       </c>
       <c r="AB22" s="16">
-        <v>0</v>
+        <v>40.333333333333329</v>
       </c>
       <c r="AC22" s="15">
-        <v>216</v>
+        <v>183.5</v>
       </c>
       <c r="AD22" s="19">
-        <v>2705</v>
+        <v>4538</v>
       </c>
       <c r="AE22" s="20">
-        <v>2948.4500000000003</v>
+        <v>4946.42</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3362,85 +3364,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>9667</v>
+        <v>11281</v>
       </c>
       <c r="F23" s="14">
-        <v>11213.72</v>
+        <v>13085.96</v>
       </c>
       <c r="G23" s="14">
-        <v>5.6416690983367372</v>
+        <v>6.5836008170411437</v>
       </c>
       <c r="H23" s="30">
         <v>37697</v>
       </c>
       <c r="I23" s="15">
-        <v>-7468</v>
+        <v>-5854</v>
       </c>
       <c r="J23" s="16">
-        <v>20171</v>
+        <v>22119</v>
       </c>
       <c r="K23" s="13">
-        <v>23398.359999999997</v>
+        <v>25658.039999999997</v>
       </c>
       <c r="L23" s="14">
-        <v>23.191115756467209</v>
+        <v>25.430781290828325</v>
       </c>
       <c r="M23" s="30">
         <v>19135</v>
       </c>
       <c r="N23" s="15">
-        <v>11473.272727272728</v>
+        <v>13421.272727272728</v>
       </c>
       <c r="O23" s="16">
-        <v>2186</v>
+        <v>2065</v>
       </c>
       <c r="P23" s="17">
-        <v>2535.7599999999998</v>
+        <v>2395.3999999999996</v>
       </c>
       <c r="Q23" s="14">
-        <v>15.252775134792262</v>
+        <v>14.40849984142087</v>
       </c>
       <c r="R23" s="16">
         <v>3153</v>
       </c>
       <c r="S23" s="15">
-        <v>36.227272727272975</v>
+        <v>-84.772727272727025</v>
       </c>
       <c r="T23" s="18">
-        <v>4060</v>
+        <v>3479</v>
       </c>
       <c r="U23" s="17">
-        <v>4709.5999999999995</v>
+        <v>4035.64</v>
       </c>
       <c r="V23" s="14">
-        <v>6.750302297460701</v>
+        <v>5.7843107617896008</v>
       </c>
       <c r="W23" s="16">
         <v>13232</v>
       </c>
       <c r="X23" s="15">
-        <v>-4961.818181818182</v>
+        <v>-5542.818181818182</v>
       </c>
       <c r="Y23" s="18">
-        <v>747</v>
+        <v>637</v>
       </c>
       <c r="Z23" s="17">
-        <v>866.52</v>
+        <v>738.92</v>
       </c>
       <c r="AA23" s="14">
-        <v>14.880478087649401</v>
+        <v>9.1</v>
       </c>
       <c r="AB23" s="16">
-        <v>1104.4000000000001</v>
+        <v>1540</v>
       </c>
       <c r="AC23" s="15">
-        <v>-6</v>
+        <v>-413</v>
       </c>
       <c r="AD23" s="19">
-        <v>36831</v>
+        <v>39581</v>
       </c>
       <c r="AE23" s="20">
-        <v>42723.96</v>
+        <v>45913.96</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3475,85 +3477,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>8018</v>
+        <v>9354</v>
       </c>
       <c r="F24" s="14">
-        <v>9300.8799999999992</v>
+        <v>10850.64</v>
       </c>
       <c r="G24" s="14">
-        <v>6.5677265619182368</v>
+        <v>7.662074614639959</v>
       </c>
       <c r="H24" s="30">
         <v>26858</v>
       </c>
       <c r="I24" s="15">
-        <v>-4190.181818181818</v>
+        <v>-2854.181818181818</v>
       </c>
       <c r="J24" s="16">
-        <v>8904</v>
+        <v>13404</v>
       </c>
       <c r="K24" s="13">
-        <v>10328.64</v>
+        <v>15548.64</v>
       </c>
       <c r="L24" s="14">
-        <v>16.417029835735836</v>
+        <v>24.714046262152195</v>
       </c>
       <c r="M24" s="30">
         <v>11932</v>
       </c>
       <c r="N24" s="15">
-        <v>3480.363636363636</v>
+        <v>7980.363636363636</v>
       </c>
       <c r="O24" s="16">
-        <v>1288</v>
+        <v>1227</v>
       </c>
       <c r="P24" s="17">
-        <v>1494.08</v>
+        <v>1423.32</v>
       </c>
       <c r="Q24" s="14">
-        <v>15.00052938062467</v>
+        <v>14.290100582318688</v>
       </c>
       <c r="R24" s="16">
         <v>1889</v>
       </c>
       <c r="S24" s="15">
-        <v>4.5454545454504114E-2</v>
+        <v>-60.954545454545496</v>
       </c>
       <c r="T24" s="18">
-        <v>3824</v>
+        <v>3551</v>
       </c>
       <c r="U24" s="17">
-        <v>4435.84</v>
+        <v>4119.16</v>
       </c>
       <c r="V24" s="14">
-        <v>11.568756875687567</v>
+        <v>10.742849284928493</v>
       </c>
       <c r="W24" s="16">
         <v>7272</v>
       </c>
       <c r="X24" s="15">
-        <v>-1134.181818181818</v>
+        <v>-1407.181818181818</v>
       </c>
       <c r="Y24" s="18">
-        <v>816</v>
+        <v>743</v>
       </c>
       <c r="Z24" s="17">
-        <v>946.56</v>
+        <v>861.88</v>
       </c>
       <c r="AA24" s="14">
-        <v>23.314285714285713</v>
+        <v>15.31958762886598</v>
       </c>
       <c r="AB24" s="16">
-        <v>770</v>
+        <v>1067</v>
       </c>
       <c r="AC24" s="15">
-        <v>291</v>
+        <v>15.5</v>
       </c>
       <c r="AD24" s="19">
-        <v>22850</v>
+        <v>28279</v>
       </c>
       <c r="AE24" s="20">
-        <v>26505.999999999996</v>
+        <v>32803.64</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3588,85 +3590,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>8261</v>
+        <v>9909</v>
       </c>
       <c r="F25" s="14">
-        <v>9582.76</v>
+        <v>11494.439999999999</v>
       </c>
       <c r="G25" s="14">
-        <v>7.0377168525402727</v>
+        <v>8.4416821561338296</v>
       </c>
       <c r="H25" s="30">
         <v>25824</v>
       </c>
       <c r="I25" s="15">
-        <v>-3477.181818181818</v>
+        <v>-1829.181818181818</v>
       </c>
       <c r="J25" s="16">
-        <v>4167</v>
+        <v>9297</v>
       </c>
       <c r="K25" s="13">
-        <v>4833.7199999999993</v>
+        <v>10784.519999999999</v>
       </c>
       <c r="L25" s="14">
-        <v>7.6965829905129715</v>
+        <v>17.17185794643607</v>
       </c>
       <c r="M25" s="30">
         <v>11911</v>
       </c>
       <c r="N25" s="15">
-        <v>-1247.090909090909</v>
+        <v>3882.909090909091</v>
       </c>
       <c r="O25" s="16">
-        <v>1408</v>
+        <v>1332</v>
       </c>
       <c r="P25" s="17">
-        <v>1633.28</v>
+        <v>1545.12</v>
       </c>
       <c r="Q25" s="14">
-        <v>14.099226217569413</v>
+        <v>13.338188438780156</v>
       </c>
       <c r="R25" s="16">
         <v>2197</v>
       </c>
       <c r="S25" s="15">
-        <v>-89.954545454545496</v>
+        <v>-165.9545454545455</v>
       </c>
       <c r="T25" s="18">
-        <v>3663</v>
+        <v>3385</v>
       </c>
       <c r="U25" s="17">
-        <v>4249.08</v>
+        <v>3926.6</v>
       </c>
       <c r="V25" s="14">
-        <v>11.183180682764363</v>
+        <v>10.334443519289481</v>
       </c>
       <c r="W25" s="16">
         <v>7206.0000000000009</v>
       </c>
       <c r="X25" s="15">
-        <v>-1250.181818181818</v>
+        <v>-1528.181818181818</v>
       </c>
       <c r="Y25" s="18">
-        <v>848</v>
+        <v>815</v>
       </c>
       <c r="Z25" s="17">
-        <v>983.68</v>
+        <v>945.4</v>
       </c>
       <c r="AA25" s="14">
-        <v>27.006369426751593</v>
+        <v>21.541850220264315</v>
       </c>
       <c r="AB25" s="16">
-        <v>690.8</v>
+        <v>832.33333333333337</v>
       </c>
       <c r="AC25" s="15">
-        <v>377</v>
+        <v>247.5</v>
       </c>
       <c r="AD25" s="19">
-        <v>18347</v>
+        <v>24738</v>
       </c>
       <c r="AE25" s="20">
-        <v>21282.519999999997</v>
+        <v>28696.079999999998</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3701,85 +3703,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>6157</v>
+        <v>7477</v>
       </c>
       <c r="F26" s="14">
-        <v>7142.12</v>
+        <v>8673.32</v>
       </c>
       <c r="G26" s="14">
-        <v>4.3172589641434262</v>
+        <v>5.2428366533864539</v>
       </c>
       <c r="H26" s="30">
         <v>31375</v>
       </c>
       <c r="I26" s="15">
-        <v>-8104.3636363636379</v>
+        <v>-6784.3636363636379</v>
       </c>
       <c r="J26" s="16">
-        <v>11022</v>
+        <v>7163</v>
       </c>
       <c r="K26" s="13">
-        <v>12785.519999999999</v>
+        <v>8309.08</v>
       </c>
       <c r="L26" s="14">
-        <v>17.198666572097313</v>
+        <v>11.177104759202781</v>
       </c>
       <c r="M26" s="30">
         <v>14099</v>
       </c>
       <c r="N26" s="15">
-        <v>4613.363636363636</v>
+        <v>754.36363636363603</v>
       </c>
       <c r="O26" s="16">
-        <v>1240</v>
+        <v>1186</v>
       </c>
       <c r="P26" s="17">
-        <v>1438.3999999999999</v>
+        <v>1375.76</v>
       </c>
       <c r="Q26" s="14">
-        <v>14.989010989010987</v>
+        <v>14.336263736263735</v>
       </c>
       <c r="R26" s="16">
         <v>1820</v>
       </c>
       <c r="S26" s="15">
-        <v>-0.90909090909099177</v>
+        <v>-54.909090909090992</v>
       </c>
       <c r="T26" s="18">
-        <v>4327</v>
+        <v>3965</v>
       </c>
       <c r="U26" s="17">
-        <v>5019.32</v>
+        <v>4599.3999999999996</v>
       </c>
       <c r="V26" s="14">
-        <v>11.433341340379535</v>
+        <v>10.476819601249099</v>
       </c>
       <c r="W26" s="16">
         <v>8326</v>
       </c>
       <c r="X26" s="15">
-        <v>-1349.818181818182</v>
+        <v>-1711.818181818182</v>
       </c>
       <c r="Y26" s="18">
-        <v>925</v>
+        <v>903</v>
       </c>
       <c r="Z26" s="17">
-        <v>1073</v>
+        <v>1047.48</v>
       </c>
       <c r="AA26" s="14">
-        <v>18.877551020408163</v>
+        <v>17.309904153354637</v>
       </c>
       <c r="AB26" s="16">
-        <v>1078</v>
+        <v>1147.6666666666665</v>
       </c>
       <c r="AC26" s="15">
-        <v>190</v>
+        <v>120.50000000000011</v>
       </c>
       <c r="AD26" s="19">
-        <v>23671</v>
+        <v>20694</v>
       </c>
       <c r="AE26" s="20">
-        <v>27458.359999999997</v>
+        <v>24005.039999999997</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3814,85 +3816,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>1164</v>
+        <v>1986</v>
       </c>
       <c r="F27" s="14">
-        <v>1350.24</v>
+        <v>2303.7599999999998</v>
       </c>
       <c r="G27" s="14">
-        <v>7.0603804797353176</v>
+        <v>12.046319272125723</v>
       </c>
       <c r="H27" s="30">
         <v>3627</v>
       </c>
       <c r="I27" s="15">
-        <v>-484.63636363636374</v>
+        <v>337.36363636363626</v>
       </c>
       <c r="J27" s="16">
-        <v>5278</v>
+        <v>3002</v>
       </c>
       <c r="K27" s="13">
-        <v>6122.48</v>
+        <v>3482.3199999999997</v>
       </c>
       <c r="L27" s="14">
-        <v>45.841294907224636</v>
+        <v>26.073430714567706</v>
       </c>
       <c r="M27" s="30">
         <v>2533</v>
       </c>
       <c r="N27" s="15">
-        <v>4126.636363636364</v>
+        <v>1850.6363636363635</v>
       </c>
       <c r="O27" s="16">
-        <v>649</v>
+        <v>608</v>
       </c>
       <c r="P27" s="17">
-        <v>752.83999999999992</v>
+        <v>705.28</v>
       </c>
       <c r="Q27" s="14">
-        <v>33.995238095238093</v>
+        <v>31.847619047619048</v>
       </c>
       <c r="R27" s="16">
         <v>420</v>
       </c>
       <c r="S27" s="15">
-        <v>362.63636363636363</v>
+        <v>321.63636363636363</v>
       </c>
       <c r="T27" s="18">
-        <v>660</v>
+        <v>400</v>
       </c>
       <c r="U27" s="17">
-        <v>765.59999999999991</v>
+        <v>463.99999999999994</v>
       </c>
       <c r="V27" s="14">
-        <v>9.5088408644400815</v>
+        <v>5.7629338572364128</v>
       </c>
       <c r="W27" s="16">
         <v>1526.9999999999998</v>
       </c>
       <c r="X27" s="15">
-        <v>-381.13636363636328</v>
+        <v>-641.13636363636328</v>
       </c>
       <c r="Y27" s="18">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="Z27" s="17">
-        <v>575.36</v>
+        <v>620.59999999999991</v>
       </c>
       <c r="AA27" s="14">
-        <v>42.03389830508474</v>
+        <v>36.067415730337075</v>
       </c>
       <c r="AB27" s="16">
-        <v>259.60000000000002</v>
+        <v>326.33333333333337</v>
       </c>
       <c r="AC27" s="15">
-        <v>319</v>
+        <v>312.5</v>
       </c>
       <c r="AD27" s="19">
-        <v>8247</v>
+        <v>6531</v>
       </c>
       <c r="AE27" s="20">
-        <v>9566.5199999999986</v>
+        <v>7575.9599999999991</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3927,85 +3929,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>1060</v>
+        <v>1126</v>
       </c>
       <c r="F28" s="14">
-        <v>1229.5999999999999</v>
+        <v>1306.1599999999999</v>
       </c>
       <c r="G28" s="14">
-        <v>6.2136957100985875</v>
+        <v>6.6005861977085001</v>
       </c>
       <c r="H28" s="30">
         <v>3753</v>
       </c>
       <c r="I28" s="15">
-        <v>-645.90909090909099</v>
+        <v>-579.90909090909099</v>
       </c>
       <c r="J28" s="16">
-        <v>1124</v>
+        <v>2299</v>
       </c>
       <c r="K28" s="13">
-        <v>1303.8399999999999</v>
+        <v>2666.8399999999997</v>
       </c>
       <c r="L28" s="14">
-        <v>7.4102487264009591</v>
+        <v>15.156727599640394</v>
       </c>
       <c r="M28" s="30">
         <v>3337</v>
       </c>
       <c r="N28" s="15">
-        <v>-392.81818181818198</v>
+        <v>782.18181818181802</v>
       </c>
       <c r="O28" s="16">
-        <v>656</v>
+        <v>594</v>
       </c>
       <c r="P28" s="17">
-        <v>760.95999999999992</v>
+        <v>689.04</v>
       </c>
       <c r="Q28" s="14">
-        <v>27.333333333333332</v>
+        <v>24.75</v>
       </c>
       <c r="R28" s="16">
         <v>528</v>
       </c>
       <c r="S28" s="15">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="T28" s="18">
-        <v>334</v>
+        <v>102</v>
       </c>
       <c r="U28" s="17">
-        <v>387.44</v>
+        <v>118.32</v>
       </c>
       <c r="V28" s="14">
-        <v>5.66538164996145</v>
+        <v>1.7301464919043947</v>
       </c>
       <c r="W28" s="16">
         <v>1297</v>
       </c>
       <c r="X28" s="15">
-        <v>-550.31818181818176</v>
+        <v>-782.31818181818176</v>
       </c>
       <c r="Y28" s="18">
-        <v>455</v>
+        <v>491</v>
       </c>
       <c r="Z28" s="17">
-        <v>527.79999999999995</v>
+        <v>569.55999999999995</v>
       </c>
       <c r="AA28" s="14">
-        <v>25.852272727272727</v>
+        <v>22.661538461538459</v>
       </c>
       <c r="AB28" s="16">
-        <v>387.20000000000005</v>
+        <v>476.66666666666669</v>
       </c>
       <c r="AC28" s="15">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="AD28" s="19">
-        <v>3629</v>
+        <v>4612</v>
       </c>
       <c r="AE28" s="20">
-        <v>4209.6399999999994</v>
+        <v>5349.92</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4040,85 +4042,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>890</v>
+        <v>1669</v>
       </c>
       <c r="F29" s="14">
-        <v>1032.3999999999999</v>
+        <v>1936.04</v>
       </c>
       <c r="G29" s="14">
-        <v>5.1458607095926405</v>
+        <v>9.6499342969776603</v>
       </c>
       <c r="H29" s="30">
         <v>3805.0000000000005</v>
       </c>
       <c r="I29" s="15">
-        <v>-839.54545454545473</v>
+        <v>-60.545454545454731</v>
       </c>
       <c r="J29" s="16">
-        <v>5730</v>
+        <v>3282</v>
       </c>
       <c r="K29" s="13">
-        <v>6646.7999999999993</v>
+        <v>3807.12</v>
       </c>
       <c r="L29" s="14">
-        <v>46.430939226519335</v>
+        <v>26.594475138121549</v>
       </c>
       <c r="M29" s="30">
         <v>2715</v>
       </c>
       <c r="N29" s="15">
-        <v>4495.909090909091</v>
+        <v>2047.909090909091</v>
       </c>
       <c r="O29" s="16">
-        <v>652</v>
+        <v>571</v>
       </c>
       <c r="P29" s="17">
-        <v>756.31999999999994</v>
+        <v>662.3599999999999</v>
       </c>
       <c r="Q29" s="14">
-        <v>29.945720250521919</v>
+        <v>26.225469728601251</v>
       </c>
       <c r="R29" s="16">
         <v>479</v>
       </c>
       <c r="S29" s="15">
-        <v>325.40909090909088</v>
+        <v>244.40909090909088</v>
       </c>
       <c r="T29" s="18">
-        <v>290</v>
+        <v>53</v>
       </c>
       <c r="U29" s="17">
-        <v>336.4</v>
+        <v>61.48</v>
       </c>
       <c r="V29" s="14">
-        <v>5.5915863277826467</v>
+        <v>1.0219106047326905</v>
       </c>
       <c r="W29" s="16">
         <v>1141</v>
       </c>
       <c r="X29" s="15">
-        <v>-487.9545454545455</v>
+        <v>-724.9545454545455</v>
       </c>
       <c r="Y29" s="18">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="Z29" s="17">
-        <v>526.64</v>
+        <v>551</v>
       </c>
       <c r="AA29" s="14">
-        <v>19.401709401709404</v>
+        <v>18.627450980392158</v>
       </c>
       <c r="AB29" s="16">
-        <v>514.79999999999995</v>
+        <v>561</v>
       </c>
       <c r="AC29" s="15">
-        <v>103</v>
+        <v>92.5</v>
       </c>
       <c r="AD29" s="19">
-        <v>8016</v>
+        <v>6050</v>
       </c>
       <c r="AE29" s="20">
-        <v>9298.56</v>
+        <v>7017.9999999999991</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4153,85 +4155,85 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>701</v>
+        <v>646</v>
       </c>
       <c r="F30" s="14">
-        <v>2579.6800000000003</v>
+        <v>2377.2800000000002</v>
       </c>
       <c r="G30" s="14">
-        <v>7.7692695214105791</v>
+        <v>7.1596977329974809</v>
       </c>
       <c r="H30" s="30">
         <v>1985</v>
       </c>
       <c r="I30" s="15">
-        <v>-201.27272727272737</v>
+        <v>-256.27272727272737</v>
       </c>
       <c r="J30" s="16">
-        <v>1670</v>
+        <v>1141</v>
       </c>
       <c r="K30" s="13">
-        <v>6145.6</v>
+        <v>4198.88</v>
       </c>
       <c r="L30" s="14">
-        <v>16.527215474583894</v>
+        <v>11.291947818263608</v>
       </c>
       <c r="M30" s="30">
         <v>2223</v>
       </c>
       <c r="N30" s="15">
-        <v>659.5454545454545</v>
+        <v>130.5454545454545</v>
       </c>
       <c r="O30" s="16">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="P30" s="17">
-        <v>294.40000000000003</v>
+        <v>276</v>
       </c>
       <c r="Q30" s="14">
-        <v>21.463414634146343</v>
+        <v>20.121951219512198</v>
       </c>
       <c r="R30" s="16">
         <v>82</v>
       </c>
       <c r="S30" s="15">
-        <v>24.090909090909093</v>
+        <v>19.090909090909093</v>
       </c>
       <c r="T30" s="18">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="U30" s="17">
-        <v>938.40000000000009</v>
+        <v>908.96</v>
       </c>
       <c r="V30" s="14">
-        <v>8.0372492836676219</v>
+        <v>7.7851002865329511</v>
       </c>
       <c r="W30" s="16">
         <v>698</v>
       </c>
       <c r="X30" s="15">
-        <v>-220.90909090909088</v>
+        <v>-228.90909090909088</v>
       </c>
       <c r="Y30" s="18">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="Z30" s="17">
-        <v>364.32</v>
+        <v>290.72000000000003</v>
       </c>
       <c r="AA30" s="14">
-        <v>165</v>
+        <v>16.928571428571427</v>
       </c>
       <c r="AB30" s="16">
-        <v>13.2</v>
+        <v>102.66666666666667</v>
       </c>
       <c r="AC30" s="15">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="AD30" s="19">
-        <v>2805</v>
+        <v>2188</v>
       </c>
       <c r="AE30" s="20">
-        <v>10322.4</v>
+        <v>8051.84</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4266,85 +4268,85 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F31" s="14">
-        <v>430.56</v>
+        <v>404.8</v>
       </c>
       <c r="G31" s="14">
-        <v>2.1467889908256881</v>
+        <v>2.0183486238532109</v>
       </c>
       <c r="H31" s="30">
         <v>1199</v>
       </c>
       <c r="I31" s="15">
-        <v>-428</v>
+        <v>-435</v>
       </c>
       <c r="J31" s="16">
-        <v>1150</v>
+        <v>904</v>
       </c>
       <c r="K31" s="13">
-        <v>4232</v>
+        <v>3326.7200000000003</v>
       </c>
       <c r="L31" s="14">
-        <v>17.281420765027327</v>
+        <v>13.584699453551915</v>
       </c>
       <c r="M31" s="30">
         <v>1463.9999999999998</v>
       </c>
       <c r="N31" s="15">
-        <v>484.54545454545473</v>
+        <v>238.54545454545473</v>
       </c>
       <c r="O31" s="16">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P31" s="17">
-        <v>121.44000000000001</v>
+        <v>117.76</v>
       </c>
       <c r="Q31" s="14">
-        <v>18.150000000000002</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="R31" s="16">
         <v>40</v>
       </c>
       <c r="S31" s="15">
-        <v>5.7272727272727266</v>
+        <v>4.7272727272727266</v>
       </c>
       <c r="T31" s="18">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="U31" s="17">
-        <v>522.56000000000006</v>
+        <v>500.48</v>
       </c>
       <c r="V31" s="14">
-        <v>11.878326996197718</v>
+        <v>11.376425855513308</v>
       </c>
       <c r="W31" s="16">
         <v>263</v>
       </c>
       <c r="X31" s="15">
-        <v>-37.318181818181813</v>
+        <v>-43.318181818181813</v>
       </c>
       <c r="Y31" s="18">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="Z31" s="17">
-        <v>250.24</v>
+        <v>228.16</v>
       </c>
       <c r="AA31" s="14">
-        <v>56.666666666666671</v>
+        <v>31</v>
       </c>
       <c r="AB31" s="16">
-        <v>26.4</v>
+        <v>44</v>
       </c>
       <c r="AC31" s="15">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AD31" s="19">
-        <v>1510</v>
+        <v>1244</v>
       </c>
       <c r="AE31" s="20">
-        <v>5556.8</v>
+        <v>4577.92</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4379,85 +4381,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>3098</v>
+        <v>1219</v>
       </c>
       <c r="F32" s="14">
-        <v>12856.7</v>
+        <v>5058.8500000000004</v>
       </c>
       <c r="G32" s="14">
-        <v>14.1843912591051</v>
+        <v>5.581269510926119</v>
       </c>
       <c r="H32" s="30">
         <v>4805</v>
       </c>
       <c r="I32" s="15">
-        <v>913.90909090909099</v>
+        <v>-965.09090909090901</v>
       </c>
       <c r="J32" s="16">
-        <v>1043</v>
+        <v>1668</v>
       </c>
       <c r="K32" s="13">
-        <v>4328.4500000000007</v>
+        <v>6922.2000000000007</v>
       </c>
       <c r="L32" s="14">
-        <v>6.0848581278175544</v>
+        <v>9.7311058074781212</v>
       </c>
       <c r="M32" s="30">
         <v>3771.0000000000005</v>
       </c>
       <c r="N32" s="15">
-        <v>-671.09090909090946</v>
+        <v>-46.090909090909463</v>
       </c>
       <c r="O32" s="16">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="P32" s="17">
-        <v>871.50000000000011</v>
+        <v>834.15000000000009</v>
       </c>
       <c r="Q32" s="14">
-        <v>16.441281138790035</v>
+        <v>15.736654804270461</v>
       </c>
       <c r="R32" s="16">
         <v>281</v>
       </c>
       <c r="S32" s="15">
-        <v>18.409090909090907</v>
+        <v>9.4090909090909065</v>
       </c>
       <c r="T32" s="18">
-        <v>427</v>
+        <v>348</v>
       </c>
       <c r="U32" s="17">
-        <v>1772.0500000000002</v>
+        <v>1444.2</v>
       </c>
       <c r="V32" s="14">
-        <v>5.1305297651556518</v>
+        <v>4.181321682140906</v>
       </c>
       <c r="W32" s="16">
         <v>1831</v>
       </c>
       <c r="X32" s="15">
-        <v>-821.40909090909099</v>
+        <v>-900.40909090909099</v>
       </c>
       <c r="Y32" s="18">
-        <v>155</v>
+        <v>316</v>
       </c>
       <c r="Z32" s="17">
-        <v>643.25</v>
+        <v>1311.4</v>
       </c>
       <c r="AA32" s="14">
-        <v>29.807692307692307</v>
+        <v>46.243902439024396</v>
       </c>
       <c r="AB32" s="16">
-        <v>114.4</v>
+        <v>150.33333333333331</v>
       </c>
       <c r="AC32" s="15">
-        <v>77</v>
+        <v>213.5</v>
       </c>
       <c r="AD32" s="19">
-        <v>4933</v>
+        <v>3752</v>
       </c>
       <c r="AE32" s="20">
-        <v>20471.95</v>
+        <v>15570.800000000001</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4492,85 +4494,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>1675</v>
+        <v>1277</v>
       </c>
       <c r="F33" s="14">
-        <v>6951.2500000000009</v>
+        <v>5299.55</v>
       </c>
       <c r="G33" s="14">
-        <v>4.182746878547106</v>
+        <v>3.1888762769580024</v>
       </c>
       <c r="H33" s="30">
         <v>8810</v>
       </c>
       <c r="I33" s="15">
-        <v>-2329.5454545454545</v>
+        <v>-2727.5454545454545</v>
       </c>
       <c r="J33" s="16">
-        <v>4267</v>
+        <v>2318</v>
       </c>
       <c r="K33" s="13">
-        <v>17708.050000000003</v>
+        <v>9619.7000000000007</v>
       </c>
       <c r="L33" s="14">
-        <v>18.504632367435441</v>
+        <v>10.05243445692884</v>
       </c>
       <c r="M33" s="30">
         <v>5073</v>
       </c>
       <c r="N33" s="15">
-        <v>1961.090909090909</v>
+        <v>12.090909090909008</v>
       </c>
       <c r="O33" s="16">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="P33" s="17">
-        <v>1103.9000000000001</v>
+        <v>971.10000000000014</v>
       </c>
       <c r="Q33" s="14">
-        <v>16.300835654596103</v>
+        <v>14.339832869080782</v>
       </c>
       <c r="R33" s="16">
         <v>359</v>
       </c>
       <c r="S33" s="15">
-        <v>21.227272727272748</v>
+        <v>-10.772727272727252</v>
       </c>
       <c r="T33" s="18">
-        <v>772</v>
+        <v>674</v>
       </c>
       <c r="U33" s="17">
-        <v>3203.8</v>
+        <v>2797.1000000000004</v>
       </c>
       <c r="V33" s="14">
-        <v>6.6291959406713508</v>
+        <v>5.7876658860265415</v>
       </c>
       <c r="W33" s="16">
         <v>2562</v>
       </c>
       <c r="X33" s="15">
-        <v>-974.81818181818176</v>
+        <v>-1072.8181818181818</v>
       </c>
       <c r="Y33" s="18">
-        <v>252</v>
+        <v>196</v>
       </c>
       <c r="Z33" s="17">
-        <v>1045.8000000000002</v>
+        <v>813.40000000000009</v>
       </c>
       <c r="AA33" s="14">
-        <v>96.92307692307692</v>
+        <v>14.341463414634148</v>
       </c>
       <c r="AB33" s="16">
-        <v>57.2</v>
+        <v>300.66666666666663</v>
       </c>
       <c r="AC33" s="15">
-        <v>213</v>
+        <v>-8.9999999999999716</v>
       </c>
       <c r="AD33" s="19">
-        <v>7232</v>
+        <v>4699</v>
       </c>
       <c r="AE33" s="20">
-        <v>30012.800000000003</v>
+        <v>19500.850000000002</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4620,10 +4622,10 @@
         <v>-403.72727272727263</v>
       </c>
       <c r="J34" s="16">
-        <v>618</v>
+        <v>552</v>
       </c>
       <c r="K34" s="13">
-        <v>2564.7000000000003</v>
+        <v>2290.8000000000002</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4632,9 +4634,11 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>618</v>
-      </c>
-      <c r="O34" s="16"/>
+        <v>552</v>
+      </c>
+      <c r="O34" s="16">
+        <v>32</v>
+      </c>
       <c r="P34" s="17">
         <v>0</v>
       </c>
@@ -4648,19 +4652,19 @@
         <v>56</v>
       </c>
       <c r="T34" s="18">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U34" s="17">
-        <v>83</v>
+        <v>41.5</v>
       </c>
       <c r="V34" s="14">
-        <v>4.6808510638297873</v>
+        <v>2.3404255319148937</v>
       </c>
       <c r="W34" s="16">
         <v>94</v>
       </c>
       <c r="X34" s="15">
-        <v>-44.090909090909093</v>
+        <v>-54.090909090909093</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4678,10 +4682,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>939</v>
+        <v>895</v>
       </c>
       <c r="AE34" s="20">
-        <v>3896.8500000000004</v>
+        <v>3714.2500000000005</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4716,85 +4720,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>2451</v>
+        <v>1121</v>
       </c>
       <c r="F35" s="14">
-        <v>3995.1299999999997</v>
+        <v>1827.2299999999998</v>
       </c>
       <c r="G35" s="14">
-        <v>5.0422666916027685</v>
+        <v>2.3061529829811112</v>
       </c>
       <c r="H35" s="30">
         <v>10694</v>
       </c>
       <c r="I35" s="15">
-        <v>-2409.909090909091</v>
+        <v>-3739.909090909091</v>
       </c>
       <c r="J35" s="16">
-        <v>1309</v>
+        <v>917</v>
       </c>
       <c r="K35" s="13">
-        <v>2133.67</v>
+        <v>1494.7099999999998</v>
       </c>
       <c r="L35" s="14">
-        <v>8.940701645451723</v>
+        <v>6.2632722756907793</v>
       </c>
       <c r="M35" s="30">
         <v>3221</v>
       </c>
       <c r="N35" s="15">
-        <v>-155.09090909090901</v>
+        <v>-547.09090909090901</v>
       </c>
       <c r="O35" s="16">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="P35" s="17">
-        <v>1129.5899999999999</v>
+        <v>1123.07</v>
       </c>
       <c r="Q35" s="14">
-        <v>15.964397905759164</v>
+        <v>15.872251308900525</v>
       </c>
       <c r="R35" s="16">
         <v>955</v>
       </c>
       <c r="S35" s="15">
-        <v>41.863636363636374</v>
+        <v>37.863636363636374</v>
       </c>
       <c r="T35" s="18">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="U35" s="17">
-        <v>725.34999999999991</v>
+        <v>671.56</v>
       </c>
       <c r="V35" s="14">
-        <v>7.1879588839941269</v>
+        <v>6.654919236417034</v>
       </c>
       <c r="W35" s="16">
         <v>1362</v>
       </c>
       <c r="X35" s="15">
-        <v>-483.63636363636363</v>
+        <v>-516.63636363636363</v>
       </c>
       <c r="Y35" s="18">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="Z35" s="17">
-        <v>717.19999999999993</v>
+        <v>704.16</v>
       </c>
       <c r="AA35" s="14">
-        <v>36.065573770491802</v>
+        <v>33.230769230769234</v>
       </c>
       <c r="AB35" s="16">
-        <v>268.39999999999998</v>
+        <v>286</v>
       </c>
       <c r="AC35" s="15">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="AD35" s="19">
-        <v>5338</v>
+        <v>3571</v>
       </c>
       <c r="AE35" s="20">
-        <v>8700.9399999999987</v>
+        <v>5820.73</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4829,85 +4833,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>1196</v>
+        <v>682</v>
       </c>
       <c r="F36" s="14">
-        <v>1949.4799999999998</v>
+        <v>1111.6599999999999</v>
       </c>
       <c r="G36" s="14">
-        <v>1.5998054356417584</v>
+        <v>0.91226363470541738</v>
       </c>
       <c r="H36" s="30">
         <v>16447</v>
       </c>
       <c r="I36" s="15">
-        <v>-6279.909090909091</v>
+        <v>-6793.909090909091</v>
       </c>
       <c r="J36" s="16">
-        <v>5663</v>
+        <v>3614</v>
       </c>
       <c r="K36" s="13">
-        <v>9230.6899999999987</v>
+        <v>5890.82</v>
       </c>
       <c r="L36" s="14">
-        <v>25.250506688285366</v>
+        <v>16.114308877178757</v>
       </c>
       <c r="M36" s="30">
         <v>4934</v>
       </c>
       <c r="N36" s="15">
-        <v>3420.272727272727</v>
+        <v>1371.272727272727</v>
       </c>
       <c r="O36" s="16">
-        <v>789</v>
+        <v>741</v>
       </c>
       <c r="P36" s="17">
-        <v>1286.07</v>
+        <v>1207.83</v>
       </c>
       <c r="Q36" s="14">
-        <v>8.6660009985022466</v>
+        <v>8.1387918122815783</v>
       </c>
       <c r="R36" s="16">
         <v>2003</v>
       </c>
       <c r="S36" s="15">
-        <v>-576.68181818181824</v>
+        <v>-624.68181818181824</v>
       </c>
       <c r="T36" s="18">
-        <v>871</v>
+        <v>795</v>
       </c>
       <c r="U36" s="17">
-        <v>1419.73</v>
+        <v>1295.8499999999999</v>
       </c>
       <c r="V36" s="14">
-        <v>6.5221238938053103</v>
+        <v>5.9530292716133433</v>
       </c>
       <c r="W36" s="16">
         <v>2938</v>
       </c>
       <c r="X36" s="15">
-        <v>-1132.181818181818</v>
+        <v>-1208.181818181818</v>
       </c>
       <c r="Y36" s="18">
-        <v>571</v>
+        <v>533</v>
       </c>
       <c r="Z36" s="17">
-        <v>930.7299999999999</v>
+        <v>868.79</v>
       </c>
       <c r="AA36" s="14">
-        <v>21.793893129770993</v>
+        <v>16.569948186528499</v>
       </c>
       <c r="AB36" s="16">
-        <v>576.4</v>
+        <v>707.66666666666663</v>
       </c>
       <c r="AC36" s="15">
-        <v>178</v>
+        <v>50.500000000000057</v>
       </c>
       <c r="AD36" s="19">
-        <v>9090</v>
+        <v>6365</v>
       </c>
       <c r="AE36" s="20">
-        <v>14816.699999999999</v>
+        <v>10374.949999999999</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4942,85 +4946,85 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>1750</v>
+        <v>2017</v>
       </c>
       <c r="F37" s="14">
-        <v>2852.5</v>
+        <v>3287.7099999999996</v>
       </c>
       <c r="G37" s="14">
-        <v>6.4608155730827317</v>
+        <v>7.4465514348044968</v>
       </c>
       <c r="H37" s="30">
         <v>5959</v>
       </c>
       <c r="I37" s="15">
-        <v>-958.63636363636397</v>
+        <v>-691.63636363636397</v>
       </c>
       <c r="J37" s="16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K37" s="13">
-        <v>0</v>
+        <v>1630</v>
       </c>
       <c r="L37" s="14">
-        <v>0</v>
+        <v>9.0834021469859625</v>
       </c>
       <c r="M37" s="30">
         <v>2422</v>
       </c>
       <c r="N37" s="15">
-        <v>-1100.909090909091</v>
+        <v>-100.90909090909099</v>
       </c>
       <c r="O37" s="16">
-        <v>374</v>
+        <v>346</v>
       </c>
       <c r="P37" s="17">
-        <v>609.62</v>
+        <v>563.98</v>
       </c>
       <c r="Q37" s="14">
-        <v>8.0904621435594883</v>
+        <v>7.4847590953785641</v>
       </c>
       <c r="R37" s="16">
         <v>1017</v>
       </c>
       <c r="S37" s="15">
-        <v>-319.40909090909088</v>
+        <v>-347.40909090909088</v>
       </c>
       <c r="T37" s="18">
-        <v>841</v>
+        <v>757</v>
       </c>
       <c r="U37" s="17">
-        <v>1370.83</v>
+        <v>1233.9099999999999</v>
       </c>
       <c r="V37" s="14">
-        <v>12.148391332895599</v>
+        <v>10.934996717005909</v>
       </c>
       <c r="W37" s="16">
         <v>1523</v>
       </c>
       <c r="X37" s="15">
-        <v>-197.40909090909099</v>
+        <v>-281.40909090909099</v>
       </c>
       <c r="Y37" s="18">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="Z37" s="17">
-        <v>444.98999999999995</v>
+        <v>376.53</v>
       </c>
       <c r="AA37" s="14">
         <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="AC37" s="15">
-        <v>273</v>
+        <v>-9</v>
       </c>
       <c r="AD37" s="19">
-        <v>3238</v>
+        <v>4351</v>
       </c>
       <c r="AE37" s="20">
-        <v>5277.94</v>
+        <v>7092.1299999999992</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5055,85 +5059,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>1881</v>
+        <v>1903</v>
       </c>
       <c r="F38" s="14">
-        <v>3066.0299999999997</v>
+        <v>3101.89</v>
       </c>
       <c r="G38" s="14">
-        <v>10.071063519104404</v>
+        <v>10.188853735702116</v>
       </c>
       <c r="H38" s="30">
         <v>4109</v>
       </c>
       <c r="I38" s="15">
-        <v>13.272727272727252</v>
+        <v>35.272727272727252</v>
       </c>
       <c r="J38" s="16">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="K38" s="13">
-        <v>74.97999999999999</v>
+        <v>1630</v>
       </c>
       <c r="L38" s="14">
-        <v>0.48513902205177378</v>
+        <v>10.546500479386387</v>
       </c>
       <c r="M38" s="30">
         <v>2086</v>
       </c>
       <c r="N38" s="15">
-        <v>-902.18181818181813</v>
+        <v>51.81818181818187</v>
       </c>
       <c r="O38" s="16">
-        <v>544</v>
+        <v>516</v>
       </c>
       <c r="P38" s="17">
-        <v>886.71999999999991</v>
+        <v>841.07999999999993</v>
       </c>
       <c r="Q38" s="14">
-        <v>15.936085219707058</v>
+        <v>15.11584553928096</v>
       </c>
       <c r="R38" s="16">
         <v>751</v>
       </c>
       <c r="S38" s="15">
-        <v>31.954545454545496</v>
+        <v>3.9545454545454959</v>
       </c>
       <c r="T38" s="18">
-        <v>572</v>
+        <v>486</v>
       </c>
       <c r="U38" s="17">
-        <v>932.3599999999999</v>
+        <v>792.18</v>
       </c>
       <c r="V38" s="14">
-        <v>12.277073170731706</v>
+        <v>10.431219512195121</v>
       </c>
       <c r="W38" s="16">
         <v>1025</v>
       </c>
       <c r="X38" s="15">
-        <v>-126.86363636363637</v>
+        <v>-212.86363636363637</v>
       </c>
       <c r="Y38" s="18">
-        <v>549</v>
+        <v>493</v>
       </c>
       <c r="Z38" s="17">
-        <v>894.86999999999989</v>
+        <v>803.58999999999992</v>
       </c>
       <c r="AA38" s="14">
-        <v>27.727272727272727</v>
+        <v>15.326424870466322</v>
       </c>
       <c r="AB38" s="16">
-        <v>435.6</v>
+        <v>707.66666666666663</v>
       </c>
       <c r="AC38" s="15">
-        <v>252</v>
+        <v>10.500000000000057</v>
       </c>
       <c r="AD38" s="19">
-        <v>3592</v>
+        <v>4398</v>
       </c>
       <c r="AE38" s="20">
-        <v>5854.96</v>
+        <v>7168.74</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5168,85 +5172,85 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>715</v>
+        <v>679</v>
       </c>
       <c r="F39" s="14">
-        <v>1165.4499999999998</v>
+        <v>1106.77</v>
       </c>
       <c r="G39" s="14">
-        <v>84.117647058823536</v>
+        <v>79.882352941176464</v>
       </c>
       <c r="H39" s="30">
         <v>187</v>
       </c>
       <c r="I39" s="15">
-        <v>630</v>
+        <v>594</v>
       </c>
       <c r="J39" s="16">
-        <v>7082</v>
+        <v>6550</v>
       </c>
       <c r="K39" s="13">
-        <v>11543.66</v>
+        <v>10676.5</v>
       </c>
       <c r="L39" s="14">
-        <v>190.93627450980395</v>
+        <v>176.59313725490199</v>
       </c>
       <c r="M39" s="30">
         <v>815.99999999999989</v>
       </c>
       <c r="N39" s="15">
-        <v>6711.090909090909</v>
+        <v>6179.090909090909</v>
       </c>
       <c r="O39" s="16">
-        <v>558</v>
+        <v>536</v>
       </c>
       <c r="P39" s="17">
-        <v>909.54</v>
+        <v>873.68</v>
       </c>
       <c r="Q39" s="14">
-        <v>1116</v>
+        <v>1072</v>
       </c>
       <c r="R39" s="16">
         <v>11</v>
       </c>
       <c r="S39" s="15">
-        <v>550.5</v>
+        <v>528.5</v>
       </c>
       <c r="T39" s="18">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="U39" s="17">
-        <v>200.48999999999998</v>
+        <v>174.41</v>
       </c>
       <c r="V39" s="14">
-        <v>5.029739776951673</v>
+        <v>4.3754646840148705</v>
       </c>
       <c r="W39" s="16">
         <v>538</v>
       </c>
       <c r="X39" s="15">
-        <v>-243.81818181818181</v>
+        <v>-259.81818181818181</v>
       </c>
       <c r="Y39" s="18">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="Z39" s="17">
-        <v>831.3</v>
+        <v>819.89</v>
       </c>
       <c r="AA39" s="14">
-        <v>170</v>
+        <v>81.567567567567551</v>
       </c>
       <c r="AB39" s="16">
-        <v>66</v>
+        <v>135.66666666666669</v>
       </c>
       <c r="AC39" s="15">
-        <v>465</v>
+        <v>410.5</v>
       </c>
       <c r="AD39" s="19">
-        <v>8988</v>
+        <v>8375</v>
       </c>
       <c r="AE39" s="20">
-        <v>14650.439999999999</v>
+        <v>13651.25</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5281,85 +5285,85 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>621</v>
+        <v>561</v>
       </c>
       <c r="F40" s="14">
-        <v>1012.2299999999999</v>
+        <v>914.43</v>
       </c>
       <c r="G40" s="14">
-        <v>73.848648648648663</v>
+        <v>66.713513513513519</v>
       </c>
       <c r="H40" s="30">
         <v>185</v>
       </c>
       <c r="I40" s="15">
-        <v>536.90909090909088</v>
+        <v>476.90909090909093</v>
       </c>
       <c r="J40" s="16">
-        <v>7076</v>
+        <v>6674</v>
       </c>
       <c r="K40" s="13">
-        <v>11533.88</v>
+        <v>10878.619999999999</v>
       </c>
       <c r="L40" s="14">
-        <v>218.0280112044818</v>
+        <v>205.64145658263305</v>
       </c>
       <c r="M40" s="30">
         <v>714</v>
       </c>
       <c r="N40" s="15">
-        <v>6751.454545454546</v>
+        <v>6349.454545454546</v>
       </c>
       <c r="O40" s="16">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="P40" s="17">
-        <v>842.70999999999992</v>
+        <v>810.1099999999999</v>
       </c>
       <c r="Q40" s="14">
-        <v>1034</v>
+        <v>994</v>
       </c>
       <c r="R40" s="16">
         <v>11</v>
       </c>
       <c r="S40" s="15">
-        <v>509.5</v>
+        <v>489.5</v>
       </c>
       <c r="T40" s="18">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="U40" s="17">
-        <v>104.32</v>
+        <v>92.91</v>
       </c>
       <c r="V40" s="14">
-        <v>2.5008880994671405</v>
+        <v>2.2273534635879217</v>
       </c>
       <c r="W40" s="16">
         <v>563</v>
       </c>
       <c r="X40" s="15">
-        <v>-319.86363636363637</v>
+        <v>-326.86363636363637</v>
       </c>
       <c r="Y40" s="18">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="Z40" s="17">
-        <v>845.96999999999991</v>
+        <v>819.89</v>
       </c>
       <c r="AA40" s="14">
-        <v>173</v>
+        <v>70.186046511627893</v>
       </c>
       <c r="AB40" s="16">
-        <v>66</v>
+        <v>157.66666666666669</v>
       </c>
       <c r="AC40" s="15">
-        <v>474</v>
+        <v>395.5</v>
       </c>
       <c r="AD40" s="19">
-        <v>8797</v>
+        <v>8292</v>
       </c>
       <c r="AE40" s="20">
-        <v>14339.109999999999</v>
+        <v>13515.96</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5394,34 +5398,34 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="F41" s="14">
-        <v>854.85</v>
+        <v>461.25</v>
       </c>
       <c r="G41" s="14">
-        <v>2.278688524590164</v>
+        <v>1.2295081967213115</v>
       </c>
       <c r="H41" s="30">
         <v>1342</v>
       </c>
       <c r="I41" s="15">
-        <v>-471</v>
+        <v>-535</v>
       </c>
       <c r="J41" s="16">
-        <v>920</v>
+        <v>662</v>
       </c>
       <c r="K41" s="13">
-        <v>5658</v>
+        <v>4071.3</v>
       </c>
       <c r="L41" s="14">
-        <v>25.555555555555557</v>
+        <v>18.388888888888889</v>
       </c>
       <c r="M41" s="30">
         <v>792</v>
       </c>
       <c r="N41" s="15">
-        <v>560</v>
+        <v>302</v>
       </c>
       <c r="O41" s="16">
         <v>70</v>
@@ -5439,40 +5443,40 @@
         <v>13.409090909090907</v>
       </c>
       <c r="T41" s="18">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="U41" s="17">
-        <v>719.55000000000007</v>
+        <v>707.25</v>
       </c>
       <c r="V41" s="14">
-        <v>6.919354838709677</v>
+        <v>6.801075268817204</v>
       </c>
       <c r="W41" s="16">
         <v>372</v>
       </c>
       <c r="X41" s="15">
-        <v>-136.63636363636365</v>
+        <v>-138.63636363636365</v>
       </c>
       <c r="Y41" s="18">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="Z41" s="17">
-        <v>596.55000000000007</v>
+        <v>528.9</v>
       </c>
       <c r="AA41" s="14">
         <v>0</v>
       </c>
       <c r="AB41" s="16">
-        <v>0</v>
+        <v>62.333333333333336</v>
       </c>
       <c r="AC41" s="15">
-        <v>97</v>
+        <v>43.5</v>
       </c>
       <c r="AD41" s="19">
-        <v>1343</v>
+        <v>1008</v>
       </c>
       <c r="AE41" s="20">
-        <v>8259.4500000000007</v>
+        <v>6199.2000000000007</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5507,34 +5511,34 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="F42" s="14">
-        <v>861</v>
+        <v>608.85</v>
       </c>
       <c r="G42" s="14">
-        <v>2.1813031161473084</v>
+        <v>1.5424929178470255</v>
       </c>
       <c r="H42" s="30">
         <v>1412</v>
       </c>
       <c r="I42" s="15">
-        <v>-501.81818181818187</v>
+        <v>-542.81818181818187</v>
       </c>
       <c r="J42" s="16">
-        <v>147</v>
+        <v>703</v>
       </c>
       <c r="K42" s="13">
-        <v>904.05000000000007</v>
+        <v>4323.45</v>
       </c>
       <c r="L42" s="14">
-        <v>3.4924406047516197</v>
+        <v>16.70194384449244</v>
       </c>
       <c r="M42" s="30">
         <v>926</v>
       </c>
       <c r="N42" s="15">
-        <v>-273.90909090909093</v>
+        <v>282.09090909090907</v>
       </c>
       <c r="O42" s="16">
         <v>57</v>
@@ -5552,40 +5556,40 @@
         <v>1.7727272727272734</v>
       </c>
       <c r="T42" s="18">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="U42" s="17">
-        <v>910.2</v>
+        <v>879.45</v>
       </c>
       <c r="V42" s="14">
-        <v>6.1433962264150948</v>
+        <v>5.9358490566037743</v>
       </c>
       <c r="W42" s="16">
         <v>530</v>
       </c>
       <c r="X42" s="15">
-        <v>-213.36363636363637</v>
+        <v>-218.36363636363637</v>
       </c>
       <c r="Y42" s="18">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="Z42" s="17">
-        <v>719.55000000000007</v>
+        <v>682.65000000000009</v>
       </c>
       <c r="AA42" s="14">
-        <v>21.666666666666664</v>
+        <v>17.076923076923077</v>
       </c>
       <c r="AB42" s="16">
-        <v>118.80000000000001</v>
+        <v>143</v>
       </c>
       <c r="AC42" s="15">
-        <v>36</v>
+        <v>13.5</v>
       </c>
       <c r="AD42" s="19">
-        <v>609</v>
+        <v>1113</v>
       </c>
       <c r="AE42" s="20">
-        <v>3745.3500000000004</v>
+        <v>6844.9500000000007</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5620,85 +5624,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2201</v>
+        <v>2017</v>
       </c>
       <c r="F43" s="14">
-        <v>2553.16</v>
+        <v>2339.7199999999998</v>
       </c>
       <c r="G43" s="14">
-        <v>6.5603576751117734</v>
+        <v>6.0119225037257822</v>
       </c>
       <c r="H43" s="30">
         <v>7381</v>
       </c>
       <c r="I43" s="15">
-        <v>-1154</v>
+        <v>-1338</v>
       </c>
       <c r="J43" s="16">
-        <v>4568</v>
+        <v>3540</v>
       </c>
       <c r="K43" s="13">
-        <v>5298.8799999999992</v>
+        <v>4106.3999999999996</v>
       </c>
       <c r="L43" s="14">
-        <v>36.610564663023681</v>
+        <v>28.371584699453553</v>
       </c>
       <c r="M43" s="30">
         <v>2745</v>
       </c>
       <c r="N43" s="15">
-        <v>3320.272727272727</v>
+        <v>2292.272727272727</v>
       </c>
       <c r="O43" s="16">
-        <v>506</v>
+        <v>465</v>
       </c>
       <c r="P43" s="17">
-        <v>586.95999999999992</v>
+        <v>539.4</v>
       </c>
       <c r="Q43" s="14">
-        <v>9.7906772207563773</v>
+        <v>8.997361477572559</v>
       </c>
       <c r="R43" s="16">
         <v>1137</v>
       </c>
       <c r="S43" s="15">
-        <v>-269.22727272727275</v>
+        <v>-310.22727272727275</v>
       </c>
       <c r="T43" s="18">
-        <v>1073</v>
+        <v>950</v>
       </c>
       <c r="U43" s="17">
-        <v>1244.6799999999998</v>
+        <v>1102</v>
       </c>
       <c r="V43" s="14">
-        <v>11.376385542168675</v>
+        <v>10.072289156626507</v>
       </c>
       <c r="W43" s="16">
         <v>2075</v>
       </c>
       <c r="X43" s="15">
-        <v>-341.77272727272725</v>
+        <v>-464.77272727272725</v>
       </c>
       <c r="Y43" s="18">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="Z43" s="17">
-        <v>501.11999999999995</v>
+        <v>476.76</v>
       </c>
       <c r="AA43" s="14">
-        <v>12.781065088757398</v>
+        <v>11.311926605504587</v>
       </c>
       <c r="AB43" s="16">
-        <v>743.59999999999991</v>
+        <v>799.33333333333337</v>
       </c>
       <c r="AC43" s="15">
-        <v>-74.999999999999943</v>
+        <v>-134</v>
       </c>
       <c r="AD43" s="19">
-        <v>8780</v>
+        <v>7383</v>
       </c>
       <c r="AE43" s="20">
-        <v>10184.799999999999</v>
+        <v>8564.2799999999988</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5733,85 +5737,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2001</v>
+        <v>1770</v>
       </c>
       <c r="F44" s="14">
-        <v>2321.16</v>
+        <v>2053.1999999999998</v>
       </c>
       <c r="G44" s="14">
-        <v>6.8378378378378377</v>
+        <v>6.0484622553588077</v>
       </c>
       <c r="H44" s="30">
         <v>6438</v>
       </c>
       <c r="I44" s="15">
-        <v>-925.36363636363603</v>
+        <v>-1156.363636363636</v>
       </c>
       <c r="J44" s="16">
-        <v>2714</v>
+        <v>2004</v>
       </c>
       <c r="K44" s="13">
-        <v>3148.24</v>
+        <v>2324.64</v>
       </c>
       <c r="L44" s="14">
-        <v>15.846072186836519</v>
+        <v>11.70063694267516</v>
       </c>
       <c r="M44" s="30">
         <v>3767.9999999999995</v>
       </c>
       <c r="N44" s="15">
-        <v>1001.2727272727275</v>
+        <v>291.27272727272748</v>
       </c>
       <c r="O44" s="16">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="P44" s="17">
-        <v>581.16</v>
+        <v>542.88</v>
       </c>
       <c r="Q44" s="14">
-        <v>14.656914893617023</v>
+        <v>13.691489361702128</v>
       </c>
       <c r="R44" s="16">
         <v>752</v>
       </c>
       <c r="S44" s="15">
-        <v>-11.727272727272748</v>
+        <v>-44.727272727272748</v>
       </c>
       <c r="T44" s="18">
-        <v>1054</v>
+        <v>994</v>
       </c>
       <c r="U44" s="17">
-        <v>1222.6399999999999</v>
+        <v>1153.04</v>
       </c>
       <c r="V44" s="14">
-        <v>12.466666666666667</v>
+        <v>11.756989247311827</v>
       </c>
       <c r="W44" s="16">
         <v>1860</v>
       </c>
       <c r="X44" s="15">
-        <v>-214.18181818181824</v>
+        <v>-274.18181818181824</v>
       </c>
       <c r="Y44" s="18">
-        <v>558</v>
+        <v>522</v>
       </c>
       <c r="Z44" s="17">
-        <v>647.28</v>
+        <v>605.52</v>
       </c>
       <c r="AA44" s="14">
-        <v>22.68292682926829</v>
+        <v>16.659574468085108</v>
       </c>
       <c r="AB44" s="16">
-        <v>541.20000000000005</v>
+        <v>689.33333333333326</v>
       </c>
       <c r="AC44" s="15">
-        <v>189</v>
+        <v>52.000000000000057</v>
       </c>
       <c r="AD44" s="19">
-        <v>6828</v>
+        <v>5758</v>
       </c>
       <c r="AE44" s="20">
-        <v>7920.48</v>
+        <v>6679.28</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5846,85 +5850,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>2214</v>
+        <v>2481</v>
       </c>
       <c r="F45" s="14">
-        <v>2568.2399999999998</v>
+        <v>2877.9599999999996</v>
       </c>
       <c r="G45" s="14">
-        <v>5.7465785747994342</v>
+        <v>6.4395941481831054</v>
       </c>
       <c r="H45" s="30">
         <v>8476</v>
       </c>
       <c r="I45" s="15">
-        <v>-1638.7272727272725</v>
+        <v>-1371.7272727272725</v>
       </c>
       <c r="J45" s="16">
-        <v>3615</v>
+        <v>2525</v>
       </c>
       <c r="K45" s="13">
-        <v>4193.3999999999996</v>
+        <v>2929</v>
       </c>
       <c r="L45" s="14">
-        <v>14.705991124260356</v>
+        <v>10.271819526627219</v>
       </c>
       <c r="M45" s="30">
         <v>5408</v>
       </c>
       <c r="N45" s="15">
-        <v>1156.818181818182</v>
+        <v>66.818181818181984</v>
       </c>
       <c r="O45" s="16">
-        <v>793</v>
+        <v>750</v>
       </c>
       <c r="P45" s="17">
-        <v>919.87999999999988</v>
+        <v>869.99999999999989</v>
       </c>
       <c r="Q45" s="14">
-        <v>15.590705987488828</v>
+        <v>14.745308310991955</v>
       </c>
       <c r="R45" s="16">
         <v>1119</v>
       </c>
       <c r="S45" s="15">
-        <v>30.045454545454504</v>
+        <v>-12.954545454545496</v>
       </c>
       <c r="T45" s="18">
-        <v>1260</v>
+        <v>1175</v>
       </c>
       <c r="U45" s="17">
-        <v>1461.6</v>
+        <v>1363</v>
       </c>
       <c r="V45" s="14">
-        <v>10.956521739130435</v>
+        <v>10.217391304347826</v>
       </c>
       <c r="W45" s="16">
         <v>2530</v>
       </c>
       <c r="X45" s="15">
-        <v>-465</v>
+        <v>-550</v>
       </c>
       <c r="Y45" s="18">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="Z45" s="17">
-        <v>530.12</v>
+        <v>505.76</v>
       </c>
       <c r="AA45" s="14">
-        <v>15.758620689655173</v>
+        <v>12.516746411483252</v>
       </c>
       <c r="AB45" s="16">
-        <v>638</v>
+        <v>766.33333333333337</v>
       </c>
       <c r="AC45" s="15">
-        <v>22</v>
+        <v>-86.5</v>
       </c>
       <c r="AD45" s="19">
-        <v>8339</v>
+        <v>7367</v>
       </c>
       <c r="AE45" s="20">
-        <v>9673.24</v>
+        <v>8545.7199999999993</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5959,85 +5963,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>3490</v>
+        <v>3333</v>
       </c>
       <c r="F46" s="14">
-        <v>4048.3999999999996</v>
+        <v>3866.2799999999997</v>
       </c>
       <c r="G46" s="14">
-        <v>13.517605633802816</v>
+        <v>12.909507042253521</v>
       </c>
       <c r="H46" s="30">
         <v>5680</v>
       </c>
       <c r="I46" s="15">
-        <v>908.18181818181802</v>
+        <v>751.18181818181802</v>
       </c>
       <c r="J46" s="16">
-        <v>1038</v>
+        <v>1784</v>
       </c>
       <c r="K46" s="13">
-        <v>1204.08</v>
+        <v>2069.44</v>
       </c>
       <c r="L46" s="14">
-        <v>5.7521410579345087</v>
+        <v>9.8861460957178835</v>
       </c>
       <c r="M46" s="30">
         <v>3970</v>
       </c>
       <c r="N46" s="15">
-        <v>-766.54545454545473</v>
+        <v>-20.545454545454731</v>
       </c>
       <c r="O46" s="16">
-        <v>650</v>
+        <v>615</v>
       </c>
       <c r="P46" s="17">
-        <v>754</v>
+        <v>713.4</v>
       </c>
       <c r="Q46" s="14">
-        <v>17.396593673965935</v>
+        <v>16.459854014598537</v>
       </c>
       <c r="R46" s="16">
         <v>822.00000000000011</v>
       </c>
       <c r="S46" s="15">
-        <v>89.545454545454504</v>
+        <v>54.545454545454504</v>
       </c>
       <c r="T46" s="18">
-        <v>674</v>
+        <v>630</v>
       </c>
       <c r="U46" s="17">
-        <v>781.83999999999992</v>
+        <v>730.8</v>
       </c>
       <c r="V46" s="14">
-        <v>11.919614147909968</v>
+        <v>11.141479099678456</v>
       </c>
       <c r="W46" s="16">
         <v>1244</v>
       </c>
       <c r="X46" s="15">
-        <v>-174.18181818181824</v>
+        <v>-218.18181818181824</v>
       </c>
       <c r="Y46" s="18">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="Z46" s="17">
-        <v>444.28</v>
+        <v>418.76</v>
       </c>
       <c r="AA46" s="14">
-        <v>23.9375</v>
+        <v>17.467741935483868</v>
       </c>
       <c r="AB46" s="16">
-        <v>352</v>
+        <v>454.66666666666669</v>
       </c>
       <c r="AC46" s="15">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="AD46" s="19">
-        <v>6235</v>
+        <v>6723</v>
       </c>
       <c r="AE46" s="20">
-        <v>7232.5999999999995</v>
+        <v>7798.6799999999994</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6085,21 +6089,23 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" s="13">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L47" s="14">
-        <v>0.6875</v>
+        <v>0</v>
       </c>
       <c r="M47" s="30">
         <v>32</v>
       </c>
       <c r="N47" s="15">
-        <v>-13.545454545454547</v>
-      </c>
-      <c r="O47" s="16"/>
+        <v>-14.545454545454547</v>
+      </c>
+      <c r="O47" s="16">
+        <v>0</v>
+      </c>
       <c r="P47" s="17">
         <v>0</v>
       </c>
@@ -6113,19 +6119,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U47" s="17">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="V47" s="14">
-        <v>13.200000000000001</v>
+        <v>11</v>
       </c>
       <c r="W47" s="16">
         <v>20</v>
       </c>
       <c r="X47" s="15">
-        <v>-1.6363636363636367</v>
+        <v>-3.6363636363636367</v>
       </c>
       <c r="Y47" s="18">
         <v>4</v>
@@ -6143,10 +6149,10 @@
         <v>4</v>
       </c>
       <c r="AD47" s="19">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE47" s="20">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6194,21 +6200,23 @@
         <v>0</v>
       </c>
       <c r="J48" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" s="13">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L48" s="14">
-        <v>2.4444444444444442</v>
+        <v>0</v>
       </c>
       <c r="M48" s="30">
         <v>9</v>
       </c>
       <c r="N48" s="15">
-        <v>-3.0909090909090908</v>
-      </c>
-      <c r="O48" s="16"/>
+        <v>-4.0909090909090908</v>
+      </c>
+      <c r="O48" s="16">
+        <v>0</v>
+      </c>
       <c r="P48" s="17">
         <v>0</v>
       </c>
@@ -6252,10 +6260,10 @@
         <v>0</v>
       </c>
       <c r="AD48" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE48" s="20">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AF48" s="31">
         <v>4.2857142857142856</v>
@@ -6290,85 +6298,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>1062</v>
+        <v>1017</v>
       </c>
       <c r="F49" s="14">
-        <v>1231.9199999999998</v>
+        <v>1179.72</v>
       </c>
       <c r="G49" s="14">
-        <v>18.88763136620857</v>
+        <v>18.08730800323363</v>
       </c>
       <c r="H49" s="30">
         <v>1237</v>
       </c>
       <c r="I49" s="15">
-        <v>499.72727272727275</v>
+        <v>454.72727272727275</v>
       </c>
       <c r="J49" s="16">
-        <v>726</v>
+        <v>347</v>
       </c>
       <c r="K49" s="13">
-        <v>842.16</v>
+        <v>402.52</v>
       </c>
       <c r="L49" s="14">
-        <v>12.953771289537713</v>
+        <v>6.1914030819140304</v>
       </c>
       <c r="M49" s="30">
         <v>1233</v>
       </c>
       <c r="N49" s="15">
-        <v>165.5454545454545</v>
+        <v>-213.4545454545455</v>
       </c>
       <c r="O49" s="16">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P49" s="17">
-        <v>47.559999999999995</v>
+        <v>45.239999999999995</v>
       </c>
       <c r="Q49" s="14">
-        <v>8.0535714285714288</v>
+        <v>7.6607142857142856</v>
       </c>
       <c r="R49" s="16">
         <v>112</v>
       </c>
       <c r="S49" s="15">
-        <v>-35.36363636363636</v>
+        <v>-37.36363636363636</v>
       </c>
       <c r="T49" s="18">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="U49" s="17">
-        <v>257.52</v>
+        <v>234.32</v>
       </c>
       <c r="V49" s="14">
-        <v>21.051724137931036</v>
+        <v>19.155172413793103</v>
       </c>
       <c r="W49" s="16">
         <v>232</v>
       </c>
       <c r="X49" s="15">
-        <v>63.818181818181813</v>
+        <v>43.818181818181813</v>
       </c>
       <c r="Y49" s="18">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z49" s="17">
-        <v>111.35999999999999</v>
+        <v>110.19999999999999</v>
       </c>
       <c r="AA49" s="14">
-        <v>18.46153846153846</v>
+        <v>14.249999999999998</v>
       </c>
       <c r="AB49" s="16">
-        <v>114.4</v>
+        <v>146.66666666666669</v>
       </c>
       <c r="AC49" s="15">
-        <v>18</v>
+        <v>-5.0000000000000142</v>
       </c>
       <c r="AD49" s="19">
-        <v>2147</v>
+        <v>1700</v>
       </c>
       <c r="AE49" s="20">
-        <v>2490.52</v>
+        <v>1971.9999999999998</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6403,85 +6411,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>2326</v>
+        <v>2036</v>
       </c>
       <c r="F50" s="14">
-        <v>2698.16</v>
+        <v>2361.7599999999998</v>
       </c>
       <c r="G50" s="14">
-        <v>9.1248216833095572</v>
+        <v>7.9871611982881596</v>
       </c>
       <c r="H50" s="30">
         <v>5608</v>
       </c>
       <c r="I50" s="15">
-        <v>-223.09090909090901</v>
+        <v>-513.09090909090901</v>
       </c>
       <c r="J50" s="16">
-        <v>919</v>
+        <v>1537</v>
       </c>
       <c r="K50" s="13">
-        <v>1066.04</v>
+        <v>1782.9199999999998</v>
       </c>
       <c r="L50" s="14">
-        <v>5.6538031319910518</v>
+        <v>9.4558165548098447</v>
       </c>
       <c r="M50" s="30">
         <v>3576</v>
       </c>
       <c r="N50" s="15">
-        <v>-706.45454545454527</v>
+        <v>-88.454545454545269</v>
       </c>
       <c r="O50" s="16">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="P50" s="17">
-        <v>448.91999999999996</v>
+        <v>392.08</v>
       </c>
       <c r="Q50" s="14">
-        <v>17.737500000000001</v>
+        <v>15.491666666666667</v>
       </c>
       <c r="R50" s="16">
         <v>480</v>
       </c>
       <c r="S50" s="15">
-        <v>59.727272727272748</v>
+        <v>10.727272727272748</v>
       </c>
       <c r="T50" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U50" s="17">
-        <v>2.3199999999999998</v>
+        <v>0</v>
       </c>
       <c r="V50" s="14">
-        <v>2.5014212620807278E-2</v>
+        <v>0</v>
       </c>
       <c r="W50" s="16">
         <v>1759</v>
       </c>
       <c r="X50" s="15">
-        <v>-1197.3181818181818</v>
+        <v>-1199.3181818181818</v>
       </c>
       <c r="Y50" s="18">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="Z50" s="17">
-        <v>213.44</v>
+        <v>193.72</v>
       </c>
       <c r="AA50" s="14">
-        <v>14.838709677419354</v>
+        <v>10.121212121212121</v>
       </c>
       <c r="AB50" s="16">
-        <v>272.8</v>
+        <v>363</v>
       </c>
       <c r="AC50" s="15">
-        <v>-2</v>
+        <v>-80.5</v>
       </c>
       <c r="AD50" s="19">
-        <v>3818</v>
+        <v>4078</v>
       </c>
       <c r="AE50" s="20">
-        <v>4428.88</v>
+        <v>4730.4799999999996</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6519,34 +6527,34 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>1223</v>
+        <v>1047</v>
       </c>
       <c r="F51" s="14">
-        <v>1418.6799999999998</v>
+        <v>1214.52</v>
       </c>
       <c r="G51" s="14">
-        <v>21.169158143194334</v>
+        <v>18.122738001573563</v>
       </c>
       <c r="H51" s="30">
         <v>1271</v>
       </c>
       <c r="I51" s="15">
-        <v>645.27272727272725</v>
+        <v>469.27272727272725</v>
       </c>
       <c r="J51" s="16">
-        <v>1524</v>
+        <v>1900</v>
       </c>
       <c r="K51" s="13">
-        <v>1767.84</v>
+        <v>2204</v>
       </c>
       <c r="L51" s="14">
-        <v>34.212244897959181</v>
+        <v>42.653061224489797</v>
       </c>
       <c r="M51" s="30">
         <v>980</v>
       </c>
       <c r="N51" s="15">
-        <v>1078.5454545454545</v>
+        <v>1454.5454545454545</v>
       </c>
       <c r="O51" s="16">
         <v>378</v>
@@ -6564,40 +6572,40 @@
         <v>378</v>
       </c>
       <c r="T51" s="18">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="U51" s="17">
-        <v>317.83999999999997</v>
+        <v>277.24</v>
       </c>
       <c r="V51" s="14">
-        <v>11.204460966542751</v>
+        <v>9.7732342007434951</v>
       </c>
       <c r="W51" s="16">
         <v>538</v>
       </c>
       <c r="X51" s="15">
-        <v>-92.818181818181813</v>
+        <v>-127.81818181818181</v>
       </c>
       <c r="Y51" s="18">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="Z51" s="17">
-        <v>187.92</v>
+        <v>179.79999999999998</v>
       </c>
       <c r="AA51" s="14">
         <v>0</v>
       </c>
       <c r="AB51" s="16">
-        <v>0</v>
+        <v>95.333333333333329</v>
       </c>
       <c r="AC51" s="15">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="AD51" s="19">
-        <v>3561</v>
+        <v>3719</v>
       </c>
       <c r="AE51" s="20">
-        <v>4130.7599999999993</v>
+        <v>4314.04</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6636,19 +6644,19 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>3820</v>
+        <v>4296</v>
       </c>
       <c r="F52" s="14">
-        <v>3094.2000000000003</v>
+        <v>3479.76</v>
       </c>
       <c r="G52" s="14">
-        <v>31.761148904006049</v>
+        <v>35.718820861678005</v>
       </c>
       <c r="H52" s="30">
         <v>2646</v>
       </c>
       <c r="I52" s="15">
-        <v>2617.272727272727</v>
+        <v>3093.272727272727</v>
       </c>
       <c r="J52" s="16">
         <v>0</v>
@@ -6681,19 +6689,19 @@
         <v>-339.54545454545456</v>
       </c>
       <c r="T52" s="18">
-        <v>223</v>
+        <v>92</v>
       </c>
       <c r="U52" s="17">
-        <v>180.63000000000002</v>
+        <v>74.52000000000001</v>
       </c>
       <c r="V52" s="14">
-        <v>5.4450610432852384</v>
+        <v>2.2463928967813542</v>
       </c>
       <c r="W52" s="16">
         <v>901</v>
       </c>
       <c r="X52" s="15">
-        <v>-391.31818181818176</v>
+        <v>-522.31818181818176</v>
       </c>
       <c r="Y52" s="18">
         <v>0</v>
@@ -6705,16 +6713,16 @@
         <v>0</v>
       </c>
       <c r="AB52" s="16">
-        <v>101.19999999999999</v>
+        <v>84.333333333333343</v>
       </c>
       <c r="AC52" s="15">
-        <v>-69</v>
+        <v>-57.500000000000007</v>
       </c>
       <c r="AD52" s="19">
-        <v>4043</v>
+        <v>4388</v>
       </c>
       <c r="AE52" s="20">
-        <v>3274.8300000000004</v>
+        <v>3554.28</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6749,85 +6757,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>2924</v>
+        <v>2567</v>
       </c>
       <c r="F53" s="14">
-        <v>2368.44</v>
+        <v>2079.27</v>
       </c>
       <c r="G53" s="14">
-        <v>12.527361246348589</v>
+        <v>10.997857838364167</v>
       </c>
       <c r="H53" s="30">
         <v>5135</v>
       </c>
       <c r="I53" s="15">
-        <v>589.90909090909099</v>
+        <v>232.90909090909099</v>
       </c>
       <c r="J53" s="16">
-        <v>4925</v>
+        <v>4028</v>
       </c>
       <c r="K53" s="13">
-        <v>3989.2500000000005</v>
+        <v>3262.6800000000003</v>
       </c>
       <c r="L53" s="14">
-        <v>34.125984251968497</v>
+        <v>27.910551181102356</v>
       </c>
       <c r="M53" s="30">
         <v>3175.0000000000005</v>
       </c>
       <c r="N53" s="15">
-        <v>3481.8181818181815</v>
+        <v>2584.8181818181815</v>
       </c>
       <c r="O53" s="16">
-        <v>600</v>
+        <v>370</v>
       </c>
       <c r="P53" s="17">
-        <v>486.00000000000006</v>
+        <v>299.70000000000005</v>
       </c>
       <c r="Q53" s="14">
-        <v>14.94903737259343</v>
+        <v>9.2185730464326152</v>
       </c>
       <c r="R53" s="16">
         <v>883.00000000000011</v>
       </c>
       <c r="S53" s="15">
-        <v>-2.0454545454546178</v>
+        <v>-232.04545454545462</v>
       </c>
       <c r="T53" s="18">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="U53" s="17">
-        <v>263.25</v>
+        <v>0</v>
       </c>
       <c r="V53" s="14">
-        <v>4.3307086614173231</v>
+        <v>0</v>
       </c>
       <c r="W53" s="16">
         <v>1651</v>
       </c>
       <c r="X53" s="15">
-        <v>-800.68181818181824</v>
+        <v>-1125.6818181818182</v>
       </c>
       <c r="Y53" s="18">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="Z53" s="17">
-        <v>77.760000000000005</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="AA53" s="14">
-        <v>20.869565217391305</v>
+        <v>15.428571428571432</v>
       </c>
       <c r="AB53" s="16">
-        <v>101.19999999999999</v>
+        <v>128.33333333333331</v>
       </c>
       <c r="AC53" s="15">
-        <v>27</v>
+        <v>2.5000000000000142</v>
       </c>
       <c r="AD53" s="19">
-        <v>8870</v>
+        <v>7055</v>
       </c>
       <c r="AE53" s="20">
-        <v>7184.7000000000007</v>
+        <v>5714.55</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6862,85 +6870,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>3183</v>
+        <v>3122</v>
       </c>
       <c r="F54" s="14">
-        <v>2578.23</v>
+        <v>2528.8200000000002</v>
       </c>
       <c r="G54" s="14">
-        <v>20.344567112144102</v>
+        <v>19.954677513073793</v>
       </c>
       <c r="H54" s="30">
         <v>3442</v>
       </c>
       <c r="I54" s="15">
-        <v>1618.4545454545453</v>
+        <v>1557.4545454545453</v>
       </c>
       <c r="J54" s="16">
-        <v>7566</v>
+        <v>6163</v>
       </c>
       <c r="K54" s="13">
-        <v>6128.46</v>
+        <v>4992.0300000000007</v>
       </c>
       <c r="L54" s="14">
-        <v>95.333333333333343</v>
+        <v>77.655211912943869</v>
       </c>
       <c r="M54" s="30">
         <v>1746</v>
       </c>
       <c r="N54" s="15">
-        <v>6772.363636363636</v>
+        <v>5369.363636363636</v>
       </c>
       <c r="O54" s="16">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="P54" s="17">
-        <v>299.70000000000005</v>
+        <v>278.64000000000004</v>
       </c>
       <c r="Q54" s="14">
-        <v>23.801169590643276</v>
+        <v>22.128654970760234</v>
       </c>
       <c r="R54" s="16">
         <v>342</v>
       </c>
       <c r="S54" s="15">
-        <v>136.81818181818181</v>
+        <v>110.81818181818181</v>
       </c>
       <c r="T54" s="18">
-        <v>855</v>
+        <v>831</v>
       </c>
       <c r="U54" s="17">
-        <v>692.55000000000007</v>
+        <v>673.11</v>
       </c>
       <c r="V54" s="14">
-        <v>30.436893203883496</v>
+        <v>29.582524271844662</v>
       </c>
       <c r="W54" s="16">
         <v>618</v>
       </c>
       <c r="X54" s="15">
-        <v>433.63636363636363</v>
+        <v>409.63636363636363</v>
       </c>
       <c r="Y54" s="18">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="Z54" s="17">
-        <v>170.91000000000003</v>
+        <v>157.14000000000001</v>
       </c>
       <c r="AA54" s="14">
-        <v>23.977272727272727</v>
+        <v>17.373134328358208</v>
       </c>
       <c r="AB54" s="16">
-        <v>193.60000000000002</v>
+        <v>245.66666666666666</v>
       </c>
       <c r="AC54" s="15">
-        <v>79</v>
+        <v>26.5</v>
       </c>
       <c r="AD54" s="19">
-        <v>12185</v>
+        <v>10654</v>
       </c>
       <c r="AE54" s="20">
-        <v>9869.85</v>
+        <v>8629.74</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -6975,85 +6983,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>4560</v>
+        <v>5236</v>
       </c>
       <c r="F55" s="14">
-        <v>3693.6000000000004</v>
+        <v>4241.16</v>
       </c>
       <c r="G55" s="14">
-        <v>36.828193832599119</v>
+        <v>42.287812041116005</v>
       </c>
       <c r="H55" s="30">
         <v>2724</v>
       </c>
       <c r="I55" s="15">
-        <v>3321.818181818182</v>
+        <v>3997.818181818182</v>
       </c>
       <c r="J55" s="16">
-        <v>8196</v>
+        <v>8045</v>
       </c>
       <c r="K55" s="13">
-        <v>6638.76</v>
+        <v>6516.4500000000007</v>
       </c>
       <c r="L55" s="14">
-        <v>92.23120204603579</v>
+        <v>90.531969309462909</v>
       </c>
       <c r="M55" s="30">
         <v>1955.0000000000002</v>
       </c>
       <c r="N55" s="15">
-        <v>7307.363636363636</v>
+        <v>7156.363636363636</v>
       </c>
       <c r="O55" s="16">
-        <v>237</v>
+        <v>309</v>
       </c>
       <c r="P55" s="17">
-        <v>191.97</v>
+        <v>250.29000000000002</v>
       </c>
       <c r="Q55" s="14">
-        <v>11.586666666666668</v>
+        <v>15.106666666666667</v>
       </c>
       <c r="R55" s="16">
         <v>449.99999999999994</v>
       </c>
       <c r="S55" s="15">
-        <v>-69.818181818181813</v>
+        <v>2.181818181818187</v>
       </c>
       <c r="T55" s="18">
-        <v>489</v>
+        <v>441</v>
       </c>
       <c r="U55" s="17">
-        <v>396.09000000000003</v>
+        <v>357.21000000000004</v>
       </c>
       <c r="V55" s="14">
-        <v>15.173483779971791</v>
+        <v>13.684062059238364</v>
       </c>
       <c r="W55" s="16">
         <v>709</v>
       </c>
       <c r="X55" s="15">
-        <v>5.5909090909091219</v>
+        <v>-42.409090909090878</v>
       </c>
       <c r="Y55" s="18">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="Z55" s="17">
-        <v>179.82000000000002</v>
+        <v>170.91000000000003</v>
       </c>
       <c r="AA55" s="14">
-        <v>25.227272727272727</v>
+        <v>18.895522388059703</v>
       </c>
       <c r="AB55" s="16">
-        <v>193.60000000000002</v>
+        <v>245.66666666666666</v>
       </c>
       <c r="AC55" s="15">
-        <v>90</v>
+        <v>43.5</v>
       </c>
       <c r="AD55" s="19">
-        <v>13704</v>
+        <v>14242</v>
       </c>
       <c r="AE55" s="20">
-        <v>11100.240000000002</v>
+        <v>11536.02</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7088,34 +7096,34 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="F56" s="14">
-        <v>395.62</v>
+        <v>351.08000000000004</v>
       </c>
       <c r="G56" s="14">
-        <v>6.6573146292585168</v>
+        <v>5.9078156312625243</v>
       </c>
       <c r="H56" s="30">
         <v>499</v>
       </c>
       <c r="I56" s="15">
-        <v>-75.818181818181841</v>
+        <v>-92.818181818181841</v>
       </c>
       <c r="J56" s="32">
-        <v>584</v>
+        <v>469</v>
       </c>
       <c r="K56" s="13">
-        <v>1530.0800000000002</v>
+        <v>1228.78</v>
       </c>
       <c r="L56" s="14">
-        <v>28.871910112359551</v>
+        <v>23.186516853932584</v>
       </c>
       <c r="M56" s="30">
         <v>445</v>
       </c>
       <c r="N56" s="15">
-        <v>381.72727272727275</v>
+        <v>266.72727272727275</v>
       </c>
       <c r="O56" s="32">
         <v>28</v>
@@ -7133,19 +7141,19 @@
         <v>7.5454545454545467</v>
       </c>
       <c r="T56" s="18">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U56" s="17">
-        <v>75.98</v>
+        <v>73.36</v>
       </c>
       <c r="V56" s="14">
-        <v>3.3936170212765959</v>
+        <v>3.2765957446808511</v>
       </c>
       <c r="W56" s="16">
         <v>188</v>
       </c>
       <c r="X56" s="15">
-        <v>-99.181818181818187</v>
+        <v>-100.18181818181819</v>
       </c>
       <c r="Y56" s="18">
         <v>64</v>
@@ -7154,19 +7162,19 @@
         <v>167.68</v>
       </c>
       <c r="AA56" s="14">
-        <v>26.666666666666668</v>
+        <v>32</v>
       </c>
       <c r="AB56" s="16">
-        <v>52.8</v>
+        <v>44</v>
       </c>
       <c r="AC56" s="15">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AD56" s="19">
-        <v>856</v>
+        <v>723</v>
       </c>
       <c r="AE56" s="20">
-        <v>2242.7200000000003</v>
+        <v>1894.26</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7201,64 +7209,64 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F57" s="14">
-        <v>131</v>
+        <v>115.28</v>
       </c>
       <c r="G57" s="14">
-        <v>1.21012101210121</v>
+        <v>1.0649064906490648</v>
       </c>
       <c r="H57" s="30">
         <v>909</v>
       </c>
       <c r="I57" s="15">
-        <v>-363.18181818181819</v>
+        <v>-369.18181818181819</v>
       </c>
       <c r="J57" s="32">
-        <v>780</v>
+        <v>235</v>
       </c>
       <c r="K57" s="13">
-        <v>2043.6000000000001</v>
+        <v>615.70000000000005</v>
       </c>
       <c r="L57" s="14">
-        <v>19.953488372093027</v>
+        <v>6.0116279069767451</v>
       </c>
       <c r="M57" s="30">
         <v>859.99999999999989</v>
       </c>
       <c r="N57" s="15">
-        <v>389.09090909090912</v>
+        <v>-155.90909090909088</v>
       </c>
       <c r="O57" s="32">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="P57" s="17">
-        <v>172.92000000000002</v>
+        <v>138.86000000000001</v>
       </c>
       <c r="Q57" s="14">
-        <v>21.043478260869566</v>
+        <v>16.898550724637683</v>
       </c>
       <c r="R57" s="16">
         <v>69</v>
       </c>
       <c r="S57" s="15">
-        <v>18.954545454545453</v>
+        <v>5.9545454545454533</v>
       </c>
       <c r="T57" s="18">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="U57" s="17">
-        <v>60.260000000000005</v>
+        <v>55.02</v>
       </c>
       <c r="V57" s="14">
-        <v>1.6375404530744337</v>
+        <v>1.4951456310679612</v>
       </c>
       <c r="W57" s="16">
         <v>309</v>
       </c>
       <c r="X57" s="15">
-        <v>-187.68181818181819</v>
+        <v>-189.68181818181819</v>
       </c>
       <c r="Y57" s="18">
         <v>80</v>
@@ -7267,19 +7275,19 @@
         <v>209.60000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>33.333333333333336</v>
+        <v>40</v>
       </c>
       <c r="AB57" s="16">
-        <v>52.8</v>
+        <v>44</v>
       </c>
       <c r="AC57" s="15">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AD57" s="19">
-        <v>999</v>
+        <v>433</v>
       </c>
       <c r="AE57" s="20">
-        <v>2617.38</v>
+        <v>1134.46</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7314,49 +7322,49 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>206</v>
+        <v>371</v>
       </c>
       <c r="F58" s="14">
-        <v>539.72</v>
+        <v>972.0200000000001</v>
       </c>
       <c r="G58" s="14">
-        <v>10.739336492890994</v>
+        <v>19.341232227488149</v>
       </c>
       <c r="H58" s="30">
         <v>422</v>
       </c>
       <c r="I58" s="15">
-        <v>14.181818181818159</v>
+        <v>179.18181818181816</v>
       </c>
       <c r="J58" s="32">
-        <v>209</v>
+        <v>18</v>
       </c>
       <c r="K58" s="13">
-        <v>547.58000000000004</v>
+        <v>47.160000000000004</v>
       </c>
       <c r="L58" s="14">
-        <v>11.297297297297296</v>
+        <v>0.97297297297297303</v>
       </c>
       <c r="M58" s="30">
         <v>407</v>
       </c>
       <c r="N58" s="15">
-        <v>24</v>
+        <v>-167</v>
       </c>
       <c r="O58" s="32">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P58" s="17">
-        <v>96.94</v>
+        <v>117.9</v>
       </c>
       <c r="Q58" s="14">
-        <v>18.088888888888889</v>
+        <v>22</v>
       </c>
       <c r="R58" s="16">
         <v>45</v>
       </c>
       <c r="S58" s="15">
-        <v>6.3181818181818201</v>
+        <v>14.31818181818182</v>
       </c>
       <c r="T58" s="18">
         <v>67</v>
@@ -7374,25 +7382,25 @@
         <v>-8.681818181818187</v>
       </c>
       <c r="Y58" s="18">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="Z58" s="17">
-        <v>165.06</v>
+        <v>141.48000000000002</v>
       </c>
       <c r="AA58" s="14">
-        <v>26.25</v>
+        <v>15.428571428571429</v>
       </c>
       <c r="AB58" s="16">
-        <v>52.8</v>
+        <v>77</v>
       </c>
       <c r="AC58" s="15">
-        <v>27</v>
+        <v>1.5</v>
       </c>
       <c r="AD58" s="19">
-        <v>582</v>
+        <v>555</v>
       </c>
       <c r="AE58" s="20">
-        <v>1524.8400000000001</v>
+        <v>1454.1000000000001</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7430,64 +7438,64 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="F59" s="14">
-        <v>159.82</v>
+        <v>110.04</v>
       </c>
       <c r="G59" s="14">
-        <v>2.6365422396856579</v>
+        <v>1.8153241650294696</v>
       </c>
       <c r="H59" s="30">
         <v>509</v>
       </c>
       <c r="I59" s="15">
-        <v>-170.36363636363637</v>
+        <v>-189.36363636363637</v>
       </c>
       <c r="J59" s="32">
-        <v>470</v>
+        <v>106</v>
       </c>
       <c r="K59" s="13">
-        <v>1231.4000000000001</v>
+        <v>277.72000000000003</v>
       </c>
       <c r="L59" s="14">
-        <v>25.594059405940595</v>
+        <v>5.7722772277227721</v>
       </c>
       <c r="M59" s="30">
         <v>404</v>
       </c>
       <c r="N59" s="15">
-        <v>286.36363636363637</v>
+        <v>-77.636363636363626</v>
       </c>
       <c r="O59" s="32">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="P59" s="17">
-        <v>62.88</v>
+        <v>36.68</v>
       </c>
       <c r="Q59" s="14">
-        <v>20.307692307692307</v>
+        <v>11.846153846153845</v>
       </c>
       <c r="R59" s="16">
         <v>26</v>
       </c>
       <c r="S59" s="15">
-        <v>6.2727272727272734</v>
+        <v>-3.7272727272727266</v>
       </c>
       <c r="T59" s="18">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="U59" s="17">
-        <v>180.78</v>
+        <v>162.44</v>
       </c>
       <c r="V59" s="14">
-        <v>7.7846153846153836</v>
+        <v>6.994871794871794</v>
       </c>
       <c r="W59" s="16">
         <v>195.00000000000003</v>
       </c>
       <c r="X59" s="15">
-        <v>-63.954545454545467</v>
+        <v>-70.954545454545467</v>
       </c>
       <c r="Y59" s="18">
         <v>56</v>
@@ -7496,19 +7504,19 @@
         <v>146.72</v>
       </c>
       <c r="AA59" s="14">
-        <v>23.333333333333336</v>
+        <v>28</v>
       </c>
       <c r="AB59" s="16">
-        <v>52.8</v>
+        <v>44</v>
       </c>
       <c r="AC59" s="15">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AD59" s="19">
-        <v>680</v>
+        <v>280</v>
       </c>
       <c r="AE59" s="20">
-        <v>1781.6000000000001</v>
+        <v>733.6</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7582,10 +7590,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="69" t="s">
+      <c r="E61" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="69"/>
+      <c r="F61" s="67"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7615,17 +7623,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="65"/>
+      <c r="C62" s="68"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>134071.12</v>
+        <v>133317.40000000002</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>32.236879817337901</v>
+        <v>32.803994035521136</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7663,11 +7671,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>191772.04999999996</v>
+        <v>189968.68000000002</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>46.110844215924459</v>
+        <v>46.743571699236732</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7705,11 +7713,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>26558.179999999997</v>
+        <v>25089.990000000009</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>6.38581117862838</v>
+        <v>6.1736268657450948</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7747,11 +7755,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>42646.009999999987</v>
+        <v>37560.999999999993</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>10.254067386466154</v>
+        <v>9.242235596915398</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7789,11 +7797,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>20846.239999999991</v>
+        <v>20336.129999999994</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>5.0123974016431116</v>
+        <v>5.0038951196586652</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7825,19 +7833,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="65" t="s">
+      <c r="B67" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="65"/>
+      <c r="C67" s="68"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>415893.59999999992</v>
-      </c>
-      <c r="E67" s="66">
+        <v>406406</v>
+      </c>
+      <c r="E67" s="69">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="66"/>
+      <c r="F67" s="69"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7937,17 +7945,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="65"/>
+      <c r="C70" s="68"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>102234</v>
+        <v>108721</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>33.81078211865556</v>
+        <v>35.380930530741622</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -7984,11 +7992,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>135340</v>
+        <v>139311</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>44.759583425659208</v>
+        <v>45.335793574085464</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8026,11 +8034,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>19804</v>
+        <v>18661</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>6.5495698992297537</v>
+        <v>6.0728244279777535</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8068,11 +8076,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>30921</v>
+        <v>27016</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>10.226179097863222</v>
+        <v>8.7917809734873256</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8110,11 +8118,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>14072</v>
+        <v>13578</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>4.6538854585922591</v>
+        <v>4.4186704937078369</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8146,19 +8154,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="68"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>302371</v>
-      </c>
-      <c r="E75" s="66">
+        <v>307287</v>
+      </c>
+      <c r="E75" s="69">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="66"/>
+      <c r="F75" s="69"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8705,6 +8713,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8713,17 +8732,6 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F462BC7-3C32-47F6-810E-BCCD2E4F9BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7668FA-29F4-4F60-9DF8-76745E8E155D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -805,6 +805,12 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -813,12 +819,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1175,6 +1175,7 @@
       <sheetName val="INVENTARIO NACIONAL 04-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 09-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 10-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1305,6 +1306,7 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1632,242 +1634,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="66" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="66"/>
-      <c r="AH1" s="66"/>
-      <c r="AI1" s="66"/>
-      <c r="AJ1" s="66"/>
-      <c r="AK1" s="66"/>
-      <c r="AL1" s="66"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
+      <c r="AJ1" s="68"/>
+      <c r="AK1" s="68"/>
+      <c r="AL1" s="68"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65"/>
-      <c r="AC2" s="65"/>
-      <c r="AD2" s="65"/>
-      <c r="AE2" s="65"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
-      <c r="AH2" s="66"/>
-      <c r="AI2" s="66"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="66"/>
-      <c r="AL2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
-      <c r="AH3" s="66"/>
-      <c r="AI3" s="66"/>
-      <c r="AJ3" s="66"/>
-      <c r="AK3" s="66"/>
-      <c r="AL3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="68"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="65"/>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
-      <c r="AE4" s="65"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="68"/>
+      <c r="AG4" s="68"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="68"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="65"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="65"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="67"/>
+      <c r="Y5" s="67"/>
+      <c r="Z5" s="67"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="67"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="65"/>
-      <c r="AB6" s="65"/>
-      <c r="AC6" s="65"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="65"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
-      <c r="AH6" s="66"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="66"/>
-      <c r="AK6" s="66"/>
-      <c r="AL6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="68"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2232,85 +2234,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>5943</v>
+        <v>5330</v>
       </c>
       <c r="F13" s="14">
-        <v>8082.4800000000005</v>
+        <v>7248.8</v>
       </c>
       <c r="G13" s="14">
-        <v>7.6267864434463046</v>
+        <v>6.8401096657527853</v>
       </c>
       <c r="H13" s="30">
         <v>17143</v>
       </c>
       <c r="I13" s="15">
-        <v>-1849.2727272727279</v>
+        <v>-2462.2727272727279</v>
       </c>
       <c r="J13" s="16">
-        <v>5646</v>
+        <v>4194</v>
       </c>
       <c r="K13" s="13">
-        <v>7678.56</v>
+        <v>5703.84</v>
       </c>
       <c r="L13" s="14">
-        <v>23.191187453323373</v>
+        <v>17.227035100821507</v>
       </c>
       <c r="M13" s="30">
         <v>5356</v>
       </c>
       <c r="N13" s="15">
-        <v>3211.4545454545455</v>
+        <v>1759.4545454545455</v>
       </c>
       <c r="O13" s="16">
-        <v>612</v>
+        <v>554</v>
       </c>
       <c r="P13" s="17">
-        <v>832.32</v>
+        <v>753.44</v>
       </c>
       <c r="Q13" s="14">
-        <v>15.637630662020907</v>
+        <v>14.155632984901279</v>
       </c>
       <c r="R13" s="16">
         <v>861</v>
       </c>
       <c r="S13" s="15">
-        <v>24.954545454545496</v>
+        <v>-33.045454545454504</v>
       </c>
       <c r="T13" s="18">
-        <v>255</v>
+        <v>857</v>
       </c>
       <c r="U13" s="17">
-        <v>346.8</v>
+        <v>1165.52</v>
       </c>
       <c r="V13" s="14">
-        <v>4.6984924623115578</v>
+        <v>15.790619765494137</v>
       </c>
       <c r="W13" s="16">
         <v>1194</v>
       </c>
       <c r="X13" s="15">
-        <v>-559.09090909090912</v>
+        <v>42.909090909090878</v>
       </c>
       <c r="Y13" s="18">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="Z13" s="17">
-        <v>644.6400000000001</v>
+        <v>595.68000000000006</v>
       </c>
       <c r="AA13" s="14">
-        <v>16.067796610169491</v>
+        <v>17.322033898305087</v>
       </c>
       <c r="AB13" s="16">
-        <v>649</v>
+        <v>556.28571428571422</v>
       </c>
       <c r="AC13" s="15">
-        <v>31.5</v>
+        <v>58.714285714285779</v>
       </c>
       <c r="AD13" s="19">
-        <v>12930</v>
+        <v>11373</v>
       </c>
       <c r="AE13" s="20">
-        <v>17584.800000000003</v>
+        <v>15467.28</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2346,19 +2348,19 @@
         <v>1.59</v>
       </c>
       <c r="E14" s="13">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="F14" s="14">
-        <v>337.08000000000004</v>
+        <v>174.9</v>
       </c>
       <c r="G14" s="14">
-        <v>6.1207349081364839</v>
+        <v>3.1758530183727038</v>
       </c>
       <c r="H14" s="30">
         <v>762</v>
       </c>
       <c r="I14" s="15">
-        <v>-134.36363636363632</v>
+        <v>-236.36363636363632</v>
       </c>
       <c r="J14" s="16">
         <v>0</v>
@@ -2406,25 +2408,25 @@
         <v>-7.1818181818181799</v>
       </c>
       <c r="Y14" s="18">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Z14" s="17">
-        <v>162.18</v>
+        <v>157.41</v>
       </c>
       <c r="AA14" s="14">
-        <v>43.714285714285708</v>
+        <v>49.5</v>
       </c>
       <c r="AB14" s="16">
-        <v>51.333333333333336</v>
+        <v>44</v>
       </c>
       <c r="AC14" s="15">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AD14" s="19">
-        <v>501</v>
+        <v>396</v>
       </c>
       <c r="AE14" s="20">
-        <v>796.59</v>
+        <v>629.64</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2460,19 +2462,19 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>1743</v>
+        <v>1183</v>
       </c>
       <c r="F15" s="14">
-        <v>3538.2899999999995</v>
+        <v>2401.4899999999998</v>
       </c>
       <c r="G15" s="14">
-        <v>5.557391304347826</v>
+        <v>3.7718840579710147</v>
       </c>
       <c r="H15" s="30">
         <v>6900</v>
       </c>
       <c r="I15" s="15">
-        <v>-1393.363636363636</v>
+        <v>-1953.363636363636</v>
       </c>
       <c r="J15" s="16">
         <v>0</v>
@@ -2490,55 +2492,55 @@
         <v>-1372.2727272727273</v>
       </c>
       <c r="O15" s="16">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P15" s="17">
-        <v>487.19999999999993</v>
+        <v>483.13999999999993</v>
       </c>
       <c r="Q15" s="14">
-        <v>17.777777777777779</v>
+        <v>17.62962962962963</v>
       </c>
       <c r="R15" s="16">
         <v>297</v>
       </c>
       <c r="S15" s="15">
-        <v>37.5</v>
+        <v>35.5</v>
       </c>
       <c r="T15" s="18">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="U15" s="17">
-        <v>64.959999999999994</v>
+        <v>54.809999999999995</v>
       </c>
       <c r="V15" s="14">
-        <v>2.0288184438040342</v>
+        <v>1.711815561959654</v>
       </c>
       <c r="W15" s="16">
         <v>347.00000000000006</v>
       </c>
       <c r="X15" s="15">
-        <v>-204.59090909090912</v>
+        <v>-209.59090909090912</v>
       </c>
       <c r="Y15" s="18">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="Z15" s="17">
-        <v>513.58999999999992</v>
+        <v>477.04999999999995</v>
       </c>
       <c r="AA15" s="14">
-        <v>37.024390243902445</v>
+        <v>40.121951219512191</v>
       </c>
       <c r="AB15" s="16">
-        <v>150.33333333333331</v>
+        <v>128.85714285714286</v>
       </c>
       <c r="AC15" s="15">
-        <v>150.5</v>
+        <v>147.14285714285714</v>
       </c>
       <c r="AD15" s="19">
-        <v>2268</v>
+        <v>1683</v>
       </c>
       <c r="AE15" s="20">
-        <v>4604.04</v>
+        <v>3416.49</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2573,85 +2575,85 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="F16" s="14">
-        <v>1516.2</v>
+        <v>1083</v>
       </c>
       <c r="G16" s="14">
-        <v>6.6141732283464565</v>
+        <v>4.7244094488188972</v>
       </c>
       <c r="H16" s="30">
         <v>1397</v>
       </c>
       <c r="I16" s="15">
-        <v>-215</v>
+        <v>-335</v>
       </c>
       <c r="J16" s="16">
-        <v>730</v>
+        <v>520</v>
       </c>
       <c r="K16" s="13">
-        <v>2635.2999999999997</v>
+        <v>1877.2</v>
       </c>
       <c r="L16" s="14">
-        <v>29.467889908256879</v>
+        <v>20.990825688073393</v>
       </c>
       <c r="M16" s="30">
         <v>545</v>
       </c>
       <c r="N16" s="15">
-        <v>482.27272727272725</v>
+        <v>272.27272727272725</v>
       </c>
       <c r="O16" s="16">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="P16" s="17">
-        <v>101.08</v>
+        <v>57.76</v>
       </c>
       <c r="Q16" s="14">
-        <v>13.391304347826084</v>
+        <v>7.6521739130434767</v>
       </c>
       <c r="R16" s="16">
         <v>46.000000000000007</v>
       </c>
       <c r="S16" s="15">
-        <v>-3.3636363636363704</v>
+        <v>-15.36363636363637</v>
       </c>
       <c r="T16" s="18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U16" s="17">
-        <v>101.08</v>
+        <v>97.47</v>
       </c>
       <c r="V16" s="14">
-        <v>12.571428571428573</v>
+        <v>12.122448979591837</v>
       </c>
       <c r="W16" s="16">
         <v>49</v>
       </c>
       <c r="X16" s="15">
-        <v>-5.4090909090909065</v>
+        <v>-6.4090909090909065</v>
       </c>
       <c r="Y16" s="18">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Z16" s="17">
-        <v>267.14</v>
+        <v>259.92</v>
       </c>
       <c r="AA16" s="14">
-        <v>34.153846153846153</v>
+        <v>38.769230769230766</v>
       </c>
       <c r="AB16" s="16">
-        <v>47.666666666666664</v>
+        <v>40.857142857142861</v>
       </c>
       <c r="AC16" s="15">
-        <v>41.5</v>
+        <v>44.142857142857139</v>
       </c>
       <c r="AD16" s="19">
-        <v>1280</v>
+        <v>935</v>
       </c>
       <c r="AE16" s="20">
-        <v>4620.8</v>
+        <v>3375.35</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2686,34 +2688,34 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F17" s="14">
-        <v>351.2</v>
+        <v>228.27999999999997</v>
       </c>
       <c r="G17" s="14">
-        <v>5.2694610778443112</v>
+        <v>3.4251497005988023</v>
       </c>
       <c r="H17" s="30">
         <v>167</v>
       </c>
       <c r="I17" s="15">
-        <v>-35.909090909090907</v>
+        <v>-49.909090909090907</v>
       </c>
       <c r="J17" s="16">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="K17" s="13">
-        <v>939.45999999999992</v>
+        <v>711.18</v>
       </c>
       <c r="L17" s="14">
-        <v>34.115942028985508</v>
+        <v>25.826086956521738</v>
       </c>
       <c r="M17" s="30">
         <v>69</v>
       </c>
       <c r="N17" s="15">
-        <v>75.63636363636364</v>
+        <v>49.63636363636364</v>
       </c>
       <c r="O17" s="16">
         <v>13</v>
@@ -2746,25 +2748,25 @@
         <v>15.636363636363637</v>
       </c>
       <c r="Y17" s="18">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Z17" s="17">
-        <v>122.91999999999999</v>
+        <v>96.58</v>
       </c>
       <c r="AA17" s="14">
-        <v>14</v>
+        <v>12.833333333333332</v>
       </c>
       <c r="AB17" s="16">
-        <v>22</v>
+        <v>18.857142857142858</v>
       </c>
       <c r="AC17" s="15">
-        <v>-1</v>
+        <v>-1.8571428571428577</v>
       </c>
       <c r="AD17" s="19">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="AE17" s="20">
-        <v>1676.9799999999998</v>
+        <v>1299.4399999999998</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2799,85 +2801,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>9753</v>
+        <v>8422</v>
       </c>
       <c r="F18" s="14">
-        <v>6144.39</v>
+        <v>5305.86</v>
       </c>
       <c r="G18" s="14">
-        <v>11.753820870994248</v>
+        <v>10.149767187072035</v>
       </c>
       <c r="H18" s="30">
         <v>18255</v>
       </c>
       <c r="I18" s="15">
-        <v>1455.2727272727279</v>
+        <v>124.27272727272793</v>
       </c>
       <c r="J18" s="16">
-        <v>6928</v>
+        <v>3246</v>
       </c>
       <c r="K18" s="13">
-        <v>4364.6400000000003</v>
+        <v>2044.98</v>
       </c>
       <c r="L18" s="14">
-        <v>22.025433526011561</v>
+        <v>10.319653179190752</v>
       </c>
       <c r="M18" s="30">
         <v>6920</v>
       </c>
       <c r="N18" s="15">
-        <v>3782.5454545454545</v>
+        <v>100.5454545454545</v>
       </c>
       <c r="O18" s="16">
-        <v>927</v>
+        <v>915</v>
       </c>
       <c r="P18" s="17">
-        <v>584.01</v>
+        <v>576.45000000000005</v>
       </c>
       <c r="Q18" s="14">
-        <v>14.11349480968858</v>
+        <v>13.930795847750863</v>
       </c>
       <c r="R18" s="16">
         <v>1445</v>
       </c>
       <c r="S18" s="15">
-        <v>-58.227272727272748</v>
+        <v>-70.227272727272748</v>
       </c>
       <c r="T18" s="18">
-        <v>962</v>
+        <v>861</v>
       </c>
       <c r="U18" s="17">
-        <v>606.06000000000006</v>
+        <v>542.42999999999995</v>
       </c>
       <c r="V18" s="14">
-        <v>5.485743908761016</v>
+        <v>4.9097978227060652</v>
       </c>
       <c r="W18" s="16">
         <v>3858</v>
       </c>
       <c r="X18" s="15">
-        <v>-1668.4545454545455</v>
+        <v>-1769.4545454545455</v>
       </c>
       <c r="Y18" s="18">
-        <v>368</v>
+        <v>323</v>
       </c>
       <c r="Z18" s="17">
-        <v>231.84</v>
+        <v>203.49</v>
       </c>
       <c r="AA18" s="14">
-        <v>25.379310344827587</v>
+        <v>25.988505747126435</v>
       </c>
       <c r="AB18" s="16">
-        <v>319</v>
+        <v>273.42857142857144</v>
       </c>
       <c r="AC18" s="15">
-        <v>150.5</v>
+        <v>136.57142857142856</v>
       </c>
       <c r="AD18" s="19">
-        <v>18938</v>
+        <v>13767</v>
       </c>
       <c r="AE18" s="20">
-        <v>11930.94</v>
+        <v>8673.2100000000009</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2912,34 +2914,34 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>155</v>
+        <v>997</v>
       </c>
       <c r="F19" s="14">
-        <v>97.65</v>
+        <v>628.11</v>
       </c>
       <c r="G19" s="14">
-        <v>2.2962962962962967</v>
+        <v>14.770370370370374</v>
       </c>
       <c r="H19" s="30">
         <v>1484.9999999999998</v>
       </c>
       <c r="I19" s="15">
-        <v>-519.99999999999989</v>
+        <v>322.00000000000011</v>
       </c>
       <c r="J19" s="16">
-        <v>1028</v>
+        <v>977</v>
       </c>
       <c r="K19" s="13">
-        <v>647.64</v>
+        <v>615.51</v>
       </c>
       <c r="L19" s="14">
-        <v>20.12099644128114</v>
+        <v>19.122775800711743</v>
       </c>
       <c r="M19" s="30">
         <v>1124</v>
       </c>
       <c r="N19" s="15">
-        <v>517.09090909090901</v>
+        <v>466.09090909090907</v>
       </c>
       <c r="O19" s="16">
         <v>85</v>
@@ -2957,40 +2959,40 @@
         <v>20.909090909090907</v>
       </c>
       <c r="T19" s="18">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="U19" s="17">
-        <v>34.020000000000003</v>
+        <v>17.010000000000002</v>
       </c>
       <c r="V19" s="14">
-        <v>3.5044247787610621</v>
+        <v>1.752212389380531</v>
       </c>
       <c r="W19" s="16">
         <v>339</v>
       </c>
       <c r="X19" s="15">
-        <v>-177.13636363636363</v>
+        <v>-204.13636363636363</v>
       </c>
       <c r="Y19" s="18">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="Z19" s="17">
-        <v>149.31</v>
+        <v>132.93</v>
       </c>
       <c r="AA19" s="14">
-        <v>15.290322580645162</v>
+        <v>15.881720430107528</v>
       </c>
       <c r="AB19" s="16">
-        <v>341</v>
+        <v>292.28571428571428</v>
       </c>
       <c r="AC19" s="15">
-        <v>4.5</v>
+        <v>11.714285714285722</v>
       </c>
       <c r="AD19" s="19">
-        <v>1559</v>
+        <v>2297</v>
       </c>
       <c r="AE19" s="20">
-        <v>982.17</v>
+        <v>1447.11</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3025,49 +3027,49 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>2180</v>
+        <v>1639</v>
       </c>
       <c r="F20" s="14">
-        <v>1373.4</v>
+        <v>1032.57</v>
       </c>
       <c r="G20" s="14">
-        <v>14.21037037037037</v>
+        <v>10.683851851851852</v>
       </c>
       <c r="H20" s="30">
         <v>3375</v>
       </c>
       <c r="I20" s="15">
-        <v>645.90909090909099</v>
+        <v>104.90909090909099</v>
       </c>
       <c r="J20" s="16">
-        <v>1130</v>
+        <v>1014</v>
       </c>
       <c r="K20" s="13">
-        <v>711.9</v>
+        <v>638.82000000000005</v>
       </c>
       <c r="L20" s="14">
-        <v>11.243781094527364</v>
+        <v>10.08955223880597</v>
       </c>
       <c r="M20" s="30">
         <v>2211</v>
       </c>
       <c r="N20" s="15">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="O20" s="16">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P20" s="17">
-        <v>148.05000000000001</v>
+        <v>144.27000000000001</v>
       </c>
       <c r="Q20" s="14">
-        <v>18.53046594982079</v>
+        <v>18.057347670250895</v>
       </c>
       <c r="R20" s="16">
         <v>279</v>
       </c>
       <c r="S20" s="15">
-        <v>44.77272727272728</v>
+        <v>38.77272727272728</v>
       </c>
       <c r="T20" s="18">
         <v>0</v>
@@ -3085,25 +3087,25 @@
         <v>-799.09090909090912</v>
       </c>
       <c r="Y20" s="18">
-        <v>366</v>
+        <v>323</v>
       </c>
       <c r="Z20" s="17">
-        <v>230.58</v>
+        <v>203.49</v>
       </c>
       <c r="AA20" s="14">
-        <v>22.875</v>
+        <v>23.552083333333332</v>
       </c>
       <c r="AB20" s="16">
-        <v>352</v>
+        <v>301.71428571428572</v>
       </c>
       <c r="AC20" s="15">
-        <v>126</v>
+        <v>117.28571428571428</v>
       </c>
       <c r="AD20" s="19">
-        <v>3911</v>
+        <v>3205</v>
       </c>
       <c r="AE20" s="20">
-        <v>2463.9299999999998</v>
+        <v>2019.15</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3138,85 +3140,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>4060</v>
+        <v>3143</v>
       </c>
       <c r="F21" s="14">
-        <v>4425.4000000000005</v>
+        <v>3425.8700000000003</v>
       </c>
       <c r="G21" s="14">
-        <v>13.995612660607961</v>
+        <v>10.834534628643059</v>
       </c>
       <c r="H21" s="30">
         <v>6382</v>
       </c>
       <c r="I21" s="15">
-        <v>1159.0909090909095</v>
+        <v>242.09090909090946</v>
       </c>
       <c r="J21" s="16">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="K21" s="13">
-        <v>154.78</v>
+        <v>0</v>
       </c>
       <c r="L21" s="14">
-        <v>0.46103896103896103</v>
+        <v>0</v>
       </c>
       <c r="M21" s="30">
         <v>6776</v>
       </c>
       <c r="N21" s="15">
-        <v>-2938</v>
+        <v>-3080</v>
       </c>
       <c r="O21" s="16">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="P21" s="17">
-        <v>386.95000000000005</v>
+        <v>367.33000000000004</v>
       </c>
       <c r="Q21" s="14">
-        <v>14.819734345351044</v>
+        <v>14.06831119544592</v>
       </c>
       <c r="R21" s="16">
         <v>527</v>
       </c>
       <c r="S21" s="15">
-        <v>-4.318181818181813</v>
+        <v>-22.318181818181813</v>
       </c>
       <c r="T21" s="18">
-        <v>403</v>
+        <v>337</v>
       </c>
       <c r="U21" s="17">
-        <v>439.27000000000004</v>
+        <v>367.33000000000004</v>
       </c>
       <c r="V21" s="14">
-        <v>4.2810236600675999</v>
+        <v>3.5799130854659582</v>
       </c>
       <c r="W21" s="16">
         <v>2071</v>
       </c>
       <c r="X21" s="15">
-        <v>-1009.0454545454545</v>
+        <v>-1075.0454545454545</v>
       </c>
       <c r="Y21" s="18">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="Z21" s="17">
-        <v>439.27000000000004</v>
+        <v>427.28000000000003</v>
       </c>
       <c r="AA21" s="14">
-        <v>16.013245033112579</v>
+        <v>18.172185430463575</v>
       </c>
       <c r="AB21" s="16">
-        <v>553.66666666666674</v>
+        <v>474.57142857142861</v>
       </c>
       <c r="AC21" s="15">
-        <v>25.499999999999943</v>
+        <v>68.428571428571388</v>
       </c>
       <c r="AD21" s="19">
-        <v>5363</v>
+        <v>4209</v>
       </c>
       <c r="AE21" s="20">
-        <v>5845.67</v>
+        <v>4587.8100000000004</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3251,85 +3253,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1242</v>
+        <v>803</v>
       </c>
       <c r="F22" s="14">
-        <v>1353.7800000000002</v>
+        <v>875.2700000000001</v>
       </c>
       <c r="G22" s="14">
-        <v>6.3707157845651663</v>
+        <v>4.1189088365586377</v>
       </c>
       <c r="H22" s="30">
         <v>4289</v>
       </c>
       <c r="I22" s="15">
-        <v>-707.54545454545473</v>
+        <v>-1146.5454545454547</v>
       </c>
       <c r="J22" s="16">
-        <v>2630</v>
+        <v>5240</v>
       </c>
       <c r="K22" s="13">
-        <v>2866.7000000000003</v>
+        <v>5711.6</v>
       </c>
       <c r="L22" s="14">
-        <v>23.938767066611504</v>
+        <v>47.695490277203149</v>
       </c>
       <c r="M22" s="30">
         <v>2417</v>
       </c>
       <c r="N22" s="15">
-        <v>1531.3636363636365</v>
+        <v>4141.363636363636</v>
       </c>
       <c r="O22" s="16">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P22" s="17">
-        <v>201.65</v>
+        <v>199.47000000000003</v>
       </c>
       <c r="Q22" s="14">
-        <v>19.950980392156865</v>
+        <v>19.735294117647062</v>
       </c>
       <c r="R22" s="16">
         <v>203.99999999999997</v>
       </c>
       <c r="S22" s="15">
-        <v>45.909090909090935</v>
+        <v>43.909090909090935</v>
       </c>
       <c r="T22" s="18">
-        <v>270</v>
+        <v>475</v>
       </c>
       <c r="U22" s="17">
-        <v>294.3</v>
+        <v>517.75</v>
       </c>
       <c r="V22" s="14">
-        <v>8.3779971791255292</v>
+        <v>14.739069111424541</v>
       </c>
       <c r="W22" s="16">
         <v>709</v>
       </c>
       <c r="X22" s="15">
-        <v>-213.40909090909088</v>
+        <v>-8.4090909090908781</v>
       </c>
       <c r="Y22" s="18">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="Z22" s="17">
-        <v>229.99</v>
+        <v>223.45000000000002</v>
       </c>
       <c r="AA22" s="14">
         <v>0</v>
       </c>
       <c r="AB22" s="16">
-        <v>40.333333333333329</v>
+        <v>34.571428571428569</v>
       </c>
       <c r="AC22" s="15">
-        <v>183.5</v>
+        <v>181.42857142857144</v>
       </c>
       <c r="AD22" s="19">
-        <v>4538</v>
+        <v>6906</v>
       </c>
       <c r="AE22" s="20">
-        <v>4946.42</v>
+        <v>7527.5400000000009</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3364,85 +3366,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>11281</v>
+        <v>13185</v>
       </c>
       <c r="F23" s="14">
-        <v>13085.96</v>
+        <v>15294.599999999999</v>
       </c>
       <c r="G23" s="14">
-        <v>6.5836008170411437</v>
+        <v>7.6947767726874821</v>
       </c>
       <c r="H23" s="30">
         <v>37697</v>
       </c>
       <c r="I23" s="15">
-        <v>-5854</v>
+        <v>-3950</v>
       </c>
       <c r="J23" s="16">
-        <v>22119</v>
+        <v>15901</v>
       </c>
       <c r="K23" s="13">
-        <v>25658.039999999997</v>
+        <v>18445.16</v>
       </c>
       <c r="L23" s="14">
-        <v>25.430781290828325</v>
+        <v>18.281787300757774</v>
       </c>
       <c r="M23" s="30">
         <v>19135</v>
       </c>
       <c r="N23" s="15">
-        <v>13421.272727272728</v>
+        <v>7203.2727272727279</v>
       </c>
       <c r="O23" s="16">
-        <v>2065</v>
+        <v>2020</v>
       </c>
       <c r="P23" s="17">
-        <v>2395.3999999999996</v>
+        <v>2343.1999999999998</v>
       </c>
       <c r="Q23" s="14">
-        <v>14.40849984142087</v>
+        <v>14.094513162067873</v>
       </c>
       <c r="R23" s="16">
         <v>3153</v>
       </c>
       <c r="S23" s="15">
-        <v>-84.772727272727025</v>
+        <v>-129.77272727272702</v>
       </c>
       <c r="T23" s="18">
-        <v>3479</v>
+        <v>5800</v>
       </c>
       <c r="U23" s="17">
-        <v>4035.64</v>
+        <v>6727.9999999999991</v>
       </c>
       <c r="V23" s="14">
-        <v>5.7843107617896008</v>
+        <v>9.64328899637243</v>
       </c>
       <c r="W23" s="16">
         <v>13232</v>
       </c>
       <c r="X23" s="15">
-        <v>-5542.818181818182</v>
+        <v>-3221.818181818182</v>
       </c>
       <c r="Y23" s="18">
-        <v>637</v>
+        <v>557</v>
       </c>
       <c r="Z23" s="17">
-        <v>738.92</v>
+        <v>646.12</v>
       </c>
       <c r="AA23" s="14">
-        <v>9.1</v>
+        <v>9.2833333333333332</v>
       </c>
       <c r="AB23" s="16">
-        <v>1540</v>
+        <v>1320</v>
       </c>
       <c r="AC23" s="15">
-        <v>-413</v>
+        <v>-343</v>
       </c>
       <c r="AD23" s="19">
-        <v>39581</v>
+        <v>37463</v>
       </c>
       <c r="AE23" s="20">
-        <v>45913.96</v>
+        <v>43457.079999999994</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3477,85 +3479,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>9354</v>
+        <v>6893</v>
       </c>
       <c r="F24" s="14">
-        <v>10850.64</v>
+        <v>7995.8799999999992</v>
       </c>
       <c r="G24" s="14">
-        <v>7.662074614639959</v>
+        <v>5.6462134187206798</v>
       </c>
       <c r="H24" s="30">
         <v>26858</v>
       </c>
       <c r="I24" s="15">
-        <v>-2854.181818181818</v>
+        <v>-5315.181818181818</v>
       </c>
       <c r="J24" s="16">
-        <v>13404</v>
+        <v>12920</v>
       </c>
       <c r="K24" s="13">
-        <v>15548.64</v>
+        <v>14987.199999999999</v>
       </c>
       <c r="L24" s="14">
-        <v>24.714046262152195</v>
+        <v>23.821656050955415</v>
       </c>
       <c r="M24" s="30">
         <v>11932</v>
       </c>
       <c r="N24" s="15">
-        <v>7980.363636363636</v>
+        <v>7496.363636363636</v>
       </c>
       <c r="O24" s="16">
-        <v>1227</v>
+        <v>1184</v>
       </c>
       <c r="P24" s="17">
-        <v>1423.32</v>
+        <v>1373.4399999999998</v>
       </c>
       <c r="Q24" s="14">
-        <v>14.290100582318688</v>
+        <v>13.789306511381684</v>
       </c>
       <c r="R24" s="16">
         <v>1889</v>
       </c>
       <c r="S24" s="15">
-        <v>-60.954545454545496</v>
+        <v>-103.9545454545455</v>
       </c>
       <c r="T24" s="18">
-        <v>3551</v>
+        <v>4753</v>
       </c>
       <c r="U24" s="17">
-        <v>4119.16</v>
+        <v>5513.48</v>
       </c>
       <c r="V24" s="14">
-        <v>10.742849284928493</v>
+        <v>14.379262926292629</v>
       </c>
       <c r="W24" s="16">
         <v>7272</v>
       </c>
       <c r="X24" s="15">
-        <v>-1407.181818181818</v>
+        <v>-205.18181818181802</v>
       </c>
       <c r="Y24" s="18">
-        <v>743</v>
+        <v>688</v>
       </c>
       <c r="Z24" s="17">
-        <v>861.88</v>
+        <v>798.07999999999993</v>
       </c>
       <c r="AA24" s="14">
-        <v>15.31958762886598</v>
+        <v>16.54982817869416</v>
       </c>
       <c r="AB24" s="16">
-        <v>1067</v>
+        <v>914.57142857142856</v>
       </c>
       <c r="AC24" s="15">
-        <v>15.5</v>
+        <v>64.428571428571445</v>
       </c>
       <c r="AD24" s="19">
-        <v>28279</v>
+        <v>26438</v>
       </c>
       <c r="AE24" s="20">
-        <v>32803.64</v>
+        <v>30668.079999999998</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3590,85 +3592,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>9909</v>
+        <v>7640</v>
       </c>
       <c r="F25" s="14">
-        <v>11494.439999999999</v>
+        <v>8862.4</v>
       </c>
       <c r="G25" s="14">
-        <v>8.4416821561338296</v>
+        <v>6.5086741016109046</v>
       </c>
       <c r="H25" s="30">
         <v>25824</v>
       </c>
       <c r="I25" s="15">
-        <v>-1829.181818181818</v>
+        <v>-4098.181818181818</v>
       </c>
       <c r="J25" s="16">
-        <v>9297</v>
+        <v>8815</v>
       </c>
       <c r="K25" s="13">
-        <v>10784.519999999999</v>
+        <v>10225.4</v>
       </c>
       <c r="L25" s="14">
-        <v>17.17185794643607</v>
+        <v>16.28158844765343</v>
       </c>
       <c r="M25" s="30">
         <v>11911</v>
       </c>
       <c r="N25" s="15">
-        <v>3882.909090909091</v>
+        <v>3400.909090909091</v>
       </c>
       <c r="O25" s="16">
-        <v>1332</v>
+        <v>1300</v>
       </c>
       <c r="P25" s="17">
-        <v>1545.12</v>
+        <v>1508</v>
       </c>
       <c r="Q25" s="14">
-        <v>13.338188438780156</v>
+        <v>13.017751479289942</v>
       </c>
       <c r="R25" s="16">
         <v>2197</v>
       </c>
       <c r="S25" s="15">
-        <v>-165.9545454545455</v>
+        <v>-197.9545454545455</v>
       </c>
       <c r="T25" s="18">
-        <v>3385</v>
+        <v>4523</v>
       </c>
       <c r="U25" s="17">
-        <v>3926.6</v>
+        <v>5246.6799999999994</v>
       </c>
       <c r="V25" s="14">
-        <v>10.334443519289481</v>
+        <v>13.808770469053567</v>
       </c>
       <c r="W25" s="16">
         <v>7206.0000000000009</v>
       </c>
       <c r="X25" s="15">
-        <v>-1528.181818181818</v>
+        <v>-390.18181818181802</v>
       </c>
       <c r="Y25" s="18">
-        <v>815</v>
+        <v>763</v>
       </c>
       <c r="Z25" s="17">
-        <v>945.4</v>
+        <v>885.07999999999993</v>
       </c>
       <c r="AA25" s="14">
-        <v>21.541850220264315</v>
+        <v>23.528634361233479</v>
       </c>
       <c r="AB25" s="16">
-        <v>832.33333333333337</v>
+        <v>713.42857142857144</v>
       </c>
       <c r="AC25" s="15">
-        <v>247.5</v>
+        <v>276.57142857142856</v>
       </c>
       <c r="AD25" s="19">
-        <v>24738</v>
+        <v>23041</v>
       </c>
       <c r="AE25" s="20">
-        <v>28696.079999999998</v>
+        <v>26727.559999999998</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3703,85 +3705,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>7477</v>
+        <v>4160</v>
       </c>
       <c r="F26" s="14">
-        <v>8673.32</v>
+        <v>4825.5999999999995</v>
       </c>
       <c r="G26" s="14">
-        <v>5.2428366533864539</v>
+        <v>2.9169721115537848</v>
       </c>
       <c r="H26" s="30">
         <v>31375</v>
       </c>
       <c r="I26" s="15">
-        <v>-6784.3636363636379</v>
+        <v>-10101.363636363638</v>
       </c>
       <c r="J26" s="16">
-        <v>7163</v>
+        <v>16424</v>
       </c>
       <c r="K26" s="13">
-        <v>8309.08</v>
+        <v>19051.84</v>
       </c>
       <c r="L26" s="14">
-        <v>11.177104759202781</v>
+        <v>25.627916873537131</v>
       </c>
       <c r="M26" s="30">
         <v>14099</v>
       </c>
       <c r="N26" s="15">
-        <v>754.36363636363603</v>
+        <v>10015.363636363636</v>
       </c>
       <c r="O26" s="16">
-        <v>1186</v>
+        <v>1145</v>
       </c>
       <c r="P26" s="17">
-        <v>1375.76</v>
+        <v>1328.1999999999998</v>
       </c>
       <c r="Q26" s="14">
-        <v>14.336263736263735</v>
+        <v>13.840659340659339</v>
       </c>
       <c r="R26" s="16">
         <v>1820</v>
       </c>
       <c r="S26" s="15">
-        <v>-54.909090909090992</v>
+        <v>-95.909090909090992</v>
       </c>
       <c r="T26" s="18">
-        <v>3965</v>
+        <v>3738</v>
       </c>
       <c r="U26" s="17">
-        <v>4599.3999999999996</v>
+        <v>4336.08</v>
       </c>
       <c r="V26" s="14">
-        <v>10.476819601249099</v>
+        <v>9.8770117703579157</v>
       </c>
       <c r="W26" s="16">
         <v>8326</v>
       </c>
       <c r="X26" s="15">
-        <v>-1711.818181818182</v>
+        <v>-1938.818181818182</v>
       </c>
       <c r="Y26" s="18">
-        <v>903</v>
+        <v>861</v>
       </c>
       <c r="Z26" s="17">
-        <v>1047.48</v>
+        <v>998.75999999999988</v>
       </c>
       <c r="AA26" s="14">
-        <v>17.309904153354637</v>
+        <v>19.255591054313097</v>
       </c>
       <c r="AB26" s="16">
-        <v>1147.6666666666665</v>
+        <v>983.71428571428578</v>
       </c>
       <c r="AC26" s="15">
-        <v>120.50000000000011</v>
+        <v>190.28571428571422</v>
       </c>
       <c r="AD26" s="19">
-        <v>20694</v>
+        <v>26328</v>
       </c>
       <c r="AE26" s="20">
-        <v>24005.039999999997</v>
+        <v>30540.48</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3816,85 +3818,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>1986</v>
+        <v>1169</v>
       </c>
       <c r="F27" s="14">
-        <v>2303.7599999999998</v>
+        <v>1356.04</v>
       </c>
       <c r="G27" s="14">
-        <v>12.046319272125723</v>
+        <v>7.0907085745795415</v>
       </c>
       <c r="H27" s="30">
         <v>3627</v>
       </c>
       <c r="I27" s="15">
-        <v>337.36363636363626</v>
+        <v>-479.63636363636374</v>
       </c>
       <c r="J27" s="16">
-        <v>3002</v>
+        <v>2824</v>
       </c>
       <c r="K27" s="13">
-        <v>3482.3199999999997</v>
+        <v>3275.8399999999997</v>
       </c>
       <c r="L27" s="14">
-        <v>26.073430714567706</v>
+        <v>24.52743782076589</v>
       </c>
       <c r="M27" s="30">
         <v>2533</v>
       </c>
       <c r="N27" s="15">
-        <v>1850.6363636363635</v>
+        <v>1672.6363636363635</v>
       </c>
       <c r="O27" s="16">
-        <v>608</v>
+        <v>582</v>
       </c>
       <c r="P27" s="17">
-        <v>705.28</v>
+        <v>675.12</v>
       </c>
       <c r="Q27" s="14">
-        <v>31.847619047619048</v>
+        <v>30.485714285714288</v>
       </c>
       <c r="R27" s="16">
         <v>420</v>
       </c>
       <c r="S27" s="15">
-        <v>321.63636363636363</v>
+        <v>295.63636363636363</v>
       </c>
       <c r="T27" s="18">
-        <v>400</v>
+        <v>919</v>
       </c>
       <c r="U27" s="17">
-        <v>463.99999999999994</v>
+        <v>1066.04</v>
       </c>
       <c r="V27" s="14">
-        <v>5.7629338572364128</v>
+        <v>13.240340537000659</v>
       </c>
       <c r="W27" s="16">
         <v>1526.9999999999998</v>
       </c>
       <c r="X27" s="15">
-        <v>-641.13636363636328</v>
+        <v>-122.13636363636328</v>
       </c>
       <c r="Y27" s="18">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="Z27" s="17">
-        <v>620.59999999999991</v>
+        <v>602.04</v>
       </c>
       <c r="AA27" s="14">
-        <v>36.067415730337075</v>
+        <v>40.82022471910112</v>
       </c>
       <c r="AB27" s="16">
-        <v>326.33333333333337</v>
+        <v>279.71428571428572</v>
       </c>
       <c r="AC27" s="15">
-        <v>312.5</v>
+        <v>328.28571428571428</v>
       </c>
       <c r="AD27" s="19">
-        <v>6531</v>
+        <v>6013</v>
       </c>
       <c r="AE27" s="20">
-        <v>7575.9599999999991</v>
+        <v>6975.08</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3929,85 +3931,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>1126</v>
+        <v>2021</v>
       </c>
       <c r="F28" s="14">
-        <v>1306.1599999999999</v>
+        <v>2344.3599999999997</v>
       </c>
       <c r="G28" s="14">
-        <v>6.6005861977085001</v>
+        <v>11.847055688782307</v>
       </c>
       <c r="H28" s="30">
         <v>3753</v>
       </c>
       <c r="I28" s="15">
-        <v>-579.90909090909099</v>
+        <v>315.09090909090901</v>
       </c>
       <c r="J28" s="16">
-        <v>2299</v>
+        <v>1475</v>
       </c>
       <c r="K28" s="13">
-        <v>2666.8399999999997</v>
+        <v>1710.9999999999998</v>
       </c>
       <c r="L28" s="14">
-        <v>15.156727599640394</v>
+        <v>9.7243032664069524</v>
       </c>
       <c r="M28" s="30">
         <v>3337</v>
       </c>
       <c r="N28" s="15">
-        <v>782.18181818181802</v>
+        <v>-41.818181818181984</v>
       </c>
       <c r="O28" s="16">
-        <v>594</v>
+        <v>558</v>
       </c>
       <c r="P28" s="17">
-        <v>689.04</v>
+        <v>647.28</v>
       </c>
       <c r="Q28" s="14">
-        <v>24.75</v>
+        <v>23.25</v>
       </c>
       <c r="R28" s="16">
         <v>528</v>
       </c>
       <c r="S28" s="15">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="T28" s="18">
-        <v>102</v>
+        <v>855</v>
       </c>
       <c r="U28" s="17">
-        <v>118.32</v>
+        <v>991.8</v>
       </c>
       <c r="V28" s="14">
-        <v>1.7301464919043947</v>
+        <v>14.502698535080956</v>
       </c>
       <c r="W28" s="16">
         <v>1297</v>
       </c>
       <c r="X28" s="15">
-        <v>-782.31818181818176</v>
+        <v>-29.318181818181756</v>
       </c>
       <c r="Y28" s="18">
-        <v>491</v>
+        <v>467</v>
       </c>
       <c r="Z28" s="17">
-        <v>569.55999999999995</v>
+        <v>541.71999999999991</v>
       </c>
       <c r="AA28" s="14">
-        <v>22.661538461538459</v>
+        <v>25.146153846153844</v>
       </c>
       <c r="AB28" s="16">
-        <v>476.66666666666669</v>
+        <v>408.57142857142861</v>
       </c>
       <c r="AC28" s="15">
-        <v>166</v>
+        <v>188.42857142857139</v>
       </c>
       <c r="AD28" s="19">
-        <v>4612</v>
+        <v>5376</v>
       </c>
       <c r="AE28" s="20">
-        <v>5349.92</v>
+        <v>6236.16</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4042,85 +4044,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>1669</v>
+        <v>855</v>
       </c>
       <c r="F29" s="14">
-        <v>1936.04</v>
+        <v>991.8</v>
       </c>
       <c r="G29" s="14">
-        <v>9.6499342969776603</v>
+        <v>4.9434954007884357</v>
       </c>
       <c r="H29" s="30">
         <v>3805.0000000000005</v>
       </c>
       <c r="I29" s="15">
-        <v>-60.545454545454731</v>
+        <v>-874.54545454545473</v>
       </c>
       <c r="J29" s="16">
-        <v>3282</v>
+        <v>3047</v>
       </c>
       <c r="K29" s="13">
-        <v>3807.12</v>
+        <v>3534.52</v>
       </c>
       <c r="L29" s="14">
-        <v>26.594475138121549</v>
+        <v>24.6902394106814</v>
       </c>
       <c r="M29" s="30">
         <v>2715</v>
       </c>
       <c r="N29" s="15">
-        <v>2047.909090909091</v>
+        <v>1812.909090909091</v>
       </c>
       <c r="O29" s="16">
-        <v>571</v>
+        <v>545</v>
       </c>
       <c r="P29" s="17">
-        <v>662.3599999999999</v>
+        <v>632.19999999999993</v>
       </c>
       <c r="Q29" s="14">
-        <v>26.225469728601251</v>
+        <v>25.031315240083508</v>
       </c>
       <c r="R29" s="16">
         <v>479</v>
       </c>
       <c r="S29" s="15">
-        <v>244.40909090909088</v>
+        <v>218.40909090909088</v>
       </c>
       <c r="T29" s="18">
-        <v>53</v>
+        <v>798</v>
       </c>
       <c r="U29" s="17">
-        <v>61.48</v>
+        <v>925.68</v>
       </c>
       <c r="V29" s="14">
-        <v>1.0219106047326905</v>
+        <v>15.386503067484661</v>
       </c>
       <c r="W29" s="16">
         <v>1141</v>
       </c>
       <c r="X29" s="15">
-        <v>-724.9545454545455</v>
+        <v>20.045454545454504</v>
       </c>
       <c r="Y29" s="18">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="Z29" s="17">
-        <v>551</v>
+        <v>530.12</v>
       </c>
       <c r="AA29" s="14">
-        <v>18.627450980392158</v>
+        <v>20.908496732026144</v>
       </c>
       <c r="AB29" s="16">
-        <v>561</v>
+        <v>480.85714285714289</v>
       </c>
       <c r="AC29" s="15">
-        <v>92.5</v>
+        <v>129.14285714285711</v>
       </c>
       <c r="AD29" s="19">
-        <v>6050</v>
+        <v>5702</v>
       </c>
       <c r="AE29" s="20">
-        <v>7017.9999999999991</v>
+        <v>6614.32</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4155,34 +4157,34 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>646</v>
+        <v>964</v>
       </c>
       <c r="F30" s="14">
-        <v>2377.2800000000002</v>
+        <v>3547.52</v>
       </c>
       <c r="G30" s="14">
-        <v>7.1596977329974809</v>
+        <v>10.684130982367757</v>
       </c>
       <c r="H30" s="30">
         <v>1985</v>
       </c>
       <c r="I30" s="15">
-        <v>-256.27272727272737</v>
+        <v>61.727272727272634</v>
       </c>
       <c r="J30" s="16">
-        <v>1141</v>
+        <v>789</v>
       </c>
       <c r="K30" s="13">
-        <v>4198.88</v>
+        <v>2903.52</v>
       </c>
       <c r="L30" s="14">
-        <v>11.291947818263608</v>
+        <v>7.808367071524966</v>
       </c>
       <c r="M30" s="30">
         <v>2223</v>
       </c>
       <c r="N30" s="15">
-        <v>130.5454545454545</v>
+        <v>-221.4545454545455</v>
       </c>
       <c r="O30" s="16">
         <v>75</v>
@@ -4200,40 +4202,40 @@
         <v>19.090909090909093</v>
       </c>
       <c r="T30" s="18">
-        <v>247</v>
+        <v>461</v>
       </c>
       <c r="U30" s="17">
-        <v>908.96</v>
+        <v>1696.48</v>
       </c>
       <c r="V30" s="14">
-        <v>7.7851002865329511</v>
+        <v>14.530085959885387</v>
       </c>
       <c r="W30" s="16">
         <v>698</v>
       </c>
       <c r="X30" s="15">
-        <v>-228.90909090909088</v>
+        <v>-14.909090909090878</v>
       </c>
       <c r="Y30" s="18">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z30" s="17">
-        <v>290.72000000000003</v>
+        <v>272.32</v>
       </c>
       <c r="AA30" s="14">
-        <v>16.928571428571427</v>
+        <v>18.5</v>
       </c>
       <c r="AB30" s="16">
-        <v>102.66666666666667</v>
+        <v>88</v>
       </c>
       <c r="AC30" s="15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AD30" s="19">
-        <v>2188</v>
+        <v>2363</v>
       </c>
       <c r="AE30" s="20">
-        <v>8051.84</v>
+        <v>8695.84</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4268,34 +4270,34 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>110</v>
+        <v>482</v>
       </c>
       <c r="F31" s="14">
-        <v>404.8</v>
+        <v>1773.76</v>
       </c>
       <c r="G31" s="14">
-        <v>2.0183486238532109</v>
+        <v>8.8440366972477058</v>
       </c>
       <c r="H31" s="30">
         <v>1199</v>
       </c>
       <c r="I31" s="15">
-        <v>-435</v>
+        <v>-63</v>
       </c>
       <c r="J31" s="16">
-        <v>904</v>
+        <v>874</v>
       </c>
       <c r="K31" s="13">
-        <v>3326.7200000000003</v>
+        <v>3216.32</v>
       </c>
       <c r="L31" s="14">
-        <v>13.584699453551915</v>
+        <v>13.133879781420768</v>
       </c>
       <c r="M31" s="30">
         <v>1463.9999999999998</v>
       </c>
       <c r="N31" s="15">
-        <v>238.54545454545473</v>
+        <v>208.54545454545473</v>
       </c>
       <c r="O31" s="16">
         <v>32</v>
@@ -4313,19 +4315,19 @@
         <v>4.7272727272727266</v>
       </c>
       <c r="T31" s="18">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="U31" s="17">
-        <v>500.48</v>
+        <v>655.04000000000008</v>
       </c>
       <c r="V31" s="14">
-        <v>11.376425855513308</v>
+        <v>14.889733840304181</v>
       </c>
       <c r="W31" s="16">
         <v>263</v>
       </c>
       <c r="X31" s="15">
-        <v>-43.318181818181813</v>
+        <v>-1.318181818181813</v>
       </c>
       <c r="Y31" s="18">
         <v>62</v>
@@ -4334,19 +4336,19 @@
         <v>228.16</v>
       </c>
       <c r="AA31" s="14">
-        <v>31</v>
+        <v>36.166666666666664</v>
       </c>
       <c r="AB31" s="16">
-        <v>44</v>
+        <v>37.714285714285715</v>
       </c>
       <c r="AC31" s="15">
-        <v>32</v>
+        <v>36.285714285714285</v>
       </c>
       <c r="AD31" s="19">
-        <v>1244</v>
+        <v>1628</v>
       </c>
       <c r="AE31" s="20">
-        <v>4577.92</v>
+        <v>5991.04</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4381,34 +4383,34 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>1219</v>
+        <v>795</v>
       </c>
       <c r="F32" s="14">
-        <v>5058.8500000000004</v>
+        <v>3299.2500000000005</v>
       </c>
       <c r="G32" s="14">
-        <v>5.581269510926119</v>
+        <v>3.6399583766909469</v>
       </c>
       <c r="H32" s="30">
         <v>4805</v>
       </c>
       <c r="I32" s="15">
-        <v>-965.09090909090901</v>
+        <v>-1389.090909090909</v>
       </c>
       <c r="J32" s="16">
-        <v>1668</v>
+        <v>1176</v>
       </c>
       <c r="K32" s="13">
-        <v>6922.2000000000007</v>
+        <v>4880.4000000000005</v>
       </c>
       <c r="L32" s="14">
-        <v>9.7311058074781212</v>
+        <v>6.8607796340493223</v>
       </c>
       <c r="M32" s="30">
         <v>3771.0000000000005</v>
       </c>
       <c r="N32" s="15">
-        <v>-46.090909090909463</v>
+        <v>-538.09090909090946</v>
       </c>
       <c r="O32" s="16">
         <v>201</v>
@@ -4426,40 +4428,40 @@
         <v>9.4090909090909065</v>
       </c>
       <c r="T32" s="18">
-        <v>348</v>
+        <v>891</v>
       </c>
       <c r="U32" s="17">
-        <v>1444.2</v>
+        <v>3697.65</v>
       </c>
       <c r="V32" s="14">
-        <v>4.181321682140906</v>
+        <v>10.705625341343527</v>
       </c>
       <c r="W32" s="16">
         <v>1831</v>
       </c>
       <c r="X32" s="15">
-        <v>-900.40909090909099</v>
+        <v>-357.40909090909099</v>
       </c>
       <c r="Y32" s="18">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="Z32" s="17">
-        <v>1311.4</v>
+        <v>1282.3500000000001</v>
       </c>
       <c r="AA32" s="14">
-        <v>46.243902439024396</v>
+        <v>52.756097560975604</v>
       </c>
       <c r="AB32" s="16">
-        <v>150.33333333333331</v>
+        <v>128.85714285714286</v>
       </c>
       <c r="AC32" s="15">
-        <v>213.5</v>
+        <v>221.14285714285714</v>
       </c>
       <c r="AD32" s="19">
-        <v>3752</v>
+        <v>3372</v>
       </c>
       <c r="AE32" s="20">
-        <v>15570.800000000001</v>
+        <v>13993.800000000001</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4494,85 +4496,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>1277</v>
+        <v>441</v>
       </c>
       <c r="F33" s="14">
-        <v>5299.55</v>
+        <v>1830.15</v>
       </c>
       <c r="G33" s="14">
-        <v>3.1888762769580024</v>
+        <v>1.1012485811577752</v>
       </c>
       <c r="H33" s="30">
         <v>8810</v>
       </c>
       <c r="I33" s="15">
-        <v>-2727.5454545454545</v>
+        <v>-3563.5454545454545</v>
       </c>
       <c r="J33" s="16">
-        <v>2318</v>
+        <v>2524</v>
       </c>
       <c r="K33" s="13">
-        <v>9619.7000000000007</v>
+        <v>10474.6</v>
       </c>
       <c r="L33" s="14">
-        <v>10.05243445692884</v>
+        <v>10.945791444904396</v>
       </c>
       <c r="M33" s="30">
         <v>5073</v>
       </c>
       <c r="N33" s="15">
-        <v>12.090909090909008</v>
+        <v>218.09090909090901</v>
       </c>
       <c r="O33" s="16">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="P33" s="17">
-        <v>971.10000000000014</v>
+        <v>946.2</v>
       </c>
       <c r="Q33" s="14">
-        <v>14.339832869080782</v>
+        <v>13.97214484679666</v>
       </c>
       <c r="R33" s="16">
         <v>359</v>
       </c>
       <c r="S33" s="15">
-        <v>-10.772727272727252</v>
+        <v>-16.772727272727252</v>
       </c>
       <c r="T33" s="18">
-        <v>674</v>
+        <v>1407</v>
       </c>
       <c r="U33" s="17">
-        <v>2797.1000000000004</v>
+        <v>5839.05</v>
       </c>
       <c r="V33" s="14">
-        <v>5.7876658860265415</v>
+        <v>12.081967213114755</v>
       </c>
       <c r="W33" s="16">
         <v>2562</v>
       </c>
       <c r="X33" s="15">
-        <v>-1072.8181818181818</v>
+        <v>-339.81818181818176</v>
       </c>
       <c r="Y33" s="18">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Z33" s="17">
-        <v>813.40000000000009</v>
+        <v>759.45</v>
       </c>
       <c r="AA33" s="14">
-        <v>14.341463414634148</v>
+        <v>15.621951219512194</v>
       </c>
       <c r="AB33" s="16">
-        <v>300.66666666666663</v>
+        <v>257.71428571428572</v>
       </c>
       <c r="AC33" s="15">
-        <v>-8.9999999999999716</v>
+        <v>7.2857142857142776</v>
       </c>
       <c r="AD33" s="19">
-        <v>4699</v>
+        <v>4783</v>
       </c>
       <c r="AE33" s="20">
-        <v>19500.850000000002</v>
+        <v>19849.45</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4607,25 +4609,25 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E34" s="13">
-        <v>269</v>
+        <v>481</v>
       </c>
       <c r="F34" s="14">
-        <v>1116.3500000000001</v>
+        <v>1996.15</v>
       </c>
       <c r="G34" s="14">
-        <v>3.9986486486486492</v>
+        <v>7.15</v>
       </c>
       <c r="H34" s="30">
         <v>1480</v>
       </c>
       <c r="I34" s="15">
-        <v>-403.72727272727263</v>
+        <v>-191.72727272727263</v>
       </c>
       <c r="J34" s="16">
-        <v>552</v>
+        <v>72</v>
       </c>
       <c r="K34" s="13">
-        <v>2290.8000000000002</v>
+        <v>298.8</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4634,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>552</v>
+        <v>72</v>
       </c>
       <c r="O34" s="16">
         <v>32</v>
@@ -4652,19 +4654,19 @@
         <v>56</v>
       </c>
       <c r="T34" s="18">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="U34" s="17">
-        <v>41.5</v>
+        <v>307.10000000000002</v>
       </c>
       <c r="V34" s="14">
-        <v>2.3404255319148937</v>
+        <v>17.319148936170215</v>
       </c>
       <c r="W34" s="16">
         <v>94</v>
       </c>
       <c r="X34" s="15">
-        <v>-54.090909090909093</v>
+        <v>9.9090909090909065</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4682,10 +4684,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>895</v>
+        <v>691</v>
       </c>
       <c r="AE34" s="20">
-        <v>3714.2500000000005</v>
+        <v>2867.65</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4720,85 +4722,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>1121</v>
+        <v>1637</v>
       </c>
       <c r="F35" s="14">
-        <v>1827.2299999999998</v>
+        <v>2668.31</v>
       </c>
       <c r="G35" s="14">
-        <v>2.3061529829811112</v>
+        <v>3.36768281279222</v>
       </c>
       <c r="H35" s="30">
         <v>10694</v>
       </c>
       <c r="I35" s="15">
-        <v>-3739.909090909091</v>
+        <v>-3223.909090909091</v>
       </c>
       <c r="J35" s="16">
-        <v>917</v>
+        <v>566</v>
       </c>
       <c r="K35" s="13">
-        <v>1494.7099999999998</v>
+        <v>922.57999999999993</v>
       </c>
       <c r="L35" s="14">
-        <v>6.2632722756907793</v>
+        <v>3.8658801614405465</v>
       </c>
       <c r="M35" s="30">
         <v>3221</v>
       </c>
       <c r="N35" s="15">
-        <v>-547.09090909090901</v>
+        <v>-898.09090909090901</v>
       </c>
       <c r="O35" s="16">
-        <v>689</v>
+        <v>648</v>
       </c>
       <c r="P35" s="17">
-        <v>1123.07</v>
+        <v>1056.24</v>
       </c>
       <c r="Q35" s="14">
-        <v>15.872251308900525</v>
+        <v>14.927748691099477</v>
       </c>
       <c r="R35" s="16">
         <v>955</v>
       </c>
       <c r="S35" s="15">
-        <v>37.863636363636374</v>
+        <v>-3.136363636363626</v>
       </c>
       <c r="T35" s="18">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="U35" s="17">
-        <v>671.56</v>
+        <v>635.69999999999993</v>
       </c>
       <c r="V35" s="14">
-        <v>6.654919236417034</v>
+        <v>6.2995594713656393</v>
       </c>
       <c r="W35" s="16">
         <v>1362</v>
       </c>
       <c r="X35" s="15">
-        <v>-516.63636363636363</v>
+        <v>-538.63636363636363</v>
       </c>
       <c r="Y35" s="18">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="Z35" s="17">
-        <v>704.16</v>
+        <v>689.49</v>
       </c>
       <c r="AA35" s="14">
-        <v>33.230769230769234</v>
+        <v>37.96153846153846</v>
       </c>
       <c r="AB35" s="16">
-        <v>286</v>
+        <v>245.14285714285714</v>
       </c>
       <c r="AC35" s="15">
-        <v>237</v>
+        <v>255.85714285714286</v>
       </c>
       <c r="AD35" s="19">
-        <v>3571</v>
+        <v>3664</v>
       </c>
       <c r="AE35" s="20">
-        <v>5820.73</v>
+        <v>5972.32</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4833,85 +4835,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>682</v>
+        <v>1218</v>
       </c>
       <c r="F36" s="14">
-        <v>1111.6599999999999</v>
+        <v>1985.34</v>
       </c>
       <c r="G36" s="14">
-        <v>0.91226363470541738</v>
+        <v>1.6292332948258039</v>
       </c>
       <c r="H36" s="30">
         <v>16447</v>
       </c>
       <c r="I36" s="15">
-        <v>-6793.909090909091</v>
+        <v>-6257.909090909091</v>
       </c>
       <c r="J36" s="16">
-        <v>3614</v>
+        <v>2164</v>
       </c>
       <c r="K36" s="13">
-        <v>5890.82</v>
+        <v>3527.3199999999997</v>
       </c>
       <c r="L36" s="14">
-        <v>16.114308877178757</v>
+        <v>9.6489663558978513</v>
       </c>
       <c r="M36" s="30">
         <v>4934</v>
       </c>
       <c r="N36" s="15">
-        <v>1371.272727272727</v>
+        <v>-78.727272727272975</v>
       </c>
       <c r="O36" s="16">
-        <v>741</v>
+        <v>723</v>
       </c>
       <c r="P36" s="17">
-        <v>1207.83</v>
+        <v>1178.49</v>
       </c>
       <c r="Q36" s="14">
-        <v>8.1387918122815783</v>
+        <v>7.9410883674488266</v>
       </c>
       <c r="R36" s="16">
         <v>2003</v>
       </c>
       <c r="S36" s="15">
-        <v>-624.68181818181824</v>
+        <v>-642.68181818181824</v>
       </c>
       <c r="T36" s="18">
-        <v>795</v>
+        <v>2003</v>
       </c>
       <c r="U36" s="17">
-        <v>1295.8499999999999</v>
+        <v>3264.89</v>
       </c>
       <c r="V36" s="14">
-        <v>5.9530292716133433</v>
+        <v>14.998638529611982</v>
       </c>
       <c r="W36" s="16">
         <v>2938</v>
       </c>
       <c r="X36" s="15">
-        <v>-1208.181818181818</v>
+        <v>-0.18181818181801646</v>
       </c>
       <c r="Y36" s="18">
-        <v>533</v>
+        <v>508</v>
       </c>
       <c r="Z36" s="17">
-        <v>868.79</v>
+        <v>828.04</v>
       </c>
       <c r="AA36" s="14">
-        <v>16.569948186528499</v>
+        <v>18.424870466321245</v>
       </c>
       <c r="AB36" s="16">
-        <v>707.66666666666663</v>
+        <v>606.57142857142856</v>
       </c>
       <c r="AC36" s="15">
-        <v>50.500000000000057</v>
+        <v>94.428571428571445</v>
       </c>
       <c r="AD36" s="19">
-        <v>6365</v>
+        <v>6616</v>
       </c>
       <c r="AE36" s="20">
-        <v>10374.949999999999</v>
+        <v>10784.08</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4946,85 +4948,85 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>2017</v>
+        <v>767</v>
       </c>
       <c r="F37" s="14">
-        <v>3287.7099999999996</v>
+        <v>1250.2099999999998</v>
       </c>
       <c r="G37" s="14">
-        <v>7.4465514348044968</v>
+        <v>2.8316831683168315</v>
       </c>
       <c r="H37" s="30">
         <v>5959</v>
       </c>
       <c r="I37" s="15">
-        <v>-691.63636363636397</v>
+        <v>-1941.636363636364</v>
       </c>
       <c r="J37" s="16">
-        <v>1000</v>
+        <v>2756</v>
       </c>
       <c r="K37" s="13">
-        <v>1630</v>
+        <v>4492.28</v>
       </c>
       <c r="L37" s="14">
-        <v>9.0834021469859625</v>
+        <v>25.03385631709331</v>
       </c>
       <c r="M37" s="30">
         <v>2422</v>
       </c>
       <c r="N37" s="15">
-        <v>-100.90909090909099</v>
+        <v>1655.090909090909</v>
       </c>
       <c r="O37" s="16">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="P37" s="17">
-        <v>563.98</v>
+        <v>611.25</v>
       </c>
       <c r="Q37" s="14">
-        <v>7.4847590953785641</v>
+        <v>8.112094395280236</v>
       </c>
       <c r="R37" s="16">
         <v>1017</v>
       </c>
       <c r="S37" s="15">
-        <v>-347.40909090909088</v>
+        <v>-318.40909090909088</v>
       </c>
       <c r="T37" s="18">
-        <v>757</v>
+        <v>716</v>
       </c>
       <c r="U37" s="17">
-        <v>1233.9099999999999</v>
+        <v>1167.08</v>
       </c>
       <c r="V37" s="14">
-        <v>10.934996717005909</v>
+        <v>10.34274458305975</v>
       </c>
       <c r="W37" s="16">
         <v>1523</v>
       </c>
       <c r="X37" s="15">
-        <v>-281.40909090909099</v>
+        <v>-322.40909090909099</v>
       </c>
       <c r="Y37" s="18">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="Z37" s="17">
-        <v>376.53</v>
+        <v>286.88</v>
       </c>
       <c r="AA37" s="14">
         <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>352</v>
+        <v>301.71428571428572</v>
       </c>
       <c r="AC37" s="15">
-        <v>-9</v>
+        <v>-29.714285714285722</v>
       </c>
       <c r="AD37" s="19">
-        <v>4351</v>
+        <v>4790</v>
       </c>
       <c r="AE37" s="20">
-        <v>7092.1299999999992</v>
+        <v>7807.7</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5059,85 +5061,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>1903</v>
+        <v>1459</v>
       </c>
       <c r="F38" s="14">
-        <v>3101.89</v>
+        <v>2378.1699999999996</v>
       </c>
       <c r="G38" s="14">
-        <v>10.188853735702116</v>
+        <v>7.8116330007301045</v>
       </c>
       <c r="H38" s="30">
         <v>4109</v>
       </c>
       <c r="I38" s="15">
-        <v>35.272727272727252</v>
+        <v>-408.72727272727275</v>
       </c>
       <c r="J38" s="16">
-        <v>1000</v>
+        <v>2763</v>
       </c>
       <c r="K38" s="13">
-        <v>1630</v>
+        <v>4503.6899999999996</v>
       </c>
       <c r="L38" s="14">
-        <v>10.546500479386387</v>
+        <v>29.139980824544583</v>
       </c>
       <c r="M38" s="30">
         <v>2086</v>
       </c>
       <c r="N38" s="15">
-        <v>51.81818181818187</v>
+        <v>1814.818181818182</v>
       </c>
       <c r="O38" s="16">
-        <v>516</v>
+        <v>468</v>
       </c>
       <c r="P38" s="17">
-        <v>841.07999999999993</v>
+        <v>762.83999999999992</v>
       </c>
       <c r="Q38" s="14">
-        <v>15.11584553928096</v>
+        <v>13.70972037283622</v>
       </c>
       <c r="R38" s="16">
         <v>751</v>
       </c>
       <c r="S38" s="15">
-        <v>3.9545454545454959</v>
+        <v>-44.045454545454504</v>
       </c>
       <c r="T38" s="18">
-        <v>486</v>
+        <v>460</v>
       </c>
       <c r="U38" s="17">
-        <v>792.18</v>
+        <v>749.8</v>
       </c>
       <c r="V38" s="14">
-        <v>10.431219512195121</v>
+        <v>9.873170731707317</v>
       </c>
       <c r="W38" s="16">
         <v>1025</v>
       </c>
       <c r="X38" s="15">
-        <v>-212.86363636363637</v>
+        <v>-238.86363636363637</v>
       </c>
       <c r="Y38" s="18">
-        <v>493</v>
+        <v>455</v>
       </c>
       <c r="Z38" s="17">
-        <v>803.58999999999992</v>
+        <v>741.65</v>
       </c>
       <c r="AA38" s="14">
-        <v>15.326424870466322</v>
+        <v>16.502590673575131</v>
       </c>
       <c r="AB38" s="16">
-        <v>707.66666666666663</v>
+        <v>606.57142857142856</v>
       </c>
       <c r="AC38" s="15">
-        <v>10.500000000000057</v>
+        <v>41.428571428571445</v>
       </c>
       <c r="AD38" s="19">
-        <v>4398</v>
+        <v>5605</v>
       </c>
       <c r="AE38" s="20">
-        <v>7168.74</v>
+        <v>9136.15</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5172,85 +5174,85 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>679</v>
+        <v>1796</v>
       </c>
       <c r="F39" s="14">
-        <v>1106.77</v>
+        <v>2927.48</v>
       </c>
       <c r="G39" s="14">
-        <v>79.882352941176464</v>
+        <v>211.29411764705881</v>
       </c>
       <c r="H39" s="30">
         <v>187</v>
       </c>
       <c r="I39" s="15">
-        <v>594</v>
+        <v>1711</v>
       </c>
       <c r="J39" s="16">
-        <v>6550</v>
+        <v>6520</v>
       </c>
       <c r="K39" s="13">
-        <v>10676.5</v>
+        <v>10627.599999999999</v>
       </c>
       <c r="L39" s="14">
-        <v>176.59313725490199</v>
+        <v>175.78431372549022</v>
       </c>
       <c r="M39" s="30">
         <v>815.99999999999989</v>
       </c>
       <c r="N39" s="15">
-        <v>6179.090909090909</v>
+        <v>6149.090909090909</v>
       </c>
       <c r="O39" s="16">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="P39" s="17">
-        <v>873.68</v>
+        <v>850.8599999999999</v>
       </c>
       <c r="Q39" s="14">
-        <v>1072</v>
+        <v>1044</v>
       </c>
       <c r="R39" s="16">
         <v>11</v>
       </c>
       <c r="S39" s="15">
-        <v>528.5</v>
+        <v>514.5</v>
       </c>
       <c r="T39" s="18">
-        <v>107</v>
+        <v>415</v>
       </c>
       <c r="U39" s="17">
-        <v>174.41</v>
+        <v>676.44999999999993</v>
       </c>
       <c r="V39" s="14">
-        <v>4.3754646840148705</v>
+        <v>16.970260223048328</v>
       </c>
       <c r="W39" s="16">
         <v>538</v>
       </c>
       <c r="X39" s="15">
-        <v>-259.81818181818181</v>
+        <v>48.181818181818187</v>
       </c>
       <c r="Y39" s="18">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="Z39" s="17">
-        <v>819.89</v>
+        <v>795.43999999999994</v>
       </c>
       <c r="AA39" s="14">
-        <v>81.567567567567551</v>
+        <v>92.324324324324323</v>
       </c>
       <c r="AB39" s="16">
-        <v>135.66666666666669</v>
+        <v>116.28571428571428</v>
       </c>
       <c r="AC39" s="15">
-        <v>410.5</v>
+        <v>408.71428571428572</v>
       </c>
       <c r="AD39" s="19">
-        <v>8375</v>
+        <v>9741</v>
       </c>
       <c r="AE39" s="20">
-        <v>13651.25</v>
+        <v>15877.829999999998</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5285,85 +5287,85 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>561</v>
+        <v>1675</v>
       </c>
       <c r="F40" s="14">
-        <v>914.43</v>
+        <v>2730.25</v>
       </c>
       <c r="G40" s="14">
-        <v>66.713513513513519</v>
+        <v>199.18918918918922</v>
       </c>
       <c r="H40" s="30">
         <v>185</v>
       </c>
       <c r="I40" s="15">
-        <v>476.90909090909093</v>
+        <v>1590.909090909091</v>
       </c>
       <c r="J40" s="16">
-        <v>6674</v>
+        <v>6649</v>
       </c>
       <c r="K40" s="13">
-        <v>10878.619999999999</v>
+        <v>10837.869999999999</v>
       </c>
       <c r="L40" s="14">
-        <v>205.64145658263305</v>
+        <v>204.87114845938376</v>
       </c>
       <c r="M40" s="30">
         <v>714</v>
       </c>
       <c r="N40" s="15">
-        <v>6349.454545454546</v>
+        <v>6324.454545454546</v>
       </c>
       <c r="O40" s="16">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="P40" s="17">
-        <v>810.1099999999999</v>
+        <v>787.29</v>
       </c>
       <c r="Q40" s="14">
-        <v>994</v>
+        <v>966</v>
       </c>
       <c r="R40" s="16">
         <v>11</v>
       </c>
       <c r="S40" s="15">
-        <v>489.5</v>
+        <v>475.5</v>
       </c>
       <c r="T40" s="18">
-        <v>57</v>
+        <v>415</v>
       </c>
       <c r="U40" s="17">
-        <v>92.91</v>
+        <v>676.44999999999993</v>
       </c>
       <c r="V40" s="14">
-        <v>2.2273534635879217</v>
+        <v>16.21669626998224</v>
       </c>
       <c r="W40" s="16">
         <v>563</v>
       </c>
       <c r="X40" s="15">
-        <v>-326.86363636363637</v>
+        <v>31.136363636363626</v>
       </c>
       <c r="Y40" s="18">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="Z40" s="17">
-        <v>819.89</v>
+        <v>800.32999999999993</v>
       </c>
       <c r="AA40" s="14">
-        <v>70.186046511627893</v>
+        <v>79.930232558139537</v>
       </c>
       <c r="AB40" s="16">
-        <v>157.66666666666669</v>
+        <v>135.14285714285714</v>
       </c>
       <c r="AC40" s="15">
-        <v>395.5</v>
+        <v>398.85714285714289</v>
       </c>
       <c r="AD40" s="19">
-        <v>8292</v>
+        <v>9713</v>
       </c>
       <c r="AE40" s="20">
-        <v>13515.96</v>
+        <v>15832.189999999999</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5398,34 +5400,34 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>75</v>
+        <v>351</v>
       </c>
       <c r="F41" s="14">
-        <v>461.25</v>
+        <v>2158.65</v>
       </c>
       <c r="G41" s="14">
-        <v>1.2295081967213115</v>
+        <v>5.7540983606557381</v>
       </c>
       <c r="H41" s="30">
         <v>1342</v>
       </c>
       <c r="I41" s="15">
-        <v>-535</v>
+        <v>-259</v>
       </c>
       <c r="J41" s="16">
-        <v>662</v>
+        <v>327</v>
       </c>
       <c r="K41" s="13">
-        <v>4071.3</v>
+        <v>2011.0500000000002</v>
       </c>
       <c r="L41" s="14">
-        <v>18.388888888888889</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="M41" s="30">
         <v>792</v>
       </c>
       <c r="N41" s="15">
-        <v>302</v>
+        <v>-33</v>
       </c>
       <c r="O41" s="16">
         <v>70</v>
@@ -5443,40 +5445,40 @@
         <v>13.409090909090907</v>
       </c>
       <c r="T41" s="18">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="U41" s="17">
-        <v>707.25</v>
+        <v>1512.9</v>
       </c>
       <c r="V41" s="14">
-        <v>6.801075268817204</v>
+        <v>14.548387096774192</v>
       </c>
       <c r="W41" s="16">
         <v>372</v>
       </c>
       <c r="X41" s="15">
-        <v>-138.63636363636365</v>
+        <v>-7.6363636363636545</v>
       </c>
       <c r="Y41" s="18">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="Z41" s="17">
-        <v>528.9</v>
+        <v>492</v>
       </c>
       <c r="AA41" s="14">
         <v>0</v>
       </c>
       <c r="AB41" s="16">
-        <v>62.333333333333336</v>
+        <v>53.428571428571423</v>
       </c>
       <c r="AC41" s="15">
-        <v>43.5</v>
+        <v>43.571428571428577</v>
       </c>
       <c r="AD41" s="19">
-        <v>1008</v>
+        <v>1074</v>
       </c>
       <c r="AE41" s="20">
-        <v>6199.2000000000007</v>
+        <v>6605.1</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5511,85 +5513,85 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>99</v>
+        <v>364</v>
       </c>
       <c r="F42" s="14">
-        <v>608.85</v>
+        <v>2238.6</v>
       </c>
       <c r="G42" s="14">
-        <v>1.5424929178470255</v>
+        <v>5.6713881019830028</v>
       </c>
       <c r="H42" s="30">
         <v>1412</v>
       </c>
       <c r="I42" s="15">
-        <v>-542.81818181818187</v>
+        <v>-277.81818181818187</v>
       </c>
       <c r="J42" s="16">
-        <v>703</v>
+        <v>358</v>
       </c>
       <c r="K42" s="13">
-        <v>4323.45</v>
+        <v>2201.7000000000003</v>
       </c>
       <c r="L42" s="14">
-        <v>16.70194384449244</v>
+        <v>8.5053995680345569</v>
       </c>
       <c r="M42" s="30">
         <v>926</v>
       </c>
       <c r="N42" s="15">
-        <v>282.09090909090907</v>
+        <v>-62.909090909090935</v>
       </c>
       <c r="O42" s="16">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="P42" s="17">
-        <v>350.55</v>
+        <v>399.75</v>
       </c>
       <c r="Q42" s="14">
-        <v>15.481481481481483</v>
+        <v>17.654320987654323</v>
       </c>
       <c r="R42" s="16">
         <v>81</v>
       </c>
       <c r="S42" s="15">
-        <v>1.7727272727272734</v>
+        <v>9.7727272727272734</v>
       </c>
       <c r="T42" s="18">
-        <v>143</v>
+        <v>359</v>
       </c>
       <c r="U42" s="17">
-        <v>879.45</v>
+        <v>2207.85</v>
       </c>
       <c r="V42" s="14">
-        <v>5.9358490566037743</v>
+        <v>14.901886792452832</v>
       </c>
       <c r="W42" s="16">
         <v>530</v>
       </c>
       <c r="X42" s="15">
-        <v>-218.36363636363637</v>
+        <v>-2.363636363636374</v>
       </c>
       <c r="Y42" s="18">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="Z42" s="17">
-        <v>682.65000000000009</v>
+        <v>645.75</v>
       </c>
       <c r="AA42" s="14">
-        <v>17.076923076923077</v>
+        <v>18.846153846153847</v>
       </c>
       <c r="AB42" s="16">
-        <v>143</v>
+        <v>122.57142857142857</v>
       </c>
       <c r="AC42" s="15">
-        <v>13.5</v>
+        <v>21.428571428571431</v>
       </c>
       <c r="AD42" s="19">
-        <v>1113</v>
+        <v>1251</v>
       </c>
       <c r="AE42" s="20">
-        <v>6844.9500000000007</v>
+        <v>7693.6500000000005</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5624,85 +5626,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2017</v>
+        <v>2358</v>
       </c>
       <c r="F43" s="14">
-        <v>2339.7199999999998</v>
+        <v>2735.2799999999997</v>
       </c>
       <c r="G43" s="14">
-        <v>6.0119225037257822</v>
+        <v>7.0283159463487328</v>
       </c>
       <c r="H43" s="30">
         <v>7381</v>
       </c>
       <c r="I43" s="15">
-        <v>-1338</v>
+        <v>-997</v>
       </c>
       <c r="J43" s="16">
-        <v>3540</v>
+        <v>4565</v>
       </c>
       <c r="K43" s="13">
-        <v>4106.3999999999996</v>
+        <v>5295.4</v>
       </c>
       <c r="L43" s="14">
-        <v>28.371584699453553</v>
+        <v>36.586520947176687</v>
       </c>
       <c r="M43" s="30">
         <v>2745</v>
       </c>
       <c r="N43" s="15">
-        <v>2292.272727272727</v>
+        <v>3317.272727272727</v>
       </c>
       <c r="O43" s="16">
-        <v>465</v>
+        <v>370</v>
       </c>
       <c r="P43" s="17">
-        <v>539.4</v>
+        <v>429.2</v>
       </c>
       <c r="Q43" s="14">
-        <v>8.997361477572559</v>
+        <v>7.1591908531222517</v>
       </c>
       <c r="R43" s="16">
         <v>1137</v>
       </c>
       <c r="S43" s="15">
-        <v>-310.22727272727275</v>
+        <v>-405.22727272727275</v>
       </c>
       <c r="T43" s="18">
-        <v>950</v>
+        <v>1300</v>
       </c>
       <c r="U43" s="17">
-        <v>1102</v>
+        <v>1508</v>
       </c>
       <c r="V43" s="14">
-        <v>10.072289156626507</v>
+        <v>13.783132530120483</v>
       </c>
       <c r="W43" s="16">
         <v>2075</v>
       </c>
       <c r="X43" s="15">
-        <v>-464.77272727272725</v>
+        <v>-114.77272727272725</v>
       </c>
       <c r="Y43" s="18">
-        <v>411</v>
+        <v>383</v>
       </c>
       <c r="Z43" s="17">
-        <v>476.76</v>
+        <v>444.28</v>
       </c>
       <c r="AA43" s="14">
-        <v>11.311926605504587</v>
+        <v>12.29816513761468</v>
       </c>
       <c r="AB43" s="16">
-        <v>799.33333333333337</v>
+        <v>685.14285714285711</v>
       </c>
       <c r="AC43" s="15">
-        <v>-134</v>
+        <v>-84.14285714285711</v>
       </c>
       <c r="AD43" s="19">
-        <v>7383</v>
+        <v>8976</v>
       </c>
       <c r="AE43" s="20">
-        <v>8564.2799999999988</v>
+        <v>10412.16</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5737,85 +5739,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>1770</v>
+        <v>923</v>
       </c>
       <c r="F44" s="14">
-        <v>2053.1999999999998</v>
+        <v>1070.6799999999998</v>
       </c>
       <c r="G44" s="14">
-        <v>6.0484622553588077</v>
+        <v>3.1540851196023612</v>
       </c>
       <c r="H44" s="30">
         <v>6438</v>
       </c>
       <c r="I44" s="15">
-        <v>-1156.363636363636</v>
+        <v>-2003.363636363636</v>
       </c>
       <c r="J44" s="16">
-        <v>2004</v>
+        <v>4144</v>
       </c>
       <c r="K44" s="13">
-        <v>2324.64</v>
+        <v>4807.04</v>
       </c>
       <c r="L44" s="14">
-        <v>11.70063694267516</v>
+        <v>24.195329087048837</v>
       </c>
       <c r="M44" s="30">
         <v>3767.9999999999995</v>
       </c>
       <c r="N44" s="15">
-        <v>291.27272727272748</v>
+        <v>2431.2727272727275</v>
       </c>
       <c r="O44" s="16">
-        <v>468</v>
+        <v>411</v>
       </c>
       <c r="P44" s="17">
-        <v>542.88</v>
+        <v>476.76</v>
       </c>
       <c r="Q44" s="14">
-        <v>13.691489361702128</v>
+        <v>12.023936170212767</v>
       </c>
       <c r="R44" s="16">
         <v>752</v>
       </c>
       <c r="S44" s="15">
-        <v>-44.727272727272748</v>
+        <v>-101.72727272727275</v>
       </c>
       <c r="T44" s="18">
-        <v>994</v>
+        <v>1220</v>
       </c>
       <c r="U44" s="17">
-        <v>1153.04</v>
+        <v>1415.1999999999998</v>
       </c>
       <c r="V44" s="14">
-        <v>11.756989247311827</v>
+        <v>14.43010752688172</v>
       </c>
       <c r="W44" s="16">
         <v>1860</v>
       </c>
       <c r="X44" s="15">
-        <v>-274.18181818181824</v>
+        <v>-48.181818181818244</v>
       </c>
       <c r="Y44" s="18">
-        <v>522</v>
+        <v>493</v>
       </c>
       <c r="Z44" s="17">
-        <v>605.52</v>
+        <v>571.88</v>
       </c>
       <c r="AA44" s="14">
-        <v>16.659574468085108</v>
+        <v>18.356382978723403</v>
       </c>
       <c r="AB44" s="16">
-        <v>689.33333333333326</v>
+        <v>590.85714285714289</v>
       </c>
       <c r="AC44" s="15">
-        <v>52.000000000000057</v>
+        <v>90.14285714285711</v>
       </c>
       <c r="AD44" s="19">
-        <v>5758</v>
+        <v>7191</v>
       </c>
       <c r="AE44" s="20">
-        <v>6679.28</v>
+        <v>8341.56</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5850,85 +5852,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>2481</v>
+        <v>2150</v>
       </c>
       <c r="F45" s="14">
-        <v>2877.9599999999996</v>
+        <v>2494</v>
       </c>
       <c r="G45" s="14">
-        <v>6.4395941481831054</v>
+        <v>5.5804624823029734</v>
       </c>
       <c r="H45" s="30">
         <v>8476</v>
       </c>
       <c r="I45" s="15">
-        <v>-1371.7272727272725</v>
+        <v>-1702.7272727272725</v>
       </c>
       <c r="J45" s="16">
-        <v>2525</v>
+        <v>4297</v>
       </c>
       <c r="K45" s="13">
-        <v>2929</v>
+        <v>4984.5199999999995</v>
       </c>
       <c r="L45" s="14">
-        <v>10.271819526627219</v>
+        <v>17.480399408284025</v>
       </c>
       <c r="M45" s="30">
         <v>5408</v>
       </c>
       <c r="N45" s="15">
-        <v>66.818181818181984</v>
+        <v>1838.818181818182</v>
       </c>
       <c r="O45" s="16">
-        <v>750</v>
+        <v>686</v>
       </c>
       <c r="P45" s="17">
-        <v>869.99999999999989</v>
+        <v>795.76</v>
       </c>
       <c r="Q45" s="14">
-        <v>14.745308310991955</v>
+        <v>13.487042001787309</v>
       </c>
       <c r="R45" s="16">
         <v>1119</v>
       </c>
       <c r="S45" s="15">
-        <v>-12.954545454545496</v>
+        <v>-76.954545454545496</v>
       </c>
       <c r="T45" s="18">
-        <v>1175</v>
+        <v>1627</v>
       </c>
       <c r="U45" s="17">
-        <v>1363</v>
+        <v>1887.32</v>
       </c>
       <c r="V45" s="14">
-        <v>10.217391304347826</v>
+        <v>14.147826086956522</v>
       </c>
       <c r="W45" s="16">
         <v>2530</v>
       </c>
       <c r="X45" s="15">
-        <v>-550</v>
+        <v>-98</v>
       </c>
       <c r="Y45" s="18">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="Z45" s="17">
-        <v>505.76</v>
+        <v>455.88</v>
       </c>
       <c r="AA45" s="14">
-        <v>12.516746411483252</v>
+        <v>13.16267942583732</v>
       </c>
       <c r="AB45" s="16">
-        <v>766.33333333333337</v>
+        <v>656.85714285714289</v>
       </c>
       <c r="AC45" s="15">
-        <v>-86.5</v>
+        <v>-54.85714285714289</v>
       </c>
       <c r="AD45" s="19">
-        <v>7367</v>
+        <v>9153</v>
       </c>
       <c r="AE45" s="20">
-        <v>8545.7199999999993</v>
+        <v>10617.48</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5963,85 +5965,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>3333</v>
+        <v>2494</v>
       </c>
       <c r="F46" s="14">
-        <v>3866.2799999999997</v>
+        <v>2893.04</v>
       </c>
       <c r="G46" s="14">
-        <v>12.909507042253521</v>
+        <v>9.6598591549295776</v>
       </c>
       <c r="H46" s="30">
         <v>5680</v>
       </c>
       <c r="I46" s="15">
-        <v>751.18181818181802</v>
+        <v>-87.818181818181984</v>
       </c>
       <c r="J46" s="16">
-        <v>1784</v>
+        <v>4185</v>
       </c>
       <c r="K46" s="13">
-        <v>2069.44</v>
+        <v>4854.5999999999995</v>
       </c>
       <c r="L46" s="14">
-        <v>9.8861460957178835</v>
+        <v>23.191435768261965</v>
       </c>
       <c r="M46" s="30">
         <v>3970</v>
       </c>
       <c r="N46" s="15">
-        <v>-20.545454545454731</v>
+        <v>2380.454545454545</v>
       </c>
       <c r="O46" s="16">
-        <v>615</v>
+        <v>573</v>
       </c>
       <c r="P46" s="17">
-        <v>713.4</v>
+        <v>664.68</v>
       </c>
       <c r="Q46" s="14">
-        <v>16.459854014598537</v>
+        <v>15.335766423357663</v>
       </c>
       <c r="R46" s="16">
         <v>822.00000000000011</v>
       </c>
       <c r="S46" s="15">
-        <v>54.545454545454504</v>
+        <v>12.545454545454504</v>
       </c>
       <c r="T46" s="18">
-        <v>630</v>
+        <v>890</v>
       </c>
       <c r="U46" s="17">
-        <v>730.8</v>
+        <v>1032.3999999999999</v>
       </c>
       <c r="V46" s="14">
-        <v>11.141479099678456</v>
+        <v>15.739549839228296</v>
       </c>
       <c r="W46" s="16">
         <v>1244</v>
       </c>
       <c r="X46" s="15">
-        <v>-218.18181818181824</v>
+        <v>41.818181818181756</v>
       </c>
       <c r="Y46" s="18">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="Z46" s="17">
-        <v>418.76</v>
+        <v>400.2</v>
       </c>
       <c r="AA46" s="14">
-        <v>17.467741935483868</v>
+        <v>19.4758064516129</v>
       </c>
       <c r="AB46" s="16">
-        <v>454.66666666666669</v>
+        <v>389.71428571428572</v>
       </c>
       <c r="AC46" s="15">
-        <v>51</v>
+        <v>79.285714285714278</v>
       </c>
       <c r="AD46" s="19">
-        <v>6723</v>
+        <v>8487</v>
       </c>
       <c r="AE46" s="20">
-        <v>7798.6799999999994</v>
+        <v>9844.92</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6075,7 +6077,9 @@
       <c r="D47" s="12">
         <v>18</v>
       </c>
-      <c r="E47" s="13"/>
+      <c r="E47" s="13">
+        <v>0</v>
+      </c>
       <c r="F47" s="14">
         <v>0</v>
       </c>
@@ -6119,19 +6123,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U47" s="17">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="V47" s="14">
-        <v>11</v>
+        <v>12.1</v>
       </c>
       <c r="W47" s="16">
         <v>20</v>
       </c>
       <c r="X47" s="15">
-        <v>-3.6363636363636367</v>
+        <v>-2.6363636363636367</v>
       </c>
       <c r="Y47" s="18">
         <v>4</v>
@@ -6149,10 +6153,10 @@
         <v>4</v>
       </c>
       <c r="AD47" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE47" s="20">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6186,7 +6190,9 @@
       <c r="D48" s="12">
         <v>18</v>
       </c>
-      <c r="E48" s="13"/>
+      <c r="E48" s="13">
+        <v>0</v>
+      </c>
       <c r="F48" s="14">
         <v>0</v>
       </c>
@@ -6298,34 +6304,34 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>1017</v>
+        <v>1032</v>
       </c>
       <c r="F49" s="14">
-        <v>1179.72</v>
+        <v>1197.1199999999999</v>
       </c>
       <c r="G49" s="14">
-        <v>18.08730800323363</v>
+        <v>18.354082457558611</v>
       </c>
       <c r="H49" s="30">
         <v>1237</v>
       </c>
       <c r="I49" s="15">
-        <v>454.72727272727275</v>
+        <v>469.72727272727275</v>
       </c>
       <c r="J49" s="16">
-        <v>347</v>
+        <v>259</v>
       </c>
       <c r="K49" s="13">
-        <v>402.52</v>
+        <v>300.44</v>
       </c>
       <c r="L49" s="14">
-        <v>6.1914030819140304</v>
+        <v>4.6212489862124899</v>
       </c>
       <c r="M49" s="30">
         <v>1233</v>
       </c>
       <c r="N49" s="15">
-        <v>-213.4545454545455</v>
+        <v>-301.4545454545455</v>
       </c>
       <c r="O49" s="16">
         <v>39</v>
@@ -6343,40 +6349,40 @@
         <v>-37.36363636363636</v>
       </c>
       <c r="T49" s="18">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="U49" s="17">
-        <v>234.32</v>
+        <v>212.27999999999997</v>
       </c>
       <c r="V49" s="14">
-        <v>19.155172413793103</v>
+        <v>17.353448275862071</v>
       </c>
       <c r="W49" s="16">
         <v>232</v>
       </c>
       <c r="X49" s="15">
-        <v>43.818181818181813</v>
+        <v>24.818181818181813</v>
       </c>
       <c r="Y49" s="18">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="Z49" s="17">
-        <v>110.19999999999999</v>
+        <v>95.11999999999999</v>
       </c>
       <c r="AA49" s="14">
-        <v>14.249999999999998</v>
+        <v>14.35</v>
       </c>
       <c r="AB49" s="16">
-        <v>146.66666666666669</v>
+        <v>125.71428571428572</v>
       </c>
       <c r="AC49" s="15">
-        <v>-5.0000000000000142</v>
+        <v>-3.7142857142857224</v>
       </c>
       <c r="AD49" s="19">
-        <v>1700</v>
+        <v>1595</v>
       </c>
       <c r="AE49" s="20">
-        <v>1971.9999999999998</v>
+        <v>1850.1999999999998</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6411,49 +6417,49 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>2036</v>
+        <v>1325</v>
       </c>
       <c r="F50" s="14">
-        <v>2361.7599999999998</v>
+        <v>1537</v>
       </c>
       <c r="G50" s="14">
-        <v>7.9871611982881596</v>
+        <v>5.1979315263908701</v>
       </c>
       <c r="H50" s="30">
         <v>5608</v>
       </c>
       <c r="I50" s="15">
-        <v>-513.09090909090901</v>
+        <v>-1224.090909090909</v>
       </c>
       <c r="J50" s="16">
-        <v>1537</v>
+        <v>3138</v>
       </c>
       <c r="K50" s="13">
-        <v>1782.9199999999998</v>
+        <v>3640.08</v>
       </c>
       <c r="L50" s="14">
-        <v>9.4558165548098447</v>
+        <v>19.30536912751678</v>
       </c>
       <c r="M50" s="30">
         <v>3576</v>
       </c>
       <c r="N50" s="15">
-        <v>-88.454545454545269</v>
+        <v>1512.5454545454547</v>
       </c>
       <c r="O50" s="16">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="P50" s="17">
-        <v>392.08</v>
+        <v>366.56</v>
       </c>
       <c r="Q50" s="14">
-        <v>15.491666666666667</v>
+        <v>14.483333333333334</v>
       </c>
       <c r="R50" s="16">
         <v>480</v>
       </c>
       <c r="S50" s="15">
-        <v>10.727272727272748</v>
+        <v>-11.272727272727252</v>
       </c>
       <c r="T50" s="18">
         <v>0</v>
@@ -6471,25 +6477,25 @@
         <v>-1199.3181818181818</v>
       </c>
       <c r="Y50" s="18">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="Z50" s="17">
-        <v>193.72</v>
+        <v>170.51999999999998</v>
       </c>
       <c r="AA50" s="14">
-        <v>10.121212121212121</v>
+        <v>10.393939393939396</v>
       </c>
       <c r="AB50" s="16">
-        <v>363</v>
+        <v>311.14285714285711</v>
       </c>
       <c r="AC50" s="15">
-        <v>-80.5</v>
+        <v>-65.14285714285711</v>
       </c>
       <c r="AD50" s="19">
-        <v>4078</v>
+        <v>4926</v>
       </c>
       <c r="AE50" s="20">
-        <v>4730.4799999999996</v>
+        <v>5714.16</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6527,40 +6533,40 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>1047</v>
+        <v>691</v>
       </c>
       <c r="F51" s="14">
-        <v>1214.52</v>
+        <v>801.56</v>
       </c>
       <c r="G51" s="14">
-        <v>18.122738001573563</v>
+        <v>11.96066089693155</v>
       </c>
       <c r="H51" s="30">
         <v>1271</v>
       </c>
       <c r="I51" s="15">
-        <v>469.27272727272725</v>
+        <v>113.27272727272725</v>
       </c>
       <c r="J51" s="16">
-        <v>1900</v>
+        <v>3678</v>
       </c>
       <c r="K51" s="13">
-        <v>2204</v>
+        <v>4266.4799999999996</v>
       </c>
       <c r="L51" s="14">
-        <v>42.653061224489797</v>
+        <v>82.567346938775515</v>
       </c>
       <c r="M51" s="30">
         <v>980</v>
       </c>
       <c r="N51" s="15">
-        <v>1454.5454545454545</v>
+        <v>3232.5454545454545</v>
       </c>
       <c r="O51" s="16">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="P51" s="17">
-        <v>438.47999999999996</v>
+        <v>415.28</v>
       </c>
       <c r="Q51" s="14">
         <v>0</v>
@@ -6569,43 +6575,43 @@
         <v>0</v>
       </c>
       <c r="S51" s="15">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="T51" s="18">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="U51" s="17">
-        <v>277.24</v>
+        <v>242.43999999999997</v>
       </c>
       <c r="V51" s="14">
-        <v>9.7732342007434951</v>
+        <v>8.5464684014869885</v>
       </c>
       <c r="W51" s="16">
         <v>538</v>
       </c>
       <c r="X51" s="15">
-        <v>-127.81818181818181</v>
+        <v>-157.81818181818181</v>
       </c>
       <c r="Y51" s="18">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="Z51" s="17">
-        <v>179.79999999999998</v>
+        <v>157.76</v>
       </c>
       <c r="AA51" s="14">
         <v>0</v>
       </c>
       <c r="AB51" s="16">
-        <v>95.333333333333329</v>
+        <v>81.714285714285722</v>
       </c>
       <c r="AC51" s="15">
-        <v>90</v>
+        <v>80.285714285714278</v>
       </c>
       <c r="AD51" s="19">
-        <v>3719</v>
+        <v>5072</v>
       </c>
       <c r="AE51" s="20">
-        <v>4314.04</v>
+        <v>5883.5199999999995</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6644,19 +6650,19 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>4296</v>
+        <v>4320</v>
       </c>
       <c r="F52" s="14">
-        <v>3479.76</v>
+        <v>3499.2000000000003</v>
       </c>
       <c r="G52" s="14">
-        <v>35.718820861678005</v>
+        <v>35.91836734693878</v>
       </c>
       <c r="H52" s="30">
         <v>2646</v>
       </c>
       <c r="I52" s="15">
-        <v>3093.272727272727</v>
+        <v>3117.272727272727</v>
       </c>
       <c r="J52" s="16">
         <v>0</v>
@@ -6689,19 +6695,19 @@
         <v>-339.54545454545456</v>
       </c>
       <c r="T52" s="18">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="U52" s="17">
-        <v>74.52000000000001</v>
+        <v>64.800000000000011</v>
       </c>
       <c r="V52" s="14">
-        <v>2.2463928967813542</v>
+        <v>1.9533851276359602</v>
       </c>
       <c r="W52" s="16">
         <v>901</v>
       </c>
       <c r="X52" s="15">
-        <v>-522.31818181818176</v>
+        <v>-534.31818181818176</v>
       </c>
       <c r="Y52" s="18">
         <v>0</v>
@@ -6713,16 +6719,16 @@
         <v>0</v>
       </c>
       <c r="AB52" s="16">
-        <v>84.333333333333343</v>
+        <v>72.285714285714278</v>
       </c>
       <c r="AC52" s="15">
-        <v>-57.500000000000007</v>
+        <v>-49.285714285714278</v>
       </c>
       <c r="AD52" s="19">
-        <v>4388</v>
+        <v>4400</v>
       </c>
       <c r="AE52" s="20">
-        <v>3554.28</v>
+        <v>3564.0000000000005</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6757,85 +6763,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>2567</v>
+        <v>1914</v>
       </c>
       <c r="F53" s="14">
-        <v>2079.27</v>
+        <v>1550.3400000000001</v>
       </c>
       <c r="G53" s="14">
-        <v>10.997857838364167</v>
+        <v>8.2001947419668948</v>
       </c>
       <c r="H53" s="30">
         <v>5135</v>
       </c>
       <c r="I53" s="15">
-        <v>232.90909090909099</v>
+        <v>-420.09090909090901</v>
       </c>
       <c r="J53" s="16">
-        <v>4028</v>
+        <v>3861</v>
       </c>
       <c r="K53" s="13">
-        <v>3262.6800000000003</v>
+        <v>3127.4100000000003</v>
       </c>
       <c r="L53" s="14">
-        <v>27.910551181102356</v>
+        <v>26.753385826771648</v>
       </c>
       <c r="M53" s="30">
         <v>3175.0000000000005</v>
       </c>
       <c r="N53" s="15">
-        <v>2584.8181818181815</v>
+        <v>2417.8181818181815</v>
       </c>
       <c r="O53" s="16">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="P53" s="17">
-        <v>299.70000000000005</v>
+        <v>272.16000000000003</v>
       </c>
       <c r="Q53" s="14">
-        <v>9.2185730464326152</v>
+        <v>8.3714609286523203</v>
       </c>
       <c r="R53" s="16">
         <v>883.00000000000011</v>
       </c>
       <c r="S53" s="15">
-        <v>-232.04545454545462</v>
+        <v>-266.04545454545462</v>
       </c>
       <c r="T53" s="18">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="U53" s="17">
-        <v>0</v>
+        <v>583.20000000000005</v>
       </c>
       <c r="V53" s="14">
-        <v>0</v>
+        <v>9.5941853422168375</v>
       </c>
       <c r="W53" s="16">
         <v>1651</v>
       </c>
       <c r="X53" s="15">
-        <v>-1125.6818181818182</v>
+        <v>-405.68181818181824</v>
       </c>
       <c r="Y53" s="18">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="Z53" s="17">
-        <v>72.900000000000006</v>
+        <v>68.040000000000006</v>
       </c>
       <c r="AA53" s="14">
-        <v>15.428571428571432</v>
+        <v>16.8</v>
       </c>
       <c r="AB53" s="16">
-        <v>128.33333333333331</v>
+        <v>110</v>
       </c>
       <c r="AC53" s="15">
-        <v>2.5000000000000142</v>
+        <v>9</v>
       </c>
       <c r="AD53" s="19">
-        <v>7055</v>
+        <v>6915</v>
       </c>
       <c r="AE53" s="20">
-        <v>5714.55</v>
+        <v>5601.1500000000005</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6870,85 +6876,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>3122</v>
+        <v>1985</v>
       </c>
       <c r="F54" s="14">
-        <v>2528.8200000000002</v>
+        <v>1607.8500000000001</v>
       </c>
       <c r="G54" s="14">
-        <v>19.954677513073793</v>
+        <v>12.687391051714119</v>
       </c>
       <c r="H54" s="30">
         <v>3442</v>
       </c>
       <c r="I54" s="15">
-        <v>1557.4545454545453</v>
+        <v>420.45454545454527</v>
       </c>
       <c r="J54" s="16">
-        <v>6163</v>
+        <v>6136</v>
       </c>
       <c r="K54" s="13">
-        <v>4992.0300000000007</v>
+        <v>4970.1600000000008</v>
       </c>
       <c r="L54" s="14">
-        <v>77.655211912943869</v>
+        <v>77.315005727376871</v>
       </c>
       <c r="M54" s="30">
         <v>1746</v>
       </c>
       <c r="N54" s="15">
-        <v>5369.363636363636</v>
+        <v>5342.363636363636</v>
       </c>
       <c r="O54" s="16">
-        <v>344</v>
+        <v>269</v>
       </c>
       <c r="P54" s="17">
-        <v>278.64000000000004</v>
+        <v>217.89000000000001</v>
       </c>
       <c r="Q54" s="14">
-        <v>22.128654970760234</v>
+        <v>17.304093567251464</v>
       </c>
       <c r="R54" s="16">
         <v>342</v>
       </c>
       <c r="S54" s="15">
-        <v>110.81818181818181</v>
+        <v>35.818181818181813</v>
       </c>
       <c r="T54" s="18">
-        <v>831</v>
+        <v>807</v>
       </c>
       <c r="U54" s="17">
-        <v>673.11</v>
+        <v>653.67000000000007</v>
       </c>
       <c r="V54" s="14">
-        <v>29.582524271844662</v>
+        <v>28.728155339805827</v>
       </c>
       <c r="W54" s="16">
         <v>618</v>
       </c>
       <c r="X54" s="15">
-        <v>409.63636363636363</v>
+        <v>385.63636363636363</v>
       </c>
       <c r="Y54" s="18">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="Z54" s="17">
-        <v>157.14000000000001</v>
+        <v>152.28</v>
       </c>
       <c r="AA54" s="14">
-        <v>17.373134328358208</v>
+        <v>19.64179104477612</v>
       </c>
       <c r="AB54" s="16">
-        <v>245.66666666666666</v>
+        <v>210.57142857142856</v>
       </c>
       <c r="AC54" s="15">
-        <v>26.5</v>
+        <v>44.428571428571445</v>
       </c>
       <c r="AD54" s="19">
-        <v>10654</v>
+        <v>9385</v>
       </c>
       <c r="AE54" s="20">
-        <v>8629.74</v>
+        <v>7601.85</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -6983,85 +6989,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>5236</v>
+        <v>5048</v>
       </c>
       <c r="F55" s="14">
-        <v>4241.16</v>
+        <v>4088.88</v>
       </c>
       <c r="G55" s="14">
-        <v>42.287812041116005</v>
+        <v>40.76945668135096</v>
       </c>
       <c r="H55" s="30">
         <v>2724</v>
       </c>
       <c r="I55" s="15">
-        <v>3997.818181818182</v>
+        <v>3809.818181818182</v>
       </c>
       <c r="J55" s="16">
-        <v>8045</v>
+        <v>8007</v>
       </c>
       <c r="K55" s="13">
-        <v>6516.4500000000007</v>
+        <v>6485.67</v>
       </c>
       <c r="L55" s="14">
-        <v>90.531969309462909</v>
+        <v>90.104347826086951</v>
       </c>
       <c r="M55" s="30">
         <v>1955.0000000000002</v>
       </c>
       <c r="N55" s="15">
-        <v>7156.363636363636</v>
+        <v>7118.363636363636</v>
       </c>
       <c r="O55" s="16">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="P55" s="17">
-        <v>250.29000000000002</v>
+        <v>246.24</v>
       </c>
       <c r="Q55" s="14">
-        <v>15.106666666666667</v>
+        <v>14.862222222222224</v>
       </c>
       <c r="R55" s="16">
         <v>449.99999999999994</v>
       </c>
       <c r="S55" s="15">
-        <v>2.181818181818187</v>
+        <v>-2.818181818181813</v>
       </c>
       <c r="T55" s="18">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="U55" s="17">
-        <v>357.21000000000004</v>
+        <v>353.97</v>
       </c>
       <c r="V55" s="14">
-        <v>13.684062059238364</v>
+        <v>13.559943582510579</v>
       </c>
       <c r="W55" s="16">
         <v>709</v>
       </c>
       <c r="X55" s="15">
-        <v>-42.409090909090878</v>
+        <v>-46.409090909090878</v>
       </c>
       <c r="Y55" s="18">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="Z55" s="17">
-        <v>170.91000000000003</v>
+        <v>161.19</v>
       </c>
       <c r="AA55" s="14">
-        <v>18.895522388059703</v>
+        <v>20.791044776119403</v>
       </c>
       <c r="AB55" s="16">
-        <v>245.66666666666666</v>
+        <v>210.57142857142856</v>
       </c>
       <c r="AC55" s="15">
-        <v>43.5</v>
+        <v>55.428571428571445</v>
       </c>
       <c r="AD55" s="19">
-        <v>14242</v>
+        <v>13995</v>
       </c>
       <c r="AE55" s="20">
-        <v>11536.02</v>
+        <v>11335.95</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7096,64 +7102,64 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="F56" s="14">
-        <v>351.08000000000004</v>
+        <v>314.40000000000003</v>
       </c>
       <c r="G56" s="14">
-        <v>5.9078156312625243</v>
+        <v>5.2905811623246493</v>
       </c>
       <c r="H56" s="30">
         <v>499</v>
       </c>
       <c r="I56" s="15">
-        <v>-92.818181818181841</v>
+        <v>-106.81818181818184</v>
       </c>
       <c r="J56" s="32">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="K56" s="13">
-        <v>1228.78</v>
+        <v>1192.1000000000001</v>
       </c>
       <c r="L56" s="14">
-        <v>23.186516853932584</v>
+        <v>22.49438202247191</v>
       </c>
       <c r="M56" s="30">
         <v>445</v>
       </c>
       <c r="N56" s="15">
-        <v>266.72727272727275</v>
+        <v>252.72727272727275</v>
       </c>
       <c r="O56" s="32">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="P56" s="17">
-        <v>73.36</v>
+        <v>57.64</v>
       </c>
       <c r="Q56" s="14">
-        <v>20.533333333333335</v>
+        <v>16.133333333333333</v>
       </c>
       <c r="R56" s="16">
         <v>30</v>
       </c>
       <c r="S56" s="15">
-        <v>7.5454545454545467</v>
+        <v>1.5454545454545467</v>
       </c>
       <c r="T56" s="18">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="U56" s="17">
-        <v>73.36</v>
+        <v>196.5</v>
       </c>
       <c r="V56" s="14">
-        <v>3.2765957446808511</v>
+        <v>8.7765957446808507</v>
       </c>
       <c r="W56" s="16">
         <v>188</v>
       </c>
       <c r="X56" s="15">
-        <v>-100.18181818181819</v>
+        <v>-53.181818181818187</v>
       </c>
       <c r="Y56" s="18">
         <v>64</v>
@@ -7162,19 +7168,19 @@
         <v>167.68</v>
       </c>
       <c r="AA56" s="14">
-        <v>32</v>
+        <v>37.333333333333329</v>
       </c>
       <c r="AB56" s="16">
-        <v>44</v>
+        <v>37.714285714285715</v>
       </c>
       <c r="AC56" s="15">
-        <v>34</v>
+        <v>38.285714285714285</v>
       </c>
       <c r="AD56" s="19">
-        <v>723</v>
+        <v>736</v>
       </c>
       <c r="AE56" s="20">
-        <v>1894.26</v>
+        <v>1928.3200000000002</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7209,34 +7215,34 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F57" s="14">
-        <v>115.28</v>
+        <v>20.96</v>
       </c>
       <c r="G57" s="14">
-        <v>1.0649064906490648</v>
+        <v>0.19361936193619361</v>
       </c>
       <c r="H57" s="30">
         <v>909</v>
       </c>
       <c r="I57" s="15">
-        <v>-369.18181818181819</v>
+        <v>-405.18181818181819</v>
       </c>
       <c r="J57" s="32">
-        <v>235</v>
+        <v>149</v>
       </c>
       <c r="K57" s="13">
-        <v>615.70000000000005</v>
+        <v>390.38</v>
       </c>
       <c r="L57" s="14">
-        <v>6.0116279069767451</v>
+        <v>3.8116279069767445</v>
       </c>
       <c r="M57" s="30">
         <v>859.99999999999989</v>
       </c>
       <c r="N57" s="15">
-        <v>-155.90909090909088</v>
+        <v>-241.90909090909088</v>
       </c>
       <c r="O57" s="32">
         <v>53</v>
@@ -7254,19 +7260,19 @@
         <v>5.9545454545454533</v>
       </c>
       <c r="T57" s="18">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="U57" s="17">
-        <v>55.02</v>
+        <v>510.90000000000003</v>
       </c>
       <c r="V57" s="14">
-        <v>1.4951456310679612</v>
+        <v>13.883495145631068</v>
       </c>
       <c r="W57" s="16">
         <v>309</v>
       </c>
       <c r="X57" s="15">
-        <v>-189.68181818181819</v>
+        <v>-15.681818181818187</v>
       </c>
       <c r="Y57" s="18">
         <v>80</v>
@@ -7275,19 +7281,19 @@
         <v>209.60000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>40</v>
+        <v>46.666666666666664</v>
       </c>
       <c r="AB57" s="16">
-        <v>44</v>
+        <v>37.714285714285715</v>
       </c>
       <c r="AC57" s="15">
-        <v>50</v>
+        <v>54.285714285714285</v>
       </c>
       <c r="AD57" s="19">
-        <v>433</v>
+        <v>485</v>
       </c>
       <c r="AE57" s="20">
-        <v>1134.46</v>
+        <v>1270.7</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7322,34 +7328,34 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>371</v>
+        <v>147</v>
       </c>
       <c r="F58" s="14">
-        <v>972.0200000000001</v>
+        <v>385.14000000000004</v>
       </c>
       <c r="G58" s="14">
-        <v>19.341232227488149</v>
+        <v>7.6635071090047386</v>
       </c>
       <c r="H58" s="30">
         <v>422</v>
       </c>
       <c r="I58" s="15">
-        <v>179.18181818181816</v>
+        <v>-44.818181818181841</v>
       </c>
       <c r="J58" s="32">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K58" s="13">
-        <v>47.160000000000004</v>
+        <v>31.44</v>
       </c>
       <c r="L58" s="14">
-        <v>0.97297297297297303</v>
+        <v>0.64864864864864868</v>
       </c>
       <c r="M58" s="30">
         <v>407</v>
       </c>
       <c r="N58" s="15">
-        <v>-167</v>
+        <v>-173</v>
       </c>
       <c r="O58" s="32">
         <v>45</v>
@@ -7388,19 +7394,19 @@
         <v>141.48000000000002</v>
       </c>
       <c r="AA58" s="14">
-        <v>15.428571428571429</v>
+        <v>18</v>
       </c>
       <c r="AB58" s="16">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AC58" s="15">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="AD58" s="19">
-        <v>555</v>
+        <v>325</v>
       </c>
       <c r="AE58" s="20">
-        <v>1454.1000000000001</v>
+        <v>851.5</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7438,34 +7444,34 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="F59" s="14">
-        <v>110.04</v>
+        <v>57.64</v>
       </c>
       <c r="G59" s="14">
-        <v>1.8153241650294696</v>
+        <v>0.95088408644400779</v>
       </c>
       <c r="H59" s="30">
         <v>509</v>
       </c>
       <c r="I59" s="15">
-        <v>-189.36363636363637</v>
+        <v>-209.36363636363637</v>
       </c>
       <c r="J59" s="32">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="K59" s="13">
-        <v>277.72000000000003</v>
+        <v>227.94</v>
       </c>
       <c r="L59" s="14">
-        <v>5.7722772277227721</v>
+        <v>4.7376237623762378</v>
       </c>
       <c r="M59" s="30">
         <v>404</v>
       </c>
       <c r="N59" s="15">
-        <v>-77.636363636363626</v>
+        <v>-96.636363636363626</v>
       </c>
       <c r="O59" s="32">
         <v>14</v>
@@ -7483,19 +7489,19 @@
         <v>-3.7272727272727266</v>
       </c>
       <c r="T59" s="18">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="U59" s="17">
-        <v>162.44</v>
+        <v>322.26</v>
       </c>
       <c r="V59" s="14">
-        <v>6.994871794871794</v>
+        <v>13.876923076923074</v>
       </c>
       <c r="W59" s="16">
         <v>195.00000000000003</v>
       </c>
       <c r="X59" s="15">
-        <v>-70.954545454545467</v>
+        <v>-9.9545454545454675</v>
       </c>
       <c r="Y59" s="18">
         <v>56</v>
@@ -7504,19 +7510,19 @@
         <v>146.72</v>
       </c>
       <c r="AA59" s="14">
-        <v>28</v>
+        <v>32.666666666666664</v>
       </c>
       <c r="AB59" s="16">
-        <v>44</v>
+        <v>37.714285714285715</v>
       </c>
       <c r="AC59" s="15">
-        <v>26</v>
+        <v>30.285714285714285</v>
       </c>
       <c r="AD59" s="19">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="AE59" s="20">
-        <v>733.6</v>
+        <v>791.24</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7590,10 +7596,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="67"/>
+      <c r="F61" s="69"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7623,17 +7629,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="68" t="s">
+      <c r="B62" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="68"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>133317.40000000002</v>
+        <v>119111.75999999997</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>32.803994035521136</v>
+        <v>28.588151863414243</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7671,11 +7677,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>189968.68000000002</v>
+        <v>194005.48000000004</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>46.743571699236732</v>
+        <v>46.563480588101271</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7713,11 +7719,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>25089.990000000009</v>
+        <v>24037.210000000006</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>6.1736268657450948</v>
+        <v>5.7691986908159185</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7755,11 +7761,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>37560.999999999993</v>
+        <v>60211.55</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>9.242235596915398</v>
+        <v>14.451444049954098</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7797,11 +7803,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>20336.129999999994</v>
+        <v>19148.489999999998</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>5.0038951196586652</v>
+        <v>4.5958513254700391</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7833,19 +7839,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="68" t="s">
+      <c r="B67" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="68"/>
+      <c r="C67" s="65"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>406406</v>
-      </c>
-      <c r="E67" s="69">
+        <v>416647.29000000004</v>
+      </c>
+      <c r="E67" s="66">
         <f>D67*100/D67</f>
-        <v>100</v>
-      </c>
-      <c r="F67" s="69"/>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="F67" s="66"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7945,17 +7951,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="68"/>
+      <c r="C70" s="65"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>108721</v>
+        <v>94843</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>35.380930530741622</v>
+        <v>30.346943803615023</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -7992,11 +7998,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>139311</v>
+        <v>147189</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>45.335793574085464</v>
+        <v>47.096109481040159</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8034,11 +8040,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>18661</v>
+        <v>17778</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>6.0728244279777535</v>
+        <v>5.688432113499867</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8076,11 +8082,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>27016</v>
+        <v>40004</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>8.7917809734873256</v>
+        <v>12.800092151448345</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8118,11 +8124,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>13578</v>
+        <v>12715</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>4.4186704937078369</v>
+        <v>4.0684224503966036</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8154,19 +8160,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="68" t="s">
+      <c r="B75" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="68"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>307287</v>
-      </c>
-      <c r="E75" s="69">
+        <v>312529</v>
+      </c>
+      <c r="E75" s="66">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="69"/>
+      <c r="F75" s="66"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8713,17 +8719,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8732,6 +8727,17 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">
